--- a/backend/Rwanda/financial-statements-CleanStep.xlsx
+++ b/backend/Rwanda/financial-statements-CleanStep.xlsx
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="D36" s="23" t="n">
-        <v>0</v>
+        <v>-1119.972</v>
       </c>
       <c r="E36" s="23" t="n">
         <v>-1120.2464</v>
@@ -2573,7 +2573,7 @@
         </is>
       </c>
       <c r="D38" s="23" t="n">
-        <v>3999.9</v>
+        <v>2879.928</v>
       </c>
       <c r="E38" s="23" t="n">
         <v>2880.6336</v>
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="D39" s="23" t="n">
-        <v>0.9999750000000001</v>
+        <v>0.719982</v>
       </c>
       <c r="E39" s="23" t="n">
         <v>0.7199784053986503</v>
@@ -2964,10 +2964,10 @@
         <v>0</v>
       </c>
       <c r="J45" s="22" t="n">
-        <v>0</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="K45" s="22" t="n">
-        <v>0</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="L45" s="22" t="n">
         <v>0</v>
@@ -3002,37 +3002,37 @@
         <v>0</v>
       </c>
       <c r="E46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="F46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="G46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="J46" s="22" t="n">
-        <v>2023</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="K46" s="22" t="n">
-        <v>2023</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="L46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="M46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="N46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="O46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" ht="15.5" customHeight="1">
@@ -3282,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="J51" s="22" t="n">
-        <v>0</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="K51" s="22" t="n">
-        <v>0</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="L51" s="22" t="n">
         <v>0</v>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="D52" s="22" t="n">
-        <v>3999.9</v>
+        <v>2879.928</v>
       </c>
       <c r="E52" s="22" t="n">
         <v>2880.6336</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="D55" s="22" t="n">
-        <v>3999.9</v>
+        <v>2879.928</v>
       </c>
       <c r="E55" s="22" t="n">
         <v>2880.6336</v>
@@ -4112,7 +4112,7 @@
         </is>
       </c>
       <c r="D67" s="22" t="n">
-        <v>3999.9</v>
+        <v>2879.928</v>
       </c>
       <c r="E67" s="22" t="n">
         <v>2880.6336</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="D71" s="22" t="n">
-        <v>0</v>
+        <v>-1119.972</v>
       </c>
       <c r="E71" s="22" t="n">
         <v>-1120.2464</v>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="D73" s="22" t="n">
-        <v>3999.9</v>
+        <v>2879.928</v>
       </c>
       <c r="E73" s="22" t="n">
         <v>2880.6336</v>
@@ -4591,7 +4591,7 @@
         </is>
       </c>
       <c r="D76" s="22" t="n">
-        <v>3999.9</v>
+        <v>2879.928</v>
       </c>
       <c r="E76" s="22" t="n">
         <v>2880.6336</v>
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="D78" s="22" t="n">
-        <v>0</v>
+        <v>2023</v>
       </c>
       <c r="E78" s="22" t="n">
         <v>2024</v>
@@ -4856,40 +4856,40 @@
         </is>
       </c>
       <c r="D81" s="22" t="n">
-        <v>-6022.9</v>
+        <v>-4902.928</v>
       </c>
       <c r="E81" s="22" t="n">
-        <v>-4001.88</v>
+        <v>-4904.6336</v>
       </c>
       <c r="F81" s="22" t="n">
-        <v>-4003.86</v>
+        <v>-4906.3392</v>
       </c>
       <c r="G81" s="22" t="n">
-        <v>-4005.84</v>
+        <v>-4908.0448</v>
       </c>
       <c r="H81" s="22" t="n">
-        <v>-4007.82</v>
+        <v>-4909.7504</v>
       </c>
       <c r="I81" s="22" t="n">
-        <v>-4009.8</v>
+        <v>-4911.456</v>
       </c>
       <c r="J81" s="22" t="n">
-        <v>-4011.78</v>
+        <v>-4913.161599999999</v>
       </c>
       <c r="K81" s="22" t="n">
-        <v>-4013.76</v>
+        <v>-4914.867200000001</v>
       </c>
       <c r="L81" s="22" t="n">
-        <v>-4015.74</v>
+        <v>-4916.5728</v>
       </c>
       <c r="M81" s="22" t="n">
-        <v>-4017.72</v>
+        <v>-4918.2784</v>
       </c>
       <c r="N81" s="22" t="n">
-        <v>-4019.7</v>
+        <v>-4919.984</v>
       </c>
       <c r="O81" s="22" t="n">
-        <v>-4021.68</v>
+        <v>-4921.6896</v>
       </c>
     </row>
     <row r="82" ht="15.5" customHeight="1">
@@ -4962,40 +4962,40 @@
         </is>
       </c>
       <c r="D83" s="22" t="n">
-        <v>-6022.9</v>
+        <v>-2879.928</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>-3999.88</v>
+        <v>-2880.6336</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>-3999.860000000001</v>
+        <v>-2881.3392</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>-3999.84</v>
+        <v>-2882.0448</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>-3999.82</v>
+        <v>-2882.7504</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>-3999.8</v>
+        <v>-2883.456</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>-3999.780000000001</v>
+        <v>-2884.161599999999</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>-3999.76</v>
+        <v>-2884.867200000001</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>-3999.74</v>
+        <v>-2885.5728</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>-3999.719999999999</v>
+        <v>-2886.2784</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>-3999.7</v>
+        <v>-2886.984</v>
       </c>
       <c r="O83" s="22" t="n">
-        <v>-3999.68</v>
+        <v>-2887.6896</v>
       </c>
     </row>
     <row r="84" ht="15.5" customHeight="1">
@@ -5015,40 +5015,40 @@
         </is>
       </c>
       <c r="D84" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="E84" s="22" t="n">
-        <v>-3143.2464</v>
+        <v>0</v>
       </c>
       <c r="F84" s="22" t="n">
-        <v>-3143.520800000001</v>
+        <v>0</v>
       </c>
       <c r="G84" s="22" t="n">
-        <v>-3143.7952</v>
+        <v>0</v>
       </c>
       <c r="H84" s="22" t="n">
-        <v>-3144.0696</v>
+        <v>0</v>
       </c>
       <c r="I84" s="22" t="n">
-        <v>-3144.344</v>
+        <v>0</v>
       </c>
       <c r="J84" s="22" t="n">
-        <v>-3144.618400000001</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="K84" s="22" t="n">
-        <v>-3144.8928</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="L84" s="22" t="n">
-        <v>-3145.1672</v>
+        <v>0</v>
       </c>
       <c r="M84" s="22" t="n">
-        <v>-3145.441599999999</v>
+        <v>0</v>
       </c>
       <c r="N84" s="22" t="n">
-        <v>-3145.716</v>
+        <v>0</v>
       </c>
       <c r="O84" s="22" t="n">
-        <v>-3145.9904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" ht="15.5" customHeight="1">
@@ -5121,40 +5121,40 @@
         </is>
       </c>
       <c r="D86" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="E86" s="22" t="n">
-        <v>901.7536</v>
+        <v>0</v>
       </c>
       <c r="F86" s="22" t="n">
-        <v>900.4792</v>
+        <v>0</v>
       </c>
       <c r="G86" s="22" t="n">
-        <v>899.2048000000002</v>
+        <v>0</v>
       </c>
       <c r="H86" s="22" t="n">
-        <v>897.9304</v>
+        <v>0</v>
       </c>
       <c r="I86" s="22" t="n">
-        <v>896.6560000000002</v>
+        <v>0</v>
       </c>
       <c r="J86" s="22" t="n">
-        <v>895.3815999999999</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="K86" s="22" t="n">
-        <v>894.1072000000001</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="L86" s="22" t="n">
-        <v>892.8327999999999</v>
+        <v>0</v>
       </c>
       <c r="M86" s="22" t="n">
-        <v>891.5584000000001</v>
+        <v>0</v>
       </c>
       <c r="N86" s="22" t="n">
-        <v>890.2839999999999</v>
+        <v>0</v>
       </c>
       <c r="O86" s="22" t="n">
-        <v>889.0096000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" ht="15.5" customHeight="1">
@@ -5174,40 +5174,40 @@
         </is>
       </c>
       <c r="D87" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>901.7536</v>
+        <v>0</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>900.4792</v>
+        <v>0</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>899.2048000000002</v>
+        <v>0</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>897.9304</v>
+        <v>0</v>
       </c>
       <c r="I87" s="22" t="n">
-        <v>896.6560000000002</v>
+        <v>0</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>895.3815999999999</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>894.1072000000001</v>
+        <v>-9.094947017729282e-13</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>892.8327999999999</v>
+        <v>0</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>891.5584000000001</v>
+        <v>0</v>
       </c>
       <c r="N87" s="22" t="n">
-        <v>890.2839999999999</v>
+        <v>0</v>
       </c>
       <c r="O87" s="22" t="n">
-        <v>889.0096000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" ht="15.5" customHeight="1">
@@ -6214,37 +6214,37 @@
         <v>0</v>
       </c>
       <c r="E106" s="24" t="n">
-        <v>10022.8</v>
+        <v>7782.856</v>
       </c>
       <c r="F106" s="24" t="n">
-        <v>16904.3136</v>
+        <v>15568.1232</v>
       </c>
       <c r="G106" s="24" t="n">
-        <v>24908.7592</v>
+        <v>23355.8016</v>
       </c>
       <c r="H106" s="24" t="n">
-        <v>32916.1648</v>
+        <v>31145.8912</v>
       </c>
       <c r="I106" s="24" t="n">
-        <v>40926.5304</v>
+        <v>38938.392</v>
       </c>
       <c r="J106" s="24" t="n">
-        <v>46699.6376</v>
+        <v>45830.276</v>
       </c>
       <c r="K106" s="24" t="n">
-        <v>53378.184</v>
+        <v>54747.57120000001</v>
       </c>
       <c r="L106" s="24" t="n">
-        <v>63201.11359999999</v>
+        <v>60524.30560000001</v>
       </c>
       <c r="M106" s="24" t="n">
-        <v>68979.4544</v>
+        <v>70349.45120000001</v>
       </c>
       <c r="N106" s="24" t="n">
-        <v>74759.2064</v>
+        <v>77250.25440000001</v>
       </c>
       <c r="O106" s="24" t="n">
-        <v>80540.36959999998</v>
+        <v>85273.9896</v>
       </c>
     </row>
     <row r="107" ht="15.5" customHeight="1">
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="D108" s="24" t="n">
-        <v>3999.9</v>
+        <v>2879.928</v>
       </c>
       <c r="E108" s="25" t="n">
         <v>2880.6336</v>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="D109" s="24" t="n">
-        <v>3999.9</v>
+        <v>4902.928</v>
       </c>
       <c r="E109" s="24" t="n">
         <v>4904.6336</v>
@@ -6445,40 +6445,40 @@
         </is>
       </c>
       <c r="D110" s="24" t="n">
-        <v>10022.8</v>
+        <v>7782.856</v>
       </c>
       <c r="E110" s="24" t="n">
-        <v>14882.3136</v>
+        <v>15568.1232</v>
       </c>
       <c r="F110" s="24" t="n">
-        <v>24910.7592</v>
+        <v>23355.8016</v>
       </c>
       <c r="G110" s="24" t="n">
-        <v>32919.1648</v>
+        <v>31145.8912</v>
       </c>
       <c r="H110" s="24" t="n">
-        <v>40930.5304</v>
+        <v>38938.392</v>
       </c>
       <c r="I110" s="24" t="n">
-        <v>46704.6376</v>
+        <v>44710.304</v>
       </c>
       <c r="J110" s="24" t="n">
-        <v>51361.184</v>
+        <v>53626.5992</v>
       </c>
       <c r="K110" s="24" t="n">
-        <v>61185.11359999999</v>
+        <v>60522.30560000001</v>
       </c>
       <c r="L110" s="24" t="n">
-        <v>66964.4544</v>
+        <v>70346.45120000001</v>
       </c>
       <c r="M110" s="24" t="n">
-        <v>72745.2064</v>
+        <v>75224.25440000001</v>
       </c>
       <c r="N110" s="24" t="n">
-        <v>78527.36959999998</v>
+        <v>85270.9896</v>
       </c>
       <c r="O110" s="24" t="n">
-        <v>84310.94400000002</v>
+        <v>93297.68479999999</v>
       </c>
     </row>
     <row r="111" ht="15.5" customHeight="1">
@@ -9108,7 +9108,7 @@
         </is>
       </c>
       <c r="D36" s="23" t="n">
-        <v>0</v>
+        <v>-1119.986</v>
       </c>
       <c r="E36" s="23" t="n">
         <v>-1120.2632</v>
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="D38" s="23" t="n">
-        <v>3999.95</v>
+        <v>2879.964</v>
       </c>
       <c r="E38" s="23" t="n">
         <v>2880.6768</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="D39" s="23" t="n">
-        <v>0.9999874999999999</v>
+        <v>0.7199909999999999</v>
       </c>
       <c r="E39" s="23" t="n">
         <v>0.7199892026993252</v>
@@ -9614,10 +9614,10 @@
         <v>90</v>
       </c>
       <c r="M45" s="22" t="n">
-        <v>65</v>
+        <v>65.00000000000091</v>
       </c>
       <c r="N45" s="22" t="n">
-        <v>45</v>
+        <v>44.99999999999909</v>
       </c>
       <c r="O45" s="22" t="n">
         <v>25</v>
@@ -9643,37 +9643,37 @@
         <v>0</v>
       </c>
       <c r="E46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="F46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="G46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="J46" s="22" t="n">
-        <v>2043</v>
+        <v>20</v>
       </c>
       <c r="K46" s="22" t="n">
-        <v>2123</v>
+        <v>100</v>
       </c>
       <c r="L46" s="22" t="n">
-        <v>2113</v>
+        <v>90</v>
       </c>
       <c r="M46" s="22" t="n">
-        <v>2088</v>
+        <v>65.00000000000091</v>
       </c>
       <c r="N46" s="22" t="n">
-        <v>2068</v>
+        <v>44.99999999999909</v>
       </c>
       <c r="O46" s="22" t="n">
-        <v>2048</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" ht="15.5" customHeight="1">
@@ -9932,10 +9932,10 @@
         <v>90</v>
       </c>
       <c r="M51" s="22" t="n">
-        <v>65</v>
+        <v>65.00000000000091</v>
       </c>
       <c r="N51" s="22" t="n">
-        <v>45</v>
+        <v>44.99999999999909</v>
       </c>
       <c r="O51" s="22" t="n">
         <v>25</v>
@@ -9958,7 +9958,7 @@
         </is>
       </c>
       <c r="D52" s="22" t="n">
-        <v>3999.95</v>
+        <v>2879.964</v>
       </c>
       <c r="E52" s="22" t="n">
         <v>2885.6768</v>
@@ -10117,7 +10117,7 @@
         </is>
       </c>
       <c r="D55" s="22" t="n">
-        <v>3999.95</v>
+        <v>2879.964</v>
       </c>
       <c r="E55" s="22" t="n">
         <v>2880.6768</v>
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="D67" s="22" t="n">
-        <v>3999.95</v>
+        <v>2879.964</v>
       </c>
       <c r="E67" s="22" t="n">
         <v>2885.6768</v>
@@ -10967,7 +10967,7 @@
         </is>
       </c>
       <c r="D71" s="22" t="n">
-        <v>0</v>
+        <v>-1119.986</v>
       </c>
       <c r="E71" s="22" t="n">
         <v>-1120.2632</v>
@@ -11073,7 +11073,7 @@
         </is>
       </c>
       <c r="D73" s="22" t="n">
-        <v>3999.95</v>
+        <v>2879.964</v>
       </c>
       <c r="E73" s="22" t="n">
         <v>2880.6768</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="D76" s="22" t="n">
-        <v>3999.95</v>
+        <v>2879.964</v>
       </c>
       <c r="E76" s="22" t="n">
         <v>2880.6768</v>
@@ -11338,7 +11338,7 @@
         </is>
       </c>
       <c r="D78" s="22" t="n">
-        <v>0</v>
+        <v>2023</v>
       </c>
       <c r="E78" s="22" t="n">
         <v>2024</v>
@@ -11497,40 +11497,40 @@
         </is>
       </c>
       <c r="D81" s="22" t="n">
-        <v>-6022.95</v>
+        <v>-4902.964</v>
       </c>
       <c r="E81" s="22" t="n">
-        <v>-4001.94</v>
+        <v>-4904.6768</v>
       </c>
       <c r="F81" s="22" t="n">
-        <v>-4003.93</v>
+        <v>-4906.3896</v>
       </c>
       <c r="G81" s="22" t="n">
-        <v>-4005.92</v>
+        <v>-4908.1024</v>
       </c>
       <c r="H81" s="22" t="n">
-        <v>-4007.91</v>
+        <v>-4909.8152</v>
       </c>
       <c r="I81" s="22" t="n">
-        <v>-4009.9</v>
+        <v>-4911.528</v>
       </c>
       <c r="J81" s="22" t="n">
-        <v>-4011.89</v>
+        <v>-4913.2408</v>
       </c>
       <c r="K81" s="22" t="n">
-        <v>-4013.88</v>
+        <v>-4914.9536</v>
       </c>
       <c r="L81" s="22" t="n">
-        <v>-4015.87</v>
+        <v>-4916.6664</v>
       </c>
       <c r="M81" s="22" t="n">
-        <v>-4017.86</v>
+        <v>-4918.379199999999</v>
       </c>
       <c r="N81" s="22" t="n">
-        <v>-4019.85</v>
+        <v>-4920.092000000001</v>
       </c>
       <c r="O81" s="22" t="n">
-        <v>-4021.84</v>
+        <v>-4921.8048</v>
       </c>
     </row>
     <row r="82" ht="15.5" customHeight="1">
@@ -11553,7 +11553,7 @@
         <v>0</v>
       </c>
       <c r="E82" s="22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F82" s="22" t="n">
         <v>0</v>
@@ -11603,40 +11603,40 @@
         </is>
       </c>
       <c r="D83" s="22" t="n">
-        <v>-6022.95</v>
+        <v>-2879.964</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>-3999.940000000001</v>
+        <v>-2880.6768</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>-3999.93</v>
+        <v>-2881.3896</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>-3999.92</v>
+        <v>-2882.1024</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>-3999.91</v>
+        <v>-2882.8152</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>-3999.9</v>
+        <v>-2883.528</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>-3979.889999999999</v>
+        <v>-2864.2408</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>-3899.88</v>
+        <v>-2784.9536</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>-3909.87</v>
+        <v>-2795.6664</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>-3934.860000000001</v>
+        <v>-2821.379199999999</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>-3954.85</v>
+        <v>-2842.092000000001</v>
       </c>
       <c r="O83" s="22" t="n">
-        <v>-3974.84</v>
+        <v>-2862.8048</v>
       </c>
     </row>
     <row r="84" ht="15.5" customHeight="1">
@@ -11656,40 +11656,40 @@
         </is>
       </c>
       <c r="D84" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="E84" s="22" t="n">
-        <v>-3143.263200000001</v>
+        <v>0</v>
       </c>
       <c r="F84" s="22" t="n">
-        <v>-3143.5404</v>
+        <v>0</v>
       </c>
       <c r="G84" s="22" t="n">
-        <v>-3143.8176</v>
+        <v>0</v>
       </c>
       <c r="H84" s="22" t="n">
-        <v>-3144.0948</v>
+        <v>0</v>
       </c>
       <c r="I84" s="22" t="n">
-        <v>-3144.372</v>
+        <v>0</v>
       </c>
       <c r="J84" s="22" t="n">
-        <v>-3124.649199999999</v>
+        <v>20</v>
       </c>
       <c r="K84" s="22" t="n">
-        <v>-3044.9264</v>
+        <v>100</v>
       </c>
       <c r="L84" s="22" t="n">
-        <v>-3055.2036</v>
+        <v>90</v>
       </c>
       <c r="M84" s="22" t="n">
-        <v>-3080.480800000001</v>
+        <v>65.00000000000091</v>
       </c>
       <c r="N84" s="22" t="n">
-        <v>-3100.758</v>
+        <v>44.99999999999909</v>
       </c>
       <c r="O84" s="22" t="n">
-        <v>-3121.0352</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85" ht="15.5" customHeight="1">
@@ -11762,40 +11762,40 @@
         </is>
       </c>
       <c r="D86" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="E86" s="22" t="n">
-        <v>901.7368000000001</v>
+        <v>0</v>
       </c>
       <c r="F86" s="22" t="n">
-        <v>900.4595999999999</v>
+        <v>0</v>
       </c>
       <c r="G86" s="22" t="n">
-        <v>899.1824000000001</v>
+        <v>0</v>
       </c>
       <c r="H86" s="22" t="n">
-        <v>897.9051999999999</v>
+        <v>0</v>
       </c>
       <c r="I86" s="22" t="n">
-        <v>896.6279999999997</v>
+        <v>0</v>
       </c>
       <c r="J86" s="22" t="n">
-        <v>915.3507999999999</v>
+        <v>20</v>
       </c>
       <c r="K86" s="22" t="n">
-        <v>994.0735999999997</v>
+        <v>100</v>
       </c>
       <c r="L86" s="22" t="n">
-        <v>982.7964000000002</v>
+        <v>90</v>
       </c>
       <c r="M86" s="22" t="n">
-        <v>956.5192</v>
+        <v>65.00000000000091</v>
       </c>
       <c r="N86" s="22" t="n">
-        <v>935.2420000000002</v>
+        <v>44.99999999999909</v>
       </c>
       <c r="O86" s="22" t="n">
-        <v>913.9648</v>
+        <v>25</v>
       </c>
     </row>
     <row r="87" ht="15.5" customHeight="1">
@@ -11815,40 +11815,40 @@
         </is>
       </c>
       <c r="D87" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>901.7368000000001</v>
+        <v>0</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>900.4595999999999</v>
+        <v>0</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>899.1824000000001</v>
+        <v>0</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>897.9051999999999</v>
+        <v>0</v>
       </c>
       <c r="I87" s="22" t="n">
-        <v>896.6279999999997</v>
+        <v>0</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>915.3507999999999</v>
+        <v>20</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>994.0735999999997</v>
+        <v>100</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>982.7964000000002</v>
+        <v>90</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>956.5192</v>
+        <v>65.00000000000091</v>
       </c>
       <c r="N87" s="22" t="n">
-        <v>935.2420000000002</v>
+        <v>44.99999999999909</v>
       </c>
       <c r="O87" s="22" t="n">
-        <v>913.9648</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88" ht="15.5" customHeight="1">
@@ -12855,37 +12855,37 @@
         <v>0</v>
       </c>
       <c r="E106" s="24" t="n">
-        <v>10022.9</v>
+        <v>7782.928</v>
       </c>
       <c r="F106" s="24" t="n">
-        <v>16904.5168</v>
+        <v>15568.2816</v>
       </c>
       <c r="G106" s="24" t="n">
-        <v>24909.0996</v>
+        <v>23356.0608</v>
       </c>
       <c r="H106" s="24" t="n">
-        <v>32916.6624</v>
+        <v>31146.2656</v>
       </c>
       <c r="I106" s="24" t="n">
-        <v>40927.2052</v>
+        <v>38938.896</v>
       </c>
       <c r="J106" s="24" t="n">
-        <v>46700.4788</v>
+        <v>45830.93799999999</v>
       </c>
       <c r="K106" s="24" t="n">
-        <v>53379.192</v>
+        <v>54748.4056</v>
       </c>
       <c r="L106" s="24" t="n">
-        <v>63202.3168</v>
+        <v>60525.3128</v>
       </c>
       <c r="M106" s="24" t="n">
-        <v>68980.86720000001</v>
+        <v>70350.6456</v>
       </c>
       <c r="N106" s="24" t="n">
-        <v>74760.8432</v>
+        <v>77251.6672</v>
       </c>
       <c r="O106" s="24" t="n">
-        <v>80542.24479999999</v>
+        <v>85275.65480000002</v>
       </c>
     </row>
     <row r="107" ht="15.5" customHeight="1">
@@ -12980,7 +12980,7 @@
         </is>
       </c>
       <c r="D108" s="24" t="n">
-        <v>3999.95</v>
+        <v>2879.964</v>
       </c>
       <c r="E108" s="25" t="n">
         <v>2880.6768</v>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="D109" s="24" t="n">
-        <v>3999.95</v>
+        <v>4902.964</v>
       </c>
       <c r="E109" s="24" t="n">
         <v>4904.6768</v>
@@ -13086,40 +13086,40 @@
         </is>
       </c>
       <c r="D110" s="24" t="n">
-        <v>10022.9</v>
+        <v>7782.928</v>
       </c>
       <c r="E110" s="24" t="n">
-        <v>14882.5168</v>
+        <v>15568.2816</v>
       </c>
       <c r="F110" s="24" t="n">
-        <v>24911.0996</v>
+        <v>23356.0608</v>
       </c>
       <c r="G110" s="24" t="n">
-        <v>32919.6624</v>
+        <v>31146.2656</v>
       </c>
       <c r="H110" s="24" t="n">
-        <v>40931.2052</v>
+        <v>38938.896</v>
       </c>
       <c r="I110" s="24" t="n">
-        <v>46705.4788</v>
+        <v>44710.952</v>
       </c>
       <c r="J110" s="24" t="n">
-        <v>51362.192</v>
+        <v>53627.41959999999</v>
       </c>
       <c r="K110" s="24" t="n">
-        <v>61186.3168</v>
+        <v>60523.3128</v>
       </c>
       <c r="L110" s="24" t="n">
-        <v>66965.86720000001</v>
+        <v>70347.6456</v>
       </c>
       <c r="M110" s="24" t="n">
-        <v>72746.8432</v>
+        <v>75225.6672</v>
       </c>
       <c r="N110" s="24" t="n">
-        <v>78529.2448</v>
+        <v>85272.65480000002</v>
       </c>
       <c r="O110" s="24" t="n">
-        <v>84313.07199999999</v>
+        <v>93299.62240000002</v>
       </c>
     </row>
     <row r="111" ht="15.5" customHeight="1">
@@ -15749,7 +15749,7 @@
         </is>
       </c>
       <c r="D36" s="23" t="n">
-        <v>0</v>
+        <v>-1119.986</v>
       </c>
       <c r="E36" s="23" t="n">
         <v>-1120.2632</v>
@@ -15855,7 +15855,7 @@
         </is>
       </c>
       <c r="D38" s="23" t="n">
-        <v>3999.95</v>
+        <v>2879.964</v>
       </c>
       <c r="E38" s="23" t="n">
         <v>2880.6768</v>
@@ -15908,7 +15908,7 @@
         </is>
       </c>
       <c r="D39" s="23" t="n">
-        <v>0.9999874999999999</v>
+        <v>0.7199909999999999</v>
       </c>
       <c r="E39" s="23" t="n">
         <v>0.7199892026993252</v>
@@ -16255,10 +16255,10 @@
         <v>90</v>
       </c>
       <c r="M45" s="22" t="n">
-        <v>65</v>
+        <v>65.00000000000091</v>
       </c>
       <c r="N45" s="22" t="n">
-        <v>45</v>
+        <v>44.99999999999909</v>
       </c>
       <c r="O45" s="22" t="n">
         <v>25</v>
@@ -16284,37 +16284,37 @@
         <v>0</v>
       </c>
       <c r="E46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="F46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="G46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="J46" s="22" t="n">
-        <v>2043</v>
+        <v>20</v>
       </c>
       <c r="K46" s="22" t="n">
-        <v>2123</v>
+        <v>100</v>
       </c>
       <c r="L46" s="22" t="n">
-        <v>2113</v>
+        <v>90</v>
       </c>
       <c r="M46" s="22" t="n">
-        <v>2088</v>
+        <v>65.00000000000091</v>
       </c>
       <c r="N46" s="22" t="n">
-        <v>2068</v>
+        <v>44.99999999999909</v>
       </c>
       <c r="O46" s="22" t="n">
-        <v>2048</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" ht="15.5" customHeight="1">
@@ -16573,10 +16573,10 @@
         <v>90</v>
       </c>
       <c r="M51" s="22" t="n">
-        <v>65</v>
+        <v>65.00000000000091</v>
       </c>
       <c r="N51" s="22" t="n">
-        <v>45</v>
+        <v>44.99999999999909</v>
       </c>
       <c r="O51" s="22" t="n">
         <v>25</v>
@@ -16599,7 +16599,7 @@
         </is>
       </c>
       <c r="D52" s="22" t="n">
-        <v>3999.95</v>
+        <v>2879.964</v>
       </c>
       <c r="E52" s="22" t="n">
         <v>2885.6768</v>
@@ -16758,7 +16758,7 @@
         </is>
       </c>
       <c r="D55" s="22" t="n">
-        <v>3999.95</v>
+        <v>2879.964</v>
       </c>
       <c r="E55" s="22" t="n">
         <v>2880.6768</v>
@@ -17394,7 +17394,7 @@
         </is>
       </c>
       <c r="D67" s="22" t="n">
-        <v>3999.95</v>
+        <v>2879.964</v>
       </c>
       <c r="E67" s="22" t="n">
         <v>2885.6768</v>
@@ -17608,7 +17608,7 @@
         </is>
       </c>
       <c r="D71" s="22" t="n">
-        <v>0</v>
+        <v>-1119.986</v>
       </c>
       <c r="E71" s="22" t="n">
         <v>-1120.2632</v>
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="D73" s="22" t="n">
-        <v>3999.95</v>
+        <v>2879.964</v>
       </c>
       <c r="E73" s="22" t="n">
         <v>2880.6768</v>
@@ -17873,7 +17873,7 @@
         </is>
       </c>
       <c r="D76" s="22" t="n">
-        <v>3999.95</v>
+        <v>2879.964</v>
       </c>
       <c r="E76" s="22" t="n">
         <v>2880.6768</v>
@@ -17979,7 +17979,7 @@
         </is>
       </c>
       <c r="D78" s="22" t="n">
-        <v>0</v>
+        <v>2023</v>
       </c>
       <c r="E78" s="22" t="n">
         <v>2024</v>
@@ -18138,40 +18138,40 @@
         </is>
       </c>
       <c r="D81" s="22" t="n">
-        <v>-6022.95</v>
+        <v>-4902.964</v>
       </c>
       <c r="E81" s="22" t="n">
-        <v>-4001.94</v>
+        <v>-4904.6768</v>
       </c>
       <c r="F81" s="22" t="n">
-        <v>-4003.93</v>
+        <v>-4906.3896</v>
       </c>
       <c r="G81" s="22" t="n">
-        <v>-4005.92</v>
+        <v>-4908.1024</v>
       </c>
       <c r="H81" s="22" t="n">
-        <v>-4007.91</v>
+        <v>-4909.8152</v>
       </c>
       <c r="I81" s="22" t="n">
-        <v>-4009.9</v>
+        <v>-4911.528</v>
       </c>
       <c r="J81" s="22" t="n">
-        <v>-4011.89</v>
+        <v>-4913.2408</v>
       </c>
       <c r="K81" s="22" t="n">
-        <v>-4013.88</v>
+        <v>-4914.9536</v>
       </c>
       <c r="L81" s="22" t="n">
-        <v>-4015.87</v>
+        <v>-4916.6664</v>
       </c>
       <c r="M81" s="22" t="n">
-        <v>-4017.86</v>
+        <v>-4918.379199999999</v>
       </c>
       <c r="N81" s="22" t="n">
-        <v>-4019.85</v>
+        <v>-4920.092000000001</v>
       </c>
       <c r="O81" s="22" t="n">
-        <v>-4021.84</v>
+        <v>-4921.8048</v>
       </c>
     </row>
     <row r="82" ht="15.5" customHeight="1">
@@ -18194,7 +18194,7 @@
         <v>0</v>
       </c>
       <c r="E82" s="22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F82" s="22" t="n">
         <v>0</v>
@@ -18244,40 +18244,40 @@
         </is>
       </c>
       <c r="D83" s="22" t="n">
-        <v>-6022.95</v>
+        <v>-2879.964</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>-3999.940000000001</v>
+        <v>-2880.6768</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>-3999.93</v>
+        <v>-2881.3896</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>-3999.92</v>
+        <v>-2882.1024</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>-3999.91</v>
+        <v>-2882.8152</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>-3999.9</v>
+        <v>-2883.528</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>-3979.889999999999</v>
+        <v>-2864.2408</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>-3899.88</v>
+        <v>-2784.9536</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>-3909.87</v>
+        <v>-2795.6664</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>-3934.860000000001</v>
+        <v>-2821.379199999999</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>-3954.85</v>
+        <v>-2842.092000000001</v>
       </c>
       <c r="O83" s="22" t="n">
-        <v>-3974.84</v>
+        <v>-2862.8048</v>
       </c>
     </row>
     <row r="84" ht="15.5" customHeight="1">
@@ -18297,40 +18297,40 @@
         </is>
       </c>
       <c r="D84" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="E84" s="22" t="n">
-        <v>-3143.263200000001</v>
+        <v>0</v>
       </c>
       <c r="F84" s="22" t="n">
-        <v>-3143.5404</v>
+        <v>0</v>
       </c>
       <c r="G84" s="22" t="n">
-        <v>-3143.8176</v>
+        <v>0</v>
       </c>
       <c r="H84" s="22" t="n">
-        <v>-3144.0948</v>
+        <v>0</v>
       </c>
       <c r="I84" s="22" t="n">
-        <v>-3144.372</v>
+        <v>0</v>
       </c>
       <c r="J84" s="22" t="n">
-        <v>-3124.649199999999</v>
+        <v>20</v>
       </c>
       <c r="K84" s="22" t="n">
-        <v>-3044.9264</v>
+        <v>100</v>
       </c>
       <c r="L84" s="22" t="n">
-        <v>-3055.2036</v>
+        <v>90</v>
       </c>
       <c r="M84" s="22" t="n">
-        <v>-3080.480800000001</v>
+        <v>65.00000000000091</v>
       </c>
       <c r="N84" s="22" t="n">
-        <v>-3100.758</v>
+        <v>44.99999999999909</v>
       </c>
       <c r="O84" s="22" t="n">
-        <v>-3121.0352</v>
+        <v>25</v>
       </c>
     </row>
     <row r="85" ht="15.5" customHeight="1">
@@ -18403,40 +18403,40 @@
         </is>
       </c>
       <c r="D86" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="E86" s="22" t="n">
-        <v>901.7368000000001</v>
+        <v>0</v>
       </c>
       <c r="F86" s="22" t="n">
-        <v>900.4595999999999</v>
+        <v>0</v>
       </c>
       <c r="G86" s="22" t="n">
-        <v>899.1824000000001</v>
+        <v>0</v>
       </c>
       <c r="H86" s="22" t="n">
-        <v>897.9051999999999</v>
+        <v>0</v>
       </c>
       <c r="I86" s="22" t="n">
-        <v>896.6279999999997</v>
+        <v>0</v>
       </c>
       <c r="J86" s="22" t="n">
-        <v>915.3507999999999</v>
+        <v>20</v>
       </c>
       <c r="K86" s="22" t="n">
-        <v>994.0735999999997</v>
+        <v>100</v>
       </c>
       <c r="L86" s="22" t="n">
-        <v>982.7964000000002</v>
+        <v>90</v>
       </c>
       <c r="M86" s="22" t="n">
-        <v>956.5192</v>
+        <v>65.00000000000091</v>
       </c>
       <c r="N86" s="22" t="n">
-        <v>935.2420000000002</v>
+        <v>44.99999999999909</v>
       </c>
       <c r="O86" s="22" t="n">
-        <v>913.9648</v>
+        <v>25</v>
       </c>
     </row>
     <row r="87" ht="15.5" customHeight="1">
@@ -18456,40 +18456,40 @@
         </is>
       </c>
       <c r="D87" s="22" t="n">
-        <v>2023</v>
+        <v>0</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>901.7368000000001</v>
+        <v>0</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>900.4595999999999</v>
+        <v>0</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>899.1824000000001</v>
+        <v>0</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>897.9051999999999</v>
+        <v>0</v>
       </c>
       <c r="I87" s="22" t="n">
-        <v>896.6279999999997</v>
+        <v>0</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>915.3507999999999</v>
+        <v>20</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>994.0735999999997</v>
+        <v>100</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>982.7964000000002</v>
+        <v>90</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>956.5192</v>
+        <v>65.00000000000091</v>
       </c>
       <c r="N87" s="22" t="n">
-        <v>935.2420000000002</v>
+        <v>44.99999999999909</v>
       </c>
       <c r="O87" s="22" t="n">
-        <v>913.9648</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88" ht="15.5" customHeight="1">
@@ -19496,37 +19496,37 @@
         <v>0</v>
       </c>
       <c r="E106" s="24" t="n">
-        <v>10022.9</v>
+        <v>7782.928</v>
       </c>
       <c r="F106" s="24" t="n">
-        <v>16904.5168</v>
+        <v>15568.2816</v>
       </c>
       <c r="G106" s="24" t="n">
-        <v>24909.0996</v>
+        <v>23356.0608</v>
       </c>
       <c r="H106" s="24" t="n">
-        <v>32916.6624</v>
+        <v>31146.2656</v>
       </c>
       <c r="I106" s="24" t="n">
-        <v>40927.2052</v>
+        <v>38938.896</v>
       </c>
       <c r="J106" s="24" t="n">
-        <v>46700.4788</v>
+        <v>45830.93799999999</v>
       </c>
       <c r="K106" s="24" t="n">
-        <v>53379.192</v>
+        <v>54748.4056</v>
       </c>
       <c r="L106" s="24" t="n">
-        <v>63202.3168</v>
+        <v>60525.3128</v>
       </c>
       <c r="M106" s="24" t="n">
-        <v>68980.86720000001</v>
+        <v>70350.6456</v>
       </c>
       <c r="N106" s="24" t="n">
-        <v>74760.8432</v>
+        <v>77251.6672</v>
       </c>
       <c r="O106" s="24" t="n">
-        <v>80542.24479999999</v>
+        <v>85275.65480000002</v>
       </c>
     </row>
     <row r="107" ht="15.5" customHeight="1">
@@ -19621,7 +19621,7 @@
         </is>
       </c>
       <c r="D108" s="24" t="n">
-        <v>3999.95</v>
+        <v>2879.964</v>
       </c>
       <c r="E108" s="25" t="n">
         <v>2880.6768</v>
@@ -19674,7 +19674,7 @@
         </is>
       </c>
       <c r="D109" s="24" t="n">
-        <v>3999.95</v>
+        <v>4902.964</v>
       </c>
       <c r="E109" s="24" t="n">
         <v>4904.6768</v>
@@ -19727,40 +19727,40 @@
         </is>
       </c>
       <c r="D110" s="24" t="n">
-        <v>10022.9</v>
+        <v>7782.928</v>
       </c>
       <c r="E110" s="24" t="n">
-        <v>14882.5168</v>
+        <v>15568.2816</v>
       </c>
       <c r="F110" s="24" t="n">
-        <v>24911.0996</v>
+        <v>23356.0608</v>
       </c>
       <c r="G110" s="24" t="n">
-        <v>32919.6624</v>
+        <v>31146.2656</v>
       </c>
       <c r="H110" s="24" t="n">
-        <v>40931.2052</v>
+        <v>38938.896</v>
       </c>
       <c r="I110" s="24" t="n">
-        <v>46705.4788</v>
+        <v>44710.952</v>
       </c>
       <c r="J110" s="24" t="n">
-        <v>51362.192</v>
+        <v>53627.41959999999</v>
       </c>
       <c r="K110" s="24" t="n">
-        <v>61186.3168</v>
+        <v>60523.3128</v>
       </c>
       <c r="L110" s="24" t="n">
-        <v>66965.86720000001</v>
+        <v>70347.6456</v>
       </c>
       <c r="M110" s="24" t="n">
-        <v>72746.8432</v>
+        <v>75225.6672</v>
       </c>
       <c r="N110" s="24" t="n">
-        <v>78529.2448</v>
+        <v>85272.65480000002</v>
       </c>
       <c r="O110" s="24" t="n">
-        <v>84313.07199999999</v>
+        <v>93299.62240000002</v>
       </c>
     </row>
     <row r="111" ht="15.5" customHeight="1">
@@ -20588,40 +20588,40 @@
         </is>
       </c>
       <c r="D2" s="22" t="n">
-        <v>0.1800000000000068</v>
+        <v>-120.3103323306667</v>
       </c>
       <c r="E2" s="22" t="n">
-        <v>-138.05618</v>
+        <v>-132.8245300488875</v>
       </c>
       <c r="F2" s="22" t="n">
-        <v>-148.2510133333333</v>
+        <v>-142.5562977135274</v>
       </c>
       <c r="G2" s="22" t="n">
-        <v>-157.4002333333333</v>
+        <v>-151.0141952197973</v>
       </c>
       <c r="H2" s="22" t="n">
-        <v>-163.93024</v>
+        <v>-156.1274384134144</v>
       </c>
       <c r="I2" s="22" t="n">
-        <v>-164.7199666666667</v>
+        <v>-153.6034758847147</v>
       </c>
       <c r="J2" s="22" t="n">
-        <v>-154.1203466666666</v>
+        <v>-135.3652372915541</v>
       </c>
       <c r="K2" s="22" t="n">
-        <v>-122.5676466666667</v>
+        <v>-87.27601239504213</v>
       </c>
       <c r="L2" s="22" t="n">
-        <v>-54.78346666666664</v>
+        <v>13.93800042632517</v>
       </c>
       <c r="M2" s="22" t="n">
-        <v>72.58392666666668</v>
+        <v>204.801931579119</v>
       </c>
       <c r="N2" s="22" t="n">
-        <v>293.9270666666669</v>
+        <v>540.388879796224</v>
       </c>
       <c r="O2" s="22" t="n">
-        <v>658.3504866666665</v>
+        <v>1100.995730866312</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
@@ -20644,37 +20644,37 @@
         <v>0</v>
       </c>
       <c r="E3" s="22" t="n">
-        <v>-76797.87777777489</v>
+        <v>13.0353314786908</v>
       </c>
       <c r="F3" s="22" t="n">
-        <v>7.384554123787357</v>
+        <v>7.326784940295306</v>
       </c>
       <c r="G3" s="22" t="n">
-        <v>6.171438423445053</v>
+        <v>5.933022701856627</v>
       </c>
       <c r="H3" s="22" t="n">
-        <v>4.148663904987893</v>
+        <v>3.385935465321599</v>
       </c>
       <c r="I3" s="22" t="n">
-        <v>0.4817455685215188</v>
+        <v>-1.616604073152372</v>
       </c>
       <c r="J3" s="22" t="n">
-        <v>-6.434933308024449</v>
+        <v>-11.87358455797516</v>
       </c>
       <c r="K3" s="22" t="n">
-        <v>-20.47276734216181</v>
+        <v>-35.52553510687225</v>
       </c>
       <c r="L3" s="22" t="n">
-        <v>-55.30348492726225</v>
+        <v>-115.9700243444176</v>
       </c>
       <c r="M3" s="22" t="n">
-        <v>-232.49239429901</v>
+        <v>1369.37814115935</v>
       </c>
       <c r="N3" s="22" t="n">
-        <v>304.947872297531</v>
+        <v>163.8592691141007</v>
       </c>
       <c r="O3" s="22" t="n">
-        <v>123.9843013210077</v>
+        <v>103.7413744119768</v>
       </c>
     </row>
     <row r="4" ht="15.5" customHeight="1">
@@ -20959,40 +20959,40 @@
         </is>
       </c>
       <c r="D9" s="22" t="n">
-        <v>-479.82</v>
+        <v>-600.3103323306667</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>-658.18618</v>
+        <v>-662.0680066923009</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>-708.5310133333334</v>
+        <v>-712.6539992209409</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>-757.8502333333332</v>
+        <v>-761.9819469061972</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>-804.57024</v>
+        <v>-807.9631937388544</v>
       </c>
       <c r="I9" s="22" t="n">
-        <v>-845.5699666666667</v>
+        <v>-846.2565309695148</v>
       </c>
       <c r="J9" s="22" t="n">
-        <v>-875.2003466666665</v>
+        <v>-868.6749702016341</v>
       </c>
       <c r="K9" s="22" t="n">
-        <v>-883.8976466666668</v>
+        <v>-860.8625580005889</v>
       </c>
       <c r="L9" s="22" t="n">
-        <v>-856.3834666666667</v>
+        <v>-799.1461971544747</v>
       </c>
       <c r="M9" s="22" t="n">
-        <v>-769.3060733333333</v>
+        <v>-646.3225458263209</v>
       </c>
       <c r="N9" s="22" t="n">
-        <v>-588.2729333333332</v>
+        <v>-346.2285052747094</v>
       </c>
       <c r="O9" s="22" t="n">
-        <v>-264.1795133333336</v>
+        <v>183.1077537428988</v>
       </c>
     </row>
     <row r="10" ht="15.5" customHeight="1">
@@ -21015,37 +21015,37 @@
         <v>0</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>37.17356091867785</v>
+        <v>8.769497188867792</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>7.649026197015152</v>
+        <v>7.639393766194624</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>6.960770816223572</v>
+        <v>6.918808499855</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>6.164807320989163</v>
+        <v>6.0286629066028</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>5.095854237246789</v>
+        <v>4.729866665528371</v>
       </c>
       <c r="J10" s="22" t="n">
-        <v>3.504190211107683</v>
+        <v>2.635468847861522</v>
       </c>
       <c r="K10" s="22" t="n">
-        <v>0.9937496063758822</v>
+        <v>-0.9153212085460161</v>
       </c>
       <c r="L10" s="22" t="n">
-        <v>-3.112824217120713</v>
+        <v>-7.181661681769558</v>
       </c>
       <c r="M10" s="22" t="n">
-        <v>-10.16803765166881</v>
+        <v>-19.11656665350018</v>
       </c>
       <c r="N10" s="22" t="n">
-        <v>-23.53200452657288</v>
+        <v>-46.3479011542303</v>
       </c>
       <c r="O10" s="22" t="n">
-        <v>-55.09235622376637</v>
+        <v>-152.2117977788191</v>
       </c>
     </row>
     <row r="11" ht="15.5" customHeight="1">
@@ -21065,40 +21065,40 @@
         </is>
       </c>
       <c r="D11" s="22" t="n">
-        <v>2665.666666666566</v>
+        <v>-5.108715790682994</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>-4.767524206449867</v>
+        <v>-4.915918240467785</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>-4.779265904511862</v>
+        <v>-4.930236748473261</v>
       </c>
       <c r="G11" s="22" t="n">
-        <v>-4.814797394413012</v>
+        <v>-4.976116279175347</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>-4.908003794784904</v>
+        <v>-5.103314615997418</v>
       </c>
       <c r="I11" s="22" t="n">
-        <v>-5.133378689772277</v>
+        <v>-5.432516882046368</v>
       </c>
       <c r="J11" s="22" t="n">
-        <v>-5.678681404471278</v>
+        <v>-6.326921552591187</v>
       </c>
       <c r="K11" s="22" t="n">
-        <v>-7.211508670558902</v>
+        <v>-9.723244556063708</v>
       </c>
       <c r="L11" s="22" t="n">
-        <v>-15.632151792755</v>
+        <v>56.51183638120653</v>
       </c>
       <c r="M11" s="22" t="n">
-        <v>10.59884892789395</v>
+        <v>3.110752244906251</v>
       </c>
       <c r="N11" s="22" t="n">
-        <v>2.001424843260435</v>
+        <v>0.6325280422733163</v>
       </c>
       <c r="O11" s="22" t="n">
-        <v>0.4012748812124627</v>
+        <v>-0.1620948436610987</v>
       </c>
     </row>
     <row r="12" ht="15.5" customHeight="1">
@@ -21118,40 +21118,40 @@
         </is>
       </c>
       <c r="D12" s="22" t="n">
-        <v>0.18</v>
+        <v>-130.3219077973333</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-138.05618</v>
+        <v>-138.5358859898709</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>-148.2510133333333</v>
+        <v>-148.7111631026177</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>-157.4002333333333</v>
+        <v>-157.6184908099413</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>-163.93024</v>
+        <v>-163.1946664173568</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>-164.7199666666667</v>
+        <v>-161.1610384045227</v>
       </c>
       <c r="J12" s="22" t="n">
-        <v>-154.1203466666666</v>
+        <v>-143.4638528485376</v>
       </c>
       <c r="K12" s="22" t="n">
-        <v>-122.5676466666667</v>
+        <v>-96.00291573007362</v>
       </c>
       <c r="L12" s="22" t="n">
-        <v>-54.78346666666667</v>
+        <v>4.441398742357308</v>
       </c>
       <c r="M12" s="22" t="n">
-        <v>72.58392666666668</v>
+        <v>194.3172644050434</v>
       </c>
       <c r="N12" s="22" t="n">
-        <v>293.9270666666669</v>
+        <v>528.5922820406612</v>
       </c>
       <c r="O12" s="22" t="n">
-        <v>658.3504866666665</v>
+        <v>1087.422926357862</v>
       </c>
     </row>
     <row r="13" ht="15.5" customHeight="1">
@@ -21174,37 +21174,37 @@
         <v>0</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-76797.87777777779</v>
+        <v>17.97657270382369</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>7.384554123787357</v>
+        <v>7.352500413270979</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>6.171438423445053</v>
+        <v>6.0101774135215</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>4.148663904987893</v>
+        <v>3.585202149529043</v>
       </c>
       <c r="I13" s="22" t="n">
-        <v>0.4817455685215188</v>
+        <v>-1.145485408514901</v>
       </c>
       <c r="J13" s="22" t="n">
-        <v>-6.434933308024449</v>
+        <v>-10.76835398425916</v>
       </c>
       <c r="K13" s="22" t="n">
-        <v>-20.47276734216181</v>
+        <v>-32.56371957349611</v>
       </c>
       <c r="L13" s="22" t="n">
-        <v>-55.30348492726223</v>
+        <v>-102.4653268184977</v>
       </c>
       <c r="M13" s="22" t="n">
-        <v>-232.4923942990099</v>
+        <v>7869.974219009127</v>
       </c>
       <c r="N13" s="22" t="n">
-        <v>304.947872297531</v>
+        <v>174.0596573135868</v>
       </c>
       <c r="O13" s="22" t="n">
-        <v>123.9843013210077</v>
+        <v>106.2866709561835</v>
       </c>
     </row>
     <row r="14" ht="15.5" customHeight="1">
@@ -21224,40 +21224,40 @@
         </is>
       </c>
       <c r="D14" s="22" t="n">
-        <v>0.9999999999999623</v>
+        <v>1.023855931604123</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>1</v>
+        <v>1.068612903354968</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>1</v>
+        <v>1.068868942760723</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>1</v>
+        <v>1.069647437256423</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>1</v>
+        <v>1.071709082267746</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>1</v>
+        <v>1.07684106766997</v>
       </c>
       <c r="J14" s="22" t="n">
-        <v>1</v>
+        <v>1.090346186028095</v>
       </c>
       <c r="K14" s="22" t="n">
-        <v>1</v>
+        <v>1.140434298831954</v>
       </c>
       <c r="L14" s="22" t="n">
-        <v>1</v>
+        <v>0.1760512821402074</v>
       </c>
       <c r="M14" s="22" t="n">
-        <v>1</v>
+        <v>0.9549102035599086</v>
       </c>
       <c r="N14" s="22" t="n">
-        <v>1</v>
+        <v>0.9918255440922487</v>
       </c>
       <c r="O14" s="22" t="n">
-        <v>1</v>
+        <v>1.004216204247163</v>
       </c>
     </row>
     <row r="15" ht="15.5" customHeight="1">
@@ -21383,40 +21383,40 @@
         </is>
       </c>
       <c r="D17" s="22" t="n">
-        <v>0.6481481481481238</v>
+        <v>-0.0009928478824150035</v>
       </c>
       <c r="E17" s="22" t="n">
-        <v>-0.00142454084030622</v>
+        <v>-0.001480650197627512</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>-0.003440111393055347</v>
+        <v>-0.003577533986080822</v>
       </c>
       <c r="G17" s="22" t="n">
-        <v>-0.009974572252857739</v>
+        <v>-0.01039637365027112</v>
       </c>
       <c r="H17" s="22" t="n">
-        <v>-0.02799971500072226</v>
+        <v>-0.02939906045115532</v>
       </c>
       <c r="I17" s="22" t="n">
-        <v>-0.07339729508606424</v>
+        <v>-0.07870915635446954</v>
       </c>
       <c r="J17" s="22" t="n">
-        <v>-0.1870183525843787</v>
+        <v>-0.2129300986726207</v>
       </c>
       <c r="K17" s="22" t="n">
-        <v>-0.5148993369484616</v>
+        <v>-0.7231081974087198</v>
       </c>
       <c r="L17" s="22" t="n">
-        <v>-2.348701311344543</v>
+        <v>9.231596790381541</v>
       </c>
       <c r="M17" s="22" t="n">
-        <v>3.403737962555346</v>
+        <v>1.206320002754583</v>
       </c>
       <c r="N17" s="22" t="n">
-        <v>1.53370246496523</v>
+        <v>0.8342078890236568</v>
       </c>
       <c r="O17" s="22" t="n">
-        <v>1.195943522403209</v>
+        <v>0.7151253887065286</v>
       </c>
     </row>
     <row r="18" ht="15.5" customHeight="1">
@@ -21542,40 +21542,40 @@
         </is>
       </c>
       <c r="D20" s="22" t="n">
-        <v>0.2777777777777673</v>
+        <v>-0.0004255062353207157</v>
       </c>
       <c r="E20" s="22" t="n">
-        <v>-0.0004346056800934228</v>
+        <v>-0.0004517237891066985</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>-0.0004721721519879888</v>
+        <v>-0.000491034076520897</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>-0.0005082584587443434</v>
+        <v>-0.0005297515235806942</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>-0.0005490140196220051</v>
+        <v>-0.0005764521657089279</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>-0.0006070909436399028</v>
+        <v>-0.0006510269342801451</v>
       </c>
       <c r="J20" s="22" t="n">
-        <v>-0.0007137279559713772</v>
+        <v>-0.000812616312732333</v>
       </c>
       <c r="K20" s="22" t="n">
-        <v>-0.0009790511873524858</v>
+        <v>-0.001374948244161724</v>
       </c>
       <c r="L20" s="22" t="n">
-        <v>-0.002372978708904877</v>
+        <v>0.009327019373199663</v>
       </c>
       <c r="M20" s="22" t="n">
-        <v>0.001928801684192891</v>
+        <v>0.0006835873027199222</v>
       </c>
       <c r="N20" s="22" t="n">
-        <v>0.000510330680672257</v>
+        <v>0.0002775778806857826</v>
       </c>
       <c r="O20" s="22" t="n">
-        <v>0.0002430316423249044</v>
+        <v>0.0001453229976415122</v>
       </c>
     </row>
     <row r="21" ht="15.5" customHeight="1">
@@ -21754,40 +21754,40 @@
         </is>
       </c>
       <c r="D24" s="22" t="n">
-        <v>-23.75333333333333</v>
+        <v>-141.4404245333333</v>
       </c>
       <c r="E24" s="22" t="n">
-        <v>-163.9260133333333</v>
+        <v>-158.6943633822208</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>-175.8250133333333</v>
+        <v>-170.1302977135274</v>
       </c>
       <c r="G24" s="22" t="n">
-        <v>-185.9327333333333</v>
+        <v>-179.5466952197973</v>
       </c>
       <c r="H24" s="22" t="n">
-        <v>-191.46224</v>
+        <v>-183.6594384134144</v>
       </c>
       <c r="I24" s="22" t="n">
-        <v>-186.7724666666667</v>
+        <v>-175.6559758847147</v>
       </c>
       <c r="J24" s="22" t="n">
-        <v>-161.4610133333333</v>
+        <v>-142.7059039582208</v>
       </c>
       <c r="K24" s="22" t="n">
-        <v>-97.6441466666667</v>
+        <v>-62.35251239504213</v>
       </c>
       <c r="L24" s="22" t="n">
-        <v>33.67653333333335</v>
+        <v>102.3980004263252</v>
       </c>
       <c r="M24" s="22" t="n">
-        <v>277.4060933333334</v>
+        <v>409.6240982457858</v>
       </c>
       <c r="N24" s="22" t="n">
-        <v>700.4637333333336</v>
+        <v>946.9255464628907</v>
       </c>
       <c r="O24" s="22" t="n">
-        <v>1399.413986666666</v>
+        <v>1842.059230866312</v>
       </c>
     </row>
     <row r="25" ht="15.5" customHeight="1">
@@ -21807,40 +21807,40 @@
         </is>
       </c>
       <c r="D25" s="22" t="n">
-        <v>-23.75333333333333</v>
+        <v>-161.4635754666666</v>
       </c>
       <c r="E25" s="22" t="n">
-        <v>-25.53316666666663</v>
+        <v>-157.84386979328</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>-26.66733333333337</v>
+        <v>-169.2149545506134</v>
       </c>
       <c r="G25" s="22" t="n">
-        <v>-25.79583333333331</v>
+        <v>-178.5703068757333</v>
       </c>
       <c r="H25" s="22" t="n">
-        <v>-19.79199999999999</v>
+        <v>-182.63498978304</v>
       </c>
       <c r="I25" s="22" t="n">
-        <v>-2.309166666666659</v>
+        <v>-174.6187499434667</v>
       </c>
       <c r="J25" s="22" t="n">
-        <v>38.38600000000002</v>
+        <v>-141.7383220599466</v>
       </c>
       <c r="K25" s="22" t="n">
-        <v>122.5068333333334</v>
+        <v>-61.62702204074672</v>
       </c>
       <c r="L25" s="22" t="n">
-        <v>282.8933333333333</v>
+        <v>102.5499237205333</v>
       </c>
       <c r="M25" s="22" t="n">
-        <v>570.4855000000001</v>
+        <v>408.6068916036269</v>
       </c>
       <c r="N25" s="22" t="n">
-        <v>1061.31</v>
+        <v>943.7264878250667</v>
       </c>
       <c r="O25" s="22" t="n">
-        <v>1865.220166666667</v>
+        <v>1835.033253193386</v>
       </c>
     </row>
     <row r="26" ht="15.5" customHeight="1">
@@ -21860,40 +21860,40 @@
         </is>
       </c>
       <c r="D26" s="22" t="n">
-        <v>-131.962962962958</v>
+        <v>1.374075162764872</v>
       </c>
       <c r="E26" s="22" t="n">
-        <v>0.1849476544017561</v>
+        <v>1.188363849171413</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>0.179879602396872</v>
+        <v>1.187004413446943</v>
       </c>
       <c r="G26" s="22" t="n">
-        <v>0.1638868811503243</v>
+        <v>1.182473651671148</v>
       </c>
       <c r="H26" s="22" t="n">
-        <v>0.1207342830706524</v>
+        <v>1.169781504385126</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>0.01401874170688471</v>
+        <v>1.136815094435264</v>
       </c>
       <c r="J26" s="22" t="n">
-        <v>-0.2490651028901572</v>
+        <v>1.047080660411106</v>
       </c>
       <c r="K26" s="22" t="n">
-        <v>-0.9995038386149431</v>
+        <v>0.7061163812320046</v>
       </c>
       <c r="L26" s="22" t="n">
-        <v>-5.163845053008695</v>
+        <v>7.357577886627397</v>
       </c>
       <c r="M26" s="22" t="n">
-        <v>7.85966709434017</v>
+        <v>1.995132020743535</v>
       </c>
       <c r="N26" s="22" t="n">
-        <v>3.610793698028487</v>
+        <v>1.74638398958346</v>
       </c>
       <c r="O26" s="22" t="n">
-        <v>2.833172002515824</v>
+        <v>1.666703332036992</v>
       </c>
     </row>
     <row r="27" ht="15.5" customHeight="1">
@@ -21913,40 +21913,40 @@
         </is>
       </c>
       <c r="D27" s="22" t="n">
-        <v>-131.962962962958</v>
+        <v>1.374075162764872</v>
       </c>
       <c r="E27" s="22" t="n">
-        <v>0.1849476544017561</v>
+        <v>1.256972817510263</v>
       </c>
       <c r="F27" s="22" t="n">
-        <v>0.179879602396872</v>
+        <v>1.255836692329952</v>
       </c>
       <c r="G27" s="22" t="n">
-        <v>0.1638868811503243</v>
+        <v>1.251934192590051</v>
       </c>
       <c r="H27" s="22" t="n">
-        <v>0.1207342830706524</v>
+        <v>1.24078757121167</v>
       </c>
       <c r="I27" s="22" t="n">
-        <v>0.01401874170688471</v>
+        <v>1.211410379592741</v>
       </c>
       <c r="J27" s="22" t="n">
-        <v>-0.2490651028901572</v>
+        <v>1.130546261596034</v>
       </c>
       <c r="K27" s="22" t="n">
-        <v>-0.9995038386149431</v>
+        <v>0.8208653024691787</v>
       </c>
       <c r="L27" s="22" t="n">
-        <v>-5.163845053008695</v>
+        <v>6.887211020486575</v>
       </c>
       <c r="M27" s="22" t="n">
-        <v>7.85966709434017</v>
+        <v>1.999194885718216</v>
       </c>
       <c r="N27" s="22" t="n">
-        <v>3.610793698028487</v>
+        <v>1.774010615803753</v>
       </c>
       <c r="O27" s="22" t="n">
-        <v>2.833172002515824</v>
+        <v>1.702997911954947</v>
       </c>
     </row>
     <row r="28" ht="15.5" customHeight="1">
@@ -21969,37 +21969,37 @@
         <v>-0.01333333333333333</v>
       </c>
       <c r="E28" s="22" t="n">
-        <v>-0.08</v>
+        <v>-0.08666666666666667</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>-0.3266666666666667</v>
+        <v>-0.3933333333333334</v>
       </c>
       <c r="G28" s="22" t="n">
-        <v>-1.086666666666667</v>
+        <v>-1.446666666666667</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>-3.06</v>
+        <v>-4.46</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>-7.553333333333333</v>
+        <v>-11.95333333333333</v>
       </c>
       <c r="J28" s="22" t="n">
-        <v>-16.79333333333333</v>
+        <v>-28.67333333333334</v>
       </c>
       <c r="K28" s="22" t="n">
-        <v>-34.35333333333333</v>
+        <v>-62.94666666666667</v>
       </c>
       <c r="L28" s="22" t="n">
-        <v>-65.63333333333334</v>
+        <v>-128.4933333333333</v>
       </c>
       <c r="M28" s="22" t="n">
-        <v>-118.4666666666667</v>
+        <v>-246.8666666666667</v>
       </c>
       <c r="N28" s="22" t="n">
-        <v>-203.8266666666667</v>
+        <v>-450.5933333333333</v>
       </c>
       <c r="O28" s="22" t="n">
-        <v>-336.6466666666666</v>
+        <v>-787.1333333333333</v>
       </c>
     </row>
     <row r="29" ht="15.5" customHeight="1">
@@ -22019,40 +22019,40 @@
         </is>
       </c>
       <c r="D29" s="23" t="n">
-        <v>0.07407407407407127</v>
+        <v>-0.0001134683294188575</v>
       </c>
       <c r="E29" s="23" t="n">
-        <v>-0.0005794742401245637</v>
+        <v>-0.0006524899175985645</v>
       </c>
       <c r="F29" s="23" t="n">
-        <v>-0.002203470042610615</v>
+        <v>-0.002759143858545993</v>
       </c>
       <c r="G29" s="23" t="n">
-        <v>-0.006903844064610666</v>
+        <v>-0.009579673384750888</v>
       </c>
       <c r="H29" s="23" t="n">
-        <v>-0.01866647666714817</v>
+        <v>-0.02856640732290909</v>
       </c>
       <c r="I29" s="23" t="n">
-        <v>-0.04585560260960065</v>
+        <v>-0.07781941954428664</v>
       </c>
       <c r="J29" s="23" t="n">
-        <v>-0.1089624679449636</v>
+        <v>-0.2118219855188948</v>
       </c>
       <c r="K29" s="23" t="n">
-        <v>-0.2802805982459644</v>
+        <v>-0.7212367400763886</v>
       </c>
       <c r="L29" s="23" t="n">
-        <v>-1.19805001995736</v>
+        <v>9.218921610207705</v>
       </c>
       <c r="M29" s="23" t="n">
-        <v>1.632133615624175</v>
+        <v>1.205392277129463</v>
       </c>
       <c r="N29" s="23" t="n">
-        <v>0.6934600102610484</v>
+        <v>0.8338316167853937</v>
       </c>
       <c r="O29" s="23" t="n">
-        <v>0.5113487017700289</v>
+        <v>0.7149285971472225</v>
       </c>
     </row>
     <row r="30" ht="15.5" customHeight="1">
@@ -22072,40 +22072,40 @@
         </is>
       </c>
       <c r="D30" s="23" t="n">
-        <v>-23.76666666666666</v>
+        <v>-161.4769087999999</v>
       </c>
       <c r="E30" s="23" t="n">
-        <v>-25.61316666666663</v>
+        <v>-157.9305364599467</v>
       </c>
       <c r="F30" s="23" t="n">
-        <v>-26.99400000000004</v>
+        <v>-169.6082878839468</v>
       </c>
       <c r="G30" s="23" t="n">
-        <v>-26.88249999999998</v>
+        <v>-180.0169735424</v>
       </c>
       <c r="H30" s="23" t="n">
-        <v>-22.85199999999999</v>
+        <v>-187.09498978304</v>
       </c>
       <c r="I30" s="23" t="n">
-        <v>-9.862499999999992</v>
+        <v>-186.5720832768</v>
       </c>
       <c r="J30" s="23" t="n">
-        <v>21.59266666666669</v>
+        <v>-170.4116553932799</v>
       </c>
       <c r="K30" s="23" t="n">
-        <v>88.15350000000007</v>
+        <v>-124.5736887074134</v>
       </c>
       <c r="L30" s="23" t="n">
-        <v>217.26</v>
+        <v>-25.94340961280001</v>
       </c>
       <c r="M30" s="23" t="n">
-        <v>452.0188333333334</v>
+        <v>161.7402249369602</v>
       </c>
       <c r="N30" s="23" t="n">
-        <v>857.4833333333332</v>
+        <v>493.1331544917334</v>
       </c>
       <c r="O30" s="23" t="n">
-        <v>1528.5735</v>
+        <v>1047.899919860053</v>
       </c>
     </row>
     <row r="31" ht="15.5" customHeight="1">
@@ -22125,40 +22125,40 @@
         </is>
       </c>
       <c r="D31" s="23" t="n">
-        <v>-131.962962962958</v>
+        <v>1.374075162764872</v>
       </c>
       <c r="E31" s="23" t="n">
-        <v>0.1849476544017561</v>
+        <v>1.188363849171413</v>
       </c>
       <c r="F31" s="23" t="n">
-        <v>0.179879602396872</v>
+        <v>1.187004413446943</v>
       </c>
       <c r="G31" s="23" t="n">
-        <v>0.1638868811503243</v>
+        <v>1.182473651671148</v>
       </c>
       <c r="H31" s="23" t="n">
-        <v>0.1207342830706524</v>
+        <v>1.169781504385126</v>
       </c>
       <c r="I31" s="23" t="n">
-        <v>0.01401874170688471</v>
+        <v>1.136815094435264</v>
       </c>
       <c r="J31" s="23" t="n">
-        <v>-0.2490651028901572</v>
+        <v>1.047080660411106</v>
       </c>
       <c r="K31" s="23" t="n">
-        <v>-0.9995038386149431</v>
+        <v>0.7061163812320046</v>
       </c>
       <c r="L31" s="23" t="n">
-        <v>-5.163845053008695</v>
+        <v>7.357577886627397</v>
       </c>
       <c r="M31" s="23" t="n">
-        <v>7.85966709434017</v>
+        <v>1.995132020743535</v>
       </c>
       <c r="N31" s="23" t="n">
-        <v>3.610793698028487</v>
+        <v>1.74638398958346</v>
       </c>
       <c r="O31" s="23" t="n">
-        <v>2.833172002515824</v>
+        <v>1.666703332036992</v>
       </c>
     </row>
     <row r="32" ht="15.5" customHeight="1">
@@ -22231,40 +22231,40 @@
         </is>
       </c>
       <c r="D33" s="23" t="n">
-        <v>-23.75333333333333</v>
+        <v>-161.4635754666666</v>
       </c>
       <c r="E33" s="23" t="n">
-        <v>-25.53316666666663</v>
+        <v>-157.84386979328</v>
       </c>
       <c r="F33" s="23" t="n">
-        <v>-26.66733333333337</v>
+        <v>-169.2149545506134</v>
       </c>
       <c r="G33" s="23" t="n">
-        <v>-25.79583333333331</v>
+        <v>-178.5703068757333</v>
       </c>
       <c r="H33" s="23" t="n">
-        <v>-19.79199999999999</v>
+        <v>-182.63498978304</v>
       </c>
       <c r="I33" s="23" t="n">
-        <v>-2.309166666666659</v>
+        <v>-174.6187499434667</v>
       </c>
       <c r="J33" s="23" t="n">
-        <v>38.38600000000002</v>
+        <v>-141.7383220599466</v>
       </c>
       <c r="K33" s="23" t="n">
-        <v>122.5068333333334</v>
+        <v>-61.62702204074672</v>
       </c>
       <c r="L33" s="23" t="n">
-        <v>282.8933333333333</v>
+        <v>102.5499237205333</v>
       </c>
       <c r="M33" s="23" t="n">
-        <v>570.4855000000001</v>
+        <v>408.6068916036269</v>
       </c>
       <c r="N33" s="23" t="n">
-        <v>1061.31</v>
+        <v>943.7264878250667</v>
       </c>
       <c r="O33" s="23" t="n">
-        <v>1865.220166666667</v>
+        <v>1835.033253193386</v>
       </c>
     </row>
     <row r="34" ht="15.5" customHeight="1">
@@ -22284,40 +22284,40 @@
         </is>
       </c>
       <c r="D34" s="23" t="n">
-        <v>456.0666666666667</v>
+        <v>438.8467568640001</v>
       </c>
       <c r="E34" s="23" t="n">
-        <v>632.6530133333334</v>
+        <v>485.9977062788608</v>
       </c>
       <c r="F34" s="23" t="n">
-        <v>681.86368</v>
+        <v>523.8088683221674</v>
       </c>
       <c r="G34" s="23" t="n">
-        <v>732.0543999999999</v>
+        <v>562.404360657664</v>
       </c>
       <c r="H34" s="23" t="n">
-        <v>784.77824</v>
+        <v>603.0464533049343</v>
       </c>
       <c r="I34" s="23" t="n">
-        <v>843.2608</v>
+        <v>648.3766308564481</v>
       </c>
       <c r="J34" s="23" t="n">
-        <v>913.5863466666665</v>
+        <v>703.4085743215276</v>
       </c>
       <c r="K34" s="23" t="n">
-        <v>1006.40448</v>
+        <v>776.9641620820821</v>
       </c>
       <c r="L34" s="23" t="n">
-        <v>1139.2768</v>
+        <v>883.6559497134082</v>
       </c>
       <c r="M34" s="23" t="n">
-        <v>1339.791573333333</v>
+        <v>1046.527042619068</v>
       </c>
       <c r="N34" s="23" t="n">
-        <v>1649.582933333333</v>
+        <v>1300.466729624576</v>
       </c>
       <c r="O34" s="23" t="n">
-        <v>2129.39968</v>
+        <v>1696.527699870328</v>
       </c>
     </row>
     <row r="35" ht="15.5" customHeight="1">
@@ -22390,40 +22390,40 @@
         </is>
       </c>
       <c r="D36" s="23" t="n">
-        <v>0</v>
+        <v>-122.0921844053334</v>
       </c>
       <c r="E36" s="23" t="n">
-        <v>-177.1428437333334</v>
+        <v>-139.1173575281077</v>
       </c>
       <c r="F36" s="23" t="n">
-        <v>-190.9218304</v>
+        <v>-149.9407925215669</v>
       </c>
       <c r="G36" s="23" t="n">
-        <v>-204.9752319999999</v>
+        <v>-160.9885462129459</v>
       </c>
       <c r="H36" s="23" t="n">
-        <v>-219.7379072</v>
+        <v>-172.6215120338616</v>
       </c>
       <c r="I36" s="23" t="n">
-        <v>-236.113024</v>
+        <v>-185.5947950014054</v>
       </c>
       <c r="J36" s="23" t="n">
-        <v>-255.8041770666666</v>
+        <v>-201.341442446721</v>
       </c>
       <c r="K36" s="23" t="n">
-        <v>-281.7932544</v>
+        <v>-222.382719695943</v>
       </c>
       <c r="L36" s="23" t="n">
-        <v>-318.997504</v>
+        <v>-252.8944731133543</v>
       </c>
       <c r="M36" s="23" t="n">
-        <v>-375.1416405333333</v>
+        <v>-299.4612510684855</v>
       </c>
       <c r="N36" s="23" t="n">
-        <v>-461.8832213333332</v>
+        <v>-372.0519815407477</v>
       </c>
       <c r="O36" s="23" t="n">
-        <v>-596.2319103999999</v>
+        <v>-485.2531332270518</v>
       </c>
     </row>
     <row r="37" ht="15.5" customHeight="1">
@@ -22496,40 +22496,40 @@
         </is>
       </c>
       <c r="D38" s="23" t="n">
-        <v>-23.75333333333333</v>
+        <v>-291.9654832639999</v>
       </c>
       <c r="E38" s="23" t="n">
-        <v>-163.9260133333333</v>
+        <v>-305.8360430932309</v>
       </c>
       <c r="F38" s="23" t="n">
-        <v>-175.8250133333334</v>
+        <v>-328.7119258273111</v>
       </c>
       <c r="G38" s="23" t="n">
-        <v>-185.9327333333333</v>
+        <v>-349.7749920387413</v>
       </c>
       <c r="H38" s="23" t="n">
-        <v>-191.46224</v>
+        <v>-366.0556515258369</v>
       </c>
       <c r="I38" s="23" t="n">
-        <v>-186.7724666666667</v>
+        <v>-371.3812167661227</v>
       </c>
       <c r="J38" s="23" t="n">
-        <v>-161.4610133333333</v>
+        <v>-354.1071824852307</v>
       </c>
       <c r="K38" s="23" t="n">
-        <v>-97.6441466666666</v>
+        <v>-293.8214327097003</v>
       </c>
       <c r="L38" s="23" t="n">
-        <v>33.67653333333331</v>
+        <v>-156.8579844512427</v>
       </c>
       <c r="M38" s="23" t="n">
-        <v>277.4060933333334</v>
+        <v>109.6929052698968</v>
       </c>
       <c r="N38" s="23" t="n">
-        <v>700.4637333333335</v>
+        <v>585.7078914614611</v>
       </c>
       <c r="O38" s="23" t="n">
-        <v>1399.413986666667</v>
+        <v>1387.773023761169</v>
       </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
@@ -22549,40 +22549,40 @@
         </is>
       </c>
       <c r="D39" s="23" t="n">
-        <v>-131.962962962958</v>
+        <v>2.399462916816149</v>
       </c>
       <c r="E39" s="23" t="n">
-        <v>1.18738627516228</v>
+        <v>2.246483872423032</v>
       </c>
       <c r="F39" s="23" t="n">
-        <v>1.185995355984526</v>
+        <v>2.249502862918447</v>
       </c>
       <c r="G39" s="23" t="n">
-        <v>1.181273555926537</v>
+        <v>2.258951316983717</v>
       </c>
       <c r="H39" s="23" t="n">
-        <v>1.167949488758145</v>
+        <v>2.28483369519425</v>
       </c>
       <c r="I39" s="23" t="n">
-        <v>1.13387873034619</v>
+        <v>2.351280037973768</v>
       </c>
       <c r="J39" s="23" t="n">
-        <v>1.047629445595157</v>
+        <v>2.530710992329255</v>
       </c>
       <c r="K39" s="23" t="n">
-        <v>0.7966551477668351</v>
+        <v>3.209257967474768</v>
       </c>
       <c r="L39" s="23" t="n">
-        <v>-0.6147207429978873</v>
+        <v>-9.994761010694262</v>
       </c>
       <c r="M39" s="23" t="n">
-        <v>3.821866714476455</v>
+        <v>0.6539026242995314</v>
       </c>
       <c r="N39" s="23" t="n">
-        <v>2.383120892121536</v>
+        <v>1.149870907201261</v>
       </c>
       <c r="O39" s="23" t="n">
-        <v>2.125636746700262</v>
+        <v>1.310184059045513</v>
       </c>
     </row>
     <row r="40" ht="15.5" customHeight="1">
@@ -22869,40 +22869,40 @@
         </is>
       </c>
       <c r="D45" s="22" t="n">
-        <v>-23.75333333333333</v>
+        <v>-10.01157546666701</v>
       </c>
       <c r="E45" s="22" t="n">
-        <v>-24.53316666666663</v>
+        <v>35.7125199633067</v>
       </c>
       <c r="F45" s="22" t="n">
-        <v>-24.66733333333337</v>
+        <v>38.49506767530653</v>
       </c>
       <c r="G45" s="22" t="n">
-        <v>-22.79583333333331</v>
+        <v>41.3512307711996</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>-15.79199999999999</v>
+        <v>44.40892209151991</v>
       </c>
       <c r="I45" s="22" t="n">
-        <v>2.690833333333341</v>
+        <v>47.94534563840034</v>
       </c>
       <c r="J45" s="22" t="n">
-        <v>44.38600000000002</v>
+        <v>52.50151409663965</v>
       </c>
       <c r="K45" s="22" t="n">
-        <v>129.5068333333334</v>
+        <v>59.0512374203733</v>
       </c>
       <c r="L45" s="22" t="n">
-        <v>249.2364563232742</v>
+        <v>69.23812080640019</v>
       </c>
       <c r="M45" s="22" t="n">
-        <v>293.0841515880621</v>
+        <v>85.69511473151982</v>
       </c>
       <c r="N45" s="22" t="n">
-        <v>360.8243215344255</v>
+        <v>112.462164087466</v>
       </c>
       <c r="O45" s="22" t="n">
-        <v>465.7422987496529</v>
+        <v>155.5185078033071</v>
       </c>
     </row>
     <row r="46" ht="15.5" customHeight="1">
@@ -22922,40 +22922,40 @@
         </is>
       </c>
       <c r="D46" s="22" t="n">
-        <v>-23.75333333333333</v>
+        <v>-10.01157546666701</v>
       </c>
       <c r="E46" s="22" t="n">
-        <v>1998.466833333333</v>
+        <v>23.12734224938617</v>
       </c>
       <c r="F46" s="22" t="n">
-        <v>1998.332666666667</v>
+        <v>24.9382849587202</v>
       </c>
       <c r="G46" s="22" t="n">
-        <v>2000.204166666667</v>
+        <v>26.83209253759981</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>2007.208</v>
+        <v>28.96902378496009</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>2025.690833333333</v>
+        <v>31.71159528320038</v>
       </c>
       <c r="J46" s="22" t="n">
-        <v>2067.386</v>
+        <v>35.79024331605382</v>
       </c>
       <c r="K46" s="22" t="n">
-        <v>2152.506833333333</v>
+        <v>42.55252536191972</v>
       </c>
       <c r="L46" s="22" t="n">
-        <v>2272.407859607966</v>
+        <v>54.31770014720021</v>
       </c>
       <c r="M46" s="22" t="n">
-        <v>2316.324432591731</v>
+        <v>74.86018117162646</v>
       </c>
       <c r="N46" s="22" t="n">
-        <v>2384.178689013023</v>
+        <v>110.0470145450656</v>
       </c>
       <c r="O46" s="22" t="n">
-        <v>2489.276966959546</v>
+        <v>168.6561879027199</v>
       </c>
     </row>
     <row r="47" ht="15.5" customHeight="1">
@@ -23187,40 +23187,40 @@
         </is>
       </c>
       <c r="D51" s="22" t="n">
-        <v>-23.75333333333333</v>
+        <v>-101.9546154666664</v>
       </c>
       <c r="E51" s="22" t="n">
-        <v>-24.53316666666663</v>
+        <v>46.56251914197338</v>
       </c>
       <c r="F51" s="22" t="n">
-        <v>-24.66733333333337</v>
+        <v>50.18902978730648</v>
       </c>
       <c r="G51" s="22" t="n">
-        <v>-22.79583333333331</v>
+        <v>53.90596373119956</v>
       </c>
       <c r="H51" s="22" t="n">
-        <v>-15.79199999999999</v>
+        <v>57.86786890752001</v>
       </c>
       <c r="I51" s="22" t="n">
-        <v>2.690833333333341</v>
+        <v>62.4072683584003</v>
       </c>
       <c r="J51" s="22" t="n">
-        <v>44.38600000000002</v>
+        <v>68.16951994197296</v>
       </c>
       <c r="K51" s="22" t="n">
-        <v>129.5068333333334</v>
+        <v>76.31107425237332</v>
       </c>
       <c r="L51" s="22" t="n">
-        <v>249.1496593636279</v>
+        <v>88.77671792640018</v>
       </c>
       <c r="M51" s="22" t="n">
-        <v>293.1039887821267</v>
+        <v>108.6725402141864</v>
       </c>
       <c r="N51" s="22" t="n">
-        <v>361.0329336440127</v>
+        <v>140.7525113941326</v>
       </c>
       <c r="O51" s="22" t="n">
-        <v>466.2148446304259</v>
+        <v>192.0377123153071</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -23240,40 +23240,40 @@
         </is>
       </c>
       <c r="D52" s="22" t="n">
-        <v>-23.75333333333333</v>
+        <v>-271.9423323306668</v>
       </c>
       <c r="E52" s="22" t="n">
-        <v>714.5739866666668</v>
+        <v>589.2253120264193</v>
       </c>
       <c r="F52" s="22" t="n">
-        <v>-175.8250133333334</v>
+        <v>-310.8630983262209</v>
       </c>
       <c r="G52" s="22" t="n">
-        <v>-185.9327333333333</v>
+        <v>-330.6159634885973</v>
       </c>
       <c r="H52" s="22" t="n">
-        <v>-191.46224</v>
+        <v>-345.5294767058944</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>-186.7724666666667</v>
+        <v>-349.3617315263147</v>
       </c>
       <c r="J52" s="22" t="n">
-        <v>-161.4610133333333</v>
+        <v>-330.3405610829141</v>
       </c>
       <c r="K52" s="22" t="n">
-        <v>-97.6441466666666</v>
+        <v>-267.8346925426688</v>
       </c>
       <c r="L52" s="22" t="n">
-        <v>33.67653333333331</v>
+        <v>-127.8227856472749</v>
       </c>
       <c r="M52" s="22" t="n">
-        <v>277.4060933333334</v>
+        <v>143.154997926639</v>
       </c>
       <c r="N52" s="22" t="n">
-        <v>700.4637333333335</v>
+        <v>625.7948365236905</v>
       </c>
       <c r="O52" s="22" t="n">
-        <v>1399.413986666667</v>
+        <v>1437.865032781619</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -23399,40 +23399,40 @@
         </is>
       </c>
       <c r="D55" s="22" t="n">
-        <v>-23.75333333333333</v>
+        <v>-281.9539077973333</v>
       </c>
       <c r="E55" s="22" t="n">
-        <v>-163.9260133333333</v>
+        <v>-298.3881646169942</v>
       </c>
       <c r="F55" s="22" t="n">
-        <v>-175.8250133333334</v>
+        <v>-320.6807998336343</v>
       </c>
       <c r="G55" s="22" t="n">
-        <v>-185.9327333333333</v>
+        <v>-341.1337151749973</v>
       </c>
       <c r="H55" s="22" t="n">
-        <v>-191.46224</v>
+        <v>-356.7252320313344</v>
       </c>
       <c r="I55" s="22" t="n">
-        <v>-186.7724666666667</v>
+        <v>-361.1647866111147</v>
       </c>
       <c r="J55" s="22" t="n">
-        <v>-161.4610133333333</v>
+        <v>-342.570293992994</v>
       </c>
       <c r="K55" s="22" t="n">
-        <v>-97.6441466666666</v>
+        <v>-280.0912381482156</v>
       </c>
       <c r="L55" s="22" t="n">
-        <v>33.67653333333331</v>
+        <v>-139.3069832280748</v>
       </c>
       <c r="M55" s="22" t="n">
-        <v>277.4060933333334</v>
+        <v>133.920520521199</v>
       </c>
       <c r="N55" s="22" t="n">
-        <v>700.4637333333335</v>
+        <v>621.3774514527572</v>
       </c>
       <c r="O55" s="22" t="n">
-        <v>1399.413986666667</v>
+        <v>1442.507055658206</v>
       </c>
     </row>
     <row r="56" ht="15.5" customHeight="1">
@@ -24035,40 +24035,40 @@
         </is>
       </c>
       <c r="D67" s="22" t="n">
-        <v>-47.75333333333333</v>
+        <v>-328.8947178666666</v>
       </c>
       <c r="E67" s="22" t="n">
-        <v>688.5674866666668</v>
+        <v>566.2562891297794</v>
       </c>
       <c r="F67" s="22" t="n">
-        <v>-203.8390133333334</v>
+        <v>-335.6080156015275</v>
       </c>
       <c r="G67" s="22" t="n">
-        <v>-215.9552333333333</v>
+        <v>-357.1513622597974</v>
       </c>
       <c r="H67" s="22" t="n">
-        <v>-223.49424</v>
+        <v>-373.9027315974144</v>
       </c>
       <c r="I67" s="22" t="n">
-        <v>-220.8149666666667</v>
+        <v>-379.6998531647147</v>
       </c>
       <c r="J67" s="22" t="n">
-        <v>-197.5150133333333</v>
+        <v>-362.9389114462207</v>
       </c>
       <c r="K67" s="22" t="n">
-        <v>-135.7106466666666</v>
+        <v>-303.3101555630422</v>
       </c>
       <c r="L67" s="22" t="n">
-        <v>-6.403466666666688</v>
+        <v>-167.3602024536748</v>
       </c>
       <c r="M67" s="22" t="n">
-        <v>235.3115933333334</v>
+        <v>97.42761706178571</v>
       </c>
       <c r="N67" s="22" t="n">
-        <v>656.3537333333335</v>
+        <v>570.2596271028907</v>
       </c>
       <c r="O67" s="22" t="n">
-        <v>1353.287486666667</v>
+        <v>1366.645755378312</v>
       </c>
     </row>
     <row r="68" ht="15.5" customHeight="1">
@@ -24196,40 +24196,40 @@
         </is>
       </c>
       <c r="D70" s="22" t="n">
-        <v>-23.75333333333333</v>
+        <v>-161.4635754666666</v>
       </c>
       <c r="E70" s="22" t="n">
-        <v>-25.53316666666663</v>
+        <v>-166.9568237700267</v>
       </c>
       <c r="F70" s="22" t="n">
-        <v>-26.66733333333337</v>
+        <v>-179.0274293913601</v>
       </c>
       <c r="G70" s="22" t="n">
-        <v>-25.79583333333331</v>
+        <v>-189.0598345621333</v>
       </c>
       <c r="H70" s="22" t="n">
-        <v>-19.79199999999999</v>
+        <v>-193.7209851084801</v>
       </c>
       <c r="I70" s="22" t="n">
-        <v>-2.309166666666659</v>
+        <v>-186.0768450282667</v>
       </c>
       <c r="J70" s="22" t="n">
-        <v>38.38600000000002</v>
+        <v>-153.0366629700265</v>
       </c>
       <c r="K70" s="22" t="n">
-        <v>122.5068333333334</v>
+        <v>-71.64185031296005</v>
       </c>
       <c r="L70" s="22" t="n">
-        <v>282.8933333333333</v>
+        <v>95.99395013973329</v>
       </c>
       <c r="M70" s="22" t="n">
-        <v>570.4855000000001</v>
+        <v>409.4389741981868</v>
       </c>
       <c r="N70" s="22" t="n">
-        <v>1061.31</v>
+        <v>958.6556094207999</v>
       </c>
       <c r="O70" s="22" t="n">
-        <v>1865.220166666667</v>
+        <v>1874.99343073664</v>
       </c>
     </row>
     <row r="71" ht="15.5" customHeight="1">
@@ -24249,40 +24249,40 @@
         </is>
       </c>
       <c r="D71" s="22" t="n">
-        <v>0</v>
+        <v>-130.5019077973333</v>
       </c>
       <c r="E71" s="22" t="n">
-        <v>-138.3928466666667</v>
+        <v>-138.8792193232042</v>
       </c>
       <c r="F71" s="22" t="n">
-        <v>-149.15768</v>
+        <v>-149.684496435951</v>
       </c>
       <c r="G71" s="22" t="n">
-        <v>-160.1369</v>
+        <v>-160.715157476608</v>
       </c>
       <c r="H71" s="22" t="n">
-        <v>-171.67024</v>
+        <v>-172.3346664173568</v>
       </c>
       <c r="I71" s="22" t="n">
-        <v>-184.4633</v>
+        <v>-185.304371737856</v>
       </c>
       <c r="J71" s="22" t="n">
-        <v>-199.8470133333333</v>
+        <v>-201.0705195152042</v>
       </c>
       <c r="K71" s="22" t="n">
-        <v>-220.15098</v>
+        <v>-222.1795823967403</v>
       </c>
       <c r="L71" s="22" t="n">
-        <v>-249.2168</v>
+        <v>-252.851934590976</v>
       </c>
       <c r="M71" s="22" t="n">
-        <v>-293.0794066666667</v>
+        <v>-299.74606892829</v>
       </c>
       <c r="N71" s="22" t="n">
-        <v>-360.8462666666665</v>
+        <v>-372.9477179593388</v>
       </c>
       <c r="O71" s="22" t="n">
-        <v>-465.80618</v>
+        <v>-487.2204069754711</v>
       </c>
     </row>
     <row r="72" ht="15.5" customHeight="1">
@@ -24355,40 +24355,40 @@
         </is>
       </c>
       <c r="D73" s="22" t="n">
-        <v>-23.75333333333333</v>
+        <v>-281.9539077973333</v>
       </c>
       <c r="E73" s="22" t="n">
-        <v>-163.9260133333333</v>
+        <v>-298.3881646169942</v>
       </c>
       <c r="F73" s="22" t="n">
-        <v>-175.8250133333334</v>
+        <v>-320.6807998336343</v>
       </c>
       <c r="G73" s="22" t="n">
-        <v>-185.9327333333333</v>
+        <v>-341.1337151749973</v>
       </c>
       <c r="H73" s="22" t="n">
-        <v>-191.46224</v>
+        <v>-356.7252320313344</v>
       </c>
       <c r="I73" s="22" t="n">
-        <v>-186.7724666666667</v>
+        <v>-361.1647866111147</v>
       </c>
       <c r="J73" s="22" t="n">
-        <v>-161.4610133333333</v>
+        <v>-342.570293992994</v>
       </c>
       <c r="K73" s="22" t="n">
-        <v>-97.6441466666666</v>
+        <v>-280.0912381482156</v>
       </c>
       <c r="L73" s="22" t="n">
-        <v>33.67653333333331</v>
+        <v>-139.3069832280748</v>
       </c>
       <c r="M73" s="22" t="n">
-        <v>277.4060933333334</v>
+        <v>133.920520521199</v>
       </c>
       <c r="N73" s="22" t="n">
-        <v>700.4637333333335</v>
+        <v>621.3774514527572</v>
       </c>
       <c r="O73" s="22" t="n">
-        <v>1399.413986666667</v>
+        <v>1442.507055658206</v>
       </c>
     </row>
     <row r="74" ht="15.5" customHeight="1">
@@ -24514,40 +24514,40 @@
         </is>
       </c>
       <c r="D76" s="22" t="n">
-        <v>-23.75333333333333</v>
+        <v>-271.9423323306668</v>
       </c>
       <c r="E76" s="22" t="n">
-        <v>-163.9260133333333</v>
+        <v>-289.2746879735808</v>
       </c>
       <c r="F76" s="22" t="n">
-        <v>-175.8250133333334</v>
+        <v>-310.8630983262209</v>
       </c>
       <c r="G76" s="22" t="n">
-        <v>-185.9327333333333</v>
+        <v>-330.6159634885973</v>
       </c>
       <c r="H76" s="22" t="n">
-        <v>-191.46224</v>
+        <v>-345.5294767058944</v>
       </c>
       <c r="I76" s="22" t="n">
-        <v>-186.7724666666667</v>
+        <v>-349.3617315263147</v>
       </c>
       <c r="J76" s="22" t="n">
-        <v>-161.4610133333333</v>
+        <v>-330.3405610829141</v>
       </c>
       <c r="K76" s="22" t="n">
-        <v>-97.6441466666666</v>
+        <v>-267.8346925426688</v>
       </c>
       <c r="L76" s="22" t="n">
-        <v>33.67653333333331</v>
+        <v>-127.8227856472749</v>
       </c>
       <c r="M76" s="22" t="n">
-        <v>277.4060933333334</v>
+        <v>143.154997926639</v>
       </c>
       <c r="N76" s="22" t="n">
-        <v>700.4637333333335</v>
+        <v>625.7948365236905</v>
       </c>
       <c r="O76" s="22" t="n">
-        <v>1399.413986666667</v>
+        <v>1437.865032781619</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -24620,7 +24620,7 @@
         </is>
       </c>
       <c r="D78" s="22" t="n">
-        <v>0</v>
+        <v>2023</v>
       </c>
       <c r="E78" s="22" t="n">
         <v>2024</v>
@@ -24779,40 +24779,40 @@
         </is>
       </c>
       <c r="D81" s="22" t="n">
-        <v>-1999.246666666667</v>
+        <v>-1698.0821312</v>
       </c>
       <c r="E81" s="22" t="n">
-        <v>0</v>
+        <v>-1716.915151028053</v>
       </c>
       <c r="F81" s="22" t="n">
-        <v>0</v>
+        <v>-1694.952070004053</v>
       </c>
       <c r="G81" s="22" t="n">
-        <v>0</v>
+        <v>-1674.838860164267</v>
       </c>
       <c r="H81" s="22" t="n">
-        <v>0</v>
+        <v>-1659.62782340096</v>
       </c>
       <c r="I81" s="22" t="n">
-        <v>-2.690833333333341</v>
+        <v>-1655.688027336533</v>
       </c>
       <c r="J81" s="22" t="n">
-        <v>-44.38600000000002</v>
+        <v>-1675.073058761387</v>
       </c>
       <c r="K81" s="22" t="n">
-        <v>-129.5068333333334</v>
+        <v>-1738.968294460587</v>
       </c>
       <c r="L81" s="22" t="n">
-        <v>-290.8933333333333</v>
+        <v>-1882.395326600533</v>
       </c>
       <c r="M81" s="22" t="n">
-        <v>-579.4855000000001</v>
+        <v>-2160.502059454294</v>
       </c>
       <c r="N81" s="22" t="n">
-        <v>-1071.31</v>
+        <v>-2656.684540518399</v>
       </c>
       <c r="O81" s="22" t="n">
-        <v>-1876.220166666667</v>
+        <v>-3492.844135348053</v>
       </c>
     </row>
     <row r="82" ht="15.5" customHeight="1">
@@ -24835,7 +24835,7 @@
         <v>0</v>
       </c>
       <c r="E82" s="22" t="n">
-        <v>878.5</v>
+        <v>1316.39583041164</v>
       </c>
       <c r="F82" s="22" t="n">
         <v>0</v>
@@ -24885,40 +24885,40 @@
         </is>
       </c>
       <c r="D83" s="22" t="n">
-        <v>-1999.246666666667</v>
+        <v>324.9178688</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>26.53316666666706</v>
+        <v>316.1978029486929</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>28.66733333333309</v>
+        <v>339.860404836694</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>28.79583333333289</v>
+        <v>361.6506675221331</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>23.79199999999992</v>
+        <v>378.45817192448</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>7.309166666666897</v>
+        <v>383.7700677482669</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>-32.38599999999997</v>
+        <v>365.2252821486929</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>-115.5068333333329</v>
+        <v>301.0465338116269</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>-274.893333333333</v>
+        <v>155.1606469802671</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>-561.4854999999998</v>
+        <v>-129.3341420488541</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>-1051.31</v>
+        <v>-638.6136621141331</v>
       </c>
       <c r="O83" s="22" t="n">
-        <v>-1854.220166666667</v>
+        <v>-1498.804312891307</v>
       </c>
     </row>
     <row r="84" ht="15.5" customHeight="1">
@@ -24938,40 +24938,40 @@
         </is>
       </c>
       <c r="D84" s="22" t="n">
-        <v>1999.246666666667</v>
+        <v>17.21990980266611</v>
       </c>
       <c r="E84" s="22" t="n">
-        <v>-2161.392846666666</v>
+        <v>16.07311579644619</v>
       </c>
       <c r="F84" s="22" t="n">
-        <v>-2172.15768</v>
+        <v>17.30334439847309</v>
       </c>
       <c r="G84" s="22" t="n">
-        <v>-2183.1369</v>
+        <v>18.47997107353564</v>
       </c>
       <c r="H84" s="22" t="n">
-        <v>-2194.67024</v>
+        <v>19.46974840258559</v>
       </c>
       <c r="I84" s="22" t="n">
-        <v>-2207.4633</v>
+        <v>19.94641350195241</v>
       </c>
       <c r="J84" s="22" t="n">
-        <v>-2222.847013333333</v>
+        <v>19.21671522044579</v>
       </c>
       <c r="K84" s="22" t="n">
-        <v>-2243.150979999999</v>
+        <v>15.9520044369583</v>
       </c>
       <c r="L84" s="22" t="n">
-        <v>-2272.2168</v>
+        <v>7.799264212992099</v>
       </c>
       <c r="M84" s="22" t="n">
-        <v>-2316.079406666666</v>
+        <v>-9.156569604880815</v>
       </c>
       <c r="N84" s="22" t="n">
-        <v>-2383.846266666666</v>
+        <v>-41.10917289710846</v>
       </c>
       <c r="O84" s="22" t="n">
-        <v>-2488.80618</v>
+        <v>-97.45848462168806</v>
       </c>
     </row>
     <row r="85" ht="15.5" customHeight="1">
@@ -25044,40 +25044,40 @@
         </is>
       </c>
       <c r="D86" s="22" t="n">
-        <v>1999.246666666667</v>
+        <v>-25.74405119999972</v>
       </c>
       <c r="E86" s="22" t="n">
-        <v>1859.073986666667</v>
+        <v>8.262460387806414</v>
       </c>
       <c r="F86" s="22" t="n">
-        <v>1847.174986666667</v>
+        <v>8.897131677832419</v>
       </c>
       <c r="G86" s="22" t="n">
-        <v>1837.067266666667</v>
+        <v>9.513139342335592</v>
       </c>
       <c r="H86" s="22" t="n">
-        <v>1831.53776</v>
+        <v>10.06154669506566</v>
       </c>
       <c r="I86" s="22" t="n">
-        <v>1836.227533333333</v>
+        <v>10.4208691435523</v>
       </c>
       <c r="J86" s="22" t="n">
-        <v>1861.538986666667</v>
+        <v>10.33075901180626</v>
       </c>
       <c r="K86" s="22" t="n">
-        <v>1925.355853333333</v>
+        <v>9.289337917917692</v>
       </c>
       <c r="L86" s="22" t="n">
-        <v>2014.904131168475</v>
+        <v>6.404050286592309</v>
       </c>
       <c r="M86" s="22" t="n">
-        <v>2013.811765797599</v>
+        <v>0.185124047598606</v>
       </c>
       <c r="N86" s="22" t="n">
-        <v>2012.654214132232</v>
+        <v>-11.73006295790947</v>
       </c>
       <c r="O86" s="22" t="n">
-        <v>2011.427899281119</v>
+        <v>-32.93419987032712</v>
       </c>
     </row>
     <row r="87" ht="15.5" customHeight="1">
@@ -25097,40 +25097,40 @@
         </is>
       </c>
       <c r="D87" s="22" t="n">
-        <v>1999.246666666667</v>
+        <v>-25.74405119999972</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>1859.073986666667</v>
+        <v>8.262460387806414</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>1847.174986666667</v>
+        <v>8.897131677832419</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>1837.067266666667</v>
+        <v>9.513139342335592</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>1831.53776</v>
+        <v>10.06154669506566</v>
       </c>
       <c r="I87" s="22" t="n">
-        <v>1836.227533333333</v>
+        <v>10.4208691435523</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>1861.538986666667</v>
+        <v>10.33075901180626</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>1925.355853333333</v>
+        <v>9.289337917917692</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>2014.904131168475</v>
+        <v>6.404050286592309</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>2013.811765797599</v>
+        <v>0.185124047598606</v>
       </c>
       <c r="N87" s="22" t="n">
-        <v>2012.654214132232</v>
+        <v>-11.73006295790947</v>
       </c>
       <c r="O87" s="22" t="n">
-        <v>2011.427899281119</v>
+        <v>-32.93419987032712</v>
       </c>
     </row>
     <row r="88" ht="15.5" customHeight="1">
@@ -25208,37 +25208,37 @@
         <v>0.2</v>
       </c>
       <c r="E89" s="22" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F89" s="22" t="n">
-        <v>4.600000000000001</v>
+        <v>5.600000000000001</v>
       </c>
       <c r="G89" s="22" t="n">
-        <v>15.8</v>
+        <v>21.2</v>
       </c>
       <c r="H89" s="22" t="n">
-        <v>45.2</v>
+        <v>66.2</v>
       </c>
       <c r="I89" s="22" t="n">
-        <v>112.4</v>
+        <v>178.4</v>
       </c>
       <c r="J89" s="22" t="n">
-        <v>250.8</v>
+        <v>429</v>
       </c>
       <c r="K89" s="22" t="n">
-        <v>514.1</v>
+        <v>943</v>
       </c>
       <c r="L89" s="22" t="n">
-        <v>983.2</v>
+        <v>1926.1</v>
       </c>
       <c r="M89" s="22" t="n">
-        <v>1775.6</v>
+        <v>3701.6</v>
       </c>
       <c r="N89" s="22" t="n">
-        <v>3055.9</v>
+        <v>6757.400000000001</v>
       </c>
       <c r="O89" s="22" t="n">
-        <v>5048.1</v>
+        <v>11805.4</v>
       </c>
     </row>
     <row r="90" ht="15.5" customHeight="1">
@@ -25258,40 +25258,40 @@
         </is>
       </c>
       <c r="D90" s="22" t="n">
-        <v>1.111111111111069</v>
+        <v>-0.001702024941282863</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>-0.007967770801712752</v>
+        <v>-0.009034475782133971</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>-0.03102845570206784</v>
+        <v>-0.03928272612167177</v>
       </c>
       <c r="G90" s="22" t="n">
-        <v>-0.1003810456020078</v>
+        <v>-0.1403841537488839</v>
       </c>
       <c r="H90" s="22" t="n">
-        <v>-0.2757270409657181</v>
+        <v>-0.4240125929992337</v>
       </c>
       <c r="I90" s="22" t="n">
-        <v>-0.6823702206512506</v>
+        <v>-1.161432050755779</v>
       </c>
       <c r="J90" s="22" t="n">
-        <v>-1.62729973961474</v>
+        <v>-3.169203619656099</v>
       </c>
       <c r="K90" s="22" t="n">
-        <v>-4.194418461815942</v>
+        <v>-10.80480161870421</v>
       </c>
       <c r="L90" s="22" t="n">
-        <v>-17.94702051227135</v>
+        <v>138.1905539593836</v>
       </c>
       <c r="M90" s="22" t="n">
-        <v>24.46271621752069</v>
+        <v>18.07404828391474</v>
       </c>
       <c r="N90" s="22" t="n">
-        <v>10.396796847109</v>
+        <v>12.50469847297405</v>
       </c>
       <c r="O90" s="22" t="n">
-        <v>7.667800210127186</v>
+        <v>10.72247572723192</v>
       </c>
     </row>
     <row r="91" ht="15.5" customHeight="1">
@@ -25367,37 +25367,37 @@
         <v>0.2</v>
       </c>
       <c r="E92" s="22" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F92" s="22" t="n">
-        <v>4.600000000000001</v>
+        <v>5.600000000000001</v>
       </c>
       <c r="G92" s="22" t="n">
-        <v>15.8</v>
+        <v>21.2</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>45.2</v>
+        <v>66.2</v>
       </c>
       <c r="I92" s="22" t="n">
-        <v>112.4</v>
+        <v>178.4</v>
       </c>
       <c r="J92" s="22" t="n">
-        <v>250.8</v>
+        <v>429</v>
       </c>
       <c r="K92" s="22" t="n">
-        <v>514.1</v>
+        <v>943</v>
       </c>
       <c r="L92" s="22" t="n">
-        <v>983.2</v>
+        <v>1926.1</v>
       </c>
       <c r="M92" s="22" t="n">
-        <v>1775.6</v>
+        <v>3701.6</v>
       </c>
       <c r="N92" s="22" t="n">
-        <v>3055.9</v>
+        <v>6757.400000000001</v>
       </c>
       <c r="O92" s="22" t="n">
-        <v>5048.1</v>
+        <v>11805.4</v>
       </c>
     </row>
     <row r="93" ht="15.5" customHeight="1">
@@ -25420,37 +25420,37 @@
         <v>-0.01333333333333333</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>-0.08</v>
+        <v>-0.08666666666666667</v>
       </c>
       <c r="F93" s="22" t="n">
-        <v>-0.3266666666666667</v>
+        <v>-0.3933333333333334</v>
       </c>
       <c r="G93" s="22" t="n">
-        <v>-1.086666666666667</v>
+        <v>-1.446666666666667</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>-3.06</v>
+        <v>-4.46</v>
       </c>
       <c r="I93" s="22" t="n">
-        <v>-7.553333333333333</v>
+        <v>-11.95333333333333</v>
       </c>
       <c r="J93" s="22" t="n">
-        <v>-16.79333333333333</v>
+        <v>-28.67333333333334</v>
       </c>
       <c r="K93" s="22" t="n">
-        <v>-34.35333333333333</v>
+        <v>-62.94666666666667</v>
       </c>
       <c r="L93" s="22" t="n">
-        <v>-65.63333333333334</v>
+        <v>-128.4933333333333</v>
       </c>
       <c r="M93" s="22" t="n">
-        <v>-118.4666666666667</v>
+        <v>-246.8666666666667</v>
       </c>
       <c r="N93" s="22" t="n">
-        <v>-203.8266666666667</v>
+        <v>-450.5933333333333</v>
       </c>
       <c r="O93" s="22" t="n">
-        <v>-336.6466666666666</v>
+        <v>-787.1333333333333</v>
       </c>
     </row>
     <row r="94" ht="15.5" customHeight="1">
@@ -26137,37 +26137,37 @@
         <v>0</v>
       </c>
       <c r="E106" s="24" t="n">
-        <v>1975.493333333334</v>
+        <v>1393.187413333334</v>
       </c>
       <c r="F106" s="24" t="n">
-        <v>1809.787486666666</v>
+        <v>2840.49645071442</v>
       </c>
       <c r="G106" s="24" t="n">
-        <v>1771.221153333334</v>
+        <v>4219.791145355059</v>
       </c>
       <c r="H106" s="24" t="n">
-        <v>1469.263045059581</v>
+        <v>5640.100630598656</v>
       </c>
       <c r="I106" s="24" t="n">
-        <v>1294.860679850404</v>
+        <v>7043.550492138478</v>
       </c>
       <c r="J106" s="24" t="n">
-        <v>1137.058966065056</v>
+        <v>6409.836918105257</v>
       </c>
       <c r="K106" s="24" t="n">
-        <v>2484.721413173426</v>
+        <v>8097.736323208073</v>
       </c>
       <c r="L106" s="24" t="n">
-        <v>5780.217368914447</v>
+        <v>7801.874969065011</v>
       </c>
       <c r="M106" s="24" t="n">
-        <v>5768.368443576807</v>
+        <v>11840.77564404745</v>
       </c>
       <c r="N106" s="24" t="n">
-        <v>6172.961747337247</v>
+        <v>12577.88649999981</v>
       </c>
       <c r="O106" s="24" t="n">
-        <v>7464.624272161158</v>
+        <v>14438.98802824379</v>
       </c>
     </row>
     <row r="107" ht="15.5" customHeight="1">
@@ -26262,40 +26262,40 @@
         </is>
       </c>
       <c r="D108" s="24" t="n">
-        <v>-23.75333333333333</v>
+        <v>-281.9539077973333</v>
       </c>
       <c r="E108" s="25" t="n">
-        <v>-163.9260133333333</v>
+        <v>-298.3881646169942</v>
       </c>
       <c r="F108" s="25" t="n">
-        <v>-175.8250133333334</v>
+        <v>-320.6807998336343</v>
       </c>
       <c r="G108" s="25" t="n">
-        <v>-185.9327333333333</v>
+        <v>-341.1337151749973</v>
       </c>
       <c r="H108" s="25" t="n">
-        <v>-191.46224</v>
+        <v>-356.7252320313344</v>
       </c>
       <c r="I108" s="25" t="n">
-        <v>-186.7724666666667</v>
+        <v>-361.1647866111147</v>
       </c>
       <c r="J108" s="25" t="n">
-        <v>-161.4610133333333</v>
+        <v>-342.570293992994</v>
       </c>
       <c r="K108" s="25" t="n">
-        <v>-97.6441466666666</v>
+        <v>-280.0912381482156</v>
       </c>
       <c r="L108" s="25" t="n">
-        <v>33.67653333333331</v>
+        <v>-139.3069832280748</v>
       </c>
       <c r="M108" s="25" t="n">
-        <v>277.4060933333334</v>
+        <v>133.920520521199</v>
       </c>
       <c r="N108" s="25" t="n">
-        <v>700.4637333333335</v>
+        <v>621.3774514527572</v>
       </c>
       <c r="O108" s="25" t="n">
-        <v>1399.413986666667</v>
+        <v>1442.507055658206</v>
       </c>
     </row>
     <row r="109" ht="15.5" customHeight="1">
@@ -26315,40 +26315,40 @@
         </is>
       </c>
       <c r="D109" s="24" t="n">
-        <v>0</v>
+        <v>1718.105282133333</v>
       </c>
       <c r="E109" s="24" t="n">
-        <v>1860.073986666667</v>
+        <v>1737.762789129779</v>
       </c>
       <c r="F109" s="24" t="n">
-        <v>1849.174986666667</v>
+        <v>1717.405984398473</v>
       </c>
       <c r="G109" s="24" t="n">
-        <v>1840.067266666667</v>
+        <v>1698.871137740203</v>
       </c>
       <c r="H109" s="24" t="n">
-        <v>1835.53776</v>
+        <v>1685.129268402586</v>
       </c>
       <c r="I109" s="24" t="n">
-        <v>1841.227533333333</v>
+        <v>1682.342646835285</v>
       </c>
       <c r="J109" s="24" t="n">
-        <v>1867.538986666667</v>
+        <v>1702.115088553779</v>
       </c>
       <c r="K109" s="24" t="n">
-        <v>1932.355853333333</v>
+        <v>1764.756344436958</v>
       </c>
       <c r="L109" s="24" t="n">
-        <v>2064.676533333333</v>
+        <v>1903.719797546325</v>
       </c>
       <c r="M109" s="24" t="n">
-        <v>2309.406093333334</v>
+        <v>2171.522117061786</v>
       </c>
       <c r="N109" s="24" t="n">
-        <v>2733.463733333333</v>
+        <v>2647.369627102891</v>
       </c>
       <c r="O109" s="24" t="n">
-        <v>3433.413986666667</v>
+        <v>3446.772255378312</v>
       </c>
     </row>
     <row r="110" ht="15.5" customHeight="1">
@@ -26368,40 +26368,40 @@
         </is>
       </c>
       <c r="D110" s="24" t="n">
-        <v>1975.493333333334</v>
+        <v>1426.139798869333</v>
       </c>
       <c r="E110" s="24" t="n">
-        <v>-187.6793466666666</v>
+        <v>2836.56035212114</v>
       </c>
       <c r="F110" s="24" t="n">
-        <v>1773.35532</v>
+        <v>4214.587783469192</v>
       </c>
       <c r="G110" s="24" t="n">
-        <v>1736.446100000001</v>
+        <v>5620.334608963669</v>
       </c>
       <c r="H110" s="24" t="n">
-        <v>1440.790832807028</v>
+        <v>7007.906473817839</v>
       </c>
       <c r="I110" s="24" t="n">
-        <v>1286.2292736995</v>
+        <v>6409.842856788566</v>
       </c>
       <c r="J110" s="24" t="n">
-        <v>943.1451277893186</v>
+        <v>8008.914464648927</v>
       </c>
       <c r="K110" s="24" t="n">
-        <v>4315.765156875953</v>
+        <v>7706.30694830768</v>
       </c>
       <c r="L110" s="24" t="n">
-        <v>4425.466135655603</v>
+        <v>11740.74093849352</v>
       </c>
       <c r="M110" s="24" t="n">
-        <v>4986.971683258218</v>
+        <v>10481.36169338691</v>
       </c>
       <c r="N110" s="24" t="n">
-        <v>6359.283280405538</v>
+        <v>14354.6234550423</v>
       </c>
       <c r="O110" s="24" t="n">
-        <v>9228.638944103619</v>
+        <v>17885.59276065106</v>
       </c>
     </row>
     <row r="111" ht="15.5" customHeight="1">
@@ -26710,40 +26710,40 @@
         </is>
       </c>
       <c r="D116" s="22" t="n">
-        <v>1.693910392140256e-05</v>
+        <v>7.741346142680751e-06</v>
       </c>
       <c r="E116" s="22" t="n">
-        <v>9.316507156771407e-05</v>
+        <v>4.64480768560845e-05</v>
       </c>
       <c r="F116" s="22" t="n">
-        <v>0.000389599390192259</v>
+        <v>0.0002167576919950611</v>
       </c>
       <c r="G116" s="22" t="n">
-        <v>0.001338189209790802</v>
+        <v>0.0008205826911241595</v>
       </c>
       <c r="H116" s="22" t="n">
-        <v>0.003828237486236978</v>
+        <v>0.002562385573227328</v>
       </c>
       <c r="I116" s="22" t="n">
-        <v>0.009519776403828237</v>
+        <v>0.006905280759271229</v>
       </c>
       <c r="J116" s="22" t="n">
-        <v>0.02124163631743881</v>
+        <v>0.01660518747605021</v>
       </c>
       <c r="K116" s="22" t="n">
-        <v>0.04354196662996528</v>
+        <v>0.03650044706273974</v>
       </c>
       <c r="L116" s="22" t="n">
-        <v>0.08327263487761498</v>
+        <v>0.07455303402708696</v>
       </c>
       <c r="M116" s="22" t="n">
-        <v>0.1503853646142119</v>
+        <v>0.1432768344087353</v>
       </c>
       <c r="N116" s="22" t="n">
-        <v>0.2588210383670704</v>
+        <v>0.2615568621227545</v>
       </c>
       <c r="O116" s="22" t="n">
-        <v>0.4275514525281613</v>
+        <v>0.4569484387640166</v>
       </c>
     </row>
     <row r="117" ht="15.5" customHeight="1">

--- a/backend/Rwanda/financial-statements-CleanStep.xlsx
+++ b/backend/Rwanda/financial-statements-CleanStep.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/Rwanda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_5C276E48EE321F23732C7DB1B9E97F9D1C40C98D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB7E8511-0302-4849-86C6-04F0C646C7F2}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="11_5C276E48EE321F23732C7DB1B9E97F9D1C40C98D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD7E12C8-FE79-4CBF-8374-1880DFF335D4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity (Only E-Cooking)" sheetId="1" r:id="rId1"/>
@@ -1227,40 +1227,40 @@
         <v>5</v>
       </c>
       <c r="D9" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F9" s="18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" s="18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" s="18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I9" s="18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J9" s="18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K9" s="18">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L9" s="18">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M9" s="18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N9" s="18">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O9" s="18">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5363,40 +5363,40 @@
         <v>5</v>
       </c>
       <c r="D97" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H97" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N97" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5692,40 +5692,40 @@
         <v>5</v>
       </c>
       <c r="D104" s="19">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="E104" s="19">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="F104" s="19">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G104" s="19">
         <v>0</v>
       </c>
       <c r="H104" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" s="19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J104" s="19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K104" s="19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L104" s="19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M104" s="19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N104" s="19">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O104" s="19">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5927,40 +5927,40 @@
         <v>5</v>
       </c>
       <c r="D109" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E109" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F109" s="18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G109" s="18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H109" s="18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I109" s="18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J109" s="18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K109" s="18">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L109" s="18">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M109" s="18">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N109" s="18">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O109" s="18">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -12630,40 +12630,40 @@
         <v>5</v>
       </c>
       <c r="D25" s="18">
-        <v>-9.2742015999999344E-2</v>
+        <v>2</v>
       </c>
       <c r="E25" s="18">
-        <v>2.1684095999999538E-2</v>
+        <v>2</v>
       </c>
       <c r="F25" s="18">
-        <v>3.5930495999998868E-2</v>
+        <v>2</v>
       </c>
       <c r="G25" s="18">
-        <v>4.9997184000000423E-2</v>
+        <v>2</v>
       </c>
       <c r="H25" s="18">
-        <v>6.3077717333332117E-2</v>
+        <v>2</v>
       </c>
       <c r="I25" s="18">
-        <v>7.5988522666666114E-2</v>
+        <v>2</v>
       </c>
       <c r="J25" s="18">
-        <v>8.4245845333335012E-2</v>
+        <v>2</v>
       </c>
       <c r="K25" s="18">
-        <v>8.7979477333334444E-2</v>
+        <v>2</v>
       </c>
       <c r="L25" s="18">
-        <v>9.1802965333336317E-2</v>
+        <v>2</v>
       </c>
       <c r="M25" s="18">
-        <v>9.5716309333333527E-2</v>
+        <v>2</v>
       </c>
       <c r="N25" s="18">
-        <v>9.9859285333334213E-2</v>
+        <v>2</v>
       </c>
       <c r="O25" s="18">
-        <v>0.103275690666667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">

--- a/backend/Rwanda/financial-statements-CleanStep.xlsx
+++ b/backend/Rwanda/financial-statements-CleanStep.xlsx
@@ -2506,34 +2506,34 @@
         <v>0</v>
       </c>
       <c r="F37" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="19" t="n">
         <v>-45.48</v>
       </c>
-      <c r="G37" s="19" t="n">
+      <c r="H37" s="19" t="n">
         <v>-136.44</v>
       </c>
-      <c r="H37" s="19" t="n">
+      <c r="I37" s="19" t="n">
         <v>-227.4</v>
       </c>
-      <c r="I37" s="19" t="n">
+      <c r="J37" s="19" t="n">
         <v>-318.36</v>
       </c>
-      <c r="J37" s="19" t="n">
+      <c r="K37" s="19" t="n">
         <v>-409.3199999999999</v>
       </c>
-      <c r="K37" s="19" t="n">
+      <c r="L37" s="19" t="n">
         <v>-500.2799999999999</v>
       </c>
-      <c r="L37" s="19" t="n">
+      <c r="M37" s="19" t="n">
         <v>-591.2399999999999</v>
       </c>
-      <c r="M37" s="19" t="n">
+      <c r="N37" s="19" t="n">
         <v>-682.1999999999999</v>
       </c>
-      <c r="N37" s="19" t="n">
+      <c r="O37" s="19" t="n">
         <v>-773.16</v>
-      </c>
-      <c r="O37" s="19" t="n">
-        <v>-864.12</v>
       </c>
     </row>
     <row r="38" ht="15.5" customHeight="1">
@@ -2821,37 +2821,37 @@
         <v>-273.9964236684048</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>-547.5645208596383</v>
+        <v>-546.9928473368097</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>-28.91237241151316</v>
+        <v>-1015.428796079918</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>-605.3365675262133</v>
+        <v>-787.3729911946183</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>-1253.133747502193</v>
+        <v>-1630.038022722473</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>-1567.49648555585</v>
+        <v>-2234.997104338955</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>-1464.45115053207</v>
+        <v>-2398.19260572833</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>-1253.055247028271</v>
+        <v>-2143.958603865033</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>-1041.642200685596</v>
+        <v>-1781.378320858076</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>-830.2376861422772</v>
+        <v>-1418.78513947524</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>-656.8710359808772</v>
+        <v>-1094.234109810682</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>-633.6845208596383</v>
+        <v>-919.8674596492822</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -2874,37 +2874,37 @@
         <v>-273.9964236684048</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>-547.5645208596383</v>
+        <v>-546.9928473368097</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>-28.91237241151316</v>
+        <v>-1015.428796079918</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>-605.3365675262133</v>
+        <v>-787.3729911946183</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>-1253.133747502193</v>
+        <v>-1630.038022722473</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>-1567.49648555585</v>
+        <v>-2234.997104338955</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>-1464.45115053207</v>
+        <v>-2398.19260572833</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>-1253.055247028271</v>
+        <v>-2143.958603865033</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>-1041.642200685596</v>
+        <v>-1781.378320858076</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>-830.2376861422772</v>
+        <v>-1418.78513947524</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>-656.8710359808772</v>
+        <v>-1094.234109810682</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>-633.6845208596383</v>
+        <v>-919.8674596492822</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -3033,37 +3033,37 @@
         <v>-273.9964236684048</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>-547.5645208596383</v>
+        <v>-546.9928473368097</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>-28.91237241151316</v>
+        <v>-1015.428796079918</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>-605.3365675262133</v>
+        <v>-787.3729911946183</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>-1253.133747502193</v>
+        <v>-1630.038022722473</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>-1567.49648555585</v>
+        <v>-2234.997104338955</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>-1464.45115053207</v>
+        <v>-2398.19260572833</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>-1253.055247028271</v>
+        <v>-2143.958603865033</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>-1041.642200685596</v>
+        <v>-1781.378320858076</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>-830.2376861422772</v>
+        <v>-1418.78513947524</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>-656.8710359808772</v>
+        <v>-1094.234109810682</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>-633.6845208596383</v>
+        <v>-919.8674596492822</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -3092,31 +3092,31 @@
         <v>-355.0763073598987</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>-888.020502474599</v>
+        <v>-842.540502474599</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>-1733.685534002453</v>
+        <v>-1642.725534002453</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>-2341.644615618935</v>
+        <v>-2446.55246717081</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>-2507.84011700831</v>
+        <v>-2904.344312123009</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>-2256.606115145014</v>
+        <v>-2920.351146672868</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>-1897.025832138057</v>
+        <v>-2518.932765306414</v>
       </c>
       <c r="M48" s="18" t="n">
+        <v>-2009.172347259296</v>
+      </c>
+      <c r="N48" s="18" t="n">
         <v>-1537.432650755221</v>
       </c>
-      <c r="N48" s="18" t="n">
+      <c r="O48" s="18" t="n">
         <v>-1215.881621090663</v>
-      </c>
-      <c r="O48" s="18" t="n">
-        <v>-1044.514970929263</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -3251,31 +3251,31 @@
         <v>0</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>-241.3478515518748</v>
+        <v>-195.8678515518748</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>-819.7720466665751</v>
+        <v>-728.812046666575</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>-1469.569226642554</v>
+        <v>-1574.477078194429</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>-1785.931964696211</v>
+        <v>-2182.436159810911</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>-1684.886629672432</v>
+        <v>-2348.631661200286</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>-1475.490726168633</v>
+        <v>-2097.39765933699</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>-1266.077679825958</v>
+        <v>-1737.817376330033</v>
       </c>
       <c r="N51" s="18" t="n">
+        <v>-1378.224194947197</v>
+      </c>
+      <c r="O51" s="18" t="n">
         <v>-1056.673165282639</v>
-      </c>
-      <c r="O51" s="18" t="n">
-        <v>-885.3065151212389</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -3301,34 +3301,34 @@
         <v>3</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>763</v>
+        <v>6</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>781</v>
+        <v>791</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -3407,34 +3407,34 @@
         <v>3</v>
       </c>
       <c r="F54" s="18" t="n">
-        <v>763</v>
+        <v>6</v>
       </c>
       <c r="G54" s="18" t="n">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="H54" s="18" t="n">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="I54" s="18" t="n">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="J54" s="18" t="n">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="K54" s="18" t="n">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="L54" s="18" t="n">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="M54" s="18" t="n">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="N54" s="18" t="n">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="O54" s="18" t="n">
-        <v>781</v>
+        <v>791</v>
       </c>
     </row>
     <row r="55" ht="15.5" customHeight="1">
@@ -3619,34 +3619,34 @@
         <v>-156.2084558080239</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>407.9236926401013</v>
+        <v>-349.0763073598987</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>-123.020502474599</v>
+        <v>-75.54050247459895</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>-966.6855340024533</v>
+        <v>-872.7255340024533</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>-1572.644615618935</v>
+        <v>-1673.55246717081</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>-1736.84011700831</v>
+        <v>-2128.344312123009</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>-1483.606115145014</v>
+        <v>-2141.351146672868</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>-1122.025832138057</v>
+        <v>-1736.932765306414</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>-760.4326507552209</v>
+        <v>-1224.172347259296</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>-436.8816210906627</v>
+        <v>-749.4326507552209</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>-263.5149709292627</v>
+        <v>-424.881621090663</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -3669,37 +3669,37 @@
         <v>-115.7879678603809</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>-391.3560650516143</v>
+        <v>-390.7843915287858</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>-436.8360650516145</v>
+        <v>-666.3524887200192</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>-482.3160650516144</v>
+        <v>-711.8324887200193</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>-286.4482134997397</v>
+        <v>-757.3124887200195</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>5.148130063085318</v>
+        <v>-561.4446371681447</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>272.3889664762396</v>
+        <v>-269.8482936053206</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>230.550868116743</v>
+        <v>-2.607457192164929</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>80.38363145246058</v>
+        <v>-44.44555555166198</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>-69.80503538705625</v>
+        <v>-194.6127922159437</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>-219.9894148902144</v>
+        <v>-344.8014590554612</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>-370.1695499303755</v>
+        <v>-494.9858385586192</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -4573,34 +4573,34 @@
         <v>-273.9964236684048</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>-547.5645208596383</v>
+        <v>-546.9928473368097</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>-28.91237241151316</v>
+        <v>-1015.428796079918</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>-605.3365675262133</v>
+        <v>-787.3729911946183</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>-1253.133747502193</v>
+        <v>-1630.038022722473</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>-1567.49648555585</v>
+        <v>-2234.997104338955</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>-1464.45115053207</v>
+        <v>-2398.19260572833</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>-1253.055247028271</v>
+        <v>-2143.958603865033</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>-1041.642200685596</v>
+        <v>-1781.378320858076</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>-830.2376861422772</v>
+        <v>-1418.78513947524</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>-656.8710359808772</v>
+        <v>-1094.234109810682</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -4676,37 +4676,37 @@
         <v>-273.9964236684048</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>-547.5645208596383</v>
+        <v>-546.9928473368097</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>-28.91237241151316</v>
+        <v>-1015.428796079918</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>-605.3365675262133</v>
+        <v>-787.3729911946183</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>-1253.133747502193</v>
+        <v>-1630.038022722473</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>-1567.49648555585</v>
+        <v>-2234.997104338955</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>-1464.45115053207</v>
+        <v>-2398.19260572833</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>-1253.055247028271</v>
+        <v>-2143.958603865033</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>-1041.642200685596</v>
+        <v>-1781.378320858076</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>-830.2376861422772</v>
+        <v>-1418.78513947524</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>-656.8710359808772</v>
+        <v>-1094.234109810682</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>-633.6845208596383</v>
+        <v>-919.8674596492822</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -5657,34 +5657,34 @@
         <v>761.5749464668912</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>842.2036917224142</v>
+        <v>842.5346606040516</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>-319.9275621043757</v>
+        <v>487.1273843625155</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>-1138.51992716426</v>
+        <v>-966.6002130270998</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>-1788.31710714024</v>
+        <v>-2052.433414500138</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>-2104.679845193897</v>
+        <v>-2660.392496116621</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>-2003.634510170117</v>
+        <v>-2826.587997505996</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>-1794.238606666318</v>
+        <v>-2575.353995642699</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>-1584.825560323643</v>
+        <v>-2215.773712635742</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>-1375.421045780324</v>
+        <v>-1856.180531252906</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>-1127.995559817816</v>
+        <v>-1458.57066578724</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -5866,37 +5866,37 @@
         <v>761.5749464668912</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>842.2036917224142</v>
+        <v>842.5346606040516</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>-319.9275621043757</v>
+        <v>487.1273843625155</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>-1138.51992716426</v>
+        <v>-966.6002130270998</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>-1788.31710714024</v>
+        <v>-2052.433414500138</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>-2104.679845193897</v>
+        <v>-2660.392496116621</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>-2003.634510170117</v>
+        <v>-2826.587997505996</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>-1794.238606666318</v>
+        <v>-2575.353995642699</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>-1584.825560323643</v>
+        <v>-2215.773712635742</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>-1375.421045780324</v>
+        <v>-1856.180531252906</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>-1127.995559817816</v>
+        <v>-1458.57066578724</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>-730.4479070615439</v>
+        <v>-910.8428779908063</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -6296,31 +6296,31 @@
         <v>3</v>
       </c>
       <c r="G108" s="18" t="n">
-        <v>763</v>
+        <v>6</v>
       </c>
       <c r="H108" s="18" t="n">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="I108" s="18" t="n">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="J108" s="18" t="n">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="K108" s="18" t="n">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="L108" s="18" t="n">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="M108" s="18" t="n">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="N108" s="18" t="n">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="O108" s="18" t="n">
-        <v>779</v>
+        <v>788</v>
       </c>
     </row>
     <row r="109" ht="15.5" customHeight="1">
@@ -6452,34 +6452,34 @@
         <v>3</v>
       </c>
       <c r="F111" s="18" t="n">
-        <v>763</v>
+        <v>6</v>
       </c>
       <c r="G111" s="18" t="n">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="H111" s="18" t="n">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="I111" s="18" t="n">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="J111" s="18" t="n">
-        <v>771</v>
+        <v>776</v>
       </c>
       <c r="K111" s="18" t="n">
-        <v>773</v>
+        <v>779</v>
       </c>
       <c r="L111" s="18" t="n">
-        <v>775</v>
+        <v>782</v>
       </c>
       <c r="M111" s="18" t="n">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="N111" s="18" t="n">
-        <v>779</v>
+        <v>788</v>
       </c>
       <c r="O111" s="18" t="n">
-        <v>781</v>
+        <v>791</v>
       </c>
     </row>
     <row r="112" ht="15.5" customHeight="1">
@@ -8776,7 +8776,7 @@
         <v>4627.282008722714</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>4206.583225413329</v>
+        <v>4818.436049145901</v>
       </c>
     </row>
     <row r="42" ht="15.5" customHeight="1">
@@ -8829,7 +8829,7 @@
         <v>4627.282008722714</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>4206.583225413329</v>
+        <v>4818.436049145901</v>
       </c>
     </row>
     <row r="43" ht="15.5" customHeight="1">
@@ -8882,7 +8882,7 @@
         <v>135.9230875941853</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>-145.2932861724019</v>
+        <v>138.003837047472</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -8935,7 +8935,7 @@
         <v>14</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>-269.2971232198739</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -9094,7 +9094,7 @@
         <v>4763.205096316899</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>4061.289939240927</v>
+        <v>4956.439886193373</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -9138,10 +9138,10 @@
         <v>3996.528176865003</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>4377.04364257835</v>
+        <v>4306.578867276742</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>4578.386145566312</v>
+        <v>4648.85092086792</v>
       </c>
       <c r="N48" s="18" t="n">
         <v>4811.950101719302</v>
@@ -9297,10 +9297,10 @@
         <v>3648.168091378179</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>4066.992952166611</v>
+        <v>3996.528176865003</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>4306.578867276742</v>
+        <v>4377.04364257835</v>
       </c>
       <c r="N51" s="18" t="n">
         <v>4578.386145566312</v>
@@ -9668,10 +9668,10 @@
         <v>3938.440612974634</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>4316.873200576842</v>
+        <v>4246.408425275234</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>4516.133546566795</v>
+        <v>4586.598321868403</v>
       </c>
       <c r="N58" s="18" t="n">
         <v>4745.616055221008</v>
@@ -9721,16 +9721,16 @@
         <v>15.58904109589093</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>-54.87573420571698</v>
+        <v>15.58904109589093</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>15.58904109589184</v>
+        <v>-54.87573420571607</v>
       </c>
       <c r="N59" s="18" t="n">
         <v>17.58904109589184</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>-874.5609058565551</v>
+        <v>20.58904109589093</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -10737,7 +10737,7 @@
         <v>14</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>-269.2971232198739</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -11108,7 +11108,7 @@
         <v>4627.282008722714</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>4206.583225413329</v>
+        <v>4818.436049145901</v>
       </c>
     </row>
     <row r="86" ht="15.5" customHeight="1">
@@ -11706,10 +11706,10 @@
         <v>18459.51422057945</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>21665.85122419476</v>
+        <v>21736.31599949639</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>25152.88362848072</v>
+        <v>25082.41885317909</v>
       </c>
       <c r="N96" s="20" t="n">
         <v>28709.12115268048</v>
@@ -11915,10 +11915,10 @@
         <v>18459.51422057945</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>21665.85122419476</v>
+        <v>21736.31599949639</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>25152.88362848072</v>
+        <v>25082.41885317909</v>
       </c>
       <c r="M100" s="20" t="n">
         <v>28709.12115268048</v>
@@ -11927,7 +11927,7 @@
         <v>32404.99899420075</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>36069.03589658669</v>
+        <v>36240.49420498676</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -14568,34 +14568,34 @@
         <v>-10.584</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>-15.274</v>
+        <v>-19.594</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>-20.946</v>
+        <v>-27.186</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>-27.01933333333334</v>
+        <v>-35.83933333333334</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>-33.684</v>
+        <v>-45.03400000000001</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>-40.64733333333334</v>
+        <v>-54.48733333333333</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>-45.93666666666666</v>
+        <v>-62.20666666666668</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>-49.192</v>
+        <v>-67.84199999999998</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>-52.03333333333333</v>
+        <v>-71.43333333333334</v>
       </c>
       <c r="N37" s="19" t="n">
-        <v>-54.87066666666666</v>
+        <v>-74.61066666666666</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>-57.69333333333333</v>
+        <v>-77.76333333333332</v>
       </c>
     </row>
     <row r="38" ht="15.5" customHeight="1">
@@ -14886,34 +14886,34 @@
         <v>0.5519529271896613</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>4.789570936428327</v>
+        <v>4.872312952428326</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>9.721677720917388</v>
+        <v>9.879931955992507</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>16.04774380171231</v>
+        <v>16.35176849320063</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>24.58991837021113</v>
+        <v>25.00580878117003</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>22.78411935783657</v>
+        <v>23.19343442632972</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>20.90041037483058</v>
+        <v>21.29986242962509</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>18.99733483624383</v>
+        <v>19.38856771295618</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>17.3672748084873</v>
+        <v>17.49056247972017</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>15.81043236270174</v>
+        <v>15.86632277366065</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>14.26727646565449</v>
+        <v>14.32152304099695</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -14939,34 +14939,34 @@
         <v>1.064829639518428</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>5.514502443277642</v>
+        <v>5.597244459277642</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>10.65455443324615</v>
+        <v>10.81280866832127</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>17.18527804828765</v>
+        <v>17.48930273977597</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>25.92717864418373</v>
+        <v>26.34306905514263</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>24.31699607016533</v>
+        <v>24.72631113865848</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>22.49493092277579</v>
+        <v>22.8943829775703</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>20.61980058966849</v>
+        <v>21.01103346638084</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>19.01686384958319</v>
+        <v>19.14015152081606</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>17.48714469146886</v>
+        <v>17.54303510242777</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>15.9694682464764</v>
+        <v>16.02371482181886</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -15098,34 +15098,34 @@
         <v>0.7979529271896613</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>5.185570936428327</v>
+        <v>5.268312952428326</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>10.25567772091739</v>
+        <v>10.41393195599251</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>16.69841046837897</v>
+        <v>17.00243515986729</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>25.34591837021113</v>
+        <v>25.76180878117003</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>23.59678602450323</v>
+        <v>24.00610109299638</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>21.72374370816392</v>
+        <v>22.12319576295842</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>19.82533483624383</v>
+        <v>20.21656771295618</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>18.19394147515397</v>
+        <v>18.31722914638684</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>16.62976569603507</v>
+        <v>16.68565610699398</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>15.06394313232115</v>
+        <v>15.11818970766361</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -15154,13 +15154,13 @@
         <v>-1.20696931622679</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>-1.304934392542375</v>
+        <v>-1.932329362843744</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>-2.339394754096205</v>
+        <v>-2.496756957377249</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>-4.08956004068785</v>
+        <v>-4.209644938240621</v>
       </c>
       <c r="J48" s="18" t="n">
         <v>-6.311502661143089</v>
@@ -15313,13 +15313,13 @@
         <v>-1.099794986071236</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>-0.9598706457534301</v>
+        <v>-1.5872656160548</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>-1.52786848908934</v>
+        <v>-1.685230692370385</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>-2.599606156371443</v>
+        <v>-2.719691053924215</v>
       </c>
       <c r="J51" s="18" t="n">
         <v>-4.46985634051586</v>
@@ -15328,7 +15328,7 @@
         <v>-6.691798960971099</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>-8.866128398362793</v>
+        <v>-8.86612839836279</v>
       </c>
       <c r="M51" s="18" t="n">
         <v>-11.04034493928043</v>
@@ -15684,13 +15684,13 @@
         <v>3.517962190622525</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>8.627942319786392</v>
+        <v>8.000547349485023</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>14.79813949247914</v>
+        <v>14.64077728919809</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>23.24770023328475</v>
+        <v>23.12761533573198</v>
       </c>
       <c r="J58" s="18" t="n">
         <v>21.22137405118568</v>
@@ -15734,34 +15734,34 @@
         <v>1.00457490110412</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>1.667608745805802</v>
+        <v>1.750350761805801</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>1.627735401130996</v>
+        <v>2.413384606507485</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>1.900270975899836</v>
+        <v>2.3616578706692</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>2.098218136926377</v>
+        <v>2.634193445438047</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>2.375411973317551</v>
+        <v>2.784727041810701</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>2.61505525875349</v>
+        <v>3.014507313547998</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>2.862917722271593</v>
+        <v>3.254150598983941</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>3.378725391269176</v>
+        <v>3.502013062502046</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>3.961930320540709</v>
+        <v>4.017820731499619</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>4.534925694265228</v>
+        <v>4.589172269607687</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -16638,31 +16638,31 @@
         <v>1.064829639518428</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>5.514502443277642</v>
+        <v>5.597244459277642</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>10.65455443324615</v>
+        <v>10.81280866832127</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>17.18527804828765</v>
+        <v>17.48930273977597</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>25.92717864418373</v>
+        <v>26.34306905514263</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>24.31699607016533</v>
+        <v>24.72631113865848</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>22.49493092277579</v>
+        <v>22.8943829775703</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>20.61980058966849</v>
+        <v>21.01103346638084</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>19.01686384958319</v>
+        <v>19.14015152081606</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>17.48714469146886</v>
+        <v>17.54303510242777</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -16741,34 +16741,34 @@
         <v>1.064829639518428</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>5.514502443277642</v>
+        <v>5.597244459277642</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>10.65455443324615</v>
+        <v>10.81280866832127</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>17.18527804828765</v>
+        <v>17.48930273977597</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>25.92717864418373</v>
+        <v>26.34306905514263</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>24.31699607016533</v>
+        <v>24.72631113865848</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>22.49493092277579</v>
+        <v>22.8943829775703</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>20.61980058966849</v>
+        <v>21.01103346638084</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>19.01686384958319</v>
+        <v>19.14015152081606</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>17.48714469146886</v>
+        <v>17.54303510242777</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>15.9694682464764</v>
+        <v>16.02371482181886</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -17722,13 +17722,13 @@
         <v>1.230311960749614</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>0.7359124553982314</v>
+        <v>1.363307425699603</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>0.2334865053282429</v>
+        <v>0.3908487086092867</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>-0.6981246572313926</v>
+        <v>-0.5780397596786215</v>
       </c>
       <c r="J96" s="20" t="n">
         <v>-2.188078541547799</v>
@@ -17737,13 +17737,13 @@
         <v>-4.029724862175027</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>-5.823757999738711</v>
+        <v>-5.823757999738709</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>-7.61767824082834</v>
+        <v>-7.617678240828338</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>-9.411706258759011</v>
+        <v>-9.411706258759009</v>
       </c>
       <c r="O96" s="20" t="n">
         <v>-11.20591395499266</v>
@@ -17931,13 +17931,13 @@
         <v>1.230311960749614</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>0.7359124553982314</v>
+        <v>1.363307425699603</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>0.2334865053282429</v>
+        <v>0.3908487086092867</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>-0.6981246572313926</v>
+        <v>-0.5780397596786215</v>
       </c>
       <c r="I100" s="20" t="n">
         <v>-2.188078541547799</v>
@@ -17946,19 +17946,19 @@
         <v>-4.029724862175027</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>-5.823757999738711</v>
+        <v>-5.823757999738709</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>-7.61767824082834</v>
+        <v>-7.617678240828338</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>-9.411706258759011</v>
+        <v>-9.411706258759009</v>
       </c>
       <c r="N100" s="20" t="n">
         <v>-11.20591395499266</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>-12.98991504465789</v>
+        <v>-12.98991504465788</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -20620,13 +20620,13 @@
         <v>-102.9455882482798</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>-211.2762969230018</v>
+        <v>-211.2762969230016</v>
       </c>
       <c r="N37" s="19" t="n">
-        <v>-357.5237612260821</v>
+        <v>-357.5237612260819</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>-541.6960463870478</v>
+        <v>-541.696046387048</v>
       </c>
     </row>
     <row r="38" ht="15.5" customHeight="1">
@@ -20835,7 +20835,7 @@
         <v>4397.880947567281</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>4627.282008722716</v>
+        <v>4627.282008722714</v>
       </c>
       <c r="O41" s="18" t="n">
         <v>4818.436049145903</v>
@@ -20888,7 +20888,7 @@
         <v>4397.880947567281</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>4627.282008722716</v>
+        <v>4627.282008722714</v>
       </c>
       <c r="O42" s="18" t="n">
         <v>4818.436049145903</v>
@@ -20917,34 +20917,34 @@
         <v>1003.391117474072</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>1279.171703532507</v>
+        <v>1278.600030009678</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>1554.947988556262</v>
+        <v>1554.376315033434</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>1830.720037317144</v>
+        <v>1830.148363794316</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>2106.48791372163</v>
+        <v>2105.916240198801</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>2382.251680821688</v>
+        <v>2381.68000729886</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>2657.881540477052</v>
+        <v>2657.309866954223</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>2933.477721258876</v>
+        <v>2932.906047736049</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>3209.073180927569</v>
+        <v>3208.501507404741</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>3484.667931097034</v>
+        <v>3484.096257574205</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>3760.261983221006</v>
+        <v>3759.690309698178</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -20970,34 +20970,34 @@
         <v>973.0429276858573</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>1248.611024877091</v>
+        <v>1248.039351354262</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>1524.179122068324</v>
+        <v>1523.607448545496</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>1799.747219259557</v>
+        <v>1799.175545736729</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>2075.315316450791</v>
+        <v>2074.743642927962</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>2350.883413642024</v>
+        <v>2350.311740119196</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>2626.451510833258</v>
+        <v>2625.879837310429</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>2902.019608024491</v>
+        <v>2901.447934501663</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>3177.587705215724</v>
+        <v>3177.016031692896</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>3453.155802406958</v>
+        <v>3452.584128884129</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>3728.723899598191</v>
+        <v>3728.152226075363</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -21129,34 +21129,34 @@
         <v>2188.934227409571</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>3000.156193255411</v>
+        <v>2999.584519732583</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>3773.12508777403</v>
+        <v>3772.553414251202</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>4507.841110498985</v>
+        <v>4507.269436976157</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>5204.304458750879</v>
+        <v>5203.73278522805</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>5862.477758388485</v>
+        <v>5861.906084865657</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>6482.234589561317</v>
+        <v>6481.662916038488</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>7063.715704532602</v>
+        <v>7063.144031009773</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>7606.95412849485</v>
+        <v>7606.382454972021</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>8111.949939819749</v>
+        <v>8111.378266296919</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>8578.698032366909</v>
+        <v>8578.126358844082</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -21185,31 +21185,31 @@
         <v>1199.810297296057</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>1581.382089146499</v>
+        <v>1581.622781487826</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>1924.697054228054</v>
+        <v>1924.937777927854</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>2229.755482662951</v>
+        <v>2229.996205699612</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>2496.527229297121</v>
+        <v>2496.767951677277</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>2724.755965443383</v>
+        <v>2724.996687173596</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>2914.675465180135</v>
+        <v>2914.916186266907</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>3066.351724776917</v>
+        <v>3066.592430323402</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>3179.784832424792</v>
+        <v>3180.025522661097</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>3254.970666066729</v>
+        <v>3255.211355974531</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -21344,31 +21344,31 @@
         <v>620.532300738528</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>1040.361149146706</v>
+        <v>1040.601841488033</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>1421.932909638675</v>
+        <v>1422.173633338475</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>1765.247875383368</v>
+        <v>1765.488598420029</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>2070.306304474771</v>
+        <v>2070.547026854927</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>2337.078051758884</v>
+        <v>2337.318773489097</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>2565.306788548587</v>
+        <v>2565.547509635359</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>2755.226303825626</v>
+        <v>2755.467009372111</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>2906.902578732588</v>
+        <v>2907.143268968893</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>3020.335686708966</v>
+        <v>3020.576376616769</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -21715,31 +21715,31 @@
         <v>1956.838659736531</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>2338.202263754451</v>
+        <v>2338.442956095779</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>2681.313277266356</v>
+        <v>2681.554000966157</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>2986.171926488003</v>
+        <v>2986.412649524663</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>3252.748003213348</v>
+        <v>3252.988725593504</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>3480.914976895479</v>
+        <v>3481.155698625693</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>3670.80639304164</v>
+        <v>3671.047114128412</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>3822.455290160962</v>
+        <v>3822.695995707447</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>3935.861744830607</v>
+        <v>3936.102435066912</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>4011.021623539805</v>
+        <v>4011.262313447607</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -21765,34 +21765,34 @@
         <v>651.952619555344</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>1043.31753351888</v>
+        <v>1042.745859996052</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>1434.922824019579</v>
+        <v>1434.110458155424</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>1826.527833232628</v>
+        <v>1825.71543601</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>2218.132532262877</v>
+        <v>2217.320135703387</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>2609.729755175137</v>
+        <v>2608.917359272154</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>3001.319612665838</v>
+        <v>3000.507217412795</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>3392.909311490962</v>
+        <v>3392.096916881361</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>3784.498838333888</v>
+        <v>3783.686459264574</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>4176.088194989143</v>
+        <v>4175.275831230007</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>4567.676408827104</v>
+        <v>4566.864045396474</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -22669,31 +22669,31 @@
         <v>973.0429276858573</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>1248.611024877091</v>
+        <v>1248.039351354262</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>1524.179122068324</v>
+        <v>1523.607448545496</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>1799.747219259557</v>
+        <v>1799.175545736729</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>2075.315316450791</v>
+        <v>2074.743642927962</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>2350.883413642024</v>
+        <v>2350.311740119196</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>2626.451510833258</v>
+        <v>2625.879837310429</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>2902.019608024491</v>
+        <v>2901.447934501663</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>3177.587705215724</v>
+        <v>3177.016031692896</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>3453.155802406958</v>
+        <v>3452.584128884129</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -22772,34 +22772,34 @@
         <v>973.0429276858573</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>1248.611024877091</v>
+        <v>1248.039351354262</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>1524.179122068324</v>
+        <v>1523.607448545496</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>1799.747219259557</v>
+        <v>1799.175545736729</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>2075.315316450791</v>
+        <v>2074.743642927962</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>2350.883413642024</v>
+        <v>2350.311740119196</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>2626.451510833258</v>
+        <v>2625.879837310429</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>2902.019608024491</v>
+        <v>2901.447934501663</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>3177.587705215724</v>
+        <v>3177.016031692896</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>3453.155802406958</v>
+        <v>3452.584128884129</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>3728.723899598191</v>
+        <v>3728.152226075363</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -23011,7 +23011,7 @@
         <v>4397.880947567281</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>4627.282008722716</v>
+        <v>4627.282008722714</v>
       </c>
     </row>
     <row r="83" ht="15.5" customHeight="1">
@@ -23167,7 +23167,7 @@
         <v>4397.880947567281</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>4627.282008722716</v>
+        <v>4627.282008722714</v>
       </c>
       <c r="O85" s="18" t="n">
         <v>4818.436049145903</v>
@@ -23753,31 +23753,31 @@
         <v>1058.692630951551</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>2566.930973380454</v>
+        <v>2566.840696840144</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>4794.793458288945</v>
+        <v>4794.703213107107</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>7692.003502190904</v>
+        <v>7691.913256345927</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>10622.61455436393</v>
+        <v>10622.52430786245</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>13363.6658221277</v>
+        <v>13363.57557497628</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>15891.55040032479</v>
+        <v>15891.46015252993</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>18201.60854197374</v>
+        <v>18201.51827863857</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>20293.74789894738</v>
+        <v>20293.65762030205</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>22167.94247925205</v>
+        <v>22167.85220027822</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -23962,34 +23962,34 @@
         <v>1058.692630951551</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>2566.930973380454</v>
+        <v>2566.840696840144</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>4794.793458288945</v>
+        <v>4794.703213107107</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>7692.003502190904</v>
+        <v>7691.913256345927</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>10622.61455436393</v>
+        <v>10622.52430786245</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>13363.6658221277</v>
+        <v>13363.57557497628</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>15891.55040032479</v>
+        <v>15891.46015252993</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>18201.60854197374</v>
+        <v>18201.51827863857</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>20293.74789894738</v>
+        <v>20293.65762030205</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>22167.94247925205</v>
+        <v>22167.85220027822</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>23824.21537012213</v>
+        <v>23824.12509082308</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -26657,7 +26657,7 @@
         <v>-27.72</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>-29.79999999999999</v>
+        <v>-29.8</v>
       </c>
     </row>
     <row r="38" ht="15.5" customHeight="1">
@@ -26948,13 +26948,13 @@
         <v>5.260595287671237</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>6.463571506849319</v>
+        <v>8.538640000000004</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>7.92795550684932</v>
+        <v>9.886275506849319</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>11.443264</v>
+        <v>11.32819550684932</v>
       </c>
       <c r="I43" s="18" t="n">
         <v>14.82104</v>
@@ -27001,13 +27001,13 @@
         <v>5.20854049315069</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>6.463571506849319</v>
+        <v>8.538640000000004</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>7.92795550684932</v>
+        <v>9.886275506849319</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>11.443264</v>
+        <v>11.32819550684932</v>
       </c>
       <c r="I44" s="18" t="n">
         <v>14.82104</v>
@@ -27160,13 +27160,13 @@
         <v>15.01059528767124</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>14.71357150684932</v>
+        <v>16.78864</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>14.67795550684932</v>
+        <v>16.63627550684932</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>16.69326400000001</v>
+        <v>16.57819550684932</v>
       </c>
       <c r="I47" s="18" t="n">
         <v>18.57104</v>
@@ -27216,10 +27216,10 @@
         <v>-34.9111464</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>-38.8500584</v>
+        <v>-36.8900584</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>-42.8097544</v>
+        <v>-40.8514344</v>
       </c>
       <c r="I48" s="18" t="n">
         <v>-44.8335944</v>
@@ -27228,7 +27228,7 @@
         <v>-46.8798984</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>-48.94866640000001</v>
+        <v>-48.9486664</v>
       </c>
       <c r="L48" s="18" t="n">
         <v>-51.01871235200001</v>
@@ -27375,10 +27375,10 @@
         <v>-34.7104256</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>-38.6268736</v>
+        <v>-36.6668736</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>-42.5641056</v>
+        <v>-40.6057856</v>
       </c>
       <c r="I51" s="18" t="n">
         <v>-44.5654816</v>
@@ -27387,13 +27387,13 @@
         <v>-46.5893216</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>-48.63562560000001</v>
+        <v>-48.6356256</v>
       </c>
       <c r="L51" s="18" t="n">
         <v>-50.70439360000001</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>-52.774439552</v>
+        <v>-52.77443955200001</v>
       </c>
       <c r="N51" s="18" t="n">
         <v>-54.845853312</v>
@@ -27746,10 +27746,10 @@
         <v>-18.9111464</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>-22.8500584</v>
+        <v>-20.8900584</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>-26.8097544</v>
+        <v>-24.8514344</v>
       </c>
       <c r="I58" s="18" t="n">
         <v>-28.8335944</v>
@@ -27758,7 +27758,7 @@
         <v>-30.8798984</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>-32.94866640000001</v>
+        <v>-32.9486664</v>
       </c>
       <c r="L58" s="18" t="n">
         <v>-35.01871235200001</v>
@@ -27796,13 +27796,13 @@
         <v>31.9077594410959</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>33.62471790684932</v>
+        <v>35.69978640000001</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>37.52801390684932</v>
+        <v>37.52633390684932</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>43.5030184</v>
+        <v>41.42962990684932</v>
       </c>
       <c r="I59" s="18" t="n">
         <v>47.40463439999999</v>
@@ -27811,7 +27811,7 @@
         <v>51.3062504</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>55.20786640000001</v>
+        <v>55.2078664</v>
       </c>
       <c r="L59" s="18" t="n">
         <v>59.1094824</v>
@@ -28700,13 +28700,13 @@
         <v>5.20854049315069</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>6.463571506849319</v>
+        <v>8.538640000000004</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>7.92795550684932</v>
+        <v>9.886275506849319</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>11.443264</v>
+        <v>11.32819550684932</v>
       </c>
       <c r="J76" s="18" t="n">
         <v>14.82104</v>
@@ -28803,13 +28803,13 @@
         <v>5.20854049315069</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>6.463571506849319</v>
+        <v>8.538640000000004</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>7.92795550684932</v>
+        <v>9.886275506849319</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>11.443264</v>
+        <v>11.32819550684932</v>
       </c>
       <c r="I78" s="18" t="n">
         <v>14.82104</v>
@@ -29784,10 +29784,10 @@
         <v>-31.1989712</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>-33.359692</v>
+        <v>-31.399692</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>-35.5411968</v>
+        <v>-33.5828768</v>
       </c>
       <c r="I96" s="20" t="n">
         <v>-35.7868456</v>
@@ -29993,10 +29993,10 @@
         <v>-31.1989712</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>-33.359692</v>
+        <v>-31.399692</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>-35.5411968</v>
+        <v>-33.5828768</v>
       </c>
       <c r="H100" s="20" t="n">
         <v>-35.7868456</v>

--- a/backend/Rwanda/financial-statements-CleanStep.xlsx
+++ b/backend/Rwanda/financial-statements-CleanStep.xlsx
@@ -2723,28 +2723,28 @@
         <v>251.9186599932068</v>
       </c>
       <c r="H41" s="18" t="n">
-        <v>275.1531675613292</v>
+        <v>316.3689062182364</v>
       </c>
       <c r="I41" s="18" t="n">
-        <v>577.006287995806</v>
+        <v>336.7595029230595</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>588.4790685160979</v>
+        <v>667.9213200358874</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>630.763261465182</v>
+        <v>707.3038573697547</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>670.6476119783471</v>
+        <v>744.3154730748016</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>708.1559550116943</v>
+        <v>778.9799721163694</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>711.1878444927193</v>
+        <v>811.3206621928357</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>880.4912861309732</v>
+        <v>760.5720528458729</v>
       </c>
     </row>
     <row r="42" ht="15.5" customHeight="1">
@@ -2776,28 +2776,28 @@
         <v>251.9186599932068</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>275.1531675613292</v>
+        <v>316.3689062182364</v>
       </c>
       <c r="I42" s="18" t="n">
-        <v>577.006287995806</v>
+        <v>336.7595029230595</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>588.4790685160979</v>
+        <v>667.9213200358874</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>630.763261465182</v>
+        <v>707.3038573697547</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>670.6476119783471</v>
+        <v>744.3154730748016</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>708.1559550116943</v>
+        <v>778.9799721163694</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>711.1878444927193</v>
+        <v>811.3206621928357</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>880.4912861309732</v>
+        <v>760.5720528458729</v>
       </c>
     </row>
     <row r="43" ht="15.5" customHeight="1">
@@ -2829,28 +2829,28 @@
         <v>9197.281372068377</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>11480.82573957372</v>
+        <v>11483.33258888879</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>12679.29223472794</v>
+        <v>13780.46810173877</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>14187.4934254505</v>
+        <v>14964.06299109146</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>15644.45273080934</v>
+        <v>16461.55477941933</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>17157.18830965172</v>
+        <v>17938.918464852</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>18754.28021538517</v>
+        <v>19457.14319605379</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>20294.88964460577</v>
+        <v>21054.186959885</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>21615.55156483038</v>
+        <v>22595.45201337327</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -2882,28 +2882,28 @@
         <v>9191.950163199999</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>11473.83333765396</v>
+        <v>11476.34018696902</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>12670.64501144313</v>
+        <v>13771.82087845396</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>14177.2073326636</v>
+        <v>14953.77689830456</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>15631.79621128332</v>
+        <v>16448.8982598933</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>17142.52585296026</v>
+        <v>17924.25600816054</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>18737.65041309164</v>
+        <v>19440.51339376026</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>20276.34063861241</v>
+        <v>21035.63795389164</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>21594.42773086953</v>
+        <v>22574.32817941241</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -3041,28 +3041,28 @@
         <v>9449.200032061584</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>11755.97890713505</v>
+        <v>11799.70149510703</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>13256.29852272374</v>
+        <v>14117.22760466183</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>14775.97249396659</v>
+        <v>15631.98431112734</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>16275.21599227453</v>
+        <v>17168.85863678908</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>17827.83592163007</v>
+        <v>18683.2339379268</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>19462.43617039686</v>
+        <v>20236.12316817016</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>21006.07748909849</v>
+        <v>21865.50762207784</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>22496.04285096136</v>
+        <v>23356.02406621914</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -3097,25 +3097,25 @@
         <v>6875.244939658902</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>7368.13318108064</v>
+        <v>8201.528672401477</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>27621.1632959618</v>
+        <v>9263.440182715221</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>21874.56757653422</v>
+        <v>30080.61511292285</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>23358.43576546627</v>
+        <v>24325.16487886935</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>24429.78287124421</v>
+        <v>25785.87816752269</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>25567.17913708061</v>
+        <v>26828.80958303212</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>25129.60404460894</v>
+        <v>27031.54785191875</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -3256,25 +3256,25 @@
         <v>4890.393112480493</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>5385.281579538066</v>
+        <v>6218.677070858902</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>25069.28842552722</v>
+        <v>6711.56531228064</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>18758.54789077317</v>
+        <v>26964.5954271618</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>20251.27059433114</v>
+        <v>21217.99970773422</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>21345.77260038779</v>
+        <v>22701.86789666627</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>22511.58455649269</v>
+        <v>23773.21500244421</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>23008.66746097079</v>
+        <v>24910.6112682806</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -3303,31 +3303,31 @@
         <v>1583.425610624798</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>2665.612136517841</v>
+        <v>1937.86665324947</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>-15351.00358996734</v>
+        <v>3032.922965436263</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>-7819.975766656626</v>
+        <v>-14970.9516726181</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>-7239.456212760299</v>
+        <v>-7994.525979185526</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>-7218.019348828238</v>
+        <v>-7960.219328959723</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>-7185.701745445002</v>
+        <v>-7915.160637145667</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>-6575.396402580449</v>
+        <v>-7859.457424159256</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>-11276.79383539876</v>
+        <v>-7226.00032778756</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>-3357.530223464731</v>
+        <v>-11045.20901394877</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -3356,31 +3356,31 @@
         <v>1583.425610624798</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>2665.612136517841</v>
+        <v>1937.86665324947</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>-15351.00358996734</v>
+        <v>3032.922965436263</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>-7819.975766656626</v>
+        <v>-14970.9516726181</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>-7239.456212760299</v>
+        <v>-7994.525979185526</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>-7218.019348828238</v>
+        <v>-7960.219328959723</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>-7185.701745445002</v>
+        <v>-7915.160637145667</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>-6575.396402580449</v>
+        <v>-7859.457424159256</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>-11276.79383539876</v>
+        <v>-7226.00032778756</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>-3357.530223464731</v>
+        <v>-11045.20901394877</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -3621,31 +3621,31 @@
         <v>5989.415167623832</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>8207.241908929956</v>
+        <v>7479.496425661585</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>-8482.751052228203</v>
+        <v>9901.175503175398</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>-460.4898088607933</v>
+        <v>-6778.070223501432</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>20371.42099041462</v>
+        <v>1258.628110742804</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>14643.89170817996</v>
+        <v>22107.7392644371</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>16158.07156332981</v>
+        <v>16395.34178503223</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>17837.75666637023</v>
+        <v>17909.79094106991</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>14271.83629568848</v>
+        <v>19584.2602492512</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>21750.94998718336</v>
+        <v>15965.21500400913</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -3674,31 +3674,31 @@
         <v>1313.135737599998</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>1241.958123131628</v>
+        <v>1969.703606399999</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>20238.72995936326</v>
+        <v>1898.525991931629</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>13716.78833158454</v>
+        <v>20895.29782816326</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>-5595.448496448022</v>
+        <v>14373.35620038454</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>1631.324284094571</v>
+        <v>-4938.880627648017</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>1669.764358300255</v>
+        <v>2287.892152894576</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>1624.67950402663</v>
+        <v>2326.332227100254</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>6734.241193410006</v>
+        <v>2281.247372826634</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>745.0928637780016</v>
+        <v>7390.80906221001</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -4581,25 +4581,25 @@
         <v>9191.950163199999</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>11473.83333765396</v>
+        <v>11476.34018696902</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>12670.64501144313</v>
+        <v>13771.82087845396</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>14177.2073326636</v>
+        <v>14953.77689830456</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>15631.79621128332</v>
+        <v>16448.8982598933</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>17142.52585296026</v>
+        <v>17924.25600816054</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>18737.65041309164</v>
+        <v>19440.51339376026</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>20276.34063861241</v>
+        <v>21035.63795389164</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -4684,28 +4684,28 @@
         <v>9191.950163199999</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>11473.83333765396</v>
+        <v>11476.34018696902</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>12670.64501144313</v>
+        <v>13771.82087845396</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>14177.2073326636</v>
+        <v>14953.77689830456</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>15631.79621128332</v>
+        <v>16448.8982598933</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>17142.52585296026</v>
+        <v>17924.25600816054</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>18737.65041309164</v>
+        <v>19440.51339376026</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>20276.34063861241</v>
+        <v>21035.63795389164</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>21594.42773086953</v>
+        <v>22574.32817941241</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -4899,25 +4899,25 @@
         <v>251.9186599932068</v>
       </c>
       <c r="I82" s="18" t="n">
-        <v>275.1531675613292</v>
+        <v>316.3689062182364</v>
       </c>
       <c r="J82" s="18" t="n">
-        <v>577.006287995806</v>
+        <v>336.7595029230595</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>588.4790685160979</v>
+        <v>667.9213200358874</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>630.763261465182</v>
+        <v>707.3038573697547</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>670.6476119783471</v>
+        <v>744.3154730748016</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>708.1559550116943</v>
+        <v>778.9799721163694</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>711.1878444927193</v>
+        <v>811.3206621928357</v>
       </c>
     </row>
     <row r="83" ht="15.5" customHeight="1">
@@ -5055,28 +5055,28 @@
         <v>251.9186599932068</v>
       </c>
       <c r="H85" s="18" t="n">
-        <v>275.1531675613292</v>
+        <v>316.3689062182364</v>
       </c>
       <c r="I85" s="18" t="n">
-        <v>577.006287995806</v>
+        <v>336.7595029230595</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>588.4790685160979</v>
+        <v>667.9213200358874</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>630.763261465182</v>
+        <v>707.3038573697547</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>670.6476119783471</v>
+        <v>744.3154730748016</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>708.1559550116943</v>
+        <v>778.9799721163694</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>711.1878444927193</v>
+        <v>811.3206621928357</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>880.4912861309732</v>
+        <v>760.5720528458729</v>
       </c>
     </row>
     <row r="86" ht="15.5" customHeight="1">
@@ -5665,25 +5665,25 @@
         <v>11559.02020173353</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>12381.03796154582</v>
+        <v>13543.87202891194</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>32486.50443830054</v>
+        <v>14368.37472622686</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>23704.22349712757</v>
+        <v>35038.37930873512</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>24794.66697401871</v>
+        <v>26820.24318288862</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>26332.30267300815</v>
+        <v>27901.83214515384</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>27881.59099082957</v>
+        <v>29444.76612146401</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>28857.52441208541</v>
+        <v>31004.29330564774</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -5874,28 +5874,28 @@
         <v>11559.02020173353</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>12381.03796154582</v>
+        <v>13543.87202891194</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>32486.50443830054</v>
+        <v>14368.37472622686</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>23704.22349712757</v>
+        <v>35038.37930873512</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>24794.66697401871</v>
+        <v>26820.24318288862</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>26332.30267300815</v>
+        <v>27901.83214515384</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>27881.59099082957</v>
+        <v>29444.76612146401</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>28857.52441208541</v>
+        <v>31004.29330564774</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>34403.94590833294</v>
+        <v>31192.23651412843</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -6033,28 +6033,28 @@
         <v>1583.425610624798</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>2665.612136517841</v>
+        <v>1937.86665324947</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>-15351.00358996734</v>
+        <v>3032.922965436263</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>-7819.975766656626</v>
+        <v>-14970.9516726181</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>-7239.456212760299</v>
+        <v>-7994.525979185526</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>-7218.019348828238</v>
+        <v>-7960.219328959723</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>-7185.701745445002</v>
+        <v>-7915.160637145667</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>-6575.396402580449</v>
+        <v>-7859.457424159256</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>-11276.79383539876</v>
+        <v>-7226.00032778756</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -6242,31 +6242,31 @@
         <v>1583.425610624798</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>2665.612136517841</v>
+        <v>1937.86665324947</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>-15351.00358996734</v>
+        <v>3032.922965436263</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>-7819.975766656626</v>
+        <v>-14970.9516726181</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>-7239.456212760299</v>
+        <v>-7994.525979185526</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>-7218.019348828238</v>
+        <v>-7960.219328959723</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>-7185.701745445002</v>
+        <v>-7915.160637145667</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>-6575.396402580449</v>
+        <v>-7859.457424159256</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>-11276.79383539876</v>
+        <v>-7226.00032778756</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>-3357.530223464731</v>
+        <v>-11045.20901394877</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -6675,40 +6675,40 @@
         </is>
       </c>
       <c r="D2" s="18" t="n">
-        <v>1566.470965598953</v>
+        <v>276.294</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>1949.276590750997</v>
+        <v>319.3776</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>1985.373746056691</v>
+        <v>371.7594</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>1997.790212637807</v>
+        <v>400.3194</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>2031.847049724634</v>
+        <v>450.3366</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>2065.3085899725</v>
+        <v>499.6202</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>2275.333706574771</v>
+        <v>547.888</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>2494.651276334292</v>
+        <v>607.9227</v>
       </c>
       <c r="L2" s="18" t="n">
-        <v>2532.734778240074</v>
+        <v>664.8774</v>
       </c>
       <c r="M2" s="18" t="n">
-        <v>2569.263982085117</v>
+        <v>720.0817000000001</v>
       </c>
       <c r="N2" s="18" t="n">
-        <v>2604.012860636191</v>
+        <v>773.328</v>
       </c>
       <c r="O2" s="18" t="n">
-        <v>2114.207905387975</v>
+        <v>857.4306000000001</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
@@ -6731,37 +6731,37 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>24.43745422409889</v>
+        <v>15.59338965015526</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>1.851823157214838</v>
+        <v>16.40121285901079</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>0.6253969362583156</v>
+        <v>7.682388125222928</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>1.704725394657913</v>
+        <v>12.49432328285864</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>1.646853302880324</v>
+        <v>10.94372520465803</v>
       </c>
       <c r="J3" s="18" t="n">
-        <v>10.16918816016097</v>
+        <v>9.660898418438645</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>9.63891885949668</v>
+        <v>10.95747671056857</v>
       </c>
       <c r="L3" s="18" t="n">
-        <v>1.526606234188521</v>
+        <v>9.368740466509973</v>
       </c>
       <c r="M3" s="18" t="n">
-        <v>1.442283027772295</v>
+        <v>8.302929231765145</v>
       </c>
       <c r="N3" s="18" t="n">
-        <v>1.352483777197278</v>
+        <v>7.394480376323953</v>
       </c>
       <c r="O3" s="18" t="n">
-        <v>-18.80962120626973</v>
+        <v>10.8754112097325</v>
       </c>
     </row>
     <row r="4" ht="15.5" customHeight="1">
@@ -6887,40 +6887,40 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>1290.176965598953</v>
+        <v>0</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>1629.898990750997</v>
+        <v>0</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>1613.614346056691</v>
+        <v>0</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>1597.470812637807</v>
+        <v>0</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>1581.510449724633</v>
+        <v>0</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>1565.6883899725</v>
+        <v>0</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>1727.445706574771</v>
+        <v>0</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>1886.728576334292</v>
+        <v>0</v>
       </c>
       <c r="L6" s="18" t="n">
-        <v>1867.857378240074</v>
+        <v>0</v>
       </c>
       <c r="M6" s="18" t="n">
-        <v>1849.182282085117</v>
+        <v>0</v>
       </c>
       <c r="N6" s="18" t="n">
-        <v>1830.684860636191</v>
+        <v>0</v>
       </c>
       <c r="O6" s="18" t="n">
-        <v>1256.777305387975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="15.5" customHeight="1">
@@ -6943,37 +6943,37 @@
         <v>0</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>26.33142849472054</v>
+        <v>0</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>-0.9991198710296745</v>
+        <v>0</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>-1.000457975496793</v>
+        <v>0</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>-0.9991020046756782</v>
+        <v>0</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>-1.000439785578922</v>
+        <v>0</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>10.33138634981587</v>
+        <v>0</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>9.22071641113118</v>
+        <v>0</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>-1.000207360556449</v>
+        <v>0</v>
       </c>
       <c r="M7" s="18" t="n">
-        <v>-0.999813817292261</v>
+        <v>0</v>
       </c>
       <c r="N7" s="18" t="n">
-        <v>-1.000302762368466</v>
+        <v>0</v>
       </c>
       <c r="O7" s="18" t="n">
-        <v>-31.34933639254406</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="15.5" customHeight="1">
@@ -6993,40 +6993,40 @@
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>-82.36200950623068</v>
+        <v>-0</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-83.6155832622525</v>
+        <v>-0</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>-81.27509237299118</v>
+        <v>-0</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>-79.96189001890076</v>
+        <v>-0</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>-77.83609745324915</v>
+        <v>-0</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>-75.80893226195062</v>
+        <v>-0</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>-75.92054306509718</v>
+        <v>-0</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>-75.63095468424356</v>
+        <v>-0</v>
       </c>
       <c r="L8" s="18" t="n">
-        <v>-73.74863701828248</v>
+        <v>-0</v>
       </c>
       <c r="M8" s="18" t="n">
-        <v>-71.97323027057698</v>
+        <v>-0</v>
       </c>
       <c r="N8" s="18" t="n">
-        <v>-70.30245081773265</v>
+        <v>-0</v>
       </c>
       <c r="O8" s="18" t="n">
-        <v>-59.44435749129157</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9" ht="15.5" customHeight="1">
@@ -7205,40 +7205,40 @@
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>22519.1893690513</v>
+        <v>22216.78679838064</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>1133.960710894445</v>
+        <v>458.916062862465</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>29629.13657155834</v>
+        <v>28597.12481997377</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>1970.683018778338</v>
+        <v>597.227568820198</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>2374.753707258462</v>
+        <v>675.2176161781581</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>2762.416696326572</v>
+        <v>752.0144710625386</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>3176.368717794799</v>
+        <v>828.1218962127755</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>3621.403989374166</v>
+        <v>909.6420423021359</v>
       </c>
       <c r="L12" s="18" t="n">
-        <v>4040.803069296072</v>
+        <v>982.7800979306027</v>
       </c>
       <c r="M12" s="18" t="n">
-        <v>4441.131139725423</v>
+        <v>1053.926952002785</v>
       </c>
       <c r="N12" s="18" t="n">
-        <v>4561.886626929738</v>
+        <v>1122.898329251985</v>
       </c>
       <c r="O12" s="18" t="n">
-        <v>4830.596179661932</v>
+        <v>1219.019969883522</v>
       </c>
     </row>
     <row r="13" ht="15.5" customHeight="1">
@@ -7261,37 +7261,37 @@
         <v>0</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>-94.96446922528715</v>
+        <v>-97.93437247687</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>2512.889166873118</v>
+        <v>6131.449960936365</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>-93.34883413150136</v>
+        <v>-97.91158176711855</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>20.5040934858522</v>
+        <v>13.058681720274</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>16.3243450418969</v>
+        <v>11.3736450359609</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>14.98514043948167</v>
+        <v>10.12047348539755</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>14.01081899233456</v>
+        <v>9.843979064214349</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>11.58111829424435</v>
+        <v>8.040311708039338</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>9.907141317309719</v>
+        <v>7.239346240526556</v>
       </c>
       <c r="N13" s="18" t="n">
-        <v>2.719025478085313</v>
+        <v>6.544227483520881</v>
       </c>
       <c r="O13" s="18" t="n">
-        <v>5.890316325398093</v>
+        <v>8.560137469931783</v>
       </c>
     </row>
     <row r="14" ht="15.5" customHeight="1">
@@ -7311,40 +7311,40 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>1437.574641572811</v>
+        <v>8040.995026450317</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>58.17341244823366</v>
+        <v>143.6907481496714</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>1492.370725179938</v>
+        <v>7692.374374386706</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>98.64314112222635</v>
+        <v>149.1877657740789</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>116.8765979496489</v>
+        <v>149.9362068679646</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>133.7532177873406</v>
+        <v>150.5172270982115</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>139.6001258459983</v>
+        <v>151.1480259127368</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>145.1667422909528</v>
+        <v>149.631201845586</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>159.5430798365675</v>
+        <v>147.8137319648108</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>172.8561631148999</v>
+        <v>146.3621352969788</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>175.1867932716436</v>
+        <v>145.2033715644571</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>228.4825521346008</v>
+        <v>142.1712695912091</v>
       </c>
     </row>
     <row r="15" ht="15.5" customHeight="1">
@@ -7470,40 +7470,40 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>1411.039239501547</v>
+        <v>8000</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>16.38441673774749</v>
+        <v>100</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>1431.904700888909</v>
+        <v>7647.058823529412</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>20.03810998109924</v>
+        <v>100</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>22.16390254675085</v>
+        <v>100</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>24.19106773804938</v>
+        <v>100</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>24.07945693490282</v>
+        <v>100</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>24.36904531575644</v>
+        <v>100</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>26.25136298171751</v>
+        <v>100</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>28.02676972942302</v>
+        <v>100</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>29.69754918226735</v>
+        <v>100</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>40.55564250870844</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" ht="15.5" customHeight="1">
@@ -7629,40 +7629,40 @@
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>6.660516850839867</v>
+        <v>37.76233382818021</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>6.121184237608023</v>
+        <v>37.35979336698412</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>6.903989753679659</v>
+        <v>36.87062115981465</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>7.731041979431367</v>
+        <v>38.58169251852395</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>8.439119471282964</v>
+        <v>38.07596362365395</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>9.109534570933301</v>
+        <v>37.65660395636525</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>8.985495156566452</v>
+        <v>37.31602079257074</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>8.567530140487639</v>
+        <v>35.15743037725027</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>8.60058470675575</v>
+        <v>32.76243108879923</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>8.633211750393489</v>
+        <v>30.80344910862198</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>8.667092380617532</v>
+        <v>29.18453750989231</v>
       </c>
       <c r="O20" s="18" t="n">
-        <v>10.85371024369008</v>
+        <v>26.76251582343807</v>
       </c>
     </row>
     <row r="21" ht="15.5" customHeight="1">
@@ -7841,40 +7841,40 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>23551.84120297172</v>
+        <v>22261.66423737277</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>2133.366499330563</v>
+        <v>503.4675085795669</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>30258.3757760567</v>
+        <v>28644.76143</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>2223.643642637807</v>
+        <v>626.1728300000001</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>2288.196819724634</v>
+        <v>706.68637</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>2351.8077799725</v>
+        <v>786.1193900000001</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>2591.377306574771</v>
+        <v>863.9316</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>2858.447841334292</v>
+        <v>971.719265</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>2946.538308240074</v>
+        <v>1078.68093</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>3031.531597085117</v>
+        <v>1182.349315</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>3112.982260401691</v>
+        <v>1282.2973997655</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>2699.296975387976</v>
+        <v>1442.51967</v>
       </c>
     </row>
     <row r="25" ht="15.5" customHeight="1">
@@ -7897,22 +7897,22 @@
         <v>22261.66423737277</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>503.4675085795668</v>
+        <v>503.4675085795669</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>28644.76143</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>626.1728300000002</v>
+        <v>626.1728300000001</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>706.6863700000004</v>
+        <v>706.68637</v>
       </c>
       <c r="I25" s="18" t="n">
         <v>786.1193900000001</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>863.9316000000001</v>
+        <v>863.9316</v>
       </c>
       <c r="K25" s="18" t="n">
         <v>971.719265</v>
@@ -7947,40 +7947,40 @@
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>1503.496823126019</v>
+        <v>8057.237666171821</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>109.4440116632521</v>
+        <v>157.6402066330159</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>1524.064465753879</v>
+        <v>7705.188202369597</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>111.3051625026129</v>
+        <v>156.4183074814761</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>112.6165879481304</v>
+        <v>156.924036376346</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>113.8719797802136</v>
+        <v>157.3433960436348</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>113.8899889315912</v>
+        <v>157.6839792074292</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>114.583062909481</v>
+        <v>159.8425696227497</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>116.3382101258759</v>
+        <v>162.2375689112008</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>117.9922194925584</v>
+        <v>164.196550891378</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>119.5455793425364</v>
+        <v>165.8154624901077</v>
       </c>
       <c r="O26" s="18" t="n">
-        <v>127.674150139583</v>
+        <v>168.2374841765619</v>
       </c>
     </row>
     <row r="27" ht="15.5" customHeight="1">
@@ -8000,40 +8000,40 @@
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>1421.134813619788</v>
+        <v>8057.237666171821</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>25.82842840099958</v>
+        <v>157.6402066330159</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>1442.789373380888</v>
+        <v>7705.188202369597</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>31.34327248371215</v>
+        <v>156.4183074814761</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>34.78049049488121</v>
+        <v>156.924036376346</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>38.06304751826299</v>
+        <v>157.3433960436348</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>37.96944586649404</v>
+        <v>157.6839792074292</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>38.95210822523742</v>
+        <v>159.8425696227497</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>42.58957310759341</v>
+        <v>162.2375689112008</v>
       </c>
       <c r="M27" s="18" t="n">
-        <v>46.01898922198141</v>
+        <v>164.196550891378</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>49.2431285248038</v>
+        <v>165.8154624901077</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>68.22979264829139</v>
+        <v>168.2374841765619</v>
       </c>
     </row>
     <row r="28" ht="15.5" customHeight="1">
@@ -8106,40 +8106,40 @@
         </is>
       </c>
       <c r="D29" s="19" t="n">
-        <v>0.5701820173850928</v>
+        <v>3.232692622135787</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>1.037290015073843</v>
+        <v>6.330954782687299</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>1.581305285018977</v>
+        <v>8.444929697480063</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>2.125256623624054</v>
+        <v>10.60607325555495</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>2.628692754476609</v>
+        <v>11.86024324431063</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>3.111122055779289</v>
+        <v>12.86062314184628</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>3.330671716143939</v>
+        <v>13.83200512016606</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>3.527119928017747</v>
+        <v>14.47377146833568</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>3.951171626432216</v>
+        <v>15.05130087601154</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>4.360597150934304</v>
+        <v>15.5586861883568</v>
       </c>
       <c r="N29" s="19" t="n">
-        <v>4.757201121780186</v>
+        <v>16.01883405456484</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>6.249119093104378</v>
+        <v>15.40875376777107</v>
       </c>
     </row>
     <row r="30" ht="15.5" customHeight="1">
@@ -8159,40 +8159,40 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>23542.90946721832</v>
+        <v>22252.73250161936</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>2113.146847888531</v>
+        <v>483.247857137535</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>30226.98095608292</v>
+        <v>28613.36661002623</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>2181.185473817609</v>
+        <v>583.7146611798021</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>2234.785803546476</v>
+        <v>653.2753538218418</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>2287.553508909961</v>
+        <v>721.8651189374614</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>2515.593410361996</v>
+        <v>788.1477037872246</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>2770.458499032156</v>
+        <v>883.7299226978641</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>2846.465610309472</v>
+        <v>978.6082320693972</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>2919.496345082332</v>
+        <v>1070.314062997215</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>2989.104131384206</v>
+        <v>1158.419270748015</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>2567.177605504453</v>
+        <v>1310.400300116478</v>
       </c>
     </row>
     <row r="31" ht="15.5" customHeight="1">
@@ -8212,40 +8212,40 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>1502.926641108633</v>
+        <v>8054.004973549685</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>108.4067216481782</v>
+        <v>151.3092518503286</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>1522.48316046886</v>
+        <v>7696.743272672117</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>109.1799058789889</v>
+        <v>145.8122342259211</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>109.9878951936538</v>
+        <v>145.0637931320354</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>110.7608577244343</v>
+        <v>144.4827729017885</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>110.5593172154473</v>
+        <v>143.8519740872632</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>111.0559429814632</v>
+        <v>145.3687981544141</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>112.3870384994437</v>
+        <v>147.1862680351892</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>113.6316223416241</v>
+        <v>148.6378647030212</v>
       </c>
       <c r="N31" s="19" t="n">
-        <v>114.7883782207563</v>
+        <v>149.7966284355429</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>121.4250310464786</v>
+        <v>152.8287304087909</v>
       </c>
     </row>
     <row r="32" ht="15.5" customHeight="1">
@@ -8318,40 +8318,40 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>23542.90946721832</v>
+        <v>22252.73250161936</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>2113.146847888531</v>
+        <v>483.247857137535</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>30226.98095608292</v>
+        <v>28613.36661002623</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>2181.185473817609</v>
+        <v>583.7146611798021</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>2234.785803546476</v>
+        <v>653.2753538218418</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>2287.553508909961</v>
+        <v>721.8651189374614</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>2515.593410361996</v>
+        <v>788.1477037872246</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>2770.458499032156</v>
+        <v>883.7299226978641</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>2846.465610309472</v>
+        <v>978.6082320693972</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>2919.496345082332</v>
+        <v>1070.314062997215</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>2989.104131384206</v>
+        <v>1158.419270748015</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>2567.177605504453</v>
+        <v>1310.400300116478</v>
       </c>
     </row>
     <row r="34" ht="15.5" customHeight="1">
@@ -8374,28 +8374,28 @@
         <v>22252.73250161936</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>483.2478571375348</v>
+        <v>483.247857137535</v>
       </c>
       <c r="F34" s="19" t="n">
         <v>28613.36661002623</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>583.7146611798023</v>
+        <v>583.7146611798021</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>653.2753538218421</v>
+        <v>653.2753538218418</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>721.8651189374611</v>
+        <v>721.8651189374614</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>788.1477037872248</v>
+        <v>788.1477037872246</v>
       </c>
       <c r="K34" s="19" t="n">
         <v>883.7299226978641</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>978.6082320693974</v>
+        <v>978.6082320693972</v>
       </c>
       <c r="M34" s="19" t="n">
         <v>1070.314062997215</v>
@@ -8480,7 +8480,7 @@
         <v>-6230.765100453422</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>-135.3093999985097</v>
+        <v>-135.3093999985098</v>
       </c>
       <c r="F36" s="19" t="n">
         <v>-8011.742650807344</v>
@@ -8489,19 +8489,19 @@
         <v>-163.4401051303446</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>-182.9170990701158</v>
+        <v>-182.9170990701157</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>-202.1222333024891</v>
+        <v>-202.1222333024892</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>-220.681357060423</v>
+        <v>-220.6813570604229</v>
       </c>
       <c r="K36" s="19" t="n">
         <v>-247.444378355402</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>-274.0103049794313</v>
+        <v>-274.0103049794312</v>
       </c>
       <c r="M36" s="19" t="n">
         <v>-299.6879376392203</v>
@@ -8510,7 +8510,7 @@
         <v>-324.3573958094441</v>
       </c>
       <c r="O36" s="19" t="n">
-        <v>-366.9120840326138</v>
+        <v>-366.9120840326139</v>
       </c>
     </row>
     <row r="37" ht="15.5" customHeight="1">
@@ -8583,40 +8583,40 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>17312.14436676489</v>
+        <v>16021.96740116594</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>1977.837447890022</v>
+        <v>347.9384571390252</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>22215.23830527558</v>
+        <v>20601.62395921888</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>2017.745368687264</v>
+        <v>420.2745560494575</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>2051.86870447636</v>
+        <v>470.3582547517261</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>2085.431275607472</v>
+        <v>519.7428856349723</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>2294.912053301573</v>
+        <v>567.4663467268017</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>2523.014120676754</v>
+        <v>636.2855443424621</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>2572.455305330041</v>
+        <v>704.597927089966</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>2619.808407443112</v>
+        <v>770.6261253579951</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>2664.746735574762</v>
+        <v>834.0618749385706</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>2200.26552147184</v>
+        <v>943.4882160838645</v>
       </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
@@ -8636,40 +8636,40 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>1105.168544259961</v>
+        <v>5798.883580955773</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>101.465202900119</v>
+        <v>108.9426613322366</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>1118.944901402017</v>
+        <v>5541.655156323924</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>100.9988614381642</v>
+        <v>104.9848086426632</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>100.9853918263404</v>
+        <v>104.4459310550655</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>100.9743185949389</v>
+        <v>104.0275964892877</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>100.8604604533492</v>
+        <v>103.5734213428295</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>101.1369462582417</v>
+        <v>104.6655346711781</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>101.5682860847186</v>
+        <v>105.9741129853363</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>101.9672725617309</v>
+        <v>107.0192625861753</v>
       </c>
       <c r="N39" s="19" t="n">
-        <v>102.3323185479097</v>
+        <v>107.8535724735908</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>104.0704424510262</v>
+        <v>110.0366858943295</v>
       </c>
     </row>
     <row r="40" ht="15.5" customHeight="1">
@@ -8757,25 +8757,25 @@
         <v>1617.82217406797</v>
       </c>
       <c r="I41" s="18" t="n">
-        <v>1665.780065485877</v>
+        <v>1913.74182395875</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>1994.678851871436</v>
+        <v>1987.381049531387</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>2348.010044059727</v>
+        <v>2340.716122696916</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>2684.920266606524</v>
+        <v>2677.622793125464</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>3005.563537208241</v>
+        <v>2998.274407130115</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>3310.108597553517</v>
+        <v>3302.819618872868</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>3474.388816792919</v>
+        <v>3467.100657981287</v>
       </c>
     </row>
     <row r="42" ht="15.5" customHeight="1">
@@ -8810,25 +8810,25 @@
         <v>1617.82217406797</v>
       </c>
       <c r="I42" s="18" t="n">
-        <v>1665.780065485877</v>
+        <v>1913.74182395875</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>1994.678851871436</v>
+        <v>1987.381049531387</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>2348.010044059727</v>
+        <v>2340.716122696916</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>2684.920266606524</v>
+        <v>2677.622793125464</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>3005.563537208241</v>
+        <v>2998.274407130115</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>3310.108597553517</v>
+        <v>3302.819618872868</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>3474.388816792919</v>
+        <v>3467.100657981287</v>
       </c>
     </row>
     <row r="43" ht="15.5" customHeight="1">
@@ -8848,40 +8848,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>4128.848823323789</v>
+        <v>1830.861282523789</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>4638.668483401062</v>
+        <v>2340.680942601061</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>9249.854353906852</v>
+        <v>6951.866813106852</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>9245.061571419181</v>
+        <v>6947.074030619181</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>11549.87221358905</v>
+        <v>9251.884672789045</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>13854.59103110137</v>
+        <v>11556.60349030137</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>16049.46356022956</v>
+        <v>13861.18491603288</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>18191.14217450843</v>
+        <v>16058.56953831175</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>20346.7787608421</v>
+        <v>18200.16760464542</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>22529.76251320316</v>
+        <v>20355.52631700648</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>24695.33700088742</v>
+        <v>22538.19624469073</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>26898.92552192528</v>
+        <v>24708.85158172861</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -8901,40 +8901,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="18" t="n">
         <v>2297.987540800001</v>
       </c>
-      <c r="E44" s="18" t="n">
+      <c r="F44" s="18" t="n">
         <v>4595.975081600001</v>
       </c>
-      <c r="F44" s="18" t="n">
+      <c r="G44" s="18" t="n">
         <v>6893.962622400002</v>
       </c>
-      <c r="G44" s="18" t="n">
+      <c r="H44" s="18" t="n">
         <v>9191.950163200003</v>
       </c>
-      <c r="H44" s="18" t="n">
+      <c r="I44" s="18" t="n">
         <v>11489.937704</v>
       </c>
-      <c r="I44" s="18" t="n">
+      <c r="J44" s="18" t="n">
         <v>13787.9252448</v>
       </c>
-      <c r="J44" s="18" t="n">
+      <c r="K44" s="18" t="n">
         <v>15976.20388899668</v>
       </c>
-      <c r="K44" s="18" t="n">
+      <c r="L44" s="18" t="n">
         <v>18108.77652519336</v>
       </c>
-      <c r="L44" s="18" t="n">
+      <c r="M44" s="18" t="n">
         <v>20255.38768139004</v>
       </c>
-      <c r="M44" s="18" t="n">
+      <c r="N44" s="18" t="n">
         <v>22429.62387758672</v>
       </c>
-      <c r="N44" s="18" t="n">
+      <c r="O44" s="18" t="n">
         <v>24586.7646337834</v>
-      </c>
-      <c r="O44" s="18" t="n">
-        <v>26776.83857398008</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -9060,40 +9060,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>4416.71183893952</v>
+        <v>2118.72429813952</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>5281.256896676743</v>
+        <v>2983.269355876742</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>10232.24684581972</v>
+        <v>7934.259305019721</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>10552.4811041367</v>
+        <v>8254.493563336706</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>13167.69438765701</v>
+        <v>10869.70684685701</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>15520.37109658725</v>
+        <v>13470.34531426012</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>18044.14241210099</v>
+        <v>15848.56596556426</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>20539.15221856815</v>
+        <v>18399.28566100866</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>23031.69902744862</v>
+        <v>20877.79039777088</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>25535.3260504114</v>
+        <v>23353.80072413659</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>28005.44559844093</v>
+        <v>25841.0158635636</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>30373.3143387182</v>
+        <v>28175.95223970989</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -9113,40 +9113,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>5850.912223281434</v>
+        <v>3904.167388882484</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>4252.118614630484</v>
+        <v>675.4747894805382</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>10823.32299188663</v>
+        <v>6923.241786278937</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>8135.565404233196</v>
+        <v>4267.912376738697</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>10032.90269256855</v>
+        <v>6197.353561406114</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>11899.87187215786</v>
+        <v>8096.105163660727</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>8991.084069367334</v>
+        <v>10004.46993441717</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>14738.79425550632</v>
+        <v>6961.451003174207</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>12245.94238099535</v>
+        <v>12533.79900327339</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>18958.43741150798</v>
+        <v>10043.29170735558</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>21046.39468753233</v>
+        <v>16758.05798882429</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>22406.71440060047</v>
+        <v>18729.33809527479</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -9166,40 +9166,40 @@
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" ht="15.5" customHeight="1">
@@ -9219,40 +9219,40 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>5194.344354481434</v>
+        <v>3904.167388882484</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>-1598.79360865095</v>
+        <v>-3228.692599401946</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>6571.204377256143</v>
+        <v>4957.59003119945</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>-2687.75758765343</v>
+        <v>-4285.228400291237</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>1897.337288335353</v>
+        <v>315.82683861072</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>1866.969179589307</v>
+        <v>301.2807896168069</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>2054.300027606583</v>
+        <v>326.8543210318118</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>2241.109085515936</v>
+        <v>354.3805091816442</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>2206.158571141428</v>
+        <v>338.3011929013531</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>2170.95685548542</v>
+        <v>321.7745734003036</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>2136.055588837613</v>
+        <v>305.3707282014215</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>1426.973442566622</v>
+        <v>170.1961371786463</v>
       </c>
     </row>
     <row r="51" ht="15.5" customHeight="1">
@@ -9275,37 +9275,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>5194.344354481434</v>
+        <v>3904.167388882484</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>3595.550745830484</v>
+        <v>1965.651755079487</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>10166.75512308663</v>
+        <v>8553.140777029934</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>7478.9975354332</v>
+        <v>5881.526722795394</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>9376.334823768553</v>
+        <v>7794.82437404392</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>6280.216172960751</v>
+        <v>9677.61561338536</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>11841.11730119039</v>
+        <v>6607.070493992563</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>9383.215941053921</v>
+        <v>12195.49781037204</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>16130.91268722256</v>
+        <v>9721.517133955274</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>18253.77122989472</v>
+        <v>16452.68726062286</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>20323.17308923385</v>
+        <v>18559.14195809614</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -9325,40 +9325,40 @@
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>351.2427064010471</v>
+        <v>-1290.176965598953</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>362.7633876500504</v>
+        <v>-1278.65628434995</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>390.5687135933597</v>
+        <v>-1250.850958406641</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>434.5175729555529</v>
+        <v>-1206.902099044447</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>1593.248493888402</v>
+        <v>-1146.99287676908</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>1565.145098694797</v>
+        <v>27.56010391590189</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>1379.868151284889</v>
+        <v>-162.300607879974</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>1036.843179212265</v>
+        <v>-506.8604250494029</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>714.2629513152137</v>
+        <v>-831.0141990278089</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>411.8807023951217</v>
+        <v>-1134.919330769903</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>118.9150994239133</v>
+        <v>-1418.804158241069</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>-751.7589854902678</v>
+        <v>-1137.862205964062</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -9378,40 +9378,40 @@
         </is>
       </c>
       <c r="D53" s="18" t="n">
-        <v>351.2427064010471</v>
+        <v>-1290.176965598953</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>362.7633876500504</v>
+        <v>-1278.65628434995</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>390.5687135933597</v>
+        <v>-1250.850958406641</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>434.5175729555529</v>
+        <v>-1206.902099044447</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>1593.248493888402</v>
+        <v>-1146.99287676908</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>1565.145098694797</v>
+        <v>27.56010391590189</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>1379.868151284889</v>
+        <v>-162.300607879974</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>1036.843179212265</v>
+        <v>-506.8604250494029</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>714.2629513152137</v>
+        <v>-831.0141990278089</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>411.8807023951217</v>
+        <v>-1134.919330769903</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>118.9150994239133</v>
+        <v>-1418.804158241069</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>-751.7589854902678</v>
+        <v>-1137.862205964062</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -9643,40 +9643,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>4394.002743049103</v>
+        <v>805.8382366501532</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>4598.438814178105</v>
+        <v>-619.6246829718418</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>8888.555541096426</v>
+        <v>3347.054663488735</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>8549.874533353133</v>
+        <v>3040.801833858633</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>11603.2306439912</v>
+        <v>5027.440142171281</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>13439.41585852389</v>
+        <v>8098.064155247862</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>10342.7244398303</v>
+        <v>9813.941545715279</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>15743.23803471859</v>
+        <v>6422.191178124804</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>12923.46171039275</v>
+        <v>11666.04118232777</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>19329.36427554694</v>
+        <v>8867.418538229509</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>21120.29862533168</v>
+        <v>15294.24266895866</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>21603.3422151102</v>
+        <v>17539.86268931072</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -9696,40 +9696,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>22.7090958904173</v>
+        <v>1312.886061489367</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>682.8180824986384</v>
+        <v>3602.894038848584</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>1343.691304723296</v>
+        <v>4587.204641530987</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>2002.606570783571</v>
+        <v>5213.691729478072</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>1564.463743665812</v>
+        <v>5842.266704685733</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>2080.955238063356</v>
+        <v>5372.281159012257</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>7701.41797227069</v>
+        <v>6034.624419848986</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>4795.914183849565</v>
+        <v>11977.09448288386</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>10108.23731705587</v>
+        <v>9211.749215443109</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>6205.96177486446</v>
+        <v>14486.38218590708</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>6885.146973109251</v>
+        <v>10546.77319460495</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>8769.972123608004</v>
+        <v>10636.08955039917</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -9805,22 +9805,22 @@
         <v>22261.66423737277</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>503.4675085795668</v>
+        <v>503.4675085795669</v>
       </c>
       <c r="F61" s="18" t="n">
         <v>28644.76143</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>626.1728300000002</v>
+        <v>626.1728300000001</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>706.6863700000004</v>
+        <v>706.68637</v>
       </c>
       <c r="I61" s="18" t="n">
         <v>786.1193900000001</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>863.9316000000001</v>
+        <v>863.9316</v>
       </c>
       <c r="K61" s="18" t="n">
         <v>971.719265</v>
@@ -9858,7 +9858,7 @@
         <v>-6230.765100453422</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>-135.3093999985097</v>
+        <v>-135.3093999985098</v>
       </c>
       <c r="F62" s="18" t="n">
         <v>-8011.742650807344</v>
@@ -9867,19 +9867,19 @@
         <v>-163.4401051303446</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>-182.9170990701158</v>
+        <v>-182.9170990701157</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>-202.1222333024891</v>
+        <v>-202.1222333024892</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>-220.681357060423</v>
+        <v>-220.6813570604229</v>
       </c>
       <c r="K62" s="18" t="n">
         <v>-247.444378355402</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>-274.0103049794313</v>
+        <v>-274.0103049794312</v>
       </c>
       <c r="M62" s="18" t="n">
         <v>-299.6879376392203</v>
@@ -9888,7 +9888,7 @@
         <v>-324.3573958094441</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>-366.9120840326138</v>
+        <v>-366.9120840326139</v>
       </c>
     </row>
     <row r="63" ht="15.5" customHeight="1">
@@ -9973,22 +9973,22 @@
         <v>5072.988165965547</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>518.3450736696105</v>
+        <v>518.3450736696103</v>
       </c>
       <c r="I64" s="18" t="n">
         <v>578.6360169714835</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>637.9969059532758</v>
+        <v>637.9969059532757</v>
       </c>
       <c r="K64" s="18" t="n">
         <v>715.9316482884335</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>795.9821811849524</v>
+        <v>795.9821811849523</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>874.2409444840678</v>
+        <v>874.2409444840675</v>
       </c>
       <c r="N64" s="18" t="n">
         <v>949.8253574192613</v>
@@ -10132,22 +10132,22 @@
         <v>4705.502956340694</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>154.5314161410064</v>
+        <v>154.5314161410062</v>
       </c>
       <c r="I67" s="18" t="n">
         <v>218.4620960181653</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>240.61202569499</v>
+        <v>240.6120256949899</v>
       </c>
       <c r="K67" s="18" t="n">
         <v>281.9050351608179</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>366.296734188613</v>
+        <v>366.2967341886129</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>448.8515519576918</v>
+        <v>448.8515519576915</v>
       </c>
       <c r="N67" s="18" t="n">
         <v>528.6911467371491</v>
@@ -10332,40 +10332,40 @@
         </is>
       </c>
       <c r="D71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="E71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="F71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="G71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="I71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="J71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="K71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="L71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="M71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="N71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="O71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" ht="15.5" customHeight="1">
@@ -10397,22 +10397,22 @@
         <v>-4705.502956340694</v>
       </c>
       <c r="H72" s="18" t="n">
-        <v>-154.5314161410064</v>
+        <v>-154.5314161410062</v>
       </c>
       <c r="I72" s="18" t="n">
         <v>-218.4620960181653</v>
       </c>
       <c r="J72" s="18" t="n">
-        <v>-240.61202569499</v>
+        <v>-240.6120256949899</v>
       </c>
       <c r="K72" s="18" t="n">
         <v>-281.9050351608179</v>
       </c>
       <c r="L72" s="18" t="n">
-        <v>-366.296734188613</v>
+        <v>-366.2967341886129</v>
       </c>
       <c r="M72" s="18" t="n">
-        <v>-448.8515519576918</v>
+        <v>-448.8515519576915</v>
       </c>
       <c r="N72" s="18" t="n">
         <v>-528.6911467371491</v>
@@ -10438,40 +10438,40 @@
         </is>
       </c>
       <c r="D73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="E73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="F73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="G73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="I73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="J73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="K73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="N73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="O73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" ht="15.5" customHeight="1">
@@ -10491,40 +10491,40 @@
         </is>
       </c>
       <c r="D74" s="18" t="n">
-        <v>-9819.812471483458</v>
+        <v>-12117.80001228346</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>-1278.643515740971</v>
+        <v>-3576.631056540971</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>-13346.04638721943</v>
+        <v>-15644.03392801943</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>-2407.515415540694</v>
+        <v>-4705.502956340694</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>2143.456124658994</v>
+        <v>-154.5314161410062</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>2079.525444781835</v>
+        <v>-218.4620960181653</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>2057.37551510501</v>
+        <v>-240.6120256949899</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>2016.082505639182</v>
+        <v>-281.9050351608179</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>1931.690806611387</v>
+        <v>-366.2967341886129</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>1849.135988842309</v>
+        <v>-448.8515519576915</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>1769.296394062851</v>
+        <v>-528.6911467371491</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>1524.695461894782</v>
+        <v>-773.2920789052182</v>
       </c>
     </row>
     <row r="75" ht="15.5" customHeight="1">
@@ -10544,40 +10544,40 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>2297.987540800001</v>
+        <v>0</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>2297.987540800001</v>
+        <v>0</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>2297.987540800001</v>
+        <v>0</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" ht="15.5" customHeight="1">
@@ -10600,37 +10600,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="18" t="n">
         <v>2297.987540800001</v>
       </c>
-      <c r="F76" s="18" t="n">
+      <c r="G76" s="18" t="n">
         <v>4595.975081600001</v>
       </c>
-      <c r="G76" s="18" t="n">
+      <c r="H76" s="18" t="n">
         <v>6893.962622400002</v>
       </c>
-      <c r="H76" s="18" t="n">
+      <c r="I76" s="18" t="n">
         <v>9191.950163200003</v>
       </c>
-      <c r="I76" s="18" t="n">
+      <c r="J76" s="18" t="n">
         <v>11489.937704</v>
       </c>
-      <c r="J76" s="18" t="n">
+      <c r="K76" s="18" t="n">
         <v>13787.9252448</v>
       </c>
-      <c r="K76" s="18" t="n">
+      <c r="L76" s="18" t="n">
         <v>15976.20388899668</v>
       </c>
-      <c r="L76" s="18" t="n">
+      <c r="M76" s="18" t="n">
         <v>18108.77652519336</v>
       </c>
-      <c r="M76" s="18" t="n">
+      <c r="N76" s="18" t="n">
         <v>20255.38768139004</v>
       </c>
-      <c r="N76" s="18" t="n">
+      <c r="O76" s="18" t="n">
         <v>22429.62387758672</v>
-      </c>
-      <c r="O76" s="18" t="n">
-        <v>24586.7646337834</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -10650,40 +10650,40 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>2297.987540800001</v>
+        <v>0</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>2297.987540800001</v>
+        <v>0</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>2297.987540800001</v>
+        <v>0</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" ht="15.5" customHeight="1">
@@ -10703,40 +10703,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="18" t="n">
         <v>2297.987540800001</v>
       </c>
-      <c r="E78" s="18" t="n">
+      <c r="F78" s="18" t="n">
         <v>4595.975081600001</v>
       </c>
-      <c r="F78" s="18" t="n">
+      <c r="G78" s="18" t="n">
         <v>6893.962622400002</v>
       </c>
-      <c r="G78" s="18" t="n">
+      <c r="H78" s="18" t="n">
         <v>9191.950163200003</v>
       </c>
-      <c r="H78" s="18" t="n">
+      <c r="I78" s="18" t="n">
         <v>11489.937704</v>
       </c>
-      <c r="I78" s="18" t="n">
+      <c r="J78" s="18" t="n">
         <v>13787.9252448</v>
       </c>
-      <c r="J78" s="18" t="n">
+      <c r="K78" s="18" t="n">
         <v>15976.20388899668</v>
       </c>
-      <c r="K78" s="18" t="n">
+      <c r="L78" s="18" t="n">
         <v>18108.77652519336</v>
       </c>
-      <c r="L78" s="18" t="n">
+      <c r="M78" s="18" t="n">
         <v>20255.38768139004</v>
       </c>
-      <c r="M78" s="18" t="n">
+      <c r="N78" s="18" t="n">
         <v>22429.62387758672</v>
       </c>
-      <c r="N78" s="18" t="n">
+      <c r="O78" s="18" t="n">
         <v>24586.7646337834</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>26776.83857398008</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -10862,40 +10862,40 @@
         </is>
       </c>
       <c r="D81" s="18" t="n">
-        <v>18.94671257157026</v>
+        <v>107.4199046555969</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>19.2350870513213</v>
+        <v>117.3986682541237</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>18.69667609679185</v>
+        <v>99.84923006949178</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>18.3945845414689</v>
+        <v>91.79800170185423</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>17.90556319570954</v>
+        <v>80.78705073684975</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>17.43923027784017</v>
+        <v>72.08954340783623</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>17.46490543826641</v>
+        <v>72.5303128117947</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>17.39828797896699</v>
+        <v>71.39503313951192</v>
       </c>
       <c r="L81" s="18" t="n">
-        <v>16.96527606001113</v>
+        <v>64.62626748876401</v>
       </c>
       <c r="M81" s="18" t="n">
-        <v>16.55685813106468</v>
+        <v>59.07515668380073</v>
       </c>
       <c r="N81" s="18" t="n">
-        <v>16.17250886307927</v>
+        <v>54.45738557017362</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>13.67469252075458</v>
+        <v>33.71834762035453</v>
       </c>
     </row>
     <row r="82" ht="15.5" customHeight="1">
@@ -10933,22 +10933,22 @@
         <v>1617.82217406797</v>
       </c>
       <c r="J82" s="18" t="n">
-        <v>1665.780065485877</v>
+        <v>1913.74182395875</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>1994.678851871436</v>
+        <v>1987.381049531387</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>2348.010044059727</v>
+        <v>2340.716122696916</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>2684.920266606524</v>
+        <v>2677.622793125464</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>3005.563537208241</v>
+        <v>2998.274407130115</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>3310.108597553517</v>
+        <v>3302.819618872868</v>
       </c>
     </row>
     <row r="83" ht="15.5" customHeight="1">
@@ -11089,25 +11089,25 @@
         <v>1617.82217406797</v>
       </c>
       <c r="I85" s="18" t="n">
-        <v>1665.780065485877</v>
+        <v>1913.74182395875</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>1994.678851871436</v>
+        <v>1987.381049531387</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>2348.010044059727</v>
+        <v>2340.716122696916</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>2684.920266606524</v>
+        <v>2677.622793125464</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>3005.563537208241</v>
+        <v>2998.274407130115</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>3310.108597553517</v>
+        <v>3302.819618872868</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>3474.388816792919</v>
+        <v>3467.100657981287</v>
       </c>
     </row>
     <row r="86" ht="15.5" customHeight="1">
@@ -11684,37 +11684,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>30086.51224784835</v>
+        <v>28139.7674134494</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>36297.54862107935</v>
+        <v>34011.08176152834</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>74813.38872317436</v>
+        <v>72543.20650831767</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>82193.20491700232</v>
+        <v>79939.16623556451</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>85056.1729064197</v>
+        <v>82818.09458789506</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>59051.19510788129</v>
+        <v>85794.37788807284</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>58618.98046590371</v>
+        <v>59859.27348030308</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>26115.7436115348</v>
+        <v>59537.17104540699</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>24863.95020488404</v>
+        <v>27186.63827281338</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>28174.98411067433</v>
+        <v>26083.42788219973</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>31543.76636293618</v>
+        <v>29537.73713235005</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -11734,40 +11734,40 @@
         </is>
       </c>
       <c r="D97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="E97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="F97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="G97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="H97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="I97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="J97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="K97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="N97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="O97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" ht="15.5" customHeight="1">
@@ -11787,40 +11787,40 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>17312.14436676489</v>
+        <v>16021.96740116594</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>1977.837447890022</v>
+        <v>347.9384571390252</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>22215.23830527558</v>
+        <v>20601.62395921888</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>2017.745368687264</v>
+        <v>420.2745560494575</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>2051.86870447636</v>
+        <v>470.3582547517261</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>2085.431275607472</v>
+        <v>519.7428856349723</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>2294.912053301573</v>
+        <v>567.4663467268017</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>2523.014120676754</v>
+        <v>636.2855443424621</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>2572.455305330041</v>
+        <v>704.597927089966</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>2619.808407443112</v>
+        <v>770.6261253579951</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>2664.746735574762</v>
+        <v>834.0618749385706</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>2200.26552147184</v>
+        <v>943.4882160838645</v>
       </c>
     </row>
     <row r="99" ht="15.5" customHeight="1">
@@ -11852,22 +11852,22 @@
         <v>4705.502956340694</v>
       </c>
       <c r="H99" s="20" t="n">
-        <v>154.5314161410064</v>
+        <v>154.5314161410062</v>
       </c>
       <c r="I99" s="20" t="n">
         <v>218.4620960181653</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>240.61202569499</v>
+        <v>240.6120256949899</v>
       </c>
       <c r="K99" s="20" t="n">
         <v>281.9050351608179</v>
       </c>
       <c r="L99" s="20" t="n">
-        <v>366.296734188613</v>
+        <v>366.2967341886129</v>
       </c>
       <c r="M99" s="20" t="n">
-        <v>448.8515519576918</v>
+        <v>448.8515519576915</v>
       </c>
       <c r="N99" s="20" t="n">
         <v>528.6911467371491</v>
@@ -11893,40 +11893,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>30086.51224784835</v>
+        <v>28139.7674134494</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>36297.54862107935</v>
+        <v>34011.08176152834</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>74813.38872317436</v>
+        <v>72543.20650831767</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>82193.20491700232</v>
+        <v>79939.16623556451</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>85056.1729064197</v>
+        <v>82818.09458789506</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>59051.19510788129</v>
+        <v>85794.37788807284</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>58618.98046590371</v>
+        <v>59859.27348030308</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>26115.7436115348</v>
+        <v>59537.17104540699</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>24863.95020488404</v>
+        <v>27186.63827281338</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>28174.98411067433</v>
+        <v>26083.42788219973</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>31543.76636293618</v>
+        <v>29537.73713235005</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>34690.48941628031</v>
+        <v>33260.54665792526</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -11999,40 +11999,40 @@
         </is>
       </c>
       <c r="D102" s="18" t="n">
-        <v>-434.7034304505982</v>
+        <v>-0</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>-434.7034304505982</v>
+        <v>-0</v>
       </c>
       <c r="F102" s="18" t="n">
-        <v>-434.7034304505983</v>
+        <v>-0</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>-434.7034304505982</v>
+        <v>-0</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>-434.7034304505982</v>
+        <v>-0</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>-434.7034304505982</v>
+        <v>-0</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>-434.7034304505983</v>
+        <v>-0</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>-434.7034304505983</v>
+        <v>-0</v>
       </c>
       <c r="L102" s="18" t="n">
-        <v>-434.7034304505982</v>
+        <v>-0</v>
       </c>
       <c r="M102" s="18" t="n">
-        <v>-434.7034304505982</v>
+        <v>-0</v>
       </c>
       <c r="N102" s="18" t="n">
-        <v>-434.7034304505982</v>
+        <v>-0</v>
       </c>
       <c r="O102" s="18" t="n">
-        <v>-434.7034304505982</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="103" ht="15.5" customHeight="1">
@@ -12055,37 +12055,37 @@
         <v>0</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>351.2427064010471</v>
+        <v>-1290.176965598953</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>362.7633876500504</v>
+        <v>-1278.65628434995</v>
       </c>
       <c r="G103" s="18" t="n">
-        <v>390.5687135933597</v>
+        <v>-1250.850958406641</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>434.5175729555529</v>
+        <v>-1206.902099044447</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>1593.248493888402</v>
+        <v>-1146.99287676908</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>1565.145098694797</v>
+        <v>27.56010391590189</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>1379.868151284889</v>
+        <v>-162.300607879974</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>1036.843179212265</v>
+        <v>-506.8604250494029</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>714.2629513152137</v>
+        <v>-831.0141990278089</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>411.8807023951217</v>
+        <v>-1134.919330769903</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>118.9150994239133</v>
+        <v>-1418.804158241069</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -12105,40 +12105,40 @@
         </is>
       </c>
       <c r="D104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="E104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="F104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="G104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="H104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="I104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="J104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="K104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="L104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="M104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="N104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="O104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" ht="15.5" customHeight="1">
@@ -12158,40 +12158,40 @@
         </is>
       </c>
       <c r="D105" s="18" t="n">
-        <v>-1290.176965598953</v>
+        <v>-0</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>-1629.898990750997</v>
+        <v>-0</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>-1613.614346056691</v>
+        <v>-0</v>
       </c>
       <c r="G105" s="18" t="n">
-        <v>-1597.470812637807</v>
+        <v>-0</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>-1581.510449724633</v>
+        <v>-0</v>
       </c>
       <c r="I105" s="18" t="n">
-        <v>-1565.6883899725</v>
+        <v>-0</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>-1727.445706574771</v>
+        <v>-0</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>-1886.728576334292</v>
+        <v>-0</v>
       </c>
       <c r="L105" s="18" t="n">
-        <v>-1867.857378240074</v>
+        <v>-0</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>-1849.182282085117</v>
+        <v>-0</v>
       </c>
       <c r="N105" s="18" t="n">
-        <v>-1830.684860636191</v>
+        <v>-0</v>
       </c>
       <c r="O105" s="18" t="n">
-        <v>-1256.777305387975</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="106" ht="15.5" customHeight="1">
@@ -12264,40 +12264,40 @@
         </is>
       </c>
       <c r="D107" s="18" t="n">
-        <v>351.2427064010471</v>
+        <v>-1290.176965598953</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>362.7633876500504</v>
+        <v>-1278.65628434995</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>390.5687135933597</v>
+        <v>-1250.850958406641</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>434.5175729555529</v>
+        <v>-1206.902099044447</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>1593.248493888402</v>
+        <v>-1146.99287676908</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>1565.145098694797</v>
+        <v>27.56010391590189</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>1379.868151284889</v>
+        <v>-162.300607879974</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>1036.843179212265</v>
+        <v>-506.8604250494029</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>714.2629513152137</v>
+        <v>-831.0141990278089</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>411.8807023951217</v>
+        <v>-1134.919330769903</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>118.9150994239133</v>
+        <v>-1418.804158241069</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>-751.7589854902678</v>
+        <v>-1137.862205964062</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -20819,25 +20819,25 @@
         <v>1301.453267849734</v>
       </c>
       <c r="I41" s="18" t="n">
-        <v>1329.020562562816</v>
+        <v>1535.766582378783</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>1326.757531835549</v>
+        <v>1559.706514568245</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>1640.706186689973</v>
+        <v>1553.970013807372</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>1940.604793531722</v>
+        <v>1856.76672414609</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>2226.583565091871</v>
+        <v>2145.626573917291</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>2498.787935360681</v>
+        <v>2420.674939575357</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>2713.816763947046</v>
+        <v>2606.395787435297</v>
       </c>
     </row>
     <row r="42">
@@ -20872,25 +20872,25 @@
         <v>1301.453267849734</v>
       </c>
       <c r="I42" s="18" t="n">
-        <v>1329.020562562816</v>
+        <v>1535.766582378783</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>1326.757531835549</v>
+        <v>1559.706514568245</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>1640.706186689973</v>
+        <v>1553.970013807372</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>1940.604793531722</v>
+        <v>1856.76672414609</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>2226.583565091871</v>
+        <v>2145.626573917291</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>2498.787935360681</v>
+        <v>2420.674939575357</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>2713.816763947046</v>
+        <v>2606.395787435297</v>
       </c>
     </row>
     <row r="43">
@@ -20928,22 +20928,22 @@
         <v>55.44556492223289</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>914.7876005156355</v>
+        <v>59.81317191628446</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>1774.684949225458</v>
+        <v>919.710520626107</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>2634.72899123361</v>
+        <v>1779.75456263426</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>3494.570452895648</v>
+        <v>2639.596024296297</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>4354.192516369377</v>
+        <v>3499.218087770026</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>5217.582355074921</v>
+        <v>4362.607926475569</v>
       </c>
     </row>
     <row r="44">
@@ -20981,22 +20981,22 @@
         <v>0</v>
       </c>
       <c r="J44" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="18" t="n">
         <v>854.9744285993511</v>
       </c>
-      <c r="K44" s="18" t="n">
+      <c r="L44" s="18" t="n">
         <v>1709.948857198702</v>
       </c>
-      <c r="L44" s="18" t="n">
+      <c r="M44" s="18" t="n">
         <v>2564.923285798053</v>
       </c>
-      <c r="M44" s="18" t="n">
+      <c r="N44" s="18" t="n">
         <v>3419.897714397404</v>
       </c>
-      <c r="N44" s="18" t="n">
+      <c r="O44" s="18" t="n">
         <v>4274.872142996755</v>
-      </c>
-      <c r="O44" s="18" t="n">
-        <v>5129.846571596107</v>
       </c>
     </row>
     <row r="45">
@@ -21137,25 +21137,25 @@
         <v>1352.403769048645</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>1384.466127485049</v>
+        <v>1591.212147301016</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>2241.545132351185</v>
+        <v>1619.519686484529</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>3415.39113591543</v>
+        <v>2473.680534433479</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>4575.333784765333</v>
+        <v>3636.52128678035</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>5721.154017987519</v>
+        <v>4785.222598213588</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>6852.980451730058</v>
+        <v>5919.893027345383</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>7931.399119021967</v>
+        <v>6969.003713910866</v>
       </c>
     </row>
     <row r="48">
@@ -21193,22 +21193,22 @@
         <v>1577.77332738734</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>-1950.442474107829</v>
+        <v>1811.836825463851</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>1647.001590470578</v>
+        <v>-1718.883879916045</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>-2127.66904892167</v>
+        <v>1867.813440901686</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>2999.495542656086</v>
+        <v>-1918.089302726937</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>3931.012726220628</v>
+        <v>3197.932903991988</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>4770.492238205654</v>
+        <v>4046.742312711115</v>
       </c>
     </row>
     <row r="49">
@@ -21352,22 +21352,22 @@
         <v>1339.977276207577</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>-2184.505972184341</v>
+        <v>1577.77332738734</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>1415.442996278794</v>
+        <v>-1950.442474107829</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>-2348.480899352778</v>
+        <v>1647.001590470578</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>2789.915796461353</v>
+        <v>-2127.66904892167</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>3732.575364884725</v>
+        <v>2999.495542656086</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>4654.762651715166</v>
+        <v>3931.012726220627</v>
       </c>
     </row>
     <row r="52">
@@ -21402,25 +21402,25 @@
         <v>0</v>
       </c>
       <c r="I52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="18" t="n">
         <v>-74.11679431732691</v>
       </c>
-      <c r="J52" s="18" t="n">
+      <c r="K52" s="18" t="n">
         <v>420.309520466836</v>
       </c>
-      <c r="K52" s="18" t="n">
+      <c r="L52" s="18" t="n">
         <v>345.7993353962562</v>
       </c>
-      <c r="L52" s="18" t="n">
+      <c r="M52" s="18" t="n">
         <v>277.9086329187738</v>
       </c>
-      <c r="M52" s="18" t="n">
+      <c r="N52" s="18" t="n">
         <v>216.5838862209679</v>
       </c>
-      <c r="N52" s="18" t="n">
+      <c r="O52" s="18" t="n">
         <v>161.7537262182767</v>
-      </c>
-      <c r="O52" s="18" t="n">
-        <v>40.53247530206283</v>
       </c>
     </row>
     <row r="53">
@@ -21455,25 +21455,25 @@
         <v>0</v>
       </c>
       <c r="I53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="18" t="n">
         <v>-74.11679431732691</v>
       </c>
-      <c r="J53" s="18" t="n">
+      <c r="K53" s="18" t="n">
         <v>420.309520466836</v>
       </c>
-      <c r="K53" s="18" t="n">
+      <c r="L53" s="18" t="n">
         <v>345.7993353962562</v>
       </c>
-      <c r="L53" s="18" t="n">
+      <c r="M53" s="18" t="n">
         <v>277.9086329187738</v>
       </c>
-      <c r="M53" s="18" t="n">
+      <c r="N53" s="18" t="n">
         <v>216.5838862209679</v>
       </c>
-      <c r="N53" s="18" t="n">
+      <c r="O53" s="18" t="n">
         <v>161.7537262182767</v>
-      </c>
-      <c r="O53" s="18" t="n">
-        <v>40.53247530206283</v>
       </c>
     </row>
     <row r="54">
@@ -21720,25 +21720,25 @@
         <v>1320.715272028655</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>1482.653160565734</v>
+        <v>1556.769954883061</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>-1552.825099180813</v>
+        <v>1715.027885606705</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>1967.935724217034</v>
+        <v>-1323.43956109901</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>-1877.001274140192</v>
+        <v>2186.371918160646</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>3186.559587835176</v>
+        <v>-1669.700510850042</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>4061.073617970818</v>
+        <v>3382.82395574487</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>4775.271011831695</v>
+        <v>4172.742337253369</v>
       </c>
     </row>
     <row r="59">
@@ -21773,25 +21773,25 @@
         <v>31.68849701998988</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>-98.18703308068484</v>
+        <v>34.44219241795531</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>3794.370231531998</v>
+        <v>-95.50819912217526</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>1447.455411698397</v>
+        <v>3797.120095532488</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>6452.335058905525</v>
+        <v>1450.149368619704</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>2534.594430152344</v>
+        <v>6454.923109063629</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>2791.90683375924</v>
+        <v>2537.069071600513</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>3156.128107190272</v>
+        <v>2796.261376657497</v>
       </c>
     </row>
     <row r="60">
@@ -22680,19 +22680,19 @@
         <v>0</v>
       </c>
       <c r="K76" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="18" t="n">
         <v>854.9744285993511</v>
       </c>
-      <c r="L76" s="18" t="n">
+      <c r="M76" s="18" t="n">
         <v>1709.948857198702</v>
       </c>
-      <c r="M76" s="18" t="n">
+      <c r="N76" s="18" t="n">
         <v>2564.923285798053</v>
       </c>
-      <c r="N76" s="18" t="n">
+      <c r="O76" s="18" t="n">
         <v>3419.897714397404</v>
-      </c>
-      <c r="O76" s="18" t="n">
-        <v>4274.872142996755</v>
       </c>
     </row>
     <row r="77">
@@ -22783,22 +22783,22 @@
         <v>0</v>
       </c>
       <c r="J78" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="18" t="n">
         <v>854.9744285993511</v>
       </c>
-      <c r="K78" s="18" t="n">
+      <c r="L78" s="18" t="n">
         <v>1709.948857198702</v>
       </c>
-      <c r="L78" s="18" t="n">
+      <c r="M78" s="18" t="n">
         <v>2564.923285798053</v>
       </c>
-      <c r="M78" s="18" t="n">
+      <c r="N78" s="18" t="n">
         <v>3419.897714397404</v>
       </c>
-      <c r="N78" s="18" t="n">
+      <c r="O78" s="18" t="n">
         <v>4274.872142996755</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>5129.846571596107</v>
       </c>
     </row>
     <row r="79">
@@ -22995,22 +22995,22 @@
         <v>1301.453267849734</v>
       </c>
       <c r="J82" s="18" t="n">
-        <v>1329.020562562816</v>
+        <v>1535.766582378783</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>1326.757531835549</v>
+        <v>1559.706514568245</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>1640.706186689973</v>
+        <v>1553.970013807372</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>1940.604793531722</v>
+        <v>1856.76672414609</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>2226.583565091871</v>
+        <v>2145.626573917291</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>2498.787935360681</v>
+        <v>2420.674939575357</v>
       </c>
     </row>
     <row r="83">
@@ -23151,25 +23151,25 @@
         <v>1301.453267849734</v>
       </c>
       <c r="I85" s="18" t="n">
-        <v>1329.020562562816</v>
+        <v>1535.766582378783</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>1326.757531835549</v>
+        <v>1559.706514568245</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>1640.706186689973</v>
+        <v>1553.970013807372</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>1940.604793531722</v>
+        <v>1856.76672414609</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>2226.583565091871</v>
+        <v>2145.626573917291</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>2498.787935360681</v>
+        <v>2420.674939575357</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>2713.816763947046</v>
+        <v>2606.395787435297</v>
       </c>
     </row>
     <row r="86">
@@ -23761,22 +23761,22 @@
         <v>69633.10339805599</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>1652988.54845142</v>
+        <v>70261.19836605332</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>3276197.41813584</v>
+        <v>1653682.30300708</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>4890752.482716009</v>
+        <v>3276965.608485644</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>6543666.583187569</v>
+        <v>4891606.088890755</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>8200687.685176608</v>
+        <v>6544602.751974707</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>9849332.404532343</v>
+        <v>8201702.699148507</v>
       </c>
     </row>
     <row r="97">
@@ -23970,25 +23970,25 @@
         <v>69633.10339805599</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>1652988.54845142</v>
+        <v>70261.19836605332</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>3276197.41813584</v>
+        <v>1653682.30300708</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>4890752.482716009</v>
+        <v>3276965.608485644</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>6543666.583187569</v>
+        <v>4891606.088890755</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>8200687.685176608</v>
+        <v>6544602.751974707</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>9849332.404532343</v>
+        <v>8201702.699148507</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>11482332.24588161</v>
+        <v>9850565.264000123</v>
       </c>
     </row>
     <row r="101">
@@ -24132,22 +24132,22 @@
         <v>0</v>
       </c>
       <c r="J103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="18" t="n">
         <v>-74.11679431732691</v>
       </c>
-      <c r="K103" s="18" t="n">
+      <c r="L103" s="18" t="n">
         <v>420.309520466836</v>
       </c>
-      <c r="L103" s="18" t="n">
+      <c r="M103" s="18" t="n">
         <v>345.7993353962562</v>
       </c>
-      <c r="M103" s="18" t="n">
+      <c r="N103" s="18" t="n">
         <v>277.9086329187738</v>
       </c>
-      <c r="N103" s="18" t="n">
+      <c r="O103" s="18" t="n">
         <v>216.5838862209679</v>
-      </c>
-      <c r="O103" s="18" t="n">
-        <v>161.7537262182767</v>
       </c>
     </row>
     <row r="104">
@@ -24341,25 +24341,25 @@
         <v>0</v>
       </c>
       <c r="I107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="18" t="n">
         <v>-74.11679431732691</v>
       </c>
-      <c r="J107" s="18" t="n">
+      <c r="K107" s="18" t="n">
         <v>420.309520466836</v>
       </c>
-      <c r="K107" s="18" t="n">
+      <c r="L107" s="18" t="n">
         <v>345.7993353962562</v>
       </c>
-      <c r="L107" s="18" t="n">
+      <c r="M107" s="18" t="n">
         <v>277.9086329187738</v>
       </c>
-      <c r="M107" s="18" t="n">
+      <c r="N107" s="18" t="n">
         <v>216.5838862209679</v>
       </c>
-      <c r="N107" s="18" t="n">
+      <c r="O107" s="18" t="n">
         <v>161.7537262182767</v>
-      </c>
-      <c r="O107" s="18" t="n">
-        <v>40.53247530206283</v>
       </c>
     </row>
     <row r="108">

--- a/backend/Rwanda/financial-statements-CleanStep.xlsx
+++ b/backend/Rwanda/financial-statements-CleanStep.xlsx
@@ -644,40 +644,40 @@
         </is>
       </c>
       <c r="D2" s="18" t="n">
-        <v>727.7454832683711</v>
+        <v>0</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>1313.109508596396</v>
+        <v>0</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>1299.978413510435</v>
+        <v>0</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>1286.978629375328</v>
+        <v>0</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>1274.108843081578</v>
+        <v>0</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>1261.367754650761</v>
+        <v>0</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>1815.9698845289</v>
+        <v>0</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>2362.182788199423</v>
+        <v>0</v>
       </c>
       <c r="L2" s="18" t="n">
-        <v>2338.560960317429</v>
+        <v>0</v>
       </c>
       <c r="M2" s="18" t="n">
-        <v>2315.175350714254</v>
+        <v>0</v>
       </c>
       <c r="N2" s="18" t="n">
-        <v>2292.023597207112</v>
+        <v>0</v>
       </c>
       <c r="O2" s="18" t="n">
-        <v>1409.834850550013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
@@ -700,37 +700,37 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>80.43526738209383</v>
+        <v>0</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>-0.999999999999801</v>
+        <v>0</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>-1.000000000000179</v>
+        <v>0</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>-0.9999999999998122</v>
+        <v>0</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>-1.000000000000056</v>
+        <v>0</v>
       </c>
       <c r="J3" s="18" t="n">
-        <v>43.96831358921918</v>
+        <v>0</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>30.07830186634517</v>
+        <v>0</v>
       </c>
       <c r="L3" s="18" t="n">
-        <v>-0.9999999999999787</v>
+        <v>0</v>
       </c>
       <c r="M3" s="18" t="n">
-        <v>-1.000000000000034</v>
+        <v>0</v>
       </c>
       <c r="N3" s="18" t="n">
-        <v>-0.9999999999999565</v>
+        <v>0</v>
       </c>
       <c r="O3" s="18" t="n">
-        <v>-38.48951414514529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" ht="15.5" customHeight="1">
@@ -856,40 +856,40 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>727.7454832683711</v>
+        <v>0</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>1313.109508596396</v>
+        <v>0</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>1299.978413510435</v>
+        <v>0</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>1286.978629375328</v>
+        <v>0</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>1274.108843081578</v>
+        <v>0</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>1261.367754650761</v>
+        <v>0</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>1815.9698845289</v>
+        <v>0</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>2362.182788199423</v>
+        <v>0</v>
       </c>
       <c r="L6" s="18" t="n">
-        <v>2338.560960317429</v>
+        <v>0</v>
       </c>
       <c r="M6" s="18" t="n">
-        <v>2315.175350714254</v>
+        <v>0</v>
       </c>
       <c r="N6" s="18" t="n">
-        <v>2292.023597207112</v>
+        <v>0</v>
       </c>
       <c r="O6" s="18" t="n">
-        <v>1409.834850550013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="15.5" customHeight="1">
@@ -912,37 +912,37 @@
         <v>0</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>80.43526738209383</v>
+        <v>0</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>-0.999999999999801</v>
+        <v>0</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>-1.000000000000179</v>
+        <v>0</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>-0.9999999999998122</v>
+        <v>0</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>-1.000000000000056</v>
+        <v>0</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>43.96831358921918</v>
+        <v>0</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>30.07830186634517</v>
+        <v>0</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>-0.9999999999999787</v>
+        <v>0</v>
       </c>
       <c r="M7" s="18" t="n">
-        <v>-1.000000000000034</v>
+        <v>0</v>
       </c>
       <c r="N7" s="18" t="n">
-        <v>-0.9999999999999565</v>
+        <v>0</v>
       </c>
       <c r="O7" s="18" t="n">
-        <v>-38.48951414514529</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="15.5" customHeight="1">
@@ -962,40 +962,40 @@
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>-100</v>
+        <v>-0</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-100</v>
+        <v>-0</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>-100</v>
+        <v>-0</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>-100</v>
+        <v>-0</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>-100</v>
+        <v>-0</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>-100</v>
+        <v>-0</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>-100</v>
+        <v>-0</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>-100</v>
+        <v>-0</v>
       </c>
       <c r="L8" s="18" t="n">
-        <v>-100</v>
+        <v>-0</v>
       </c>
       <c r="M8" s="18" t="n">
-        <v>-100</v>
+        <v>-0</v>
       </c>
       <c r="N8" s="18" t="n">
-        <v>-100</v>
+        <v>-0</v>
       </c>
       <c r="O8" s="18" t="n">
-        <v>-100</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9" ht="15.5" customHeight="1">
@@ -1174,40 +1174,40 @@
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>677.3399371011983</v>
+        <v>374.9373664305385</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>704.386516235232</v>
+        <v>29.34186820325215</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>3762.818838458421</v>
+        <v>2730.80708687385</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>1446.027177317412</v>
+        <v>72.57172735927247</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>1794.441322104577</v>
+        <v>94.90523102427369</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>2127.542214554026</v>
+        <v>117.1399892899926</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>2488.351305638484</v>
+        <v>140.1044840564599</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>2884.641382258654</v>
+        <v>172.8794351866234</v>
       </c>
       <c r="L12" s="18" t="n">
-        <v>3259.203386944134</v>
+        <v>201.1804155786651</v>
       </c>
       <c r="M12" s="18" t="n">
-        <v>3616.177098890353</v>
+        <v>228.9729111677146</v>
       </c>
       <c r="N12" s="18" t="n">
-        <v>3695.129413382933</v>
+        <v>256.14111570518</v>
       </c>
       <c r="O12" s="18" t="n">
-        <v>3901.392803533351</v>
+        <v>289.816593754941</v>
       </c>
     </row>
     <row r="13" ht="15.5" customHeight="1">
@@ -1230,37 +1230,37 @@
         <v>0</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>3.993058382144787</v>
+        <v>-92.17419472415052</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>434.1980222122561</v>
+        <v>9206.861676146365</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>-61.57064053846846</v>
+        <v>-97.34248062750011</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>24.09457790644869</v>
+        <v>30.77438622128603</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>18.56293033080498</v>
+        <v>23.42838010692161</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>16.95896272310113</v>
+        <v>19.60431694219828</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>15.92580901748866</v>
+        <v>23.39322067447582</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>12.98469913761693</v>
+        <v>16.37035681050836</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>10.95279028538691</v>
+        <v>13.81471228653575</v>
       </c>
       <c r="N13" s="18" t="n">
-        <v>2.183308846151566</v>
+        <v>11.8652483382917</v>
       </c>
       <c r="O13" s="18" t="n">
-        <v>5.582034269310787</v>
+        <v>13.14723641967799</v>
       </c>
     </row>
     <row r="14" ht="15.5" customHeight="1">
@@ -1280,40 +1280,40 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>93.07373974472546</v>
+        <v>0</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>53.64263312571409</v>
+        <v>0</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>289.4524093132733</v>
+        <v>0</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>112.3582897424864</v>
+        <v>0</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>140.838934746306</v>
+        <v>0</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>168.6694627090008</v>
+        <v>0</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>137.0260226690936</v>
+        <v>0</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>122.1176192066608</v>
+        <v>0</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>139.3679036915822</v>
+        <v>0</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>156.1945231394558</v>
+        <v>0</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>161.2169009902664</v>
+        <v>0</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>276.7269373438539</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="15.5" customHeight="1">
@@ -1439,40 +1439,40 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>51.07664525397499</v>
+        <v>0</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>1.467487999416797</v>
+        <v>0</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>208.7681302319329</v>
+        <v>0</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>3.809375718738334</v>
+        <v>0</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>5.085375550288797</v>
+        <v>0</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>6.387790181291267</v>
+        <v>0</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>5.300134466601298</v>
+        <v>0</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>5.199718992703466</v>
+        <v>0</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>6.286134665676212</v>
+        <v>0</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>7.374018022502872</v>
+        <v>0</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>8.458011088151519</v>
+        <v>0</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>15.95803494134613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" ht="15.5" customHeight="1">
@@ -1598,40 +1598,40 @@
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>-0.2771793200433282</v>
+        <v>-0</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>-0.5081548773492677</v>
+        <v>-0</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>-0.8693630952377401</v>
+        <v>-0</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>-1.230571313126219</v>
+        <v>-0</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>-1.591779531014687</v>
+        <v>-0</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>-1.952987748903165</v>
+        <v>-0</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>-1.591359897192886</v>
+        <v>-0</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>-1.319152239556599</v>
+        <v>-0</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>-1.342198574573817</v>
+        <v>-0</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>-1.365244909591037</v>
+        <v>-0</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>-1.388291244608255</v>
+        <v>-0</v>
       </c>
       <c r="O20" s="18" t="n">
-        <v>-2.27152197614928</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="21" ht="15.5" customHeight="1">
@@ -1810,40 +1810,40 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>1101.470622091352</v>
+        <v>373.7251388229811</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>1339.051863067119</v>
+        <v>25.94235447072258</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>4025.220573388032</v>
+        <v>2725.242159877597</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>1351.841670607261</v>
+        <v>64.86304123193298</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>1359.183066438736</v>
+        <v>85.07422335715859</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>1366.575637949261</v>
+        <v>105.2078832984997</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>1941.117346769409</v>
+        <v>125.1474622405089</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>2516.170442432754</v>
+        <v>153.9876542333309</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>2516.954183396834</v>
+        <v>178.3932230794047</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>2517.5046119522</v>
+        <v>202.329261237946</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>2517.70317012632</v>
+        <v>225.6795729192084</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>1666.841497073714</v>
+        <v>257.006646523701</v>
       </c>
     </row>
     <row r="25" ht="15.5" customHeight="1">
@@ -1866,34 +1866,34 @@
         <v>373.7251388229811</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>25.94235447072265</v>
+        <v>25.94235447072258</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>2725.242159877597</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>64.86304123193304</v>
+        <v>64.86304123193298</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>85.07422335715864</v>
+        <v>85.07422335715859</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>105.2078832984998</v>
+        <v>105.2078832984997</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>125.147462240509</v>
+        <v>125.1474622405089</v>
       </c>
       <c r="K25" s="18" t="n">
         <v>153.9876542333309</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>178.3932230794048</v>
+        <v>178.3932230794047</v>
       </c>
       <c r="M25" s="18" t="n">
         <v>202.329261237946</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>225.6795729192081</v>
+        <v>225.6795729192084</v>
       </c>
       <c r="O25" s="18" t="n">
         <v>257.006646523701</v>
@@ -1916,40 +1916,40 @@
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>151.3538245740183</v>
+        <v>0</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>101.9756428767661</v>
+        <v>0</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>309.6374933271707</v>
+        <v>0</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>105.0399470318646</v>
+        <v>0</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>106.6771550813035</v>
+        <v>0</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>108.3407779301944</v>
+        <v>0</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>106.8914943637942</v>
+        <v>0</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>106.5188712322601</v>
+        <v>0</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>107.62833324025</v>
+        <v>0</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>108.7392629320939</v>
+        <v>0</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>109.8463023327598</v>
+        <v>0</v>
       </c>
       <c r="O26" s="18" t="n">
-        <v>118.2295569174954</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" ht="15.5" customHeight="1">
@@ -1969,40 +1969,40 @@
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>51.35382457401831</v>
+        <v>0</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>1.97564287676607</v>
+        <v>0</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>209.6374933271707</v>
+        <v>0</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>5.039947031864559</v>
+        <v>0</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>6.677155081303489</v>
+        <v>0</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>8.34077793019444</v>
+        <v>0</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>6.891494363794186</v>
+        <v>0</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>6.518871232260066</v>
+        <v>0</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>7.628333240250034</v>
+        <v>0</v>
       </c>
       <c r="M27" s="18" t="n">
-        <v>8.73926293209391</v>
+        <v>0</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>9.846302332759763</v>
+        <v>0</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>18.22955691749541</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" ht="15.5" customHeight="1">
@@ -2075,40 +2075,40 @@
         </is>
       </c>
       <c r="D29" s="19" t="n">
-        <v>0.1665730169992766</v>
+        <v>-0</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>0.2588903446570329</v>
+        <v>-0</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>0.428078415642744</v>
+        <v>-0</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>0.5989754570424528</v>
+        <v>-0</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>0.7715987311835713</v>
+        <v>-0</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>0.9459656747604603</v>
+        <v>-0</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>0.8236382080659429</v>
+        <v>-0</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>0.7997594871856938</v>
+        <v>-0</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>0.9744108828434106</v>
+        <v>-0</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>1.150826434012825</v>
+        <v>-0</v>
       </c>
       <c r="N29" s="19" t="n">
-        <v>1.329023960446571</v>
+        <v>-0</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>2.327219192974291</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="30" ht="15.5" customHeight="1">
@@ -2128,40 +2128,40 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>1100.258394483796</v>
+        <v>372.512911215425</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>1335.65234933459</v>
+        <v>22.5428407381931</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>4019.655646391779</v>
+        <v>2719.677232881344</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>1344.132984479922</v>
+        <v>57.15435510459341</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>1349.352058771621</v>
+        <v>75.24321569004346</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>1354.643531957768</v>
+        <v>93.27577730700679</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>1926.160324953458</v>
+        <v>110.1904404245579</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>2497.278661479461</v>
+        <v>135.0958732800384</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>2494.166990897573</v>
+        <v>155.6060305801443</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>2490.860962022431</v>
+        <v>175.6856113081772</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>2487.241627340349</v>
+        <v>195.2180301332365</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>1634.031549842474</v>
+        <v>224.1966992924607</v>
       </c>
     </row>
     <row r="31" ht="15.5" customHeight="1">
@@ -2181,40 +2181,40 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>151.187251557019</v>
+        <v>0</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>101.716752532109</v>
+        <v>0</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>309.2094149115279</v>
+        <v>0</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>104.4409715748221</v>
+        <v>0</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>105.9055563501199</v>
+        <v>0</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>107.394812255434</v>
+        <v>0</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>106.0678561557283</v>
+        <v>0</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>105.7191117450744</v>
+        <v>0</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>106.6539223574066</v>
+        <v>0</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>107.5884364980811</v>
+        <v>0</v>
       </c>
       <c r="N31" s="19" t="n">
-        <v>108.5172783723132</v>
+        <v>0</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>115.9023377245211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" ht="15.5" customHeight="1">
@@ -2287,40 +2287,40 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>1100.258394483796</v>
+        <v>372.512911215425</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>1335.65234933459</v>
+        <v>22.5428407381931</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>4019.655646391779</v>
+        <v>2719.677232881344</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>1344.132984479922</v>
+        <v>57.15435510459341</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>1349.352058771621</v>
+        <v>75.24321569004346</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>1354.643531957768</v>
+        <v>93.27577730700679</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>1926.160324953458</v>
+        <v>110.1904404245579</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>2497.278661479461</v>
+        <v>135.0958732800384</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>2494.166990897573</v>
+        <v>155.6060305801443</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>2490.860962022431</v>
+        <v>175.6856113081772</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>2487.241627340349</v>
+        <v>195.2180301332365</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>1634.031549842474</v>
+        <v>224.1966992924607</v>
       </c>
     </row>
     <row r="34" ht="15.5" customHeight="1">
@@ -2343,25 +2343,25 @@
         <v>372.512911215425</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>22.54284073819326</v>
+        <v>22.5428407381931</v>
       </c>
       <c r="F34" s="19" t="n">
         <v>2719.677232881344</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>57.15435510459338</v>
+        <v>57.15435510459341</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>75.2432156900436</v>
+        <v>75.24321569004346</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>93.27577730700682</v>
+        <v>93.27577730700679</v>
       </c>
       <c r="J34" s="19" t="n">
         <v>110.1904404245579</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>135.0958732800386</v>
+        <v>135.0958732800384</v>
       </c>
       <c r="L34" s="19" t="n">
         <v>155.6060305801443</v>
@@ -2370,10 +2370,10 @@
         <v>175.6856113081772</v>
       </c>
       <c r="N34" s="19" t="n">
-        <v>195.2180301332364</v>
+        <v>195.2180301332365</v>
       </c>
       <c r="O34" s="19" t="n">
-        <v>224.1966992924606</v>
+        <v>224.1966992924607</v>
       </c>
     </row>
     <row r="35" ht="15.5" customHeight="1">
@@ -2449,7 +2449,7 @@
         <v>-104.303615140319</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>-6.311995406694114</v>
+        <v>-6.311995406694067</v>
       </c>
       <c r="F36" s="19" t="n">
         <v>-761.5096252067763</v>
@@ -2458,28 +2458,28 @@
         <v>-16.00321942928615</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>-21.06810039321221</v>
+        <v>-21.06810039321217</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>-26.11721764596191</v>
+        <v>-26.1172176459619</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>-30.85332331887621</v>
+        <v>-30.85332331887622</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>-37.82684451841082</v>
+        <v>-37.82684451841076</v>
       </c>
       <c r="L36" s="19" t="n">
         <v>-43.5696885624404</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>-49.1919711662896</v>
+        <v>-49.19197116628962</v>
       </c>
       <c r="N36" s="19" t="n">
-        <v>-54.6610484373062</v>
+        <v>-54.66104843730622</v>
       </c>
       <c r="O36" s="19" t="n">
-        <v>-62.77507580188897</v>
+        <v>-62.77507580188899</v>
       </c>
     </row>
     <row r="37" ht="15.5" customHeight="1">
@@ -2552,40 +2552,40 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>995.9547793434771</v>
+        <v>268.2092960751061</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>1329.340353927895</v>
+        <v>16.23084533149903</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>3258.146021185003</v>
+        <v>1958.167607674568</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>1328.129765050636</v>
+        <v>41.15113567530726</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>1328.283958378409</v>
+        <v>54.17511529683129</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>1328.526314311806</v>
+        <v>67.15855966104489</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>1895.307001634582</v>
+        <v>79.3371171056817</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>2459.451816961051</v>
+        <v>97.26902876162768</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>2450.597302335133</v>
+        <v>112.0363420177039</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>2441.668990856142</v>
+        <v>126.4936401418876</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>2432.580578903042</v>
+        <v>140.5569816959303</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>1571.256474040585</v>
+        <v>161.4216234905717</v>
       </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
@@ -2605,40 +2605,40 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>136.8548211210537</v>
+        <v>0</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>101.2360618231185</v>
+        <v>0</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>250.6307787363001</v>
+        <v>0</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>103.1974995338719</v>
+        <v>0</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>104.2520005720863</v>
+        <v>0</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>105.3242648239125</v>
+        <v>0</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>104.3688564321243</v>
+        <v>0</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>104.1177604564536</v>
+        <v>0</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>104.7908240973328</v>
+        <v>0</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>105.4636742786184</v>
+        <v>0</v>
       </c>
       <c r="N39" s="19" t="n">
-        <v>106.1324404280655</v>
+        <v>0</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>111.4496831616552</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" ht="15.5" customHeight="1">
@@ -2726,25 +2726,25 @@
         <v>316.3689062182364</v>
       </c>
       <c r="I41" s="18" t="n">
-        <v>336.7595029230595</v>
+        <v>377.9752415799667</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>667.9213200358874</v>
+        <v>427.6745349631409</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>707.3038573697547</v>
+        <v>786.7461088895443</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>744.3154730748016</v>
+        <v>820.8560689793743</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>778.9799721163694</v>
+        <v>852.6478332128239</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>811.3206621928357</v>
+        <v>882.1446792975107</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>760.5720528458729</v>
+        <v>860.7048705459894</v>
       </c>
     </row>
     <row r="42" ht="15.5" customHeight="1">
@@ -2779,25 +2779,25 @@
         <v>316.3689062182364</v>
       </c>
       <c r="I42" s="18" t="n">
-        <v>336.7595029230595</v>
+        <v>377.9752415799667</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>667.9213200358874</v>
+        <v>427.6745349631409</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>707.3038573697547</v>
+        <v>786.7461088895443</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>744.3154730748016</v>
+        <v>820.8560689793743</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>778.9799721163694</v>
+        <v>852.6478332128239</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>811.3206621928357</v>
+        <v>882.1446792975107</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>760.5720528458729</v>
+        <v>860.7048705459894</v>
       </c>
     </row>
     <row r="43" ht="15.5" customHeight="1">
@@ -2817,40 +2817,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>2328.70467549778</v>
+        <v>30.71713469777927</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>4598.107329912662</v>
+        <v>2300.119789112662</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>7117.955128691308</v>
+        <v>4819.967587891309</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>9197.281372068377</v>
+        <v>6899.293831268377</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>11483.33258888879</v>
+        <v>9185.34504808879</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>13780.46810173877</v>
+        <v>11484.98741025383</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>14964.06299109146</v>
+        <v>13767.25131730229</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>16461.55477941933</v>
+        <v>14940.13680426029</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>17938.918464852</v>
+        <v>16458.03297266198</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>19457.14319605379</v>
+        <v>17940.88581045407</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>21054.186959885</v>
+        <v>19459.06239975362</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>22595.45201337327</v>
+        <v>21056.76178785249</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -2870,40 +2870,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="18" t="n">
         <v>2297.9875408</v>
       </c>
-      <c r="E44" s="18" t="n">
+      <c r="F44" s="18" t="n">
         <v>4595.9750816</v>
       </c>
-      <c r="F44" s="18" t="n">
+      <c r="G44" s="18" t="n">
         <v>6893.962622399999</v>
       </c>
-      <c r="G44" s="18" t="n">
-        <v>9191.950163199999</v>
-      </c>
       <c r="H44" s="18" t="n">
+        <v>9178.352646169024</v>
+      </c>
+      <c r="I44" s="18" t="n">
         <v>11476.34018696902</v>
       </c>
-      <c r="I44" s="18" t="n">
-        <v>13771.82087845396</v>
-      </c>
       <c r="J44" s="18" t="n">
-        <v>14953.77689830456</v>
+        <v>13756.96522451539</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>16448.8982598933</v>
+        <v>14927.48028473426</v>
       </c>
       <c r="L44" s="18" t="n">
+        <v>16443.37051597052</v>
+      </c>
+      <c r="M44" s="18" t="n">
         <v>17924.25600816054</v>
       </c>
-      <c r="M44" s="18" t="n">
+      <c r="N44" s="18" t="n">
         <v>19440.51339376026</v>
       </c>
-      <c r="N44" s="18" t="n">
+      <c r="O44" s="18" t="n">
         <v>21035.63795389164</v>
-      </c>
-      <c r="O44" s="18" t="n">
-        <v>22574.32817941241</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -3029,40 +3029,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>2369.920414154687</v>
+        <v>71.93287335468639</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>4712.478569211108</v>
+        <v>2414.491028411108</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>7302.550905223829</v>
+        <v>5004.56336442383</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>9449.200032061584</v>
+        <v>7151.212491261584</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>11799.70149510703</v>
+        <v>9501.713954307026</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>14117.22760466183</v>
+        <v>11862.9626518338</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>15631.98431112734</v>
+        <v>14194.92585226543</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>17168.85863678908</v>
+        <v>15726.88291314983</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>18683.2339379268</v>
+        <v>17278.88904164136</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>20236.12316817016</v>
+        <v>18793.53364366689</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>21865.50762207784</v>
+        <v>20341.20707905113</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>23356.02406621914</v>
+        <v>21917.46665839848</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -3082,40 +3082,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>1486.963360120837</v>
+        <v>102.6500080524657</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>2816.058596588538</v>
+        <v>118.6357359237707</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>4629.982063290343</v>
+        <v>1360.326272383511</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>5546.960981280493</v>
+        <v>2303.43606959473</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>6875.244939658902</v>
+        <v>3657.589598401996</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>8201.528672401477</v>
+        <v>5009.484205869137</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>9263.440182715221</v>
+        <v>6362.930166056397</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>30080.61511292285</v>
+        <v>6888.171458147949</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>24325.16487886935</v>
+        <v>27173.90079794113</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>25785.87816752269</v>
+        <v>21442.30310109409</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>26828.80958303212</v>
+        <v>22921.13806258924</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>27031.54785191875</v>
+        <v>23934.75198131315</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -3135,40 +3135,40 @@
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" ht="15.5" customHeight="1">
@@ -3188,40 +3188,40 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>830.3954913208368</v>
+        <v>102.6500080524657</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>1329.095236467701</v>
+        <v>15.98572787130502</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>1813.923466701804</v>
+        <v>513.9450531913692</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>916.9789179901509</v>
+        <v>-369.9997113851774</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>1328.283958378409</v>
+        <v>54.17511529683129</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>1326.283732742575</v>
+        <v>64.91597809181376</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>1895.307001634582</v>
+        <v>79.3371171056817</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>2459.451816961051</v>
+        <v>97.26902876162768</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>2450.597302335133</v>
+        <v>112.0363420177039</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>2427.44240205642</v>
+        <v>112.2670513421661</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>2399.026711787913</v>
+        <v>107.0031145808009</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>1464.368714838152</v>
+        <v>54.53386428813877</v>
       </c>
     </row>
     <row r="51" ht="15.5" customHeight="1">
@@ -3244,37 +3244,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>830.3954913208368</v>
+        <v>102.6500080524657</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>2159.490727788538</v>
+        <v>846.3812191921418</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>3973.414194490342</v>
+        <v>2673.435780979908</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>4890.393112480493</v>
+        <v>3603.414483105165</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>6218.677070858902</v>
+        <v>4944.568227777324</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>6711.56531228064</v>
+        <v>6283.593048950715</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>26964.5954271618</v>
+        <v>6790.902429386321</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>21217.99970773422</v>
+        <v>27061.86445592343</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>22701.86789666627</v>
+        <v>21330.03604975193</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>23773.21500244421</v>
+        <v>22814.13494800844</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>24910.6112682806</v>
+        <v>23880.21811702501</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -3294,40 +3294,40 @@
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>913.6741887316289</v>
+        <v>-727.7454832683711</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>1241.984352135233</v>
+        <v>-399.4353198647671</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>1583.425610624798</v>
+        <v>-57.99406137520214</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>1937.86665324947</v>
+        <v>296.4469812494701</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>3032.922965436263</v>
+        <v>663.7578101678919</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>-14970.9516726181</v>
+        <v>1771.555210785502</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>-7994.525979185526</v>
+        <v>-16786.921557147</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>-7960.219328959723</v>
+        <v>-10356.70876738495</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>-7915.160637145667</v>
+        <v>-10298.78028927715</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>-7859.457424159256</v>
+        <v>-10230.33598785992</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>-7226.00032778756</v>
+        <v>-10151.48102136637</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>-11045.20901394877</v>
+        <v>-8635.835178337573</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -3347,40 +3347,40 @@
         </is>
       </c>
       <c r="D53" s="18" t="n">
-        <v>913.6741887316289</v>
+        <v>-727.7454832683711</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>1241.984352135233</v>
+        <v>-399.4353198647671</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>1583.425610624798</v>
+        <v>-57.99406137520214</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>1937.86665324947</v>
+        <v>296.4469812494701</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>3032.922965436263</v>
+        <v>663.7578101678919</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>-14970.9516726181</v>
+        <v>1771.555210785502</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>-7994.525979185526</v>
+        <v>-16786.921557147</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>-7960.219328959723</v>
+        <v>-10356.70876738495</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>-7915.160637145667</v>
+        <v>-10298.78028927715</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>-7859.457424159256</v>
+        <v>-10230.33598785992</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>-7226.00032778756</v>
+        <v>-10151.48102136637</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>-11045.20901394877</v>
+        <v>-8635.835178337573</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -3612,40 +3612,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>2369.920414154686</v>
+        <v>-655.8126099136847</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>4055.910700411109</v>
+        <v>-282.9318322536585</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>5989.415167623832</v>
+        <v>1078.339704716999</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>7479.496425661585</v>
+        <v>2594.551841975823</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>9901.175503175398</v>
+        <v>4314.355006650122</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>-6778.070223501432</v>
+        <v>6772.392193369831</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>1258.628110742804</v>
+        <v>-10434.27748387749</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>22107.7392644371</v>
+        <v>-3481.193828763027</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>16395.34178503223</v>
+        <v>16860.45805197252</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>17909.79094106991</v>
+        <v>11195.33731094064</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>19584.2602492512</v>
+        <v>12751.10803522951</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>15965.21500400913</v>
+        <v>15277.79296901473</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -3665,40 +3665,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>727.7454832683711</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>656.5678687999989</v>
+        <v>2697.422860664767</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>1313.135737599998</v>
+        <v>3926.22365970683</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>1969.703606399999</v>
+        <v>4556.660649285761</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>1898.525991931629</v>
+        <v>5187.358947656904</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>20895.29782816326</v>
+        <v>5090.570458463964</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>14373.35620038454</v>
+        <v>24629.20333614292</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>-4938.880627648017</v>
+        <v>19208.07674191286</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>2287.892152894576</v>
+        <v>418.4309896688319</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>2326.332227100254</v>
+        <v>7598.196332726257</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>2281.247372826634</v>
+        <v>7590.099043821618</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>7390.80906221001</v>
+        <v>6639.673689383757</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -3774,34 +3774,34 @@
         <v>373.7251388229811</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>25.94235447072265</v>
+        <v>25.94235447072258</v>
       </c>
       <c r="F61" s="18" t="n">
         <v>2725.242159877597</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>64.86304123193304</v>
+        <v>64.86304123193298</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>85.07422335715864</v>
+        <v>85.07422335715859</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>105.2078832984998</v>
+        <v>105.2078832984997</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>125.147462240509</v>
+        <v>125.1474622405089</v>
       </c>
       <c r="K61" s="18" t="n">
         <v>153.9876542333309</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>178.3932230794048</v>
+        <v>178.3932230794047</v>
       </c>
       <c r="M61" s="18" t="n">
         <v>202.329261237946</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>225.6795729192081</v>
+        <v>225.6795729192084</v>
       </c>
       <c r="O61" s="18" t="n">
         <v>257.006646523701</v>
@@ -3827,7 +3827,7 @@
         <v>-104.303615140319</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>-6.311995406694114</v>
+        <v>-6.311995406694067</v>
       </c>
       <c r="F62" s="18" t="n">
         <v>-761.5096252067763</v>
@@ -3836,28 +3836,28 @@
         <v>-16.00321942928615</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>-21.06810039321221</v>
+        <v>-21.06810039321217</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>-26.11721764596191</v>
+        <v>-26.1172176459619</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>-30.85332331887621</v>
+        <v>-30.85332331887622</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>-37.82684451841082</v>
+        <v>-37.82684451841076</v>
       </c>
       <c r="L62" s="18" t="n">
         <v>-43.5696885624404</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>-49.1919711662896</v>
+        <v>-49.19197116628962</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>-54.6610484373062</v>
+        <v>-54.66104843730622</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>-62.77507580188897</v>
+        <v>-62.77507580188899</v>
       </c>
     </row>
     <row r="63" ht="15.5" customHeight="1">
@@ -3933,34 +3933,34 @@
         <v>207.9872542871036</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>76.80013183426281</v>
+        <v>76.80013183426279</v>
       </c>
       <c r="F64" s="18" t="n">
         <v>1520.012018713527</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>486.1824166485095</v>
+        <v>486.1824166485094</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>60.68373686116963</v>
+        <v>60.68373686116961</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>75.78102292245445</v>
+        <v>75.78102292245435</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>91.01639991746686</v>
+        <v>91.01639991746681</v>
       </c>
       <c r="K64" s="18" t="n">
         <v>111.419956236648</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>130.811660186103</v>
+        <v>130.8116601861029</v>
       </c>
       <c r="M64" s="18" t="n">
         <v>149.2025988675126</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>167.1801170822424</v>
+        <v>167.1801170822426</v>
       </c>
       <c r="O64" s="18" t="n">
         <v>189.0819147868269</v>
@@ -4089,37 +4089,37 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>165.5592880226403</v>
+        <v>165.5592880226404</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>0.245117460194038</v>
+        <v>0.2451174601940096</v>
       </c>
       <c r="F67" s="18" t="n">
         <v>1444.222554483199</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>411.1508470604847</v>
+        <v>411.1508470604846</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>-13.59751703097509</v>
+        <v>-13.59751703097511</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>2.242581569231234</v>
+        <v>2.242581569231135</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-14.85565393856558</v>
+        <v>-14.85565393856562</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>-26.29661357030142</v>
+        <v>-26.29661357030139</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>-5.527743922776949</v>
+        <v>-5.527743922777063</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>14.2265887997215</v>
+        <v>14.22658879972147</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>33.55386711512915</v>
+        <v>33.55386711512938</v>
       </c>
       <c r="O67" s="18" t="n">
         <v>106.8877592024329</v>
@@ -4301,40 +4301,40 @@
         </is>
       </c>
       <c r="D71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="E71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="F71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="G71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="I71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="J71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="K71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="L71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="M71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="N71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="O71" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" ht="15.5" customHeight="1">
@@ -4354,22 +4354,22 @@
         </is>
       </c>
       <c r="D72" s="18" t="n">
-        <v>-165.5592880226403</v>
+        <v>-165.5592880226404</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>-0.245117460194038</v>
+        <v>-0.2451174601940096</v>
       </c>
       <c r="F72" s="18" t="n">
         <v>-1444.222554483199</v>
       </c>
       <c r="G72" s="18" t="n">
-        <v>-411.1508470604847</v>
+        <v>-411.1508470604846</v>
       </c>
       <c r="H72" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I72" s="18" t="n">
-        <v>-2.242581569231234</v>
+        <v>-2.242581569231135</v>
       </c>
       <c r="J72" s="18" t="n">
         <v>0</v>
@@ -4381,10 +4381,10 @@
         <v>0</v>
       </c>
       <c r="M72" s="18" t="n">
-        <v>-14.2265887997215</v>
+        <v>-14.22658879972147</v>
       </c>
       <c r="N72" s="18" t="n">
-        <v>-33.55386711512915</v>
+        <v>-33.55386711512938</v>
       </c>
       <c r="O72" s="18" t="n">
         <v>-106.8877592024329</v>
@@ -4407,40 +4407,40 @@
         </is>
       </c>
       <c r="D73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="E73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="F73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="G73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="I73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="J73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="K73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="N73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="O73" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" ht="15.5" customHeight="1">
@@ -4460,40 +4460,40 @@
         </is>
       </c>
       <c r="D74" s="18" t="n">
-        <v>2132.42825277736</v>
+        <v>-165.5592880226404</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>2297.742423339806</v>
+        <v>-0.2451174601940096</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>853.7649863168015</v>
+        <v>-1444.222554483199</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>1886.836693739515</v>
+        <v>-411.1508470604846</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>2295.744959230769</v>
+        <v>-2.242581569231135</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>2283.760952000278</v>
+        <v>-14.22658879972147</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>2264.433673684871</v>
+        <v>-33.55386711512938</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>2191.099781597567</v>
+        <v>-106.8877592024329</v>
       </c>
     </row>
     <row r="75" ht="15.5" customHeight="1">
@@ -4513,40 +4513,40 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>2284.390023769025</v>
+        <v>-13.59751703097511</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>2283.131886861434</v>
+        <v>-14.85565393856562</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>2271.690927229698</v>
+        <v>-26.29661357030139</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>2292.459796877223</v>
+        <v>-5.527743922777063</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" ht="15.5" customHeight="1">
@@ -4569,37 +4569,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="18" t="n">
         <v>2297.9875408</v>
       </c>
-      <c r="F76" s="18" t="n">
+      <c r="G76" s="18" t="n">
         <v>4595.9750816</v>
       </c>
-      <c r="G76" s="18" t="n">
+      <c r="H76" s="18" t="n">
         <v>6893.962622399999</v>
       </c>
-      <c r="H76" s="18" t="n">
-        <v>9191.950163199999</v>
-      </c>
       <c r="I76" s="18" t="n">
+        <v>9178.352646169024</v>
+      </c>
+      <c r="J76" s="18" t="n">
         <v>11476.34018696902</v>
       </c>
-      <c r="J76" s="18" t="n">
-        <v>13771.82087845396</v>
-      </c>
       <c r="K76" s="18" t="n">
-        <v>14953.77689830456</v>
+        <v>13756.96522451539</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>16448.8982598933</v>
+        <v>14927.48028473426</v>
       </c>
       <c r="M76" s="18" t="n">
+        <v>16443.37051597052</v>
+      </c>
+      <c r="N76" s="18" t="n">
         <v>17924.25600816054</v>
       </c>
-      <c r="N76" s="18" t="n">
+      <c r="O76" s="18" t="n">
         <v>19440.51339376026</v>
-      </c>
-      <c r="O76" s="18" t="n">
-        <v>21035.63795389164</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -4619,40 +4619,40 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>2284.390023769025</v>
+        <v>-13.59751703097511</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>2283.131886861434</v>
+        <v>-14.85565393856562</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>2271.690927229698</v>
+        <v>-26.29661357030139</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>2292.459796877223</v>
+        <v>-5.527743922777063</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" ht="15.5" customHeight="1">
@@ -4672,40 +4672,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="18" t="n">
         <v>2297.9875408</v>
       </c>
-      <c r="E78" s="18" t="n">
+      <c r="F78" s="18" t="n">
         <v>4595.9750816</v>
       </c>
-      <c r="F78" s="18" t="n">
+      <c r="G78" s="18" t="n">
         <v>6893.962622399999</v>
       </c>
-      <c r="G78" s="18" t="n">
-        <v>9191.950163199999</v>
-      </c>
       <c r="H78" s="18" t="n">
+        <v>9178.352646169024</v>
+      </c>
+      <c r="I78" s="18" t="n">
         <v>11476.34018696902</v>
       </c>
-      <c r="I78" s="18" t="n">
-        <v>13771.82087845396</v>
-      </c>
       <c r="J78" s="18" t="n">
-        <v>14953.77689830456</v>
+        <v>13756.96522451539</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>16448.8982598933</v>
+        <v>14927.48028473426</v>
       </c>
       <c r="L78" s="18" t="n">
+        <v>16443.37051597052</v>
+      </c>
+      <c r="M78" s="18" t="n">
         <v>17924.25600816054</v>
       </c>
-      <c r="M78" s="18" t="n">
+      <c r="N78" s="18" t="n">
         <v>19440.51339376026</v>
       </c>
-      <c r="N78" s="18" t="n">
+      <c r="O78" s="18" t="n">
         <v>21035.63795389164</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>22574.32817941241</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -4831,40 +4831,40 @@
         </is>
       </c>
       <c r="D81" s="18" t="n">
-        <v>5.830055594974682</v>
+        <v>0</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>5.830055594974684</v>
+        <v>0</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>5.830055594974683</v>
+        <v>0</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>5.830055594974682</v>
+        <v>0</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>5.830055594974684</v>
+        <v>0</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>5.830055594974683</v>
+        <v>0</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>5.830055594974683</v>
+        <v>0</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>5.830055594974683</v>
+        <v>0</v>
       </c>
       <c r="L81" s="18" t="n">
-        <v>5.830055594974683</v>
+        <v>0</v>
       </c>
       <c r="M81" s="18" t="n">
-        <v>5.830055594974683</v>
+        <v>0</v>
       </c>
       <c r="N81" s="18" t="n">
-        <v>5.830055594974681</v>
+        <v>0</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>5.830055594974684</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" ht="15.5" customHeight="1">
@@ -4902,22 +4902,22 @@
         <v>316.3689062182364</v>
       </c>
       <c r="J82" s="18" t="n">
-        <v>336.7595029230595</v>
+        <v>377.9752415799667</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>667.9213200358874</v>
+        <v>427.6745349631409</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>707.3038573697547</v>
+        <v>786.7461088895443</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>744.3154730748016</v>
+        <v>820.8560689793743</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>778.9799721163694</v>
+        <v>852.6478332128239</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>811.3206621928357</v>
+        <v>882.1446792975107</v>
       </c>
     </row>
     <row r="83" ht="15.5" customHeight="1">
@@ -5058,25 +5058,25 @@
         <v>316.3689062182364</v>
       </c>
       <c r="I85" s="18" t="n">
-        <v>336.7595029230595</v>
+        <v>377.9752415799667</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>667.9213200358874</v>
+        <v>427.6745349631409</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>707.3038573697547</v>
+        <v>786.7461088895443</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>744.3154730748016</v>
+        <v>820.8560689793743</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>778.9799721163694</v>
+        <v>852.6478332128239</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>811.3206621928357</v>
+        <v>882.1446792975107</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>760.5720528458729</v>
+        <v>860.7048705459894</v>
       </c>
     </row>
     <row r="86" ht="15.5" customHeight="1">
@@ -5653,37 +5653,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>1818.081936166117</v>
+        <v>433.7685840977465</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>3804.235276354206</v>
+        <v>1834.55789895781</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>9163.171720822407</v>
+        <v>7206.625438511972</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>11559.02020173353</v>
+        <v>9615.473703558198</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>13543.87202891194</v>
+        <v>11613.19531703036</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>14368.37472622686</v>
+        <v>13613.27317014221</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>35038.37930873512</v>
+        <v>14447.71184333254</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>26820.24318288862</v>
+        <v>35135.64833749675</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>27901.83214515384</v>
+        <v>26932.27952490632</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>29444.76612146401</v>
+        <v>28042.55237409545</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>31004.29330564774</v>
+        <v>29618.87697027507</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -5703,40 +5703,40 @@
         </is>
       </c>
       <c r="D97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="E97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="F97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="G97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="H97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="I97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="J97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="K97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="N97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
       <c r="O97" s="19" t="n">
-        <v>656.5678688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" ht="15.5" customHeight="1">
@@ -5756,40 +5756,40 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>995.9547793434771</v>
+        <v>268.2092960751061</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>1329.340353927895</v>
+        <v>16.23084533149903</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>3258.146021185003</v>
+        <v>1958.167607674568</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>1328.129765050636</v>
+        <v>41.15113567530726</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>1328.283958378409</v>
+        <v>54.17511529683129</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>1328.526314311806</v>
+        <v>67.15855966104489</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>1895.307001634582</v>
+        <v>79.3371171056817</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>2459.451816961051</v>
+        <v>97.26902876162768</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>2450.597302335133</v>
+        <v>112.0363420177039</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>2441.668990856142</v>
+        <v>126.4936401418876</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>2432.580578903042</v>
+        <v>140.5569816959303</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>1571.256474040585</v>
+        <v>161.4216234905717</v>
       </c>
     </row>
     <row r="99" ht="15.5" customHeight="1">
@@ -5809,22 +5809,22 @@
         </is>
       </c>
       <c r="D99" s="20" t="n">
-        <v>165.5592880226403</v>
+        <v>165.5592880226404</v>
       </c>
       <c r="E99" s="20" t="n">
-        <v>0.245117460194038</v>
+        <v>0.2451174601940096</v>
       </c>
       <c r="F99" s="20" t="n">
         <v>1444.222554483199</v>
       </c>
       <c r="G99" s="20" t="n">
-        <v>411.1508470604847</v>
+        <v>411.1508470604846</v>
       </c>
       <c r="H99" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>2.242581569231234</v>
+        <v>2.242581569231135</v>
       </c>
       <c r="J99" s="20" t="n">
         <v>0</v>
@@ -5836,10 +5836,10 @@
         <v>0</v>
       </c>
       <c r="M99" s="20" t="n">
-        <v>14.2265887997215</v>
+        <v>14.22658879972147</v>
       </c>
       <c r="N99" s="20" t="n">
-        <v>33.55386711512915</v>
+        <v>33.55386711512938</v>
       </c>
       <c r="O99" s="20" t="n">
         <v>106.8877592024329</v>
@@ -5862,40 +5862,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>1818.081936166117</v>
+        <v>433.7685840977465</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>3804.235276354206</v>
+        <v>1834.55789895781</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>9163.171720822407</v>
+        <v>7206.625438511972</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>11559.02020173353</v>
+        <v>9615.473703558198</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>13543.87202891194</v>
+        <v>11613.19531703036</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>14368.37472622686</v>
+        <v>13613.27317014221</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>35038.37930873512</v>
+        <v>14447.71184333254</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>26820.24318288862</v>
+        <v>35135.64833749675</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>27901.83214515384</v>
+        <v>26932.27952490632</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>29444.76612146401</v>
+        <v>28042.55237409545</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>31004.29330564774</v>
+        <v>29618.87697027507</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>31192.23651412843</v>
+        <v>31272.60268834075</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -5968,40 +5968,40 @@
         </is>
       </c>
       <c r="D102" s="18" t="n">
-        <v>-1715.249509562083</v>
+        <v>-0</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>-1715.249509562082</v>
+        <v>-0</v>
       </c>
       <c r="F102" s="18" t="n">
-        <v>-1715.249509562082</v>
+        <v>-0</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>-1715.249509562083</v>
+        <v>-0</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>-1715.249509562082</v>
+        <v>-0</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>-1715.249509562082</v>
+        <v>-0</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>-1715.249509562082</v>
+        <v>-0</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>-1715.249509562082</v>
+        <v>-0</v>
       </c>
       <c r="L102" s="18" t="n">
-        <v>-1715.249509562082</v>
+        <v>-0</v>
       </c>
       <c r="M102" s="18" t="n">
-        <v>-1715.249509562082</v>
+        <v>-0</v>
       </c>
       <c r="N102" s="18" t="n">
-        <v>-1715.249509562083</v>
+        <v>-0</v>
       </c>
       <c r="O102" s="18" t="n">
-        <v>-1715.249509562082</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="103" ht="15.5" customHeight="1">
@@ -6024,37 +6024,37 @@
         <v>0</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>913.6741887316289</v>
+        <v>-727.7454832683711</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>1241.984352135233</v>
+        <v>-399.4353198647671</v>
       </c>
       <c r="G103" s="18" t="n">
-        <v>1583.425610624798</v>
+        <v>-57.99406137520214</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>1937.86665324947</v>
+        <v>296.4469812494701</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>3032.922965436263</v>
+        <v>663.7578101678919</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>-14970.9516726181</v>
+        <v>1771.555210785502</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>-7994.525979185526</v>
+        <v>-16786.921557147</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>-7960.219328959723</v>
+        <v>-10356.70876738495</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>-7915.160637145667</v>
+        <v>-10298.78028927715</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>-7859.457424159256</v>
+        <v>-10230.33598785992</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>-7226.00032778756</v>
+        <v>-10151.48102136637</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -6074,40 +6074,40 @@
         </is>
       </c>
       <c r="D104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="E104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="F104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="G104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="H104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="I104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="J104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="K104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="L104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="M104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="N104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
       <c r="O104" s="19" t="n">
-        <v>1641.419672</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" ht="15.5" customHeight="1">
@@ -6127,40 +6127,40 @@
         </is>
       </c>
       <c r="D105" s="18" t="n">
-        <v>-727.7454832683711</v>
+        <v>-0</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>-1313.109508596396</v>
+        <v>-0</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>-1299.978413510435</v>
+        <v>-0</v>
       </c>
       <c r="G105" s="18" t="n">
-        <v>-1286.978629375328</v>
+        <v>-0</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>-1274.108843081578</v>
+        <v>-0</v>
       </c>
       <c r="I105" s="18" t="n">
-        <v>-1261.367754650761</v>
+        <v>-0</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>-1815.9698845289</v>
+        <v>-0</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>-2362.182788199423</v>
+        <v>-0</v>
       </c>
       <c r="L105" s="18" t="n">
-        <v>-2338.560960317429</v>
+        <v>-0</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>-2315.175350714254</v>
+        <v>-0</v>
       </c>
       <c r="N105" s="18" t="n">
-        <v>-2292.023597207112</v>
+        <v>-0</v>
       </c>
       <c r="O105" s="18" t="n">
-        <v>-1409.834850550013</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="106" ht="15.5" customHeight="1">
@@ -6233,40 +6233,40 @@
         </is>
       </c>
       <c r="D107" s="18" t="n">
-        <v>913.6741887316289</v>
+        <v>-727.7454832683711</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>1241.984352135233</v>
+        <v>-399.4353198647671</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>1583.425610624798</v>
+        <v>-57.99406137520214</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>1937.86665324947</v>
+        <v>296.4469812494701</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>3032.922965436263</v>
+        <v>663.7578101678919</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>-14970.9516726181</v>
+        <v>1771.555210785502</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>-7994.525979185526</v>
+        <v>-16786.921557147</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>-7960.219328959723</v>
+        <v>-10356.70876738495</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>-7915.160637145667</v>
+        <v>-10298.78028927715</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>-7859.457424159256</v>
+        <v>-10230.33598785992</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>-7226.00032778756</v>
+        <v>-10151.48102136637</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>-11045.20901394877</v>
+        <v>-8635.835178337573</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -6993,40 +6993,40 @@
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="15.5" customHeight="1">
@@ -8760,22 +8760,22 @@
         <v>1913.74182395875</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>1987.381049531387</v>
+        <v>2235.34280800426</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>2340.716122696916</v>
+        <v>2333.418320356867</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>2677.622793125464</v>
+        <v>2670.328871762653</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>2998.274407130115</v>
+        <v>2990.976933649055</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>3302.819618872868</v>
+        <v>3295.530488794742</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>3467.100657981287</v>
+        <v>3459.811679300637</v>
       </c>
     </row>
     <row r="42" ht="15.5" customHeight="1">
@@ -8813,22 +8813,22 @@
         <v>1913.74182395875</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>1987.381049531387</v>
+        <v>2235.34280800426</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>2340.716122696916</v>
+        <v>2333.418320356867</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>2677.622793125464</v>
+        <v>2670.328871762653</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>2998.274407130115</v>
+        <v>2990.976933649055</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>3302.819618872868</v>
+        <v>3295.530488794742</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>3467.100657981287</v>
+        <v>3459.811679300637</v>
       </c>
     </row>
     <row r="43" ht="15.5" customHeight="1">
@@ -8851,37 +8851,37 @@
         <v>1830.861282523789</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>2340.680942601061</v>
+        <v>42.6934018010603</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>6951.866813106852</v>
+        <v>4653.879272306851</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>6947.074030619181</v>
+        <v>4649.08648981918</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>9251.884672789045</v>
+        <v>6953.897131989042</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>11556.60349030137</v>
+        <v>9258.615949501373</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>13861.18491603288</v>
+        <v>11563.19737523288</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>16058.56953831175</v>
+        <v>13870.29089411507</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>18200.16760464542</v>
+        <v>16067.59496844874</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>20355.52631700648</v>
+        <v>18208.9151608098</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>22538.19624469073</v>
+        <v>20363.96004849405</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>24708.85158172861</v>
+        <v>22551.71082553193</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -8904,37 +8904,37 @@
         <v>0</v>
       </c>
       <c r="E44" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="18" t="n">
         <v>2297.987540800001</v>
       </c>
-      <c r="F44" s="18" t="n">
+      <c r="G44" s="18" t="n">
         <v>4595.975081600001</v>
       </c>
-      <c r="G44" s="18" t="n">
+      <c r="H44" s="18" t="n">
         <v>6893.962622400002</v>
       </c>
-      <c r="H44" s="18" t="n">
+      <c r="I44" s="18" t="n">
         <v>9191.950163200003</v>
       </c>
-      <c r="I44" s="18" t="n">
+      <c r="J44" s="18" t="n">
         <v>11489.937704</v>
       </c>
-      <c r="J44" s="18" t="n">
+      <c r="K44" s="18" t="n">
         <v>13787.9252448</v>
       </c>
-      <c r="K44" s="18" t="n">
+      <c r="L44" s="18" t="n">
         <v>15976.20388899668</v>
       </c>
-      <c r="L44" s="18" t="n">
+      <c r="M44" s="18" t="n">
         <v>18108.77652519336</v>
       </c>
-      <c r="M44" s="18" t="n">
+      <c r="N44" s="18" t="n">
         <v>20255.38768139004</v>
       </c>
-      <c r="N44" s="18" t="n">
+      <c r="O44" s="18" t="n">
         <v>22429.62387758672</v>
-      </c>
-      <c r="O44" s="18" t="n">
-        <v>24586.7646337834</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -9063,37 +9063,37 @@
         <v>2118.72429813952</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>2983.269355876742</v>
+        <v>685.2818150767414</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>7934.259305019721</v>
+        <v>5636.27176421972</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>8254.493563336706</v>
+        <v>5956.506022536704</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>10869.70684685701</v>
+        <v>8571.719306057012</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>13470.34531426012</v>
+        <v>11172.35777346012</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>15848.56596556426</v>
+        <v>13798.54018323714</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>18399.28566100866</v>
+        <v>16203.70921447194</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>20877.79039777088</v>
+        <v>18737.92384021139</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>23353.80072413659</v>
+        <v>21199.89209445885</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>25841.0158635636</v>
+        <v>23659.4905372888</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>28175.95223970989</v>
+        <v>26011.52250483256</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -9119,34 +9119,34 @@
         <v>675.4747894805382</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>6923.241786278937</v>
+        <v>5633.064820679988</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>4267.912376738697</v>
+        <v>2638.013385987701</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>6197.353561406114</v>
+        <v>4583.739215349417</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>8096.105163660727</v>
+        <v>6498.634351022921</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>10004.46993441717</v>
+        <v>8422.959484692539</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>6961.451003174207</v>
+        <v>10358.85044359882</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>12533.79900327339</v>
+        <v>7299.752196075559</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>10043.29170735558</v>
+        <v>12855.5735766737</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>16758.05798882429</v>
+        <v>10348.662435557</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>18729.33809527479</v>
+        <v>16928.25412600293</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -9278,34 +9278,34 @@
         <v>3904.167388882484</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>1965.651755079487</v>
+        <v>675.4747894805378</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>8553.140777029934</v>
+        <v>6923.241786278937</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>5881.526722795394</v>
+        <v>4267.912376738697</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>7794.82437404392</v>
+        <v>6197.353561406114</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>9677.61561338536</v>
+        <v>8096.105163660727</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>6607.070493992563</v>
+        <v>10004.46993441717</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>12195.49781037204</v>
+        <v>6961.451003174207</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>9721.517133955274</v>
+        <v>12533.79900327339</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>16452.68726062286</v>
+        <v>10043.29170735558</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>18559.14195809614</v>
+        <v>16758.05798882428</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -9325,40 +9325,40 @@
         </is>
       </c>
       <c r="D52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="18" t="n">
         <v>-1290.176965598953</v>
       </c>
-      <c r="E52" s="18" t="n">
+      <c r="F52" s="18" t="n">
         <v>-1278.65628434995</v>
       </c>
-      <c r="F52" s="18" t="n">
+      <c r="G52" s="18" t="n">
         <v>-1250.850958406641</v>
       </c>
-      <c r="G52" s="18" t="n">
+      <c r="H52" s="18" t="n">
         <v>-1206.902099044447</v>
       </c>
-      <c r="H52" s="18" t="n">
+      <c r="I52" s="18" t="n">
         <v>-1146.99287676908</v>
       </c>
-      <c r="I52" s="18" t="n">
+      <c r="J52" s="18" t="n">
         <v>27.56010391590189</v>
       </c>
-      <c r="J52" s="18" t="n">
+      <c r="K52" s="18" t="n">
         <v>-162.300607879974</v>
       </c>
-      <c r="K52" s="18" t="n">
+      <c r="L52" s="18" t="n">
         <v>-506.8604250494029</v>
       </c>
-      <c r="L52" s="18" t="n">
+      <c r="M52" s="18" t="n">
         <v>-831.0141990278089</v>
       </c>
-      <c r="M52" s="18" t="n">
+      <c r="N52" s="18" t="n">
         <v>-1134.919330769903</v>
       </c>
-      <c r="N52" s="18" t="n">
+      <c r="O52" s="18" t="n">
         <v>-1418.804158241069</v>
-      </c>
-      <c r="O52" s="18" t="n">
-        <v>-1137.862205964062</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -9378,40 +9378,40 @@
         </is>
       </c>
       <c r="D53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="18" t="n">
         <v>-1290.176965598953</v>
       </c>
-      <c r="E53" s="18" t="n">
+      <c r="F53" s="18" t="n">
         <v>-1278.65628434995</v>
       </c>
-      <c r="F53" s="18" t="n">
+      <c r="G53" s="18" t="n">
         <v>-1250.850958406641</v>
       </c>
-      <c r="G53" s="18" t="n">
+      <c r="H53" s="18" t="n">
         <v>-1206.902099044447</v>
       </c>
-      <c r="H53" s="18" t="n">
+      <c r="I53" s="18" t="n">
         <v>-1146.99287676908</v>
       </c>
-      <c r="I53" s="18" t="n">
+      <c r="J53" s="18" t="n">
         <v>27.56010391590189</v>
       </c>
-      <c r="J53" s="18" t="n">
+      <c r="K53" s="18" t="n">
         <v>-162.300607879974</v>
       </c>
-      <c r="K53" s="18" t="n">
+      <c r="L53" s="18" t="n">
         <v>-506.8604250494029</v>
       </c>
-      <c r="L53" s="18" t="n">
+      <c r="M53" s="18" t="n">
         <v>-831.0141990278089</v>
       </c>
-      <c r="M53" s="18" t="n">
+      <c r="N53" s="18" t="n">
         <v>-1134.919330769903</v>
       </c>
-      <c r="N53" s="18" t="n">
+      <c r="O53" s="18" t="n">
         <v>-1418.804158241069</v>
-      </c>
-      <c r="O53" s="18" t="n">
-        <v>-1137.862205964062</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -9643,40 +9643,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>805.8382366501532</v>
+        <v>2096.015202249106</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>-619.6246829718418</v>
+        <v>-631.1453642208451</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>3347.054663488735</v>
+        <v>2029.072371946476</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>3040.801833858633</v>
+        <v>1366.953983745443</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>5027.440142171281</v>
+        <v>3353.916573839217</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>8098.064155247862</v>
+        <v>5326.040361925074</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>9813.941545715279</v>
+        <v>8422.291807786522</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>6422.191178124804</v>
+        <v>10164.15043571884</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>11666.04118232777</v>
+        <v>6756.148149108349</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>8867.418538229509</v>
+        <v>11983.60553928972</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>15294.24266895866</v>
+        <v>9168.731943162536</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>17539.86268931072</v>
+        <v>15457.83676776186</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -9696,40 +9696,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>1312.886061489367</v>
+        <v>22.70909589041412</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>3602.894038848584</v>
+        <v>1316.427179297586</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>4587.204641530987</v>
+        <v>3607.199392273244</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>5213.691729478072</v>
+        <v>4589.552038791261</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>5842.266704685733</v>
+        <v>5217.802732217795</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>5372.281159012257</v>
+        <v>5846.317411535048</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>6034.624419848986</v>
+        <v>5376.248375450617</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>11977.09448288386</v>
+        <v>6039.558778753093</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>9211.749215443109</v>
+        <v>11981.77569110304</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>14486.38218590708</v>
+        <v>9216.286555169127</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>10546.77319460495</v>
+        <v>14490.75859412626</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>10636.08955039917</v>
+        <v>10553.6857370707</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -10603,34 +10603,34 @@
         <v>0</v>
       </c>
       <c r="F76" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="18" t="n">
         <v>2297.987540800001</v>
       </c>
-      <c r="G76" s="18" t="n">
+      <c r="H76" s="18" t="n">
         <v>4595.975081600001</v>
       </c>
-      <c r="H76" s="18" t="n">
+      <c r="I76" s="18" t="n">
         <v>6893.962622400002</v>
       </c>
-      <c r="I76" s="18" t="n">
+      <c r="J76" s="18" t="n">
         <v>9191.950163200003</v>
       </c>
-      <c r="J76" s="18" t="n">
+      <c r="K76" s="18" t="n">
         <v>11489.937704</v>
       </c>
-      <c r="K76" s="18" t="n">
+      <c r="L76" s="18" t="n">
         <v>13787.9252448</v>
       </c>
-      <c r="L76" s="18" t="n">
+      <c r="M76" s="18" t="n">
         <v>15976.20388899668</v>
       </c>
-      <c r="M76" s="18" t="n">
+      <c r="N76" s="18" t="n">
         <v>18108.77652519336</v>
       </c>
-      <c r="N76" s="18" t="n">
+      <c r="O76" s="18" t="n">
         <v>20255.38768139004</v>
-      </c>
-      <c r="O76" s="18" t="n">
-        <v>22429.62387758672</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -10706,37 +10706,37 @@
         <v>0</v>
       </c>
       <c r="E78" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="18" t="n">
         <v>2297.987540800001</v>
       </c>
-      <c r="F78" s="18" t="n">
+      <c r="G78" s="18" t="n">
         <v>4595.975081600001</v>
       </c>
-      <c r="G78" s="18" t="n">
+      <c r="H78" s="18" t="n">
         <v>6893.962622400002</v>
       </c>
-      <c r="H78" s="18" t="n">
+      <c r="I78" s="18" t="n">
         <v>9191.950163200003</v>
       </c>
-      <c r="I78" s="18" t="n">
+      <c r="J78" s="18" t="n">
         <v>11489.937704</v>
       </c>
-      <c r="J78" s="18" t="n">
+      <c r="K78" s="18" t="n">
         <v>13787.9252448</v>
       </c>
-      <c r="K78" s="18" t="n">
+      <c r="L78" s="18" t="n">
         <v>15976.20388899668</v>
       </c>
-      <c r="L78" s="18" t="n">
+      <c r="M78" s="18" t="n">
         <v>18108.77652519336</v>
       </c>
-      <c r="M78" s="18" t="n">
+      <c r="N78" s="18" t="n">
         <v>20255.38768139004</v>
       </c>
-      <c r="N78" s="18" t="n">
+      <c r="O78" s="18" t="n">
         <v>22429.62387758672</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>24586.7646337834</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -10936,19 +10936,19 @@
         <v>1913.74182395875</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>1987.381049531387</v>
+        <v>2235.34280800426</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>2340.716122696916</v>
+        <v>2333.418320356867</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>2677.622793125464</v>
+        <v>2670.328871762653</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>2998.274407130115</v>
+        <v>2990.976933649055</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>3302.819618872868</v>
+        <v>3295.530488794742</v>
       </c>
     </row>
     <row r="83" ht="15.5" customHeight="1">
@@ -11092,22 +11092,22 @@
         <v>1913.74182395875</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>1987.381049531387</v>
+        <v>2235.34280800426</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>2340.716122696916</v>
+        <v>2333.418320356867</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>2677.622793125464</v>
+        <v>2670.328871762653</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>2998.274407130115</v>
+        <v>2990.976933649055</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>3302.819618872868</v>
+        <v>3295.530488794742</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>3467.100657981287</v>
+        <v>3459.811679300637</v>
       </c>
     </row>
     <row r="86" ht="15.5" customHeight="1">
@@ -11687,34 +11687,34 @@
         <v>28139.7674134494</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>34011.08176152834</v>
+        <v>32064.3369271294</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>72543.20650831767</v>
+        <v>70256.73964876666</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>79939.16623556451</v>
+        <v>77668.98402070782</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>82818.09458789506</v>
+        <v>80564.05590645724</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>85794.37788807284</v>
+        <v>83556.29956954819</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>59859.27348030308</v>
+        <v>86602.45626049463</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>59537.17104540699</v>
+        <v>60777.46405980636</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>27186.63827281338</v>
+        <v>60608.06570668557</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>26083.42788219973</v>
+        <v>28406.11595012907</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>29537.73713235005</v>
+        <v>27446.18090387545</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -11896,37 +11896,37 @@
         <v>28139.7674134494</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>34011.08176152834</v>
+        <v>32064.3369271294</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>72543.20650831767</v>
+        <v>70256.73964876666</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>79939.16623556451</v>
+        <v>77668.98402070782</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>82818.09458789506</v>
+        <v>80564.05590645724</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>85794.37788807284</v>
+        <v>83556.29956954819</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>59859.27348030308</v>
+        <v>86602.45626049463</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>59537.17104540699</v>
+        <v>60777.46405980636</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>27186.63827281338</v>
+        <v>60608.06570668557</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>26083.42788219973</v>
+        <v>28406.11595012907</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>29537.73713235005</v>
+        <v>27446.18090387545</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>33260.54665792526</v>
+        <v>31254.51742733913</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -11999,40 +11999,40 @@
         </is>
       </c>
       <c r="D102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" ht="15.5" customHeight="1">
@@ -12055,37 +12055,37 @@
         <v>0</v>
       </c>
       <c r="E103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="18" t="n">
         <v>-1290.176965598953</v>
       </c>
-      <c r="F103" s="18" t="n">
+      <c r="G103" s="18" t="n">
         <v>-1278.65628434995</v>
       </c>
-      <c r="G103" s="18" t="n">
+      <c r="H103" s="18" t="n">
         <v>-1250.850958406641</v>
       </c>
-      <c r="H103" s="18" t="n">
+      <c r="I103" s="18" t="n">
         <v>-1206.902099044447</v>
       </c>
-      <c r="I103" s="18" t="n">
+      <c r="J103" s="18" t="n">
         <v>-1146.99287676908</v>
       </c>
-      <c r="J103" s="18" t="n">
+      <c r="K103" s="18" t="n">
         <v>27.56010391590189</v>
       </c>
-      <c r="K103" s="18" t="n">
+      <c r="L103" s="18" t="n">
         <v>-162.300607879974</v>
       </c>
-      <c r="L103" s="18" t="n">
+      <c r="M103" s="18" t="n">
         <v>-506.8604250494029</v>
       </c>
-      <c r="M103" s="18" t="n">
+      <c r="N103" s="18" t="n">
         <v>-831.0141990278089</v>
       </c>
-      <c r="N103" s="18" t="n">
+      <c r="O103" s="18" t="n">
         <v>-1134.919330769903</v>
-      </c>
-      <c r="O103" s="18" t="n">
-        <v>-1418.804158241069</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -12158,40 +12158,40 @@
         </is>
       </c>
       <c r="D105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" ht="15.5" customHeight="1">
@@ -12264,40 +12264,40 @@
         </is>
       </c>
       <c r="D107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="18" t="n">
         <v>-1290.176965598953</v>
       </c>
-      <c r="E107" s="18" t="n">
+      <c r="F107" s="18" t="n">
         <v>-1278.65628434995</v>
       </c>
-      <c r="F107" s="18" t="n">
+      <c r="G107" s="18" t="n">
         <v>-1250.850958406641</v>
       </c>
-      <c r="G107" s="18" t="n">
+      <c r="H107" s="18" t="n">
         <v>-1206.902099044447</v>
       </c>
-      <c r="H107" s="18" t="n">
+      <c r="I107" s="18" t="n">
         <v>-1146.99287676908</v>
       </c>
-      <c r="I107" s="18" t="n">
+      <c r="J107" s="18" t="n">
         <v>27.56010391590189</v>
       </c>
-      <c r="J107" s="18" t="n">
+      <c r="K107" s="18" t="n">
         <v>-162.300607879974</v>
       </c>
-      <c r="K107" s="18" t="n">
+      <c r="L107" s="18" t="n">
         <v>-506.8604250494029</v>
       </c>
-      <c r="L107" s="18" t="n">
+      <c r="M107" s="18" t="n">
         <v>-831.0141990278089</v>
       </c>
-      <c r="M107" s="18" t="n">
+      <c r="N107" s="18" t="n">
         <v>-1134.919330769903</v>
       </c>
-      <c r="N107" s="18" t="n">
+      <c r="O107" s="18" t="n">
         <v>-1418.804158241069</v>
-      </c>
-      <c r="O107" s="18" t="n">
-        <v>-1137.862205964062</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -12706,40 +12706,40 @@
         </is>
       </c>
       <c r="D2" s="18" t="n">
-        <v>63.40677504</v>
+        <v>24.15496192</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>6858.829320000001</v>
+        <v>26.1288736</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>100.88896203</v>
+        <v>35.09181288000001</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>129.42566928</v>
+        <v>48.53462598</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>163.62358818</v>
+        <v>56.63893437</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>191.58404391</v>
+        <v>70.9570533</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>218.60993672</v>
+        <v>78.07497740000001</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>291.1399782</v>
+        <v>106.75132534</v>
       </c>
       <c r="L2" s="18" t="n">
-        <v>294.32376717</v>
+        <v>104.43746577</v>
       </c>
       <c r="M2" s="18" t="n">
-        <v>306.30572181</v>
+        <v>111.38389884</v>
       </c>
       <c r="N2" s="18" t="n">
-        <v>308.3242502000001</v>
+        <v>108.8203236</v>
       </c>
       <c r="O2" s="18" t="n">
-        <v>318.74498172</v>
+        <v>115.10235451</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
@@ -12762,37 +12762,37 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>10717.18683164871</v>
+        <v>8.171868316487085</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>-98.52906440264066</v>
+        <v>34.30281541107079</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>28.28526201063937</v>
+        <v>38.30754810522059</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>26.42282561893972</v>
+        <v>16.69799287902125</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>17.08827928846119</v>
+        <v>25.27964039094615</v>
       </c>
       <c r="J3" s="18" t="n">
-        <v>14.10654679713092</v>
+        <v>10.03131298294768</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>33.17783380217427</v>
+        <v>36.72924270356559</v>
       </c>
       <c r="L3" s="18" t="n">
-        <v>1.093559527511156</v>
+        <v>-2.167523037892427</v>
       </c>
       <c r="M3" s="18" t="n">
-        <v>4.071011578578809</v>
+        <v>6.651284592923723</v>
       </c>
       <c r="N3" s="18" t="n">
-        <v>0.6589914083459769</v>
+        <v>-2.301567162487728</v>
       </c>
       <c r="O3" s="18" t="n">
-        <v>3.379796273968183</v>
+        <v>5.772847113643387</v>
       </c>
     </row>
     <row r="4" ht="15.5" customHeight="1">
@@ -12812,40 +12812,40 @@
         </is>
       </c>
       <c r="D4" s="18" t="n">
-        <v>63.40677504</v>
+        <v>24.15496192</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>6858.829320000001</v>
+        <v>26.1288736</v>
       </c>
       <c r="F4" s="18" t="n">
-        <v>100.88896203</v>
+        <v>35.09181288000001</v>
       </c>
       <c r="G4" s="18" t="n">
-        <v>129.42566928</v>
+        <v>48.53462598</v>
       </c>
       <c r="H4" s="18" t="n">
-        <v>163.62358818</v>
+        <v>56.63893437</v>
       </c>
       <c r="I4" s="18" t="n">
-        <v>191.58404391</v>
+        <v>70.9570533</v>
       </c>
       <c r="J4" s="18" t="n">
-        <v>218.60993672</v>
+        <v>78.07497740000001</v>
       </c>
       <c r="K4" s="18" t="n">
-        <v>291.1399782</v>
+        <v>106.75132534</v>
       </c>
       <c r="L4" s="18" t="n">
-        <v>294.32376717</v>
+        <v>104.43746577</v>
       </c>
       <c r="M4" s="18" t="n">
-        <v>306.30572181</v>
+        <v>111.38389884</v>
       </c>
       <c r="N4" s="18" t="n">
-        <v>308.3242502000001</v>
+        <v>108.8203236</v>
       </c>
       <c r="O4" s="18" t="n">
-        <v>318.74498172</v>
+        <v>115.10235451</v>
       </c>
     </row>
     <row r="5" ht="15.5" customHeight="1">
@@ -12868,37 +12868,37 @@
         <v>0</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>10717.18683164871</v>
+        <v>8.171868316487085</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>-98.52906440264066</v>
+        <v>34.30281541107079</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>28.28526201063937</v>
+        <v>38.30754810522059</v>
       </c>
       <c r="H5" s="18" t="n">
-        <v>26.42282561893972</v>
+        <v>16.69799287902125</v>
       </c>
       <c r="I5" s="18" t="n">
-        <v>17.08827928846119</v>
+        <v>25.27964039094615</v>
       </c>
       <c r="J5" s="18" t="n">
-        <v>14.10654679713092</v>
+        <v>10.03131298294768</v>
       </c>
       <c r="K5" s="18" t="n">
-        <v>33.17783380217427</v>
+        <v>36.72924270356559</v>
       </c>
       <c r="L5" s="18" t="n">
-        <v>1.093559527511156</v>
+        <v>-2.167523037892427</v>
       </c>
       <c r="M5" s="18" t="n">
-        <v>4.071011578578809</v>
+        <v>6.651284592923723</v>
       </c>
       <c r="N5" s="18" t="n">
-        <v>0.6589914083459769</v>
+        <v>-2.301567162487728</v>
       </c>
       <c r="O5" s="18" t="n">
-        <v>3.379796273968183</v>
+        <v>5.772847113643387</v>
       </c>
     </row>
     <row r="6" ht="15.5" customHeight="1">
@@ -13342,40 +13342,40 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>78.50997930488211</v>
+        <v>206.0886956753155</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>0.9184106350908815</v>
+        <v>241.0827917113564</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>86.50943654893452</v>
+        <v>248.7146300781868</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>89.61379983235702</v>
+        <v>238.9701328862853</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>85.12777441536231</v>
+        <v>245.92468164438</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>88.08106642289535</v>
+        <v>237.8188793418174</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>87.31641520821644</v>
+        <v>244.485962583006</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>77.06699524014552</v>
+        <v>210.182714291306</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>76.40677545555505</v>
+        <v>215.3281853747461</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>76.60494469949916</v>
+        <v>210.6635979236227</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>76.18238182209009</v>
+        <v>215.8500818292553</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>76.53959536135075</v>
+        <v>211.9558025391251</v>
       </c>
     </row>
     <row r="15" ht="15.5" customHeight="1">
@@ -13501,40 +13501,40 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>38.0952380952381</v>
+        <v>100</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>0.3809523809523809</v>
+        <v>100</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>34.78260869565217</v>
+        <v>100</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>34.61538461538461</v>
+        <v>100</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>37.03703703703704</v>
+        <v>100</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>35.71428571428572</v>
+        <v>100</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>36.66666666666667</v>
+        <v>100</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>35.48387096774194</v>
+        <v>100</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>36.36363636363636</v>
+        <v>100</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>35.29411764705882</v>
+        <v>100</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>36.11111111111111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" ht="15.5" customHeight="1">
@@ -13660,40 +13660,40 @@
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>40.13271640267636</v>
+        <v>105.3483805570255</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>0.5302037624073439</v>
+        <v>139.1784876319278</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>50.91908773310067</v>
+        <v>146.3923772326644</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>51.2400325784793</v>
+        <v>136.6400868759448</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>49.62898259042947</v>
+        <v>143.3726163723518</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>50.1260590203329</v>
+        <v>135.3403593548988</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>50.68619579795521</v>
+        <v>141.9213482342746</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>39.65262901490109</v>
+        <v>108.143533677003</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>40.12423448126587</v>
+        <v>113.0773880835674</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>39.41736058728612</v>
+        <v>108.3977416150368</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>40.01378554642303</v>
+        <v>113.3723923815319</v>
       </c>
       <c r="O20" s="18" t="n">
-        <v>39.52972303224912</v>
+        <v>109.4669253200745</v>
       </c>
     </row>
     <row r="21" ht="15.5" customHeight="1">
@@ -13713,40 +13713,40 @@
         </is>
       </c>
       <c r="D21" s="18" t="n">
-        <v>-3.170338752</v>
+        <v>-1.207748096</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>-342.941466</v>
+        <v>-1.30644368</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>-5.0444481015</v>
+        <v>-1.754590644000001</v>
       </c>
       <c r="G21" s="18" t="n">
-        <v>-6.471283463999999</v>
+        <v>-2.426731299</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>-8.181179409000002</v>
+        <v>-2.8319467185</v>
       </c>
       <c r="I21" s="18" t="n">
-        <v>-9.579202195499999</v>
+        <v>-3.547852665</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>-10.930496836</v>
+        <v>-3.903748870000001</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>-14.55699891</v>
+        <v>-5.337566267</v>
       </c>
       <c r="L21" s="18" t="n">
-        <v>-14.7161883585</v>
+        <v>-5.221873288499999</v>
       </c>
       <c r="M21" s="18" t="n">
-        <v>-15.3152860905</v>
+        <v>-5.569194942</v>
       </c>
       <c r="N21" s="18" t="n">
-        <v>-15.41621251</v>
+        <v>-5.44101618</v>
       </c>
       <c r="O21" s="18" t="n">
-        <v>-15.937249086</v>
+        <v>-5.755117725500001</v>
       </c>
     </row>
     <row r="22" ht="15.5" customHeight="1">
@@ -13769,37 +13769,37 @@
         <v>0</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>10717.18683164871</v>
+        <v>8.171868316487064</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>-98.52906440264066</v>
+        <v>34.30281541107079</v>
       </c>
       <c r="G22" s="18" t="n">
-        <v>28.28526201063937</v>
+        <v>38.30754810522057</v>
       </c>
       <c r="H22" s="18" t="n">
-        <v>26.42282561893974</v>
+        <v>16.69799287902125</v>
       </c>
       <c r="I22" s="18" t="n">
-        <v>17.08827928846117</v>
+        <v>25.27964039094612</v>
       </c>
       <c r="J22" s="18" t="n">
-        <v>14.10654679713092</v>
+        <v>10.0313129829477</v>
       </c>
       <c r="K22" s="18" t="n">
-        <v>33.17783380217427</v>
+        <v>36.72924270356559</v>
       </c>
       <c r="L22" s="18" t="n">
-        <v>1.093559527511156</v>
+        <v>-2.167523037892438</v>
       </c>
       <c r="M22" s="18" t="n">
-        <v>4.071011578578809</v>
+        <v>6.651284592923745</v>
       </c>
       <c r="N22" s="18" t="n">
-        <v>0.6589914083459769</v>
+        <v>-2.301567162487739</v>
       </c>
       <c r="O22" s="18" t="n">
-        <v>3.379796273968183</v>
+        <v>5.772847113643409</v>
       </c>
     </row>
     <row r="23" ht="15.5" customHeight="1">
@@ -13825,13 +13825,13 @@
         <v>5</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>5</v>
+        <v>5.000000000000001</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>5</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>5.000000000000001</v>
+        <v>5</v>
       </c>
       <c r="I23" s="18" t="n">
         <v>5</v>
@@ -13872,40 +13872,40 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>58.94453700111382</v>
+        <v>21.65531453711382</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>6505.650956488262</v>
+        <v>14.58553240826196</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>79.56458771942971</v>
+        <v>17.05729602692968</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>105.1712566920131</v>
+        <v>28.32476555701313</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>130.8766210493118</v>
+        <v>29.24119992981179</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>156.9283640906329</v>
+        <v>42.33272301113291</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>174.9493567243148</v>
+        <v>41.44114537031481</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>267.88964916029</v>
+        <v>92.72042894329009</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>265.9498861081142</v>
+        <v>85.5578997781142</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>281.6367036941628</v>
+        <v>96.46097187266281</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>278.3561570273553</v>
+        <v>88.82742675735521</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>291.9110786908909</v>
+        <v>98.45058284139093</v>
       </c>
     </row>
     <row r="25" ht="15.5" customHeight="1">
@@ -13925,40 +13925,40 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>58.94453700111382</v>
+        <v>21.65531453711382</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>6505.650956488262</v>
+        <v>14.58553240826196</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>79.56458771942971</v>
+        <v>17.05729602692968</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>105.1712566920131</v>
+        <v>28.32476555701313</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>130.8766210493118</v>
+        <v>29.24119992981179</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>156.9283640906329</v>
+        <v>42.33272301113291</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>174.9493567243148</v>
+        <v>41.44114537031481</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>267.88964916029</v>
+        <v>92.72042894329009</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>265.9498861081142</v>
+        <v>85.5578997781142</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>281.6367036941628</v>
+        <v>96.46097187266281</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>278.3561570273553</v>
+        <v>88.82742675735521</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>291.9110786908909</v>
+        <v>98.45058284139093</v>
       </c>
     </row>
     <row r="26" ht="15.5" customHeight="1">
@@ -13978,40 +13978,40 @@
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>92.96252169256174</v>
+        <v>89.65161944297456</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>94.85074861854503</v>
+        <v>55.82151236807223</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>78.86352096255152</v>
+        <v>48.60762276733557</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>81.25996742152071</v>
+        <v>58.35991312405522</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>79.98640202495515</v>
+        <v>51.62738362764821</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>81.91097801670414</v>
+        <v>59.65964064510118</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>80.0280899163305</v>
+        <v>53.0786517657254</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>92.01403765176556</v>
+        <v>86.85646632299702</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>90.35963648647606</v>
+        <v>81.92261191643256</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>91.94627577635023</v>
+        <v>86.60225838496318</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>90.2803321006358</v>
+        <v>81.62760761846806</v>
       </c>
       <c r="O26" s="18" t="n">
-        <v>91.58138807886198</v>
+        <v>85.53307467992552</v>
       </c>
     </row>
     <row r="27" ht="15.5" customHeight="1">
@@ -14031,40 +14031,40 @@
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>92.96252169256174</v>
+        <v>89.65161944297456</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>94.85074861854503</v>
+        <v>55.82151236807223</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>78.86352096255152</v>
+        <v>48.60762276733557</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>81.25996742152071</v>
+        <v>58.35991312405522</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>79.98640202495515</v>
+        <v>51.62738362764821</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>81.91097801670414</v>
+        <v>59.65964064510118</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>80.0280899163305</v>
+        <v>53.0786517657254</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>92.01403765176556</v>
+        <v>86.85646632299702</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>90.35963648647606</v>
+        <v>81.92261191643256</v>
       </c>
       <c r="M27" s="18" t="n">
-        <v>91.94627577635023</v>
+        <v>86.60225838496318</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>90.2803321006358</v>
+        <v>81.62760761846806</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>91.58138807886198</v>
+        <v>85.53307467992552</v>
       </c>
     </row>
     <row r="28" ht="15.5" customHeight="1">
@@ -14137,40 +14137,40 @@
         </is>
       </c>
       <c r="D29" s="19" t="n">
-        <v>0.2820248069676451</v>
+        <v>0.7403151182900686</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>0.007254491731156651</v>
+        <v>1.904304079428621</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>0.8077401201816858</v>
+        <v>2.322252845522347</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>0.8737672538777133</v>
+        <v>2.330046010340569</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>0.8834072095482247</v>
+        <v>2.552065272028205</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>0.9179703655254027</v>
+        <v>2.478519986918587</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>0.915933695975501</v>
+        <v>2.564614348731403</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>0.7476995585777585</v>
+        <v>2.039180614302978</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>0.7986700065472496</v>
+        <v>2.250797291178613</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>0.8239477485766797</v>
+        <v>2.26585630858587</v>
       </c>
       <c r="N29" s="19" t="n">
-        <v>0.874478628608239</v>
+        <v>2.477689447723344</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>0.8987612179905011</v>
+        <v>2.488877219050619</v>
       </c>
     </row>
     <row r="30" ht="15.5" customHeight="1">
@@ -14190,40 +14190,40 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>58.76571416620286</v>
+        <v>21.47649170220286</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>6505.153383282388</v>
+        <v>14.08795920238841</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>78.74966709627853</v>
+        <v>16.2423754037785</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>104.0403775757324</v>
+        <v>27.19388644073243</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>129.4311584748082</v>
+        <v>27.79573735530818</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>155.1696793424639</v>
+        <v>40.57403826296393</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>172.9470346511456</v>
+        <v>39.43882329714562</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>265.7127968284453</v>
+        <v>90.5435766114453</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>263.5992104575874</v>
+        <v>83.20722412758745</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>279.1129045955478</v>
+        <v>93.93717277404777</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>275.6599273525397</v>
+        <v>86.13119708253961</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>289.0463224109006</v>
+        <v>95.58582656140065</v>
       </c>
     </row>
     <row r="31" ht="15.5" customHeight="1">
@@ -14243,40 +14243,40 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>92.6804968855941</v>
+        <v>88.91130432468451</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>94.84349412681387</v>
+        <v>53.91720828864361</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>78.05578084236984</v>
+        <v>46.28536992181323</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>80.38620016764301</v>
+        <v>56.02986711371465</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>79.10299481540693</v>
+        <v>49.07531835562</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>80.99300765117874</v>
+        <v>57.18112065818259</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>79.11215622035499</v>
+        <v>50.51403741699401</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>91.26633809318781</v>
+        <v>84.81728570869404</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>89.56096647992882</v>
+        <v>79.67181462525396</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>91.12232802777356</v>
+        <v>84.33640207637731</v>
       </c>
       <c r="N31" s="19" t="n">
-        <v>89.40585347202756</v>
+        <v>79.14991817074473</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>90.68262686087148</v>
+        <v>83.0441974608749</v>
       </c>
     </row>
     <row r="32" ht="15.5" customHeight="1">
@@ -14349,40 +14349,40 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>58.76571416620286</v>
+        <v>21.47649170220286</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>6505.153383282388</v>
+        <v>14.08795920238841</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>78.74966709627853</v>
+        <v>16.2423754037785</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>104.0403775757324</v>
+        <v>27.19388644073243</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>129.4311584748082</v>
+        <v>27.79573735530818</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>155.1696793424639</v>
+        <v>40.57403826296393</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>172.9470346511456</v>
+        <v>39.43882329714562</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>265.7127968284453</v>
+        <v>90.5435766114453</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>263.5992104575874</v>
+        <v>83.20722412758745</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>279.1129045955478</v>
+        <v>93.93717277404777</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>275.6599273525397</v>
+        <v>86.13119708253961</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>289.0463224109006</v>
+        <v>95.58582656140065</v>
       </c>
     </row>
     <row r="34" ht="15.5" customHeight="1">
@@ -14402,40 +14402,40 @@
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>58.76571416620286</v>
+        <v>21.47649170220286</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>6505.153383282388</v>
+        <v>14.08795920238841</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>78.74966709627853</v>
+        <v>16.2423754037785</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>104.0403775757324</v>
+        <v>27.19388644073243</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>129.4311584748082</v>
+        <v>27.79573735530818</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>155.1696793424639</v>
+        <v>40.57403826296393</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>172.9470346511456</v>
+        <v>39.43882329714562</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>265.7127968284453</v>
+        <v>90.5435766114453</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>263.5992104575874</v>
+        <v>83.20722412758745</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>279.1129045955478</v>
+        <v>93.93717277404777</v>
       </c>
       <c r="N34" s="19" t="n">
-        <v>275.6599273525397</v>
+        <v>86.13119708253961</v>
       </c>
       <c r="O34" s="19" t="n">
-        <v>289.0463224109006</v>
+        <v>95.58582656140065</v>
       </c>
     </row>
     <row r="35" ht="15.5" customHeight="1">
@@ -14508,40 +14508,40 @@
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>-16.4543999665368</v>
+        <v>-6.0134176766168</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>-1821.442947319068</v>
+        <v>-3.944628576668756</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-22.04990678695799</v>
+        <v>-4.547865113057981</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>-29.13130572120508</v>
+        <v>-7.61428820340508</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>-36.2407243729463</v>
+        <v>-7.78280645948629</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>-43.4475102158899</v>
+        <v>-11.3607307136299</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>-48.42516970232077</v>
+        <v>-11.04287052320077</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>-74.39958311196467</v>
+        <v>-25.35220145120468</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>-73.80777892812448</v>
+        <v>-23.29802275572449</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>-78.15161328675339</v>
+        <v>-26.30240837673337</v>
       </c>
       <c r="N36" s="19" t="n">
-        <v>-77.18477965871111</v>
+        <v>-24.11673518311109</v>
       </c>
       <c r="O36" s="19" t="n">
-        <v>-80.93297027505217</v>
+        <v>-26.76403143719218</v>
       </c>
     </row>
     <row r="37" ht="15.5" customHeight="1">
@@ -14614,40 +14614,40 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>42.31131419966606</v>
+        <v>15.46307402558606</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>4683.710435963319</v>
+        <v>10.14333062571966</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>56.69976030932054</v>
+        <v>11.69451029072052</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>74.90907185452735</v>
+        <v>19.57959823732735</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>93.19043410186191</v>
+        <v>20.01293089582189</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>111.722169126574</v>
+        <v>29.21330754933403</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>124.5218649488248</v>
+        <v>28.39595277394485</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>191.3132137164806</v>
+        <v>65.19137516024063</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>189.791431529463</v>
+        <v>59.90920137186296</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>200.9612913087944</v>
+        <v>67.6347643973144</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>198.4751476938286</v>
+        <v>62.01446189942853</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>208.1133521358484</v>
+        <v>68.82179512420846</v>
       </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
@@ -14667,40 +14667,40 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>66.72995775762776</v>
+        <v>64.01613911377284</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>68.28731577130598</v>
+        <v>38.8203899678234</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>56.20016220650628</v>
+        <v>33.32546634370552</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>57.87806412070297</v>
+        <v>40.34150432187455</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>56.95415626709299</v>
+        <v>35.3342292160464</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>58.31496550884868</v>
+        <v>41.17040687389147</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>56.96075247865559</v>
+        <v>36.37010694023569</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>65.71176342709524</v>
+        <v>61.06844571025972</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>64.48389586554875</v>
+        <v>57.36370653018285</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>65.60807617999697</v>
+        <v>60.72220949499167</v>
       </c>
       <c r="N39" s="19" t="n">
-        <v>64.37221449985985</v>
+        <v>56.9879410829362</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>65.29149133982746</v>
+        <v>59.79182217182992</v>
       </c>
     </row>
     <row r="40" ht="15.5" customHeight="1">
@@ -14879,40 +14879,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>5.105332253680588</v>
+        <v>1.87915583285867</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>562.8980073278024</v>
+        <v>1.306189815473586</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>6.954167327747645</v>
+        <v>1.546182466103809</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>9.176099190905189</v>
+        <v>2.527520289535326</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>11.42940825684755</v>
+        <v>2.63614903958727</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>13.68555339338079</v>
+        <v>3.771006219956129</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>15.27779618303958</v>
+        <v>3.726977608792998</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>23.21479299207864</v>
+        <v>8.059561250160829</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>23.06844447670802</v>
+        <v>7.461351210954594</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>24.40701285901338</v>
+        <v>8.386041108054478</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>24.14567420854975</v>
+        <v>7.748091200330567</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>25.30260228303213</v>
+        <v>8.564852101388295</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -14985,40 +14985,40 @@
         </is>
       </c>
       <c r="D45" s="18" t="n">
-        <v>5.211515756712329</v>
+        <v>1.985339335890411</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>563.7393961643836</v>
+        <v>2.147578652054795</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>8.292243454520548</v>
+        <v>2.884258592876713</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>10.63772624219178</v>
+        <v>3.989147340821918</v>
       </c>
       <c r="H45" s="18" t="n">
-        <v>13.4485140969863</v>
+        <v>4.655254879726027</v>
       </c>
       <c r="I45" s="18" t="n">
-        <v>15.7466337460274</v>
+        <v>5.832086572602739</v>
       </c>
       <c r="J45" s="18" t="n">
-        <v>17.96794000438356</v>
+        <v>6.417121430136986</v>
       </c>
       <c r="K45" s="18" t="n">
-        <v>23.92931327671233</v>
+        <v>8.77408153479452</v>
       </c>
       <c r="L45" s="18" t="n">
-        <v>24.19099456191781</v>
+        <v>8.583901296164385</v>
       </c>
       <c r="M45" s="18" t="n">
-        <v>25.17581275150685</v>
+        <v>9.154841000547945</v>
       </c>
       <c r="N45" s="18" t="n">
-        <v>25.34171919452055</v>
+        <v>8.944136186301371</v>
       </c>
       <c r="O45" s="18" t="n">
-        <v>26.19821767561644</v>
+        <v>9.460467493972605</v>
       </c>
     </row>
     <row r="46" ht="15.5" customHeight="1">
@@ -15091,40 +15091,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>7.608851942434153</v>
+        <v>4.382675521612235</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>569.6852093751211</v>
+        <v>8.09339186279229</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>17.68666001107961</v>
+        <v>12.27867514943578</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>23.51709015489939</v>
+        <v>16.86851125352953</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>29.04368851968179</v>
+        <v>20.25042930242152</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>34.23948151302642</v>
+        <v>24.32493433960176</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>37.48396210451939</v>
+        <v>25.93314353027282</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>45.8620604618474</v>
+        <v>30.70682871992959</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>45.97238607617956</v>
+        <v>30.36529281042614</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>47.38400708119427</v>
+        <v>31.36303533023536</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>47.01289739892333</v>
+        <v>30.61531439070415</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>47.83296827103558</v>
+        <v>31.09521808939174</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -15144,13 +15144,13 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>2.291152682690083</v>
+        <v>2.291152682690086</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>5.104424374156153</v>
+        <v>5.104424374156288</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>8.056340429786026</v>
+        <v>8.056340429786157</v>
       </c>
       <c r="G48" s="18" t="n">
         <v>11.41773686142088</v>
@@ -15162,16 +15162,16 @@
         <v>16.43176741435227</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>16.82587827879167</v>
+        <v>16.82587827879169</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>21.21822690050121</v>
+        <v>21.21822690050123</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>20.6588414290518</v>
+        <v>20.65884142905179</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>21.43939443719379</v>
+        <v>21.4393944371938</v>
       </c>
       <c r="N48" s="18" t="n">
         <v>20.47513321843181</v>
@@ -15250,40 +15250,40 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>2.291152682690083</v>
+        <v>2.291152682690086</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>2.81327169146607</v>
+        <v>2.813271691466202</v>
       </c>
       <c r="F50" s="18" t="n">
         <v>2.951916055629873</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>3.361396431634859</v>
+        <v>3.361396431634855</v>
       </c>
       <c r="H50" s="18" t="n">
         <v>2.15833172113571</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>2.855698831795678</v>
+        <v>2.855698831795682</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>0.3941108644393978</v>
+        <v>0.3941108644394227</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>4.392348621709544</v>
+        <v>4.392348621709537</v>
       </c>
       <c r="L50" s="18" t="n">
         <v>-0.5593854714494171</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>0.7805530081419931</v>
+        <v>0.7805530081420073</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>-0.9642612187619761</v>
+        <v>-0.9642612187619832</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>0.2640019844028529</v>
+        <v>0.2640019844028672</v>
       </c>
     </row>
     <row r="51" ht="15.5" customHeight="1">
@@ -15306,10 +15306,10 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>2.291152682690083</v>
+        <v>2.291152682690086</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>5.104424374156153</v>
+        <v>5.104424374156284</v>
       </c>
       <c r="G51" s="18" t="n">
         <v>8.056340429786026</v>
@@ -15324,7 +15324,7 @@
         <v>16.43176741435227</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>16.82587827879167</v>
+        <v>16.82587827879169</v>
       </c>
       <c r="L51" s="18" t="n">
         <v>21.21822690050121</v>
@@ -15333,7 +15333,7 @@
         <v>20.65884142905179</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>21.43939443719378</v>
+        <v>21.4393944371938</v>
       </c>
       <c r="O51" s="18" t="n">
         <v>20.4751332184318</v>
@@ -15674,40 +15674,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>2.397336185721823</v>
+        <v>2.397336185721827</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>5.945813210737362</v>
+        <v>5.945813210737497</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>9.39441655655893</v>
+        <v>9.394416556559062</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>12.87936391270748</v>
+        <v>12.87936391270747</v>
       </c>
       <c r="H58" s="18" t="n">
         <v>15.59517442269535</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>18.49284776699887</v>
+        <v>18.49284776699888</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>19.51602210013565</v>
+        <v>19.51602210013568</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>21.9327471851349</v>
+        <v>21.93274718513492</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>21.78139151426159</v>
+        <v>21.78139151426158</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>22.20819432968726</v>
+        <v>22.20819432968727</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>21.67117820440261</v>
+        <v>21.67117820440262</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>21.63475059541896</v>
+        <v>21.63475059541897</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -15727,40 +15727,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>5.21151575671233</v>
+        <v>1.985339335890408</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>563.7393961643837</v>
+        <v>2.147578652054793</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>8.292243454520683</v>
+        <v>2.884258592876716</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>10.63772624219192</v>
+        <v>3.989147340822061</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>13.44851409698644</v>
+        <v>4.655254879726172</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>15.74663374602754</v>
+        <v>5.832086572602883</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>17.96794000438374</v>
+        <v>6.417121430137133</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>23.9293132767125</v>
+        <v>8.774081534794671</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>24.19099456191797</v>
+        <v>8.583901296164555</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>25.17581275150701</v>
+        <v>9.154841000548092</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>25.34171919452072</v>
+        <v>8.944136186301527</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>26.19821767561662</v>
+        <v>9.460467493972772</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -15833,40 +15833,40 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>58.94453700111382</v>
+        <v>21.65531453711382</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>6505.650956488262</v>
+        <v>14.58553240826196</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>79.56458771942971</v>
+        <v>17.05729602692968</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>105.1712566920131</v>
+        <v>28.32476555701313</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>130.8766210493118</v>
+        <v>29.24119992981179</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>156.9283640906329</v>
+        <v>42.33272301113291</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>174.9493567243148</v>
+        <v>41.44114537031481</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>267.88964916029</v>
+        <v>92.72042894329009</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>265.9498861081142</v>
+        <v>85.5578997781142</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>281.6367036941628</v>
+        <v>96.46097187266281</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>278.3561570273553</v>
+        <v>88.82742675735521</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>291.9110786908909</v>
+        <v>98.45058284139093</v>
       </c>
     </row>
     <row r="62" ht="15.5" customHeight="1">
@@ -15886,40 +15886,40 @@
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>-16.4543999665368</v>
+        <v>-6.0134176766168</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>-1821.442947319068</v>
+        <v>-3.944628576668756</v>
       </c>
       <c r="F62" s="18" t="n">
-        <v>-22.04990678695799</v>
+        <v>-4.547865113057981</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>-29.13130572120508</v>
+        <v>-7.61428820340508</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>-36.2407243729463</v>
+        <v>-7.78280645948629</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>-43.4475102158899</v>
+        <v>-11.3607307136299</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>-48.42516970232077</v>
+        <v>-11.04287052320077</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>-74.39958311196467</v>
+        <v>-25.35220145120468</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>-73.80777892812448</v>
+        <v>-23.29802275572449</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>-78.15161328675339</v>
+        <v>-26.30240837673337</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>-77.18477965871111</v>
+        <v>-24.11673518311109</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>-80.93297027505217</v>
+        <v>-26.76403143719218</v>
       </c>
     </row>
     <row r="63" ht="15.5" customHeight="1">
@@ -15992,40 +15992,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>42.70250404064051</v>
+        <v>15.8542638665605</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>4685.678419836292</v>
+        <v>12.11131449869214</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>58.50805551285511</v>
+        <v>13.50280549425509</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>76.28705281983544</v>
+        <v>20.95757920263543</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>95.75085425406985</v>
+        <v>22.57335104802983</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>113.5648028997587</v>
+        <v>31.05594132251871</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>127.7823139593888</v>
+        <v>31.6564017845088</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>189.5388189749048</v>
+        <v>63.41698041866481</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>192.9581667811419</v>
+        <v>63.07593662354191</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>202.7775900219768</v>
+        <v>69.45106311049678</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>202.0258675555988</v>
+        <v>65.5651817611988</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>210.3772492290657</v>
+        <v>71.08569221742574</v>
       </c>
     </row>
     <row r="65" ht="15.5" customHeight="1">
@@ -16151,40 +16151,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>40.02016151697597</v>
+        <v>13.17192134289597</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>4680.897164271853</v>
+        <v>7.330058934253456</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>53.74784425369067</v>
+        <v>8.74259423509065</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>71.5476754228925</v>
+        <v>16.21820180569249</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>91.0321023807262</v>
+        <v>17.85459917468618</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>108.8664702947783</v>
+        <v>26.35760871753835</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>124.1277540843854</v>
+        <v>28.00184190950542</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>186.9208650947711</v>
+        <v>60.79902653853109</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>190.3508170009124</v>
+        <v>60.46858684331238</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>200.1807383006524</v>
+        <v>66.85421138917239</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>199.4394089125906</v>
+        <v>62.97872311819051</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>207.8493501514455</v>
+        <v>68.5577931398056</v>
       </c>
     </row>
     <row r="68" ht="15.5" customHeight="1">
@@ -16416,40 +16416,40 @@
         </is>
       </c>
       <c r="D72" s="18" t="n">
-        <v>-40.02016151697597</v>
+        <v>-13.17192134289597</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>-4680.897164271853</v>
+        <v>-7.330058934253456</v>
       </c>
       <c r="F72" s="18" t="n">
-        <v>-53.74784425369067</v>
+        <v>-8.74259423509065</v>
       </c>
       <c r="G72" s="18" t="n">
-        <v>-71.5476754228925</v>
+        <v>-16.21820180569249</v>
       </c>
       <c r="H72" s="18" t="n">
-        <v>-91.0321023807262</v>
+        <v>-17.85459917468618</v>
       </c>
       <c r="I72" s="18" t="n">
-        <v>-108.8664702947783</v>
+        <v>-26.35760871753835</v>
       </c>
       <c r="J72" s="18" t="n">
-        <v>-124.1277540843854</v>
+        <v>-28.00184190950542</v>
       </c>
       <c r="K72" s="18" t="n">
-        <v>-186.9208650947711</v>
+        <v>-60.79902653853109</v>
       </c>
       <c r="L72" s="18" t="n">
-        <v>-190.3508170009124</v>
+        <v>-60.46858684331238</v>
       </c>
       <c r="M72" s="18" t="n">
-        <v>-200.1807383006524</v>
+        <v>-66.85421138917239</v>
       </c>
       <c r="N72" s="18" t="n">
-        <v>-199.4394089125906</v>
+        <v>-62.97872311819051</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>-207.8493501514455</v>
+        <v>-68.5577931398056</v>
       </c>
     </row>
     <row r="73" ht="15.5" customHeight="1">
@@ -16522,40 +16522,40 @@
         </is>
       </c>
       <c r="D74" s="18" t="n">
-        <v>-40.02016151697597</v>
+        <v>-13.17192134289597</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>-4680.897164271853</v>
+        <v>-7.330058934253456</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>-53.74784425369067</v>
+        <v>-8.74259423509065</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>-71.5476754228925</v>
+        <v>-16.21820180569249</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>-91.0321023807262</v>
+        <v>-17.85459917468618</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>-108.8664702947783</v>
+        <v>-26.35760871753835</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>-124.1277540843854</v>
+        <v>-28.00184190950542</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>-186.9208650947711</v>
+        <v>-60.79902653853109</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>-190.3508170009124</v>
+        <v>-60.46858684331238</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>-200.1807383006524</v>
+        <v>-66.85421138917239</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>-199.4394089125906</v>
+        <v>-62.97872311819051</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>-207.8493501514455</v>
+        <v>-68.5577931398056</v>
       </c>
     </row>
     <row r="75" ht="15.5" customHeight="1">
@@ -16893,40 +16893,40 @@
         </is>
       </c>
       <c r="D81" s="18" t="n">
-        <v>4.230372104514676</v>
+        <v>11.10472677435102</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>0.06970949911957694</v>
+        <v>18.29874351888895</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>4.71826765127087</v>
+        <v>13.56501949740375</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>3.661852724662952</v>
+        <v>9.764940599101205</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>2.88390685342545</v>
+        <v>8.331286465451301</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>2.452361120004069</v>
+        <v>6.621375024010985</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>1.671726331307717</v>
+        <v>4.680833727661606</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>0.8992079673562754</v>
+        <v>2.452385365517115</v>
       </c>
       <c r="L81" s="18" t="n">
-        <v>0.885878094487538</v>
+        <v>2.496565539010335</v>
       </c>
       <c r="M81" s="18" t="n">
-        <v>0.8477973267946985</v>
+        <v>2.331442648685421</v>
       </c>
       <c r="N81" s="18" t="n">
-        <v>0.838876164080684</v>
+        <v>2.376815798228605</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>0.7930788632276456</v>
+        <v>2.196218390476557</v>
       </c>
     </row>
     <row r="82" ht="15.5" customHeight="1">
@@ -17211,40 +17211,40 @@
         </is>
       </c>
       <c r="D87" s="18" t="n">
-        <v>5.211515756712329</v>
+        <v>1.985339335890411</v>
       </c>
       <c r="E87" s="18" t="n">
-        <v>563.7393961643836</v>
+        <v>2.147578652054795</v>
       </c>
       <c r="F87" s="18" t="n">
-        <v>8.292243454520548</v>
+        <v>2.884258592876713</v>
       </c>
       <c r="G87" s="18" t="n">
-        <v>10.63772624219178</v>
+        <v>3.989147340821918</v>
       </c>
       <c r="H87" s="18" t="n">
-        <v>13.4485140969863</v>
+        <v>4.655254879726027</v>
       </c>
       <c r="I87" s="18" t="n">
-        <v>15.7466337460274</v>
+        <v>5.832086572602739</v>
       </c>
       <c r="J87" s="18" t="n">
-        <v>17.96794000438356</v>
+        <v>6.417121430136986</v>
       </c>
       <c r="K87" s="18" t="n">
-        <v>23.92931327671233</v>
+        <v>8.77408153479452</v>
       </c>
       <c r="L87" s="18" t="n">
-        <v>24.19099456191781</v>
+        <v>8.583901296164385</v>
       </c>
       <c r="M87" s="18" t="n">
-        <v>25.17581275150685</v>
+        <v>9.154841000547945</v>
       </c>
       <c r="N87" s="18" t="n">
-        <v>25.34171919452055</v>
+        <v>8.944136186301371</v>
       </c>
       <c r="O87" s="18" t="n">
-        <v>26.19821767561644</v>
+        <v>9.460467493972605</v>
       </c>
     </row>
     <row r="88" ht="15.5" customHeight="1">
@@ -17715,37 +17715,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>82.33147571664203</v>
+        <v>28.63499536848203</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>9446.939075951816</v>
+        <v>99.80486527661515</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>9557.386680514826</v>
+        <v>9467.376180477626</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>9703.843427792246</v>
+        <v>9593.184480557846</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>9888.065964274834</v>
+        <v>9741.710957862753</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>10108.65460369619</v>
+        <v>9943.636880541706</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>10357.3042227294</v>
+        <v>10165.05239837964</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>10735.53830154065</v>
+        <v>10483.29462442817</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>11115.68055007103</v>
+        <v>10855.91608975582</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>11516.82257968048</v>
+        <v>11250.16952585752</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>11914.7371362869</v>
+        <v>11641.8157646981</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -17818,40 +17818,40 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>42.31131419966606</v>
+        <v>15.46307402558606</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>4683.710435963319</v>
+        <v>10.14333062571966</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>56.69976030932054</v>
+        <v>11.69451029072052</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>74.90907185452735</v>
+        <v>19.57959823732735</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>93.19043410186191</v>
+        <v>20.01293089582189</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>111.722169126574</v>
+        <v>29.21330754933403</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>124.5218649488248</v>
+        <v>28.39595277394485</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>191.3132137164806</v>
+        <v>65.19137516024063</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>189.791431529463</v>
+        <v>59.90920137186296</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>200.9612913087944</v>
+        <v>67.6347643973144</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>198.4751476938286</v>
+        <v>62.01446189942853</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>208.1133521358484</v>
+        <v>68.82179512420846</v>
       </c>
     </row>
     <row r="99" ht="15.5" customHeight="1">
@@ -17871,40 +17871,40 @@
         </is>
       </c>
       <c r="D99" s="20" t="n">
-        <v>40.02016151697597</v>
+        <v>13.17192134289597</v>
       </c>
       <c r="E99" s="20" t="n">
-        <v>4680.897164271853</v>
+        <v>7.330058934253456</v>
       </c>
       <c r="F99" s="20" t="n">
-        <v>53.74784425369067</v>
+        <v>8.74259423509065</v>
       </c>
       <c r="G99" s="20" t="n">
-        <v>71.5476754228925</v>
+        <v>16.21820180569249</v>
       </c>
       <c r="H99" s="20" t="n">
-        <v>91.0321023807262</v>
+        <v>17.85459917468618</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>108.8664702947783</v>
+        <v>26.35760871753835</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>124.1277540843854</v>
+        <v>28.00184190950542</v>
       </c>
       <c r="K99" s="20" t="n">
-        <v>186.9208650947711</v>
+        <v>60.79902653853109</v>
       </c>
       <c r="L99" s="20" t="n">
-        <v>190.3508170009124</v>
+        <v>60.46858684331238</v>
       </c>
       <c r="M99" s="20" t="n">
-        <v>200.1807383006524</v>
+        <v>66.85421138917239</v>
       </c>
       <c r="N99" s="20" t="n">
-        <v>199.4394089125906</v>
+        <v>62.97872311819051</v>
       </c>
       <c r="O99" s="20" t="n">
-        <v>207.8493501514455</v>
+        <v>68.5577931398056</v>
       </c>
     </row>
     <row r="100" ht="15.5" customHeight="1">
@@ -17924,40 +17924,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>82.33147571664203</v>
+        <v>28.63499536848203</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>9446.939075951816</v>
+        <v>99.80486527661515</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>9557.386680514826</v>
+        <v>9467.376180477626</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>9703.843427792246</v>
+        <v>9593.184480557846</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>9888.065964274834</v>
+        <v>9741.710957862753</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>10108.65460369619</v>
+        <v>9943.636880541706</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>10357.3042227294</v>
+        <v>10165.05239837964</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>10735.53830154065</v>
+        <v>10483.29462442817</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>11115.68055007103</v>
+        <v>10855.91608975582</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>11516.82257968048</v>
+        <v>11250.16952585752</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>11914.7371362869</v>
+        <v>11641.8157646981</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>12330.69983857419</v>
+        <v>12052.11672455091</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -20822,22 +20822,22 @@
         <v>1535.766582378783</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>1559.706514568245</v>
+        <v>1766.452534384212</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>1553.970013807372</v>
+        <v>1786.918996540068</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>1856.76672414609</v>
+        <v>1770.030551263489</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>2145.626573917291</v>
+        <v>2061.788504531658</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>2420.674939575357</v>
+        <v>2339.717948400777</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>2606.395787435297</v>
+        <v>2528.282791649973</v>
       </c>
     </row>
     <row r="42">
@@ -20875,22 +20875,22 @@
         <v>1535.766582378783</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>1559.706514568245</v>
+        <v>1766.452534384212</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>1553.970013807372</v>
+        <v>1786.918996540068</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>1856.76672414609</v>
+        <v>1770.030551263489</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>2145.626573917291</v>
+        <v>2061.788504531658</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>2420.674939575357</v>
+        <v>2339.717948400777</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>2606.395787435297</v>
+        <v>2528.282791649973</v>
       </c>
     </row>
     <row r="43">
@@ -20931,19 +20931,19 @@
         <v>59.81317191628446</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>919.710520626107</v>
+        <v>64.73609202675598</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>1779.75456263426</v>
+        <v>924.7801340349087</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>2639.596024296297</v>
+        <v>1784.621595696946</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>3499.218087770026</v>
+        <v>2644.243659170675</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>4362.607926475569</v>
+        <v>3507.633497876217</v>
       </c>
     </row>
     <row r="44">
@@ -20984,19 +20984,19 @@
         <v>0</v>
       </c>
       <c r="K44" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="18" t="n">
         <v>854.9744285993511</v>
       </c>
-      <c r="L44" s="18" t="n">
+      <c r="M44" s="18" t="n">
         <v>1709.948857198702</v>
       </c>
-      <c r="M44" s="18" t="n">
+      <c r="N44" s="18" t="n">
         <v>2564.923285798053</v>
       </c>
-      <c r="N44" s="18" t="n">
+      <c r="O44" s="18" t="n">
         <v>3419.897714397404</v>
-      </c>
-      <c r="O44" s="18" t="n">
-        <v>4274.872142996755</v>
       </c>
     </row>
     <row r="45">
@@ -21140,22 +21140,22 @@
         <v>1591.212147301016</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>1619.519686484529</v>
+        <v>1826.265706300496</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>2473.680534433479</v>
+        <v>1851.655088566824</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>3636.52128678035</v>
+        <v>2694.810685298398</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>4785.222598213588</v>
+        <v>3846.410100228605</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>5919.893027345383</v>
+        <v>4983.961607571451</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>6969.003713910866</v>
+        <v>6035.91628952619</v>
       </c>
     </row>
     <row r="48">
@@ -21196,19 +21196,19 @@
         <v>1811.836825463851</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>-1718.883879916045</v>
+        <v>2043.395419655636</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>1867.813440901686</v>
+        <v>-1498.072029484937</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>-1918.089302726937</v>
+        <v>2077.393187096419</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>3197.932903991988</v>
+        <v>-1719.651941391034</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>4046.742312711115</v>
+        <v>3313.662490482477</v>
       </c>
     </row>
     <row r="49">
@@ -21355,19 +21355,19 @@
         <v>1577.77332738734</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>-1950.442474107829</v>
+        <v>1811.836825463852</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>1647.001590470578</v>
+        <v>-1718.883879916045</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>-2127.66904892167</v>
+        <v>1867.813440901686</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>2999.495542656086</v>
+        <v>-1918.089302726937</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>3931.012726220627</v>
+        <v>3197.932903991988</v>
       </c>
     </row>
     <row r="52">
@@ -21405,22 +21405,22 @@
         <v>0</v>
       </c>
       <c r="J52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="18" t="n">
         <v>-74.11679431732691</v>
       </c>
-      <c r="K52" s="18" t="n">
+      <c r="L52" s="18" t="n">
         <v>420.309520466836</v>
       </c>
-      <c r="L52" s="18" t="n">
+      <c r="M52" s="18" t="n">
         <v>345.7993353962562</v>
       </c>
-      <c r="M52" s="18" t="n">
+      <c r="N52" s="18" t="n">
         <v>277.9086329187738</v>
       </c>
-      <c r="N52" s="18" t="n">
+      <c r="O52" s="18" t="n">
         <v>216.5838862209679</v>
-      </c>
-      <c r="O52" s="18" t="n">
-        <v>161.7537262182767</v>
       </c>
     </row>
     <row r="53">
@@ -21458,22 +21458,22 @@
         <v>0</v>
       </c>
       <c r="J53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="18" t="n">
         <v>-74.11679431732691</v>
       </c>
-      <c r="K53" s="18" t="n">
+      <c r="L53" s="18" t="n">
         <v>420.309520466836</v>
       </c>
-      <c r="L53" s="18" t="n">
+      <c r="M53" s="18" t="n">
         <v>345.7993353962562</v>
       </c>
-      <c r="M53" s="18" t="n">
+      <c r="N53" s="18" t="n">
         <v>277.9086329187738</v>
       </c>
-      <c r="N53" s="18" t="n">
+      <c r="O53" s="18" t="n">
         <v>216.5838862209679</v>
-      </c>
-      <c r="O53" s="18" t="n">
-        <v>161.7537262182767</v>
       </c>
     </row>
     <row r="54">
@@ -21723,22 +21723,22 @@
         <v>1556.769954883061</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>1715.027885606705</v>
+        <v>1789.144679924031</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>-1323.43956109901</v>
+        <v>1944.413423688509</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>2186.371918160646</v>
+        <v>-1105.003367155397</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>-1669.700510850042</v>
+        <v>2393.672681450797</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>3382.82395574487</v>
+        <v>-1473.436142940347</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>4172.742337253369</v>
+        <v>3494.492675027422</v>
       </c>
     </row>
     <row r="59">
@@ -21776,22 +21776,22 @@
         <v>34.44219241795531</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>-95.50819912217526</v>
+        <v>37.1210263764649</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>3797.120095532488</v>
+        <v>-92.75833512168492</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>1450.149368619704</v>
+        <v>3799.814052453795</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>6454.923109063629</v>
+        <v>1452.737418777808</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>2537.069071600513</v>
+        <v>6457.397750511798</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>2796.261376657497</v>
+        <v>2541.423614498768</v>
       </c>
     </row>
     <row r="60">
@@ -22683,16 +22683,16 @@
         <v>0</v>
       </c>
       <c r="L76" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="18" t="n">
         <v>854.9744285993511</v>
       </c>
-      <c r="M76" s="18" t="n">
+      <c r="N76" s="18" t="n">
         <v>1709.948857198702</v>
       </c>
-      <c r="N76" s="18" t="n">
+      <c r="O76" s="18" t="n">
         <v>2564.923285798053</v>
-      </c>
-      <c r="O76" s="18" t="n">
-        <v>3419.897714397404</v>
       </c>
     </row>
     <row r="77">
@@ -22786,19 +22786,19 @@
         <v>0</v>
       </c>
       <c r="K78" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="18" t="n">
         <v>854.9744285993511</v>
       </c>
-      <c r="L78" s="18" t="n">
+      <c r="M78" s="18" t="n">
         <v>1709.948857198702</v>
       </c>
-      <c r="M78" s="18" t="n">
+      <c r="N78" s="18" t="n">
         <v>2564.923285798053</v>
       </c>
-      <c r="N78" s="18" t="n">
+      <c r="O78" s="18" t="n">
         <v>3419.897714397404</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>4274.872142996755</v>
       </c>
     </row>
     <row r="79">
@@ -22998,19 +22998,19 @@
         <v>1535.766582378783</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>1559.706514568245</v>
+        <v>1766.452534384212</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>1553.970013807372</v>
+        <v>1786.918996540068</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>1856.76672414609</v>
+        <v>1770.030551263489</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>2145.626573917291</v>
+        <v>2061.788504531658</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>2420.674939575357</v>
+        <v>2339.717948400777</v>
       </c>
     </row>
     <row r="83">
@@ -23154,22 +23154,22 @@
         <v>1535.766582378783</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>1559.706514568245</v>
+        <v>1766.452534384212</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>1553.970013807372</v>
+        <v>1786.918996540068</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>1856.76672414609</v>
+        <v>1770.030551263489</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>2145.626573917291</v>
+        <v>2061.788504531658</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>2420.674939575357</v>
+        <v>2339.717948400777</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>2606.395787435297</v>
+        <v>2528.282791649973</v>
       </c>
     </row>
     <row r="86">
@@ -23764,19 +23764,19 @@
         <v>70261.19836605332</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>1653682.30300708</v>
+        <v>70954.9529217129</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>3276965.608485644</v>
+        <v>1654450.493356884</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>4891606.088890755</v>
+        <v>3277819.21466039</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>6544602.751974707</v>
+        <v>4892542.257677892</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>8201702.699148507</v>
+        <v>6545617.765946605</v>
       </c>
     </row>
     <row r="97">
@@ -23973,22 +23973,22 @@
         <v>70261.19836605332</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>1653682.30300708</v>
+        <v>70954.9529217129</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>3276965.608485644</v>
+        <v>1654450.493356884</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>4891606.088890755</v>
+        <v>3277819.21466039</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>6544602.751974707</v>
+        <v>4892542.257677892</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>8201702.699148507</v>
+        <v>6545617.765946605</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>9850565.264000123</v>
+        <v>8202935.558616287</v>
       </c>
     </row>
     <row r="101">
@@ -24135,19 +24135,19 @@
         <v>0</v>
       </c>
       <c r="K103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="18" t="n">
         <v>-74.11679431732691</v>
       </c>
-      <c r="L103" s="18" t="n">
+      <c r="M103" s="18" t="n">
         <v>420.309520466836</v>
       </c>
-      <c r="M103" s="18" t="n">
+      <c r="N103" s="18" t="n">
         <v>345.7993353962562</v>
       </c>
-      <c r="N103" s="18" t="n">
+      <c r="O103" s="18" t="n">
         <v>277.9086329187738</v>
-      </c>
-      <c r="O103" s="18" t="n">
-        <v>216.5838862209679</v>
       </c>
     </row>
     <row r="104">
@@ -24344,22 +24344,22 @@
         <v>0</v>
       </c>
       <c r="J107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="18" t="n">
         <v>-74.11679431732691</v>
       </c>
-      <c r="K107" s="18" t="n">
+      <c r="L107" s="18" t="n">
         <v>420.309520466836</v>
       </c>
-      <c r="L107" s="18" t="n">
+      <c r="M107" s="18" t="n">
         <v>345.7993353962562</v>
       </c>
-      <c r="M107" s="18" t="n">
+      <c r="N107" s="18" t="n">
         <v>277.9086329187738</v>
       </c>
-      <c r="N107" s="18" t="n">
+      <c r="O107" s="18" t="n">
         <v>216.5838862209679</v>
-      </c>
-      <c r="O107" s="18" t="n">
-        <v>161.7537262182767</v>
       </c>
     </row>
     <row r="108">

--- a/backend/Rwanda/financial-statements-CleanStep.xlsx
+++ b/backend/Rwanda/financial-statements-CleanStep.xlsx
@@ -962,40 +962,40 @@
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O8" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" ht="15.5" customHeight="1">
@@ -1598,40 +1598,40 @@
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O20" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" ht="15.5" customHeight="1">
@@ -2075,40 +2075,40 @@
         </is>
       </c>
       <c r="D29" s="19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N29" s="19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" ht="15.5" customHeight="1">
@@ -2729,22 +2729,22 @@
         <v>377.9752415799667</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>427.6745349631409</v>
+        <v>468.8902736200481</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>786.7461088895443</v>
+        <v>546.4993238167979</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>820.8560689793743</v>
+        <v>900.2983204991639</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>852.6478332128239</v>
+        <v>929.1884291173966</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>882.1446792975107</v>
+        <v>955.8125403939653</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>860.7048705459894</v>
+        <v>931.5288876506644</v>
       </c>
     </row>
     <row r="42" ht="15.5" customHeight="1">
@@ -2782,22 +2782,22 @@
         <v>377.9752415799667</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>427.6745349631409</v>
+        <v>468.8902736200481</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>786.7461088895443</v>
+        <v>546.4993238167979</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>820.8560689793743</v>
+        <v>900.2983204991639</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>852.6478332128239</v>
+        <v>929.1884291173966</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>882.1446792975107</v>
+        <v>955.8125403939653</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>860.7048705459894</v>
+        <v>931.5288876506644</v>
       </c>
     </row>
     <row r="43" ht="15.5" customHeight="1">
@@ -2820,37 +2820,37 @@
         <v>30.71713469777927</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>2300.119789112662</v>
+        <v>2.13224831266213</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>4819.967587891309</v>
+        <v>2521.980047091309</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>6899.293831268377</v>
+        <v>4601.306290468377</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>9185.34504808879</v>
+        <v>6887.357507288791</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>11484.98741025383</v>
+        <v>9186.999869453832</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>13767.25131730229</v>
+        <v>11471.77062581735</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>14940.13680426029</v>
+        <v>13743.32513047112</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>16458.03297266198</v>
+        <v>14936.61499750294</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>17940.88581045407</v>
+        <v>16460.00031826405</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>19459.06239975362</v>
+        <v>17942.8050141539</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>21056.76178785249</v>
+        <v>19461.63722772111</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -2873,37 +2873,37 @@
         <v>0</v>
       </c>
       <c r="E44" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="18" t="n">
         <v>2297.9875408</v>
       </c>
-      <c r="F44" s="18" t="n">
+      <c r="G44" s="18" t="n">
         <v>4595.9750816</v>
       </c>
-      <c r="G44" s="18" t="n">
-        <v>6893.962622399999</v>
-      </c>
       <c r="H44" s="18" t="n">
+        <v>6880.365105369025</v>
+      </c>
+      <c r="I44" s="18" t="n">
         <v>9178.352646169024</v>
       </c>
-      <c r="I44" s="18" t="n">
-        <v>11476.34018696902</v>
-      </c>
       <c r="J44" s="18" t="n">
-        <v>13756.96522451539</v>
+        <v>11461.48453303045</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>14927.48028473426</v>
+        <v>13730.66861094509</v>
       </c>
       <c r="L44" s="18" t="n">
+        <v>14921.95254081148</v>
+      </c>
+      <c r="M44" s="18" t="n">
         <v>16443.37051597052</v>
       </c>
-      <c r="M44" s="18" t="n">
+      <c r="N44" s="18" t="n">
         <v>17924.25600816054</v>
       </c>
-      <c r="N44" s="18" t="n">
+      <c r="O44" s="18" t="n">
         <v>19440.51339376026</v>
-      </c>
-      <c r="O44" s="18" t="n">
-        <v>21035.63795389164</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -3032,37 +3032,37 @@
         <v>71.93287335468639</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>2414.491028411108</v>
+        <v>116.5034876111085</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>5004.56336442383</v>
+        <v>2706.575823623831</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>7151.212491261584</v>
+        <v>4853.224950461584</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>9501.713954307026</v>
+        <v>7203.726413507027</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>11862.9626518338</v>
+        <v>9564.975111033798</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>14194.92585226543</v>
+        <v>11940.66089943739</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>15726.88291314983</v>
+        <v>14289.82445428791</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>17278.88904164136</v>
+        <v>15836.9133180021</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>18793.53364366689</v>
+        <v>17389.18874738145</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>20341.20707905113</v>
+        <v>18898.61755454787</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>21917.46665839848</v>
+        <v>20393.16611537178</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -3088,34 +3088,34 @@
         <v>118.6357359237707</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>1360.326272383511</v>
+        <v>632.5807891151399</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>2303.43606959473</v>
+        <v>990.3265609983337</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>3657.589598401996</v>
+        <v>2357.611184891562</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>5009.484205869137</v>
+        <v>3722.50557649381</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>6362.930166056397</v>
+        <v>5088.821322974819</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>6888.171458147949</v>
+        <v>6460.199194818024</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>27173.90079794113</v>
+        <v>7000.207800165653</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>21442.30310109409</v>
+        <v>27286.1678492833</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>22921.13806258924</v>
+        <v>21549.3062156749</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>23934.75198131315</v>
+        <v>22975.67192687738</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -3247,34 +3247,34 @@
         <v>102.6500080524657</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>846.3812191921418</v>
+        <v>118.6357359237707</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>2673.435780979908</v>
+        <v>1360.326272383511</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>3603.414483105165</v>
+        <v>2303.436069594731</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>4944.568227777324</v>
+        <v>3657.589598401996</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>6283.593048950715</v>
+        <v>5009.484205869137</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>6790.902429386321</v>
+        <v>6362.930166056396</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>27061.86445592343</v>
+        <v>6888.171458147949</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>21330.03604975193</v>
+        <v>27173.90079794114</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>22814.13494800844</v>
+        <v>21442.30310109409</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>23880.21811702501</v>
+        <v>22921.13806258924</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -3294,40 +3294,40 @@
         </is>
       </c>
       <c r="D52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="18" t="n">
         <v>-727.7454832683711</v>
       </c>
-      <c r="E52" s="18" t="n">
+      <c r="F52" s="18" t="n">
         <v>-399.4353198647671</v>
       </c>
-      <c r="F52" s="18" t="n">
+      <c r="G52" s="18" t="n">
         <v>-57.99406137520214</v>
       </c>
-      <c r="G52" s="18" t="n">
+      <c r="H52" s="18" t="n">
         <v>296.4469812494701</v>
       </c>
-      <c r="H52" s="18" t="n">
+      <c r="I52" s="18" t="n">
         <v>663.7578101678919</v>
       </c>
-      <c r="I52" s="18" t="n">
+      <c r="J52" s="18" t="n">
         <v>1771.555210785502</v>
       </c>
-      <c r="J52" s="18" t="n">
+      <c r="K52" s="18" t="n">
         <v>-16786.921557147</v>
       </c>
-      <c r="K52" s="18" t="n">
+      <c r="L52" s="18" t="n">
         <v>-10356.70876738495</v>
       </c>
-      <c r="L52" s="18" t="n">
+      <c r="M52" s="18" t="n">
         <v>-10298.78028927715</v>
       </c>
-      <c r="M52" s="18" t="n">
+      <c r="N52" s="18" t="n">
         <v>-10230.33598785992</v>
       </c>
-      <c r="N52" s="18" t="n">
+      <c r="O52" s="18" t="n">
         <v>-10151.48102136637</v>
-      </c>
-      <c r="O52" s="18" t="n">
-        <v>-8635.835178337573</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -3347,40 +3347,40 @@
         </is>
       </c>
       <c r="D53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="18" t="n">
         <v>-727.7454832683711</v>
       </c>
-      <c r="E53" s="18" t="n">
+      <c r="F53" s="18" t="n">
         <v>-399.4353198647671</v>
       </c>
-      <c r="F53" s="18" t="n">
+      <c r="G53" s="18" t="n">
         <v>-57.99406137520214</v>
       </c>
-      <c r="G53" s="18" t="n">
+      <c r="H53" s="18" t="n">
         <v>296.4469812494701</v>
       </c>
-      <c r="H53" s="18" t="n">
+      <c r="I53" s="18" t="n">
         <v>663.7578101678919</v>
       </c>
-      <c r="I53" s="18" t="n">
+      <c r="J53" s="18" t="n">
         <v>1771.555210785502</v>
       </c>
-      <c r="J53" s="18" t="n">
+      <c r="K53" s="18" t="n">
         <v>-16786.921557147</v>
       </c>
-      <c r="K53" s="18" t="n">
+      <c r="L53" s="18" t="n">
         <v>-10356.70876738495</v>
       </c>
-      <c r="L53" s="18" t="n">
+      <c r="M53" s="18" t="n">
         <v>-10298.78028927715</v>
       </c>
-      <c r="M53" s="18" t="n">
+      <c r="N53" s="18" t="n">
         <v>-10230.33598785992</v>
       </c>
-      <c r="N53" s="18" t="n">
+      <c r="O53" s="18" t="n">
         <v>-10151.48102136637</v>
-      </c>
-      <c r="O53" s="18" t="n">
-        <v>-8635.835178337573</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -3612,40 +3612,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>-655.8126099136847</v>
+        <v>71.93287335468639</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>-282.9318322536585</v>
+        <v>-611.2419956572626</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>1078.339704716999</v>
+        <v>9.152962959063387</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>2594.551841975823</v>
+        <v>927.0012907547534</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>4314.355006650122</v>
+        <v>2647.065764221266</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>6772.392193369831</v>
+        <v>4377.616163376893</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>-10434.27748387749</v>
+        <v>6850.090440973429</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>-3481.193828763027</v>
+        <v>-10339.378881855</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>16860.45805197252</v>
+        <v>-3371.163423910754</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>11195.33731094064</v>
+        <v>16970.75775771262</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>12751.10803522951</v>
+        <v>11300.42122182162</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>15277.79296901473</v>
+        <v>12803.06707155016</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -3665,40 +3665,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="18" t="n">
         <v>727.7454832683711</v>
       </c>
-      <c r="E59" s="18" t="n">
-        <v>2697.422860664767</v>
-      </c>
       <c r="F59" s="18" t="n">
+        <v>2697.422860664768</v>
+      </c>
+      <c r="G59" s="18" t="n">
         <v>3926.22365970683</v>
       </c>
-      <c r="G59" s="18" t="n">
+      <c r="H59" s="18" t="n">
         <v>4556.660649285761</v>
       </c>
-      <c r="H59" s="18" t="n">
-        <v>5187.358947656904</v>
-      </c>
       <c r="I59" s="18" t="n">
-        <v>5090.570458463964</v>
+        <v>5187.358947656905</v>
       </c>
       <c r="J59" s="18" t="n">
+        <v>5090.570458463965</v>
+      </c>
+      <c r="K59" s="18" t="n">
         <v>24629.20333614292</v>
       </c>
-      <c r="K59" s="18" t="n">
+      <c r="L59" s="18" t="n">
         <v>19208.07674191286</v>
       </c>
-      <c r="L59" s="18" t="n">
-        <v>418.4309896688319</v>
-      </c>
       <c r="M59" s="18" t="n">
-        <v>7598.196332726257</v>
+        <v>418.4309896688246</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>7590.099043821618</v>
+        <v>7598.196332726249</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>6639.673689383757</v>
+        <v>7590.099043821616</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -4572,34 +4572,34 @@
         <v>0</v>
       </c>
       <c r="F76" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="18" t="n">
         <v>2297.9875408</v>
       </c>
-      <c r="G76" s="18" t="n">
+      <c r="H76" s="18" t="n">
         <v>4595.9750816</v>
       </c>
-      <c r="H76" s="18" t="n">
-        <v>6893.962622399999</v>
-      </c>
       <c r="I76" s="18" t="n">
+        <v>6880.365105369025</v>
+      </c>
+      <c r="J76" s="18" t="n">
         <v>9178.352646169024</v>
       </c>
-      <c r="J76" s="18" t="n">
-        <v>11476.34018696902</v>
-      </c>
       <c r="K76" s="18" t="n">
-        <v>13756.96522451539</v>
+        <v>11461.48453303045</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>14927.48028473426</v>
+        <v>13730.66861094509</v>
       </c>
       <c r="M76" s="18" t="n">
+        <v>14921.95254081148</v>
+      </c>
+      <c r="N76" s="18" t="n">
         <v>16443.37051597052</v>
       </c>
-      <c r="N76" s="18" t="n">
+      <c r="O76" s="18" t="n">
         <v>17924.25600816054</v>
-      </c>
-      <c r="O76" s="18" t="n">
-        <v>19440.51339376026</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -4675,37 +4675,37 @@
         <v>0</v>
       </c>
       <c r="E78" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="18" t="n">
         <v>2297.9875408</v>
       </c>
-      <c r="F78" s="18" t="n">
+      <c r="G78" s="18" t="n">
         <v>4595.9750816</v>
       </c>
-      <c r="G78" s="18" t="n">
-        <v>6893.962622399999</v>
-      </c>
       <c r="H78" s="18" t="n">
+        <v>6880.365105369025</v>
+      </c>
+      <c r="I78" s="18" t="n">
         <v>9178.352646169024</v>
       </c>
-      <c r="I78" s="18" t="n">
-        <v>11476.34018696902</v>
-      </c>
       <c r="J78" s="18" t="n">
-        <v>13756.96522451539</v>
+        <v>11461.48453303045</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>14927.48028473426</v>
+        <v>13730.66861094509</v>
       </c>
       <c r="L78" s="18" t="n">
+        <v>14921.95254081148</v>
+      </c>
+      <c r="M78" s="18" t="n">
         <v>16443.37051597052</v>
       </c>
-      <c r="M78" s="18" t="n">
+      <c r="N78" s="18" t="n">
         <v>17924.25600816054</v>
       </c>
-      <c r="N78" s="18" t="n">
+      <c r="O78" s="18" t="n">
         <v>19440.51339376026</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>21035.63795389164</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -4905,19 +4905,19 @@
         <v>377.9752415799667</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>427.6745349631409</v>
+        <v>468.8902736200481</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>786.7461088895443</v>
+        <v>546.4993238167979</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>820.8560689793743</v>
+        <v>900.2983204991639</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>852.6478332128239</v>
+        <v>929.1884291173966</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>882.1446792975107</v>
+        <v>955.8125403939653</v>
       </c>
     </row>
     <row r="83" ht="15.5" customHeight="1">
@@ -5061,22 +5061,22 @@
         <v>377.9752415799667</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>427.6745349631409</v>
+        <v>468.8902736200481</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>786.7461088895443</v>
+        <v>546.4993238167979</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>820.8560689793743</v>
+        <v>900.2983204991639</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>852.6478332128239</v>
+        <v>929.1884291173966</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>882.1446792975107</v>
+        <v>955.8125403939653</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>860.7048705459894</v>
+        <v>931.5288876506644</v>
       </c>
     </row>
     <row r="86" ht="15.5" customHeight="1">
@@ -5656,34 +5656,34 @@
         <v>433.7685840977465</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>1834.55789895781</v>
+        <v>450.2445468894396</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>7206.625438511972</v>
+        <v>5236.948061115576</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>9615.473703558198</v>
+        <v>7658.927421247764</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>11613.19531703036</v>
+        <v>9669.64881885503</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>13613.27317014221</v>
+        <v>11682.59645826064</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>14447.71184333254</v>
+        <v>13692.61028724789</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>35135.64833749675</v>
+        <v>14544.98087209417</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>26932.27952490632</v>
+        <v>35247.68467951445</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>28042.55237409545</v>
+        <v>27072.99975384793</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>29618.87697027507</v>
+        <v>28216.66322290651</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -5865,37 +5865,37 @@
         <v>433.7685840977465</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>1834.55789895781</v>
+        <v>450.2445468894396</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>7206.625438511972</v>
+        <v>5236.948061115576</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>9615.473703558198</v>
+        <v>7658.927421247764</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>11613.19531703036</v>
+        <v>9669.64881885503</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>13613.27317014221</v>
+        <v>11682.59645826064</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>14447.71184333254</v>
+        <v>13692.61028724789</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>35135.64833749675</v>
+        <v>14544.98087209417</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>26932.27952490632</v>
+        <v>35247.68467951445</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>28042.55237409545</v>
+        <v>27072.99975384793</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>29618.87697027507</v>
+        <v>28216.66322290651</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>31272.60268834075</v>
+        <v>29887.18635296807</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -5968,40 +5968,40 @@
         </is>
       </c>
       <c r="D102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O102" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" ht="15.5" customHeight="1">
@@ -6024,37 +6024,37 @@
         <v>0</v>
       </c>
       <c r="E103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="18" t="n">
         <v>-727.7454832683711</v>
       </c>
-      <c r="F103" s="18" t="n">
+      <c r="G103" s="18" t="n">
         <v>-399.4353198647671</v>
       </c>
-      <c r="G103" s="18" t="n">
+      <c r="H103" s="18" t="n">
         <v>-57.99406137520214</v>
       </c>
-      <c r="H103" s="18" t="n">
+      <c r="I103" s="18" t="n">
         <v>296.4469812494701</v>
       </c>
-      <c r="I103" s="18" t="n">
+      <c r="J103" s="18" t="n">
         <v>663.7578101678919</v>
       </c>
-      <c r="J103" s="18" t="n">
+      <c r="K103" s="18" t="n">
         <v>1771.555210785502</v>
       </c>
-      <c r="K103" s="18" t="n">
+      <c r="L103" s="18" t="n">
         <v>-16786.921557147</v>
       </c>
-      <c r="L103" s="18" t="n">
+      <c r="M103" s="18" t="n">
         <v>-10356.70876738495</v>
       </c>
-      <c r="M103" s="18" t="n">
+      <c r="N103" s="18" t="n">
         <v>-10298.78028927715</v>
       </c>
-      <c r="N103" s="18" t="n">
+      <c r="O103" s="18" t="n">
         <v>-10230.33598785992</v>
-      </c>
-      <c r="O103" s="18" t="n">
-        <v>-10151.48102136637</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -6127,40 +6127,40 @@
         </is>
       </c>
       <c r="D105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O105" s="18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" ht="15.5" customHeight="1">
@@ -6233,40 +6233,40 @@
         </is>
       </c>
       <c r="D107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="18" t="n">
         <v>-727.7454832683711</v>
       </c>
-      <c r="E107" s="18" t="n">
+      <c r="F107" s="18" t="n">
         <v>-399.4353198647671</v>
       </c>
-      <c r="F107" s="18" t="n">
+      <c r="G107" s="18" t="n">
         <v>-57.99406137520214</v>
       </c>
-      <c r="G107" s="18" t="n">
+      <c r="H107" s="18" t="n">
         <v>296.4469812494701</v>
       </c>
-      <c r="H107" s="18" t="n">
+      <c r="I107" s="18" t="n">
         <v>663.7578101678919</v>
       </c>
-      <c r="I107" s="18" t="n">
+      <c r="J107" s="18" t="n">
         <v>1771.555210785502</v>
       </c>
-      <c r="J107" s="18" t="n">
+      <c r="K107" s="18" t="n">
         <v>-16786.921557147</v>
       </c>
-      <c r="K107" s="18" t="n">
+      <c r="L107" s="18" t="n">
         <v>-10356.70876738495</v>
       </c>
-      <c r="L107" s="18" t="n">
+      <c r="M107" s="18" t="n">
         <v>-10298.78028927715</v>
       </c>
-      <c r="M107" s="18" t="n">
+      <c r="N107" s="18" t="n">
         <v>-10230.33598785992</v>
       </c>
-      <c r="N107" s="18" t="n">
+      <c r="O107" s="18" t="n">
         <v>-10151.48102136637</v>
-      </c>
-      <c r="O107" s="18" t="n">
-        <v>-8635.835178337573</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -8763,19 +8763,19 @@
         <v>2235.34280800426</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>2333.418320356867</v>
+        <v>2581.38007882974</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>2670.328871762653</v>
+        <v>2663.031069422604</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>2990.976933649055</v>
+        <v>2983.683012286244</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>3295.530488794742</v>
+        <v>3288.233015313682</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>3459.811679300637</v>
+        <v>3452.522549222511</v>
       </c>
     </row>
     <row r="42" ht="15.5" customHeight="1">
@@ -8816,19 +8816,19 @@
         <v>2235.34280800426</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>2333.418320356867</v>
+        <v>2581.38007882974</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>2670.328871762653</v>
+        <v>2663.031069422604</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>2990.976933649055</v>
+        <v>2983.683012286244</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>3295.530488794742</v>
+        <v>3288.233015313682</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>3459.811679300637</v>
+        <v>3452.522549222511</v>
       </c>
     </row>
     <row r="43" ht="15.5" customHeight="1">
@@ -8854,34 +8854,34 @@
         <v>42.6934018010603</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>4653.879272306851</v>
+        <v>2355.89173150685</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>4649.08648981918</v>
+        <v>2351.098949019179</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>6953.897131989042</v>
+        <v>4655.909591189042</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>9258.615949501373</v>
+        <v>6960.628408701372</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>11563.19737523288</v>
+        <v>9265.209834432881</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>13870.29089411507</v>
+        <v>11572.30335331507</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>16067.59496844874</v>
+        <v>13879.31632425206</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>18208.9151608098</v>
+        <v>16076.34252461312</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>20363.96004849405</v>
+        <v>18217.34889229737</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>22551.71082553193</v>
+        <v>20377.47462933524</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -8907,34 +8907,34 @@
         <v>0</v>
       </c>
       <c r="F44" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="18" t="n">
         <v>2297.987540800001</v>
       </c>
-      <c r="G44" s="18" t="n">
+      <c r="H44" s="18" t="n">
         <v>4595.975081600001</v>
       </c>
-      <c r="H44" s="18" t="n">
+      <c r="I44" s="18" t="n">
         <v>6893.962622400002</v>
       </c>
-      <c r="I44" s="18" t="n">
+      <c r="J44" s="18" t="n">
         <v>9191.950163200003</v>
       </c>
-      <c r="J44" s="18" t="n">
+      <c r="K44" s="18" t="n">
         <v>11489.937704</v>
       </c>
-      <c r="K44" s="18" t="n">
+      <c r="L44" s="18" t="n">
         <v>13787.9252448</v>
       </c>
-      <c r="L44" s="18" t="n">
+      <c r="M44" s="18" t="n">
         <v>15976.20388899668</v>
       </c>
-      <c r="M44" s="18" t="n">
+      <c r="N44" s="18" t="n">
         <v>18108.77652519336</v>
       </c>
-      <c r="N44" s="18" t="n">
+      <c r="O44" s="18" t="n">
         <v>20255.38768139004</v>
-      </c>
-      <c r="O44" s="18" t="n">
-        <v>22429.62387758672</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -9066,34 +9066,34 @@
         <v>685.2818150767414</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>5636.27176421972</v>
+        <v>3338.28422341972</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>5956.506022536704</v>
+        <v>3658.518481736704</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>8571.719306057012</v>
+        <v>6273.731765257012</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>11172.35777346012</v>
+        <v>8874.370232660121</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>13798.54018323714</v>
+        <v>11500.55264243714</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>16203.70921447194</v>
+        <v>14153.68343214481</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>18737.92384021139</v>
+        <v>16542.34739367466</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>21199.89209445885</v>
+        <v>19060.02553689936</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>23659.4905372888</v>
+        <v>21505.58190761106</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>26011.52250483256</v>
+        <v>23829.99717855775</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -9122,31 +9122,31 @@
         <v>5633.064820679988</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>2638.013385987701</v>
+        <v>1347.836420388751</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>4583.739215349417</v>
+        <v>2953.840224598421</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>6498.634351022921</v>
+        <v>4885.020004966224</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>8422.959484692539</v>
+        <v>6825.488672054733</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>10358.85044359882</v>
+        <v>8777.339993874184</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>7299.752196075559</v>
+        <v>10697.15163650017</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>12855.5735766737</v>
+        <v>7621.526769475863</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>10348.662435557</v>
+        <v>13160.94430487512</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>16928.25412600293</v>
+        <v>10518.85857273565</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -9281,31 +9281,31 @@
         <v>675.4747894805378</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>6923.241786278937</v>
+        <v>5633.064820679988</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>4267.912376738697</v>
+        <v>2638.013385987701</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>6197.353561406114</v>
+        <v>4583.739215349417</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>8096.105163660727</v>
+        <v>6498.634351022921</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>10004.46993441717</v>
+        <v>8422.959484692539</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>6961.451003174207</v>
+        <v>10358.85044359881</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>12533.79900327339</v>
+        <v>7299.752196075559</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>10043.29170735558</v>
+        <v>12855.57357667369</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>16758.05798882428</v>
+        <v>10348.662435557</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -9328,37 +9328,37 @@
         <v>0</v>
       </c>
       <c r="E52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="18" t="n">
         <v>-1290.176965598953</v>
       </c>
-      <c r="F52" s="18" t="n">
+      <c r="G52" s="18" t="n">
         <v>-1278.65628434995</v>
       </c>
-      <c r="G52" s="18" t="n">
+      <c r="H52" s="18" t="n">
         <v>-1250.850958406641</v>
       </c>
-      <c r="H52" s="18" t="n">
+      <c r="I52" s="18" t="n">
         <v>-1206.902099044447</v>
       </c>
-      <c r="I52" s="18" t="n">
+      <c r="J52" s="18" t="n">
         <v>-1146.99287676908</v>
       </c>
-      <c r="J52" s="18" t="n">
+      <c r="K52" s="18" t="n">
         <v>27.56010391590189</v>
       </c>
-      <c r="K52" s="18" t="n">
+      <c r="L52" s="18" t="n">
         <v>-162.300607879974</v>
       </c>
-      <c r="L52" s="18" t="n">
+      <c r="M52" s="18" t="n">
         <v>-506.8604250494029</v>
       </c>
-      <c r="M52" s="18" t="n">
+      <c r="N52" s="18" t="n">
         <v>-831.0141990278089</v>
       </c>
-      <c r="N52" s="18" t="n">
+      <c r="O52" s="18" t="n">
         <v>-1134.919330769903</v>
-      </c>
-      <c r="O52" s="18" t="n">
-        <v>-1418.804158241069</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -9381,37 +9381,37 @@
         <v>0</v>
       </c>
       <c r="E53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="18" t="n">
         <v>-1290.176965598953</v>
       </c>
-      <c r="F53" s="18" t="n">
+      <c r="G53" s="18" t="n">
         <v>-1278.65628434995</v>
       </c>
-      <c r="G53" s="18" t="n">
+      <c r="H53" s="18" t="n">
         <v>-1250.850958406641</v>
       </c>
-      <c r="H53" s="18" t="n">
+      <c r="I53" s="18" t="n">
         <v>-1206.902099044447</v>
       </c>
-      <c r="I53" s="18" t="n">
+      <c r="J53" s="18" t="n">
         <v>-1146.99287676908</v>
       </c>
-      <c r="J53" s="18" t="n">
+      <c r="K53" s="18" t="n">
         <v>27.56010391590189</v>
       </c>
-      <c r="K53" s="18" t="n">
+      <c r="L53" s="18" t="n">
         <v>-162.300607879974</v>
       </c>
-      <c r="L53" s="18" t="n">
+      <c r="M53" s="18" t="n">
         <v>-506.8604250494029</v>
       </c>
-      <c r="M53" s="18" t="n">
+      <c r="N53" s="18" t="n">
         <v>-831.0141990278089</v>
       </c>
-      <c r="N53" s="18" t="n">
+      <c r="O53" s="18" t="n">
         <v>-1134.919330769903</v>
-      </c>
-      <c r="O53" s="18" t="n">
-        <v>-1418.804158241069</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -9646,37 +9646,37 @@
         <v>2096.015202249106</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>-631.1453642208451</v>
+        <v>659.031601378108</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>2029.072371946476</v>
+        <v>2017.551690697473</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>1366.953983745443</v>
+        <v>48.97169220318482</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>3353.916573839217</v>
+        <v>1680.068723726026</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>5326.040361925074</v>
+        <v>3652.51679359301</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>8422.291807786522</v>
+        <v>5650.268014463735</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>10164.15043571884</v>
+        <v>8772.500697790087</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>6756.148149108349</v>
+        <v>10498.10740670239</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>11983.60553928972</v>
+        <v>7073.712506070297</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>9168.731943162536</v>
+        <v>12284.91894422275</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>15457.83676776186</v>
+        <v>9332.326041965745</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -9699,37 +9699,37 @@
         <v>22.70909589041412</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>1316.427179297586</v>
+        <v>26.25021369863339</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>3607.199392273244</v>
+        <v>1320.732532722247</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>4589.552038791261</v>
+        <v>3609.546789533519</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>5217.802732217795</v>
+        <v>4593.663041530986</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>5846.317411535048</v>
+        <v>5221.853439067111</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>5376.248375450617</v>
+        <v>5850.284627973407</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>6039.558778753093</v>
+        <v>5381.182734354721</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>11981.77569110304</v>
+        <v>6044.239986972274</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>9216.286555169127</v>
+        <v>11986.31303082907</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>14490.75859412626</v>
+        <v>9220.662963388311</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>10553.6857370707</v>
+        <v>14497.67113659201</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -10606,31 +10606,31 @@
         <v>0</v>
       </c>
       <c r="G76" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="18" t="n">
         <v>2297.987540800001</v>
       </c>
-      <c r="H76" s="18" t="n">
+      <c r="I76" s="18" t="n">
         <v>4595.975081600001</v>
       </c>
-      <c r="I76" s="18" t="n">
+      <c r="J76" s="18" t="n">
         <v>6893.962622400002</v>
       </c>
-      <c r="J76" s="18" t="n">
+      <c r="K76" s="18" t="n">
         <v>9191.950163200003</v>
       </c>
-      <c r="K76" s="18" t="n">
+      <c r="L76" s="18" t="n">
         <v>11489.937704</v>
       </c>
-      <c r="L76" s="18" t="n">
+      <c r="M76" s="18" t="n">
         <v>13787.9252448</v>
       </c>
-      <c r="M76" s="18" t="n">
+      <c r="N76" s="18" t="n">
         <v>15976.20388899668</v>
       </c>
-      <c r="N76" s="18" t="n">
+      <c r="O76" s="18" t="n">
         <v>18108.77652519336</v>
-      </c>
-      <c r="O76" s="18" t="n">
-        <v>20255.38768139004</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -10709,34 +10709,34 @@
         <v>0</v>
       </c>
       <c r="F78" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="18" t="n">
         <v>2297.987540800001</v>
       </c>
-      <c r="G78" s="18" t="n">
+      <c r="H78" s="18" t="n">
         <v>4595.975081600001</v>
       </c>
-      <c r="H78" s="18" t="n">
+      <c r="I78" s="18" t="n">
         <v>6893.962622400002</v>
       </c>
-      <c r="I78" s="18" t="n">
+      <c r="J78" s="18" t="n">
         <v>9191.950163200003</v>
       </c>
-      <c r="J78" s="18" t="n">
+      <c r="K78" s="18" t="n">
         <v>11489.937704</v>
       </c>
-      <c r="K78" s="18" t="n">
+      <c r="L78" s="18" t="n">
         <v>13787.9252448</v>
       </c>
-      <c r="L78" s="18" t="n">
+      <c r="M78" s="18" t="n">
         <v>15976.20388899668</v>
       </c>
-      <c r="M78" s="18" t="n">
+      <c r="N78" s="18" t="n">
         <v>18108.77652519336</v>
       </c>
-      <c r="N78" s="18" t="n">
+      <c r="O78" s="18" t="n">
         <v>20255.38768139004</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>22429.62387758672</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -10939,16 +10939,16 @@
         <v>2235.34280800426</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>2333.418320356867</v>
+        <v>2581.38007882974</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>2670.328871762653</v>
+        <v>2663.031069422604</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>2990.976933649055</v>
+        <v>2983.683012286244</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>3295.530488794742</v>
+        <v>3288.233015313682</v>
       </c>
     </row>
     <row r="83" ht="15.5" customHeight="1">
@@ -11095,19 +11095,19 @@
         <v>2235.34280800426</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>2333.418320356867</v>
+        <v>2581.38007882974</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>2670.328871762653</v>
+        <v>2663.031069422604</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>2990.976933649055</v>
+        <v>2983.683012286244</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>3295.530488794742</v>
+        <v>3288.233015313682</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>3459.811679300637</v>
+        <v>3452.522549222511</v>
       </c>
     </row>
     <row r="86" ht="15.5" customHeight="1">
@@ -11690,31 +11690,31 @@
         <v>32064.3369271294</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>70256.73964876666</v>
+        <v>68309.99481436772</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>77668.98402070782</v>
+        <v>75382.51716115681</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>80564.05590645724</v>
+        <v>78293.87369160056</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>83556.29956954819</v>
+        <v>81302.26088811038</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>86602.45626049463</v>
+        <v>84364.37794196999</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>60777.46405980636</v>
+        <v>87520.64683999791</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>60608.06570668557</v>
+        <v>61848.35872108494</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>28406.11595012907</v>
+        <v>61827.54338400126</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>27446.18090387545</v>
+        <v>29768.86897180479</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -11899,34 +11899,34 @@
         <v>32064.3369271294</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>70256.73964876666</v>
+        <v>68309.99481436772</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>77668.98402070782</v>
+        <v>75382.51716115681</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>80564.05590645724</v>
+        <v>78293.87369160056</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>83556.29956954819</v>
+        <v>81302.26088811038</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>86602.45626049463</v>
+        <v>84364.37794196999</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>60777.46405980636</v>
+        <v>87520.64683999791</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>60608.06570668557</v>
+        <v>61848.35872108494</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>28406.11595012907</v>
+        <v>61827.54338400126</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>27446.18090387545</v>
+        <v>29768.86897180479</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>31254.51742733913</v>
+        <v>29162.96119886453</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -12058,34 +12058,34 @@
         <v>0</v>
       </c>
       <c r="F103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="18" t="n">
         <v>-1290.176965598953</v>
       </c>
-      <c r="G103" s="18" t="n">
+      <c r="H103" s="18" t="n">
         <v>-1278.65628434995</v>
       </c>
-      <c r="H103" s="18" t="n">
+      <c r="I103" s="18" t="n">
         <v>-1250.850958406641</v>
       </c>
-      <c r="I103" s="18" t="n">
+      <c r="J103" s="18" t="n">
         <v>-1206.902099044447</v>
       </c>
-      <c r="J103" s="18" t="n">
+      <c r="K103" s="18" t="n">
         <v>-1146.99287676908</v>
       </c>
-      <c r="K103" s="18" t="n">
+      <c r="L103" s="18" t="n">
         <v>27.56010391590189</v>
       </c>
-      <c r="L103" s="18" t="n">
+      <c r="M103" s="18" t="n">
         <v>-162.300607879974</v>
       </c>
-      <c r="M103" s="18" t="n">
+      <c r="N103" s="18" t="n">
         <v>-506.8604250494029</v>
       </c>
-      <c r="N103" s="18" t="n">
+      <c r="O103" s="18" t="n">
         <v>-831.0141990278089</v>
-      </c>
-      <c r="O103" s="18" t="n">
-        <v>-1134.919330769903</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -12267,37 +12267,37 @@
         <v>0</v>
       </c>
       <c r="E107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="18" t="n">
         <v>-1290.176965598953</v>
       </c>
-      <c r="F107" s="18" t="n">
+      <c r="G107" s="18" t="n">
         <v>-1278.65628434995</v>
       </c>
-      <c r="G107" s="18" t="n">
+      <c r="H107" s="18" t="n">
         <v>-1250.850958406641</v>
       </c>
-      <c r="H107" s="18" t="n">
+      <c r="I107" s="18" t="n">
         <v>-1206.902099044447</v>
       </c>
-      <c r="I107" s="18" t="n">
+      <c r="J107" s="18" t="n">
         <v>-1146.99287676908</v>
       </c>
-      <c r="J107" s="18" t="n">
+      <c r="K107" s="18" t="n">
         <v>27.56010391590189</v>
       </c>
-      <c r="K107" s="18" t="n">
+      <c r="L107" s="18" t="n">
         <v>-162.300607879974</v>
       </c>
-      <c r="L107" s="18" t="n">
+      <c r="M107" s="18" t="n">
         <v>-506.8604250494029</v>
       </c>
-      <c r="M107" s="18" t="n">
+      <c r="N107" s="18" t="n">
         <v>-831.0141990278089</v>
       </c>
-      <c r="N107" s="18" t="n">
+      <c r="O107" s="18" t="n">
         <v>-1134.919330769903</v>
-      </c>
-      <c r="O107" s="18" t="n">
-        <v>-1418.804158241069</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -15150,10 +15150,10 @@
         <v>5.104424374156288</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>8.056340429786157</v>
+        <v>8.056340429786161</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>11.41773686142088</v>
+        <v>11.41773686142101</v>
       </c>
       <c r="H48" s="18" t="n">
         <v>13.57606858255659</v>
@@ -15168,7 +15168,7 @@
         <v>21.21822690050123</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>20.65884142905179</v>
+        <v>20.65884142905181</v>
       </c>
       <c r="M48" s="18" t="n">
         <v>21.4393944371938</v>
@@ -15177,7 +15177,7 @@
         <v>20.47513321843181</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>20.73913520283466</v>
+        <v>20.73913520283469</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -15309,10 +15309,10 @@
         <v>2.291152682690086</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>5.104424374156284</v>
+        <v>5.104424374156288</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>8.056340429786026</v>
+        <v>8.056340429786157</v>
       </c>
       <c r="H51" s="18" t="n">
         <v>11.41773686142088</v>
@@ -15327,7 +15327,7 @@
         <v>16.82587827879169</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>21.21822690050121</v>
+        <v>21.21822690050123</v>
       </c>
       <c r="M51" s="18" t="n">
         <v>20.65884142905179</v>
@@ -15336,7 +15336,7 @@
         <v>21.4393944371938</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>20.4751332184318</v>
+        <v>20.47513321843182</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -15680,10 +15680,10 @@
         <v>5.945813210737497</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>9.394416556559062</v>
+        <v>9.394416556559065</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>12.87936391270747</v>
+        <v>12.8793639127076</v>
       </c>
       <c r="H58" s="18" t="n">
         <v>15.59517442269535</v>
@@ -15698,7 +15698,7 @@
         <v>21.93274718513492</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>21.78139151426158</v>
+        <v>21.7813915142616</v>
       </c>
       <c r="M58" s="18" t="n">
         <v>22.20819432968727</v>
@@ -15707,7 +15707,7 @@
         <v>21.67117820440262</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>21.63475059541897</v>
+        <v>21.63475059541899</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -15733,10 +15733,10 @@
         <v>2.147578652054793</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>2.884258592876716</v>
+        <v>2.884258592876712</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>3.989147340822061</v>
+        <v>3.98914734082193</v>
       </c>
       <c r="H59" s="18" t="n">
         <v>4.655254879726172</v>
@@ -15751,7 +15751,7 @@
         <v>8.774081534794671</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>8.583901296164555</v>
+        <v>8.583901296164534</v>
       </c>
       <c r="M59" s="18" t="n">
         <v>9.154841000548092</v>
@@ -15760,7 +15760,7 @@
         <v>8.944136186301527</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>9.460467493972772</v>
+        <v>9.46046749397275</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -17718,34 +17718,34 @@
         <v>28.63499536848203</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>99.80486527661515</v>
+        <v>46.10838492845514</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>9467.376180477626</v>
+        <v>120.2419698024263</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>9593.184480557846</v>
+        <v>9503.173980520645</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>9741.710957862753</v>
+        <v>9631.052010628353</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>9943.636880541706</v>
+        <v>9797.281874129625</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>10165.05239837964</v>
+        <v>10000.03467522516</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>10483.29462442817</v>
+        <v>10291.04280007841</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>10855.91608975582</v>
+        <v>10603.67241264335</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>11250.16952585752</v>
+        <v>10990.40506554231</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>11641.8157646981</v>
+        <v>11375.16271087514</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -17927,37 +17927,37 @@
         <v>28.63499536848203</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>99.80486527661515</v>
+        <v>46.10838492845514</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>9467.376180477626</v>
+        <v>120.2419698024263</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>9593.184480557846</v>
+        <v>9503.173980520645</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>9741.710957862753</v>
+        <v>9631.052010628353</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>9943.636880541706</v>
+        <v>9797.281874129625</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>10165.05239837964</v>
+        <v>10000.03467522516</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>10483.29462442817</v>
+        <v>10291.04280007841</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>10855.91608975582</v>
+        <v>10603.67241264335</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>11250.16952585752</v>
+        <v>10990.40506554231</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>11641.8157646981</v>
+        <v>11375.16271087514</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>12052.11672455091</v>
+        <v>11779.19535296211</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -20825,19 +20825,19 @@
         <v>1766.452534384212</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>1786.918996540068</v>
+        <v>1993.665016356035</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>1770.030551263489</v>
+        <v>2002.979533996185</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>2061.788504531658</v>
+        <v>1975.052331649058</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>2339.717948400777</v>
+        <v>2255.879879015144</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>2528.282791649973</v>
+        <v>2447.325800475393</v>
       </c>
     </row>
     <row r="42">
@@ -20878,19 +20878,19 @@
         <v>1766.452534384212</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>1786.918996540068</v>
+        <v>1993.665016356035</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>1770.030551263489</v>
+        <v>2002.979533996185</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>2061.788504531658</v>
+        <v>1975.052331649058</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>2339.717948400777</v>
+        <v>2255.879879015144</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>2528.282791649973</v>
+        <v>2447.325800475393</v>
       </c>
     </row>
     <row r="43">
@@ -20934,16 +20934,16 @@
         <v>64.73609202675598</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>924.7801340349087</v>
+        <v>69.80570543555764</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>1784.621595696946</v>
+        <v>929.6471670975955</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>2644.243659170675</v>
+        <v>1789.269230571323</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>3507.633497876217</v>
+        <v>2652.659069276866</v>
       </c>
     </row>
     <row r="44">
@@ -20987,16 +20987,16 @@
         <v>0</v>
       </c>
       <c r="L44" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="18" t="n">
         <v>854.9744285993511</v>
       </c>
-      <c r="M44" s="18" t="n">
+      <c r="N44" s="18" t="n">
         <v>1709.948857198702</v>
       </c>
-      <c r="N44" s="18" t="n">
+      <c r="O44" s="18" t="n">
         <v>2564.923285798053</v>
-      </c>
-      <c r="O44" s="18" t="n">
-        <v>3419.897714397404</v>
       </c>
     </row>
     <row r="45">
@@ -21143,19 +21143,19 @@
         <v>1826.265706300496</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>1851.655088566824</v>
+        <v>2058.401108382791</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>2694.810685298398</v>
+        <v>2072.785239431743</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>3846.410100228605</v>
+        <v>2904.699498746653</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>4983.961607571451</v>
+        <v>4045.149109586468</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>6035.91628952619</v>
+        <v>5099.984869752259</v>
       </c>
     </row>
     <row r="48">
@@ -21199,16 +21199,16 @@
         <v>2043.395419655636</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>-1498.072029484937</v>
+        <v>2264.207270086744</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>2077.393187096419</v>
+        <v>-1288.492283290204</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>-1719.651941391034</v>
+        <v>2275.830548432321</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>3313.662490482477</v>
+        <v>-1603.922354900547</v>
       </c>
     </row>
     <row r="49">
@@ -21358,16 +21358,16 @@
         <v>1811.836825463852</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>-1718.883879916045</v>
+        <v>2043.395419655636</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>1867.813440901686</v>
+        <v>-1498.072029484937</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>-1918.089302726937</v>
+        <v>2077.393187096419</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>3197.932903991988</v>
+        <v>-1719.651941391035</v>
       </c>
     </row>
     <row r="52">
@@ -21408,19 +21408,19 @@
         <v>0</v>
       </c>
       <c r="K52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="18" t="n">
         <v>-74.11679431732691</v>
       </c>
-      <c r="L52" s="18" t="n">
+      <c r="M52" s="18" t="n">
         <v>420.309520466836</v>
       </c>
-      <c r="M52" s="18" t="n">
+      <c r="N52" s="18" t="n">
         <v>345.7993353962562</v>
       </c>
-      <c r="N52" s="18" t="n">
+      <c r="O52" s="18" t="n">
         <v>277.9086329187738</v>
-      </c>
-      <c r="O52" s="18" t="n">
-        <v>216.5838862209679</v>
       </c>
     </row>
     <row r="53">
@@ -21461,19 +21461,19 @@
         <v>0</v>
       </c>
       <c r="K53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="18" t="n">
         <v>-74.11679431732691</v>
       </c>
-      <c r="L53" s="18" t="n">
+      <c r="M53" s="18" t="n">
         <v>420.309520466836</v>
       </c>
-      <c r="M53" s="18" t="n">
+      <c r="N53" s="18" t="n">
         <v>345.7993353962562</v>
       </c>
-      <c r="N53" s="18" t="n">
+      <c r="O53" s="18" t="n">
         <v>277.9086329187738</v>
-      </c>
-      <c r="O53" s="18" t="n">
-        <v>216.5838862209679</v>
       </c>
     </row>
     <row r="54">
@@ -21726,19 +21726,19 @@
         <v>1789.144679924031</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>1944.413423688509</v>
+        <v>2018.530218005836</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>-1105.003367155397</v>
+        <v>2162.849617632121</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>2393.672681450797</v>
+        <v>-897.7026038652465</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>-1473.436142940347</v>
+        <v>2589.937049360491</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>3494.492675027422</v>
+        <v>-1361.767423657796</v>
       </c>
     </row>
     <row r="59">
@@ -21779,19 +21779,19 @@
         <v>37.1210263764649</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>-92.75833512168492</v>
+        <v>39.87089037695523</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>3799.814052453795</v>
+        <v>-90.06437820037809</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>1452.737418777808</v>
+        <v>3802.4021026119</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>6457.397750511798</v>
+        <v>1455.212060225977</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>2541.423614498768</v>
+        <v>6461.752293410055</v>
       </c>
     </row>
     <row r="60">
@@ -22686,13 +22686,13 @@
         <v>0</v>
       </c>
       <c r="M76" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="18" t="n">
         <v>854.9744285993511</v>
       </c>
-      <c r="N76" s="18" t="n">
+      <c r="O76" s="18" t="n">
         <v>1709.948857198702</v>
-      </c>
-      <c r="O76" s="18" t="n">
-        <v>2564.923285798053</v>
       </c>
     </row>
     <row r="77">
@@ -22789,16 +22789,16 @@
         <v>0</v>
       </c>
       <c r="L78" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="18" t="n">
         <v>854.9744285993511</v>
       </c>
-      <c r="M78" s="18" t="n">
+      <c r="N78" s="18" t="n">
         <v>1709.948857198702</v>
       </c>
-      <c r="N78" s="18" t="n">
+      <c r="O78" s="18" t="n">
         <v>2564.923285798053</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>3419.897714397404</v>
       </c>
     </row>
     <row r="79">
@@ -23001,16 +23001,16 @@
         <v>1766.452534384212</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>1786.918996540068</v>
+        <v>1993.665016356035</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>1770.030551263489</v>
+        <v>2002.979533996185</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>2061.788504531658</v>
+        <v>1975.052331649058</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>2339.717948400777</v>
+        <v>2255.879879015144</v>
       </c>
     </row>
     <row r="83">
@@ -23157,19 +23157,19 @@
         <v>1766.452534384212</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>1786.918996540068</v>
+        <v>1993.665016356035</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>1770.030551263489</v>
+        <v>2002.979533996185</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>2061.788504531658</v>
+        <v>1975.052331649058</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>2339.717948400777</v>
+        <v>2255.879879015144</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>2528.282791649973</v>
+        <v>2447.325800475393</v>
       </c>
     </row>
     <row r="86">
@@ -23767,16 +23767,16 @@
         <v>70954.9529217129</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>1654450.493356884</v>
+        <v>71723.14327151733</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>3277819.21466039</v>
+        <v>1655304.099531629</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>4892542.257677892</v>
+        <v>3278755.383447527</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>6545617.765946605</v>
+        <v>4893557.271649791</v>
       </c>
     </row>
     <row r="97">
@@ -23976,19 +23976,19 @@
         <v>70954.9529217129</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>1654450.493356884</v>
+        <v>71723.14327151733</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>3277819.21466039</v>
+        <v>1655304.099531629</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>4892542.257677892</v>
+        <v>3278755.383447527</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>6545617.765946605</v>
+        <v>4893557.271649791</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>8202935.558616287</v>
+        <v>6546850.625414385</v>
       </c>
     </row>
     <row r="101">
@@ -24138,16 +24138,16 @@
         <v>0</v>
       </c>
       <c r="L103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="18" t="n">
         <v>-74.11679431732691</v>
       </c>
-      <c r="M103" s="18" t="n">
+      <c r="N103" s="18" t="n">
         <v>420.309520466836</v>
       </c>
-      <c r="N103" s="18" t="n">
+      <c r="O103" s="18" t="n">
         <v>345.7993353962562</v>
-      </c>
-      <c r="O103" s="18" t="n">
-        <v>277.9086329187738</v>
       </c>
     </row>
     <row r="104">
@@ -24347,19 +24347,19 @@
         <v>0</v>
       </c>
       <c r="K107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="18" t="n">
         <v>-74.11679431732691</v>
       </c>
-      <c r="L107" s="18" t="n">
+      <c r="M107" s="18" t="n">
         <v>420.309520466836</v>
       </c>
-      <c r="M107" s="18" t="n">
+      <c r="N107" s="18" t="n">
         <v>345.7993353962562</v>
       </c>
-      <c r="N107" s="18" t="n">
+      <c r="O107" s="18" t="n">
         <v>277.9086329187738</v>
-      </c>
-      <c r="O107" s="18" t="n">
-        <v>216.5838862209679</v>
       </c>
     </row>
     <row r="108">

--- a/backend/Rwanda/financial-statements-CleanStep.xlsx
+++ b/backend/Rwanda/financial-statements-CleanStep.xlsx
@@ -1174,40 +1174,40 @@
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>374.9373664305385</v>
+        <v>3.229387589725505</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>29.34186820325215</v>
+        <v>10.07214374539899</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>2730.80708687385</v>
+        <v>16.86645956936991</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>72.57172735927247</v>
+        <v>23.5458759464974</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>94.90523102427369</v>
+        <v>30.11201143413581</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>117.1399892899926</v>
+        <v>36.56646370843731</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>140.1044840564599</v>
+        <v>43.85563830344378</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>172.8794351866234</v>
+        <v>50.05256810624567</v>
       </c>
       <c r="L12" s="18" t="n">
-        <v>201.1804155786651</v>
+        <v>54.17532437418072</v>
       </c>
       <c r="M12" s="18" t="n">
-        <v>228.9729111677146</v>
+        <v>58.25146355350148</v>
       </c>
       <c r="N12" s="18" t="n">
-        <v>256.14111570518</v>
+        <v>62.28150571035337</v>
       </c>
       <c r="O12" s="18" t="n">
-        <v>289.816593754941</v>
+        <v>64.83465568889523</v>
       </c>
     </row>
     <row r="13" ht="15.5" customHeight="1">
@@ -1230,37 +1230,37 @@
         <v>0</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>-92.17419472415052</v>
+        <v>211.8902103124485</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>9206.861676146365</v>
+        <v>67.45650177078339</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>-97.34248062750011</v>
+        <v>39.60176911850282</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>30.77438622128603</v>
+        <v>27.88656282127045</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>23.42838010692161</v>
+        <v>21.43480945608487</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>19.60431694219828</v>
+        <v>19.93404298847901</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>23.39322067447582</v>
+        <v>14.13029211871093</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>16.37035681050836</v>
+        <v>8.236852620995872</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>13.81471228653575</v>
+        <v>7.523977431436291</v>
       </c>
       <c r="N13" s="18" t="n">
-        <v>11.8652483382917</v>
+        <v>6.918353481626216</v>
       </c>
       <c r="O13" s="18" t="n">
-        <v>13.14723641967799</v>
+        <v>4.099370992113682</v>
       </c>
     </row>
     <row r="14" ht="15.5" customHeight="1">
@@ -1333,40 +1333,40 @@
         </is>
       </c>
       <c r="D15" s="18" t="n">
-        <v>371.7079788408118</v>
+        <v>0</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>19.26972445785299</v>
+        <v>0</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>2713.940627304481</v>
+        <v>0</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>49.02585141277518</v>
+        <v>0</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>64.79321959013799</v>
+        <v>0</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>80.57352558155543</v>
+        <v>0</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>96.24884575301604</v>
+        <v>0</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>122.8268670803777</v>
+        <v>0</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>147.0050912044844</v>
+        <v>0</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>170.7214476142132</v>
+        <v>0</v>
       </c>
       <c r="N15" s="18" t="n">
-        <v>193.8596099948269</v>
+        <v>0</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>224.981938066046</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="15.5" customHeight="1">
@@ -1389,37 +1389,37 @@
         <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>-94.81589700658391</v>
+        <v>0</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>13983.96177766034</v>
+        <v>0</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>-98.19355475504751</v>
+        <v>0</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>32.16133473054614</v>
+        <v>0</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>24.35487245615946</v>
+        <v>0</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>19.454678268477</v>
+        <v>0</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>27.61385980208368</v>
+        <v>0</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>19.68480080851087</v>
+        <v>0</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>16.13301703730738</v>
+        <v>0</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>13.55316669578626</v>
+        <v>0</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>16.05405482454527</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="15.5" customHeight="1">
@@ -1810,40 +1810,40 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>373.7251388229811</v>
+        <v>2.017159982169304</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>25.94235447072258</v>
+        <v>6.67263001286959</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>2725.242159877597</v>
+        <v>11.30153257311679</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>64.86304123193298</v>
+        <v>15.8371898191578</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>85.07422335715859</v>
+        <v>20.28100376702059</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>105.2078832984997</v>
+        <v>24.63435771694429</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>125.1474622405089</v>
+        <v>28.89861648749289</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>153.9876542333309</v>
+        <v>31.16078715295319</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>178.3932230794047</v>
+        <v>31.3881318749203</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>202.329261237946</v>
+        <v>31.6078136237328</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>225.6795729192084</v>
+        <v>31.81996292438151</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>257.006646523701</v>
+        <v>32.0247084576549</v>
       </c>
     </row>
     <row r="25" ht="15.5" customHeight="1">
@@ -1863,40 +1863,40 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>373.7251388229811</v>
+        <v>2.017159982169304</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>25.94235447072258</v>
+        <v>6.67263001286959</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>2725.242159877597</v>
+        <v>11.30153257311679</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>64.86304123193298</v>
+        <v>15.8371898191578</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>85.07422335715859</v>
+        <v>20.28100376702059</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>105.2078832984997</v>
+        <v>24.63435771694429</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>125.1474622405089</v>
+        <v>28.89861648749289</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>153.9876542333309</v>
+        <v>31.16078715295319</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>178.3932230794047</v>
+        <v>31.3881318749203</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>202.329261237946</v>
+        <v>31.6078136237328</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>225.6795729192084</v>
+        <v>31.81996292438151</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>257.006646523701</v>
+        <v>32.0247084576549</v>
       </c>
     </row>
     <row r="26" ht="15.5" customHeight="1">
@@ -2128,40 +2128,40 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>372.512911215425</v>
+        <v>0.8049323746132124</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>22.5428407381931</v>
+        <v>3.273116280340108</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>2719.677232881344</v>
+        <v>5.736605576863639</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>57.15435510459341</v>
+        <v>8.128503691818231</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>75.24321569004346</v>
+        <v>10.44999609990546</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>93.27577730700679</v>
+        <v>12.70225172545135</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>110.1904404245579</v>
+        <v>13.94159467154188</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>135.0958732800384</v>
+        <v>12.26900619966077</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>155.6060305801443</v>
+        <v>8.600939375659905</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>175.6856113081772</v>
+        <v>4.964163693964039</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>195.2180301332365</v>
+        <v>1.358420138409599</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>224.1966992924607</v>
+        <v>-0.7852387735854194</v>
       </c>
     </row>
     <row r="31" ht="15.5" customHeight="1">
@@ -2287,40 +2287,40 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>372.512911215425</v>
+        <v>0.8049323746132124</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>22.5428407381931</v>
+        <v>3.273116280340108</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>2719.677232881344</v>
+        <v>5.736605576863639</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>57.15435510459341</v>
+        <v>8.128503691818231</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>75.24321569004346</v>
+        <v>10.44999609990546</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>93.27577730700679</v>
+        <v>12.70225172545135</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>110.1904404245579</v>
+        <v>13.94159467154188</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>135.0958732800384</v>
+        <v>12.26900619966077</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>155.6060305801443</v>
+        <v>8.600939375659905</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>175.6856113081772</v>
+        <v>4.964163693964039</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>195.2180301332365</v>
+        <v>1.358420138409599</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>224.1966992924607</v>
+        <v>-0.7852387735854194</v>
       </c>
     </row>
     <row r="34" ht="15.5" customHeight="1">
@@ -2340,40 +2340,40 @@
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>372.512911215425</v>
+        <v>0.8049323746132124</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>22.5428407381931</v>
+        <v>3.273116280340108</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>2719.677232881344</v>
+        <v>5.736605576863639</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>57.15435510459341</v>
+        <v>8.128503691818231</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>75.24321569004346</v>
+        <v>10.44999609990546</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>93.27577730700679</v>
+        <v>12.70225172545135</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>110.1904404245579</v>
+        <v>13.94159467154188</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>135.0958732800384</v>
+        <v>12.26900619966077</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>155.6060305801443</v>
+        <v>8.600939375659905</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>175.6856113081772</v>
+        <v>4.964163693964039</v>
       </c>
       <c r="N34" s="19" t="n">
-        <v>195.2180301332365</v>
+        <v>1.358420138409599</v>
       </c>
       <c r="O34" s="19" t="n">
-        <v>224.1966992924607</v>
+        <v>-0.7852387735854194</v>
       </c>
     </row>
     <row r="35" ht="15.5" customHeight="1">
@@ -2446,40 +2446,40 @@
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>-104.303615140319</v>
+        <v>-0.2253810648916995</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>-6.311995406694067</v>
+        <v>-0.9164725584952303</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-761.5096252067763</v>
+        <v>-1.606249561521819</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>-16.00321942928615</v>
+        <v>-2.275981033709105</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>-21.06810039321217</v>
+        <v>-2.92599890797353</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>-26.1172176459619</v>
+        <v>-3.556630483126379</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>-30.85332331887622</v>
+        <v>-3.903646508031726</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>-37.82684451841076</v>
+        <v>-3.435321735905014</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>-43.5696885624404</v>
+        <v>-2.408263025184774</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>-49.19197116628962</v>
+        <v>-1.389965834309931</v>
       </c>
       <c r="N36" s="19" t="n">
-        <v>-54.66104843730622</v>
+        <v>-0.3803576387546878</v>
       </c>
       <c r="O36" s="19" t="n">
-        <v>-62.77507580188899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" ht="15.5" customHeight="1">
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>0</v>
+        <v>-0.7852387735854194</v>
       </c>
     </row>
     <row r="38" ht="15.5" customHeight="1">
@@ -2552,40 +2552,40 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>268.2092960751061</v>
+        <v>0.5795513097215129</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>16.23084533149903</v>
+        <v>2.356643721844878</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>1958.167607674568</v>
+        <v>4.130356015341819</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>41.15113567530726</v>
+        <v>5.852522658109127</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>54.17511529683129</v>
+        <v>7.523997191931933</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>67.15855966104489</v>
+        <v>9.145621242324975</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>79.3371171056817</v>
+        <v>10.03794816351015</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>97.26902876162768</v>
+        <v>8.833684463755752</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>112.0363420177039</v>
+        <v>6.192676350475132</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>126.4936401418876</v>
+        <v>3.574197859654108</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>140.5569816959303</v>
+        <v>0.9780624996549113</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>161.4216234905717</v>
+        <v>-0.7852387735854194</v>
       </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
@@ -2732,19 +2732,19 @@
         <v>468.8902736200481</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>546.4993238167979</v>
+        <v>587.7150624737051</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>900.2983204991639</v>
+        <v>701.2672740833247</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>929.1884291173966</v>
+        <v>809.5996342213469</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>955.8125403939653</v>
+        <v>912.7643414024883</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>931.5288876506644</v>
+        <v>920.9328110987348</v>
       </c>
     </row>
     <row r="42" ht="15.5" customHeight="1">
@@ -2785,19 +2785,19 @@
         <v>468.8902736200481</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>546.4993238167979</v>
+        <v>587.7150624737051</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>900.2983204991639</v>
+        <v>701.2672740833247</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>929.1884291173966</v>
+        <v>809.5996342213469</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>955.8125403939653</v>
+        <v>912.7643414024883</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>931.5288876506644</v>
+        <v>920.9328110987348</v>
       </c>
     </row>
     <row r="43" ht="15.5" customHeight="1">
@@ -2817,40 +2817,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>30.71713469777927</v>
+        <v>-40.8019813183228</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>2.13224831266213</v>
+        <v>-111.9834796104035</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>2521.980047091309</v>
+        <v>-178.4581185738147</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>4601.306290468377</v>
+        <v>-199.3334978331807</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>6887.357507288791</v>
+        <v>-185.0608521838274</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>9186.999869453832</v>
+        <v>-171.0242795088361</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>11471.77062581735</v>
+        <v>2107.951638687432</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>13743.32513047112</v>
+        <v>4339.821365228168</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>14936.61499750294</v>
+        <v>6583.607018848254</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>16460.00031826405</v>
+        <v>8843.540745318216</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>17942.8050141539</v>
+        <v>11123.39055899854</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>19461.63722772111</v>
+        <v>13470.55413802822</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -2870,40 +2870,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>0</v>
+        <v>-40.96777528946001</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>0</v>
+        <v>-112.5319149539271</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>-179.3870116620161</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>4595.9750816</v>
+        <v>-200.635184667632</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>6880.365105369025</v>
+        <v>-186.7277840002949</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>9178.352646169024</v>
+        <v>-173.0490212389959</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>11461.48453303045</v>
+        <v>2105.576409935035</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>13730.66861094509</v>
+        <v>4337.260204640254</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>14921.95254081148</v>
+        <v>6581.027172392782</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>16443.37051597052</v>
+        <v>8840.942842828594</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>17924.25600816054</v>
+        <v>11120.77521958009</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>19440.51339376026</v>
+        <v>13467.92197020978</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -2976,40 +2976,40 @@
         </is>
       </c>
       <c r="D46" s="18" t="n">
-        <v>30.71713469777927</v>
+        <v>0.165793971137203</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>2.13224831266213</v>
+        <v>0.548435343523528</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>223.9925062913094</v>
+        <v>0.9288930882013798</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>5.331208868378053</v>
+        <v>1.301686834451326</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>6.992401919766459</v>
+        <v>1.666931816467446</v>
       </c>
       <c r="I46" s="18" t="n">
-        <v>8.647223284808195</v>
+        <v>2.024741730159805</v>
       </c>
       <c r="J46" s="18" t="n">
-        <v>10.28609278689114</v>
+        <v>2.375228752396676</v>
       </c>
       <c r="K46" s="18" t="n">
-        <v>12.65651952602719</v>
+        <v>2.561160587913961</v>
       </c>
       <c r="L46" s="18" t="n">
-        <v>14.66245669145792</v>
+        <v>2.579846455472902</v>
       </c>
       <c r="M46" s="18" t="n">
-        <v>16.62980229352981</v>
+        <v>2.597902489621874</v>
       </c>
       <c r="N46" s="18" t="n">
-        <v>18.54900599335959</v>
+        <v>2.615339418442316</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>21.12383396085214</v>
+        <v>2.632167818437388</v>
       </c>
     </row>
     <row r="47" ht="15.5" customHeight="1">
@@ -3029,40 +3029,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>71.93287335468639</v>
+        <v>0.4137573385843183</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>116.5034876111085</v>
+        <v>2.387759688042863</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>2706.575823623831</v>
+        <v>6.137657958706825</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>4853.224950461584</v>
+        <v>52.58516216002607</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>7203.726413507027</v>
+        <v>131.3080540344089</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>9564.975111033798</v>
+        <v>206.9509620711306</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>11940.66089943739</v>
+        <v>2576.84191230748</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>14289.82445428791</v>
+        <v>4927.536427701873</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>15836.9133180021</v>
+        <v>7284.874292931579</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>17389.18874738145</v>
+        <v>9653.140379539564</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>18898.61755454787</v>
+        <v>12036.15490040102</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>20393.16611537178</v>
+        <v>14391.48694912695</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -3082,40 +3082,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>102.6500080524657</v>
+        <v>0.5795513097215129</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>118.6357359237707</v>
+        <v>2.936195031566391</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>632.5807891151399</v>
+        <v>7.06655104690821</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>990.3265609983337</v>
+        <v>12.91907370501734</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>2357.611184891562</v>
+        <v>122.5135276396935</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>3722.50557649381</v>
+        <v>145.2882330314785</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>5088.821322974819</v>
+        <v>665.140878371016</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>6460.199194818024</v>
+        <v>1025.867812059857</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>7000.207800165653</v>
+        <v>2391.821115111629</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>27286.1678492833</v>
+        <v>3751.144083331205</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>21549.3062156749</v>
+        <v>5108.399944148359</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>22975.67192687738</v>
+        <v>6470.158892754222</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -3188,40 +3188,40 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>102.6500080524657</v>
+        <v>0.5795513097215129</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>15.98572787130502</v>
+        <v>2.356643721844878</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>513.9450531913692</v>
+        <v>4.130356015341819</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>-369.9997113851774</v>
+        <v>5.852522658109127</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>54.17511529683129</v>
+        <v>7.523997191931933</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>64.91597809181376</v>
+        <v>9.145621242324975</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>79.3371171056817</v>
+        <v>10.03794816351015</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>97.26902876162768</v>
+        <v>8.833684463755752</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>112.0363420177039</v>
+        <v>6.192676350475132</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>112.2670513421661</v>
+        <v>3.574197859654108</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>107.0031145808009</v>
+        <v>0.9780624996549113</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>54.53386428813877</v>
+        <v>-0.7852387735854194</v>
       </c>
     </row>
     <row r="51" ht="15.5" customHeight="1">
@@ -3244,37 +3244,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>102.6500080524657</v>
+        <v>0.5795513097215129</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>118.6357359237707</v>
+        <v>2.936195031566391</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>1360.326272383511</v>
+        <v>7.06655104690821</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>2303.436069594731</v>
+        <v>114.9895304477615</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>3657.589598401996</v>
+        <v>136.1426117891535</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>5009.484205869137</v>
+        <v>655.1029302075059</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>6362.930166056396</v>
+        <v>1017.034127596101</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>6888.171458147949</v>
+        <v>2385.628438761154</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>27173.90079794114</v>
+        <v>3747.569885471551</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>21442.30310109409</v>
+        <v>5107.421881648705</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>22921.13806258924</v>
+        <v>6470.944131527807</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -3297,37 +3297,37 @@
         <v>0</v>
       </c>
       <c r="E52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="18" t="n">
         <v>-727.7454832683711</v>
       </c>
-      <c r="F52" s="18" t="n">
+      <c r="J52" s="18" t="n">
         <v>-399.4353198647671</v>
       </c>
-      <c r="G52" s="18" t="n">
+      <c r="K52" s="18" t="n">
         <v>-57.99406137520214</v>
       </c>
-      <c r="H52" s="18" t="n">
+      <c r="L52" s="18" t="n">
         <v>296.4469812494701</v>
       </c>
-      <c r="I52" s="18" t="n">
+      <c r="M52" s="18" t="n">
         <v>663.7578101678919</v>
       </c>
-      <c r="J52" s="18" t="n">
+      <c r="N52" s="18" t="n">
         <v>1771.555210785502</v>
       </c>
-      <c r="K52" s="18" t="n">
+      <c r="O52" s="18" t="n">
         <v>-16786.921557147</v>
-      </c>
-      <c r="L52" s="18" t="n">
-        <v>-10356.70876738495</v>
-      </c>
-      <c r="M52" s="18" t="n">
-        <v>-10298.78028927715</v>
-      </c>
-      <c r="N52" s="18" t="n">
-        <v>-10230.33598785992</v>
-      </c>
-      <c r="O52" s="18" t="n">
-        <v>-10151.48102136637</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -3350,37 +3350,37 @@
         <v>0</v>
       </c>
       <c r="E53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="18" t="n">
         <v>-727.7454832683711</v>
       </c>
-      <c r="F53" s="18" t="n">
+      <c r="J53" s="18" t="n">
         <v>-399.4353198647671</v>
       </c>
-      <c r="G53" s="18" t="n">
+      <c r="K53" s="18" t="n">
         <v>-57.99406137520214</v>
       </c>
-      <c r="H53" s="18" t="n">
+      <c r="L53" s="18" t="n">
         <v>296.4469812494701</v>
       </c>
-      <c r="I53" s="18" t="n">
+      <c r="M53" s="18" t="n">
         <v>663.7578101678919</v>
       </c>
-      <c r="J53" s="18" t="n">
+      <c r="N53" s="18" t="n">
         <v>1771.555210785502</v>
       </c>
-      <c r="K53" s="18" t="n">
+      <c r="O53" s="18" t="n">
         <v>-16786.921557147</v>
-      </c>
-      <c r="L53" s="18" t="n">
-        <v>-10356.70876738495</v>
-      </c>
-      <c r="M53" s="18" t="n">
-        <v>-10298.78028927715</v>
-      </c>
-      <c r="N53" s="18" t="n">
-        <v>-10230.33598785992</v>
-      </c>
-      <c r="O53" s="18" t="n">
-        <v>-10151.48102136637</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -3453,40 +3453,40 @@
         </is>
       </c>
       <c r="D55" s="18" t="n">
-        <v>-30.71713469777927</v>
+        <v>-0.165793971137203</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>-2.13224831266213</v>
+        <v>-0.548435343523528</v>
       </c>
       <c r="F55" s="18" t="n">
-        <v>-223.9925062913094</v>
+        <v>-0.9288930882013798</v>
       </c>
       <c r="G55" s="18" t="n">
-        <v>-5.331208868378053</v>
+        <v>-1.301686834451326</v>
       </c>
       <c r="H55" s="18" t="n">
-        <v>-6.992401919766459</v>
+        <v>-1.666931816467446</v>
       </c>
       <c r="I55" s="18" t="n">
-        <v>-8.647223284808195</v>
+        <v>-2.024741730159805</v>
       </c>
       <c r="J55" s="18" t="n">
-        <v>-10.28609278689114</v>
+        <v>-2.375228752396676</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>-12.65651952602719</v>
+        <v>-2.561160587913961</v>
       </c>
       <c r="L55" s="18" t="n">
-        <v>-14.66245669145792</v>
+        <v>-2.579846455472902</v>
       </c>
       <c r="M55" s="18" t="n">
-        <v>-16.62980229352981</v>
+        <v>-2.597902489621874</v>
       </c>
       <c r="N55" s="18" t="n">
-        <v>-18.54900599335959</v>
+        <v>-2.615339418442316</v>
       </c>
       <c r="O55" s="18" t="n">
-        <v>-21.12383396085214</v>
+        <v>-2.632167818437388</v>
       </c>
     </row>
     <row r="56" ht="15.5" customHeight="1">
@@ -3506,40 +3506,40 @@
         </is>
       </c>
       <c r="D56" s="18" t="n">
-        <v>-30.71713469777927</v>
+        <v>-0.165793971137203</v>
       </c>
       <c r="E56" s="18" t="n">
-        <v>-2.13224831266213</v>
+        <v>-0.548435343523528</v>
       </c>
       <c r="F56" s="18" t="n">
-        <v>-223.9925062913094</v>
+        <v>-0.9288930882013798</v>
       </c>
       <c r="G56" s="18" t="n">
-        <v>-5.331208868378053</v>
+        <v>-1.301686834451326</v>
       </c>
       <c r="H56" s="18" t="n">
-        <v>-6.992401919766459</v>
+        <v>-1.666931816467446</v>
       </c>
       <c r="I56" s="18" t="n">
-        <v>-8.647223284808195</v>
+        <v>-2.024741730159805</v>
       </c>
       <c r="J56" s="18" t="n">
-        <v>-10.28609278689114</v>
+        <v>-2.375228752396676</v>
       </c>
       <c r="K56" s="18" t="n">
-        <v>-12.65651952602719</v>
+        <v>-2.561160587913961</v>
       </c>
       <c r="L56" s="18" t="n">
-        <v>-14.66245669145792</v>
+        <v>-2.579846455472902</v>
       </c>
       <c r="M56" s="18" t="n">
-        <v>-16.62980229352981</v>
+        <v>-2.597902489621874</v>
       </c>
       <c r="N56" s="18" t="n">
-        <v>-18.54900599335959</v>
+        <v>-2.615339418442316</v>
       </c>
       <c r="O56" s="18" t="n">
-        <v>-21.12383396085214</v>
+        <v>-2.632167818437388</v>
       </c>
     </row>
     <row r="57" ht="15.5" customHeight="1">
@@ -3612,40 +3612,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>71.93287335468639</v>
+        <v>0.4137573385843099</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>-611.2419956572626</v>
+        <v>2.387759688042863</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>9.152962959063387</v>
+        <v>6.13765795870683</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>927.0012907547534</v>
+        <v>11.61738687056601</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>2647.065764221266</v>
+        <v>120.846595823226</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>4377.616163376893</v>
+        <v>-584.4819919670524</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>6850.090440973429</v>
+        <v>263.3303297538523</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>-10339.378881855</v>
+        <v>965.3125900967409</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>-3371.163423910754</v>
+        <v>2685.688249905626</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>16970.75775771262</v>
+        <v>4412.303991009476</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>11300.42122182162</v>
+        <v>6877.339815515419</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>12803.06707155016</v>
+        <v>-10319.39483221122</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -3665,40 +3665,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>0</v>
+        <v>8.43769498715119e-15</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>727.7454832683711</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>2697.422860664768</v>
+        <v>-5.329070518200751e-15</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>3926.22365970683</v>
+        <v>40.96777528946006</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>4556.660649285761</v>
+        <v>10.4614582111829</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>5187.358947656905</v>
+        <v>791.432954038183</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>5090.570458463965</v>
+        <v>2313.511582553627</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>24629.20333614292</v>
+        <v>3962.223837605133</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>19208.07674191286</v>
+        <v>4599.186043025953</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>418.4309896688246</v>
+        <v>5240.836388530088</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>7598.196332726249</v>
+        <v>5158.815084885604</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>7590.099043821616</v>
+        <v>24710.88178133817</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -3771,40 +3771,40 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>373.7251388229811</v>
+        <v>2.017159982169304</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>25.94235447072258</v>
+        <v>6.67263001286959</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>2725.242159877597</v>
+        <v>11.30153257311679</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>64.86304123193298</v>
+        <v>15.8371898191578</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>85.07422335715859</v>
+        <v>20.28100376702059</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>105.2078832984997</v>
+        <v>24.63435771694429</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>125.1474622405089</v>
+        <v>28.89861648749289</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>153.9876542333309</v>
+        <v>31.16078715295319</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>178.3932230794047</v>
+        <v>31.3881318749203</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>202.329261237946</v>
+        <v>31.6078136237328</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>225.6795729192084</v>
+        <v>31.81996292438151</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>257.006646523701</v>
+        <v>32.0247084576549</v>
       </c>
     </row>
     <row r="62" ht="15.5" customHeight="1">
@@ -3824,40 +3824,40 @@
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>-104.303615140319</v>
+        <v>-0.2253810648916995</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>-6.311995406694067</v>
+        <v>-0.9164725584952303</v>
       </c>
       <c r="F62" s="18" t="n">
-        <v>-761.5096252067763</v>
+        <v>-1.606249561521819</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>-16.00321942928615</v>
+        <v>-2.275981033709105</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>-21.06810039321217</v>
+        <v>-2.92599890797353</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>-26.1172176459619</v>
+        <v>-3.556630483126379</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>-30.85332331887622</v>
+        <v>-3.903646508031726</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>-37.82684451841076</v>
+        <v>-3.435321735905014</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>-43.5696885624404</v>
+        <v>-2.408263025184774</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>-49.19197116628962</v>
+        <v>-1.389965834309931</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>-54.66104843730622</v>
+        <v>-0.3803576387546878</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>-62.77507580188899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" ht="15.5" customHeight="1">
@@ -3877,40 +3877,40 @@
         </is>
       </c>
       <c r="D63" s="18" t="n">
-        <v>-61.43426939555854</v>
+        <v>-0.3315879422744061</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>57.16977277023427</v>
+        <v>-0.7652827447726498</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>-443.7205159572944</v>
+        <v>-0.7609154893557037</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>437.3225948458626</v>
+        <v>-0.7455874924998922</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>-3.322386102776811</v>
+        <v>-0.7304899640322402</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>-3.309642730083473</v>
+        <v>-0.7156198273847183</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>-3.277739004165898</v>
+        <v>-0.7009740444737416</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>-4.740853478272097</v>
+        <v>-0.3718636710345704</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>-4.011874330861456</v>
+        <v>-0.0373717351178815</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>-3.934691204143771</v>
+        <v>-0.03611206829794344</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>-3.838407399659573</v>
+        <v>-0.03487385764088469</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>-5.149655934985084</v>
+        <v>-0.03365679999014493</v>
       </c>
     </row>
     <row r="64" ht="15.5" customHeight="1">
@@ -3930,40 +3930,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>207.9872542871036</v>
+        <v>1.460190975003198</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>76.80013183426279</v>
+        <v>4.99087470960171</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>1520.012018713527</v>
+        <v>8.934367522239265</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>486.1824166485094</v>
+        <v>12.8156212929488</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>60.68373686116961</v>
+        <v>16.62451489501482</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>75.78102292245435</v>
+        <v>20.3621074064332</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>91.01639991746681</v>
+        <v>24.29399593498742</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>111.419956236648</v>
+        <v>27.35360174601361</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>130.8116601861029</v>
+        <v>28.94249711461765</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>149.2025988675126</v>
+        <v>30.18173572112492</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>167.1801170822426</v>
+        <v>31.40473142798594</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>189.0819147868269</v>
+        <v>31.99105165766475</v>
       </c>
     </row>
     <row r="65" ht="15.5" customHeight="1">
@@ -4089,40 +4089,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>165.5592880226404</v>
+        <v>-40.96777528946001</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>0.2451174601940096</v>
+        <v>-71.56413966446706</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>1444.222554483199</v>
+        <v>-66.85509670808896</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>411.1508470604846</v>
+        <v>-62.215948295076</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>-13.59751703097511</v>
+        <v>-57.65673899712989</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>2.242581569231135</v>
+        <v>-53.17633394679002</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-14.85565393856562</v>
+        <v>-81.57805792104502</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>-26.29661357030139</v>
+        <v>-110.3629680609358</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>-5.527743922777063</v>
+        <v>-107.3969069942623</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>14.22658879972147</v>
+        <v>-104.7942743466662</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>33.55386711512938</v>
+        <v>-102.2215185391273</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>106.8877592024329</v>
+        <v>-50.20310392672924</v>
       </c>
     </row>
     <row r="68" ht="15.5" customHeight="1">
@@ -4354,22 +4354,22 @@
         </is>
       </c>
       <c r="D72" s="18" t="n">
-        <v>-165.5592880226404</v>
+        <v>0</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>-0.2451174601940096</v>
+        <v>0</v>
       </c>
       <c r="F72" s="18" t="n">
-        <v>-1444.222554483199</v>
+        <v>0</v>
       </c>
       <c r="G72" s="18" t="n">
-        <v>-411.1508470604846</v>
+        <v>0</v>
       </c>
       <c r="H72" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I72" s="18" t="n">
-        <v>-2.242581569231135</v>
+        <v>0</v>
       </c>
       <c r="J72" s="18" t="n">
         <v>0</v>
@@ -4381,13 +4381,13 @@
         <v>0</v>
       </c>
       <c r="M72" s="18" t="n">
-        <v>-14.22658879972147</v>
+        <v>0</v>
       </c>
       <c r="N72" s="18" t="n">
-        <v>-33.55386711512938</v>
+        <v>0</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>-106.8877592024329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" ht="15.5" customHeight="1">
@@ -4460,22 +4460,22 @@
         </is>
       </c>
       <c r="D74" s="18" t="n">
-        <v>-165.5592880226404</v>
+        <v>0</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>-0.2451174601940096</v>
+        <v>0</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>-1444.222554483199</v>
+        <v>0</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>-411.1508470604846</v>
+        <v>0</v>
       </c>
       <c r="H74" s="18" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>-2.242581569231135</v>
+        <v>0</v>
       </c>
       <c r="J74" s="18" t="n">
         <v>0</v>
@@ -4487,13 +4487,13 @@
         <v>0</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>-14.22658879972147</v>
+        <v>0</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>-33.55386711512938</v>
+        <v>0</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>-106.8877592024329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" ht="15.5" customHeight="1">
@@ -4513,40 +4513,40 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>0</v>
+        <v>-40.96777528946001</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>0</v>
+        <v>-71.56413966446706</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>0</v>
+        <v>-66.85509670808896</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>0</v>
+        <v>-62.215948295076</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>-13.59751703097511</v>
+        <v>-57.65673899712989</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>0</v>
+        <v>-53.17633394679002</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>-14.85565393856562</v>
+        <v>-81.57805792104502</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>-26.29661357030139</v>
+        <v>-110.3629680609358</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>-5.527743922777063</v>
+        <v>-107.3969069942623</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>0</v>
+        <v>-104.7942743466662</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>0</v>
+        <v>-102.2215185391273</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>0</v>
+        <v>-50.20310392672924</v>
       </c>
     </row>
     <row r="76" ht="15.5" customHeight="1">
@@ -4569,37 +4569,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>0</v>
+        <v>-40.96777528946001</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>0</v>
+        <v>-112.5319149539271</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>-179.3870116620161</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>4595.9750816</v>
+        <v>-200.635184667632</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>6880.365105369025</v>
+        <v>-186.7277840002949</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>9178.352646169024</v>
+        <v>-173.0490212389959</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>11461.48453303045</v>
+        <v>2105.576409935035</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>13730.66861094509</v>
+        <v>4337.260204640254</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>14921.95254081148</v>
+        <v>6581.027172392782</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>16443.37051597052</v>
+        <v>8840.942842828594</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>17924.25600816054</v>
+        <v>11120.77521958009</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -4619,40 +4619,40 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>0</v>
+        <v>-40.96777528946001</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>0</v>
+        <v>-71.56413966446706</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>0</v>
+        <v>-66.85509670808896</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>0</v>
+        <v>-62.215948295076</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>-13.59751703097511</v>
+        <v>-57.65673899712989</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>0</v>
+        <v>-53.17633394679002</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>-14.85565393856562</v>
+        <v>-81.57805792104502</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>-26.29661357030139</v>
+        <v>-110.3629680609358</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>-5.527743922777063</v>
+        <v>-107.3969069942623</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>0</v>
+        <v>-104.7942743466662</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>0</v>
+        <v>-102.2215185391273</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>0</v>
+        <v>-50.20310392672924</v>
       </c>
     </row>
     <row r="78" ht="15.5" customHeight="1">
@@ -4672,40 +4672,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>0</v>
+        <v>-40.96777528946001</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>0</v>
+        <v>-112.5319149539271</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>2297.9875408</v>
+        <v>-179.3870116620161</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>4595.9750816</v>
+        <v>-200.635184667632</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>6880.365105369025</v>
+        <v>-186.7277840002949</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>9178.352646169024</v>
+        <v>-173.0490212389959</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>11461.48453303045</v>
+        <v>2105.576409935035</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>13730.66861094509</v>
+        <v>4337.260204640254</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>14921.95254081148</v>
+        <v>6581.027172392782</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>16443.37051597052</v>
+        <v>8840.942842828594</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>17924.25600816054</v>
+        <v>11120.77521958009</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>19440.51339376026</v>
+        <v>13467.92197020978</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -4908,16 +4908,16 @@
         <v>468.8902736200481</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>546.4993238167979</v>
+        <v>587.7150624737051</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>900.2983204991639</v>
+        <v>701.2672740833247</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>929.1884291173966</v>
+        <v>809.5996342213469</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>955.8125403939653</v>
+        <v>912.7643414024883</v>
       </c>
     </row>
     <row r="83" ht="15.5" customHeight="1">
@@ -5064,19 +5064,19 @@
         <v>468.8902736200481</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>546.4993238167979</v>
+        <v>587.7150624737051</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>900.2983204991639</v>
+        <v>701.2672740833247</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>929.1884291173966</v>
+        <v>809.5996342213469</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>955.8125403939653</v>
+        <v>912.7643414024883</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>931.5288876506644</v>
+        <v>920.9328110987348</v>
       </c>
     </row>
     <row r="86" ht="15.5" customHeight="1">
@@ -5202,40 +5202,40 @@
         </is>
       </c>
       <c r="D88" s="18" t="n">
-        <v>30.71713469777927</v>
+        <v>0.165793971137203</v>
       </c>
       <c r="E88" s="18" t="n">
-        <v>2.13224831266213</v>
+        <v>0.548435343523528</v>
       </c>
       <c r="F88" s="18" t="n">
-        <v>223.9925062913094</v>
+        <v>0.9288930882013798</v>
       </c>
       <c r="G88" s="18" t="n">
-        <v>5.331208868378053</v>
+        <v>1.301686834451326</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>6.992401919766459</v>
+        <v>1.666931816467446</v>
       </c>
       <c r="I88" s="18" t="n">
-        <v>8.647223284808195</v>
+        <v>2.024741730159805</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>10.28609278689114</v>
+        <v>2.375228752396676</v>
       </c>
       <c r="K88" s="18" t="n">
-        <v>12.65651952602719</v>
+        <v>2.561160587913961</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>14.66245669145792</v>
+        <v>2.579846455472902</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>16.62980229352981</v>
+        <v>2.597902489621874</v>
       </c>
       <c r="N88" s="18" t="n">
-        <v>18.54900599335959</v>
+        <v>2.615339418442316</v>
       </c>
       <c r="O88" s="18" t="n">
-        <v>21.12383396085214</v>
+        <v>2.632167818437388</v>
       </c>
     </row>
     <row r="89" ht="15.5" customHeight="1">
@@ -5255,40 +5255,40 @@
         </is>
       </c>
       <c r="D89" s="18" t="n">
-        <v>30.71713469777927</v>
+        <v>0.165793971137203</v>
       </c>
       <c r="E89" s="18" t="n">
-        <v>2.13224831266213</v>
+        <v>0.548435343523528</v>
       </c>
       <c r="F89" s="18" t="n">
-        <v>223.9925062913094</v>
+        <v>0.9288930882013798</v>
       </c>
       <c r="G89" s="18" t="n">
-        <v>5.331208868378053</v>
+        <v>1.301686834451326</v>
       </c>
       <c r="H89" s="18" t="n">
-        <v>6.992401919766459</v>
+        <v>1.666931816467446</v>
       </c>
       <c r="I89" s="18" t="n">
-        <v>8.647223284808195</v>
+        <v>2.024741730159805</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>10.28609278689114</v>
+        <v>2.375228752396676</v>
       </c>
       <c r="K89" s="18" t="n">
-        <v>12.65651952602719</v>
+        <v>2.561160587913961</v>
       </c>
       <c r="L89" s="18" t="n">
-        <v>14.66245669145792</v>
+        <v>2.579846455472902</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>16.62980229352981</v>
+        <v>2.597902489621874</v>
       </c>
       <c r="N89" s="18" t="n">
-        <v>18.54900599335959</v>
+        <v>2.615339418442316</v>
       </c>
       <c r="O89" s="18" t="n">
-        <v>21.12383396085214</v>
+        <v>2.632167818437388</v>
       </c>
     </row>
     <row r="90" ht="15.5" customHeight="1">
@@ -5308,40 +5308,40 @@
         </is>
       </c>
       <c r="D90" s="18" t="n">
-        <v>61.43426939555854</v>
+        <v>0.3315879422744061</v>
       </c>
       <c r="E90" s="18" t="n">
-        <v>4.264496625324259</v>
+        <v>1.096870687047056</v>
       </c>
       <c r="F90" s="18" t="n">
-        <v>447.9850125826187</v>
+        <v>1.85778617640276</v>
       </c>
       <c r="G90" s="18" t="n">
-        <v>10.66241773675611</v>
+        <v>2.603373668902652</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>13.98480383953292</v>
+        <v>3.333863632934892</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>17.29444656961639</v>
+        <v>4.04948346031961</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>20.57218557378229</v>
+        <v>4.750457504793352</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>25.31303905205439</v>
+        <v>5.122321175827922</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>29.32491338291584</v>
+        <v>5.159692910945804</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>33.25960458705961</v>
+        <v>5.195804979243747</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>37.09801198671919</v>
+        <v>5.230678836884632</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>42.24766792170427</v>
+        <v>5.264335636874777</v>
       </c>
     </row>
     <row r="91" ht="15.5" customHeight="1">
@@ -5361,40 +5361,40 @@
         </is>
       </c>
       <c r="D91" s="18" t="n">
-        <v>61.43426939555854</v>
+        <v>0.3315879422744061</v>
       </c>
       <c r="E91" s="18" t="n">
-        <v>-57.16977277023427</v>
+        <v>0.7652827447726498</v>
       </c>
       <c r="F91" s="18" t="n">
-        <v>443.7205159572944</v>
+        <v>0.7609154893557037</v>
       </c>
       <c r="G91" s="18" t="n">
-        <v>-437.3225948458626</v>
+        <v>0.7455874924998922</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>3.322386102776811</v>
+        <v>0.7304899640322402</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>3.309642730083473</v>
+        <v>0.7156198273847183</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>3.277739004165898</v>
+        <v>0.7009740444737416</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>4.740853478272097</v>
+        <v>0.3718636710345704</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>4.011874330861456</v>
+        <v>0.0373717351178815</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>3.934691204143771</v>
+        <v>0.03611206829794344</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>3.838407399659573</v>
+        <v>0.03487385764088469</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>5.149655934985084</v>
+        <v>0.03365679999014493</v>
       </c>
     </row>
     <row r="92" ht="15.5" customHeight="1">
@@ -5653,37 +5653,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>433.7685840977465</v>
+        <v>0.5795513097215129</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>450.2445468894396</v>
+        <v>2.936195031566391</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>5236.948061115576</v>
+        <v>7.06655104690821</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>7658.927421247764</v>
+        <v>446.1081064930423</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>9669.64881885503</v>
+        <v>467.7514227548224</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>11682.59645826064</v>
+        <v>3875.156850139572</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>13692.61028724789</v>
+        <v>5715.957610449134</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>14544.98087209417</v>
+        <v>7741.119790414185</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>35247.68467951445</v>
+        <v>9764.114269063046</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>27072.99975384793</v>
+        <v>11780.5341340402</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>28216.66322290651</v>
+        <v>13800.6242527193</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -5756,40 +5756,40 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>268.2092960751061</v>
+        <v>0.5795513097215129</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>16.23084533149903</v>
+        <v>2.356643721844878</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>1958.167607674568</v>
+        <v>4.130356015341819</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>41.15113567530726</v>
+        <v>5.852522658109127</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>54.17511529683129</v>
+        <v>7.523997191931933</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>67.15855966104489</v>
+        <v>9.145621242324975</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>79.3371171056817</v>
+        <v>10.03794816351015</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>97.26902876162768</v>
+        <v>8.833684463755752</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>112.0363420177039</v>
+        <v>6.192676350475132</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>126.4936401418876</v>
+        <v>3.574197859654108</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>140.5569816959303</v>
+        <v>0.9780624996549113</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>161.4216234905717</v>
+        <v>-0.7852387735854194</v>
       </c>
     </row>
     <row r="99" ht="15.5" customHeight="1">
@@ -5809,22 +5809,22 @@
         </is>
       </c>
       <c r="D99" s="20" t="n">
-        <v>165.5592880226404</v>
+        <v>0</v>
       </c>
       <c r="E99" s="20" t="n">
-        <v>0.2451174601940096</v>
+        <v>0</v>
       </c>
       <c r="F99" s="20" t="n">
-        <v>1444.222554483199</v>
+        <v>0</v>
       </c>
       <c r="G99" s="20" t="n">
-        <v>411.1508470604846</v>
+        <v>0</v>
       </c>
       <c r="H99" s="20" t="n">
         <v>0</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>2.242581569231135</v>
+        <v>0</v>
       </c>
       <c r="J99" s="20" t="n">
         <v>0</v>
@@ -5836,13 +5836,13 @@
         <v>0</v>
       </c>
       <c r="M99" s="20" t="n">
-        <v>14.22658879972147</v>
+        <v>0</v>
       </c>
       <c r="N99" s="20" t="n">
-        <v>33.55386711512938</v>
+        <v>0</v>
       </c>
       <c r="O99" s="20" t="n">
-        <v>106.8877592024329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" ht="15.5" customHeight="1">
@@ -5862,40 +5862,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>433.7685840977465</v>
+        <v>0.5795513097215129</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>450.2445468894396</v>
+        <v>2.936195031566391</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>5236.948061115576</v>
+        <v>7.06655104690821</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>7658.927421247764</v>
+        <v>446.1081064930423</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>9669.64881885503</v>
+        <v>467.7514227548224</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>11682.59645826064</v>
+        <v>3875.156850139572</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>13692.61028724789</v>
+        <v>5715.957610449134</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>14544.98087209417</v>
+        <v>7741.119790414185</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>35247.68467951445</v>
+        <v>9764.114269063046</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>27072.99975384793</v>
+        <v>11780.5341340402</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>28216.66322290651</v>
+        <v>13800.6242527193</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>29887.18635296807</v>
+        <v>14660.78423569759</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -6027,34 +6027,34 @@
         <v>0</v>
       </c>
       <c r="F103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="18" t="n">
         <v>-727.7454832683711</v>
       </c>
-      <c r="G103" s="18" t="n">
+      <c r="K103" s="18" t="n">
         <v>-399.4353198647671</v>
       </c>
-      <c r="H103" s="18" t="n">
+      <c r="L103" s="18" t="n">
         <v>-57.99406137520214</v>
       </c>
-      <c r="I103" s="18" t="n">
+      <c r="M103" s="18" t="n">
         <v>296.4469812494701</v>
       </c>
-      <c r="J103" s="18" t="n">
+      <c r="N103" s="18" t="n">
         <v>663.7578101678919</v>
       </c>
-      <c r="K103" s="18" t="n">
+      <c r="O103" s="18" t="n">
         <v>1771.555210785502</v>
-      </c>
-      <c r="L103" s="18" t="n">
-        <v>-16786.921557147</v>
-      </c>
-      <c r="M103" s="18" t="n">
-        <v>-10356.70876738495</v>
-      </c>
-      <c r="N103" s="18" t="n">
-        <v>-10298.78028927715</v>
-      </c>
-      <c r="O103" s="18" t="n">
-        <v>-10230.33598785992</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -6236,37 +6236,37 @@
         <v>0</v>
       </c>
       <c r="E107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="18" t="n">
         <v>-727.7454832683711</v>
       </c>
-      <c r="F107" s="18" t="n">
+      <c r="J107" s="18" t="n">
         <v>-399.4353198647671</v>
       </c>
-      <c r="G107" s="18" t="n">
+      <c r="K107" s="18" t="n">
         <v>-57.99406137520214</v>
       </c>
-      <c r="H107" s="18" t="n">
+      <c r="L107" s="18" t="n">
         <v>296.4469812494701</v>
       </c>
-      <c r="I107" s="18" t="n">
+      <c r="M107" s="18" t="n">
         <v>663.7578101678919</v>
       </c>
-      <c r="J107" s="18" t="n">
+      <c r="N107" s="18" t="n">
         <v>1771.555210785502</v>
       </c>
-      <c r="K107" s="18" t="n">
+      <c r="O107" s="18" t="n">
         <v>-16786.921557147</v>
-      </c>
-      <c r="L107" s="18" t="n">
-        <v>-10356.70876738495</v>
-      </c>
-      <c r="M107" s="18" t="n">
-        <v>-10298.78028927715</v>
-      </c>
-      <c r="N107" s="18" t="n">
-        <v>-10230.33598785992</v>
-      </c>
-      <c r="O107" s="18" t="n">
-        <v>-10151.48102136637</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -7205,40 +7205,40 @@
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>22216.78679838064</v>
+        <v>113.2667983806361</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>458.916062862465</v>
+        <v>139.538462862465</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>28597.12481997377</v>
+        <v>168.4648199737737</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>597.227568820198</v>
+        <v>196.9081688201981</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>675.2176161781581</v>
+        <v>224.8810161781582</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>752.0144710625386</v>
+        <v>252.3942710625387</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>828.1218962127755</v>
+        <v>280.2338962127754</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>909.6420423021359</v>
+        <v>301.7193423021359</v>
       </c>
       <c r="L12" s="18" t="n">
-        <v>982.7800979306027</v>
+        <v>317.9026979306027</v>
       </c>
       <c r="M12" s="18" t="n">
-        <v>1053.926952002785</v>
+        <v>333.8452520027849</v>
       </c>
       <c r="N12" s="18" t="n">
-        <v>1122.898329251985</v>
+        <v>349.5703292519852</v>
       </c>
       <c r="O12" s="18" t="n">
-        <v>1219.019969883522</v>
+        <v>361.5893698835221</v>
       </c>
     </row>
     <row r="13" ht="15.5" customHeight="1">
@@ -7261,37 +7261,37 @@
         <v>0</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>-97.93437247687</v>
+        <v>23.19449729084975</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>6131.449960936365</v>
+        <v>20.73002419398857</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>-97.91158176711855</v>
+        <v>16.88385079499231</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>13.058681720274</v>
+        <v>14.20603701997902</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>11.3736450359609</v>
+        <v>12.23458313732608</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>10.12047348539755</v>
+        <v>11.03021278297502</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>9.843979064214349</v>
+        <v>7.666969049685202</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>8.040311708039338</v>
+        <v>5.363711688149286</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>7.239346240526556</v>
+        <v>5.014916254552326</v>
       </c>
       <c r="N13" s="18" t="n">
-        <v>6.544227483520881</v>
+        <v>4.710289319636374</v>
       </c>
       <c r="O13" s="18" t="n">
-        <v>8.560137469931783</v>
+        <v>3.438232488797155</v>
       </c>
     </row>
     <row r="14" ht="15.5" customHeight="1">
@@ -7311,40 +7311,40 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>8040.995026450317</v>
+        <v>40.995026450316</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>143.6907481496714</v>
+        <v>43.69074814967141</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>7692.374374386706</v>
+        <v>45.31555085729472</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>149.1877657740789</v>
+        <v>49.1877657740789</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>149.9362068679646</v>
+        <v>49.93620686796458</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>150.5172270982115</v>
+        <v>50.51722709821154</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>151.1480259127368</v>
+        <v>51.14802591273681</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>149.631201845586</v>
+        <v>49.63120184558594</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>147.8137319648108</v>
+        <v>47.81373196481076</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>146.3621352969788</v>
+        <v>46.36213529697878</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>145.2033715644571</v>
+        <v>45.20337156445715</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>142.1712695912091</v>
+        <v>42.17126959120914</v>
       </c>
     </row>
     <row r="15" ht="15.5" customHeight="1">
@@ -7364,40 +7364,40 @@
         </is>
       </c>
       <c r="D15" s="18" t="n">
-        <v>22103.52</v>
+        <v>221.0352</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>319.3776</v>
+        <v>259.4943</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>28428.66</v>
+        <v>284.2866</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>400.3194</v>
+        <v>329.6748000000001</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>450.3366</v>
+        <v>375.2805</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>499.6202</v>
+        <v>394.437</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>547.888</v>
+        <v>438.3104</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>607.9227</v>
+        <v>492.1279</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>664.8774</v>
+        <v>543.9906</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>720.0817000000001</v>
+        <v>594.8501</v>
       </c>
       <c r="N15" s="18" t="n">
-        <v>773.328</v>
+        <v>644.4400000000001</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>857.4306000000001</v>
+        <v>692.5401000000001</v>
       </c>
     </row>
     <row r="16" ht="15.5" customHeight="1">
@@ -7420,37 +7420,37 @@
         <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>-98.55508262937306</v>
+        <v>17.39953636343894</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>8801.269218630237</v>
+        <v>9.554082690833665</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>-98.59184569374708</v>
+        <v>15.96564875024009</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>12.49432328285864</v>
+        <v>13.83354141717836</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>10.94372520465803</v>
+        <v>5.104581772833905</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>9.660898418438645</v>
+        <v>11.12304373068451</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>10.95747671056857</v>
+        <v>12.27839905236106</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>9.368740466509973</v>
+        <v>10.5384596158844</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>8.302929231765145</v>
+        <v>9.349334345115533</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>7.394480376323953</v>
+        <v>8.336537221730334</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>10.8754112097325</v>
+        <v>7.463860095586861</v>
       </c>
     </row>
     <row r="17" ht="15.5" customHeight="1">
@@ -7470,40 +7470,40 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>8000</v>
+        <v>80</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>100</v>
+        <v>81.25000000000001</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>7647.058823529412</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>100</v>
+        <v>82.35294117647059</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>100</v>
+        <v>83.33333333333333</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>100</v>
+        <v>78.94736842105262</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>100</v>
+        <v>80.95238095238096</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>100</v>
+        <v>81.81818181818183</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>100</v>
+        <v>82.60869565217391</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>100</v>
+        <v>80.76923076923076</v>
       </c>
     </row>
     <row r="18" ht="15.5" customHeight="1">
@@ -7841,40 +7841,40 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>22261.66423737277</v>
+        <v>379.1794373727678</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>503.4675085795669</v>
+        <v>443.5842085795669</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>28644.76143</v>
+        <v>500.3880300000001</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>626.1728300000001</v>
+        <v>555.52823</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>706.68637</v>
+        <v>631.63027</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>786.1193900000001</v>
+        <v>680.93619</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>863.9316</v>
+        <v>754.3539999999999</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>971.719265</v>
+        <v>855.9244650000001</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>1078.68093</v>
+        <v>957.79413</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>1182.349315</v>
+        <v>1057.117715</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>1282.2973997655</v>
+        <v>1153.4093997655</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>1442.51967</v>
+        <v>1277.62917</v>
       </c>
     </row>
     <row r="25" ht="15.5" customHeight="1">
@@ -7894,40 +7894,40 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>22261.66423737277</v>
+        <v>379.1794373727678</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>503.4675085795669</v>
+        <v>443.5842085795669</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>28644.76143</v>
+        <v>500.3880300000001</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>626.1728300000001</v>
+        <v>555.52823</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>706.68637</v>
+        <v>631.63027</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>786.1193900000001</v>
+        <v>680.93619</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>863.9316</v>
+        <v>754.3539999999999</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>971.719265</v>
+        <v>855.9244650000001</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>1078.68093</v>
+        <v>957.79413</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>1182.349315</v>
+        <v>1057.117715</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>1282.2973997655</v>
+        <v>1153.4093997655</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>1442.51967</v>
+        <v>1277.62917</v>
       </c>
     </row>
     <row r="26" ht="15.5" customHeight="1">
@@ -7947,40 +7947,40 @@
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>8057.237666171821</v>
+        <v>137.2376661718198</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>157.6402066330159</v>
+        <v>138.8902066330159</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>7705.188202369597</v>
+        <v>134.5999670754795</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>156.4183074814761</v>
+        <v>138.7712486579466</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>156.924036376346</v>
+        <v>140.2573697096794</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>157.3433960436348</v>
+        <v>136.2907644646874</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>157.6839792074292</v>
+        <v>137.6839792074292</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>159.8425696227497</v>
+        <v>140.7949505751307</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>162.2375689112008</v>
+        <v>144.0557507293826</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>164.196550891378</v>
+        <v>146.8052465435519</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>165.8154624901077</v>
+        <v>149.148795823441</v>
       </c>
       <c r="O26" s="18" t="n">
-        <v>168.2374841765619</v>
+        <v>149.0067149457927</v>
       </c>
     </row>
     <row r="27" ht="15.5" customHeight="1">
@@ -8000,40 +8000,40 @@
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>8057.237666171821</v>
+        <v>137.2376661718198</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>157.6402066330159</v>
+        <v>138.8902066330159</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>7705.188202369597</v>
+        <v>134.5999670754795</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>156.4183074814761</v>
+        <v>138.7712486579466</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>156.924036376346</v>
+        <v>140.2573697096794</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>157.3433960436348</v>
+        <v>136.2907644646874</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>157.6839792074292</v>
+        <v>137.6839792074292</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>159.8425696227497</v>
+        <v>140.7949505751307</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>162.2375689112008</v>
+        <v>144.0557507293826</v>
       </c>
       <c r="M27" s="18" t="n">
-        <v>164.196550891378</v>
+        <v>146.8052465435519</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>165.8154624901077</v>
+        <v>149.148795823441</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>168.2374841765619</v>
+        <v>149.0067149457927</v>
       </c>
     </row>
     <row r="28" ht="15.5" customHeight="1">
@@ -8159,40 +8159,40 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>22252.73250161936</v>
+        <v>370.2477016193639</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>483.247857137535</v>
+        <v>423.364557137535</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>28613.36661002623</v>
+        <v>468.9932100262264</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>583.7146611798021</v>
+        <v>513.070061179802</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>653.2753538218418</v>
+        <v>578.2192538218418</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>721.8651189374614</v>
+        <v>616.6819189374613</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>788.1477037872246</v>
+        <v>678.5701037872245</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>883.7299226978641</v>
+        <v>767.9351226978642</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>978.6082320693972</v>
+        <v>857.7214320693972</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>1070.314062997215</v>
+        <v>945.0824629972152</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>1158.419270748015</v>
+        <v>1029.531270748015</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>1310.400300116478</v>
+        <v>1145.509800116478</v>
       </c>
     </row>
     <row r="31" ht="15.5" customHeight="1">
@@ -8212,40 +8212,40 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>8054.004973549685</v>
+        <v>134.004973549684</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>151.3092518503286</v>
+        <v>132.5592518503286</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>7696.743272672117</v>
+        <v>126.1550373779994</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>145.8122342259211</v>
+        <v>128.1651754023917</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>145.0637931320354</v>
+        <v>128.3971264653687</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>144.4827729017885</v>
+        <v>123.4301413228411</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>143.8519740872632</v>
+        <v>123.8519740872632</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>145.3687981544141</v>
+        <v>126.321179106795</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>147.1862680351892</v>
+        <v>129.0044498533711</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>148.6378647030212</v>
+        <v>131.2465603551951</v>
       </c>
       <c r="N31" s="19" t="n">
-        <v>149.7966284355429</v>
+        <v>133.1299617688762</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>152.8287304087909</v>
+        <v>133.5979611780216</v>
       </c>
     </row>
     <row r="32" ht="15.5" customHeight="1">
@@ -8318,40 +8318,40 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>22252.73250161936</v>
+        <v>370.2477016193639</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>483.247857137535</v>
+        <v>423.364557137535</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>28613.36661002623</v>
+        <v>468.9932100262264</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>583.7146611798021</v>
+        <v>513.070061179802</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>653.2753538218418</v>
+        <v>578.2192538218418</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>721.8651189374614</v>
+        <v>616.6819189374613</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>788.1477037872246</v>
+        <v>678.5701037872245</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>883.7299226978641</v>
+        <v>767.9351226978642</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>978.6082320693972</v>
+        <v>857.7214320693972</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>1070.314062997215</v>
+        <v>945.0824629972152</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>1158.419270748015</v>
+        <v>1029.531270748015</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>1310.400300116478</v>
+        <v>1145.509800116478</v>
       </c>
     </row>
     <row r="34" ht="15.5" customHeight="1">
@@ -8371,40 +8371,40 @@
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>22252.73250161936</v>
+        <v>370.2477016193639</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>483.247857137535</v>
+        <v>423.364557137535</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>28613.36661002623</v>
+        <v>468.9932100262264</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>583.7146611798021</v>
+        <v>513.070061179802</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>653.2753538218418</v>
+        <v>578.2192538218418</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>721.8651189374614</v>
+        <v>616.6819189374613</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>788.1477037872246</v>
+        <v>678.5701037872245</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>883.7299226978641</v>
+        <v>767.9351226978642</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>978.6082320693972</v>
+        <v>857.7214320693972</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>1070.314062997215</v>
+        <v>945.0824629972152</v>
       </c>
       <c r="N34" s="19" t="n">
-        <v>1158.419270748015</v>
+        <v>1029.531270748015</v>
       </c>
       <c r="O34" s="19" t="n">
-        <v>1310.400300116478</v>
+        <v>1145.509800116478</v>
       </c>
     </row>
     <row r="35" ht="15.5" customHeight="1">
@@ -8477,40 +8477,40 @@
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>-6230.765100453422</v>
+        <v>-103.6693564534219</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>-135.3093999985098</v>
+        <v>-118.5420759985098</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-8011.742650807344</v>
+        <v>-131.3180988073434</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>-163.4401051303446</v>
+        <v>-143.6596171303446</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>-182.9170990701157</v>
+        <v>-161.9013910701157</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>-202.1222333024892</v>
+        <v>-172.6709373024892</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>-220.6813570604229</v>
+        <v>-189.9996290604229</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>-247.444378355402</v>
+        <v>-215.021834355402</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>-274.0103049794312</v>
+        <v>-240.1620009794312</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>-299.6879376392203</v>
+        <v>-264.6230896392203</v>
       </c>
       <c r="N36" s="19" t="n">
-        <v>-324.3573958094441</v>
+        <v>-288.2687558094441</v>
       </c>
       <c r="O36" s="19" t="n">
-        <v>-366.9120840326139</v>
+        <v>-320.7427440326139</v>
       </c>
     </row>
     <row r="37" ht="15.5" customHeight="1">
@@ -8583,40 +8583,40 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>16021.96740116594</v>
+        <v>266.578345165942</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>347.9384571390252</v>
+        <v>304.8224811390252</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>20601.62395921888</v>
+        <v>337.675111218883</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>420.2745560494575</v>
+        <v>369.4104440494574</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>470.3582547517261</v>
+        <v>416.3178627517261</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>519.7428856349723</v>
+        <v>444.0109816349722</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>567.4663467268017</v>
+        <v>488.5704747268016</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>636.2855443424621</v>
+        <v>552.9132883424622</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>704.597927089966</v>
+        <v>617.559431089966</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>770.6261253579951</v>
+        <v>680.459373357995</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>834.0618749385706</v>
+        <v>741.2625149385706</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>943.4882160838645</v>
+        <v>824.7670560838644</v>
       </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
@@ -8636,40 +8636,40 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>5798.883580955773</v>
+        <v>96.48358095577248</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>108.9426613322366</v>
+        <v>95.44266133223658</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>5541.655156323924</v>
+        <v>90.83162691215959</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>104.9848086426632</v>
+        <v>92.27892628972199</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>104.4459310550655</v>
+        <v>92.4459310550655</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>104.0275964892877</v>
+        <v>88.86970175244558</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>103.5734213428295</v>
+        <v>89.17342134282949</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>104.6655346711781</v>
+        <v>90.95124895689243</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>105.9741129853363</v>
+        <v>92.88320389442715</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>107.0192625861753</v>
+        <v>94.49752345574049</v>
       </c>
       <c r="N39" s="19" t="n">
-        <v>107.8535724735908</v>
+        <v>95.85357247359084</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>110.0366858943295</v>
+        <v>96.1905320481756</v>
       </c>
     </row>
     <row r="40" ht="15.5" customHeight="1">
@@ -8766,16 +8766,16 @@
         <v>2581.38007882974</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>2663.031069422604</v>
+        <v>2910.992827895477</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>2983.683012286244</v>
+        <v>3224.346968419068</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>3288.233015313682</v>
+        <v>3521.603050083695</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>3452.522549222511</v>
+        <v>3678.595110511465</v>
       </c>
     </row>
     <row r="42" ht="15.5" customHeight="1">
@@ -8819,16 +8819,16 @@
         <v>2581.38007882974</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>2663.031069422604</v>
+        <v>2910.992827895477</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>2983.683012286244</v>
+        <v>3224.346968419068</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>3288.233015313682</v>
+        <v>3521.603050083695</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>3452.522549222511</v>
+        <v>3678.595110511465</v>
       </c>
     </row>
     <row r="43" ht="15.5" customHeight="1">
@@ -8848,40 +8848,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>1830.861282523789</v>
+        <v>-8.167366672208189</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>42.6934018010603</v>
+        <v>-179.2694368813634</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>2355.89173150685</v>
+        <v>-358.1856245260058</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>2351.098949019179</v>
+        <v>-554.147088854773</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>4655.909591189042</v>
+        <v>-574.5329977290414</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>6960.628408701372</v>
+        <v>-497.4911208687323</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>9265.209834432881</v>
+        <v>-420.5241379658888</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>11572.30335331507</v>
+        <v>1930.250943202108</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>13879.31632425206</v>
+        <v>4252.403732939727</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>16076.34252461312</v>
+        <v>6588.89217996497</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>18217.34889229737</v>
+        <v>8980.413235063193</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>20377.47462933524</v>
+        <v>11415.53464132181</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -8901,40 +8901,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>0</v>
+        <v>-40.46825467544937</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>0</v>
+        <v>-217.0409236139305</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>0</v>
+        <v>-400.8411861698415</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>2297.987540800001</v>
+        <v>-601.4520915944991</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>4595.975081600001</v>
+        <v>-628.2985127975346</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>6893.962622400002</v>
+        <v>-555.5117126495542</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>9191.950163200003</v>
+        <v>-484.7774311165737</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>11489.937704</v>
+        <v>1857.402674708957</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>13787.9252448</v>
+        <v>4170.948554857536</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>15976.20388899668</v>
+        <v>6499.04655256771</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>18108.77652519336</v>
+        <v>8882.434402205754</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>20255.38768139004</v>
+        <v>11307.00033721222</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -9007,40 +9007,40 @@
         </is>
       </c>
       <c r="D46" s="18" t="n">
-        <v>1808.152186633378</v>
+        <v>9.591792112830227</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>16.44318810243016</v>
+        <v>11.52127303393701</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>2325.336164383562</v>
+        <v>12.09999452054795</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>20.20844383561644</v>
+        <v>14.40203835616439</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>22.92054246575343</v>
+        <v>16.75154794520548</v>
       </c>
       <c r="I46" s="18" t="n">
-        <v>25.60111232876713</v>
+        <v>16.95591780821918</v>
       </c>
       <c r="J46" s="18" t="n">
-        <v>28.22778082191781</v>
+        <v>19.22140273972603</v>
       </c>
       <c r="K46" s="18" t="n">
-        <v>32.3994</v>
+        <v>22.88201917808219</v>
       </c>
       <c r="L46" s="18" t="n">
-        <v>36.74362191780821</v>
+        <v>26.8077205479452</v>
       </c>
       <c r="M46" s="18" t="n">
-        <v>40.95383835616439</v>
+        <v>30.6608301369863</v>
       </c>
       <c r="N46" s="18" t="n">
-        <v>45.01116162456164</v>
+        <v>34.41762737798631</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>51.61320000000001</v>
+        <v>38.06055616438356</v>
       </c>
     </row>
     <row r="47" ht="15.5" customHeight="1">
@@ -9060,40 +9060,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>2118.72429813952</v>
+        <v>279.6956489435228</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>685.2818150767414</v>
+        <v>463.3189763943177</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>3338.28422341972</v>
+        <v>624.2068673868639</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>3658.518481736704</v>
+        <v>753.2724438627512</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>6273.731765257012</v>
+        <v>1043.289176338928</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>8874.370232660121</v>
+        <v>1416.250703090017</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>11500.55264243714</v>
+        <v>1814.818670038372</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>14153.68343214481</v>
+        <v>4511.631022031847</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>16542.34739367466</v>
+        <v>7163.396560835204</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>19060.02553689936</v>
+        <v>9813.239148384038</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>21505.58190761106</v>
+        <v>12502.01628514689</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>23829.99717855775</v>
+        <v>15094.12975183327</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -9113,40 +9113,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>3904.167388882484</v>
+        <v>266.578345165942</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>675.4747894805382</v>
+        <v>571.4008263049672</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>5633.064820679988</v>
+        <v>749.9305935238502</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>1347.836420388751</v>
+        <v>892.7258259997379</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>2953.840224598421</v>
+        <v>1003.141134528266</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>4885.020004966224</v>
+        <v>4898.617371435184</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>6825.488672054733</v>
+        <v>1709.084383025935</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>8777.339993874184</v>
+        <v>6750.73211072686</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>10697.15163650017</v>
+        <v>3807.955272608856</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>7621.526769475863</v>
+        <v>5773.848255560788</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>13160.94430487512</v>
+        <v>7721.91877303045</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>10518.85857273565</v>
+        <v>9568.641779630152</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -9219,40 +9219,40 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>3904.167388882484</v>
+        <v>266.578345165942</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>-3228.692599401946</v>
+        <v>304.8224811390252</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>4957.59003119945</v>
+        <v>337.675111218883</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>-4285.228400291237</v>
+        <v>329.6311284758876</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>315.82683861072</v>
+        <v>315.1016605285281</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>301.2807896168069</v>
+        <v>296.3283896168069</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>326.8543210318118</v>
+        <v>326.1319539085242</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>354.3805091816442</v>
+        <v>353.3585037021921</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>338.3011929013531</v>
+        <v>337.4641518054627</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>321.7745734003036</v>
+        <v>321.0603597016734</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>305.3707282014215</v>
+        <v>304.769676146627</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>170.1961371786463</v>
+        <v>164.2779180005641</v>
       </c>
     </row>
     <row r="51" ht="15.5" customHeight="1">
@@ -9275,37 +9275,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>3904.167388882484</v>
+        <v>266.578345165942</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>675.4747894805378</v>
+        <v>412.2554823049672</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>5633.064820679988</v>
+        <v>563.0946975238503</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>2638.013385987701</v>
+        <v>688.0394739997377</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>4583.739215349417</v>
+        <v>4602.288981818378</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>6498.634351022921</v>
+        <v>1382.952429117411</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>8422.959484692539</v>
+        <v>6397.373607024668</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>10358.85044359881</v>
+        <v>3470.491120803393</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>7299.752196075559</v>
+        <v>5452.787895859115</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>12855.57357667369</v>
+        <v>7417.149096883823</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>10348.662435557</v>
+        <v>9404.363861629588</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -9331,34 +9331,34 @@
         <v>0</v>
       </c>
       <c r="F52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="18" t="n">
         <v>-1290.176965598953</v>
       </c>
-      <c r="G52" s="18" t="n">
+      <c r="K52" s="18" t="n">
         <v>-1278.65628434995</v>
       </c>
-      <c r="H52" s="18" t="n">
+      <c r="L52" s="18" t="n">
         <v>-1250.850958406641</v>
       </c>
-      <c r="I52" s="18" t="n">
+      <c r="M52" s="18" t="n">
         <v>-1206.902099044447</v>
       </c>
-      <c r="J52" s="18" t="n">
+      <c r="N52" s="18" t="n">
         <v>-1146.99287676908</v>
       </c>
-      <c r="K52" s="18" t="n">
+      <c r="O52" s="18" t="n">
         <v>27.56010391590189</v>
-      </c>
-      <c r="L52" s="18" t="n">
-        <v>-162.300607879974</v>
-      </c>
-      <c r="M52" s="18" t="n">
-        <v>-506.8604250494029</v>
-      </c>
-      <c r="N52" s="18" t="n">
-        <v>-831.0141990278089</v>
-      </c>
-      <c r="O52" s="18" t="n">
-        <v>-1134.919330769903</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -9384,34 +9384,34 @@
         <v>0</v>
       </c>
       <c r="F53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="18" t="n">
         <v>-1290.176965598953</v>
       </c>
-      <c r="G53" s="18" t="n">
+      <c r="K53" s="18" t="n">
         <v>-1278.65628434995</v>
       </c>
-      <c r="H53" s="18" t="n">
+      <c r="L53" s="18" t="n">
         <v>-1250.850958406641</v>
       </c>
-      <c r="I53" s="18" t="n">
+      <c r="M53" s="18" t="n">
         <v>-1206.902099044447</v>
       </c>
-      <c r="J53" s="18" t="n">
+      <c r="N53" s="18" t="n">
         <v>-1146.99287676908</v>
       </c>
-      <c r="K53" s="18" t="n">
+      <c r="O53" s="18" t="n">
         <v>27.56010391590189</v>
-      </c>
-      <c r="L53" s="18" t="n">
-        <v>-162.300607879974</v>
-      </c>
-      <c r="M53" s="18" t="n">
-        <v>-506.8604250494029</v>
-      </c>
-      <c r="N53" s="18" t="n">
-        <v>-831.0141990278089</v>
-      </c>
-      <c r="O53" s="18" t="n">
-        <v>-1134.919330769903</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -9484,40 +9484,40 @@
         </is>
       </c>
       <c r="D55" s="18" t="n">
-        <v>-1808.152186633378</v>
+        <v>-9.591792112830227</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>-16.44318810243016</v>
+        <v>-11.52127303393701</v>
       </c>
       <c r="F55" s="18" t="n">
-        <v>-2325.336164383562</v>
+        <v>-12.09999452054795</v>
       </c>
       <c r="G55" s="18" t="n">
-        <v>-20.20844383561644</v>
+        <v>-14.40203835616439</v>
       </c>
       <c r="H55" s="18" t="n">
-        <v>-22.92054246575343</v>
+        <v>-16.75154794520548</v>
       </c>
       <c r="I55" s="18" t="n">
-        <v>-25.60111232876713</v>
+        <v>-16.95591780821918</v>
       </c>
       <c r="J55" s="18" t="n">
-        <v>-28.22778082191781</v>
+        <v>-19.22140273972603</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>-32.3994</v>
+        <v>-22.88201917808219</v>
       </c>
       <c r="L55" s="18" t="n">
-        <v>-36.74362191780821</v>
+        <v>-26.8077205479452</v>
       </c>
       <c r="M55" s="18" t="n">
-        <v>-40.95383835616439</v>
+        <v>-30.6608301369863</v>
       </c>
       <c r="N55" s="18" t="n">
-        <v>-45.01116162456164</v>
+        <v>-34.41762737798631</v>
       </c>
       <c r="O55" s="18" t="n">
-        <v>-51.61320000000001</v>
+        <v>-38.06055616438356</v>
       </c>
     </row>
     <row r="56" ht="15.5" customHeight="1">
@@ -9537,40 +9537,40 @@
         </is>
       </c>
       <c r="D56" s="18" t="n">
-        <v>-1808.152186633378</v>
+        <v>-9.591792112830227</v>
       </c>
       <c r="E56" s="18" t="n">
-        <v>-16.44318810243016</v>
+        <v>-11.52127303393701</v>
       </c>
       <c r="F56" s="18" t="n">
-        <v>-2325.336164383562</v>
+        <v>-12.09999452054795</v>
       </c>
       <c r="G56" s="18" t="n">
-        <v>-20.20844383561644</v>
+        <v>-14.40203835616439</v>
       </c>
       <c r="H56" s="18" t="n">
-        <v>-22.92054246575343</v>
+        <v>-16.75154794520548</v>
       </c>
       <c r="I56" s="18" t="n">
-        <v>-25.60111232876713</v>
+        <v>-16.95591780821918</v>
       </c>
       <c r="J56" s="18" t="n">
-        <v>-28.22778082191781</v>
+        <v>-19.22140273972603</v>
       </c>
       <c r="K56" s="18" t="n">
-        <v>-32.3994</v>
+        <v>-22.88201917808219</v>
       </c>
       <c r="L56" s="18" t="n">
-        <v>-36.74362191780821</v>
+        <v>-26.8077205479452</v>
       </c>
       <c r="M56" s="18" t="n">
-        <v>-40.95383835616439</v>
+        <v>-30.6608301369863</v>
       </c>
       <c r="N56" s="18" t="n">
-        <v>-45.01116162456164</v>
+        <v>-34.41762737798631</v>
       </c>
       <c r="O56" s="18" t="n">
-        <v>-51.61320000000001</v>
+        <v>-38.06055616438356</v>
       </c>
     </row>
     <row r="57" ht="15.5" customHeight="1">
@@ -9643,40 +9643,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>2096.015202249106</v>
+        <v>256.9865530531118</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>659.031601378108</v>
+        <v>559.8795532710301</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>2017.551690697473</v>
+        <v>737.8305990033023</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>48.97169220318482</v>
+        <v>878.3237876435735</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>1680.068723726026</v>
+        <v>986.3895865830602</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>3652.51679359301</v>
+        <v>4881.661453626965</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>5650.268014463735</v>
+        <v>399.6860146872561</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>8772.500697790087</v>
+        <v>5449.193807198827</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>10498.10740670239</v>
+        <v>2530.29659365427</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>7073.712506070297</v>
+        <v>4536.285326379355</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>12284.91894422275</v>
+        <v>6540.508268883384</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>9332.326041965745</v>
+        <v>9558.141327381671</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -9696,40 +9696,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>22.70909589041412</v>
+        <v>22.70909589041099</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>26.25021369863339</v>
+        <v>-96.56057687671239</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>1320.732532722247</v>
+        <v>-113.6237316164384</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>3609.546789533519</v>
+        <v>-125.0513437808223</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>4593.663041530986</v>
+        <v>56.89958975586819</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>5221.853439067111</v>
+        <v>-3465.410750536948</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>5850.284627973407</v>
+        <v>1415.132655351116</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>5381.182734354721</v>
+        <v>-937.5627851669797</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>6044.239986972274</v>
+        <v>4633.099967180934</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>11986.31303082907</v>
+        <v>5276.953822004683</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>9220.662963388311</v>
+        <v>5961.508016263505</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>14497.67113659201</v>
+        <v>5535.988424451602</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -9802,40 +9802,40 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>22261.66423737277</v>
+        <v>379.1794373727678</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>503.4675085795669</v>
+        <v>443.5842085795669</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>28644.76143</v>
+        <v>500.3880300000001</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>626.1728300000001</v>
+        <v>555.52823</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>706.68637</v>
+        <v>631.63027</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>786.1193900000001</v>
+        <v>680.93619</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>863.9316</v>
+        <v>754.3539999999999</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>971.719265</v>
+        <v>855.9244650000001</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>1078.68093</v>
+        <v>957.79413</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>1182.349315</v>
+        <v>1057.117715</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>1282.2973997655</v>
+        <v>1153.4093997655</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>1442.51967</v>
+        <v>1277.62917</v>
       </c>
     </row>
     <row r="62" ht="15.5" customHeight="1">
@@ -9855,40 +9855,40 @@
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>-6230.765100453422</v>
+        <v>-103.6693564534219</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>-135.3093999985098</v>
+        <v>-118.5420759985098</v>
       </c>
       <c r="F62" s="18" t="n">
-        <v>-8011.742650807344</v>
+        <v>-131.3180988073434</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>-163.4401051303446</v>
+        <v>-143.6596171303446</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>-182.9170990701157</v>
+        <v>-161.9013910701157</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>-202.1222333024892</v>
+        <v>-172.6709373024892</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>-220.6813570604229</v>
+        <v>-189.9996290604229</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>-247.444378355402</v>
+        <v>-215.021834355402</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>-274.0103049794312</v>
+        <v>-240.1620009794312</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>-299.6879376392203</v>
+        <v>-264.6230896392203</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>-324.3573958094441</v>
+        <v>-288.2687558094441</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>-366.9120840326139</v>
+        <v>-320.7427440326139</v>
       </c>
     </row>
     <row r="63" ht="15.5" customHeight="1">
@@ -9908,40 +9908,40 @@
         </is>
       </c>
       <c r="D63" s="18" t="n">
-        <v>-3616.304373266757</v>
+        <v>-19.18358422566045</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>3583.417997061896</v>
+        <v>-3.858961842213564</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>-4617.785952562263</v>
+        <v>-1.157442973221876</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>4610.255441095891</v>
+        <v>-4.604087671232886</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>-5.424197260273971</v>
+        <v>-4.699019178082182</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>-5.361139726027396</v>
+        <v>-0.4087397260273917</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>-5.25333698630137</v>
+        <v>-4.530969863013709</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>-8.343238356164377</v>
+        <v>-7.321232876712322</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>-8.688443835616425</v>
+        <v>-7.851402739726019</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>-8.420432876712354</v>
+        <v>-7.706219178082193</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>-8.11464653679451</v>
+        <v>-7.513594482000016</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>-13.20407675087672</v>
+        <v>-7.285857572794512</v>
       </c>
     </row>
     <row r="64" ht="15.5" customHeight="1">
@@ -9961,40 +9961,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>12414.59476365259</v>
+        <v>256.3264966936854</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>3951.576105642953</v>
+        <v>321.1831707388436</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>16015.2328266304</v>
+        <v>367.9124882194349</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>5072.988165965547</v>
+        <v>407.2645251984225</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>518.3450736696103</v>
+        <v>465.0298597518022</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>578.6360169714835</v>
+        <v>507.8565129714834</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>637.9969059532757</v>
+        <v>559.8234010765633</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>715.9316482884335</v>
+        <v>633.5813977678857</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>795.9821811849523</v>
+        <v>709.7807262808427</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>874.2409444840675</v>
+        <v>784.7884061826976</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>949.8253574192613</v>
+        <v>857.6270494740558</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>1062.40350921651</v>
+        <v>949.600568394592</v>
       </c>
     </row>
     <row r="65" ht="15.5" customHeight="1">
@@ -10120,40 +10120,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>12117.80001228346</v>
+        <v>-40.46825467544937</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>3576.631056540971</v>
+        <v>-53.76187836313863</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>15644.03392801943</v>
+        <v>-3.286410391527397</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>4705.502956340694</v>
+        <v>39.77931557356982</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>154.5314161410062</v>
+        <v>101.216202223198</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>218.4620960181653</v>
+        <v>147.6825920181652</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>240.6120256949899</v>
+        <v>162.4385208182775</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>281.9050351608179</v>
+        <v>199.5547846402701</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>366.2967341886129</v>
+        <v>280.0952792845033</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>448.8515519576915</v>
+        <v>359.3990136563216</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>528.6911467371491</v>
+        <v>436.4928387919435</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>773.2920789052182</v>
+        <v>660.4891380833003</v>
       </c>
     </row>
     <row r="68" ht="15.5" customHeight="1">
@@ -10385,40 +10385,40 @@
         </is>
       </c>
       <c r="D72" s="18" t="n">
-        <v>-12117.80001228346</v>
+        <v>0</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>-3576.631056540971</v>
+        <v>0</v>
       </c>
       <c r="F72" s="18" t="n">
-        <v>-15644.03392801943</v>
+        <v>0</v>
       </c>
       <c r="G72" s="18" t="n">
-        <v>-4705.502956340694</v>
+        <v>-39.77931557356982</v>
       </c>
       <c r="H72" s="18" t="n">
-        <v>-154.5314161410062</v>
+        <v>-101.216202223198</v>
       </c>
       <c r="I72" s="18" t="n">
-        <v>-218.4620960181653</v>
+        <v>-147.6825920181652</v>
       </c>
       <c r="J72" s="18" t="n">
-        <v>-240.6120256949899</v>
+        <v>-162.4385208182775</v>
       </c>
       <c r="K72" s="18" t="n">
-        <v>-281.9050351608179</v>
+        <v>-199.5547846402701</v>
       </c>
       <c r="L72" s="18" t="n">
-        <v>-366.2967341886129</v>
+        <v>-280.0952792845033</v>
       </c>
       <c r="M72" s="18" t="n">
-        <v>-448.8515519576915</v>
+        <v>-359.3990136563216</v>
       </c>
       <c r="N72" s="18" t="n">
-        <v>-528.6911467371491</v>
+        <v>-436.4928387919435</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>-773.2920789052182</v>
+        <v>-660.4891380833003</v>
       </c>
     </row>
     <row r="73" ht="15.5" customHeight="1">
@@ -10491,40 +10491,40 @@
         </is>
       </c>
       <c r="D74" s="18" t="n">
-        <v>-12117.80001228346</v>
+        <v>0</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>-3576.631056540971</v>
+        <v>0</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>-15644.03392801943</v>
+        <v>0</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>-4705.502956340694</v>
+        <v>-39.77931557356982</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>-154.5314161410062</v>
+        <v>-101.216202223198</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>-218.4620960181653</v>
+        <v>-147.6825920181652</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>-240.6120256949899</v>
+        <v>-162.4385208182775</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>-281.9050351608179</v>
+        <v>-199.5547846402701</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>-366.2967341886129</v>
+        <v>-280.0952792845033</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>-448.8515519576915</v>
+        <v>-359.3990136563216</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>-528.6911467371491</v>
+        <v>-436.4928387919435</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>-773.2920789052182</v>
+        <v>-660.4891380833003</v>
       </c>
     </row>
     <row r="75" ht="15.5" customHeight="1">
@@ -10544,13 +10544,13 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>0</v>
+        <v>-40.46825467544937</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>0</v>
+        <v>-53.76187836313863</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>0</v>
+        <v>-3.286410391527397</v>
       </c>
       <c r="G75" s="18" t="n">
         <v>0</v>
@@ -10600,37 +10600,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>0</v>
+        <v>-40.46825467544937</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>0</v>
+        <v>-217.0409236139305</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0</v>
+        <v>-400.8411861698415</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>2297.987540800001</v>
+        <v>-601.4520915944991</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>4595.975081600001</v>
+        <v>-628.2985127975346</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>6893.962622400002</v>
+        <v>-555.5117126495542</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>9191.950163200003</v>
+        <v>-484.7774311165737</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>11489.937704</v>
+        <v>1857.402674708957</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>13787.9252448</v>
+        <v>4170.948554857536</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>15976.20388899668</v>
+        <v>6499.04655256771</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>18108.77652519336</v>
+        <v>8882.434402205754</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -10650,13 +10650,13 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>0</v>
+        <v>-40.46825467544937</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>0</v>
+        <v>-53.76187836313863</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>0</v>
+        <v>-3.286410391527397</v>
       </c>
       <c r="G77" s="18" t="n">
         <v>0</v>
@@ -10703,40 +10703,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>0</v>
+        <v>-40.46825467544937</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>0</v>
+        <v>-217.0409236139305</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>0</v>
+        <v>-400.8411861698415</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>2297.987540800001</v>
+        <v>-601.4520915944991</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>4595.975081600001</v>
+        <v>-628.2985127975346</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>6893.962622400002</v>
+        <v>-555.5117126495542</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>9191.950163200003</v>
+        <v>-484.7774311165737</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>11489.937704</v>
+        <v>1857.402674708957</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>13787.9252448</v>
+        <v>4170.948554857536</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>15976.20388899668</v>
+        <v>6499.04655256771</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>18108.77652519336</v>
+        <v>8882.434402205754</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>20255.38768139004</v>
+        <v>11307.00033721222</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -10942,13 +10942,13 @@
         <v>2581.38007882974</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>2663.031069422604</v>
+        <v>2910.992827895477</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>2983.683012286244</v>
+        <v>3224.346968419068</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>3288.233015313682</v>
+        <v>3521.603050083695</v>
       </c>
     </row>
     <row r="83" ht="15.5" customHeight="1">
@@ -11098,16 +11098,16 @@
         <v>2581.38007882974</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>2663.031069422604</v>
+        <v>2910.992827895477</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>2983.683012286244</v>
+        <v>3224.346968419068</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>3288.233015313682</v>
+        <v>3521.603050083695</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>3452.522549222511</v>
+        <v>3678.595110511465</v>
       </c>
     </row>
     <row r="86" ht="15.5" customHeight="1">
@@ -11233,40 +11233,40 @@
         </is>
       </c>
       <c r="D88" s="18" t="n">
-        <v>1808.152186633378</v>
+        <v>9.591792112830227</v>
       </c>
       <c r="E88" s="18" t="n">
-        <v>16.44318810243016</v>
+        <v>11.52127303393701</v>
       </c>
       <c r="F88" s="18" t="n">
-        <v>2325.336164383562</v>
+        <v>12.09999452054795</v>
       </c>
       <c r="G88" s="18" t="n">
-        <v>20.20844383561644</v>
+        <v>14.40203835616439</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>22.92054246575343</v>
+        <v>16.75154794520548</v>
       </c>
       <c r="I88" s="18" t="n">
-        <v>25.60111232876713</v>
+        <v>16.95591780821918</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>28.22778082191781</v>
+        <v>19.22140273972603</v>
       </c>
       <c r="K88" s="18" t="n">
-        <v>32.3994</v>
+        <v>22.88201917808219</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>36.74362191780821</v>
+        <v>26.8077205479452</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>40.95383835616439</v>
+        <v>30.6608301369863</v>
       </c>
       <c r="N88" s="18" t="n">
-        <v>45.01116162456164</v>
+        <v>34.41762737798631</v>
       </c>
       <c r="O88" s="18" t="n">
-        <v>51.61320000000001</v>
+        <v>38.06055616438356</v>
       </c>
     </row>
     <row r="89" ht="15.5" customHeight="1">
@@ -11286,40 +11286,40 @@
         </is>
       </c>
       <c r="D89" s="18" t="n">
-        <v>1808.152186633378</v>
+        <v>9.591792112830227</v>
       </c>
       <c r="E89" s="18" t="n">
-        <v>16.44318810243016</v>
+        <v>11.52127303393701</v>
       </c>
       <c r="F89" s="18" t="n">
-        <v>2325.336164383562</v>
+        <v>12.09999452054795</v>
       </c>
       <c r="G89" s="18" t="n">
-        <v>20.20844383561644</v>
+        <v>14.40203835616439</v>
       </c>
       <c r="H89" s="18" t="n">
-        <v>22.92054246575343</v>
+        <v>16.75154794520548</v>
       </c>
       <c r="I89" s="18" t="n">
-        <v>25.60111232876713</v>
+        <v>16.95591780821918</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>28.22778082191781</v>
+        <v>19.22140273972603</v>
       </c>
       <c r="K89" s="18" t="n">
-        <v>32.3994</v>
+        <v>22.88201917808219</v>
       </c>
       <c r="L89" s="18" t="n">
-        <v>36.74362191780821</v>
+        <v>26.8077205479452</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>40.95383835616439</v>
+        <v>30.6608301369863</v>
       </c>
       <c r="N89" s="18" t="n">
-        <v>45.01116162456164</v>
+        <v>34.41762737798631</v>
       </c>
       <c r="O89" s="18" t="n">
-        <v>51.61320000000001</v>
+        <v>38.06055616438356</v>
       </c>
     </row>
     <row r="90" ht="15.5" customHeight="1">
@@ -11339,40 +11339,40 @@
         </is>
       </c>
       <c r="D90" s="18" t="n">
-        <v>3616.304373266757</v>
+        <v>19.18358422566045</v>
       </c>
       <c r="E90" s="18" t="n">
-        <v>32.88637620486032</v>
+        <v>23.04254606787402</v>
       </c>
       <c r="F90" s="18" t="n">
-        <v>4650.672328767124</v>
+        <v>24.19998904109589</v>
       </c>
       <c r="G90" s="18" t="n">
-        <v>40.41688767123289</v>
+        <v>28.80407671232878</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>45.84108493150686</v>
+        <v>33.50309589041096</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>51.20222465753425</v>
+        <v>33.91183561643835</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>56.45556164383562</v>
+        <v>38.44280547945206</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>64.7988</v>
+        <v>45.76403835616438</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>73.48724383561643</v>
+        <v>53.6154410958904</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>81.90767671232878</v>
+        <v>61.3216602739726</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>90.02232324912329</v>
+        <v>68.83525475597261</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>103.2264</v>
+        <v>76.12111232876713</v>
       </c>
     </row>
     <row r="91" ht="15.5" customHeight="1">
@@ -11392,40 +11392,40 @@
         </is>
       </c>
       <c r="D91" s="18" t="n">
-        <v>3616.304373266757</v>
+        <v>19.18358422566045</v>
       </c>
       <c r="E91" s="18" t="n">
-        <v>-3583.417997061896</v>
+        <v>3.858961842213564</v>
       </c>
       <c r="F91" s="18" t="n">
-        <v>4617.785952562263</v>
+        <v>1.157442973221876</v>
       </c>
       <c r="G91" s="18" t="n">
-        <v>-4610.255441095891</v>
+        <v>4.604087671232886</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>5.424197260273971</v>
+        <v>4.699019178082182</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>5.361139726027396</v>
+        <v>0.4087397260273917</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>5.25333698630137</v>
+        <v>4.530969863013709</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>8.343238356164377</v>
+        <v>7.321232876712322</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>8.688443835616425</v>
+        <v>7.851402739726019</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>8.420432876712354</v>
+        <v>7.706219178082193</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>8.11464653679451</v>
+        <v>7.513594482000016</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>13.20407675087672</v>
+        <v>7.285857572794512</v>
       </c>
     </row>
     <row r="92" ht="15.5" customHeight="1">
@@ -11684,37 +11684,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>28139.7674134494</v>
+        <v>266.578345165942</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>32064.3369271294</v>
+        <v>412.2554823049672</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>68309.99481436772</v>
+        <v>563.0946975238503</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>75382.51716115681</v>
+        <v>767.5981051468773</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>78293.87369160056</v>
+        <v>29040.32141083169</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>81302.26088811038</v>
+        <v>33067.17975080261</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>84364.37794196999</v>
+        <v>69399.18064234895</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>87520.64683999791</v>
+        <v>76614.10446525304</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>61848.35872108494</v>
+        <v>79723.11293067926</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>61827.54338400126</v>
+        <v>82939.57366128392</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>29768.86897180479</v>
+        <v>86218.76799649093</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -11787,40 +11787,40 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>16021.96740116594</v>
+        <v>266.578345165942</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>347.9384571390252</v>
+        <v>304.8224811390252</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>20601.62395921888</v>
+        <v>337.675111218883</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>420.2745560494575</v>
+        <v>369.4104440494574</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>470.3582547517261</v>
+        <v>416.3178627517261</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>519.7428856349723</v>
+        <v>444.0109816349722</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>567.4663467268017</v>
+        <v>488.5704747268016</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>636.2855443424621</v>
+        <v>552.9132883424622</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>704.597927089966</v>
+        <v>617.559431089966</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>770.6261253579951</v>
+        <v>680.459373357995</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>834.0618749385706</v>
+        <v>741.2625149385706</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>943.4882160838645</v>
+        <v>824.7670560838644</v>
       </c>
     </row>
     <row r="99" ht="15.5" customHeight="1">
@@ -11840,40 +11840,40 @@
         </is>
       </c>
       <c r="D99" s="20" t="n">
-        <v>12117.80001228346</v>
+        <v>0</v>
       </c>
       <c r="E99" s="20" t="n">
-        <v>3576.631056540971</v>
+        <v>0</v>
       </c>
       <c r="F99" s="20" t="n">
-        <v>15644.03392801943</v>
+        <v>0</v>
       </c>
       <c r="G99" s="20" t="n">
-        <v>4705.502956340694</v>
+        <v>39.77931557356982</v>
       </c>
       <c r="H99" s="20" t="n">
-        <v>154.5314161410062</v>
+        <v>101.216202223198</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>218.4620960181653</v>
+        <v>147.6825920181652</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>240.6120256949899</v>
+        <v>162.4385208182775</v>
       </c>
       <c r="K99" s="20" t="n">
-        <v>281.9050351608179</v>
+        <v>199.5547846402701</v>
       </c>
       <c r="L99" s="20" t="n">
-        <v>366.2967341886129</v>
+        <v>280.0952792845033</v>
       </c>
       <c r="M99" s="20" t="n">
-        <v>448.8515519576915</v>
+        <v>359.3990136563216</v>
       </c>
       <c r="N99" s="20" t="n">
-        <v>528.6911467371491</v>
+        <v>436.4928387919435</v>
       </c>
       <c r="O99" s="20" t="n">
-        <v>773.2920789052182</v>
+        <v>660.4891380833003</v>
       </c>
     </row>
     <row r="100" ht="15.5" customHeight="1">
@@ -11893,40 +11893,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>28139.7674134494</v>
+        <v>266.578345165942</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>32064.3369271294</v>
+        <v>412.2554823049672</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>68309.99481436772</v>
+        <v>563.0946975238503</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>75382.51716115681</v>
+        <v>767.5981051468773</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>78293.87369160056</v>
+        <v>29040.32141083169</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>81302.26088811038</v>
+        <v>33067.17975080261</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>84364.37794196999</v>
+        <v>69399.18064234895</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>87520.64683999791</v>
+        <v>76614.10446525304</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>61848.35872108494</v>
+        <v>79723.11293067926</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>61827.54338400126</v>
+        <v>82939.57366128392</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>29768.86897180479</v>
+        <v>86218.76799649093</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>29162.96119886453</v>
+        <v>89761.2222495516</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -12061,31 +12061,31 @@
         <v>0</v>
       </c>
       <c r="G103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="18" t="n">
         <v>-1290.176965598953</v>
       </c>
-      <c r="H103" s="18" t="n">
+      <c r="L103" s="18" t="n">
         <v>-1278.65628434995</v>
       </c>
-      <c r="I103" s="18" t="n">
+      <c r="M103" s="18" t="n">
         <v>-1250.850958406641</v>
       </c>
-      <c r="J103" s="18" t="n">
+      <c r="N103" s="18" t="n">
         <v>-1206.902099044447</v>
       </c>
-      <c r="K103" s="18" t="n">
+      <c r="O103" s="18" t="n">
         <v>-1146.99287676908</v>
-      </c>
-      <c r="L103" s="18" t="n">
-        <v>27.56010391590189</v>
-      </c>
-      <c r="M103" s="18" t="n">
-        <v>-162.300607879974</v>
-      </c>
-      <c r="N103" s="18" t="n">
-        <v>-506.8604250494029</v>
-      </c>
-      <c r="O103" s="18" t="n">
-        <v>-831.0141990278089</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -12270,34 +12270,34 @@
         <v>0</v>
       </c>
       <c r="F107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="18" t="n">
         <v>-1290.176965598953</v>
       </c>
-      <c r="G107" s="18" t="n">
+      <c r="K107" s="18" t="n">
         <v>-1278.65628434995</v>
       </c>
-      <c r="H107" s="18" t="n">
+      <c r="L107" s="18" t="n">
         <v>-1250.850958406641</v>
       </c>
-      <c r="I107" s="18" t="n">
+      <c r="M107" s="18" t="n">
         <v>-1206.902099044447</v>
       </c>
-      <c r="J107" s="18" t="n">
+      <c r="N107" s="18" t="n">
         <v>-1146.99287676908</v>
       </c>
-      <c r="K107" s="18" t="n">
+      <c r="O107" s="18" t="n">
         <v>27.56010391590189</v>
-      </c>
-      <c r="L107" s="18" t="n">
-        <v>-162.300607879974</v>
-      </c>
-      <c r="M107" s="18" t="n">
-        <v>-506.8604250494029</v>
-      </c>
-      <c r="N107" s="18" t="n">
-        <v>-831.0141990278089</v>
-      </c>
-      <c r="O107" s="18" t="n">
-        <v>-1134.919330769903</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -14511,37 +14511,37 @@
         <v>-6.0134176766168</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>-3.944628576668756</v>
+        <v>-3.194656915685555</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-4.547865113057981</v>
+        <v>-0.4264374207435335</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>-7.61428820340508</v>
+        <v>0</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>-7.78280645948629</v>
+        <v>0</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>-11.3607307136299</v>
+        <v>0</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>-11.04287052320077</v>
+        <v>0</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>-25.35220145120468</v>
+        <v>0</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>-23.29802275572449</v>
+        <v>0</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>-26.30240837673337</v>
+        <v>-5.001647924063321</v>
       </c>
       <c r="N36" s="19" t="n">
-        <v>-24.11673518311109</v>
+        <v>-8.749014580773643</v>
       </c>
       <c r="O36" s="19" t="n">
-        <v>-26.76403143719218</v>
+        <v>-9.581525053961133</v>
       </c>
     </row>
     <row r="37" ht="15.5" customHeight="1">
@@ -14570,22 +14570,22 @@
         <v>0</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>0</v>
+        <v>-6.374935650897825</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>0</v>
+        <v>-24.43535405779248</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>0</v>
+        <v>-28.45933576721696</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>0</v>
+        <v>-41.12812829384985</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>0</v>
+        <v>-7.318789543136972</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>0</v>
+        <v>-2.019693740857704</v>
       </c>
       <c r="M37" s="19" t="n">
         <v>0</v>
@@ -14617,37 +14617,37 @@
         <v>15.46307402558606</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>10.14333062571966</v>
+        <v>10.89330228670286</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>11.69451029072052</v>
+        <v>15.81593798303497</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>19.57959823732735</v>
+        <v>27.19388644073243</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>20.01293089582189</v>
+        <v>27.79573735530818</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>29.21330754933403</v>
+        <v>40.57403826296393</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>28.39595277394485</v>
+        <v>39.43882329714562</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>65.19137516024063</v>
+        <v>90.5435766114453</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>59.90920137186296</v>
+        <v>83.20722412758745</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>67.6347643973144</v>
+        <v>88.93552484998445</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>62.01446189942853</v>
+        <v>77.38218250176597</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>68.82179512420846</v>
+        <v>86.00430150743952</v>
       </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
@@ -14670,37 +14670,37 @@
         <v>64.01613911377284</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>38.8203899678234</v>
+        <v>41.69066930884789</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>33.32546634370552</v>
+        <v>45.07016504709849</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>40.34150432187455</v>
+        <v>56.02986711371465</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>35.3342292160464</v>
+        <v>49.07531835562</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>41.17040687389147</v>
+        <v>57.18112065818259</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>36.37010694023569</v>
+        <v>50.51403741699401</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>61.06844571025972</v>
+        <v>84.81728570869404</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>57.36370653018285</v>
+        <v>79.67181462525396</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>60.72220949499167</v>
+        <v>79.84594342288014</v>
       </c>
       <c r="N39" s="19" t="n">
-        <v>56.9879410829362</v>
+        <v>71.11004630551012</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>59.79182217182992</v>
+        <v>74.7198455440523</v>
       </c>
     </row>
     <row r="40" ht="15.5" customHeight="1">
@@ -14882,37 +14882,37 @@
         <v>1.87915583285867</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>1.306189815473586</v>
+        <v>0.3072455867671769</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>1.546182466103809</v>
+        <v>-13.98246921935162</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>2.527520289535326</v>
+        <v>-33.32912504612766</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>2.63614903958727</v>
+        <v>-54.71391054238131</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>3.771006219956129</v>
+        <v>-68.71865956328276</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>3.726977608792998</v>
+        <v>-79.31974500731667</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>8.059561250160829</v>
+        <v>-90.35499814316215</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>7.461351210954594</v>
+        <v>-77.17007166529821</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>8.386041108054478</v>
+        <v>-66.41154793334337</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>7.748091200330567</v>
+        <v>-46.2747022541691</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>8.564852101388295</v>
+        <v>-51.71803913935377</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -14935,37 +14935,37 @@
         <v>0</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>0</v>
+        <v>-0.9989442287064092</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>0</v>
+        <v>-15.52865168545543</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>0</v>
+        <v>-35.85664533566298</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>0</v>
+        <v>-57.35005958196858</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>0</v>
+        <v>-72.48966578323888</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>0</v>
+        <v>-83.04672261610966</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>0</v>
+        <v>-98.41455939332297</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>0</v>
+        <v>-84.6314228762528</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>0</v>
+        <v>-74.79758904139786</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>0</v>
+        <v>-54.02279345449966</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>0</v>
+        <v>-60.28289124074206</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -15094,37 +15094,37 @@
         <v>4.382675521612235</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>8.09339186279229</v>
+        <v>7.09444763408588</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>12.27867514943578</v>
+        <v>-3.249976536019654</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>16.86851125352953</v>
+        <v>-18.98813408213345</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>20.25042930242152</v>
+        <v>-37.09963027954706</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>24.32493433960176</v>
+        <v>-48.16473144363712</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>25.93314353027282</v>
+        <v>-57.11357908583685</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>30.70682871992959</v>
+        <v>-67.70773067339339</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>30.36529281042614</v>
+        <v>-54.26613006582667</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>31.36303533023536</v>
+        <v>-43.43455371116249</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>30.61531439070415</v>
+        <v>-23.40747906379552</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>31.09521808939174</v>
+        <v>-29.18767315135032</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -15150,34 +15150,34 @@
         <v>5.104424374156288</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>8.056340429786161</v>
+        <v>3.08671752929893</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>11.41773686142101</v>
+        <v>-8.406072128144007</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>13.57606858255659</v>
+        <v>-28.04909393885968</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>16.43176741435227</v>
+        <v>-44.92590817747919</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>16.82587827879169</v>
+        <v>-60.67913995978952</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>21.21822690050123</v>
+        <v>-67.72415167506036</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>20.65884142905181</v>
+        <v>-82.6116661429013</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>21.4393944371938</v>
+        <v>-71.42968174919598</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>20.47513321843181</v>
+        <v>-59.82608527008934</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>20.73913520283469</v>
+        <v>-38.7590973924869</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -15256,31 +15256,31 @@
         <v>2.813271691466202</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>2.951916055629873</v>
+        <v>2.951916055629875</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>3.361396431634855</v>
+        <v>3.361396431634859</v>
       </c>
       <c r="H50" s="18" t="n">
         <v>2.15833172113571</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>2.855698831795682</v>
+        <v>2.855698831795685</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>0.3941108644394227</v>
+        <v>0.3941108644394262</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>4.392348621709537</v>
+        <v>4.39234862170953</v>
       </c>
       <c r="L50" s="18" t="n">
         <v>-0.5593854714494171</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>0.7805530081420073</v>
+        <v>0.7805530081419931</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>-0.9642612187619832</v>
+        <v>-0.9642612187619903</v>
       </c>
       <c r="O50" s="18" t="n">
         <v>0.2640019844028672</v>
@@ -15309,34 +15309,34 @@
         <v>2.291152682690086</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>5.104424374156288</v>
+        <v>0.134801473669055</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>8.056340429786157</v>
+        <v>-11.76746855977887</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>11.41773686142088</v>
+        <v>-30.20742565999539</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>13.57606858255659</v>
+        <v>-47.78160700927488</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>16.43176741435227</v>
+        <v>-61.07325082422894</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>16.82587827879169</v>
+        <v>-72.11650029676989</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>21.21822690050123</v>
+        <v>-82.05228067145188</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>20.65884142905179</v>
+        <v>-72.21023475733797</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>21.4393944371938</v>
+        <v>-58.86182405132735</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>20.47513321843182</v>
+        <v>-39.02309937688977</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -15680,34 +15680,34 @@
         <v>5.945813210737497</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>9.394416556559065</v>
+        <v>4.424793656071834</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>12.8793639127076</v>
+        <v>-6.944445076857416</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>15.59517442269535</v>
+        <v>-26.02998809872093</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>18.49284776699888</v>
+        <v>-42.86482782483258</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>19.51602210013568</v>
+        <v>-57.98899613844553</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>21.93274718513492</v>
+        <v>-67.00963139042666</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>21.7813915142616</v>
+        <v>-81.4891160576915</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>22.20819432968727</v>
+        <v>-70.66088185670252</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>21.67117820440262</v>
+        <v>-58.63004028411853</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>21.63475059541899</v>
+        <v>-37.86348199990259</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -15730,37 +15730,37 @@
         <v>1.985339335890408</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>2.147578652054793</v>
+        <v>1.148634423348383</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>2.884258592876712</v>
+        <v>-7.674770192091487</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>3.98914734082193</v>
+        <v>-12.04368900527604</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>4.655254879726172</v>
+        <v>-11.06964218082613</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>5.832086572602883</v>
+        <v>-5.299903618804542</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>6.417121430137133</v>
+        <v>0.8754170526086824</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>8.774081534794671</v>
+        <v>-0.698099282966723</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>8.583901296164534</v>
+        <v>27.22298599186484</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>9.154841000548092</v>
+        <v>27.22632814554003</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>8.944136186301527</v>
+        <v>35.22256122032301</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>9.46046749397275</v>
+        <v>8.675808848552268</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -15889,37 +15889,37 @@
         <v>-6.0134176766168</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>-3.944628576668756</v>
+        <v>-3.194656915685555</v>
       </c>
       <c r="F62" s="18" t="n">
-        <v>-4.547865113057981</v>
+        <v>-0.4264374207435335</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>-7.61428820340508</v>
+        <v>0</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>-7.78280645948629</v>
+        <v>0</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>-11.3607307136299</v>
+        <v>0</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>-11.04287052320077</v>
+        <v>0</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>-25.35220145120468</v>
+        <v>0</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>-23.29802275572449</v>
+        <v>0</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>-26.30240837673337</v>
+        <v>-5.001647924063321</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>-24.11673518311109</v>
+        <v>-8.749014580773643</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>-26.76403143719218</v>
+        <v>-9.581525053961133</v>
       </c>
     </row>
     <row r="63" ht="15.5" customHeight="1">
@@ -15995,37 +15995,37 @@
         <v>15.8542638665605</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>12.11131449869214</v>
+        <v>12.86128615967534</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>13.50280549425509</v>
+        <v>17.62423318656954</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>20.95757920263543</v>
+        <v>28.57186740604051</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>22.57335104802983</v>
+        <v>30.35615750751612</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>31.05594132251871</v>
+        <v>42.41667203614861</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>31.6564017845088</v>
+        <v>42.69927230770957</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>63.41698041866481</v>
+        <v>88.7691818698695</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>63.07593662354191</v>
+        <v>86.37395937926641</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>69.45106311049678</v>
+        <v>90.75182356316684</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>65.5651817611988</v>
+        <v>80.93290236353624</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>71.08569221742574</v>
+        <v>88.2681986006568</v>
       </c>
     </row>
     <row r="65" ht="15.5" customHeight="1">
@@ -16154,37 +16154,37 @@
         <v>13.17192134289597</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>7.330058934253456</v>
+        <v>8.080030595236657</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>8.74259423509065</v>
+        <v>12.86402192740509</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>16.21820180569249</v>
+        <v>23.83249000909757</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>17.85459917468618</v>
+        <v>25.63740563417247</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>26.35760871753835</v>
+        <v>37.71833943116825</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>28.00184190950542</v>
+        <v>39.04471243270619</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>60.79902653853109</v>
+        <v>86.15122798973577</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>60.46858684331238</v>
+        <v>83.76660959903687</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>66.85421138917239</v>
+        <v>88.15497184184245</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>62.97872311819051</v>
+        <v>78.34644372052796</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>68.5577931398056</v>
+        <v>85.74029952303665</v>
       </c>
     </row>
     <row r="68" ht="15.5" customHeight="1">
@@ -16419,37 +16419,37 @@
         <v>-13.17192134289597</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>-7.330058934253456</v>
+        <v>-8.080030595236657</v>
       </c>
       <c r="F72" s="18" t="n">
-        <v>-8.74259423509065</v>
+        <v>-12.86402192740509</v>
       </c>
       <c r="G72" s="18" t="n">
-        <v>-16.21820180569249</v>
+        <v>-23.83249000909757</v>
       </c>
       <c r="H72" s="18" t="n">
-        <v>-17.85459917468618</v>
+        <v>-25.63740563417247</v>
       </c>
       <c r="I72" s="18" t="n">
-        <v>-26.35760871753835</v>
+        <v>-37.71833943116825</v>
       </c>
       <c r="J72" s="18" t="n">
-        <v>-28.00184190950542</v>
+        <v>-39.04471243270619</v>
       </c>
       <c r="K72" s="18" t="n">
-        <v>-60.79902653853109</v>
+        <v>-86.15122798973577</v>
       </c>
       <c r="L72" s="18" t="n">
-        <v>-60.46858684331238</v>
+        <v>-83.76660959903687</v>
       </c>
       <c r="M72" s="18" t="n">
-        <v>-66.85421138917239</v>
+        <v>-88.15497184184245</v>
       </c>
       <c r="N72" s="18" t="n">
-        <v>-62.97872311819051</v>
+        <v>-78.34644372052796</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>-68.5577931398056</v>
+        <v>-85.74029952303665</v>
       </c>
     </row>
     <row r="73" ht="15.5" customHeight="1">
@@ -16525,37 +16525,37 @@
         <v>-13.17192134289597</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>-7.330058934253456</v>
+        <v>-8.080030595236657</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>-8.74259423509065</v>
+        <v>-12.86402192740509</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>-16.21820180569249</v>
+        <v>-23.83249000909757</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>-17.85459917468618</v>
+        <v>-25.63740563417247</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>-26.35760871753835</v>
+        <v>-37.71833943116825</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>-28.00184190950542</v>
+        <v>-39.04471243270619</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>-60.79902653853109</v>
+        <v>-86.15122798973577</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>-60.46858684331238</v>
+        <v>-83.76660959903687</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>-66.85421138917239</v>
+        <v>-88.15497184184245</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>-62.97872311819051</v>
+        <v>-78.34644372052796</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>-68.5577931398056</v>
+        <v>-85.74029952303665</v>
       </c>
     </row>
     <row r="75" ht="15.5" customHeight="1">
@@ -16634,34 +16634,34 @@
         <v>0</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>0</v>
+        <v>-0.9989442287064092</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0</v>
+        <v>-15.52865168545543</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>0</v>
+        <v>-35.85664533566298</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>0</v>
+        <v>-57.35005958196858</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>0</v>
+        <v>-72.48966578323888</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>0</v>
+        <v>-83.04672261610966</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>0</v>
+        <v>-98.41455939332297</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>0</v>
+        <v>-84.6314228762528</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>0</v>
+        <v>-74.79758904139786</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>0</v>
+        <v>-54.02279345449966</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -16737,37 +16737,37 @@
         <v>0</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>0</v>
+        <v>-0.9989442287064092</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>0</v>
+        <v>-15.52865168545543</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0</v>
+        <v>-35.85664533566298</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>0</v>
+        <v>-57.35005958196858</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>0</v>
+        <v>-72.48966578323888</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>0</v>
+        <v>-83.04672261610966</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>0</v>
+        <v>-98.41455939332297</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>0</v>
+        <v>-84.6314228762528</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>0</v>
+        <v>-74.79758904139786</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>0</v>
+        <v>-54.02279345449966</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>0</v>
+        <v>-60.28289124074206</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -17718,34 +17718,34 @@
         <v>28.63499536848203</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>46.10838492845514</v>
+        <v>16.29486266414237</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>120.2419698024263</v>
+        <v>13.96057529503132</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>9503.173980520645</v>
+        <v>17.45755435819974</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>9631.052010628353</v>
+        <v>29.837046944862</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>9797.281874129625</v>
+        <v>55.3673885924064</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>10000.03467522516</v>
+        <v>118.1585539412826</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>10291.04280007841</v>
+        <v>9582.006418967243</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>10603.67241264335</v>
+        <v>9712.798926486532</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>10990.40506554231</v>
+        <v>9898.29822634763</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>11375.16271087514</v>
+        <v>10100.87858501053</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -17821,37 +17821,37 @@
         <v>15.46307402558606</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>10.14333062571966</v>
+        <v>10.89330228670286</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>11.69451029072052</v>
+        <v>15.81593798303497</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>19.57959823732735</v>
+        <v>27.19388644073243</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>20.01293089582189</v>
+        <v>27.79573735530818</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>29.21330754933403</v>
+        <v>40.57403826296393</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>28.39595277394485</v>
+        <v>39.43882329714562</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>65.19137516024063</v>
+        <v>90.5435766114453</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>59.90920137186296</v>
+        <v>83.20722412758745</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>67.6347643973144</v>
+        <v>88.93552484998445</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>62.01446189942853</v>
+        <v>77.38218250176597</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>68.82179512420846</v>
+        <v>86.00430150743952</v>
       </c>
     </row>
     <row r="99" ht="15.5" customHeight="1">
@@ -17874,37 +17874,37 @@
         <v>13.17192134289597</v>
       </c>
       <c r="E99" s="20" t="n">
-        <v>7.330058934253456</v>
+        <v>8.080030595236657</v>
       </c>
       <c r="F99" s="20" t="n">
-        <v>8.74259423509065</v>
+        <v>12.86402192740509</v>
       </c>
       <c r="G99" s="20" t="n">
-        <v>16.21820180569249</v>
+        <v>23.83249000909757</v>
       </c>
       <c r="H99" s="20" t="n">
-        <v>17.85459917468618</v>
+        <v>25.63740563417247</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>26.35760871753835</v>
+        <v>37.71833943116825</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>28.00184190950542</v>
+        <v>39.04471243270619</v>
       </c>
       <c r="K99" s="20" t="n">
-        <v>60.79902653853109</v>
+        <v>86.15122798973577</v>
       </c>
       <c r="L99" s="20" t="n">
-        <v>60.46858684331238</v>
+        <v>83.76660959903687</v>
       </c>
       <c r="M99" s="20" t="n">
-        <v>66.85421138917239</v>
+        <v>88.15497184184245</v>
       </c>
       <c r="N99" s="20" t="n">
-        <v>62.97872311819051</v>
+        <v>78.34644372052796</v>
       </c>
       <c r="O99" s="20" t="n">
-        <v>68.5577931398056</v>
+        <v>85.74029952303665</v>
       </c>
     </row>
     <row r="100" ht="15.5" customHeight="1">
@@ -17927,37 +17927,37 @@
         <v>28.63499536848203</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>46.10838492845514</v>
+        <v>16.29486266414237</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>120.2419698024263</v>
+        <v>13.96057529503132</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>9503.173980520645</v>
+        <v>17.45755435819974</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>9631.052010628353</v>
+        <v>29.837046944862</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>9797.281874129625</v>
+        <v>55.3673885924064</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>10000.03467522516</v>
+        <v>118.1585539412826</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>10291.04280007841</v>
+        <v>9582.006418967243</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>10603.67241264335</v>
+        <v>9712.798926486532</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>10990.40506554231</v>
+        <v>9898.29822634763</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>11375.16271087514</v>
+        <v>10100.87858501053</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>11779.19535296211</v>
+        <v>10401.42130688306</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -19267,40 +19267,40 @@
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>21841.8494319501</v>
+        <v>110.0374107909106</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>429.5741946592129</v>
+        <v>129.466319117066</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>25866.31773309992</v>
+        <v>151.5983604044038</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>524.6558414609256</v>
+        <v>173.3622928737007</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>580.3123851538844</v>
+        <v>194.7690047440224</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>634.874481772546</v>
+        <v>215.8278073541014</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>688.0174121563156</v>
+        <v>236.3782579093316</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>736.7626071155125</v>
+        <v>251.6667741958902</v>
       </c>
       <c r="L12" s="18" t="n">
-        <v>781.5996823519375</v>
+        <v>263.727373556422</v>
       </c>
       <c r="M12" s="18" t="n">
-        <v>824.9540408350703</v>
+        <v>275.5937884492834</v>
       </c>
       <c r="N12" s="18" t="n">
-        <v>866.7572135468049</v>
+        <v>287.2888235416318</v>
       </c>
       <c r="O12" s="18" t="n">
-        <v>929.203376128581</v>
+        <v>296.7547141946269</v>
       </c>
     </row>
     <row r="13">
@@ -19323,37 +19323,37 @@
         <v>0</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>-98.03325173540097</v>
+        <v>17.65663894352576</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>5921.385375259802</v>
+        <v>17.09482546369885</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>-97.97166397291429</v>
+        <v>14.35631124983112</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>10.60820051826372</v>
+        <v>12.34796305210215</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>9.402194062115887</v>
+        <v>10.81219398217688</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>8.370620005925655</v>
+        <v>9.521688056402144</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>7.08487810016678</v>
+        <v>6.467818327192743</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>6.085688226220642</v>
+        <v>4.792289089041257</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>5.546875141079077</v>
+        <v>4.499500652071164</v>
       </c>
       <c r="N13" s="18" t="n">
-        <v>5.067333529201079</v>
+        <v>4.243577171370339</v>
       </c>
       <c r="O13" s="18" t="n">
-        <v>7.204573738272546</v>
+        <v>3.29490390064664</v>
       </c>
     </row>
     <row r="14">
@@ -19373,40 +19373,40 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>8040.507403868128</v>
+        <v>40.50740386812575</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>143.1399272288953</v>
+        <v>43.13992722889532</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>7692.141235775918</v>
+        <v>45.08241224650655</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>149.3496944566449</v>
+        <v>49.34969445664487</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>150.518051830372</v>
+        <v>50.51805183037202</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>151.5044792214682</v>
+        <v>51.50447922146824</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>152.3378577093131</v>
+        <v>52.3378577093131</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>151.879805415189</v>
+        <v>51.87980541518896</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>150.9251738463885</v>
+        <v>50.92517384638846</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>150.1663138627926</v>
+        <v>50.16631386279259</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>149.5779974364205</v>
+        <v>49.57799743642049</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>146.9215498515224</v>
+        <v>46.92154985152244</v>
       </c>
     </row>
     <row r="15">
@@ -19426,40 +19426,40 @@
         </is>
       </c>
       <c r="D15" s="18" t="n">
-        <v>21731.81202115919</v>
+        <v>217.3181202115919</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>300.107875542147</v>
+        <v>243.8376488779945</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>25714.71937269552</v>
+        <v>257.1471937269552</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>351.2935485872248</v>
+        <v>289.3005694247734</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>385.543380409862</v>
+        <v>321.2861503415517</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>419.0466744184446</v>
+        <v>330.8263219092984</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>451.639154246984</v>
+        <v>361.3113233975872</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>485.0958329196223</v>
+        <v>392.6966266492181</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>517.8723087955156</v>
+        <v>423.7137071963309</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>549.3602523857869</v>
+        <v>453.8193389273891</v>
       </c>
       <c r="N15" s="18" t="n">
-        <v>579.4683900051731</v>
+        <v>482.890325004311</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>632.4486619339541</v>
+        <v>510.8239192543475</v>
       </c>
     </row>
     <row r="16">
@@ -19482,37 +19482,37 @@
         <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>-98.61903887604979</v>
+        <v>12.20309132095469</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>8468.492021824382</v>
+        <v>5.45836334553087</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>-98.63388146105831</v>
+        <v>12.50387967755127</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>9.749633023543304</v>
+        <v>11.05617627382358</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>8.689889571691278</v>
+        <v>2.969369067918048</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>7.777768401043028</v>
+        <v>9.214805313056939</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>7.407833966127342</v>
+        <v>8.686498656200282</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>6.756701181831049</v>
+        <v>7.898484082171464</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>6.080252420429089</v>
+        <v>7.105182395505705</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>5.480581729135148</v>
+        <v>6.405849989917067</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>9.142909750143247</v>
+        <v>5.78466637321573</v>
       </c>
     </row>
     <row r="17">
@@ -19532,40 +19532,40 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>8000.000000000002</v>
+        <v>80</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>100</v>
+        <v>81.25000000000001</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>7647.058823529412</v>
+        <v>76.47058823529412</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>100</v>
+        <v>82.35294117647058</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>100</v>
+        <v>78.94736842105263</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>100</v>
+        <v>80.95238095238096</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>100</v>
+        <v>81.81818181818181</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>100</v>
+        <v>82.60869565217391</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>100</v>
+        <v>80.76923076923076</v>
       </c>
     </row>
     <row r="18">
@@ -19903,40 +19903,40 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>21887.55938626539</v>
+        <v>373.0654853177943</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>472.5641758996232</v>
+        <v>416.2939492354706</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>25908.40684209097</v>
+        <v>450.8346631224048</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>546.4096095642461</v>
+        <v>484.4166304017947</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>600.6205955662515</v>
+        <v>536.363365497941</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>653.6353728329113</v>
+        <v>565.4150203237651</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>705.1449672691116</v>
+        <v>614.817136419715</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>763.3676613462168</v>
+        <v>670.9684550758126</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>823.4091340261756</v>
+        <v>729.2505324269908</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>881.0503057760172</v>
+        <v>785.5093923176196</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>936.091123199969</v>
+        <v>839.5130581991069</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>1035.829599228865</v>
+        <v>914.2048565492587</v>
       </c>
     </row>
     <row r="25">
@@ -19956,40 +19956,40 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>21887.55938626539</v>
+        <v>373.0654853177943</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>472.5641758996232</v>
+        <v>416.2939492354706</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>25908.40684209097</v>
+        <v>450.8346631224048</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>546.4096095642461</v>
+        <v>484.4166304017947</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>600.6205955662515</v>
+        <v>536.363365497941</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>653.6353728329113</v>
+        <v>565.4150203237651</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>705.1449672691116</v>
+        <v>614.817136419715</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>763.3676613462168</v>
+        <v>670.9684550758126</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>823.4091340261756</v>
+        <v>729.2505324269908</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>881.0503057760172</v>
+        <v>785.5093923176196</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>936.091123199969</v>
+        <v>839.5130581991069</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>1035.829599228865</v>
+        <v>914.2048565492587</v>
       </c>
     </row>
     <row r="26">
@@ -20009,40 +20009,40 @@
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>8057.334331791408</v>
+        <v>137.3343317914066</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>157.4647699751073</v>
+        <v>138.7147699751073</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>7704.657720502802</v>
+        <v>134.0694852086853</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>155.5421702908315</v>
+        <v>137.8951114673021</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>155.7854773508875</v>
+        <v>139.1188106842208</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>155.981520134966</v>
+        <v>134.9288885560186</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>156.1301673334316</v>
+        <v>136.1301673334317</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>157.364299905809</v>
+        <v>138.31668085819</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>158.9984867005706</v>
+        <v>140.8166685187524</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>160.3775121970968</v>
+        <v>142.9862078492707</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>161.5430866197227</v>
+        <v>144.876419953056</v>
       </c>
       <c r="O26" s="18" t="n">
-        <v>163.7808191516161</v>
+        <v>144.5500499208468</v>
       </c>
     </row>
     <row r="27">
@@ -20062,40 +20062,40 @@
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>8057.334331791408</v>
+        <v>137.3343317914066</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>157.4647699751073</v>
+        <v>138.7147699751073</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>7704.657720502802</v>
+        <v>134.0694852086853</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>155.5421702908315</v>
+        <v>137.8951114673021</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>155.7854773508875</v>
+        <v>139.1188106842208</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>155.981520134966</v>
+        <v>134.9288885560186</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>156.1301673334316</v>
+        <v>136.1301673334317</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>157.364299905809</v>
+        <v>138.31668085819</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>158.9984867005706</v>
+        <v>140.8166685187524</v>
       </c>
       <c r="M27" s="18" t="n">
-        <v>160.3775121970968</v>
+        <v>142.9862078492707</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>161.5430866197227</v>
+        <v>144.876419953056</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>163.7808191516161</v>
+        <v>144.5500499208468</v>
       </c>
     </row>
     <row r="28">
@@ -20221,40 +20221,40 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>21879.83987811954</v>
+        <v>365.3459771719465</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>455.7440381901208</v>
+        <v>399.4738115259682</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>25882.57694911345</v>
+        <v>425.0047701448842</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>511.6601268713877</v>
+        <v>449.6671477089362</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>557.0405870552084</v>
+        <v>492.783356986898</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>601.3132077618656</v>
+        <v>513.0928552527193</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>644.3180928722871</v>
+        <v>553.9902620228905</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>694.2700999973733</v>
+        <v>601.8708937269691</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>746.1236285948332</v>
+        <v>651.9650269956485</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>795.658703703001</v>
+        <v>700.1177902446034</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>842.6745369684558</v>
+        <v>746.0964719675936</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>936.5201765765836</v>
+        <v>814.8954338969769</v>
       </c>
     </row>
     <row r="31">
@@ -20274,40 +20274,40 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>8054.492596131875</v>
+        <v>134.4925961318743</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>151.8600727711047</v>
+        <v>133.1100727711047</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>7696.976411282905</v>
+        <v>126.3881759887876</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>145.6503055433551</v>
+        <v>128.0032467198257</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>144.481948169628</v>
+        <v>127.8152815029613</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>143.4955207785318</v>
+        <v>122.4428891995844</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>142.6621422906869</v>
+        <v>122.6621422906869</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>143.120194584811</v>
+        <v>124.072575537192</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>144.0748261536115</v>
+        <v>125.8930079717933</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>144.8336861372074</v>
+        <v>127.4423817893813</v>
       </c>
       <c r="N31" s="19" t="n">
-        <v>145.4220025635795</v>
+        <v>128.7553358969129</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>148.0784501484776</v>
+        <v>128.8476809177083</v>
       </c>
     </row>
     <row r="32">
@@ -20380,40 +20380,40 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>21879.83987811954</v>
+        <v>365.3459771719465</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>455.7440381901208</v>
+        <v>399.4738115259682</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>25882.57694911345</v>
+        <v>425.0047701448842</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>511.6601268713877</v>
+        <v>449.6671477089362</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>557.0405870552084</v>
+        <v>492.783356986898</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>601.3132077618656</v>
+        <v>513.0928552527193</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>644.3180928722871</v>
+        <v>553.9902620228905</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>694.2700999973733</v>
+        <v>601.8708937269691</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>746.1236285948332</v>
+        <v>651.9650269956485</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>795.658703703001</v>
+        <v>700.1177902446034</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>842.6745369684558</v>
+        <v>746.0964719675936</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>936.5201765765836</v>
+        <v>814.8954338969769</v>
       </c>
     </row>
     <row r="34">
@@ -20433,40 +20433,40 @@
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>21879.83987811954</v>
+        <v>365.3459771719465</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>455.7440381901208</v>
+        <v>399.4738115259682</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>25882.57694911345</v>
+        <v>425.0047701448842</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>511.6601268713877</v>
+        <v>449.6671477089362</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>557.0405870552084</v>
+        <v>492.783356986898</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>601.3132077618656</v>
+        <v>513.0928552527193</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>644.3180928722871</v>
+        <v>553.9902620228905</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>694.2700999973733</v>
+        <v>601.8708937269691</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>746.1236285948332</v>
+        <v>651.9650269956485</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>795.658703703001</v>
+        <v>700.1177902446034</v>
       </c>
       <c r="N34" s="19" t="n">
-        <v>842.6745369684558</v>
+        <v>746.0964719675936</v>
       </c>
       <c r="O34" s="19" t="n">
-        <v>936.5201765765836</v>
+        <v>814.8954338969769</v>
       </c>
     </row>
     <row r="35">
@@ -20539,40 +20539,40 @@
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>-6126.355165873472</v>
+        <v>-102.296873608145</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>-127.6083306932338</v>
+        <v>-111.8526672272711</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-7247.121545751766</v>
+        <v>-119.0013356405676</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>-143.2648355239886</v>
+        <v>-125.9068013585022</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>-155.9713643754584</v>
+        <v>-137.9793399563314</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>-168.3676981733223</v>
+        <v>-143.6659994707614</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>-180.4090660042404</v>
+        <v>-155.1172733664094</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>-194.3956279992645</v>
+        <v>-168.5238502435514</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>-208.9146160065533</v>
+        <v>-182.5502075587816</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>-222.7844370368403</v>
+        <v>-196.032981268489</v>
       </c>
       <c r="N36" s="19" t="n">
-        <v>-235.9488703511676</v>
+        <v>-208.9070121509262</v>
       </c>
       <c r="O36" s="19" t="n">
-        <v>-262.2256494414434</v>
+        <v>-228.1707214911535</v>
       </c>
     </row>
     <row r="37">
@@ -20645,40 +20645,40 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>15753.48471224607</v>
+        <v>263.0491035638015</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>328.1357074968869</v>
+        <v>287.6211442986971</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>18635.45540336169</v>
+        <v>306.0034345043167</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>368.3952913473991</v>
+        <v>323.7603463504341</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>401.0692226797501</v>
+        <v>354.8040170305666</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>432.9455095885432</v>
+        <v>369.4268557819579</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>463.9090268680467</v>
+        <v>398.8729886564812</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>499.8744719981088</v>
+        <v>433.3470434834178</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>537.20901258828</v>
+        <v>469.4148194368669</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>572.8742666661608</v>
+        <v>504.0848089761145</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>606.7256666172882</v>
+        <v>537.1894598166674</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>674.2945271351402</v>
+        <v>586.7247124058233</v>
       </c>
     </row>
     <row r="39">
@@ -20698,40 +20698,40 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>5799.23466921495</v>
+        <v>96.83466921494947</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>109.3392523951954</v>
+        <v>95.83925239519537</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>5541.823016123692</v>
+        <v>90.99948671192705</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>104.8682199912157</v>
+        <v>92.16233763827452</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>104.0270026821321</v>
+        <v>92.02700268213214</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>103.3167749605429</v>
+        <v>88.15888022370078</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>102.7167424492946</v>
+        <v>88.31674244929459</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>103.046540101064</v>
+        <v>89.33225438677826</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>103.7338748306003</v>
+        <v>90.64296573969118</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>104.2802540187893</v>
+        <v>91.75851488835455</v>
       </c>
       <c r="N39" s="19" t="n">
-        <v>104.7038418457773</v>
+        <v>92.70384184577726</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>106.6164841069039</v>
+        <v>92.77033026074997</v>
       </c>
     </row>
     <row r="40">
@@ -20828,16 +20828,16 @@
         <v>1993.665016356035</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>2002.979533996185</v>
+        <v>2209.725553812152</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>1975.052331649058</v>
+        <v>2414.747334197721</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>2255.879879015144</v>
+        <v>2608.838708681207</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>2447.325800475393</v>
+        <v>2716.446560755823</v>
       </c>
     </row>
     <row r="42">
@@ -20881,16 +20881,16 @@
         <v>1993.665016356035</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>2002.979533996185</v>
+        <v>2209.725553812152</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>1975.052331649058</v>
+        <v>2414.747334197721</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>2255.879879015144</v>
+        <v>2608.838708681207</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>2447.325800475393</v>
+        <v>2716.446560755823</v>
       </c>
     </row>
     <row r="43">
@@ -20910,40 +20910,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>1800.093844009201</v>
+        <v>29.27695805960458</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>40.07421120630662</v>
+        <v>-87.79857762111885</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>2130.840025680825</v>
+        <v>-252.6250664649972</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>46.35405098577594</v>
+        <v>-396.3681599933672</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>50.95050119891052</v>
+        <v>-408.8387960742691</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>55.44556492223289</v>
+        <v>-358.9063314807942</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>59.81317191628446</v>
+        <v>-309.2036999916999</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>64.73609202675598</v>
+        <v>-254.2992020946029</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>69.80570543555764</v>
+        <v>-204.4205023302442</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>929.6471670975955</v>
+        <v>-149.6933138973359</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>1789.269230571323</v>
+        <v>-82.22269093607284</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>2652.659069276866</v>
+        <v>-4.392170603149005</v>
       </c>
     </row>
     <row r="44">
@@ -20963,40 +20963,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>0</v>
+        <v>-2.502318748424358</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>0</v>
+        <v>-123.2478386906458</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>0</v>
+        <v>-291.0618993538855</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>0</v>
+        <v>-437.6268976233252</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>0</v>
+        <v>-454.5078811031815</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>0</v>
+        <v>-407.100908525563</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>0</v>
+        <v>-361.5926666326915</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>0</v>
+        <v>-311.4408388114627</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>0</v>
+        <v>-266.4871446206634</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>854.9744285993511</v>
+        <v>-216.5133745770818</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>1709.948857198702</v>
+        <v>-153.6051411579385</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>2564.923285798053</v>
+        <v>-82.13139988911803</v>
       </c>
     </row>
     <row r="45">
@@ -21069,40 +21069,40 @@
         </is>
       </c>
       <c r="D46" s="18" t="n">
-        <v>1777.766639877873</v>
+        <v>9.452072676701011</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>15.40781047681508</v>
+        <v>10.78286034003542</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>2103.201444268655</v>
+        <v>10.79825147671824</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>17.48060863614103</v>
+        <v>12.38529528032311</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>19.26200417892186</v>
+        <v>13.98058800892375</v>
       </c>
       <c r="I46" s="18" t="n">
-        <v>21.00337250427854</v>
+        <v>13.75238462681447</v>
       </c>
       <c r="J46" s="18" t="n">
-        <v>22.69214553982001</v>
+        <v>15.26794026452713</v>
       </c>
       <c r="K46" s="18" t="n">
-        <v>24.86520164980072</v>
+        <v>17.27074633990449</v>
       </c>
       <c r="L46" s="18" t="n">
-        <v>27.2408581372961</v>
+        <v>19.50179499215763</v>
       </c>
       <c r="M46" s="18" t="n">
-        <v>29.51984104187833</v>
+        <v>21.66716322337989</v>
       </c>
       <c r="N46" s="18" t="n">
-        <v>31.69283446808668</v>
+        <v>23.75491131733089</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>35.75370167602266</v>
+        <v>25.75714748317828</v>
       </c>
     </row>
     <row r="47">
@@ -21122,40 +21122,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>2046.741120968025</v>
+        <v>275.9242350184284</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>568.2913851835414</v>
+        <v>440.4185963561159</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>2928.636741061173</v>
+        <v>545.1716489153512</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>1101.854923710094</v>
+        <v>659.1327127309506</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>1352.403769048645</v>
+        <v>892.6144717754653</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>1591.212147301016</v>
+        <v>1176.860250897989</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>1826.265706300496</v>
+        <v>1457.248834392512</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>2058.401108382791</v>
+        <v>1739.365814261432</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>2072.785239431743</v>
+        <v>2005.305051481908</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>2904.699498746653</v>
+        <v>2265.054020300385</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>4045.149109586468</v>
+        <v>2526.616017745134</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>5099.984869752259</v>
+        <v>2712.054390152674</v>
       </c>
     </row>
     <row r="48">
@@ -21175,40 +21175,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>3802.180556714569</v>
+        <v>263.0491035638015</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>559.0327949308635</v>
+        <v>547.2805759088812</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>5004.199603917657</v>
+        <v>660.4218530330144</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>1090.462089996599</v>
+        <v>749.1266627456548</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>1339.977276207577</v>
+        <v>849.5167746727024</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>1577.77332738734</v>
+        <v>4633.559873554064</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>1811.836825463851</v>
+        <v>1386.406146146704</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>2043.395419655636</v>
+        <v>5839.3085904776</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>2264.207270086744</v>
+        <v>1935.64154748193</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>-1288.492283290204</v>
+        <v>2190.418639929675</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>2275.830548432321</v>
+        <v>2439.067973268449</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>-1603.922354900547</v>
+        <v>2613.997328041434</v>
       </c>
     </row>
     <row r="49">
@@ -21281,40 +21281,40 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>3802.180556714569</v>
+        <v>263.0491035638015</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>-3243.147761783706</v>
+        <v>284.2314723450798</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>4445.166808986794</v>
+        <v>269.6103236764792</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>-3913.737513921059</v>
+        <v>260.8782449511792</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>249.5151862109781</v>
+        <v>249.1429805826177</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>237.7960511797626</v>
+        <v>233.8569077648306</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>234.0634980765118</v>
+        <v>233.7170632808542</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>231.5585941917843</v>
+        <v>231.2180941225775</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>220.8118504311078</v>
+        <v>220.5226347606234</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>209.5797461947332</v>
+        <v>209.3525168480132</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>198.4373613359024</v>
+        <v>198.2668706713877</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>115.7295864904879</v>
+        <v>111.6123244063106</v>
       </c>
     </row>
     <row r="51">
@@ -21337,37 +21337,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>3802.180556714569</v>
+        <v>263.0491035638015</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>559.032794930863</v>
+        <v>390.8115293565352</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>5004.199603917657</v>
+        <v>488.2484177944757</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>1090.462089996599</v>
+        <v>600.3737940900846</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>1339.977276207577</v>
+        <v>4399.702965789234</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>1577.77332738734</v>
+        <v>1152.689082865849</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>1811.836825463852</v>
+        <v>5608.090496355022</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>2043.395419655636</v>
+        <v>1715.118912721307</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>-1498.072029484937</v>
+        <v>1981.066123081662</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>2077.393187096419</v>
+        <v>2240.801102597061</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>-1719.651941391035</v>
+        <v>2502.385003635124</v>
       </c>
     </row>
     <row r="52">
@@ -21411,16 +21411,16 @@
         <v>0</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>-74.11679431732691</v>
+        <v>0</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>420.309520466836</v>
+        <v>0</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>345.7993353962562</v>
+        <v>0</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>277.9086329187738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -21464,16 +21464,16 @@
         <v>0</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>-74.11679431732691</v>
+        <v>0</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>420.309520466836</v>
+        <v>0</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>345.7993353962562</v>
+        <v>0</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>277.9086329187738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -21546,40 +21546,40 @@
         </is>
       </c>
       <c r="D55" s="18" t="n">
-        <v>-1777.766639877873</v>
+        <v>-9.452072676701011</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>-15.40781047681508</v>
+        <v>-10.78286034003542</v>
       </c>
       <c r="F55" s="18" t="n">
-        <v>-2103.201444268655</v>
+        <v>-10.79825147671824</v>
       </c>
       <c r="G55" s="18" t="n">
-        <v>-17.48060863614103</v>
+        <v>-12.38529528032311</v>
       </c>
       <c r="H55" s="18" t="n">
-        <v>-19.26200417892186</v>
+        <v>-13.98058800892375</v>
       </c>
       <c r="I55" s="18" t="n">
-        <v>-21.00337250427854</v>
+        <v>-13.75238462681447</v>
       </c>
       <c r="J55" s="18" t="n">
-        <v>-22.69214553982001</v>
+        <v>-15.26794026452713</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>-24.86520164980072</v>
+        <v>-17.27074633990449</v>
       </c>
       <c r="L55" s="18" t="n">
-        <v>-27.2408581372961</v>
+        <v>-19.50179499215763</v>
       </c>
       <c r="M55" s="18" t="n">
-        <v>-29.51984104187833</v>
+        <v>-21.66716322337989</v>
       </c>
       <c r="N55" s="18" t="n">
-        <v>-31.69283446808668</v>
+        <v>-23.75491131733089</v>
       </c>
       <c r="O55" s="18" t="n">
-        <v>-35.75370167602266</v>
+        <v>-25.75714748317828</v>
       </c>
     </row>
     <row r="56">
@@ -21599,40 +21599,40 @@
         </is>
       </c>
       <c r="D56" s="18" t="n">
-        <v>-1777.766639877873</v>
+        <v>-9.452072676701011</v>
       </c>
       <c r="E56" s="18" t="n">
-        <v>-15.40781047681508</v>
+        <v>-10.78286034003542</v>
       </c>
       <c r="F56" s="18" t="n">
-        <v>-2103.201444268655</v>
+        <v>-10.79825147671824</v>
       </c>
       <c r="G56" s="18" t="n">
-        <v>-17.48060863614103</v>
+        <v>-12.38529528032311</v>
       </c>
       <c r="H56" s="18" t="n">
-        <v>-19.26200417892186</v>
+        <v>-13.98058800892375</v>
       </c>
       <c r="I56" s="18" t="n">
-        <v>-21.00337250427854</v>
+        <v>-13.75238462681447</v>
       </c>
       <c r="J56" s="18" t="n">
-        <v>-22.69214553982001</v>
+        <v>-15.26794026452713</v>
       </c>
       <c r="K56" s="18" t="n">
-        <v>-24.86520164980072</v>
+        <v>-17.27074633990449</v>
       </c>
       <c r="L56" s="18" t="n">
-        <v>-27.2408581372961</v>
+        <v>-19.50179499215763</v>
       </c>
       <c r="M56" s="18" t="n">
-        <v>-29.51984104187833</v>
+        <v>-21.66716322337989</v>
       </c>
       <c r="N56" s="18" t="n">
-        <v>-31.69283446808668</v>
+        <v>-23.75491131733089</v>
       </c>
       <c r="O56" s="18" t="n">
-        <v>-35.75370167602266</v>
+        <v>-25.75714748317828</v>
       </c>
     </row>
     <row r="57">
@@ -21705,40 +21705,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>2024.413916836696</v>
+        <v>253.5970308871005</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>543.6249844540484</v>
+        <v>536.4977155688458</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>2900.998159649002</v>
+        <v>649.6236015562961</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>1072.981481360458</v>
+        <v>736.7413674653317</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>1320.715272028655</v>
+        <v>835.5361866637786</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>1556.769954883061</v>
+        <v>4619.80748892725</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>1789.144679924031</v>
+        <v>1371.138205882176</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>2018.530218005836</v>
+        <v>5822.037844137695</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>2162.849617632121</v>
+        <v>1916.139752489772</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>-897.7026038652465</v>
+        <v>2168.751476706296</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>2589.937049360491</v>
+        <v>2415.313061951118</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>-1361.767423657796</v>
+        <v>2588.240180558256</v>
       </c>
     </row>
     <row r="59">
@@ -21758,40 +21758,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>22.32720413132915</v>
+        <v>22.32720413132793</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>24.66640072949292</v>
+        <v>-96.07911921272989</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>27.63858141217088</v>
+        <v>-104.4519526409449</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>28.87344234963598</v>
+        <v>-77.60865473438105</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>31.68849701998988</v>
+        <v>57.07828511168668</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>34.44219241795531</v>
+        <v>-3442.947238029261</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>37.1210263764649</v>
+        <v>86.11062851033535</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>39.87089037695523</v>
+        <v>-4082.672029876263</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>-90.06437820037809</v>
+        <v>89.16529899213538</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>3802.4021026119</v>
+        <v>96.302543594089</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>1455.212060225977</v>
+        <v>111.3029557940163</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>6461.752293410055</v>
+        <v>123.8142095944181</v>
       </c>
     </row>
     <row r="60">
@@ -21864,40 +21864,40 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>21887.55938626539</v>
+        <v>373.0654853177943</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>472.5641758996232</v>
+        <v>416.2939492354706</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>25908.40684209097</v>
+        <v>450.8346631224048</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>546.4096095642461</v>
+        <v>484.4166304017947</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>600.6205955662515</v>
+        <v>536.363365497941</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>653.6353728329113</v>
+        <v>565.4150203237651</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>705.1449672691116</v>
+        <v>614.817136419715</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>763.3676613462168</v>
+        <v>670.9684550758126</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>823.4091340261756</v>
+        <v>729.2505324269908</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>881.0503057760172</v>
+        <v>785.5093923176196</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>936.091123199969</v>
+        <v>839.5130581991069</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>1035.829599228865</v>
+        <v>914.2048565492587</v>
       </c>
     </row>
     <row r="62">
@@ -21917,40 +21917,40 @@
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>-6126.355165873472</v>
+        <v>-102.296873608145</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>-127.6083306932338</v>
+        <v>-111.8526672272711</v>
       </c>
       <c r="F62" s="18" t="n">
-        <v>-7247.121545751766</v>
+        <v>-119.0013356405676</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>-143.2648355239886</v>
+        <v>-125.9068013585022</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>-155.9713643754584</v>
+        <v>-137.9793399563314</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>-168.3676981733223</v>
+        <v>-143.6659994707614</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>-180.4090660042404</v>
+        <v>-155.1172733664094</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>-194.3956279992645</v>
+        <v>-168.5238502435514</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>-208.9146160065533</v>
+        <v>-182.5502075587816</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>-222.7844370368403</v>
+        <v>-196.032981268489</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>-235.9488703511676</v>
+        <v>-208.9070121509262</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>-262.2256494414434</v>
+        <v>-228.1707214911535</v>
       </c>
     </row>
     <row r="63">
@@ -21970,40 +21970,40 @@
         </is>
       </c>
       <c r="D63" s="18" t="n">
-        <v>-3555.533279755747</v>
+        <v>-18.90414535340202</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>3524.717658802117</v>
+        <v>-2.661575326668817</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>-4175.58726758368</v>
+        <v>-0.0307822733656451</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>4171.441671265028</v>
+        <v>-3.174087607209728</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>-3.562791085561656</v>
+        <v>-3.190585457201287</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>-3.482736650713363</v>
+        <v>0.4564067642185599</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>-3.377546071082946</v>
+        <v>-3.031111275425321</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>-4.346112219961419</v>
+        <v>-4.005612150754729</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>-4.751312974990746</v>
+        <v>-4.462097304506273</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>-4.557965809164472</v>
+        <v>-4.330736462444513</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>-4.345986852416694</v>
+        <v>-4.175496187901999</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>-8.121734415871956</v>
+        <v>-4.004472331694785</v>
       </c>
     </row>
     <row r="64">
@@ -22023,40 +22023,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>12205.67094063617</v>
+        <v>251.8644663562472</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>3869.673504008506</v>
+        <v>301.7797066815307</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>14485.69802875553</v>
+        <v>331.8025452084715</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>4574.586445305285</v>
+        <v>355.3357414360828</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>441.0864401052314</v>
+        <v>395.1934400844083</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>481.7849380088757</v>
+        <v>422.2054276172223</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>521.3583551937883</v>
+        <v>456.6687517778803</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>564.6259211269908</v>
+        <v>498.4389926815065</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>609.7432050446316</v>
+        <v>542.2382275637029</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>653.7079029300126</v>
+        <v>585.1456745866861</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>695.7962659963848</v>
+        <v>626.4305498602787</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>765.48221537155</v>
+        <v>682.0296627264104</v>
       </c>
     </row>
     <row r="65">
@@ -22182,40 +22182,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>11951.3041555315</v>
+        <v>-2.502318748424358</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>3571.283469280593</v>
+        <v>3.389671953617324</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>14190.28859437489</v>
+        <v>36.39311082783746</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>4282.132805268458</v>
+        <v>62.88210139925491</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>151.5540364687719</v>
+        <v>105.6610364479488</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>195.1494584087807</v>
+        <v>135.5699480171273</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>229.8455287915349</v>
+        <v>165.155925375627</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>268.3158778063245</v>
+        <v>202.1289493608403</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>316.3971621571721</v>
+        <v>248.8921846762435</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>363.2945204714276</v>
+        <v>294.7322921281012</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>408.2883052813858</v>
+        <v>338.9225891452797</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>558.5649406446523</v>
+        <v>475.1123879995127</v>
       </c>
     </row>
     <row r="68">
@@ -22447,40 +22447,40 @@
         </is>
       </c>
       <c r="D72" s="18" t="n">
-        <v>-11951.3041555315</v>
+        <v>0</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>-3571.283469280593</v>
+        <v>-3.389671953617324</v>
       </c>
       <c r="F72" s="18" t="n">
-        <v>-14190.28859437489</v>
+        <v>-36.39311082783746</v>
       </c>
       <c r="G72" s="18" t="n">
-        <v>-4282.132805268458</v>
+        <v>-62.88210139925491</v>
       </c>
       <c r="H72" s="18" t="n">
-        <v>-151.5540364687719</v>
+        <v>-105.6610364479488</v>
       </c>
       <c r="I72" s="18" t="n">
-        <v>-195.1494584087807</v>
+        <v>-135.5699480171273</v>
       </c>
       <c r="J72" s="18" t="n">
-        <v>-229.8455287915349</v>
+        <v>-165.155925375627</v>
       </c>
       <c r="K72" s="18" t="n">
-        <v>-268.3158778063245</v>
+        <v>-202.1289493608403</v>
       </c>
       <c r="L72" s="18" t="n">
-        <v>-316.3971621571721</v>
+        <v>-248.8921846762435</v>
       </c>
       <c r="M72" s="18" t="n">
-        <v>-363.2945204714276</v>
+        <v>-294.7322921281012</v>
       </c>
       <c r="N72" s="18" t="n">
-        <v>-408.2883052813858</v>
+        <v>-338.9225891452797</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>-558.5649406446523</v>
+        <v>-475.1123879995127</v>
       </c>
     </row>
     <row r="73">
@@ -22553,40 +22553,40 @@
         </is>
       </c>
       <c r="D74" s="18" t="n">
-        <v>-11951.3041555315</v>
+        <v>0</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>-3571.283469280593</v>
+        <v>-3.389671953617324</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>-14190.28859437489</v>
+        <v>-36.39311082783746</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>-4282.132805268458</v>
+        <v>-62.88210139925491</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>-151.5540364687719</v>
+        <v>-105.6610364479488</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>-195.1494584087807</v>
+        <v>-135.5699480171273</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>-229.8455287915349</v>
+        <v>-165.155925375627</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>-268.3158778063245</v>
+        <v>-202.1289493608403</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>-316.3971621571721</v>
+        <v>-248.8921846762435</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>-363.2945204714276</v>
+        <v>-294.7322921281012</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>-408.2883052813858</v>
+        <v>-338.9225891452797</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>-558.5649406446523</v>
+        <v>-475.1123879995127</v>
       </c>
     </row>
     <row r="75">
@@ -22606,7 +22606,7 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>0</v>
+        <v>-2.502318748424358</v>
       </c>
       <c r="E75" s="18" t="n">
         <v>0</v>
@@ -22662,37 +22662,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>0</v>
+        <v>-2.502318748424358</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>0</v>
+        <v>-123.2478386906458</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0</v>
+        <v>-291.0618993538855</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>0</v>
+        <v>-437.6268976233252</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>0</v>
+        <v>-454.5078811031815</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>0</v>
+        <v>-407.100908525563</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>0</v>
+        <v>-361.5926666326915</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>0</v>
+        <v>-311.4408388114627</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>0</v>
+        <v>-266.4871446206634</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>854.9744285993511</v>
+        <v>-216.5133745770818</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>1709.948857198702</v>
+        <v>-153.6051411579385</v>
       </c>
     </row>
     <row r="77">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>0</v>
+        <v>-2.502318748424358</v>
       </c>
       <c r="E77" s="18" t="n">
         <v>0</v>
@@ -22765,40 +22765,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>0</v>
+        <v>-2.502318748424358</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>0</v>
+        <v>-123.2478386906458</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>0</v>
+        <v>-291.0618993538855</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0</v>
+        <v>-437.6268976233252</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>0</v>
+        <v>-454.5078811031815</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>0</v>
+        <v>-407.100908525563</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>0</v>
+        <v>-361.5926666326915</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>0</v>
+        <v>-311.4408388114627</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>0</v>
+        <v>-266.4871446206634</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>854.9744285993511</v>
+        <v>-216.5133745770818</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>1709.948857198702</v>
+        <v>-153.6051411579385</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>2564.923285798053</v>
+        <v>-82.13139988911803</v>
       </c>
     </row>
     <row r="79">
@@ -23004,13 +23004,13 @@
         <v>1993.665016356035</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>2002.979533996185</v>
+        <v>2209.725553812152</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>1975.052331649058</v>
+        <v>2414.747334197721</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>2255.879879015144</v>
+        <v>2608.838708681207</v>
       </c>
     </row>
     <row r="83">
@@ -23160,16 +23160,16 @@
         <v>1993.665016356035</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>2002.979533996185</v>
+        <v>2209.725553812152</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>1975.052331649058</v>
+        <v>2414.747334197721</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>2255.879879015144</v>
+        <v>2608.838708681207</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>2447.325800475393</v>
+        <v>2716.446560755823</v>
       </c>
     </row>
     <row r="86">
@@ -23295,40 +23295,40 @@
         </is>
       </c>
       <c r="D88" s="18" t="n">
-        <v>1777.766639877873</v>
+        <v>9.452072676701011</v>
       </c>
       <c r="E88" s="18" t="n">
-        <v>15.40781047681508</v>
+        <v>10.78286034003542</v>
       </c>
       <c r="F88" s="18" t="n">
-        <v>2103.201444268655</v>
+        <v>10.79825147671824</v>
       </c>
       <c r="G88" s="18" t="n">
-        <v>17.48060863614103</v>
+        <v>12.38529528032311</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>19.26200417892186</v>
+        <v>13.98058800892375</v>
       </c>
       <c r="I88" s="18" t="n">
-        <v>21.00337250427854</v>
+        <v>13.75238462681447</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>22.69214553982001</v>
+        <v>15.26794026452713</v>
       </c>
       <c r="K88" s="18" t="n">
-        <v>24.86520164980072</v>
+        <v>17.27074633990449</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>27.2408581372961</v>
+        <v>19.50179499215763</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>29.51984104187833</v>
+        <v>21.66716322337989</v>
       </c>
       <c r="N88" s="18" t="n">
-        <v>31.69283446808668</v>
+        <v>23.75491131733089</v>
       </c>
       <c r="O88" s="18" t="n">
-        <v>35.75370167602266</v>
+        <v>25.75714748317828</v>
       </c>
     </row>
     <row r="89">
@@ -23348,40 +23348,40 @@
         </is>
       </c>
       <c r="D89" s="18" t="n">
-        <v>1777.766639877873</v>
+        <v>9.452072676701011</v>
       </c>
       <c r="E89" s="18" t="n">
-        <v>15.40781047681508</v>
+        <v>10.78286034003542</v>
       </c>
       <c r="F89" s="18" t="n">
-        <v>2103.201444268655</v>
+        <v>10.79825147671824</v>
       </c>
       <c r="G89" s="18" t="n">
-        <v>17.48060863614103</v>
+        <v>12.38529528032311</v>
       </c>
       <c r="H89" s="18" t="n">
-        <v>19.26200417892186</v>
+        <v>13.98058800892375</v>
       </c>
       <c r="I89" s="18" t="n">
-        <v>21.00337250427854</v>
+        <v>13.75238462681447</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>22.69214553982001</v>
+        <v>15.26794026452713</v>
       </c>
       <c r="K89" s="18" t="n">
-        <v>24.86520164980072</v>
+        <v>17.27074633990449</v>
       </c>
       <c r="L89" s="18" t="n">
-        <v>27.2408581372961</v>
+        <v>19.50179499215763</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>29.51984104187833</v>
+        <v>21.66716322337989</v>
       </c>
       <c r="N89" s="18" t="n">
-        <v>31.69283446808668</v>
+        <v>23.75491131733089</v>
       </c>
       <c r="O89" s="18" t="n">
-        <v>35.75370167602266</v>
+        <v>25.75714748317828</v>
       </c>
     </row>
     <row r="90">
@@ -23401,40 +23401,40 @@
         </is>
       </c>
       <c r="D90" s="18" t="n">
-        <v>3555.533279755747</v>
+        <v>18.90414535340202</v>
       </c>
       <c r="E90" s="18" t="n">
-        <v>30.81562095363016</v>
+        <v>21.56572068007084</v>
       </c>
       <c r="F90" s="18" t="n">
-        <v>4206.40288853731</v>
+        <v>21.59650295343648</v>
       </c>
       <c r="G90" s="18" t="n">
-        <v>34.96121727228206</v>
+        <v>24.77059056064621</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>38.52400835784372</v>
+        <v>27.9611760178475</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>42.00674500855708</v>
+        <v>27.50476925362894</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>45.38429107964003</v>
+        <v>30.53588052905426</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>49.73040329960145</v>
+        <v>34.54149267980899</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>54.48171627459219</v>
+        <v>39.00358998431526</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>59.03968208375667</v>
+        <v>43.33432644675977</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>63.38566893617336</v>
+        <v>47.50982263466177</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>71.50740335204532</v>
+        <v>51.51429496635656</v>
       </c>
     </row>
     <row r="91">
@@ -23454,40 +23454,40 @@
         </is>
       </c>
       <c r="D91" s="18" t="n">
-        <v>3555.533279755747</v>
+        <v>18.90414535340202</v>
       </c>
       <c r="E91" s="18" t="n">
-        <v>-3524.717658802117</v>
+        <v>2.661575326668817</v>
       </c>
       <c r="F91" s="18" t="n">
-        <v>4175.58726758368</v>
+        <v>0.0307822733656451</v>
       </c>
       <c r="G91" s="18" t="n">
-        <v>-4171.441671265028</v>
+        <v>3.174087607209728</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>3.562791085561656</v>
+        <v>3.190585457201287</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>3.482736650713363</v>
+        <v>-0.4564067642185599</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>3.377546071082946</v>
+        <v>3.031111275425321</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>4.346112219961419</v>
+        <v>4.005612150754729</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>4.751312974990746</v>
+        <v>4.462097304506273</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>4.557965809164472</v>
+        <v>4.330736462444513</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>4.345986852416694</v>
+        <v>4.175496187901999</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>8.121734415871956</v>
+        <v>4.004472331694785</v>
       </c>
     </row>
     <row r="92">
@@ -23746,37 +23746,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>27704.78886777757</v>
+        <v>263.0491035638015</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>31604.20804455505</v>
+        <v>397.5908732637698</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>64429.95204229162</v>
+        <v>561.0346394501506</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>69080.48013890747</v>
+        <v>726.1379968885944</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>69633.10339805599</v>
+        <v>28513.63334974814</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>70261.19836605332</v>
+        <v>32469.00422852429</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>70954.9529217129</v>
+        <v>65364.15478548025</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>71723.14327151733</v>
+        <v>70109.39486035387</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>1655304.099531629</v>
+        <v>70771.97661428257</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>3278755.383447527</v>
+        <v>71513.69072551925</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>4893557.271649791</v>
+        <v>72323.34627817474</v>
       </c>
     </row>
     <row r="97">
@@ -23849,40 +23849,40 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>15753.48471224607</v>
+        <v>263.0491035638015</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>328.1357074968869</v>
+        <v>287.6211442986971</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>18635.45540336169</v>
+        <v>306.0034345043167</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>368.3952913473991</v>
+        <v>323.7603463504341</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>401.0692226797501</v>
+        <v>354.8040170305666</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>432.9455095885432</v>
+        <v>369.4268557819579</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>463.9090268680467</v>
+        <v>398.8729886564812</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>499.8744719981088</v>
+        <v>433.3470434834178</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>537.20901258828</v>
+        <v>469.4148194368669</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>572.8742666661608</v>
+        <v>504.0848089761145</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>606.7256666172882</v>
+        <v>537.1894598166674</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>674.2945271351402</v>
+        <v>586.7247124058233</v>
       </c>
     </row>
     <row r="99">
@@ -23902,40 +23902,40 @@
         </is>
       </c>
       <c r="D99" s="20" t="n">
-        <v>11951.3041555315</v>
+        <v>0</v>
       </c>
       <c r="E99" s="20" t="n">
-        <v>3571.283469280593</v>
+        <v>3.389671953617324</v>
       </c>
       <c r="F99" s="20" t="n">
-        <v>14190.28859437489</v>
+        <v>36.39311082783746</v>
       </c>
       <c r="G99" s="20" t="n">
-        <v>4282.132805268458</v>
+        <v>62.88210139925491</v>
       </c>
       <c r="H99" s="20" t="n">
-        <v>151.5540364687719</v>
+        <v>105.6610364479488</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>195.1494584087807</v>
+        <v>135.5699480171273</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>229.8455287915349</v>
+        <v>165.155925375627</v>
       </c>
       <c r="K99" s="20" t="n">
-        <v>268.3158778063245</v>
+        <v>202.1289493608403</v>
       </c>
       <c r="L99" s="20" t="n">
-        <v>316.3971621571721</v>
+        <v>248.8921846762435</v>
       </c>
       <c r="M99" s="20" t="n">
-        <v>363.2945204714276</v>
+        <v>294.7322921281012</v>
       </c>
       <c r="N99" s="20" t="n">
-        <v>408.2883052813858</v>
+        <v>338.9225891452797</v>
       </c>
       <c r="O99" s="20" t="n">
-        <v>558.5649406446523</v>
+        <v>475.1123879995127</v>
       </c>
     </row>
     <row r="100">
@@ -23955,40 +23955,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>27704.78886777757</v>
+        <v>263.0491035638015</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>31604.20804455505</v>
+        <v>397.5908732637698</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>64429.95204229162</v>
+        <v>561.0346394501506</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>69080.48013890747</v>
+        <v>726.1379968885944</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>69633.10339805599</v>
+        <v>28513.63334974814</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>70261.19836605332</v>
+        <v>32469.00422852429</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>70954.9529217129</v>
+        <v>65364.15478548025</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>71723.14327151733</v>
+        <v>70109.39486035387</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>1655304.099531629</v>
+        <v>70771.97661428257</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>3278755.383447527</v>
+        <v>71513.69072551925</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>4893557.271649791</v>
+        <v>72323.34627817474</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>6546850.625414385</v>
+        <v>73316.16463294013</v>
       </c>
     </row>
     <row r="101">
@@ -24141,13 +24141,13 @@
         <v>0</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>-74.11679431732691</v>
+        <v>0</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>420.309520466836</v>
+        <v>0</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>345.7993353962562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -24350,16 +24350,16 @@
         <v>0</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>-74.11679431732691</v>
+        <v>0</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>420.309520466836</v>
+        <v>0</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>345.7993353962562</v>
+        <v>0</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>277.9086329187738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">

--- a/backend/Rwanda/financial-statements-CleanStep.xlsx
+++ b/backend/Rwanda/financial-statements-CleanStep.xlsx
@@ -644,40 +644,40 @@
         </is>
       </c>
       <c r="D2" s="18" t="n">
-        <v>21.00744523721673</v>
+        <v>-1914774.054075216</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>37.90483998391895</v>
+        <v>-3454927.684233574</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>37.52579158407983</v>
+        <v>-3420378.407391245</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>37.15053366823896</v>
+        <v>-3386174.623317326</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>36.77902833155665</v>
+        <v>-3352312.87708416</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>36.41123804824105</v>
+        <v>-3318789.748313316</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>52.42064537500877</v>
+        <v>-4778005.632218572</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>68.18788533119022</v>
+        <v>-6215148.589468248</v>
       </c>
       <c r="L2" s="18" t="n">
-        <v>67.50600647787832</v>
+        <v>-6152997.103573568</v>
       </c>
       <c r="M2" s="18" t="n">
-        <v>66.83094641309953</v>
+        <v>-6091467.13253783</v>
       </c>
       <c r="N2" s="18" t="n">
-        <v>66.16263694896854</v>
+        <v>-6030552.461212453</v>
       </c>
       <c r="O2" s="18" t="n">
-        <v>40.69695944169418</v>
+        <v>-3709422.11862368</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>80.4352673820939</v>
+        <v>80.43526738209388</v>
       </c>
       <c r="F3" s="18" t="n">
         <v>-0.9999999999998233</v>
@@ -709,25 +709,25 @@
         <v>-1.000000000000167</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>-0.9999999999998122</v>
+        <v>-0.999999999999801</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>-1.000000000000068</v>
+        <v>-1.000000000000056</v>
       </c>
       <c r="J3" s="18" t="n">
-        <v>43.9683135892192</v>
+        <v>43.96831358921916</v>
       </c>
       <c r="K3" s="18" t="n">
         <v>30.07830186634517</v>
       </c>
       <c r="L3" s="18" t="n">
-        <v>-1.000000000000001</v>
+        <v>-0.9999999999999565</v>
       </c>
       <c r="M3" s="18" t="n">
-        <v>-1.000000000000012</v>
+        <v>-1.000000000000045</v>
       </c>
       <c r="N3" s="18" t="n">
-        <v>-0.9999999999999898</v>
+        <v>-0.9999999999999676</v>
       </c>
       <c r="O3" s="18" t="n">
         <v>-38.48951414514526</v>
@@ -856,40 +856,40 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>21.00744523721673</v>
+        <v>-1914774.054075216</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>37.90483998391895</v>
+        <v>-3454927.684233574</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>37.52579158407983</v>
+        <v>-3420378.407391245</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>37.15053366823896</v>
+        <v>-3386174.623317326</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>36.77902833155665</v>
+        <v>-3352312.87708416</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>36.41123804824105</v>
+        <v>-3318789.748313316</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>52.42064537500877</v>
+        <v>-4778005.632218572</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>68.18788533119022</v>
+        <v>-6215148.589468248</v>
       </c>
       <c r="L6" s="18" t="n">
-        <v>67.50600647787832</v>
+        <v>-6152997.103573568</v>
       </c>
       <c r="M6" s="18" t="n">
-        <v>66.83094641309953</v>
+        <v>-6091467.13253783</v>
       </c>
       <c r="N6" s="18" t="n">
-        <v>66.16263694896854</v>
+        <v>-6030552.461212453</v>
       </c>
       <c r="O6" s="18" t="n">
-        <v>40.69695944169418</v>
+        <v>-3709422.11862368</v>
       </c>
     </row>
     <row r="7" ht="15.5" customHeight="1">
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>80.4352673820939</v>
+        <v>80.43526738209388</v>
       </c>
       <c r="F7" s="18" t="n">
         <v>-0.9999999999998233</v>
@@ -921,25 +921,25 @@
         <v>-1.000000000000167</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>-0.9999999999998122</v>
+        <v>-0.999999999999801</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>-1.000000000000068</v>
+        <v>-1.000000000000056</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>43.9683135892192</v>
+        <v>43.96831358921916</v>
       </c>
       <c r="K7" s="18" t="n">
         <v>30.07830186634517</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>-1.000000000000001</v>
+        <v>-0.9999999999999565</v>
       </c>
       <c r="M7" s="18" t="n">
-        <v>-1.000000000000012</v>
+        <v>-1.000000000000045</v>
       </c>
       <c r="N7" s="18" t="n">
-        <v>-0.9999999999999898</v>
+        <v>-0.9999999999999676</v>
       </c>
       <c r="O7" s="18" t="n">
         <v>-38.48951414514526</v>
@@ -1280,40 +1280,40 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>-15.37258602014267</v>
+        <v>0.000168656326988158</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>-26.57218378885672</v>
+        <v>0.0002915297993460997</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>-44.94631254234604</v>
+        <v>0.0004931167713175373</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>-63.37964390166334</v>
+        <v>0.0006953532692720455</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>-81.87277587292731</v>
+        <v>0.000898245854078132</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>-100.426312502724</v>
+        <v>0.00110180115287572</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>-83.66100415152785</v>
+        <v>0.0009178649352717545</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>-73.403901386792</v>
+        <v>0.0008053318015768958</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>-80.25259854755879</v>
+        <v>0.0008804705001846417</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>-87.16241005092758</v>
+        <v>0.0009562796988979686</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>-94.13395321349012</v>
+        <v>0.001032766170445213</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>-159.3108098942445</v>
+        <v>0.001747837092019904</v>
       </c>
     </row>
     <row r="15" ht="15.5" customHeight="1">
@@ -1439,40 +1439,40 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>-14.74508896899298</v>
+        <v>0.0001617719063900793</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>-31.77319252968107</v>
+        <v>0.0003485913132456718</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>-55.63231442328146</v>
+        <v>0.000610355460049909</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>-77.62670755337476</v>
+        <v>0.0008516612204987085</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>-195.7432522748146</v>
+        <v>0.0021475461524905</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>-232.9342312994107</v>
+        <v>0.002555577300350929</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>-183.6086623208613</v>
+        <v>0.00201441465669275</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>-171.5524217825703</v>
+        <v>0.001882142751119442</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>-197.9690385741763</v>
+        <v>0.002171965787639656</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>-222.132770334243</v>
+        <v>0.002437071882322751</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>-244.1705506996234</v>
+        <v>0.002678853654532493</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>-425.248056994327</v>
+        <v>0.004665498391587368</v>
       </c>
     </row>
     <row r="18" ht="15.5" customHeight="1">
@@ -1598,40 +1598,40 @@
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>-9.60211943618784</v>
+        <v>0.0001053471545572795</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>-17.60363588317598</v>
+        <v>0.0001931337099563581</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>-30.11670665972418</v>
+        <v>0.0003304176096040957</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>-42.62977743627263</v>
+        <v>0.0004677015092518357</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>-55.14284821282067</v>
+        <v>0.0006049854088995715</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>-67.65591898936907</v>
+        <v>0.000742269308547311</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>-55.12831114679509</v>
+        <v>0.0006048259192627696</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>-45.69842135682092</v>
+        <v>0.0005013683374482158</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>-46.49679859999744</v>
+        <v>0.0005101275256035883</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>-47.29517584317398</v>
+        <v>0.0005188867137589616</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>-48.09355308635047</v>
+        <v>0.000527645901914334</v>
       </c>
       <c r="O20" s="18" t="n">
-        <v>-78.69066607675232</v>
+        <v>0.0008633341645554521</v>
       </c>
     </row>
     <row r="21" ht="15.5" customHeight="1">
@@ -1810,40 +1810,40 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>-15.89271876470734</v>
+        <v>1914779.168801688</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>-19.18863218489126</v>
+        <v>3454946.400441373</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>-5.347792647082457</v>
+        <v>3420410.585390181</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>7.525392276080723</v>
+        <v>3386219.299243271</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>55.4944416467284</v>
+        <v>3352405.150554138</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>73.03735712297208</v>
+        <v>3318899.196908487</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>72.72681686550015</v>
+        <v>4778130.779680813</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>79.95087046974183</v>
+        <v>6215296.728224049</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>97.5231174011189</v>
+        <v>6153162.132697447</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>113.2302999186447</v>
+        <v>6091647.193784161</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>127.207000971102</v>
+        <v>6030745.830850373</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>164.3907782975346</v>
+        <v>3709627.20636142</v>
       </c>
     </row>
     <row r="25" ht="15.5" customHeight="1">
@@ -1863,40 +1863,40 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>-36.90016400192406</v>
+        <v>3829553.222876904</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>-57.09347216881021</v>
+        <v>6909874.084674947</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>-42.87358423116228</v>
+        <v>6840788.992781426</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>-29.62514139215824</v>
+        <v>6772393.922560597</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>18.71541331517176</v>
+        <v>6704718.027638298</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>36.62611907473103</v>
+        <v>6637688.945221804</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>20.30617149049138</v>
+        <v>9556136.411899384</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>11.76298513855161</v>
+        <v>12430445.3176923</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>30.01711092324058</v>
+        <v>12306159.23627102</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>46.39935350554515</v>
+        <v>12183114.32632199</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>61.04436402213346</v>
+        <v>12061298.29206283</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>123.6938188558404</v>
+        <v>7419049.3249851</v>
       </c>
     </row>
     <row r="26" ht="15.5" customHeight="1">
@@ -1916,40 +1916,40 @@
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>-75.65279159481918</v>
+        <v>-100.0002671190609</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>-50.62317158714297</v>
+        <v>-100.0005417250232</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>-14.25097891699435</v>
+        <v>-100.0009407730696</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>20.25648498964738</v>
+        <v>-100.0013193627298</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>150.8861004876353</v>
+        <v>-100.0027525315614</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>200.5901502887797</v>
+        <v>-100.0032978466089</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>138.7369734676564</v>
+        <v>-100.002619240576</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>117.2508431393913</v>
+        <v>-100.0023835110886</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>144.4658371741738</v>
+        <v>-100.0026820933132</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>169.427946177417</v>
+        <v>-100.0029559585961</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>192.2641037859739</v>
+        <v>-100.0032064995564</v>
       </c>
       <c r="O26" s="18" t="n">
-        <v>403.9387230710793</v>
+        <v>-100.0055288325562</v>
       </c>
     </row>
     <row r="27" ht="15.5" customHeight="1">
@@ -1969,40 +1969,40 @@
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>-175.6527915948192</v>
+        <v>-200.0002671190609</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>-150.623171587143</v>
+        <v>-200.0005417250232</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>-114.2509789169944</v>
+        <v>-200.0009407730696</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>-79.74351501035261</v>
+        <v>-200.0013193627297</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>50.88610048763527</v>
+        <v>-200.0027525315614</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>100.5901502887798</v>
+        <v>-200.0032978466089</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>38.73697346765636</v>
+        <v>-200.0026192405759</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>17.25084313939127</v>
+        <v>-200.0023835110886</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>44.46583717417379</v>
+        <v>-200.0026820933133</v>
       </c>
       <c r="M27" s="18" t="n">
-        <v>69.42794617741703</v>
+        <v>-200.0029559585961</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>92.26410378597393</v>
+        <v>-200.0032064995565</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>303.9387230710794</v>
+        <v>-200.0055288325562</v>
       </c>
     </row>
     <row r="28" ht="15.5" customHeight="1">
@@ -2075,40 +2075,40 @@
         </is>
       </c>
       <c r="D29" s="19" t="n">
-        <v>5.770466583954304</v>
+        <v>-6.330917243087276e-05</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>8.968547905680959</v>
+        <v>-9.839608938974404e-05</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>14.82960588262194</v>
+        <v>-0.0001626991617134425</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>20.74986646539062</v>
+        <v>-0.0002276517600202088</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>26.72992766010641</v>
+        <v>-0.0002932604451785579</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>32.77039351335474</v>
+        <v>-0.0003595318443284063</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>28.53269300473298</v>
+        <v>-0.0003130390160089872</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>27.70548002997099</v>
+        <v>-0.0003039634641286792</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>33.75579994756134</v>
+        <v>-0.0003703429745810532</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>39.8672342077537</v>
+        <v>-0.0004373929851390081</v>
       </c>
       <c r="N29" s="19" t="n">
-        <v>46.04040012713973</v>
+        <v>-0.0005051202685308797</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>80.62014381749219</v>
+        <v>-0.0008845029274644511</v>
       </c>
     </row>
     <row r="30" ht="15.5" customHeight="1">
@@ -2128,40 +2128,40 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>-17.10494637226343</v>
+        <v>1914777.956574081</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>-22.58814591742074</v>
+        <v>3454943.000927641</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-10.91271964333561</v>
+        <v>3420405.020463185</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>-0.1832938512588456</v>
+        <v>3386211.590557144</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>45.66343397961327</v>
+        <v>3352395.319546471</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>61.10525113147914</v>
+        <v>3318887.264802496</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>57.76979504954915</v>
+        <v>4778115.822658997</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>61.0590895164494</v>
+        <v>6215277.836443096</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>74.7359249018585</v>
+        <v>6153139.345504948</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>86.58664998887592</v>
+        <v>6091620.550134231</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>96.74545818513009</v>
+        <v>6030715.369307587</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>131.5808310662943</v>
+        <v>3709594.396414188</v>
       </c>
     </row>
     <row r="31" ht="15.5" customHeight="1">
@@ -2181,40 +2181,40 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>-81.42325817877348</v>
+        <v>-100.0002038098885</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>-59.59171949282393</v>
+        <v>-100.0004433289338</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>-29.08058479961629</v>
+        <v>-100.0007780739079</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>-0.4933814757432371</v>
+        <v>-100.0010917109697</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>124.1561728275289</v>
+        <v>-100.0024592711162</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>167.819756775425</v>
+        <v>-100.0029383147646</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>110.2042804629234</v>
+        <v>-100.0023062015599</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>89.54536310942028</v>
+        <v>-100.0020795476245</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>110.7100372266125</v>
+        <v>-100.0023117503387</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>129.5607119696633</v>
+        <v>-100.0025185656109</v>
       </c>
       <c r="N31" s="19" t="n">
-        <v>146.2237036588342</v>
+        <v>-100.0027013792879</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>323.3185792535872</v>
+        <v>-100.0046443296287</v>
       </c>
     </row>
     <row r="32" ht="15.5" customHeight="1">
@@ -2287,40 +2287,40 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>-17.10494637226343</v>
+        <v>1914777.956574081</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>-22.58814591742074</v>
+        <v>3454943.000927641</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>-10.91271964333561</v>
+        <v>3420405.020463185</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>-0.1832938512588456</v>
+        <v>3386211.590557144</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>45.66343397961327</v>
+        <v>3352395.319546471</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>61.10525113147914</v>
+        <v>3318887.264802496</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>57.76979504954915</v>
+        <v>4778115.822658997</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>61.0590895164494</v>
+        <v>6215277.836443096</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>74.7359249018585</v>
+        <v>6153139.345504948</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>86.58664998887592</v>
+        <v>6091620.550134231</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>96.74545818513009</v>
+        <v>6030715.369307587</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>131.5808310662943</v>
+        <v>3709594.396414188</v>
       </c>
     </row>
     <row r="34" ht="15.5" customHeight="1">
@@ -2340,40 +2340,40 @@
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>-38.11239160948016</v>
+        <v>3829552.010649296</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>-60.49298590133969</v>
+        <v>6909870.685161214</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-48.43851122741543</v>
+        <v>6840783.42785443</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>-37.33382751949781</v>
+        <v>6772386.21387447</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>8.884405648056628</v>
+        <v>6704708.196630631</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>24.69401308323809</v>
+        <v>6637677.013115812</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>5.349149674540371</v>
+        <v>9556121.45487757</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>-7.128795814740812</v>
+        <v>12430426.42591134</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>7.22991842398018</v>
+        <v>12306136.44907852</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>19.75570357577639</v>
+        <v>12183087.68267206</v>
       </c>
       <c r="N34" s="19" t="n">
-        <v>30.58282123616155</v>
+        <v>12061267.83052004</v>
       </c>
       <c r="O34" s="19" t="n">
-        <v>90.88387162460006</v>
+        <v>7419016.515037868</v>
       </c>
     </row>
     <row r="35" ht="15.5" customHeight="1">
@@ -2446,40 +2446,40 @@
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>0</v>
+        <v>-1072274.562981803</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>0</v>
+        <v>-1934763.79184514</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>0</v>
+        <v>-1915419.35979924</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>0</v>
+        <v>-1896268.139884852</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>0</v>
+        <v>-1877318.295056577</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>0</v>
+        <v>-1858549.563672428</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>0</v>
+        <v>-2675714.00736572</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>0</v>
+        <v>-3480519.399255177</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>0</v>
+        <v>-3445718.205741984</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>0</v>
+        <v>-3411264.551148178</v>
       </c>
       <c r="N36" s="19" t="n">
-        <v>0</v>
+        <v>-3377154.992545612</v>
       </c>
       <c r="O36" s="19" t="n">
-        <v>0</v>
+        <v>-2077324.624210603</v>
       </c>
     </row>
     <row r="37" ht="15.5" customHeight="1">
@@ -2499,40 +2499,40 @@
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>-38.11239160948016</v>
+        <v>0</v>
       </c>
       <c r="E37" s="19" t="n">
-        <v>-63.40513331513459</v>
+        <v>0</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>-60.82204606908083</v>
+        <v>0</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>-58.73662821567898</v>
+        <v>0</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>-23.36132123535184</v>
+        <v>0</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>-18.85034047530475</v>
+        <v>0</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>-45.55927669070992</v>
+        <v>0</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>-70.18627774561173</v>
+        <v>0</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>-79.93234872714096</v>
+        <v>0</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>-91.9202498522328</v>
+        <v>0</v>
       </c>
       <c r="N37" s="19" t="n">
-        <v>-105.4837761424853</v>
+        <v>0</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>-69.30738323267934</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" ht="15.5" customHeight="1">
@@ -2552,40 +2552,40 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>-17.10494637226343</v>
+        <v>842503.3935922775</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>-22.58814591742074</v>
+        <v>1520179.209082501</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-10.91271964333561</v>
+        <v>1504985.660663945</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>-0.1832938512588456</v>
+        <v>1489943.450672292</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>45.66343397961327</v>
+        <v>1475077.024489895</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>61.10525113147914</v>
+        <v>1460337.701130068</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>57.76979504954915</v>
+        <v>2102401.815293277</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>61.0590895164494</v>
+        <v>2734758.437187919</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>74.7359249018585</v>
+        <v>2707421.139762964</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>86.58664998887592</v>
+        <v>2680355.998986054</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>96.74545818513009</v>
+        <v>2653560.376761975</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>131.5808310662943</v>
+        <v>1632269.772203585</v>
       </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
@@ -2605,40 +2605,40 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>-81.42325817877348</v>
+        <v>-44.00014674311972</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>-59.59171949282393</v>
+        <v>-44.00031919683236</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>-29.08058479961629</v>
+        <v>-44.00056021321371</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>-0.4933814757432371</v>
+        <v>-44.00078603189821</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>124.1561728275289</v>
+        <v>-44.00177067520368</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>167.819756775425</v>
+        <v>-44.00211558663049</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>110.2042804629234</v>
+        <v>-44.00166046512315</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>89.54536310942028</v>
+        <v>-44.00149727428959</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>110.7100372266125</v>
+        <v>-44.00166446024384</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>129.5607119696633</v>
+        <v>-44.00181336723987</v>
       </c>
       <c r="N39" s="19" t="n">
-        <v>146.2237036588342</v>
+        <v>-44.00194499308729</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>323.3185792535872</v>
+        <v>-44.00334391733265</v>
       </c>
     </row>
     <row r="40" ht="15.5" customHeight="1">
@@ -2817,40 +2817,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>-12.97960432912783</v>
+        <v>-7609789.543544516</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>-112.1954152756952</v>
+        <v>-7928248.051413828</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>-181.7340005017653</v>
+        <v>-7934961.533243593</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>-245.7100716152933</v>
+        <v>-7938027.886845451</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>-269.0698955312246</v>
+        <v>-7938921.070936996</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>-285.8060178654374</v>
+        <v>-7939864.617604261</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>-325.2020365239119</v>
+        <v>-7939767.983300803</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>-393.6350047445423</v>
+        <v>-7939645.019732312</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>1849.764848802694</v>
+        <v>-7942572.281087654</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>4079.046119714742</v>
+        <v>-7946470.533356968</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>6318.313564514343</v>
+        <v>-7948304.0420189</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>8628.846569430483</v>
+        <v>-7949111.341035689</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -2870,40 +2870,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>-12.89080379420969</v>
+        <v>-7609789.454743981</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>-111.7539675135071</v>
+        <v>-7928247.609966066</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>-180.9470196422504</v>
+        <v>-7934960.746262733</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>-244.6414513709642</v>
+        <v>-7938026.818225207</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>-264.8196383440264</v>
+        <v>-7938916.820679809</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>-280.8597263801778</v>
+        <v>-7939859.671312776</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>-319.6664012418141</v>
+        <v>-7939762.447665521</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>-386.5815377723484</v>
+        <v>-7939637.96626534</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>1858.169193470844</v>
+        <v>-7942563.876742985</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>4088.649869228518</v>
+        <v>-7946460.929607455</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>6328.976280574999</v>
+        <v>-7948293.379302839</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>8640.438760183135</v>
+        <v>-7949099.748844936</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -3029,40 +3029,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>28.23613432777929</v>
+        <v>-7609748.327805859</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>2.175824022751257</v>
+        <v>-7928133.68017453</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>2.861776030756204</v>
+        <v>-7934776.93746706</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>6.208588377913458</v>
+        <v>-7937775.968185457</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>47.29901068701179</v>
+        <v>-7938604.702030778</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>92.16922371452927</v>
+        <v>-7939486.642362681</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>143.6882370961362</v>
+        <v>-7939299.093027183</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>194.0800577291628</v>
+        <v>-7939057.304669838</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>2551.032122886018</v>
+        <v>-7941871.01381357</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>4888.645753936089</v>
+        <v>-7945660.933722747</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>7231.077905916831</v>
+        <v>-7947391.277677497</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>9590.995119186126</v>
+        <v>-7948149.192485933</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -3082,40 +3082,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>1.772782626653562</v>
+        <v>-5205776.601344177</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>-20.81536329076718</v>
+        <v>-8660631.835371565</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>-17.53528397563426</v>
+        <v>-10229521.80012366</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>-4.022268027621354</v>
+        <v>-10213639.41197227</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>45.89126346265664</v>
+        <v>-10146630.65323666</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>100.4672382735091</v>
+        <v>-10079216.71270177</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>209.1979520691639</v>
+        <v>-11504218.78129222</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>222.9407989888188</v>
+        <v>-14399294.69342276</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>746.7181916938598</v>
+        <v>-15822386.96572444</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>1110.072164334631</v>
+        <v>-15747619.76426221</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>2476.162322506068</v>
+        <v>-15624980.47491582</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>3815.348693687808</v>
+        <v>-13241711.36922383</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -3135,40 +3135,40 @@
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
     </row>
     <row r="50" ht="15.5" customHeight="1">
@@ -3188,40 +3188,40 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>-17.10494637226343</v>
+        <v>-1914733.015937628</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>-22.58814591742074</v>
+        <v>-3454855.234027387</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>-10.91271964333561</v>
+        <v>-3420308.873920204</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>-0.1832938512588456</v>
+        <v>-3386107.863712635</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>45.66343397961327</v>
+        <v>-3352254.79011182</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>61.10525113147914</v>
+        <v>-3318729.534046552</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>57.76979504954915</v>
+        <v>-4777915.895874124</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>61.0590895164494</v>
+        <v>-6215032.800342774</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>74.7359249018585</v>
+        <v>-6152886.253117351</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>86.58664998887592</v>
+        <v>-6091361.198987383</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>96.74545818513009</v>
+        <v>-6030451.414438367</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>88.22221841085697</v>
+        <v>-3709374.593364711</v>
       </c>
     </row>
     <row r="51" ht="15.5" customHeight="1">
@@ -3244,37 +3244,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>-17.10494637226343</v>
+        <v>-1914733.015937628</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>-25.50029333121564</v>
+        <v>-3518169.340796908</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>-22.7167031752795</v>
+        <v>-3536487.962853086</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>-18.64989951587362</v>
+        <v>-3503332.277718294</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>20.48425814311301</v>
+        <v>-3469443.593248669</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>132.5504280206978</v>
+        <v>-3435259.300011547</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>143.0039804734524</v>
+        <v>-4893218.307673439</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>653.1045377930843</v>
+        <v>-6378457.127200537</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>1004.607785346838</v>
+        <v>-6365214.979868273</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>2360.539135322021</v>
+        <v>-6303485.475070905</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>3708.248746278034</v>
+        <v>-6241293.190452569</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -3294,40 +3294,40 @@
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4255390.724430324</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4349267.896404509</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4348235.339838852</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4349043.278031831</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4349209.610948668</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4350231.024988095</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4301892.069965376</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>-680.3634868649468</v>
+        <v>-4255796.414535776</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>-352.0533234613428</v>
+        <v>-4259785.470733798</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>-10.61206497177784</v>
+        <v>-4262726.227166624</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>343.8289776528944</v>
+        <v>-4265155.049027689</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>711.1398065713162</v>
+        <v>-4341868.210950826</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -3347,40 +3347,40 @@
         </is>
       </c>
       <c r="D53" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4255390.724430324</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4349267.896404509</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4348235.339838852</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4349043.278031831</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4349209.610948668</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4350231.024988095</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4301892.069965376</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>-680.3634868649468</v>
+        <v>-4255796.414535776</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>-352.0533234613428</v>
+        <v>-4259785.470733798</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>-10.61206497177784</v>
+        <v>-4262726.227166624</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>343.8289776528944</v>
+        <v>-4265155.049027689</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>711.1398065713162</v>
+        <v>-4341868.210950826</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -3612,40 +3612,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>49.24357956499601</v>
+        <v>-9461167.236973967</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>27.00808087484522</v>
+        <v>-13009899.29032831</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>30.63369328730487</v>
+        <v>-14577756.35298165</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>44.42834862013205</v>
+        <v>-14562681.62138386</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>97.52351705327906</v>
+        <v>-14495836.01392815</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>152.795526162193</v>
+        <v>-14429442.79139838</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>262.115583754686</v>
+        <v>-15806105.31562231</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>-450.3692209039341</v>
+        <v>-18655084.05449157</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>403.0692129006669</v>
+        <v>-20082164.03211357</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>1109.06384887663</v>
+        <v>-20010336.38767932</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>2830.654016219617</v>
+        <v>-19890124.86122745</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>4538.080691011775</v>
+        <v>-17583567.9879839</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -3665,40 +3665,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>-21.00744523721673</v>
+        <v>1851418.909168108</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>-24.83225685209396</v>
+        <v>5081765.610153781</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>-27.77191725654867</v>
+        <v>6642979.415514593</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>-38.21976024221859</v>
+        <v>6624905.653198398</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>-50.22450636626728</v>
+        <v>6557231.311897367</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>-60.62630244766373</v>
+        <v>6489956.149035697</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>-118.4273466585498</v>
+        <v>7866806.222595132</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>644.4492786330969</v>
+        <v>10716026.74982173</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>2147.962909985351</v>
+        <v>12140293.0183</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>3779.581905059459</v>
+        <v>12064675.45395657</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>4400.423889697213</v>
+        <v>11942733.58354995</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>5052.91442817435</v>
+        <v>9635418.795497969</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -3771,40 +3771,40 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>-36.90016400192406</v>
+        <v>3829553.222876904</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>-57.09347216881021</v>
+        <v>6909874.084674947</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>-42.87358423116228</v>
+        <v>6840788.992781426</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>-29.62514139215824</v>
+        <v>6772393.922560597</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>18.71541331517176</v>
+        <v>6704718.027638298</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>36.62611907473103</v>
+        <v>6637688.945221804</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>20.30617149049138</v>
+        <v>9556136.411899384</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>11.76298513855161</v>
+        <v>12430445.3176923</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>30.01711092324058</v>
+        <v>12306159.23627102</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>46.39935350554515</v>
+        <v>12183114.32632199</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>61.04436402213346</v>
+        <v>12061298.29206283</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>123.6938188558404</v>
+        <v>7419049.3249851</v>
       </c>
     </row>
     <row r="62" ht="15.5" customHeight="1">
@@ -3824,40 +3824,40 @@
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>0</v>
+        <v>-1072274.562981803</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>0</v>
+        <v>-1934763.79184514</v>
       </c>
       <c r="F62" s="18" t="n">
-        <v>0</v>
+        <v>-1915419.35979924</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>0</v>
+        <v>-1896268.139884852</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>0</v>
+        <v>-1877318.295056577</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>0</v>
+        <v>-1858549.563672428</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>0</v>
+        <v>-2675714.00736572</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>0</v>
+        <v>-3480519.399255177</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>0</v>
+        <v>-3445718.205741984</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>0</v>
+        <v>-3411264.551148178</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>0</v>
+        <v>-3377154.992545612</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>0</v>
+        <v>-2077324.624210603</v>
       </c>
     </row>
     <row r="63" ht="15.5" customHeight="1">
@@ -3930,40 +3930,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>-36.72256293208777</v>
+        <v>2757278.83749617</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>-56.38817771427031</v>
+        <v>4975110.998124261</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>-42.18251803650881</v>
+        <v>4925370.324048379</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>-29.0618626225297</v>
+        <v>4876126.345954515</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>25.0786872009098</v>
+        <v>4827406.095855607</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>38.01818767085388</v>
+        <v>4779140.773617974</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>21.48485908416787</v>
+        <v>6880423.583221258</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>14.79864851874381</v>
+        <v>8949928.954100501</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>32.71886631515252</v>
+        <v>8860443.732284423</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>48.79816319679809</v>
+        <v>8771852.173983505</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>63.16229711589164</v>
+        <v>8684145.417450309</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>125.5527682398313</v>
+        <v>5341726.55972388</v>
       </c>
     </row>
     <row r="65" ht="15.5" customHeight="1">
@@ -4089,40 +4089,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>-79.15052919655098</v>
+        <v>2757236.409529906</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>-132.9431920883391</v>
+        <v>4975034.443109888</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>-117.971982266837</v>
+        <v>4925294.534584149</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>-104.0934322105545</v>
+        <v>4876051.314384927</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>-49.20256669123491</v>
+        <v>4827331.814601715</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>-35.52025368236934</v>
+        <v>4779067.23517662</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-84.38719477186457</v>
+        <v>6880317.711167402</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>-122.9179212882056</v>
+        <v>8949791.237530693</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>-103.6205377937274</v>
+        <v>8860307.392880315</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>-86.17784687099301</v>
+        <v>8771717.197973438</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>-70.46395285122156</v>
+        <v>8684011.791200342</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>43.35861265543728</v>
+        <v>5341644.365568296</v>
       </c>
     </row>
     <row r="68" ht="15.5" customHeight="1">
@@ -4301,40 +4301,40 @@
         </is>
       </c>
       <c r="D71" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="E71" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="F71" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="G71" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="I71" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="J71" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="K71" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="L71" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="M71" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="N71" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="O71" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
     </row>
     <row r="72" ht="15.5" customHeight="1">
@@ -4354,40 +4354,40 @@
         </is>
       </c>
       <c r="D72" s="18" t="n">
-        <v>0</v>
+        <v>-2757236.409529906</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>0</v>
+        <v>-4975034.443109888</v>
       </c>
       <c r="F72" s="18" t="n">
-        <v>0</v>
+        <v>-4925294.534584149</v>
       </c>
       <c r="G72" s="18" t="n">
-        <v>0</v>
+        <v>-4876051.314384927</v>
       </c>
       <c r="H72" s="18" t="n">
-        <v>0</v>
+        <v>-4827331.814601715</v>
       </c>
       <c r="I72" s="18" t="n">
-        <v>0</v>
+        <v>-4779067.23517662</v>
       </c>
       <c r="J72" s="18" t="n">
-        <v>0</v>
+        <v>-6880317.711167402</v>
       </c>
       <c r="K72" s="18" t="n">
-        <v>0</v>
+        <v>-8949791.237530693</v>
       </c>
       <c r="L72" s="18" t="n">
-        <v>0</v>
+        <v>-8860307.392880315</v>
       </c>
       <c r="M72" s="18" t="n">
-        <v>0</v>
+        <v>-8771717.197973438</v>
       </c>
       <c r="N72" s="18" t="n">
-        <v>0</v>
+        <v>-8684011.791200342</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>-43.35861265543728</v>
+        <v>-5341644.365568296</v>
       </c>
     </row>
     <row r="73" ht="15.5" customHeight="1">
@@ -4407,40 +4407,40 @@
         </is>
       </c>
       <c r="D73" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="E73" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="F73" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="G73" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="I73" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="J73" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="K73" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="N73" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="O73" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
     </row>
     <row r="74" ht="15.5" customHeight="1">
@@ -4460,40 +4460,40 @@
         </is>
       </c>
       <c r="D74" s="18" t="n">
-        <v>66.25972540234129</v>
+        <v>-10367025.86427389</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>66.25972540234129</v>
+        <v>-12584823.89785387</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>66.25972540234129</v>
+        <v>-12535083.98932813</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>66.25972540234129</v>
+        <v>-12485840.76912891</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>66.25972540234129</v>
+        <v>-12437121.2693457</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>66.25972540234129</v>
+        <v>-12388856.6899206</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>66.25972540234129</v>
+        <v>-14490107.16591138</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>66.25972540234129</v>
+        <v>-16559580.69227467</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>66.25972540234129</v>
+        <v>-16470096.8476243</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>66.25972540234129</v>
+        <v>-16381506.65271742</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>66.25972540234129</v>
+        <v>-16293801.24594432</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>22.90111274690401</v>
+        <v>-12951433.82031228</v>
       </c>
     </row>
     <row r="75" ht="15.5" customHeight="1">
@@ -4513,40 +4513,40 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>-12.89080379420969</v>
+        <v>-7609789.454743981</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-66.6834666859978</v>
+        <v>-7609789.454743982</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>-51.71225686449576</v>
+        <v>-7609789.454743982</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>-37.83370680821322</v>
+        <v>-7609789.45474398</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>17.05715871110637</v>
+        <v>-7609789.454743982</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>30.73947171997195</v>
+        <v>-7609789.45474398</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>-18.12746936952328</v>
+        <v>-7609789.454743982</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>-56.6581958858643</v>
+        <v>-7609789.454743981</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>-37.36081239138612</v>
+        <v>-7609789.454743981</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>-19.91812146865172</v>
+        <v>-7609789.454743981</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>-4.204227448880275</v>
+        <v>-7609789.454743981</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>66.25972540234129</v>
+        <v>-7609789.45474398</v>
       </c>
     </row>
     <row r="76" ht="15.5" customHeight="1">
@@ -4569,37 +4569,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>-12.89080379420969</v>
+        <v>-7609789.454743981</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>-111.7539675135071</v>
+        <v>-7928247.609966066</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>-180.9470196422504</v>
+        <v>-7934960.746262733</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>-244.6414513709642</v>
+        <v>-7938026.818225207</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>-264.8196383440264</v>
+        <v>-7938916.820679809</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>-280.8597263801778</v>
+        <v>-7939859.671312776</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>-319.6664012418141</v>
+        <v>-7939762.447665521</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>-386.5815377723484</v>
+        <v>-7939637.96626534</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>1858.169193470844</v>
+        <v>-7942563.876742985</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>4088.649869228518</v>
+        <v>-7946460.929607455</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>6328.976280574999</v>
+        <v>-7948293.379302839</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -4619,40 +4619,40 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>-12.89080379420969</v>
+        <v>-7609789.454743981</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-66.6834666859978</v>
+        <v>-7609789.454743982</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>-51.71225686449576</v>
+        <v>-7609789.454743982</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>-37.83370680821322</v>
+        <v>-7609789.45474398</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>17.05715871110637</v>
+        <v>-7609789.454743982</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>30.73947171997195</v>
+        <v>-7609789.45474398</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>-18.12746936952328</v>
+        <v>-7609789.454743982</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>-56.6581958858643</v>
+        <v>-7609789.454743981</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>-37.36081239138612</v>
+        <v>-7609789.454743981</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>-19.91812146865172</v>
+        <v>-7609789.454743981</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>-4.204227448880275</v>
+        <v>-7609789.454743981</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>66.25972540234129</v>
+        <v>-7609789.45474398</v>
       </c>
     </row>
     <row r="78" ht="15.5" customHeight="1">
@@ -4672,40 +4672,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>-12.89080379420969</v>
+        <v>-7609789.454743981</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>-111.7539675135071</v>
+        <v>-7928247.609966066</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>-180.9470196422504</v>
+        <v>-7934960.746262733</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>-244.6414513709642</v>
+        <v>-7938026.818225207</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>-264.8196383440264</v>
+        <v>-7938916.820679809</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>-280.8597263801778</v>
+        <v>-7939859.671312776</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>-319.6664012418141</v>
+        <v>-7939762.447665521</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>-386.5815377723484</v>
+        <v>-7939637.96626534</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>1858.169193470844</v>
+        <v>-7942563.876742985</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>4088.649869228518</v>
+        <v>-7946460.929607455</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>6328.976280574999</v>
+        <v>-7948293.379302839</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>8640.438760183135</v>
+        <v>-7949099.748844936</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -4831,40 +4831,40 @@
         </is>
       </c>
       <c r="D81" s="18" t="n">
-        <v>201.9663304384007</v>
+        <v>-0.002215821035080548</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>201.9663304384007</v>
+        <v>-0.002215821035080548</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>201.9663304384007</v>
+        <v>-0.002215821035080548</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>201.9663304384007</v>
+        <v>-0.002215821035080547</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>201.9663304384007</v>
+        <v>-0.002215821035080548</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>201.9663304384007</v>
+        <v>-0.002215821035080548</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>201.9663304384007</v>
+        <v>-0.002215821035080548</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>201.9663304384007</v>
+        <v>-0.002215821035080548</v>
       </c>
       <c r="L81" s="18" t="n">
-        <v>201.9663304384007</v>
+        <v>-0.002215821035080547</v>
       </c>
       <c r="M81" s="18" t="n">
-        <v>201.9663304384007</v>
+        <v>-0.002215821035080548</v>
       </c>
       <c r="N81" s="18" t="n">
-        <v>201.9663304384007</v>
+        <v>-0.002215821035080547</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>201.9663304384007</v>
+        <v>-0.002215821035080547</v>
       </c>
     </row>
     <row r="82" ht="15.5" customHeight="1">
@@ -5653,37 +5653,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>1.772782626653562</v>
+        <v>308696.217715634</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>-6.622564332298655</v>
+        <v>3147680.801105952</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>-3.838974176362507</v>
+        <v>3171599.760695905</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>0.2278294830433651</v>
+        <v>3105404.320405772</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>39.36198714203</v>
+        <v>3039803.634937002</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>482.5467330648956</v>
+        <v>2974861.436564016</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>493.4905204380382</v>
+        <v>5716138.742694573</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>3892.036186724068</v>
+        <v>8508753.224930426</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>5722.408997198788</v>
+        <v>8481540.1778911</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>7734.908215973969</v>
+        <v>8362314.264539823</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>9743.670858868447</v>
+        <v>8244575.768517966</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -5703,40 +5703,40 @@
         </is>
       </c>
       <c r="D97" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="E97" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="F97" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="G97" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="H97" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="I97" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="J97" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="K97" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="N97" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
       <c r="O97" s="19" t="n">
-        <v>18.87772899891699</v>
+        <v>-3291043.585406549</v>
       </c>
     </row>
     <row r="98" ht="15.5" customHeight="1">
@@ -5756,40 +5756,40 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>-17.10494637226343</v>
+        <v>842503.3935922775</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>-22.58814591742074</v>
+        <v>1520179.209082501</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>-10.91271964333561</v>
+        <v>1504985.660663945</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>-0.1832938512588456</v>
+        <v>1489943.450672292</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>45.66343397961327</v>
+        <v>1475077.024489895</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>61.10525113147914</v>
+        <v>1460337.701130068</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>57.76979504954915</v>
+        <v>2102401.815293277</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>61.0590895164494</v>
+        <v>2734758.437187919</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>74.7359249018585</v>
+        <v>2707421.139762964</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>86.58664998887592</v>
+        <v>2680355.998986054</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>96.74545818513009</v>
+        <v>2653560.376761975</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>131.5808310662943</v>
+        <v>1632269.772203585</v>
       </c>
     </row>
     <row r="99" ht="15.5" customHeight="1">
@@ -5809,40 +5809,40 @@
         </is>
       </c>
       <c r="D99" s="20" t="n">
-        <v>0</v>
+        <v>2757236.409529906</v>
       </c>
       <c r="E99" s="20" t="n">
-        <v>0</v>
+        <v>4975034.443109888</v>
       </c>
       <c r="F99" s="20" t="n">
-        <v>0</v>
+        <v>4925294.534584149</v>
       </c>
       <c r="G99" s="20" t="n">
-        <v>0</v>
+        <v>4876051.314384927</v>
       </c>
       <c r="H99" s="20" t="n">
-        <v>0</v>
+        <v>4827331.814601715</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>0</v>
+        <v>4779067.23517662</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>0</v>
+        <v>6880317.711167402</v>
       </c>
       <c r="K99" s="20" t="n">
-        <v>0</v>
+        <v>8949791.237530693</v>
       </c>
       <c r="L99" s="20" t="n">
-        <v>0</v>
+        <v>8860307.392880315</v>
       </c>
       <c r="M99" s="20" t="n">
-        <v>0</v>
+        <v>8771717.197973438</v>
       </c>
       <c r="N99" s="20" t="n">
-        <v>0</v>
+        <v>8684011.791200342</v>
       </c>
       <c r="O99" s="20" t="n">
-        <v>43.35861265543728</v>
+        <v>5341644.365568296</v>
       </c>
     </row>
     <row r="100" ht="15.5" customHeight="1">
@@ -5862,40 +5862,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>1.772782626653562</v>
+        <v>308696.217715634</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>-6.622564332298655</v>
+        <v>3147680.801105952</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>-3.838974176362507</v>
+        <v>3171599.760695905</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>0.2278294830433651</v>
+        <v>3105404.320405772</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>39.36198714203</v>
+        <v>3039803.634937002</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>482.5467330648956</v>
+        <v>2974861.436564016</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>493.4905204380382</v>
+        <v>5716138.742694573</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>3892.036186724068</v>
+        <v>8508753.224930426</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>5722.408997198788</v>
+        <v>8481540.1778911</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>7734.908215973969</v>
+        <v>8362314.264539823</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>9743.670858868447</v>
+        <v>8244575.768517966</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>11814.16005190357</v>
+        <v>3877239.717566536</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -5968,40 +5968,40 @@
         </is>
       </c>
       <c r="D102" s="18" t="n">
-        <v>-49.51320340520806</v>
+        <v>4512999.85047596</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>-49.51320340520807</v>
+        <v>4512999.85047596</v>
       </c>
       <c r="F102" s="18" t="n">
-        <v>-49.51320340520806</v>
+        <v>4512999.850475959</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>-49.51320340520807</v>
+        <v>4512999.850475961</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>-49.51320340520806</v>
+        <v>4512999.85047596</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>-49.51320340520806</v>
+        <v>4512999.850475961</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>-49.51320340520807</v>
+        <v>4512999.85047596</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>-49.51320340520807</v>
+        <v>4512999.85047596</v>
       </c>
       <c r="L102" s="18" t="n">
-        <v>-49.51320340520806</v>
+        <v>4512999.850475961</v>
       </c>
       <c r="M102" s="18" t="n">
-        <v>-49.51320340520807</v>
+        <v>4512999.85047596</v>
       </c>
       <c r="N102" s="18" t="n">
-        <v>-49.51320340520807</v>
+        <v>4512999.850475961</v>
       </c>
       <c r="O102" s="18" t="n">
-        <v>-49.51320340520807</v>
+        <v>4512999.850475961</v>
       </c>
     </row>
     <row r="103" ht="15.5" customHeight="1">
@@ -6024,37 +6024,37 @@
         <v>0</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4255390.724430324</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4349267.896404509</v>
       </c>
       <c r="G103" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4348235.339838852</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4349043.278031831</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4349209.610948668</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4350231.024988095</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4301892.069965376</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>-680.3634868649468</v>
+        <v>-4255796.414535776</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>-352.0533234613428</v>
+        <v>-4259785.470733798</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>-10.61206497177784</v>
+        <v>-4262726.227166624</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>343.8289776528944</v>
+        <v>-4265155.049027689</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -6074,40 +6074,40 @@
         </is>
       </c>
       <c r="D104" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="E104" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="F104" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="G104" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="H104" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="I104" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="J104" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="K104" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="L104" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="M104" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="N104" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
       <c r="O104" s="19" t="n">
-        <v>47.3819964034243</v>
+        <v>-4318745.869337432</v>
       </c>
     </row>
     <row r="105" ht="15.5" customHeight="1">
@@ -6127,40 +6127,40 @@
         </is>
       </c>
       <c r="D105" s="18" t="n">
-        <v>-21.00744523721673</v>
+        <v>1914774.054075216</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>-37.90483998391895</v>
+        <v>3454927.684233574</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>-37.52579158407983</v>
+        <v>3420378.407391245</v>
       </c>
       <c r="G105" s="18" t="n">
-        <v>-37.15053366823896</v>
+        <v>3386174.623317326</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>-36.77902833155665</v>
+        <v>3352312.87708416</v>
       </c>
       <c r="I105" s="18" t="n">
-        <v>-36.41123804824105</v>
+        <v>3318789.748313316</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>-52.42064537500877</v>
+        <v>4778005.632218572</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>-68.18788533119022</v>
+        <v>6215148.589468248</v>
       </c>
       <c r="L105" s="18" t="n">
-        <v>-67.50600647787832</v>
+        <v>6152997.103573568</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>-66.83094641309953</v>
+        <v>6091467.13253783</v>
       </c>
       <c r="N105" s="18" t="n">
-        <v>-66.16263694896854</v>
+        <v>6030552.461212453</v>
       </c>
       <c r="O105" s="18" t="n">
-        <v>-40.69695944169418</v>
+        <v>3709422.11862368</v>
       </c>
     </row>
     <row r="106" ht="15.5" customHeight="1">
@@ -6233,40 +6233,40 @@
         </is>
       </c>
       <c r="D107" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4255390.724430324</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4349267.896404509</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4348235.339838852</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4349043.278031831</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4349209.610948668</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4350231.024988095</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>47.3819964034243</v>
+        <v>-4301892.069965376</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>-680.3634868649468</v>
+        <v>-4255796.414535776</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>-352.0533234613428</v>
+        <v>-4259785.470733798</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>-10.61206497177784</v>
+        <v>-4262726.227166624</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>343.8289776528944</v>
+        <v>-4265155.049027689</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>711.1398065713162</v>
+        <v>-4341868.210950826</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -6675,40 +6675,40 @@
         </is>
       </c>
       <c r="D2" s="18" t="n">
-        <v>15716.15545699833</v>
+        <v>229652843.897368</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>13272.74255237291</v>
+        <v>290117136.5731548</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>13182.26265043306</v>
+        <v>287218560.7430964</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>13088.35529541582</v>
+        <v>284345097.7206781</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>12991.70468604554</v>
+        <v>281504234.2645646</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>12892.27844411412</v>
+        <v>278687984.4548331</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>14191.86712563408</v>
+        <v>307480284.4769629</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>15481.02574800273</v>
+        <v>335832150.0955243</v>
       </c>
       <c r="L2" s="18" t="n">
-        <v>15357.43432954528</v>
+        <v>332473163.4620945</v>
       </c>
       <c r="M2" s="18" t="n">
-        <v>15231.65579378531</v>
+        <v>329149078.6022264</v>
       </c>
       <c r="N2" s="18" t="n">
-        <v>15103.83859589641</v>
+        <v>325856615.8221337</v>
       </c>
       <c r="O2" s="18" t="n">
-        <v>10915.81608973005</v>
+        <v>223703276.1013565</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
@@ -6731,37 +6731,37 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>-15.54714135598211</v>
+        <v>26.3285625597601</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>-0.6816971065537025</v>
+        <v>-0.999105349065621</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>-0.7123766041344459</v>
+        <v>-1.000444753634322</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>-0.7384473235084621</v>
+        <v>-0.9990900067861186</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>-0.7653055879435433</v>
+        <v>-1.000428933898256</v>
       </c>
       <c r="J3" s="18" t="n">
-        <v>10.08036467063183</v>
+        <v>10.33137473739778</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>9.083784472869748</v>
+        <v>9.22071009098655</v>
       </c>
       <c r="L3" s="18" t="n">
-        <v>-0.7983412757607278</v>
+        <v>-1.000198055032664</v>
       </c>
       <c r="M3" s="18" t="n">
-        <v>-0.819007479120315</v>
+        <v>-0.9998054655761757</v>
       </c>
       <c r="N3" s="18" t="n">
-        <v>-0.8391549784170782</v>
+        <v>-1.000295305116627</v>
       </c>
       <c r="O3" s="18" t="n">
-        <v>-27.72819955388167</v>
+        <v>-31.34916854857929</v>
       </c>
     </row>
     <row r="4" ht="15.5" customHeight="1">
@@ -6887,40 +6887,40 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>10190.27545699833</v>
+        <v>229647318.017368</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>12873.52055237291</v>
+        <v>290116737.3511548</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>12744.89865043306</v>
+        <v>287218123.3790964</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>12617.39129541582</v>
+        <v>284344626.7566781</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>12491.33068604555</v>
+        <v>281503733.8905646</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>12366.36244411412</v>
+        <v>278687458.5388331</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>13643.97912563408</v>
+        <v>307479736.5889629</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>14902.05174800273</v>
+        <v>335831571.1215243</v>
       </c>
       <c r="L6" s="18" t="n">
-        <v>14753.00032954528</v>
+        <v>332472559.0280945</v>
       </c>
       <c r="M6" s="18" t="n">
-        <v>14605.49779378531</v>
+        <v>329148452.4442264</v>
       </c>
       <c r="N6" s="18" t="n">
-        <v>14459.39859589641</v>
+        <v>325855971.3821337</v>
       </c>
       <c r="O6" s="18" t="n">
-        <v>9926.473089730054</v>
+        <v>223702286.7583565</v>
       </c>
     </row>
     <row r="7" ht="15.5" customHeight="1">
@@ -6946,34 +6946,34 @@
         <v>26.33142849472054</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>-0.9991198710296856</v>
+        <v>-0.9991198710296967</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>-1.000457975496771</v>
+        <v>-1.00045797549676</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>-0.9991020046756893</v>
+        <v>-0.9991020046756782</v>
       </c>
       <c r="I7" s="18" t="n">
         <v>-1.000439785578922</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>10.33138634981587</v>
+        <v>10.33138634981585</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>9.22071641113118</v>
+        <v>9.220716411131203</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>-1.000207360556427</v>
+        <v>-1.000207360556449</v>
       </c>
       <c r="M7" s="18" t="n">
-        <v>-0.999813817292261</v>
+        <v>-0.9998138172922499</v>
       </c>
       <c r="N7" s="18" t="n">
         <v>-1.000302762368488</v>
       </c>
       <c r="O7" s="18" t="n">
-        <v>-31.34933639254405</v>
+        <v>-31.34933639254406</v>
       </c>
     </row>
     <row r="8" ht="15.5" customHeight="1">
@@ -6993,40 +6993,40 @@
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>-64.83949261561071</v>
+        <v>-99.99759381163925</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-96.99216647633516</v>
+        <v>-99.99986239282356</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>-96.68217807824038</v>
+        <v>-99.99984772432572</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>-96.40165636269857</v>
+        <v>-99.99983436886946</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>-96.14851159188174</v>
+        <v>-99.99982224992057</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>-95.92069002946408</v>
+        <v>-99.99981128859895</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>-96.13942270492106</v>
+        <v>-99.99982181361614</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>-96.26010569697104</v>
+        <v>-99.99982760018665</v>
       </c>
       <c r="L8" s="18" t="n">
-        <v>-96.06422539709537</v>
+        <v>-99.99981820066508</v>
       </c>
       <c r="M8" s="18" t="n">
-        <v>-95.8891009061833</v>
+        <v>-99.99980976462014</v>
       </c>
       <c r="N8" s="18" t="n">
-        <v>-95.73327008291065</v>
+        <v>-99.99980223203437</v>
       </c>
       <c r="O8" s="18" t="n">
-        <v>-90.93660985246163</v>
+        <v>-99.99955774317783</v>
       </c>
     </row>
     <row r="9" ht="15.5" customHeight="1">
@@ -7311,40 +7311,40 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>0.7207029651147852</v>
+        <v>4.932087774678509e-05</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>1.051315975668633</v>
+        <v>4.809728391458859e-05</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>1.277965888263039</v>
+        <v>5.865387652452504e-05</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>1.504453114052955</v>
+        <v>6.924971465962382e-05</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>1.730958497076246</v>
+        <v>7.988548263427168e-05</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>1.957716567762835</v>
+        <v>9.056517867330019e-05</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>1.974609075268205</v>
+        <v>9.113881779102203e-05</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>1.948962214865264</v>
+        <v>8.984230432265483e-05</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>2.070024791309106</v>
+        <v>9.561755138978217e-05</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>2.191785689767212</v>
+        <v>0.0001014267618249157</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>2.314446933688503</v>
+        <v>0.0001072773460099995</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>3.312527134125288</v>
+        <v>0.0001616379411983629</v>
       </c>
     </row>
     <row r="15" ht="15.5" customHeight="1">
@@ -7470,40 +7470,40 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>1.172016912812977</v>
+        <v>8.02062786918142e-05</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>1.503916761832418</v>
+        <v>6.880358821881136e-05</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>1.658910960879815</v>
+        <v>7.613783713497571e-05</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>1.799171818650715</v>
+        <v>8.281556527178888e-05</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>3.851488408118253</v>
+        <v>0.0001777500794285518</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>4.079309970535918</v>
+        <v>0.0001887114010418469</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>3.86057729507893</v>
+        <v>0.000178186383862621</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>3.739894303028956</v>
+        <v>0.0001723998133696599</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>3.93577460290463</v>
+        <v>0.0001817993349315582</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>4.110899093816704</v>
+        <v>0.000190235379864668</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>4.266729917089349</v>
+        <v>0.000197767965635463</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>6.042260098358902</v>
+        <v>0.000294837881453807</v>
       </c>
     </row>
     <row r="18" ht="15.5" customHeight="1">
@@ -7629,40 +7629,40 @@
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>0.6638714087087519</v>
+        <v>4.543164406614517e-05</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>0.8989763114112478</v>
+        <v>4.112780542018968e-05</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>1.039806318799884</v>
+        <v>4.772323893183307e-05</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>1.180056596217983</v>
+        <v>5.431779947608646e-05</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>1.319842192719919</v>
+        <v>6.091205002580824e-05</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>1.459323119769369</v>
+        <v>6.750918966529457e-05</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>1.440613826144919</v>
+        <v>6.649206805170556e-05</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>1.380593272558662</v>
+        <v>6.364191157374496e-05</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>1.4184009862958</v>
+        <v>6.551807000953175e-05</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>1.456243516811225</v>
+        <v>6.738891718668771e-05</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>1.494270471718486</v>
+        <v>6.926119933611916e-05</v>
       </c>
       <c r="O20" s="18" t="n">
-        <v>2.102179059391561</v>
+        <v>0.0001025778450808341</v>
       </c>
     </row>
     <row r="21" ht="15.5" customHeight="1">
@@ -7841,40 +7841,40 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>-16280.98051962557</v>
+        <v>-229653408.7224307</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>-13611.63346379334</v>
+        <v>-290117475.4640662</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>-13559.88285043306</v>
+        <v>-287218938.3632964</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>-13501.83549541582</v>
+        <v>-284345511.2008781</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>-13688.56738604554</v>
+        <v>-281504931.1272646</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>-13632.63024411411</v>
+        <v>-278688724.8066331</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>-14971.59952563408</v>
+        <v>-307481064.2093629</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>-16302.67844800273</v>
+        <v>-335832971.7482243</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>-16209.92002954528</v>
+        <v>-332474015.9477945</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>-16110.93169378531</v>
+        <v>-329149957.8781264</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>-16006.19279613091</v>
+        <v>-325857518.176334</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>-11854.31523973005</v>
+        <v>-223704214.6005065</v>
       </c>
     </row>
     <row r="25" ht="15.5" customHeight="1">
@@ -7894,40 +7894,40 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>-26471.2559766239</v>
+        <v>-459300726.7397987</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>-26485.15401616625</v>
+        <v>-580234212.8152211</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>-26304.78150086612</v>
+        <v>-574437061.7423928</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>-26119.22679083164</v>
+        <v>-568690137.9575562</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>-26179.89807209109</v>
+        <v>-563008665.0178292</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>-25998.99268822823</v>
+        <v>-557376183.3454663</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>-28615.57865126816</v>
+        <v>-614960800.7983258</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>-31204.73019600546</v>
+        <v>-671664542.8697486</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>-30962.92035909056</v>
+        <v>-664946574.975889</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>-30716.42948757063</v>
+        <v>-658298410.3223529</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>-30465.59139202732</v>
+        <v>-651713489.5584676</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>-21780.78832946011</v>
+        <v>-447406501.3588631</v>
       </c>
     </row>
     <row r="26" ht="15.5" customHeight="1">
@@ -7947,40 +7947,40 @@
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>-103.5939136907412</v>
+        <v>-100.0002459473408</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>-102.5532847494269</v>
+        <v>-100.0001168117524</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>-102.8646083757677</v>
+        <v>-100.0001314748598</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>-103.1591455967338</v>
+        <v>-100.0001454149213</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>-105.3639050212441</v>
+        <v>-100.0002475496334</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>-105.7425985888321</v>
+        <v>-100.0002656561607</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>-105.4942199859778</v>
+        <v>-100.0002535877711</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>-105.3074822907391</v>
+        <v>-100.0002446617156</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>-105.5509643193457</v>
+        <v>-100.0002564073717</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>-105.7726875653187</v>
+        <v>-100.000267136066</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>-105.9743368846623</v>
+        <v>-100.0002769175633</v>
       </c>
       <c r="O26" s="18" t="n">
-        <v>-108.5976086651274</v>
+        <v>-100.0004195285676</v>
       </c>
     </row>
     <row r="27" ht="15.5" customHeight="1">
@@ -8000,40 +8000,40 @@
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>-168.4334063063519</v>
+        <v>-199.99783975898</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>-199.5454512257621</v>
+        <v>-199.9999792045761</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>-199.5467864540081</v>
+        <v>-199.9999791991855</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>-199.5608019594324</v>
+        <v>-199.9999797837908</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>-201.5124166131259</v>
+        <v>-200.000069799554</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>-201.6632886182962</v>
+        <v>-200.0000769447597</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>-201.6336426908989</v>
+        <v>-200.0000754013873</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>-201.5675879877101</v>
+        <v>-200.0000722619022</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>-201.615189716441</v>
+        <v>-200.0000746080368</v>
       </c>
       <c r="M27" s="18" t="n">
-        <v>-201.661788471502</v>
+        <v>-200.0000769006862</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>-201.707606967573</v>
+        <v>-200.0000791495976</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>-199.534218517589</v>
+        <v>-199.9999772717455</v>
       </c>
     </row>
     <row r="28" ht="15.5" customHeight="1">
@@ -8106,40 +8106,40 @@
         </is>
       </c>
       <c r="D29" s="19" t="n">
-        <v>0.05683155640603306</v>
+        <v>3.889233680639917e-06</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>0.1523396642573846</v>
+        <v>6.9694784943989e-06</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>0.2381595694631553</v>
+        <v>1.093063759269196e-05</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>0.3243965178349718</v>
+        <v>1.493191518353735e-05</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>0.4111163043563268</v>
+        <v>1.897343260846343e-05</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>0.4983934479934659</v>
+        <v>2.30559890080056e-05</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>0.533995249123286</v>
+        <v>2.464674973931648e-05</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>0.5683689423066021</v>
+        <v>2.620039274890987e-05</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>0.6516238050133064</v>
+        <v>3.009948138025043e-05</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>0.7355421729559863</v>
+        <v>3.403784463822802e-05</v>
       </c>
       <c r="N29" s="19" t="n">
-        <v>0.8201764619700178</v>
+        <v>3.801614667388036e-05</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>1.210348074733727</v>
+        <v>5.906009611752884e-05</v>
       </c>
     </row>
     <row r="30" ht="15.5" customHeight="1">
@@ -8159,40 +8159,40 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>-16289.91225537897</v>
+        <v>-229653417.6541664</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>-13631.85311523537</v>
+        <v>-290117495.6837177</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-13591.27767040683</v>
+        <v>-287218969.7581164</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>-13544.29366423602</v>
+        <v>-284345553.6590469</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>-13741.9784022237</v>
+        <v>-281504984.5382808</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>-13696.88451517665</v>
+        <v>-278688789.0609042</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>-15047.38342184685</v>
+        <v>-307481139.9932591</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>-16390.66779030487</v>
+        <v>-335833059.7375666</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>-16309.99272747588</v>
+        <v>-332474116.0204924</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>-16222.9669457881</v>
+        <v>-329150069.9133784</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>-16130.0709251484</v>
+        <v>-325857642.054463</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>-11986.43460961358</v>
+        <v>-223704346.7198764</v>
       </c>
     </row>
     <row r="31" ht="15.5" customHeight="1">
@@ -8212,40 +8212,40 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>-103.6507452471472</v>
+        <v>-100.0002498365745</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>-102.7056244136843</v>
+        <v>-100.000123781231</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>-103.1027679452308</v>
+        <v>-100.0001424054974</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>-103.4835421145687</v>
+        <v>-100.0001603468365</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>-105.7750213256004</v>
+        <v>-100.000266523066</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>-106.2409920368255</v>
+        <v>-100.0002887121498</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>-106.0282152351011</v>
+        <v>-100.0002782345208</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>-105.8758512330457</v>
+        <v>-100.0002708621084</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>-106.202588124359</v>
+        <v>-100.0002865068531</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>-106.5082297382747</v>
+        <v>-100.0003011739107</v>
       </c>
       <c r="N31" s="19" t="n">
-        <v>-106.7945133466323</v>
+        <v>-100.0003149337099</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>-109.8079567398611</v>
+        <v>-100.0004785886638</v>
       </c>
     </row>
     <row r="32" ht="15.5" customHeight="1">
@@ -8318,40 +8318,40 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>-16289.91225537897</v>
+        <v>-229653417.6541664</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>-13631.85311523537</v>
+        <v>-290117495.6837177</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>-13591.27767040683</v>
+        <v>-287218969.7581164</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>-13544.29366423602</v>
+        <v>-284345553.6590469</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>-13741.9784022237</v>
+        <v>-281504984.5382808</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>-13696.88451517665</v>
+        <v>-278688789.0609042</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>-15047.38342184685</v>
+        <v>-307481139.9932591</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>-16390.66779030487</v>
+        <v>-335833059.7375666</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>-16309.99272747588</v>
+        <v>-332474116.0204924</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>-16222.9669457881</v>
+        <v>-329150069.9133784</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>-16130.0709251484</v>
+        <v>-325857642.054463</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>-11986.43460961358</v>
+        <v>-223704346.7198764</v>
       </c>
     </row>
     <row r="34" ht="15.5" customHeight="1">
@@ -8371,40 +8371,40 @@
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>-26480.1877123773</v>
+        <v>-459300735.6715345</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>-26505.37366760828</v>
+        <v>-580234233.0348725</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-26336.17632083989</v>
+        <v>-574437093.1372128</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>-26161.68495965184</v>
+        <v>-568690180.415725</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>-26233.30908826925</v>
+        <v>-563008718.4288454</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>-26063.24695929077</v>
+        <v>-557376247.5997374</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>-28691.36254748093</v>
+        <v>-614960876.582222</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>-31292.7195383076</v>
+        <v>-671664630.859091</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>-31062.99305702116</v>
+        <v>-664946675.0485868</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>-30828.46473957341</v>
+        <v>-658298522.3576049</v>
       </c>
       <c r="N34" s="19" t="n">
-        <v>-30589.46952104481</v>
+        <v>-651713613.4365966</v>
       </c>
       <c r="O34" s="19" t="n">
-        <v>-21912.90769934363</v>
+        <v>-447406633.478233</v>
       </c>
     </row>
     <row r="35" ht="15.5" customHeight="1">
@@ -8530,40 +8530,40 @@
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>-26480.1877123773</v>
+        <v>-459300735.6715345</v>
       </c>
       <c r="E37" s="19" t="n">
-        <v>-32681.65972287583</v>
+        <v>-618513263.9445796</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>-27191.34098485819</v>
+        <v>-625982481.1198653</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>-27103.92861201725</v>
+        <v>-620856750.7252771</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>-27255.11700412065</v>
+        <v>-614746986.2063509</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>-27407.85201927719</v>
+        <v>-608624830.7316256</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>-30114.9019757028</v>
+        <v>-665703878.0007443</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>-32798.75117422023</v>
+        <v>-727158594.0642114</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>-32663.69941497716</v>
+        <v>-725562400.559692</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>-32496.42631757024</v>
+        <v>-718781305.1302665</v>
       </c>
       <c r="N37" s="19" t="n">
-        <v>-32316.79836791858</v>
+        <v>-711631365.9192364</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>-23692.34079390408</v>
+        <v>-506731148.2315705</v>
       </c>
     </row>
     <row r="38" ht="15.5" customHeight="1">
@@ -8583,40 +8583,40 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>-16289.91225537897</v>
+        <v>-229653417.6541664</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>-13631.85311523537</v>
+        <v>-290117495.6837177</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-13591.27767040683</v>
+        <v>-287218969.7581164</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>-13544.29366423602</v>
+        <v>-284345553.6590469</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>-13741.9784022237</v>
+        <v>-281504984.5382808</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>-13696.88451517665</v>
+        <v>-278688789.0609042</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>-15047.38342184685</v>
+        <v>-307481139.9932591</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>-16390.66779030487</v>
+        <v>-335833059.7375666</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>-16309.99272747588</v>
+        <v>-332474116.0204924</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>-16222.9669457881</v>
+        <v>-329150069.9133784</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>-16130.0709251484</v>
+        <v>-325857642.054463</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>-11986.43460961358</v>
+        <v>-223704346.7198764</v>
       </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
@@ -8636,40 +8636,40 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>-103.6507452471472</v>
+        <v>-100.0002498365745</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>-102.7056244136843</v>
+        <v>-100.000123781231</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>-103.1027679452308</v>
+        <v>-100.0001424054974</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>-103.4835421145687</v>
+        <v>-100.0001603468365</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>-105.7750213256004</v>
+        <v>-100.000266523066</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>-106.2409920368255</v>
+        <v>-100.0002887121498</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>-106.0282152351011</v>
+        <v>-100.0002782345208</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>-105.8758512330457</v>
+        <v>-100.0002708621084</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>-106.202588124359</v>
+        <v>-100.0002865068531</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>-106.5082297382747</v>
+        <v>-100.0003011739107</v>
       </c>
       <c r="N39" s="19" t="n">
-        <v>-106.7945133466323</v>
+        <v>-100.0003149337099</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>-109.8079567398611</v>
+        <v>-100.0004785886638</v>
       </c>
     </row>
     <row r="40" ht="15.5" customHeight="1">
@@ -8848,40 +8848,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>-8170.111749915332</v>
+        <v>-50266242.13656235</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>-15079.45217366233</v>
+        <v>-175394796.3231033</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>-9665.388446766925</v>
+        <v>-180025398.6897788</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>-9721.970180331356</v>
+        <v>-174664855.479233</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>-10045.29622322384</v>
+        <v>-168537268.9977562</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>-10368.25995837062</v>
+        <v>-162397257.7515707</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>-13071.26804855735</v>
+        <v>-219476557.0195454</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>-15730.22691717655</v>
+        <v>-280931357.834957</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>-15531.18491539334</v>
+        <v>-279335315.3825813</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>-12985.13691062612</v>
+        <v>-272554376.7594017</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>-10455.77609559728</v>
+        <v>-265404610.1645752</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>683.4741699025743</v>
+        <v>-60504197.75087576</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -8901,40 +8901,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>-8630.857580384327</v>
+        <v>-50266702.88239282</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>-15118.86429875106</v>
+        <v>-175394835.7352284</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>-9708.044008410761</v>
+        <v>-180025441.3453405</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>-9767.339714577933</v>
+        <v>-174664900.8487673</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>-10113.45605884028</v>
+        <v>-168537337.1575918</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>-10439.24834193227</v>
+        <v>-162397328.7399543</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>-13144.52771979023</v>
+        <v>-219476630.2792167</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>-15807.83387608066</v>
+        <v>-280931435.4419159</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>-15612.64009347553</v>
+        <v>-279335396.8377594</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>-13069.83603391379</v>
+        <v>-272554461.4585249</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>-10543.16139420814</v>
+        <v>-265404697.5498739</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>566.8082794916154</v>
+        <v>-60504314.41676617</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -9060,40 +9060,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>-7882.248734299602</v>
+        <v>-50265954.27354674</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>-14436.86376038665</v>
+        <v>-175394153.73469</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>-8682.995954854056</v>
+        <v>-180024416.2972869</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>-8414.550647613833</v>
+        <v>-174663548.0597003</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>-8427.474049155871</v>
+        <v>-168535651.1755821</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>-8454.518134411872</v>
+        <v>-162395344.0097468</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>-10835.92524055309</v>
+        <v>-219474321.6767374</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>-13148.84683834682</v>
+        <v>-280928776.4548782</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>-12620.19208749786</v>
+        <v>-279332404.3897534</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>-9760.789942207051</v>
+        <v>-272551152.4124333</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>-6934.173045513586</v>
+        <v>-265401088.5615252</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>4362.069280414039</v>
+        <v>-60500519.15576524</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -9113,40 +9113,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>-11104.10626311318</v>
+        <v>-112786465.1456</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>-24735.95937834856</v>
+        <v>-402903960.8293177</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>-28175.28622020051</v>
+        <v>-479612078.2065203</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>-22489.9356106515</v>
+        <v>-480473693.8846037</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>-22582.52192805856</v>
+        <v>-475070723.0177279</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>-22664.31736994652</v>
+        <v>-469200270.6047463</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>-24168.04885884027</v>
+        <v>-494932209.060774</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>-23026.98698770976</v>
+        <v>-551824354.1417892</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>-27586.62006246025</v>
+        <v>-579190196.3677251</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>-22494.44127410259</v>
+        <v>-575068307.161132</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>-25309.21774583103</v>
+        <v>-568385566.2933545</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>-19150.31064607535</v>
+        <v>-462657548.2934567</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -9166,40 +9166,40 @@
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
     </row>
     <row r="50" ht="15.5" customHeight="1">
@@ -9219,40 +9219,40 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>-16289.91225537897</v>
+        <v>-229653417.6541664</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>-13631.85311523537</v>
+        <v>-290117495.6837177</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>-13591.27767040683</v>
+        <v>-287218969.7581164</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>-13544.29366423602</v>
+        <v>-284345553.6590469</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>-13741.9784022237</v>
+        <v>-281504984.5382808</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>-13696.88451517665</v>
+        <v>-278688789.0609042</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>-15047.38342184685</v>
+        <v>-307481139.9932591</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>-16390.66779030487</v>
+        <v>-335833059.7375666</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>-16309.99272747588</v>
+        <v>-332474116.0204924</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>-16222.9669457881</v>
+        <v>-329150069.9133784</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>-16130.0709251484</v>
+        <v>-325857642.054463</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>-11986.43460961358</v>
+        <v>-223704346.7198764</v>
       </c>
     </row>
     <row r="51" ht="15.5" customHeight="1">
@@ -9275,37 +9275,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>-16289.91225537897</v>
+        <v>-229653417.6541664</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>-19769.81454205947</v>
+        <v>-309260060.9569704</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>-14131.44793868127</v>
+        <v>-312995092.7341233</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>-14026.34951810065</v>
+        <v>-310432690.9880135</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>-14153.23884703565</v>
+        <v>-307378434.0524086</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>-14306.47142925921</v>
+        <v>-304318021.5760814</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>-11822.12518967068</v>
+        <v>-332858246.9127889</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>-16462.43332725016</v>
+        <v>-363583032.8557992</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>-11457.28032058028</v>
+        <v>-362785189.75632</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>-14364.95281294842</v>
+        <v>-359394876.747458</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>-12349.68202872756</v>
+        <v>-355820154.0821467</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -9325,40 +9325,40 @@
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>12926.19035222101</v>
+        <v>273030915.6349618</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>12964.85720180161</v>
+        <v>290744366.4194118</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>12965.34093618371</v>
+        <v>292462021.0070488</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>12965.82047886393</v>
+        <v>292844589.3197446</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>12966.29458047539</v>
+        <v>293103021.481392</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>12966.76457379986</v>
+        <v>293369442.114091</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>12961.9595825296</v>
+        <v>290991661.8628128</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>12957.22809455259</v>
+        <v>288431145.85156</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>11667.61169674746</v>
+        <v>288497972.5274707</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>11679.68712059408</v>
+        <v>288780832.9558733</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>11708.04191131865</v>
+        <v>289077661.8328309</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>11769.03865977068</v>
+        <v>297613757.0963305</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -9378,40 +9378,40 @@
         </is>
       </c>
       <c r="D53" s="18" t="n">
-        <v>12926.19035222101</v>
+        <v>273030915.6349618</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>12964.85720180161</v>
+        <v>290744366.4194118</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>12965.34093618371</v>
+        <v>292462021.0070488</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>12965.82047886393</v>
+        <v>292844589.3197446</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>12966.29458047539</v>
+        <v>293103021.481392</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>12966.76457379986</v>
+        <v>293369442.114091</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>12961.9595825296</v>
+        <v>290991661.8628128</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>12957.22809455259</v>
+        <v>288431145.85156</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>11667.61169674746</v>
+        <v>288497972.5274707</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>11679.68712059408</v>
+        <v>288780832.9558733</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>11708.04191131865</v>
+        <v>289077661.8328309</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>11769.03865977068</v>
+        <v>297613757.0963305</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -9643,40 +9643,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>1815.520176447054</v>
+        <v>160244443.9254492</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>-11777.70153451239</v>
+        <v>-112159601.0092639</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>-15216.65311963325</v>
+        <v>-187150063.9073071</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>-9530.775296171136</v>
+        <v>-187629111.2250235</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>-9643.260553062621</v>
+        <v>-181967728.5695413</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>-9725.315207105561</v>
+        <v>-175830856.2530663</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>-11234.31705713259</v>
+        <v>-203940575.4257421</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>-10099.77894795169</v>
+        <v>-263393238.310284</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>-15950.78403694567</v>
+        <v>-290692255.6159257</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>-10847.98823570029</v>
+        <v>-286287507.4393408</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>-13635.59346189036</v>
+        <v>-279307938.878151</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>-7416.622013701932</v>
+        <v>-165043826.5471535</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -9696,40 +9696,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>-9697.768910746656</v>
+        <v>-210510398.1989959</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>-2659.162225874259</v>
+        <v>-63234552.72542617</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>6533.65716477919</v>
+        <v>7125647.610020161</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>1116.224648557303</v>
+        <v>12965563.16532323</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>1215.786503906749</v>
+        <v>13432077.39395919</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>1270.797072693689</v>
+        <v>13435512.24331951</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>398.3918165795039</v>
+        <v>-15533746.25099534</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>-3049.067890395127</v>
+        <v>-17535538.14459416</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>3330.591949447804</v>
+        <v>11359851.22617227</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>1087.198293493237</v>
+        <v>13736355.02690756</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>6701.420416376772</v>
+        <v>13906850.31662583</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>11778.69129411597</v>
+        <v>104543307.3913883</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -9802,40 +9802,40 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>-26471.2559766239</v>
+        <v>-459300726.7397987</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>-26485.15401616625</v>
+        <v>-580234212.8152211</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>-26304.78150086612</v>
+        <v>-574437061.7423928</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>-26119.22679083164</v>
+        <v>-568690137.9575562</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>-26179.89807209109</v>
+        <v>-563008665.0178292</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>-25998.99268822823</v>
+        <v>-557376183.3454663</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>-28615.57865126816</v>
+        <v>-614960800.7983258</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>-31204.73019600546</v>
+        <v>-671664542.8697486</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>-30962.92035909056</v>
+        <v>-664946574.975889</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>-30716.42948757063</v>
+        <v>-658298410.3223529</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>-30465.59139202732</v>
+        <v>-651713489.5584676</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>-21780.78832946011</v>
+        <v>-447406501.3588631</v>
       </c>
     </row>
     <row r="62" ht="15.5" customHeight="1">
@@ -9961,40 +9961,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>-26484.38380194545</v>
+        <v>-459300739.867624</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>-26485.22490677558</v>
+        <v>-580234212.8861117</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>-26304.99845616811</v>
+        <v>-574437061.9593481</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>-26119.13144836589</v>
+        <v>-568690137.8622137</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>-26220.64415428287</v>
+        <v>-563008705.7639114</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>-26000.45109918714</v>
+        <v>-557376184.8038772</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>-28616.50939099419</v>
+        <v>-614960801.7290655</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>-31208.31474395067</v>
+        <v>-671664546.4542966</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>-30966.43159196727</v>
+        <v>-664946578.4871218</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>-30719.34630948844</v>
+        <v>-658298413.2391748</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>-30467.95848239974</v>
+        <v>-651713491.925558</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>-21782.65312949866</v>
+        <v>-447406503.2236632</v>
       </c>
     </row>
     <row r="65" ht="15.5" customHeight="1">
@@ -10120,40 +10120,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>-26781.17855331458</v>
+        <v>-459301036.6623754</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>-26860.16995587757</v>
+        <v>-580234587.8311608</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>-26676.19735477907</v>
+        <v>-574437433.1582466</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>-26486.61665799074</v>
+        <v>-568690505.3474233</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>-26584.45781181148</v>
+        <v>-563009069.5775689</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>-26360.62502014045</v>
+        <v>-557376544.9777982</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-29013.89427125247</v>
+        <v>-614961199.1139458</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>-31642.34135707828</v>
+        <v>-671664980.4809097</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>-31396.11703896361</v>
+        <v>-664947008.1725688</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>-31144.73570201481</v>
+        <v>-658298838.6285673</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>-30889.09269308185</v>
+        <v>-651713913.0597687</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>-22071.76455980995</v>
+        <v>-447406792.3350934</v>
       </c>
     </row>
     <row r="68" ht="15.5" customHeight="1">
@@ -10332,40 +10332,40 @@
         </is>
       </c>
       <c r="D71" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="E71" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="F71" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="G71" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="I71" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="J71" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="K71" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="L71" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="M71" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="N71" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="O71" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
     </row>
     <row r="72" ht="15.5" customHeight="1">
@@ -10438,40 +10438,40 @@
         </is>
       </c>
       <c r="D73" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="E73" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="F73" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="G73" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="I73" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="J73" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="K73" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="N73" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="O73" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
     </row>
     <row r="74" ht="15.5" customHeight="1">
@@ -10491,40 +10491,40 @@
         </is>
       </c>
       <c r="D74" s="18" t="n">
-        <v>18150.32097293026</v>
+        <v>409034333.7799826</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>18150.32097293026</v>
+        <v>409034333.7799826</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>18150.32097293026</v>
+        <v>409034333.7799826</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>18150.32097293026</v>
+        <v>409034333.7799826</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>18150.32097293026</v>
+        <v>409034333.7799826</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>18150.32097293026</v>
+        <v>409034333.7799826</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>18150.32097293026</v>
+        <v>409034333.7799826</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>18150.32097293026</v>
+        <v>409034333.7799826</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>18150.32097293026</v>
+        <v>409034333.7799826</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>18150.32097293026</v>
+        <v>409034333.7799826</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>18150.32097293026</v>
+        <v>409034333.7799826</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>18150.32097293026</v>
+        <v>409034333.7799826</v>
       </c>
     </row>
     <row r="75" ht="15.5" customHeight="1">
@@ -10544,40 +10544,40 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>-8630.857580384327</v>
+        <v>-50266702.88239282</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-8709.848982947307</v>
+        <v>-171200254.0511782</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>-8525.876381848811</v>
+        <v>-165403099.3782641</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>-8336.295685060486</v>
+        <v>-159656171.5674407</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>-8434.136838881219</v>
+        <v>-153974735.7975863</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>-8210.304047210197</v>
+        <v>-148342211.1978157</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>-10863.57329832222</v>
+        <v>-205926865.3339633</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>-13492.02038414803</v>
+        <v>-262630646.7009271</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>-13245.79606603336</v>
+        <v>-255912674.3925862</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>-12994.41472908455</v>
+        <v>-249264504.8485848</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>-12738.77172015159</v>
+        <v>-242679579.2797861</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>-3921.44358687969</v>
+        <v>-38372458.55511087</v>
       </c>
     </row>
     <row r="76" ht="15.5" customHeight="1">
@@ -10600,37 +10600,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>-8630.857580384327</v>
+        <v>-50266702.88239282</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>-15118.86429875106</v>
+        <v>-175394835.7352284</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>-9708.044008410761</v>
+        <v>-180025441.3453405</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>-9767.339714577933</v>
+        <v>-174664900.8487673</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>-10113.45605884028</v>
+        <v>-168537337.1575918</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>-10439.24834193227</v>
+        <v>-162397328.7399543</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>-13144.52771979023</v>
+        <v>-219476630.2792167</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>-15807.83387608066</v>
+        <v>-280931435.4419159</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>-15612.64009347553</v>
+        <v>-279335396.8377594</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>-13069.83603391379</v>
+        <v>-272554461.4585249</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>-10543.16139420814</v>
+        <v>-265404697.5498739</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -10650,40 +10650,40 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>-8630.857580384327</v>
+        <v>-50266702.88239282</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-8709.848982947307</v>
+        <v>-171200254.0511782</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>-8525.876381848811</v>
+        <v>-165403099.3782641</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>-8336.295685060486</v>
+        <v>-159656171.5674407</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>-8434.136838881219</v>
+        <v>-153974735.7975863</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>-8210.304047210197</v>
+        <v>-148342211.1978157</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>-10863.57329832222</v>
+        <v>-205926865.3339633</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>-13492.02038414803</v>
+        <v>-262630646.7009271</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>-13245.79606603336</v>
+        <v>-255912674.3925862</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>-12994.41472908455</v>
+        <v>-249264504.8485848</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>-12738.77172015159</v>
+        <v>-242679579.2797861</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>-3921.44358687969</v>
+        <v>-38372458.55511087</v>
       </c>
     </row>
     <row r="78" ht="15.5" customHeight="1">
@@ -10703,40 +10703,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>-8630.857580384327</v>
+        <v>-50266702.88239282</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>-15118.86429875106</v>
+        <v>-175394835.7352284</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>-9708.044008410761</v>
+        <v>-180025441.3453405</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>-9767.339714577933</v>
+        <v>-174664900.8487673</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>-10113.45605884028</v>
+        <v>-168537337.1575918</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>-10439.24834193227</v>
+        <v>-162397328.7399543</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>-13144.52771979023</v>
+        <v>-219476630.2792167</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>-15807.83387608066</v>
+        <v>-280931435.4419159</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>-15612.64009347553</v>
+        <v>-279335396.8377594</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>-13069.83603391379</v>
+        <v>-272554461.4585249</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>-10543.16139420814</v>
+        <v>-265404697.5498739</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>566.8082794916154</v>
+        <v>-60504314.41676617</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -10862,40 +10862,40 @@
         </is>
       </c>
       <c r="D81" s="18" t="n">
-        <v>1.888469175436754</v>
+        <v>0.0001292362621478237</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>2.824925200066879</v>
+        <v>0.0001292391940478971</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>2.815896697360735</v>
+        <v>0.0001292391750904226</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>2.807726420397251</v>
+        <v>0.0001292391578299148</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>2.800353504951342</v>
+        <v>0.0001292391421674614</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>2.793718135352198</v>
+        <v>0.0001292391280011182</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>2.800088788461871</v>
+        <v>0.0001292391416035843</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>2.803603715881754</v>
+        <v>0.0001292391490821116</v>
       </c>
       <c r="L81" s="18" t="n">
-        <v>2.797898644890784</v>
+        <v>0.000129239136934229</v>
       </c>
       <c r="M81" s="18" t="n">
-        <v>2.792798092902937</v>
+        <v>0.0001292391260315375</v>
       </c>
       <c r="N81" s="18" t="n">
-        <v>2.788259474624755</v>
+        <v>0.000129239116296471</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>2.648555343317819</v>
+        <v>0.0001292388003206084</v>
       </c>
     </row>
     <row r="82" ht="15.5" customHeight="1">
@@ -11684,37 +11684,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>-11104.10626311318</v>
+        <v>-112786465.1456</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>-14564.50524110766</v>
+        <v>-182654608.3865474</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>-8926.138637729458</v>
+        <v>-185578511.1390696</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>-8821.040217148837</v>
+        <v>-182948927.9547646</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>-8947.92954608384</v>
+        <v>-179889485.2131674</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>-9021.603497160257</v>
+        <v>-176823886.9308479</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>17821.21654029444</v>
+        <v>-205364092.7642468</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>20427.10329538685</v>
+        <v>-236088878.7072571</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>56749.83601569581</v>
+        <v>-235291035.6077779</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>63983.96983245303</v>
+        <v>-231900722.5989158</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>67125.9523070444</v>
+        <v>-228325920.3749734</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -11734,40 +11734,40 @@
         </is>
       </c>
       <c r="D97" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="E97" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="F97" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="G97" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="H97" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="I97" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="J97" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="K97" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="N97" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
       <c r="O97" s="19" t="n">
-        <v>5185.805992265788</v>
+        <v>116866952.5085665</v>
       </c>
     </row>
     <row r="98" ht="15.5" customHeight="1">
@@ -11787,40 +11787,40 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>-16289.91225537897</v>
+        <v>-229653417.6541664</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>-13631.85311523537</v>
+        <v>-290117495.6837177</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>-13591.27767040683</v>
+        <v>-287218969.7581164</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>-13544.29366423602</v>
+        <v>-284345553.6590469</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>-13741.9784022237</v>
+        <v>-281504984.5382808</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>-13696.88451517665</v>
+        <v>-278688789.0609042</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>-15047.38342184685</v>
+        <v>-307481139.9932591</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>-16390.66779030487</v>
+        <v>-335833059.7375666</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>-16309.99272747588</v>
+        <v>-332474116.0204924</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>-16222.9669457881</v>
+        <v>-329150069.9133784</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>-16130.0709251484</v>
+        <v>-325857642.054463</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>-11986.43460961358</v>
+        <v>-223704346.7198764</v>
       </c>
     </row>
     <row r="99" ht="15.5" customHeight="1">
@@ -11893,40 +11893,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>-11104.10626311318</v>
+        <v>-112786465.1456</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>-14564.50524110766</v>
+        <v>-182654608.3865474</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>-8926.138637729458</v>
+        <v>-185578511.1390696</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>-8821.040217148837</v>
+        <v>-182948927.9547646</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>-8947.92954608384</v>
+        <v>-179889485.2131674</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>-9021.603497160257</v>
+        <v>-176823886.9308479</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>17821.21654029444</v>
+        <v>-205364092.7642468</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>20427.10329538685</v>
+        <v>-236088878.7072571</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>56749.83601569581</v>
+        <v>-235291035.6077779</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>63983.96983245303</v>
+        <v>-231900722.5989158</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>67125.9523070444</v>
+        <v>-228325920.3749734</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>74433.39564071594</v>
+        <v>-125847943.4647366</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -11999,40 +11999,40 @@
         </is>
       </c>
       <c r="D102" s="18" t="n">
-        <v>-3433.441935879892</v>
+        <v>-77375801.61306392</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>-3433.441935879892</v>
+        <v>-77375801.61306392</v>
       </c>
       <c r="F102" s="18" t="n">
-        <v>-3433.441935879892</v>
+        <v>-77375801.6130639</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>-3433.441935879892</v>
+        <v>-77375801.61306393</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>-3433.441935879892</v>
+        <v>-77375801.61306393</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>-3433.441935879891</v>
+        <v>-77375801.61306392</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>-3433.441935879892</v>
+        <v>-77375801.61306393</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>-3433.441935879891</v>
+        <v>-77375801.61306393</v>
       </c>
       <c r="L102" s="18" t="n">
-        <v>-3433.441935879891</v>
+        <v>-77375801.61306392</v>
       </c>
       <c r="M102" s="18" t="n">
-        <v>-3433.441935879891</v>
+        <v>-77375801.61306392</v>
       </c>
       <c r="N102" s="18" t="n">
-        <v>-3433.441935879891</v>
+        <v>-77375801.6130639</v>
       </c>
       <c r="O102" s="18" t="n">
-        <v>-3433.441935879892</v>
+        <v>-77375801.61306393</v>
       </c>
     </row>
     <row r="103" ht="15.5" customHeight="1">
@@ -12055,37 +12055,37 @@
         <v>0</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>12926.19035222101</v>
+        <v>273030915.6349618</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>12964.85720180161</v>
+        <v>290744366.4194118</v>
       </c>
       <c r="G103" s="18" t="n">
-        <v>12965.34093618371</v>
+        <v>292462021.0070488</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>12965.82047886393</v>
+        <v>292844589.3197446</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>12966.29458047539</v>
+        <v>293103021.481392</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>12966.76457379986</v>
+        <v>293369442.114091</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>12961.9595825296</v>
+        <v>290991661.8628128</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>12957.22809455259</v>
+        <v>288431145.85156</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>11667.61169674746</v>
+        <v>288497972.5274707</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>11679.68712059408</v>
+        <v>288780832.9558733</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>11708.04191131865</v>
+        <v>289077661.8328309</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -12105,40 +12105,40 @@
         </is>
       </c>
       <c r="D104" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="E104" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="F104" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="G104" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="H104" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="I104" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="J104" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="K104" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="L104" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="M104" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="N104" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
       <c r="O104" s="19" t="n">
-        <v>12964.51498066447</v>
+        <v>292167381.2714161</v>
       </c>
     </row>
     <row r="105" ht="15.5" customHeight="1">
@@ -12158,40 +12158,40 @@
         </is>
       </c>
       <c r="D105" s="18" t="n">
-        <v>-10190.27545699833</v>
+        <v>-229647318.017368</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>-12873.52055237291</v>
+        <v>-290116737.3511548</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>-12744.89865043306</v>
+        <v>-287218123.3790964</v>
       </c>
       <c r="G105" s="18" t="n">
-        <v>-12617.39129541582</v>
+        <v>-284344626.7566781</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>-12491.33068604555</v>
+        <v>-281503733.8905646</v>
       </c>
       <c r="I105" s="18" t="n">
-        <v>-12366.36244411412</v>
+        <v>-278687458.5388331</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>-13643.97912563408</v>
+        <v>-307479736.5889629</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>-14902.05174800273</v>
+        <v>-335831571.1215243</v>
       </c>
       <c r="L105" s="18" t="n">
-        <v>-14753.00032954528</v>
+        <v>-332472559.0280945</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>-14605.49779378531</v>
+        <v>-329148452.4442264</v>
       </c>
       <c r="N105" s="18" t="n">
-        <v>-14459.39859589641</v>
+        <v>-325855971.3821337</v>
       </c>
       <c r="O105" s="18" t="n">
-        <v>-9926.473089730054</v>
+        <v>-223702286.7583565</v>
       </c>
     </row>
     <row r="106" ht="15.5" customHeight="1">
@@ -12264,40 +12264,40 @@
         </is>
       </c>
       <c r="D107" s="18" t="n">
-        <v>12926.19035222101</v>
+        <v>273030915.6349618</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>12964.85720180161</v>
+        <v>290744366.4194118</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>12965.34093618371</v>
+        <v>292462021.0070488</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>12965.82047886393</v>
+        <v>292844589.3197446</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>12966.29458047539</v>
+        <v>293103021.481392</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>12966.76457379986</v>
+        <v>293369442.114091</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>12961.9595825296</v>
+        <v>290991661.8628128</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>12957.22809455259</v>
+        <v>288431145.85156</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>11667.61169674746</v>
+        <v>288497972.5274707</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>11679.68712059408</v>
+        <v>288780832.9558733</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>11708.04191131865</v>
+        <v>289077661.8328309</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>11769.03865977068</v>
+        <v>297613757.0963305</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -14567,34 +14567,34 @@
         <v>-165.5708911754087</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>-214.5524113138331</v>
+        <v>-289.6957672916302</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>-291.0694935954891</v>
+        <v>-456.6403847708978</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>-365.7046176039594</v>
+        <v>-655.4003848955897</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>-448.3891107126258</v>
+        <v>-898.6545598326258</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>-540.550615297683</v>
+        <v>-1171.51564613548</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>-637.782146818626</v>
+        <v>-1432.834014906238</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>-712.132491994817</v>
+        <v>-1676.949118661038</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>-693.4598510815017</v>
+        <v>-1904.422665130769</v>
       </c>
       <c r="N37" s="19" t="n">
-        <v>-702.7682136442703</v>
+        <v>-2093.003080619859</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>-713.9736887960598</v>
+        <v>-2277.127090380663</v>
       </c>
     </row>
     <row r="38" ht="15.5" customHeight="1">
@@ -14882,37 +14882,37 @@
         <v>1388.860275383018</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>1295.046502476556</v>
+        <v>2759.462130687203</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>1245.644211615822</v>
+        <v>4097.040959376629</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>1168.561398188722</v>
+        <v>5392.131911499804</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>1080.298779808049</v>
+        <v>6655.737836614676</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>985.3017834802808</v>
+        <v>7875.178448236859</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>891.4274753013457</v>
+        <v>7601.879222458402</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>785.8762531400109</v>
+        <v>7342.792241389992</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>713.9929299542645</v>
+        <v>7100.452640530194</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>688.024880850321</v>
+        <v>6861.545439548302</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>686.967484841932</v>
+        <v>6662.699673802575</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>684.9094617089368</v>
+        <v>6477.853758840154</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -14935,37 +14935,37 @@
         <v>1386.98111955016</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>1293.740312661082</v>
+        <v>2758.155940871729</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>1244.098029149718</v>
+        <v>4095.494776910525</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>1166.033877899187</v>
+        <v>5389.60439121027</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>1077.662630768461</v>
+        <v>6653.101687575088</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>981.5307772603247</v>
+        <v>7871.407442016904</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>887.7004976925527</v>
+        <v>7598.152244849609</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>777.8166918898501</v>
+        <v>7334.732680139832</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>706.5315787433099</v>
+        <v>7092.99128931924</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>679.6388397422666</v>
+        <v>6853.159398440248</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>679.2193936416014</v>
+        <v>6654.951582602245</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>676.3446096075485</v>
+        <v>6469.288906738766</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -15094,37 +15094,37 @@
         <v>1391.363795071772</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>1301.833704523874</v>
+        <v>2766.249332734522</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>1256.376704299154</v>
+        <v>4107.773452059961</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>1182.902389152716</v>
+        <v>5406.472902463798</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>1097.913060070883</v>
+        <v>6673.352116877511</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>1005.855711599927</v>
+        <v>7895.732376356505</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>913.6336412228255</v>
+        <v>7624.085388379882</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>808.5235206097797</v>
+        <v>7365.439508859761</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>736.896871553736</v>
+        <v>7123.356582129665</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>711.0018750725019</v>
+        <v>6884.522433770483</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>709.8347080323056</v>
+        <v>6685.566896992949</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>707.4398276969403</v>
+        <v>6500.384124828158</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -15153,31 +15153,31 @@
         <v>1174.719860919017</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>1085.209752100236</v>
+        <v>1007.775243439749</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>974.7209359641349</v>
+        <v>809.0152433150572</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>843.6893671098724</v>
+        <v>565.761068378021</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>719.3329411860693</v>
+        <v>292.8999820751668</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>564.057035212927</v>
+        <v>-43.56174267338793</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>459.4769273825964</v>
+        <v>-300.6698729653133</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>369.6963416269577</v>
+        <v>-563.9971115626749</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>347.0721886833699</v>
+        <v>-800.9246027973618</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>326.6332820712969</v>
+        <v>-1017.243533896909</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -15312,31 +15312,31 @@
         <v>-165.5708911754087</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>-212.2612586311431</v>
+        <v>-289.6957672916302</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>-290.9346921218201</v>
+        <v>-456.6403847708978</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>-377.4720861637384</v>
+        <v>-655.4003848955897</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>-472.2216007217232</v>
+        <v>-898.6545598326258</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>-563.8968682491653</v>
+        <v>-1171.51564613548</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>-670.396061875638</v>
+        <v>-1430.542862223548</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>-743.1208639977369</v>
+        <v>-1676.81431718737</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>-768.1933422098166</v>
+        <v>-1916.190133690548</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>-772.9587546607506</v>
+        <v>-2116.835570628956</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -15683,31 +15683,31 @@
         <v>1176.05793704579</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>1086.671379151523</v>
+        <v>1009.236870491036</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>976.7400418042737</v>
+        <v>811.034349155196</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>845.750447462519</v>
+        <v>567.8221487306677</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>722.0230850074133</v>
+        <v>295.5901258965108</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>564.7715554975606</v>
+        <v>-42.84722238875423</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>460.5994774678062</v>
+        <v>-299.5473228801035</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>370.4651415194512</v>
+        <v>-563.2283116701815</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>348.2682336693406</v>
+        <v>-799.7285578113909</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>327.5288974638812</v>
+        <v>-1016.347918504324</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -15730,37 +15730,37 @@
         <v>1.98533933589033</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>2.147578652055017</v>
+        <v>1466.563206862703</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>80.31876725336383</v>
+        <v>2931.715515014171</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>96.23101000119368</v>
+        <v>4397.236031972762</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>121.1730182666092</v>
+        <v>5862.317767722315</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>160.1052641374075</v>
+        <v>7327.910227625837</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>191.6105562154122</v>
+        <v>7328.495262483371</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>243.7519651122191</v>
+        <v>7408.286731248515</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>276.2973940859298</v>
+        <v>7422.903905009769</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>340.5367335530507</v>
+        <v>7447.750745440664</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>361.5664743629649</v>
+        <v>7485.29545480434</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>379.910930233059</v>
+        <v>7516.732043332482</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -16634,34 +16634,34 @@
         <v>1386.98111955016</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>1293.740312661082</v>
+        <v>2758.155940871729</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>1244.098029149718</v>
+        <v>4095.494776910525</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>1166.033877899187</v>
+        <v>5389.60439121027</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>1077.662630768461</v>
+        <v>6653.101687575088</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>981.5307772603247</v>
+        <v>7871.407442016904</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>887.7004976925527</v>
+        <v>7598.152244849609</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>777.8166918898501</v>
+        <v>7334.732680139832</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>706.5315787433099</v>
+        <v>7092.99128931924</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>679.6388397422666</v>
+        <v>6853.159398440248</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>679.2193936416014</v>
+        <v>6654.951582602245</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -16737,37 +16737,37 @@
         <v>1386.98111955016</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>1293.740312661082</v>
+        <v>2758.155940871729</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>1244.098029149718</v>
+        <v>4095.494776910525</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>1166.033877899187</v>
+        <v>5389.60439121027</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>1077.662630768461</v>
+        <v>6653.101687575088</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>981.5307772603247</v>
+        <v>7871.407442016904</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>887.7004976925527</v>
+        <v>7598.152244849609</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>777.8166918898501</v>
+        <v>7334.732680139832</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>706.5315787433099</v>
+        <v>7092.99128931924</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>679.6388397422666</v>
+        <v>6853.159398440248</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>679.2193936416014</v>
+        <v>6654.951582602245</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>676.3446096075485</v>
+        <v>6469.288906738766</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -17718,34 +17718,34 @@
         <v>1389.27227223285</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>1298.844737035238</v>
+        <v>2763.260365245885</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>1278.498212265296</v>
+        <v>4103.551117340311</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>1189.6409972793</v>
+        <v>5401.022128071691</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>1112.671585901719</v>
+        <v>6666.677756157646</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>1039.859007507119</v>
+        <v>7887.839209431258</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>978.1374139156185</v>
+        <v>7614.978123128402</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>910.4602057516443</v>
+        <v>7382.294749726126</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>911.5698184509622</v>
+        <v>7125.839513266985</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>10360.28098563953</v>
+        <v>6896.031679428144</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>10476.46603479377</v>
+        <v>6717.323178653118</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -17927,37 +17927,37 @@
         <v>1389.27227223285</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>1298.844737035238</v>
+        <v>2763.260365245885</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>1278.498212265296</v>
+        <v>4103.551117340311</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>1189.6409972793</v>
+        <v>5401.022128071691</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>1112.671585901719</v>
+        <v>6666.677756157646</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>1039.859007507119</v>
+        <v>7887.839209431258</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>978.1374139156185</v>
+        <v>7614.978123128402</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>910.4602057516443</v>
+        <v>7382.294749726126</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>911.5698184509622</v>
+        <v>7125.839513266985</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>10360.28098563953</v>
+        <v>6896.031679428144</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>10476.46603479377</v>
+        <v>6717.323178653118</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>10648.74016576222</v>
+        <v>6563.639079885875</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -18737,40 +18737,40 @@
         </is>
       </c>
       <c r="D2" s="18" t="n">
-        <v>15828.51775208206</v>
+        <v>341438002.8327024</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>12569.85957837899</v>
+        <v>400524666.6287988</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>12468.52341961993</v>
+        <v>396523873.7286324</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>12365.4002802857</v>
+        <v>392556374.7394217</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>12261.10901453531</v>
+        <v>388635259.7584491</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>12155.43657903713</v>
+        <v>384746776.509854</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>12365.30335430366</v>
+        <v>391293573.6183391</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>12571.71483444678</v>
+        <v>397732813.4526422</v>
       </c>
       <c r="L2" s="18" t="n">
-        <v>12459.37784149539</v>
+        <v>393754290.6790842</v>
       </c>
       <c r="M2" s="18" t="n">
-        <v>12346.43624718032</v>
+        <v>389817833.2193102</v>
       </c>
       <c r="N2" s="18" t="n">
-        <v>12232.88205289869</v>
+        <v>385917936.0963264</v>
       </c>
       <c r="O2" s="18" t="n">
-        <v>9186.127404170737</v>
+        <v>277742561.6210265</v>
       </c>
     </row>
     <row r="3">
@@ -18793,37 +18793,37 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>-20.58726044183403</v>
+        <v>17.30523940097193</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>-0.8061836978144332</v>
+        <v>-0.9988880170205161</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>-0.82706777590007</v>
+        <v>-1.00057001660534</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>-0.8434119671537843</v>
+        <v>-0.9988667190987344</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>-0.8618505501656215</v>
+        <v>-1.000548239244137</v>
       </c>
       <c r="J3" s="18" t="n">
-        <v>1.726526019052788</v>
+        <v>1.701585954240592</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>1.669279549630098</v>
+        <v>1.645628824097112</v>
       </c>
       <c r="L3" s="18" t="n">
-        <v>-0.8935693692604607</v>
+        <v>-1.000300362200757</v>
       </c>
       <c r="M3" s="18" t="n">
-        <v>-0.9064786039229222</v>
+        <v>-0.999724333920271</v>
       </c>
       <c r="N3" s="18" t="n">
-        <v>-0.919732560945008</v>
+        <v>-1.000440921539314</v>
       </c>
       <c r="O3" s="18" t="n">
-        <v>-24.90627012958074</v>
+        <v>-28.03066775530717</v>
       </c>
     </row>
     <row r="4">
@@ -18949,40 +18949,40 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>10395.56474679226</v>
+        <v>341432569.8796971</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>12194.72473395131</v>
+        <v>400524291.4939544</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>12072.91235234769</v>
+        <v>396523478.1175651</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>11952.11375253603</v>
+        <v>392555961.4528939</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>11832.72748074657</v>
+        <v>388634831.3769153</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>11714.3348164914</v>
+        <v>384746335.4080915</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>11913.66420005668</v>
+        <v>391293121.9791849</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>12109.71880309476</v>
+        <v>397732351.4566109</v>
       </c>
       <c r="L6" s="18" t="n">
-        <v>11988.58483349947</v>
+        <v>393753819.8860762</v>
       </c>
       <c r="M6" s="18" t="n">
-        <v>11868.73167988833</v>
+        <v>389817355.5147429</v>
       </c>
       <c r="N6" s="18" t="n">
-        <v>11749.99172789437</v>
+        <v>385917453.2060013</v>
       </c>
       <c r="O6" s="18" t="n">
-        <v>8456.378948093097</v>
+        <v>277741831.8725704</v>
       </c>
     </row>
     <row r="7">
@@ -19008,16 +19008,16 @@
         <v>17.30699611788007</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>-0.9988940649432898</v>
+        <v>-0.9988940649433009</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>-1.000575472480569</v>
+        <v>-1.000575472480558</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>-0.998871616027952</v>
+        <v>-0.9988716160279631</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>-1.000552615175299</v>
+        <v>-1.000552615175287</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>1.701585166275676</v>
@@ -19026,16 +19026,16 @@
         <v>1.645628076684802</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>-1.000303735907848</v>
+        <v>-1.000303735907859</v>
       </c>
       <c r="M7" s="18" t="n">
-        <v>-0.9997272845434724</v>
+        <v>-0.9997272845434835</v>
       </c>
       <c r="N7" s="18" t="n">
-        <v>-1.000443477841551</v>
+        <v>-1.000443477841528</v>
       </c>
       <c r="O7" s="18" t="n">
-        <v>-28.03076679605033</v>
+        <v>-28.03076679605034</v>
       </c>
     </row>
     <row r="8">
@@ -19055,40 +19055,40 @@
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>-65.67617328176445</v>
+        <v>-99.99840880248823</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-97.01560035664247</v>
+        <v>-99.99990633914071</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>-96.82712175324849</v>
+        <v>-99.99990023020213</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>-96.65771816211576</v>
+        <v>-99.99989471919083</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>-96.50617629057129</v>
+        <v>-99.99988977285949</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>-96.37115656292887</v>
+        <v>-99.99988535270742</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>-96.34752871558308</v>
+        <v>-99.99988457792698</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>-96.3251152493044</v>
+        <v>-99.99988384261601</v>
       </c>
       <c r="L8" s="18" t="n">
-        <v>-96.22137626785852</v>
+        <v>-99.99988043482469</v>
       </c>
       <c r="M8" s="18" t="n">
-        <v>-96.13083032440971</v>
+        <v>-99.99987745440906</v>
       </c>
       <c r="N8" s="18" t="n">
-        <v>-96.0525220228876</v>
+        <v>-99.99987487227729</v>
       </c>
       <c r="O8" s="18" t="n">
-        <v>-92.0559728384965</v>
+        <v>-99.99973725724577</v>
       </c>
     </row>
     <row r="9">
@@ -19373,40 +19373,40 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>0.6951845555875658</v>
+        <v>3.222764012148544e-05</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>1.029974267491077</v>
+        <v>3.232418123127826e-05</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>1.21584854358821</v>
+        <v>3.823183683213804e-05</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>1.401994993644437</v>
+        <v>4.416239399723883e-05</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>1.58851050515192</v>
+        <v>5.011614356995771e-05</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>1.775566068324613</v>
+        <v>5.609606643411961e-05</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>1.91162522371165</v>
+        <v>6.040944034002736e-05</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>2.001849210787996</v>
+        <v>6.327533602551403e-05</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>2.116697775053342</v>
+        <v>6.697765073279261e-05</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>2.232172773841711</v>
+        <v>7.069809663998497e-05</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>2.34849663635526</v>
+        <v>7.444298299468611e-05</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>3.230465909496233</v>
+        <v>0.0001068452427538067</v>
       </c>
     </row>
     <row r="15">
@@ -19532,40 +19532,40 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>1.144127557274518</v>
+        <v>5.303991705879161e-05</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>1.492199821678761</v>
+        <v>4.683042964434373e-05</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>1.586439123375757</v>
+        <v>4.988489892830283e-05</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>1.671140918942121</v>
+        <v>5.264040458189161e-05</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>3.493823709428712</v>
+        <v>0.0001102271404954327</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>3.628843437071121</v>
+        <v>0.0001146472925769747</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>3.652471284416924</v>
+        <v>0.0001154220730155678</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>3.6748847506956</v>
+        <v>0.0001161573839838666</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>3.778623732141493</v>
+        <v>0.0001195651753239247</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>3.869169675590288</v>
+        <v>0.0001225455909358651</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>3.9474779771124</v>
+        <v>0.0001251277227197287</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>5.296018107668997</v>
+        <v>0.0001751618361546774</v>
       </c>
     </row>
     <row r="18">
@@ -19691,40 +19691,40 @@
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>0.6464149344091563</v>
+        <v>2.996675876621635e-05</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>0.8961610167970581</v>
+        <v>2.812465518183992e-05</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>1.008687742679934</v>
+        <v>3.171775415292017e-05</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>1.120973094593907</v>
+        <v>3.53102940368382e-05</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>1.233077660868587</v>
+        <v>3.890254227754549e-05</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>1.345123568535845</v>
+        <v>4.249694923145588e-05</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>1.419709476447317</v>
+        <v>4.486436664143553e-05</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>1.452222033757901</v>
+        <v>4.590247690709712e-05</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>1.496397898008547</v>
+        <v>4.734979974530174e-05</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>1.540543218855608</v>
+        <v>4.879258211598033e-05</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>1.584845145009625</v>
+        <v>5.023664856606389e-05</v>
       </c>
       <c r="O20" s="18" t="n">
-        <v>2.149385512035245</v>
+        <v>7.108931752842216e-05</v>
       </c>
     </row>
     <row r="21">
@@ -19903,40 +19903,40 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>-16383.58173850127</v>
+        <v>-341438557.8966888</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>-12888.82992422178</v>
+        <v>-400524985.5991447</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>-12811.87797404655</v>
+        <v>-396524217.0831868</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>-12731.32068072887</v>
+        <v>-392556740.6598221</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>-12862.09862124646</v>
+        <v>-388635860.7480558</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>-12782.0990719932</v>
+        <v>-384747403.1723469</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>-13015.07584977551</v>
+        <v>-391294223.3908346</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>-13239.37988021345</v>
+        <v>-397733481.1176879</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>-13140.15236801619</v>
+        <v>-393754971.4536107</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>-13038.22822921317</v>
+        <v>-389818525.0112923</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>-12933.78913146333</v>
+        <v>-385918637.0034049</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>-9906.55908923539</v>
+        <v>-277743282.0527115</v>
       </c>
     </row>
     <row r="25">
@@ -19956,40 +19956,40 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>-26779.14648529353</v>
+        <v>-682871127.7763858</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>-25083.55465817308</v>
+        <v>-801049277.0930991</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>-24884.79032639424</v>
+        <v>-793047695.2007519</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>-24683.43443326489</v>
+        <v>-785112702.112716</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>-24694.82610199303</v>
+        <v>-777270692.1249712</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>-24496.43388848459</v>
+        <v>-769493738.5804384</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>-24928.74004983218</v>
+        <v>-782587345.3700194</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>-25349.09868330821</v>
+        <v>-795465832.5742989</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>-25128.73720151565</v>
+        <v>-787508791.3396869</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>-24906.9599091015</v>
+        <v>-779635880.5260352</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>-24683.78085935771</v>
+        <v>-771836090.2094063</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>-18362.93803732849</v>
+        <v>-555485113.925282</v>
       </c>
     </row>
     <row r="26">
@@ -20009,40 +20009,40 @@
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>-103.5067338275955</v>
+        <v>-100.0001625665514</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>-102.5375808206437</v>
+        <v>-100.0000796381278</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>-102.7537707783933</v>
+        <v>-100.000086591143</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>-102.9592281054302</v>
+        <v>-100.0000932147391</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>-104.9015925557687</v>
+        <v>-100.0001546410398</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>-105.1554091774605</v>
+        <v>-100.0001628766064</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>-105.2548043250851</v>
+        <v>-100.0001660575433</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>-105.3108510219883</v>
+        <v>-100.0001678677301</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>-105.4639528167571</v>
+        <v>-100.0001728932338</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>-105.6031713782254</v>
+        <v>-100.0001774654526</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>-105.7296970209777</v>
+        <v>-100.0001816207574</v>
       </c>
       <c r="O26" s="18" t="n">
-        <v>-107.8426049777794</v>
+        <v>-100.0002593882914</v>
       </c>
     </row>
     <row r="27">
@@ -20062,40 +20062,40 @@
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>-169.1829071093599</v>
+        <v>-199.9985713690396</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>-199.5531811772861</v>
+        <v>-199.9999859772685</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>-199.5808925316418</v>
+        <v>-199.9999868213451</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>-199.616946267546</v>
+        <v>-199.9999879339299</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>-201.40776884634</v>
+        <v>-200.0000444138993</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>-201.5265657403894</v>
+        <v>-200.0000482293138</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>-201.6023330406682</v>
+        <v>-200.0000506354703</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>-201.6359662712927</v>
+        <v>-200.0000517103461</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>-201.6853290846156</v>
+        <v>-200.0000533280585</v>
       </c>
       <c r="M27" s="18" t="n">
-        <v>-201.7340017026351</v>
+        <v>-200.0000549198617</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>-201.7822190438653</v>
+        <v>-200.0000564930347</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>-199.8985778162759</v>
+        <v>-199.9999966455372</v>
       </c>
     </row>
     <row r="28">
@@ -20168,40 +20168,40 @@
         </is>
       </c>
       <c r="D29" s="19" t="n">
-        <v>0.04876962117840977</v>
+        <v>2.260881355269103e-06</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>0.1338132506940189</v>
+        <v>4.199526049438328e-06</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>0.2071608009082755</v>
+        <v>6.514082679217862e-06</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>0.2810218990505303</v>
+        <v>8.852099960400628e-06</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>0.3554328442833336</v>
+        <v>1.121360129241222e-05</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>0.4304424997887683</v>
+        <v>1.359911720266373e-05</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>0.4919157472643323</v>
+        <v>1.554507369859181e-05</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>0.5496271770300944</v>
+        <v>1.73728591184169e-05</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>0.6202998770447948</v>
+        <v>1.962785098749087e-05</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>0.6916295549861029</v>
+        <v>2.190551452400463e-05</v>
       </c>
       <c r="N29" s="19" t="n">
-        <v>0.7636514913456345</v>
+        <v>2.42063344286222e-05</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>1.081080397460988</v>
+        <v>3.575592522538453e-05</v>
       </c>
     </row>
     <row r="30">
@@ -20221,40 +20221,40 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>-16391.30124664712</v>
+        <v>-341438565.6161969</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>-12905.65006193128</v>
+        <v>-400525002.4192824</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-12837.70786702407</v>
+        <v>-396524242.9130798</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>-12766.07016342172</v>
+        <v>-392556775.4093048</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>-12905.6786297575</v>
+        <v>-388635904.3280643</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>-12834.42123706425</v>
+        <v>-384747455.494512</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>-13075.90272417233</v>
+        <v>-391294284.2177089</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>-13308.47744156229</v>
+        <v>-397733550.2152493</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>-13217.43787344753</v>
+        <v>-393755048.7391161</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>-13123.61983128619</v>
+        <v>-389818610.4028944</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>-13027.20571769484</v>
+        <v>-385918730.4199911</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>-10005.86851188767</v>
+        <v>-277743381.3621342</v>
       </c>
     </row>
     <row r="31">
@@ -20274,40 +20274,40 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>-103.5555034487738</v>
+        <v>-100.0001648274328</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>-102.6713940713377</v>
+        <v>-100.0000838376538</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>-102.9609315793016</v>
+        <v>-100.0000931052257</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>-103.2402500044808</v>
+        <v>-100.000102066839</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>-105.2570254000521</v>
+        <v>-100.0001658546411</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>-105.5858516772493</v>
+        <v>-100.0001764757236</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>-105.7467200723494</v>
+        <v>-100.000181602617</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>-105.8604781990184</v>
+        <v>-100.0001852405892</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>-106.0842526938019</v>
+        <v>-100.0001925210848</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>-106.2948009332115</v>
+        <v>-100.0001993709671</v>
       </c>
       <c r="N31" s="19" t="n">
-        <v>-106.4933485123233</v>
+        <v>-100.0002058270918</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>-108.9236853752404</v>
+        <v>-100.0002951442167</v>
       </c>
     </row>
     <row r="32">
@@ -20380,40 +20380,40 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>-16391.30124664712</v>
+        <v>-341438565.6161969</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>-12905.65006193128</v>
+        <v>-400525002.4192824</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>-12837.70786702407</v>
+        <v>-396524242.9130798</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>-12766.07016342172</v>
+        <v>-392556775.4093048</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>-12905.6786297575</v>
+        <v>-388635904.3280643</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>-12834.42123706425</v>
+        <v>-384747455.494512</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>-13075.90272417233</v>
+        <v>-391294284.2177089</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>-13308.47744156229</v>
+        <v>-397733550.2152493</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>-13217.43787344753</v>
+        <v>-393755048.7391161</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>-13123.61983128619</v>
+        <v>-389818610.4028944</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>-13027.20571769484</v>
+        <v>-385918730.4199911</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>-10005.86851188767</v>
+        <v>-277743381.3621342</v>
       </c>
     </row>
     <row r="34">
@@ -20433,40 +20433,40 @@
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>-26786.86599343937</v>
+        <v>-682871135.495894</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>-25100.37479588258</v>
+        <v>-801049293.9132369</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-24910.62021937176</v>
+        <v>-793047721.0306449</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>-24718.18391595775</v>
+        <v>-785112736.8621987</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>-24738.40611050407</v>
+        <v>-777270735.7049797</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>-24548.75605355564</v>
+        <v>-769493790.9026035</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>-24989.56692422901</v>
+        <v>-782587406.1968938</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>-25418.19624465705</v>
+        <v>-795465901.6718602</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>-25206.02270694699</v>
+        <v>-787508868.6251923</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>-24992.35151117452</v>
+        <v>-779635965.9176373</v>
       </c>
       <c r="N34" s="19" t="n">
-        <v>-24777.19744558922</v>
+        <v>-771836183.6259925</v>
       </c>
       <c r="O34" s="19" t="n">
-        <v>-18462.24745998077</v>
+        <v>-555485213.2347046</v>
       </c>
     </row>
     <row r="35">
@@ -20592,40 +20592,40 @@
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>-26786.86599343937</v>
+        <v>-682871135.495894</v>
       </c>
       <c r="E37" s="19" t="n">
-        <v>-31098.59500777721</v>
+        <v>-852785924.6054109</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>-25624.45911533781</v>
+        <v>-857655496.5264665</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>-25485.8638951625</v>
+        <v>-850088299.8335174</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>-25555.21812467356</v>
+        <v>-841671970.4218833</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>-25624.5342820397</v>
+        <v>-833277415.2088397</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>-26112.45213785738</v>
+        <v>-845737940.3717122</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>-26583.28118567569</v>
+        <v>-859555020.0431517</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>-26407.67460375326</v>
+        <v>-852645357.9556391</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>-26224.06886809006</v>
+        <v>-844249194.8345419</v>
       </c>
       <c r="N37" s="19" t="n">
-        <v>-26034.92127859632</v>
+        <v>-835813519.2415581</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>-19742.26876199876</v>
+        <v>-618824062.8142952</v>
       </c>
     </row>
     <row r="38">
@@ -20645,40 +20645,40 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>-16391.30124664712</v>
+        <v>-341438565.6161969</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>-12905.65006193128</v>
+        <v>-400525002.4192824</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-12837.70786702407</v>
+        <v>-396524242.9130798</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>-12766.07016342172</v>
+        <v>-392556775.4093048</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>-12905.6786297575</v>
+        <v>-388635904.3280643</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>-12834.42123706425</v>
+        <v>-384747455.494512</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>-13075.90272417233</v>
+        <v>-391294284.2177089</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>-13308.47744156229</v>
+        <v>-397733550.2152493</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>-13217.43787344753</v>
+        <v>-393755048.7391161</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>-13123.61983128619</v>
+        <v>-389818610.4028944</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>-13027.20571769484</v>
+        <v>-385918730.4199911</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>-10005.86851188767</v>
+        <v>-277743381.3621342</v>
       </c>
     </row>
     <row r="39">
@@ -20698,40 +20698,40 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>-103.5555034487738</v>
+        <v>-100.0001648274328</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>-102.6713940713377</v>
+        <v>-100.0000838376538</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>-102.9609315793016</v>
+        <v>-100.0000931052257</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>-103.2402500044808</v>
+        <v>-100.000102066839</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>-105.2570254000521</v>
+        <v>-100.0001658546411</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>-105.5858516772493</v>
+        <v>-100.0001764757236</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>-105.7467200723494</v>
+        <v>-100.000181602617</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>-105.8604781990184</v>
+        <v>-100.0001852405892</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>-106.0842526938019</v>
+        <v>-100.0001925210848</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>-106.2948009332115</v>
+        <v>-100.0001993709671</v>
       </c>
       <c r="N39" s="19" t="n">
-        <v>-106.4933485123233</v>
+        <v>-100.0002058270918</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>-108.9236853752404</v>
+        <v>-100.0002951442167</v>
       </c>
     </row>
     <row r="40">
@@ -20910,40 +20910,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>-9835.935442274234</v>
+        <v>-132486287.3294363</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>-14842.62637842383</v>
+        <v>-260707233.7314882</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>-9379.054812258999</v>
+        <v>-262419663.5706231</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>-9336.191688005494</v>
+        <v>-254614792.5984507</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>-9566.157661519921</v>
+        <v>-246181967.581073</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>-9758.294268503345</v>
+        <v>-237770888.160159</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>-10212.45379545189</v>
+        <v>-250231641.0170678</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>-10628.13188788206</v>
+        <v>-264048690.2289988</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>-10392.32129695128</v>
+        <v>-257139083.69375</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>-10135.51508006206</v>
+        <v>-248743023.9939961</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>-9878.333507898129</v>
+        <v>-240307431.7102009</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>-3417.488496643477</v>
+        <v>-23317799.14978604</v>
       </c>
     </row>
     <row r="44">
@@ -20963,40 +20963,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>-10288.95463702665</v>
+        <v>-132486740.348631</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>-14879.61728953895</v>
+        <v>-260707270.7223993</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>-9417.491645147888</v>
+        <v>-262419702.007456</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>-9375.751987850179</v>
+        <v>-254614832.1587506</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>-9624.150050945495</v>
+        <v>-246182025.5734624</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>-9817.365327364309</v>
+        <v>-237770947.2312178</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>-10272.26696736817</v>
+        <v>-250231700.8302397</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>-10689.07075225387</v>
+        <v>-264048751.1678632</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>-10454.3879392417</v>
+        <v>-257139145.7603923</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>-10198.40880183256</v>
+        <v>-248743086.8877178</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>-9941.77803496924</v>
+        <v>-240307495.154728</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>-3501.225658445153</v>
+        <v>-23317882.88694784</v>
       </c>
     </row>
     <row r="45">
@@ -21122,40 +21122,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>-9589.288165315411</v>
+        <v>-132486040.6821593</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>-14314.40920444659</v>
+        <v>-260706705.5143142</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>-8581.25809687865</v>
+        <v>-262418865.7739077</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>-8280.690815281176</v>
+        <v>-254613737.097578</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>-8264.704393670187</v>
+        <v>-246180666.1278051</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>-8222.527686124562</v>
+        <v>-237769352.3935766</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>-8446.001261067673</v>
+        <v>-250229874.5645334</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>-8634.466871526027</v>
+        <v>-264046696.5639825</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>-8182.595743139125</v>
+        <v>-257136873.9681962</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>-7720.767745864345</v>
+        <v>-248740609.2466618</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>-7269.494799216922</v>
+        <v>-240304822.8714922</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>-701.0419358876538</v>
+        <v>-23315082.70322528</v>
       </c>
     </row>
     <row r="48">
@@ -21175,40 +21175,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>-11154.57972863984</v>
+        <v>-169443361.0084581</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>-24060.22979057113</v>
+        <v>-569968363.4277406</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>-26503.61476682282</v>
+        <v>-650925353.9389603</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>-20816.38952084773</v>
+        <v>-649393054.7934705</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>-20810.45349275598</v>
+        <v>-641688992.343961</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>-20830.5141435476</v>
+        <v>-633592915.2801661</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>-21147.59333788671</v>
+        <v>-635943026.4400514</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>-17869.44149903873</v>
+        <v>-648613136.1382902</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>-21300.16644670385</v>
+        <v>-651540512.9598424</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>-16696.45095800832</v>
+        <v>-644149374.7812946</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>-20429.27031668426</v>
+        <v>-636051560.8472726</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>-17071.59258069606</v>
+        <v>-523658493.496337</v>
       </c>
     </row>
     <row r="49">
@@ -21228,40 +21228,40 @@
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
     </row>
     <row r="50">
@@ -21281,40 +21281,40 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>-16391.30124664712</v>
+        <v>-341438565.6161969</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>-12905.65006193128</v>
+        <v>-400525002.4192824</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>-12837.70786702407</v>
+        <v>-396524242.9130798</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>-12766.07016342172</v>
+        <v>-392556775.4093048</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>-12905.6786297575</v>
+        <v>-388635904.3280643</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>-12834.42123706425</v>
+        <v>-384747455.494512</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>-13075.90272417233</v>
+        <v>-391294284.2177089</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>-13308.47744156229</v>
+        <v>-397733550.2152493</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>-13217.43787344753</v>
+        <v>-393755048.7391161</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>-13123.61983128619</v>
+        <v>-389818610.4028944</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>-13027.20571769484</v>
+        <v>-385918730.4199911</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>-10005.86851188767</v>
+        <v>-277743381.3621342</v>
       </c>
     </row>
     <row r="51">
@@ -21337,37 +21337,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>-16391.30124664712</v>
+        <v>-341438565.6161969</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>-18902.62841780602</v>
+        <v>-426396315.6336194</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>-13287.04087543328</v>
+        <v>-428831483.9919045</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>-13141.49638100575</v>
+        <v>-425048292.6236354</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>-13232.81442449062</v>
+        <v>-420840664.3933929</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>-13308.41213172165</v>
+        <v>-416643946.8300813</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>-9797.685575483707</v>
+        <v>-422874790.5307796</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>-13319.45009126359</v>
+        <v>-429780668.8284651</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>-8809.552644729403</v>
+        <v>-426325968.986139</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>-12638.78611699669</v>
+        <v>-422128035.0350204</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>-12302.44558681566</v>
+        <v>-417910316.7419416</v>
       </c>
     </row>
     <row r="52">
@@ -21387,40 +21387,40 @@
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>11519.54548359611</v>
+        <v>352524132.6591883</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>11520.70683093459</v>
+        <v>374753911.7440073</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>11520.72138266344</v>
+        <v>376741119.6012489</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>11520.73581328573</v>
+        <v>377192267.7200502</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>11520.75007519106</v>
+        <v>377513130.1882982</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>11520.76421839987</v>
+        <v>377841756.0845569</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>11520.74040647613</v>
+        <v>377370048.6136078</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>11520.71698575826</v>
+        <v>376846607.0506854</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>11520.73145644389</v>
+        <v>377108469.2862191</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>11520.74577412301</v>
+        <v>377426636.4027589</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>11520.75995881887</v>
+        <v>377745981.5521668</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>11521.15341438933</v>
+        <v>385964854.7369099</v>
       </c>
     </row>
     <row r="53">
@@ -21440,40 +21440,40 @@
         </is>
       </c>
       <c r="D53" s="18" t="n">
-        <v>11519.54548359611</v>
+        <v>352524132.6591883</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>11520.70683093459</v>
+        <v>374753911.7440073</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>11520.72138266344</v>
+        <v>376741119.6012489</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>11520.73581328573</v>
+        <v>377192267.7200502</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>11520.75007519106</v>
+        <v>377513130.1882982</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>11520.76421839987</v>
+        <v>377841756.0845569</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>11520.74040647613</v>
+        <v>377370048.6136078</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>11520.71698575826</v>
+        <v>376846607.0506854</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>11520.73145644389</v>
+        <v>377108469.2862191</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>11520.74577412301</v>
+        <v>377426636.4027589</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>11520.75995881887</v>
+        <v>377745981.5521668</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>11521.15341438933</v>
+        <v>385964854.7369099</v>
       </c>
     </row>
     <row r="54">
@@ -21705,40 +21705,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>358.490642830408</v>
+        <v>183080765.175618</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>-12545.68086983979</v>
+        <v>-195214457.8416435</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>-14988.81423891631</v>
+        <v>-274184240.2585662</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>-9301.245251701232</v>
+        <v>-272200792.6649644</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>-9312.486365857168</v>
+        <v>-264175884.9386111</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>-9332.566044621375</v>
+        <v>-255751182.0117287</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>-9649.5450769504</v>
+        <v>-258573000.5185891</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>-6371.691101102791</v>
+        <v>-271766552.0541926</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>-9802.806316824684</v>
+        <v>-274432067.0449499</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>-5199.335516563319</v>
+        <v>-266722762.0088684</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>-8932.265269182724</v>
+        <v>-258305603.0500171</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>-5574.19700295134</v>
+        <v>-137693662.5172638</v>
       </c>
     </row>
     <row r="59">
@@ -21758,40 +21758,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>-9947.778808145818</v>
+        <v>-315566805.8577773</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>-1768.728334606805</v>
+        <v>-65492247.67267072</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>6407.556142037658</v>
+        <v>11765374.48465848</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>1020.554436420056</v>
+        <v>17587055.56738645</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>1047.781972186982</v>
+        <v>17995218.81080601</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>1110.038358496813</v>
+        <v>17981829.61815208</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>1203.543815882727</v>
+        <v>8343125.954055697</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>-2262.775770423236</v>
+        <v>7719855.490210146</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>1620.210573685559</v>
+        <v>17295193.07675368</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>-2521.432229301025</v>
+        <v>17982152.76220652</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>1662.770469965802</v>
+        <v>18000780.17852488</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>4873.155067063686</v>
+        <v>114378579.8140385</v>
       </c>
     </row>
     <row r="60">
@@ -21864,40 +21864,40 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>-26779.14648529353</v>
+        <v>-682871127.7763858</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>-25083.55465817308</v>
+        <v>-801049277.0930991</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>-24884.79032639424</v>
+        <v>-793047695.2007519</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>-24683.43443326489</v>
+        <v>-785112702.112716</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>-24694.82610199303</v>
+        <v>-777270692.1249712</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>-24496.43388848459</v>
+        <v>-769493738.5804384</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>-24928.74004983218</v>
+        <v>-782587345.3700194</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>-25349.09868330821</v>
+        <v>-795465832.5742989</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>-25128.73720151565</v>
+        <v>-787508791.3396869</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>-24906.9599091015</v>
+        <v>-779635880.5260352</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>-24683.78085935771</v>
+        <v>-771836090.2094063</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>-18362.93803732849</v>
+        <v>-555485113.925282</v>
       </c>
     </row>
     <row r="62">
@@ -22023,40 +22023,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>-26792.09670954524</v>
+        <v>-682871140.7266101</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>-25082.92025432788</v>
+        <v>-801049276.4586953</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>-24884.31621550158</v>
+        <v>-793047694.7266411</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>-24682.77581202951</v>
+        <v>-785112701.4540948</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>-24729.20891029907</v>
+        <v>-777270726.5077795</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>-24496.50023084737</v>
+        <v>-769493738.6467807</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>-24928.49210196453</v>
+        <v>-782587345.1220716</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>-25349.64756787322</v>
+        <v>-795465833.1231834</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>-25129.54667900045</v>
+        <v>-787508792.1491643</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>-24907.47792132806</v>
+        <v>-779635881.0440475</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>-24684.03001663636</v>
+        <v>-771836090.4585636</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>-18362.94388798304</v>
+        <v>-555485113.9311327</v>
       </c>
     </row>
     <row r="65">
@@ -22182,40 +22182,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>-27046.46349464991</v>
+        <v>-682871395.0933951</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>-25381.31028905579</v>
+        <v>-801049574.84873</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>-25179.72564988221</v>
+        <v>-793047990.1360755</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>-24975.22945206633</v>
+        <v>-785112993.9077348</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>-25018.74131393553</v>
+        <v>-777271016.0401831</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>-24783.13571044747</v>
+        <v>-769494025.2822603</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-25220.00492836679</v>
+        <v>-782587636.6348981</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>-25645.95761119389</v>
+        <v>-795466129.4332267</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>-25422.89272188791</v>
+        <v>-787509085.4952072</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>-25197.89130378664</v>
+        <v>-779636171.4574299</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>-24971.53797735136</v>
+        <v>-771836377.9665242</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>-18569.86116270994</v>
+        <v>-555485320.8484074</v>
       </c>
     </row>
     <row r="68">
@@ -22394,40 +22394,40 @@
         </is>
       </c>
       <c r="D71" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="E71" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="F71" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="G71" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="I71" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="J71" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="K71" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="L71" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="M71" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="N71" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="O71" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
     </row>
     <row r="72">
@@ -22500,40 +22500,40 @@
         </is>
       </c>
       <c r="D73" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="E73" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="F73" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="G73" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="I73" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="J73" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="K73" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="N73" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="O73" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
     </row>
     <row r="74">
@@ -22553,40 +22553,40 @@
         </is>
       </c>
       <c r="D74" s="18" t="n">
-        <v>16757.50885762326</v>
+        <v>550384654.7447641</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>16757.50885762326</v>
+        <v>550384654.7447641</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>16757.50885762326</v>
+        <v>550384654.7447641</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>16757.50885762326</v>
+        <v>550384654.7447641</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>16757.50885762326</v>
+        <v>550384654.7447641</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>16757.50885762326</v>
+        <v>550384654.7447641</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>16757.50885762326</v>
+        <v>550384654.7447641</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>16757.50885762326</v>
+        <v>550384654.7447641</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>16757.50885762326</v>
+        <v>550384654.7447641</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>16757.50885762326</v>
+        <v>550384654.7447641</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>16757.50885762326</v>
+        <v>550384654.7447641</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>16757.50885762326</v>
+        <v>550384654.7447641</v>
       </c>
     </row>
     <row r="75">
@@ -22606,40 +22606,40 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>-10288.95463702665</v>
+        <v>-132486740.348631</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-8623.801431432526</v>
+        <v>-250664920.1039659</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>-8422.216792258951</v>
+        <v>-242663335.3913114</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>-8217.720594443072</v>
+        <v>-234728339.1629707</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>-8261.232456312267</v>
+        <v>-226886361.295419</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>-8025.626852824207</v>
+        <v>-219109370.5374962</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>-8462.496070743524</v>
+        <v>-232202981.890134</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>-8888.448753570625</v>
+        <v>-245081474.6884626</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>-8665.383864264648</v>
+        <v>-237124430.7504431</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>-8440.382446163381</v>
+        <v>-229251516.7126658</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>-8214.029119728097</v>
+        <v>-221451723.2217602</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>-1812.352305086679</v>
+        <v>-5100666.103643298</v>
       </c>
     </row>
     <row r="76">
@@ -22662,37 +22662,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>-10288.95463702665</v>
+        <v>-132486740.348631</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>-14879.61728953895</v>
+        <v>-260707270.7223993</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>-9417.491645147888</v>
+        <v>-262419702.007456</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>-9375.751987850179</v>
+        <v>-254614832.1587506</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>-9624.150050945495</v>
+        <v>-246182025.5734624</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>-9817.365327364309</v>
+        <v>-237770947.2312178</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>-10272.26696736817</v>
+        <v>-250231700.8302397</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>-10689.07075225387</v>
+        <v>-264048751.1678632</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>-10454.3879392417</v>
+        <v>-257139145.7603923</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>-10198.40880183256</v>
+        <v>-248743086.8877178</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>-9941.77803496924</v>
+        <v>-240307495.154728</v>
       </c>
     </row>
     <row r="77">
@@ -22712,40 +22712,40 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>-10288.95463702665</v>
+        <v>-132486740.348631</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-8623.801431432526</v>
+        <v>-250664920.1039659</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>-8422.216792258951</v>
+        <v>-242663335.3913114</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>-8217.720594443072</v>
+        <v>-234728339.1629707</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>-8261.232456312267</v>
+        <v>-226886361.295419</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>-8025.626852824207</v>
+        <v>-219109370.5374962</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>-8462.496070743524</v>
+        <v>-232202981.890134</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>-8888.448753570625</v>
+        <v>-245081474.6884626</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>-8665.383864264648</v>
+        <v>-237124430.7504431</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>-8440.382446163381</v>
+        <v>-229251516.7126658</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>-8214.029119728097</v>
+        <v>-221451723.2217602</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>-1812.352305086679</v>
+        <v>-5100666.103643298</v>
       </c>
     </row>
     <row r="78">
@@ -22765,40 +22765,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>-10288.95463702665</v>
+        <v>-132486740.348631</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>-14879.61728953895</v>
+        <v>-260707270.7223993</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>-9417.491645147888</v>
+        <v>-262419702.007456</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>-9375.751987850179</v>
+        <v>-254614832.1587506</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>-9624.150050945495</v>
+        <v>-246182025.5734624</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>-9817.365327364309</v>
+        <v>-237770947.2312178</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>-10272.26696736817</v>
+        <v>-250231700.8302397</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>-10689.07075225387</v>
+        <v>-264048751.1678632</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>-10454.3879392417</v>
+        <v>-257139145.7603923</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>-10198.40880183256</v>
+        <v>-248743086.8877178</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>-9941.77803496924</v>
+        <v>-240307495.154728</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>-3501.225658445153</v>
+        <v>-23317882.88694784</v>
       </c>
     </row>
     <row r="79">
@@ -22924,40 +22924,40 @@
         </is>
       </c>
       <c r="D81" s="18" t="n">
-        <v>1.607015824783799</v>
+        <v>7.449867413537622e-05</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>2.373853366199607</v>
+        <v>7.44997897980794e-05</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>2.369241524748556</v>
+        <v>7.449978524692877e-05</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>2.365096425572976</v>
+        <v>7.449978114123307e-05</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>2.36138838088157</v>
+        <v>7.449977745622319e-05</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>2.358084612891792</v>
+        <v>7.44997741632161e-05</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>2.357506468296989</v>
+        <v>7.449977358600575e-05</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>2.356958038125158</v>
+        <v>7.449977303820011e-05</v>
       </c>
       <c r="L81" s="18" t="n">
-        <v>2.354419671827304</v>
+        <v>7.449977049940036e-05</v>
       </c>
       <c r="M81" s="18" t="n">
-        <v>2.352204123071624</v>
+        <v>7.44997682789949e-05</v>
       </c>
       <c r="N81" s="18" t="n">
-        <v>2.350288014482013</v>
+        <v>7.449976635531034e-05</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>2.252497332368283</v>
+        <v>7.449966383230512e-05</v>
       </c>
     </row>
     <row r="82">
@@ -23746,37 +23746,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>-11154.57972863984</v>
+        <v>-169443361.0084581</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>-13665.28132011164</v>
+        <v>-241371567.3786175</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>-8049.6937777389</v>
+        <v>-242820045.1927059</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>-7897.36993940414</v>
+        <v>-238962500.636533</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>-7922.681105140569</v>
+        <v>-234749635.6847724</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>-7945.300831228768</v>
+        <v>-230547681.3999428</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>19553.59190616957</v>
+        <v>-236778524.4750614</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>23234.21215208923</v>
+        <v>-243684402.772747</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>56183.85874209019</v>
+        <v>-240229696.1510769</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>60992.83692833027</v>
+        <v>-236031696.1930805</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>61725.81200207962</v>
+        <v>-231813924.9220206</v>
       </c>
     </row>
     <row r="97">
@@ -23796,40 +23796,40 @@
         </is>
       </c>
       <c r="D97" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="E97" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="F97" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="G97" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="H97" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="I97" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="J97" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="K97" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="N97" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
       <c r="O97" s="19" t="n">
-        <v>5236.72151800727</v>
+        <v>171995204.6077388</v>
       </c>
     </row>
     <row r="98">
@@ -23849,40 +23849,40 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>-16391.30124664712</v>
+        <v>-341438565.6161969</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>-12905.65006193128</v>
+        <v>-400525002.4192824</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>-12837.70786702407</v>
+        <v>-396524242.9130798</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>-12766.07016342172</v>
+        <v>-392556775.4093048</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>-12905.6786297575</v>
+        <v>-388635904.3280643</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>-12834.42123706425</v>
+        <v>-384747455.494512</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>-13075.90272417233</v>
+        <v>-391294284.2177089</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>-13308.47744156229</v>
+        <v>-397733550.2152493</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>-13217.43787344753</v>
+        <v>-393755048.7391161</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>-13123.61983128619</v>
+        <v>-389818610.4028944</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>-13027.20571769484</v>
+        <v>-385918730.4199911</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>-10005.86851188767</v>
+        <v>-277743381.3621342</v>
       </c>
     </row>
     <row r="99">
@@ -23955,40 +23955,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>-11154.57972863984</v>
+        <v>-169443361.0084581</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>-13665.28132011164</v>
+        <v>-241371567.3786175</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>-8049.6937777389</v>
+        <v>-242820045.1927059</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>-7897.36993940414</v>
+        <v>-238962500.636533</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>-7922.681105140569</v>
+        <v>-234749635.6847724</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>-7945.300831228768</v>
+        <v>-230547681.3999428</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>19553.59190616957</v>
+        <v>-236778524.4750614</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>23234.21215208923</v>
+        <v>-243684402.772747</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>56183.85874209019</v>
+        <v>-240229696.1510769</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>60992.83692833027</v>
+        <v>-236031696.1930805</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>61725.81200207962</v>
+        <v>-231813924.9220206</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>65466.55166541673</v>
+        <v>-123291647.4822437</v>
       </c>
     </row>
     <row r="101">
@@ -24061,40 +24061,40 @@
         </is>
       </c>
       <c r="D102" s="18" t="n">
-        <v>-4086.840482146479</v>
+        <v>-134228440.9260423</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>-4086.84048214648</v>
+        <v>-134228440.9260423</v>
       </c>
       <c r="F102" s="18" t="n">
-        <v>-4086.840482146479</v>
+        <v>-134228440.9260423</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>-4086.840482146479</v>
+        <v>-134228440.9260423</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>-4086.840482146479</v>
+        <v>-134228440.9260423</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>-4086.840482146479</v>
+        <v>-134228440.9260423</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>-4086.840482146479</v>
+        <v>-134228440.9260423</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>-4086.840482146479</v>
+        <v>-134228440.9260423</v>
       </c>
       <c r="L102" s="18" t="n">
-        <v>-4086.840482146479</v>
+        <v>-134228440.9260423</v>
       </c>
       <c r="M102" s="18" t="n">
-        <v>-4086.840482146479</v>
+        <v>-134228440.9260423</v>
       </c>
       <c r="N102" s="18" t="n">
-        <v>-4086.840482146479</v>
+        <v>-134228440.9260423</v>
       </c>
       <c r="O102" s="18" t="n">
-        <v>-4086.840482146479</v>
+        <v>-134228440.9260423</v>
       </c>
     </row>
     <row r="103">
@@ -24117,37 +24117,37 @@
         <v>0</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>11519.54548359611</v>
+        <v>352524132.6591883</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>11520.70683093459</v>
+        <v>374753911.7440073</v>
       </c>
       <c r="G103" s="18" t="n">
-        <v>11520.72138266344</v>
+        <v>376741119.6012489</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>11520.73581328573</v>
+        <v>377192267.7200502</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>11520.75007519106</v>
+        <v>377513130.1882982</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>11520.76421839987</v>
+        <v>377841756.0845569</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>11520.74040647613</v>
+        <v>377370048.6136078</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>11520.71698575826</v>
+        <v>376846607.0506854</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>11520.73145644389</v>
+        <v>377108469.2862191</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>11520.74577412301</v>
+        <v>377426636.4027589</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>11520.75995881887</v>
+        <v>377745981.5521668</v>
       </c>
     </row>
     <row r="104">
@@ -24167,40 +24167,40 @@
         </is>
       </c>
       <c r="D104" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="E104" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="F104" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="G104" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="H104" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="I104" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="J104" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="K104" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="L104" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="M104" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="N104" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
       <c r="O104" s="19" t="n">
-        <v>11520.78733961599</v>
+        <v>378389450.1370254</v>
       </c>
     </row>
     <row r="105">
@@ -24220,40 +24220,40 @@
         </is>
       </c>
       <c r="D105" s="18" t="n">
-        <v>-10395.56474679226</v>
+        <v>-341432569.8796971</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>-12194.72473395131</v>
+        <v>-400524291.4939544</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>-12072.91235234769</v>
+        <v>-396523478.1175651</v>
       </c>
       <c r="G105" s="18" t="n">
-        <v>-11952.11375253603</v>
+        <v>-392555961.4528939</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>-11832.72748074657</v>
+        <v>-388634831.3769153</v>
       </c>
       <c r="I105" s="18" t="n">
-        <v>-11714.3348164914</v>
+        <v>-384746335.4080915</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>-11913.66420005668</v>
+        <v>-391293121.9791849</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>-12109.71880309476</v>
+        <v>-397732351.4566109</v>
       </c>
       <c r="L105" s="18" t="n">
-        <v>-11988.58483349947</v>
+        <v>-393753819.8860762</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>-11868.73167988833</v>
+        <v>-389817355.5147429</v>
       </c>
       <c r="N105" s="18" t="n">
-        <v>-11749.99172789437</v>
+        <v>-385917453.2060013</v>
       </c>
       <c r="O105" s="18" t="n">
-        <v>-8456.378948093097</v>
+        <v>-277741831.8725704</v>
       </c>
     </row>
     <row r="106">
@@ -24326,40 +24326,40 @@
         </is>
       </c>
       <c r="D107" s="18" t="n">
-        <v>11519.54548359611</v>
+        <v>352524132.6591883</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>11520.70683093459</v>
+        <v>374753911.7440073</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>11520.72138266344</v>
+        <v>376741119.6012489</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>11520.73581328573</v>
+        <v>377192267.7200502</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>11520.75007519106</v>
+        <v>377513130.1882982</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>11520.76421839987</v>
+        <v>377841756.0845569</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>11520.74040647613</v>
+        <v>377370048.6136078</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>11520.71698575826</v>
+        <v>376846607.0506854</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>11520.73145644389</v>
+        <v>377108469.2862191</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>11520.74577412301</v>
+        <v>377426636.4027589</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>11520.75995881887</v>
+        <v>377745981.5521668</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>11521.15341438933</v>
+        <v>385964854.7369099</v>
       </c>
     </row>
     <row r="108">

--- a/backend/Rwanda/financial-statements-CleanStep.xlsx
+++ b/backend/Rwanda/financial-statements-CleanStep.xlsx
@@ -644,40 +644,40 @@
         </is>
       </c>
       <c r="D2" s="18" t="n">
-        <v>-1914774.054075216</v>
+        <v>-55004086.32041625</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>-3454927.684233574</v>
+        <v>-99246770.22332075</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>-3420378.407391245</v>
+        <v>-98254302.52108774</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>-3386174.623317326</v>
+        <v>-97271759.49587667</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>-3352312.87708416</v>
+        <v>-96299041.9009181</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>-3318789.748313316</v>
+        <v>-95336051.48190886</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>-4778005.632218572</v>
+        <v>-137253705.561054</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>-6215148.589468248</v>
+        <v>-178537289.4424525</v>
       </c>
       <c r="L2" s="18" t="n">
-        <v>-6152997.103573568</v>
+        <v>-176751916.5480278</v>
       </c>
       <c r="M2" s="18" t="n">
-        <v>-6091467.13253783</v>
+        <v>-174984397.3825475</v>
       </c>
       <c r="N2" s="18" t="n">
-        <v>-6030552.461212453</v>
+        <v>-173234553.4087222</v>
       </c>
       <c r="O2" s="18" t="n">
-        <v>-3709422.11862368</v>
+        <v>-106557415.4701928</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
@@ -700,13 +700,13 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>80.43526738209388</v>
+        <v>80.43526738209383</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>-0.9999999999998233</v>
+        <v>-0.9999999999998122</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>-1.000000000000167</v>
+        <v>-1.00000000000019</v>
       </c>
       <c r="H3" s="18" t="n">
         <v>-0.999999999999801</v>
@@ -715,22 +715,22 @@
         <v>-1.000000000000056</v>
       </c>
       <c r="J3" s="18" t="n">
-        <v>43.96831358921916</v>
+        <v>43.9683135892192</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>30.07830186634517</v>
+        <v>30.07830186634521</v>
       </c>
       <c r="L3" s="18" t="n">
-        <v>-0.9999999999999565</v>
+        <v>-1.000000000000056</v>
       </c>
       <c r="M3" s="18" t="n">
-        <v>-1.000000000000045</v>
+        <v>-1.000000000000023</v>
       </c>
       <c r="N3" s="18" t="n">
-        <v>-0.9999999999999676</v>
+        <v>-0.9999999999999232</v>
       </c>
       <c r="O3" s="18" t="n">
-        <v>-38.48951414514526</v>
+        <v>-38.48951414514529</v>
       </c>
     </row>
     <row r="4" ht="15.5" customHeight="1">
@@ -856,40 +856,40 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>-1914774.054075216</v>
+        <v>-55004086.32041625</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>-3454927.684233574</v>
+        <v>-99246770.22332075</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>-3420378.407391245</v>
+        <v>-98254302.52108774</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>-3386174.623317326</v>
+        <v>-97271759.49587667</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>-3352312.87708416</v>
+        <v>-96299041.9009181</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>-3318789.748313316</v>
+        <v>-95336051.48190886</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>-4778005.632218572</v>
+        <v>-137253705.561054</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>-6215148.589468248</v>
+        <v>-178537289.4424525</v>
       </c>
       <c r="L6" s="18" t="n">
-        <v>-6152997.103573568</v>
+        <v>-176751916.5480278</v>
       </c>
       <c r="M6" s="18" t="n">
-        <v>-6091467.13253783</v>
+        <v>-174984397.3825475</v>
       </c>
       <c r="N6" s="18" t="n">
-        <v>-6030552.461212453</v>
+        <v>-173234553.4087222</v>
       </c>
       <c r="O6" s="18" t="n">
-        <v>-3709422.11862368</v>
+        <v>-106557415.4701928</v>
       </c>
     </row>
     <row r="7" ht="15.5" customHeight="1">
@@ -912,13 +912,13 @@
         <v>0</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>80.43526738209388</v>
+        <v>80.43526738209383</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>-0.9999999999998233</v>
+        <v>-0.9999999999998122</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>-1.000000000000167</v>
+        <v>-1.00000000000019</v>
       </c>
       <c r="H7" s="18" t="n">
         <v>-0.999999999999801</v>
@@ -927,22 +927,22 @@
         <v>-1.000000000000056</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>43.96831358921916</v>
+        <v>43.9683135892192</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>30.07830186634517</v>
+        <v>30.07830186634521</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>-0.9999999999999565</v>
+        <v>-1.000000000000056</v>
       </c>
       <c r="M7" s="18" t="n">
-        <v>-1.000000000000045</v>
+        <v>-1.000000000000023</v>
       </c>
       <c r="N7" s="18" t="n">
-        <v>-0.9999999999999676</v>
+        <v>-0.9999999999999232</v>
       </c>
       <c r="O7" s="18" t="n">
-        <v>-38.48951414514526</v>
+        <v>-38.48951414514529</v>
       </c>
     </row>
     <row r="8" ht="15.5" customHeight="1">
@@ -1280,40 +1280,40 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>0.000168656326988158</v>
+        <v>5.871177590176297e-06</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>0.0002915297993460997</v>
+        <v>1.014858591643344e-05</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>0.0004931167713175373</v>
+        <v>1.716612823723415e-05</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>0.0006953532692720455</v>
+        <v>2.420628152356544e-05</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>0.000898245854078132</v>
+        <v>3.126927416901822e-05</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>0.00110180115287572</v>
+        <v>3.835533687418996e-05</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>0.0009178649352717545</v>
+        <v>3.19522435654283e-05</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>0.0008053318015768958</v>
+        <v>2.803479780753533e-05</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>0.0008804705001846417</v>
+        <v>3.06504876621578e-05</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>0.0009562796988979686</v>
+        <v>3.328951862271083e-05</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>0.001032766170445213</v>
+        <v>3.595212645794113e-05</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>0.001747837092019904</v>
+        <v>6.084480878482959e-05</v>
       </c>
     </row>
     <row r="15" ht="15.5" customHeight="1">
@@ -1439,40 +1439,40 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>0.0001617719063900793</v>
+        <v>5.631520669747659e-06</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>0.0003485913132456718</v>
+        <v>1.21349820846141e-05</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>0.000610355460049909</v>
+        <v>2.1247381364699e-05</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0.0008516612204987085</v>
+        <v>2.964759378736678e-05</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>0.0021475461524905</v>
+        <v>7.475927567933372e-05</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>0.002555577300350929</v>
+        <v>8.896344681357329e-05</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>0.00201441465669275</v>
+        <v>7.012477030006456e-05</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>0.001882142751119442</v>
+        <v>6.552018853500299e-05</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>0.002171965787639656</v>
+        <v>7.560935949894685e-05</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>0.002437071882322751</v>
+        <v>8.483809695527617e-05</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>0.002678853654532493</v>
+        <v>9.325488005532917e-05</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>0.004665498391587368</v>
+        <v>0.0001624129381497477</v>
       </c>
     </row>
     <row r="18" ht="15.5" customHeight="1">
@@ -1598,40 +1598,40 @@
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>0.0001053471545572795</v>
+        <v>3.667291136187059e-06</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>0.0001931337099563581</v>
+        <v>6.723271697260404e-06</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>0.0003304176096040957</v>
+        <v>1.150232843054502e-05</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>0.0004677015092518357</v>
+        <v>1.628138516382973e-05</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>0.0006049854088995715</v>
+        <v>2.106044189711428e-05</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>0.000742269308547311</v>
+        <v>2.583949863039897e-05</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>0.0006048259192627696</v>
+        <v>2.105488982564339e-05</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>0.0005013683374482158</v>
+        <v>1.745337752704999e-05</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>0.0005101275256035883</v>
+        <v>1.775829789454723e-05</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>0.0005188867137589616</v>
+        <v>1.806321826204447e-05</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>0.000527645901914334</v>
+        <v>1.836813862954168e-05</v>
       </c>
       <c r="O20" s="18" t="n">
-        <v>0.0008633341645554521</v>
+        <v>3.005394633150908e-05</v>
       </c>
     </row>
     <row r="21" ht="15.5" customHeight="1">
@@ -1810,40 +1810,40 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>1914779.168801688</v>
+        <v>55004091.43514273</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>3454946.400441373</v>
+        <v>99246788.93952855</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>3420410.585390181</v>
+        <v>98254334.69908667</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>3386219.299243271</v>
+        <v>97271804.17180263</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>3352405.150554138</v>
+        <v>96299134.17438808</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>3318899.196908487</v>
+        <v>95336160.93050404</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>4778130.779680813</v>
+        <v>137253830.7085162</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>6215296.728224049</v>
+        <v>178537437.5812083</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>6153162.132697447</v>
+        <v>176752081.5771517</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>6091647.193784161</v>
+        <v>174984577.4437939</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>6030745.830850373</v>
+        <v>173234746.7783601</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>3709627.20636142</v>
+        <v>106557620.5579305</v>
       </c>
     </row>
     <row r="25" ht="15.5" customHeight="1">
@@ -1863,40 +1863,40 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>3829553.222876904</v>
+        <v>110008177.755559</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>6909874.084674947</v>
+        <v>198493559.1628493</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>6840788.992781426</v>
+        <v>196508637.2201744</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>6772393.922560597</v>
+        <v>194543563.6676793</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>6704718.027638298</v>
+        <v>192598176.0753062</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>6637688.945221804</v>
+        <v>190672212.4124129</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>9556136.411899384</v>
+        <v>274507536.2695702</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>12430445.3176923</v>
+        <v>357074727.0236607</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>12306159.23627102</v>
+        <v>353503998.1251796</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>12183114.32632199</v>
+        <v>349968974.8263414</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>12061298.29206283</v>
+        <v>346469300.1870823</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>7419049.3249851</v>
+        <v>213115036.0281233</v>
       </c>
     </row>
     <row r="26" ht="15.5" customHeight="1">
@@ -1916,40 +1916,40 @@
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>-100.0002671190609</v>
+        <v>-100.0000092988118</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>-100.0005417250232</v>
+        <v>-100.0000188582538</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>-100.0009407730696</v>
+        <v>-100.0000327497098</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>-100.0013193627298</v>
+        <v>-100.0000459289789</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>-100.0027525315614</v>
+        <v>-100.0000958197176</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>-100.0032978466089</v>
+        <v>-100.0001148029455</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>-100.002619240576</v>
+        <v>-100.0000911796601</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>-100.0023835110886</v>
+        <v>-100.0000829735661</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>-100.0026820933132</v>
+        <v>-100.0000933676574</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>-100.0029559585961</v>
+        <v>-100.0001029013152</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>-100.0032064995564</v>
+        <v>-100.0001116230187</v>
       </c>
       <c r="O26" s="18" t="n">
-        <v>-100.0055288325562</v>
+        <v>-100.0001924668845</v>
       </c>
     </row>
     <row r="27" ht="15.5" customHeight="1">
@@ -1969,40 +1969,40 @@
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>-200.0002671190609</v>
+        <v>-200.0000092988118</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>-200.0005417250232</v>
+        <v>-200.0000188582538</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>-200.0009407730696</v>
+        <v>-200.0000327497098</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>-200.0013193627297</v>
+        <v>-200.000045928979</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>-200.0027525315614</v>
+        <v>-200.0000958197176</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>-200.0032978466089</v>
+        <v>-200.0001148029454</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>-200.0026192405759</v>
+        <v>-200.0000911796601</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>-200.0023835110886</v>
+        <v>-200.0000829735661</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>-200.0026820933133</v>
+        <v>-200.0000933676574</v>
       </c>
       <c r="M27" s="18" t="n">
-        <v>-200.0029559585961</v>
+        <v>-200.0001029013152</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>-200.0032064995565</v>
+        <v>-200.0001116230187</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>-200.0055288325562</v>
+        <v>-200.0001924668845</v>
       </c>
     </row>
     <row r="28" ht="15.5" customHeight="1">
@@ -2075,40 +2075,40 @@
         </is>
       </c>
       <c r="D29" s="19" t="n">
-        <v>-6.330917243087276e-05</v>
+        <v>-2.203886453989038e-06</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>-9.839608938974404e-05</v>
+        <v>-3.425314219173122e-06</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>-0.0001626991617134425</v>
+        <v>-5.66379980668916e-06</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>-0.0002276517600202088</v>
+        <v>-7.924896359735672e-06</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>-0.0002932604451785579</v>
+        <v>-1.020883227190384e-05</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>-0.0003595318443284063</v>
+        <v>-1.251583824379091e-05</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>-0.0003130390160089872</v>
+        <v>-1.0897353739785e-05</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>-0.0003039634641286792</v>
+        <v>-1.058142028048531e-05</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>-0.0003703429745810532</v>
+        <v>-1.289218976761056e-05</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>-0.0004373929851390081</v>
+        <v>-1.52263003606664e-05</v>
       </c>
       <c r="N29" s="19" t="n">
-        <v>-0.0005051202685308797</v>
+        <v>-1.758398782839948e-05</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>-0.0008845029274644511</v>
+        <v>-3.079086245332049e-05</v>
       </c>
     </row>
     <row r="30" ht="15.5" customHeight="1">
@@ -2128,40 +2128,40 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>1914777.956574081</v>
+        <v>55004090.22291512</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>3454943.000927641</v>
+        <v>99246785.54001482</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>3420405.020463185</v>
+        <v>98254329.13415967</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>3386211.590557144</v>
+        <v>97271796.4631165</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>3352395.319546471</v>
+        <v>96299124.34338041</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>3318887.264802496</v>
+        <v>95336148.99839805</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>4778115.822658997</v>
+        <v>137253815.7514944</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>6215277.836443096</v>
+        <v>178537418.6894273</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>6153139.345504948</v>
+        <v>176752058.7899593</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>6091620.550134231</v>
+        <v>174984550.8001439</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>6030715.369307587</v>
+        <v>173234716.3168173</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>3709594.396414188</v>
+        <v>106557587.7479833</v>
       </c>
     </row>
     <row r="31" ht="15.5" customHeight="1">
@@ -2181,40 +2181,40 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>-100.0002038098885</v>
+        <v>-100.0000070949254</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>-100.0004433289338</v>
+        <v>-100.0000154329396</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>-100.0007780739079</v>
+        <v>-100.00002708591</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>-100.0010917109697</v>
+        <v>-100.0000380040826</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>-100.0024592711162</v>
+        <v>-100.0000856108853</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>-100.0029383147646</v>
+        <v>-100.0001022871072</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>-100.0023062015599</v>
+        <v>-100.0000802823064</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>-100.0020795476245</v>
+        <v>-100.0000723921458</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>-100.0023117503387</v>
+        <v>-100.0000804754676</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>-100.0025185656109</v>
+        <v>-100.0000876750149</v>
       </c>
       <c r="N31" s="19" t="n">
-        <v>-100.0027013792879</v>
+        <v>-100.0000940390309</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>-100.0046443296287</v>
+        <v>-100.000161676022</v>
       </c>
     </row>
     <row r="32" ht="15.5" customHeight="1">
@@ -2287,40 +2287,40 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>1914777.956574081</v>
+        <v>55004090.22291512</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>3454943.000927641</v>
+        <v>99246785.54001482</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>3420405.020463185</v>
+        <v>98254329.13415967</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>3386211.590557144</v>
+        <v>97271796.4631165</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>3352395.319546471</v>
+        <v>96299124.34338041</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>3318887.264802496</v>
+        <v>95336148.99839805</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>4778115.822658997</v>
+        <v>137253815.7514944</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>6215277.836443096</v>
+        <v>178537418.6894273</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>6153139.345504948</v>
+        <v>176752058.7899593</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>6091620.550134231</v>
+        <v>174984550.8001439</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>6030715.369307587</v>
+        <v>173234716.3168173</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>3709594.396414188</v>
+        <v>106557587.7479833</v>
       </c>
     </row>
     <row r="34" ht="15.5" customHeight="1">
@@ -2340,40 +2340,40 @@
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>3829552.010649296</v>
+        <v>110008176.5433314</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>6909870.685161214</v>
+        <v>198493555.7633356</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>6840783.42785443</v>
+        <v>196508631.6552474</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>6772386.21387447</v>
+        <v>194543555.9589932</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>6704708.196630631</v>
+        <v>192598166.2442985</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>6637677.013115812</v>
+        <v>190672200.4803069</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>9556121.45487757</v>
+        <v>274507521.3125484</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>12430426.42591134</v>
+        <v>357074708.1318798</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>12306136.44907852</v>
+        <v>353503975.3379871</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>12183087.68267206</v>
+        <v>349968948.1826915</v>
       </c>
       <c r="N34" s="19" t="n">
-        <v>12061267.83052004</v>
+        <v>346469269.7255395</v>
       </c>
       <c r="O34" s="19" t="n">
-        <v>7419016.515037868</v>
+        <v>213115003.2181761</v>
       </c>
     </row>
     <row r="35" ht="15.5" customHeight="1">
@@ -2446,40 +2446,40 @@
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>-1072274.562981803</v>
+        <v>-30802289.43213278</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>-1934763.79184514</v>
+        <v>-55578195.61373396</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-1915419.35979924</v>
+        <v>-55022416.86346927</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>-1896268.139884852</v>
+        <v>-54472195.66851809</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>-1877318.295056577</v>
+        <v>-53927486.54840359</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>-1858549.563672428</v>
+        <v>-53388216.13448594</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>-2675714.00736572</v>
+        <v>-76862105.96751355</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>-3480519.399255177</v>
+        <v>-99980918.27692634</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>-3445718.205741984</v>
+        <v>-98981113.09463638</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>-3411264.551148178</v>
+        <v>-97991305.4911536</v>
       </c>
       <c r="N36" s="19" t="n">
-        <v>-3377154.992545612</v>
+        <v>-97011395.52315105</v>
       </c>
       <c r="O36" s="19" t="n">
-        <v>-2077324.624210603</v>
+        <v>-59672200.9010893</v>
       </c>
     </row>
     <row r="37" ht="15.5" customHeight="1">
@@ -2552,40 +2552,40 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>842503.3935922775</v>
+        <v>24201800.79078234</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>1520179.209082501</v>
+        <v>43668589.92628086</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>1504985.660663945</v>
+        <v>43231912.2706904</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>1489943.450672292</v>
+        <v>42799600.79459841</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>1475077.024489895</v>
+        <v>42371637.79497682</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>1460337.701130068</v>
+        <v>41947932.86391211</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>2102401.815293277</v>
+        <v>60391709.78398089</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>2734758.437187919</v>
+        <v>78556500.41250098</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>2707421.139762964</v>
+        <v>77770945.69532287</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>2680355.998986054</v>
+        <v>76993245.30899033</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>2653560.376761975</v>
+        <v>76223320.79366626</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>1632269.772203585</v>
+        <v>46885386.846894</v>
       </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
@@ -2605,40 +2605,40 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>-44.00014674311972</v>
+        <v>-44.00000510834626</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>-44.00031919683236</v>
+        <v>-44.00001111171648</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>-44.00056021321371</v>
+        <v>-44.00001950185519</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>-44.00078603189821</v>
+        <v>-44.00002736293947</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>-44.00177067520368</v>
+        <v>-44.0000616398374</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>-44.00211558663049</v>
+        <v>-44.00007364671719</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>-44.00166046512315</v>
+        <v>-44.00005780326062</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>-44.00149727428959</v>
+        <v>-44.00005212234496</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>-44.00166446024384</v>
+        <v>-44.00005794233671</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>-44.00181336723987</v>
+        <v>-44.0000631260107</v>
       </c>
       <c r="N39" s="19" t="n">
-        <v>-44.00194499308729</v>
+        <v>-44.00006770810221</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>-44.00334391733265</v>
+        <v>-44.00011640673586</v>
       </c>
     </row>
     <row r="40" ht="15.5" customHeight="1">
@@ -2817,40 +2817,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>-7609789.543544516</v>
+        <v>-2356664837.262258</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>-7928248.051413828</v>
+        <v>-2498015158.579686</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>-7934961.533243593</v>
+        <v>-2505624948.379963</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>-7938027.886845451</v>
+        <v>-2505943406.816825</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>-7938921.070936996</v>
+        <v>-2505950123.134758</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>-7939864.617604261</v>
+        <v>-2505953189.902755</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>-7939767.983300803</v>
+        <v>-2505954080.494554</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>-7939645.019732312</v>
+        <v>-2505955024.863018</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>-7942572.281087654</v>
+        <v>-2505954928.990249</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>-7946470.533356968</v>
+        <v>-2505954805.708253</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>-7948304.0420189</v>
+        <v>-2505957732.677697</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>-7949111.341035689</v>
+        <v>-2505961630.660037</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -2870,40 +2870,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>-7609789.454743981</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>-7928247.609966066</v>
+        <v>-2498015158.138238</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>-7934960.746262733</v>
+        <v>-2505624947.592983</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>-7938026.818225207</v>
+        <v>-2505943405.748205</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>-7938916.820679809</v>
+        <v>-2505950118.884501</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>-7939859.671312776</v>
+        <v>-2505953184.956463</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>-7939762.447665521</v>
+        <v>-2505954074.958919</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>-7939637.96626534</v>
+        <v>-2505955017.809551</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>-7942563.876742985</v>
+        <v>-2505954920.585904</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>-7946460.929607455</v>
+        <v>-2505954796.104504</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>-7948293.379302839</v>
+        <v>-2505957722.014981</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>-7949099.748844936</v>
+        <v>-2505961619.067846</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -3029,40 +3029,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>-7609748.327805859</v>
+        <v>-2356664796.046519</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>-7928133.68017453</v>
+        <v>-2498015044.208447</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>-7934776.93746706</v>
+        <v>-2505624763.784187</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>-7937775.968185457</v>
+        <v>-2505943154.898165</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>-7938604.702030778</v>
+        <v>-2505949806.765852</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>-7939486.642362681</v>
+        <v>-2505952811.927513</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>-7939299.093027183</v>
+        <v>-2505953611.60428</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>-7939057.304669838</v>
+        <v>-2505954437.147955</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>-7941871.01381357</v>
+        <v>-2505954227.722975</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>-7945660.933722747</v>
+        <v>-2505953996.108619</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>-7947391.277677497</v>
+        <v>-2505956819.913356</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>-7948149.192485933</v>
+        <v>-2505960668.511487</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -3082,40 +3082,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>-5205776.601344177</v>
+        <v>-922937592.6992105</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>-8660631.835371565</v>
+        <v>-1022184290.472325</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>-10229521.80012366</v>
+        <v>-1068620079.942388</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>-10213639.41197227</v>
+        <v>-1071122156.815735</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>-10146630.65323666</v>
+        <v>-1070712866.652567</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>-10079216.71270177</v>
+        <v>-1068738581.151078</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>-11504218.78129222</v>
+        <v>-1109603729.774847</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>-14399294.69342276</v>
+        <v>-1192715248.338019</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>-15822386.96572444</v>
+        <v>-1234606947.169693</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>-15747619.76426221</v>
+        <v>-1234902997.58347</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>-15624980.47491582</v>
+        <v>-1232767485.501029</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>-13241711.36922383</v>
+        <v>-1164224956.286575</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -3135,40 +3135,40 @@
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
     </row>
     <row r="50" ht="15.5" customHeight="1">
@@ -3188,40 +3188,40 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>-1914733.015937628</v>
+        <v>-55004045.28227866</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>-3454855.234027387</v>
+        <v>-99246697.77311459</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>-3420308.873920204</v>
+        <v>-98254232.98761669</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>-3386107.863712635</v>
+        <v>-97271692.73627198</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>-3352254.79011182</v>
+        <v>-96298983.81394576</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>-3318729.534046552</v>
+        <v>-95335991.26764208</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>-4777915.895874124</v>
+        <v>-137253615.8247095</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>-6215032.800342774</v>
+        <v>-178537173.653327</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>-6152886.253117351</v>
+        <v>-176751805.6975716</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>-6091361.198987383</v>
+        <v>-174984291.4489971</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>-6030451.414438367</v>
+        <v>-173234452.3619481</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>-3709374.593364711</v>
+        <v>-106557367.9449338</v>
       </c>
     </row>
     <row r="51" ht="15.5" customHeight="1">
@@ -3244,37 +3244,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>-1914733.015937628</v>
+        <v>-55004045.28227866</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>-3518169.340796908</v>
+        <v>-102432299.5378394</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>-3536487.962853086</v>
+        <v>-105916916.6625312</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>-3503332.277718294</v>
+        <v>-106480335.4216891</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>-3469443.593248669</v>
+        <v>-105469042.4665045</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>-3435259.300011547</v>
+        <v>-104416566.5332053</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>-4893218.307673439</v>
+        <v>-146244527.2677605</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>-6378457.127200537</v>
+        <v>-189921594.0551898</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>-6365214.979868273</v>
+        <v>-191985158.7175408</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>-6303485.475070905</v>
+        <v>-191599485.7221484</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>-6241293.190452569</v>
+        <v>-189734040.9247089</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -3294,40 +3294,40 @@
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>-4255390.724430324</v>
+        <v>-1485545646.953663</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>-4349267.896404509</v>
+        <v>-1567290561.458876</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>-4348235.339838852</v>
+        <v>-1570063278.78424</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>-4349043.278031831</v>
+        <v>-1570248610.661837</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>-4349209.610948668</v>
+        <v>-1570338118.263839</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>-4350231.024988095</v>
+        <v>-1570428560.959013</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>-4301892.069965376</v>
+        <v>-1568034527.646574</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>-4255796.414535776</v>
+        <v>-1564185333.513483</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>-4259785.470733798</v>
+        <v>-1562803254.106225</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>-4262726.227166624</v>
+        <v>-1562921678.416653</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>-4265155.049027689</v>
+        <v>-1563088542.239052</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>-4341868.210950826</v>
+        <v>-1567014102.474558</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -3347,40 +3347,40 @@
         </is>
       </c>
       <c r="D53" s="18" t="n">
-        <v>-4255390.724430324</v>
+        <v>-1485545646.953663</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>-4349267.896404509</v>
+        <v>-1567290561.458876</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>-4348235.339838852</v>
+        <v>-1570063278.78424</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>-4349043.278031831</v>
+        <v>-1570248610.661837</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>-4349209.610948668</v>
+        <v>-1570338118.263839</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>-4350231.024988095</v>
+        <v>-1570428560.959013</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>-4301892.069965376</v>
+        <v>-1568034527.646574</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>-4255796.414535776</v>
+        <v>-1564185333.513483</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>-4259785.470733798</v>
+        <v>-1562803254.106225</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>-4262726.227166624</v>
+        <v>-1562921678.416653</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>-4265155.049027689</v>
+        <v>-1563088542.239052</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>-4341868.210950826</v>
+        <v>-1567014102.474558</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -3612,40 +3612,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>-9461167.236973967</v>
+        <v>-2408483239.564073</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>-13009899.29032831</v>
+        <v>-2589474851.489753</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>-14577756.35298165</v>
+        <v>-2638683357.939647</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>-14562681.62138386</v>
+        <v>-2641370766.408952</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>-14495836.01392815</v>
+        <v>-2641050980.666149</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>-14429442.79139838</v>
+        <v>-2639167137.1638</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>-15806105.31562231</v>
+        <v>-2677638251.885785</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>-18655084.05449157</v>
+        <v>-2756900574.798035</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>-20082164.03211357</v>
+        <v>-2797410192.871573</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>-20010336.38767932</v>
+        <v>-2797824666.396373</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>-19890124.86122745</v>
+        <v>-2795856017.077364</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>-17583567.9879839</v>
+        <v>-2731239047.168941</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -3665,40 +3665,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>1851418.909168108</v>
+        <v>51818443.51755381</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>5081765.610153781</v>
+        <v>91459807.28130627</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>6642979.415514593</v>
+        <v>133058594.1554599</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>6624905.653198398</v>
+        <v>135427611.5107875</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>6557231.311897367</v>
+        <v>135101173.9002962</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>6489956.149035697</v>
+        <v>133214325.2362866</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>7866806.222595132</v>
+        <v>171684640.2815046</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>10716026.74982173</v>
+        <v>250946137.6500797</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>12140293.0183</v>
+        <v>291455965.1485987</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>12064675.45395657</v>
+        <v>291870670.2877541</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>11942733.58354995</v>
+        <v>289899197.1640086</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>9635418.795497969</v>
+        <v>225278378.657454</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -3771,40 +3771,40 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>3829553.222876904</v>
+        <v>110008177.755559</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>6909874.084674947</v>
+        <v>198493559.1628493</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>6840788.992781426</v>
+        <v>196508637.2201744</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>6772393.922560597</v>
+        <v>194543563.6676793</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>6704718.027638298</v>
+        <v>192598176.0753062</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>6637688.945221804</v>
+        <v>190672212.4124129</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>9556136.411899384</v>
+        <v>274507536.2695702</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>12430445.3176923</v>
+        <v>357074727.0236607</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>12306159.23627102</v>
+        <v>353503998.1251796</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>12183114.32632199</v>
+        <v>349968974.8263414</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>12061298.29206283</v>
+        <v>346469300.1870823</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>7419049.3249851</v>
+        <v>213115036.0281233</v>
       </c>
     </row>
     <row r="62" ht="15.5" customHeight="1">
@@ -3824,40 +3824,40 @@
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>-1072274.562981803</v>
+        <v>-30802289.43213278</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>-1934763.79184514</v>
+        <v>-55578195.61373396</v>
       </c>
       <c r="F62" s="18" t="n">
-        <v>-1915419.35979924</v>
+        <v>-55022416.86346927</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>-1896268.139884852</v>
+        <v>-54472195.66851809</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>-1877318.295056577</v>
+        <v>-53927486.54840359</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>-1858549.563672428</v>
+        <v>-53388216.13448594</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>-2675714.00736572</v>
+        <v>-76862105.96751355</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>-3480519.399255177</v>
+        <v>-99980918.27692634</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>-3445718.205741984</v>
+        <v>-98981113.09463638</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>-3411264.551148178</v>
+        <v>-97991305.4911536</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>-3377154.992545612</v>
+        <v>-97011395.52315105</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>-2077324.624210603</v>
+        <v>-59672200.9010893</v>
       </c>
     </row>
     <row r="63" ht="15.5" customHeight="1">
@@ -3930,40 +3930,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>2757278.83749617</v>
+        <v>79205888.50102726</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>4975110.998124261</v>
+        <v>142915364.2544098</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>4925370.324048379</v>
+        <v>141486221.0477713</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>4876126.345954515</v>
+        <v>140071368.56244</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>4827406.095855607</v>
+        <v>138670695.8901765</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>4779140.773617974</v>
+        <v>137283997.6699955</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>6880423.583221258</v>
+        <v>197645431.4807443</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>8949928.954100501</v>
+        <v>257093811.7823977</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>8860443.732284423</v>
+        <v>254522887.7322986</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>8771852.173983505</v>
+        <v>251977671.7339975</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>8684145.417450309</v>
+        <v>249457906.7818643</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>5341726.55972388</v>
+        <v>153442836.9859834</v>
       </c>
     </row>
     <row r="65" ht="15.5" customHeight="1">
@@ -4089,40 +4089,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>2757236.409529906</v>
+        <v>79205846.07306099</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>4975034.443109888</v>
+        <v>142915287.6993954</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>4925294.534584149</v>
+        <v>141486145.2583071</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>4876051.314384927</v>
+        <v>140071293.5308704</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>4827331.814601715</v>
+        <v>138670621.6089226</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>4779067.23517662</v>
+        <v>137283924.1315542</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>6880317.711167402</v>
+        <v>197645325.6086904</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>8949791.237530693</v>
+        <v>257093674.0658279</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>8860307.392880315</v>
+        <v>254522751.3928945</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>8771717.197973438</v>
+        <v>251977536.7579874</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>8684011.791200342</v>
+        <v>249457773.1556144</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>5341644.365568296</v>
+        <v>153442754.7918278</v>
       </c>
     </row>
     <row r="68" ht="15.5" customHeight="1">
@@ -4301,40 +4301,40 @@
         </is>
       </c>
       <c r="D71" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="E71" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="F71" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="G71" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="I71" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="J71" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="K71" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="L71" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="M71" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="N71" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="O71" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
     </row>
     <row r="72" ht="15.5" customHeight="1">
@@ -4354,40 +4354,40 @@
         </is>
       </c>
       <c r="D72" s="18" t="n">
-        <v>-2757236.409529906</v>
+        <v>-79205846.07306099</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>-4975034.443109888</v>
+        <v>-142915287.6993954</v>
       </c>
       <c r="F72" s="18" t="n">
-        <v>-4925294.534584149</v>
+        <v>-141486145.2583071</v>
       </c>
       <c r="G72" s="18" t="n">
-        <v>-4876051.314384927</v>
+        <v>-140071293.5308704</v>
       </c>
       <c r="H72" s="18" t="n">
-        <v>-4827331.814601715</v>
+        <v>-138670621.6089226</v>
       </c>
       <c r="I72" s="18" t="n">
-        <v>-4779067.23517662</v>
+        <v>-137283924.1315542</v>
       </c>
       <c r="J72" s="18" t="n">
-        <v>-6880317.711167402</v>
+        <v>-197645325.6086904</v>
       </c>
       <c r="K72" s="18" t="n">
-        <v>-8949791.237530693</v>
+        <v>-257093674.0658279</v>
       </c>
       <c r="L72" s="18" t="n">
-        <v>-8860307.392880315</v>
+        <v>-254522751.3928945</v>
       </c>
       <c r="M72" s="18" t="n">
-        <v>-8771717.197973438</v>
+        <v>-251977536.7579874</v>
       </c>
       <c r="N72" s="18" t="n">
-        <v>-8684011.791200342</v>
+        <v>-249457773.1556144</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>-5341644.365568296</v>
+        <v>-153442754.7918278</v>
       </c>
     </row>
     <row r="73" ht="15.5" customHeight="1">
@@ -4407,40 +4407,40 @@
         </is>
       </c>
       <c r="D73" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="E73" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="F73" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="G73" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="I73" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="J73" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="K73" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="N73" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="O73" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
     </row>
     <row r="74" ht="15.5" customHeight="1">
@@ -4460,40 +4460,40 @@
         </is>
       </c>
       <c r="D74" s="18" t="n">
-        <v>-10367025.86427389</v>
+        <v>-2435870683.246518</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>-12584823.89785387</v>
+        <v>-2499580124.872852</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>-12535083.98932813</v>
+        <v>-2498150982.431764</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>-12485840.76912891</v>
+        <v>-2496736130.704328</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>-12437121.2693457</v>
+        <v>-2495335458.78238</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>-12388856.6899206</v>
+        <v>-2493948761.305011</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>-14490107.16591138</v>
+        <v>-2554310162.782147</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>-16559580.69227467</v>
+        <v>-2613758511.239285</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>-16470096.8476243</v>
+        <v>-2611187588.566351</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>-16381506.65271742</v>
+        <v>-2608642373.931444</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>-16293801.24594432</v>
+        <v>-2606122610.329071</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>-12951433.82031228</v>
+        <v>-2510107591.965285</v>
       </c>
     </row>
     <row r="75" ht="15.5" customHeight="1">
@@ -4513,40 +4513,40 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>-7609789.454743981</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-7609789.454743982</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>-7609789.454743982</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>-7609789.45474398</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>-7609789.454743982</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>-7609789.45474398</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>-7609789.454743982</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>-7609789.454743981</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>-7609789.454743981</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>-7609789.454743981</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>-7609789.454743981</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>-7609789.45474398</v>
+        <v>-2356664837.173457</v>
       </c>
     </row>
     <row r="76" ht="15.5" customHeight="1">
@@ -4569,37 +4569,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>-7609789.454743981</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>-7928247.609966066</v>
+        <v>-2498015158.138238</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>-7934960.746262733</v>
+        <v>-2505624947.592983</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>-7938026.818225207</v>
+        <v>-2505943405.748205</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>-7938916.820679809</v>
+        <v>-2505950118.884501</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>-7939859.671312776</v>
+        <v>-2505953184.956463</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>-7939762.447665521</v>
+        <v>-2505954074.958919</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>-7939637.96626534</v>
+        <v>-2505955017.809551</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>-7942563.876742985</v>
+        <v>-2505954920.585904</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>-7946460.929607455</v>
+        <v>-2505954796.104504</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>-7948293.379302839</v>
+        <v>-2505957722.014981</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -4619,40 +4619,40 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>-7609789.454743981</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-7609789.454743982</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>-7609789.454743982</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>-7609789.45474398</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>-7609789.454743982</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>-7609789.45474398</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>-7609789.454743982</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>-7609789.454743981</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>-7609789.454743981</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>-7609789.454743981</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>-7609789.454743981</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>-7609789.45474398</v>
+        <v>-2356664837.173457</v>
       </c>
     </row>
     <row r="78" ht="15.5" customHeight="1">
@@ -4672,40 +4672,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>-7609789.454743981</v>
+        <v>-2356664837.173457</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>-7928247.609966066</v>
+        <v>-2498015158.138238</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>-7934960.746262733</v>
+        <v>-2505624947.592983</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>-7938026.818225207</v>
+        <v>-2505943405.748205</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>-7938916.820679809</v>
+        <v>-2505950118.884501</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>-7939859.671312776</v>
+        <v>-2505953184.956463</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>-7939762.447665521</v>
+        <v>-2505954074.958919</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>-7939637.96626534</v>
+        <v>-2505955017.809551</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>-7942563.876742985</v>
+        <v>-2505954920.585904</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>-7946460.929607455</v>
+        <v>-2505954796.104504</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>-7948293.379302839</v>
+        <v>-2505957722.014981</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>-7949099.748844936</v>
+        <v>-2505961619.067846</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -4831,40 +4831,40 @@
         </is>
       </c>
       <c r="D81" s="18" t="n">
-        <v>-0.002215821035080548</v>
+        <v>-7.713602588961635e-05</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>-0.002215821035080548</v>
+        <v>-7.713602588961638e-05</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>-0.002215821035080548</v>
+        <v>-7.713602588961638e-05</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>-0.002215821035080547</v>
+        <v>-7.713602588961638e-05</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>-0.002215821035080548</v>
+        <v>-7.713602588961639e-05</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>-0.002215821035080548</v>
+        <v>-7.713602588961638e-05</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>-0.002215821035080548</v>
+        <v>-7.713602588961638e-05</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>-0.002215821035080548</v>
+        <v>-7.713602588961634e-05</v>
       </c>
       <c r="L81" s="18" t="n">
-        <v>-0.002215821035080547</v>
+        <v>-7.713602588961641e-05</v>
       </c>
       <c r="M81" s="18" t="n">
-        <v>-0.002215821035080548</v>
+        <v>-7.713602588961639e-05</v>
       </c>
       <c r="N81" s="18" t="n">
-        <v>-0.002215821035080547</v>
+        <v>-7.713602588961635e-05</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>-0.002215821035080547</v>
+        <v>-7.713602588961638e-05</v>
       </c>
     </row>
     <row r="82" ht="15.5" customHeight="1">
@@ -5653,37 +5653,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>308696.217715634</v>
+        <v>-764525900.5530885</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>3147680.801105952</v>
+        <v>-730488948.8395859</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>3171599.760695905</v>
+        <v>-727228812.7182935</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>3105404.320405772</v>
+        <v>-726345034.9893652</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>3039803.634937002</v>
+        <v>-728256715.4735849</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>2974861.436564016</v>
+        <v>-730239151.5494022</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>5716138.742694573</v>
+        <v>-651604407.5185683</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>8508753.224930426</v>
+        <v>-569492103.0875134</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>8481540.1778911</v>
+        <v>-565612222.416002</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>8362314.264539823</v>
+        <v>-566336896.0130259</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>8244575.768517966</v>
+        <v>-569846228.9102314</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -5703,40 +5703,40 @@
         </is>
       </c>
       <c r="D97" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="E97" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="F97" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="G97" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="H97" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="I97" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="J97" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="K97" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="N97" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
       <c r="O97" s="19" t="n">
-        <v>-3291043.585406549</v>
+        <v>-867933547.4169319</v>
       </c>
     </row>
     <row r="98" ht="15.5" customHeight="1">
@@ -5756,40 +5756,40 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>842503.3935922775</v>
+        <v>24201800.79078234</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>1520179.209082501</v>
+        <v>43668589.92628086</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>1504985.660663945</v>
+        <v>43231912.2706904</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>1489943.450672292</v>
+        <v>42799600.79459841</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>1475077.024489895</v>
+        <v>42371637.79497682</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>1460337.701130068</v>
+        <v>41947932.86391211</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>2102401.815293277</v>
+        <v>60391709.78398089</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>2734758.437187919</v>
+        <v>78556500.41250098</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>2707421.139762964</v>
+        <v>77770945.69532287</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>2680355.998986054</v>
+        <v>76993245.30899033</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>2653560.376761975</v>
+        <v>76223320.79366626</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>1632269.772203585</v>
+        <v>46885386.846894</v>
       </c>
     </row>
     <row r="99" ht="15.5" customHeight="1">
@@ -5809,40 +5809,40 @@
         </is>
       </c>
       <c r="D99" s="20" t="n">
-        <v>2757236.409529906</v>
+        <v>79205846.07306099</v>
       </c>
       <c r="E99" s="20" t="n">
-        <v>4975034.443109888</v>
+        <v>142915287.6993954</v>
       </c>
       <c r="F99" s="20" t="n">
-        <v>4925294.534584149</v>
+        <v>141486145.2583071</v>
       </c>
       <c r="G99" s="20" t="n">
-        <v>4876051.314384927</v>
+        <v>140071293.5308704</v>
       </c>
       <c r="H99" s="20" t="n">
-        <v>4827331.814601715</v>
+        <v>138670621.6089226</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>4779067.23517662</v>
+        <v>137283924.1315542</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>6880317.711167402</v>
+        <v>197645325.6086904</v>
       </c>
       <c r="K99" s="20" t="n">
-        <v>8949791.237530693</v>
+        <v>257093674.0658279</v>
       </c>
       <c r="L99" s="20" t="n">
-        <v>8860307.392880315</v>
+        <v>254522751.3928945</v>
       </c>
       <c r="M99" s="20" t="n">
-        <v>8771717.197973438</v>
+        <v>251977536.7579874</v>
       </c>
       <c r="N99" s="20" t="n">
-        <v>8684011.791200342</v>
+        <v>249457773.1556144</v>
       </c>
       <c r="O99" s="20" t="n">
-        <v>5341644.365568296</v>
+        <v>153442754.7918278</v>
       </c>
     </row>
     <row r="100" ht="15.5" customHeight="1">
@@ -5862,40 +5862,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>308696.217715634</v>
+        <v>-764525900.5530885</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>3147680.801105952</v>
+        <v>-730488948.8395859</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>3171599.760695905</v>
+        <v>-727228812.7182935</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>3105404.320405772</v>
+        <v>-726345034.9893652</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>3039803.634937002</v>
+        <v>-728256715.4735849</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>2974861.436564016</v>
+        <v>-730239151.5494022</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>5716138.742694573</v>
+        <v>-651604407.5185683</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>8508753.224930426</v>
+        <v>-569492103.0875134</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>8481540.1778911</v>
+        <v>-565612222.416002</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>8362314.264539823</v>
+        <v>-566336896.0130259</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>8244575.768517966</v>
+        <v>-569846228.9102314</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>3877239.717566536</v>
+        <v>-695508916.795956</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -5968,40 +5968,40 @@
         </is>
       </c>
       <c r="D102" s="18" t="n">
-        <v>4512999.85047596</v>
+        <v>129641109.7754797</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>4512999.85047596</v>
+        <v>129641109.7754797</v>
       </c>
       <c r="F102" s="18" t="n">
-        <v>4512999.850475959</v>
+        <v>129641109.7754797</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>4512999.850475961</v>
+        <v>129641109.7754797</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>4512999.85047596</v>
+        <v>129641109.7754797</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>4512999.850475961</v>
+        <v>129641109.7754797</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>4512999.85047596</v>
+        <v>129641109.7754797</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>4512999.85047596</v>
+        <v>129641109.7754797</v>
       </c>
       <c r="L102" s="18" t="n">
-        <v>4512999.850475961</v>
+        <v>129641109.7754796</v>
       </c>
       <c r="M102" s="18" t="n">
-        <v>4512999.85047596</v>
+        <v>129641109.7754796</v>
       </c>
       <c r="N102" s="18" t="n">
-        <v>4512999.850475961</v>
+        <v>129641109.7754797</v>
       </c>
       <c r="O102" s="18" t="n">
-        <v>4512999.850475961</v>
+        <v>129641109.7754797</v>
       </c>
     </row>
     <row r="103" ht="15.5" customHeight="1">
@@ -6024,37 +6024,37 @@
         <v>0</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>-4255390.724430324</v>
+        <v>-1485545646.953663</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>-4349267.896404509</v>
+        <v>-1567290561.458876</v>
       </c>
       <c r="G103" s="18" t="n">
-        <v>-4348235.339838852</v>
+        <v>-1570063278.78424</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>-4349043.278031831</v>
+        <v>-1570248610.661837</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>-4349209.610948668</v>
+        <v>-1570338118.263839</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>-4350231.024988095</v>
+        <v>-1570428560.959013</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>-4301892.069965376</v>
+        <v>-1568034527.646574</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>-4255796.414535776</v>
+        <v>-1564185333.513483</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>-4259785.470733798</v>
+        <v>-1562803254.106225</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>-4262726.227166624</v>
+        <v>-1562921678.416653</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>-4265155.049027689</v>
+        <v>-1563088542.239052</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -6074,40 +6074,40 @@
         </is>
       </c>
       <c r="D104" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="E104" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="F104" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="G104" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="H104" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="I104" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="J104" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="K104" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="L104" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="M104" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="N104" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
       <c r="O104" s="19" t="n">
-        <v>-4318745.869337432</v>
+        <v>-1488731289.756525</v>
       </c>
     </row>
     <row r="105" ht="15.5" customHeight="1">
@@ -6127,40 +6127,40 @@
         </is>
       </c>
       <c r="D105" s="18" t="n">
-        <v>1914774.054075216</v>
+        <v>55004086.32041625</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>3454927.684233574</v>
+        <v>99246770.22332075</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>3420378.407391245</v>
+        <v>98254302.52108774</v>
       </c>
       <c r="G105" s="18" t="n">
-        <v>3386174.623317326</v>
+        <v>97271759.49587667</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>3352312.87708416</v>
+        <v>96299041.9009181</v>
       </c>
       <c r="I105" s="18" t="n">
-        <v>3318789.748313316</v>
+        <v>95336051.48190886</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>4778005.632218572</v>
+        <v>137253705.561054</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>6215148.589468248</v>
+        <v>178537289.4424525</v>
       </c>
       <c r="L105" s="18" t="n">
-        <v>6152997.103573568</v>
+        <v>176751916.5480278</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>6091467.13253783</v>
+        <v>174984397.3825475</v>
       </c>
       <c r="N105" s="18" t="n">
-        <v>6030552.461212453</v>
+        <v>173234553.4087222</v>
       </c>
       <c r="O105" s="18" t="n">
-        <v>3709422.11862368</v>
+        <v>106557415.4701928</v>
       </c>
     </row>
     <row r="106" ht="15.5" customHeight="1">
@@ -6233,40 +6233,40 @@
         </is>
       </c>
       <c r="D107" s="18" t="n">
-        <v>-4255390.724430324</v>
+        <v>-1485545646.953663</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>-4349267.896404509</v>
+        <v>-1567290561.458876</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>-4348235.339838852</v>
+        <v>-1570063278.78424</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>-4349043.278031831</v>
+        <v>-1570248610.661837</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>-4349209.610948668</v>
+        <v>-1570338118.263839</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>-4350231.024988095</v>
+        <v>-1570428560.959013</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>-4301892.069965376</v>
+        <v>-1568034527.646574</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>-4255796.414535776</v>
+        <v>-1564185333.513483</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>-4259785.470733798</v>
+        <v>-1562803254.106225</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>-4262726.227166624</v>
+        <v>-1562921678.416653</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>-4265155.049027689</v>
+        <v>-1563088542.239052</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>-4341868.210950826</v>
+        <v>-1567014102.474558</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -6675,40 +6675,40 @@
         </is>
       </c>
       <c r="D2" s="18" t="n">
-        <v>229652843.897368</v>
+        <v>11404036525.47465</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>290117136.5731548</v>
+        <v>6365389140.67323</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>287218560.7430964</v>
+        <v>437.364</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>284345097.7206781</v>
+        <v>470.9640000000001</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>281504234.2645646</v>
+        <v>500.3740000000001</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>278687984.4548331</v>
+        <v>525.9160000000001</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>307480284.4769629</v>
+        <v>547.888</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>335832150.0955243</v>
+        <v>578.974</v>
       </c>
       <c r="L2" s="18" t="n">
-        <v>332473163.4620945</v>
+        <v>604.4340000000001</v>
       </c>
       <c r="M2" s="18" t="n">
-        <v>329149078.6022264</v>
+        <v>626.158</v>
       </c>
       <c r="N2" s="18" t="n">
-        <v>325856615.8221337</v>
+        <v>644.4400000000001</v>
       </c>
       <c r="O2" s="18" t="n">
-        <v>223703276.1013565</v>
+        <v>989.3430000000001</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
@@ -6731,37 +6731,37 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>26.3285625597601</v>
+        <v>-44.18301689534184</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>-0.999105349065621</v>
+        <v>-99.99999312902966</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>-1.000444753634322</v>
+        <v>7.682388125222928</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>-0.9990900067861186</v>
+        <v>6.244638656033152</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>-1.000428933898256</v>
+        <v>5.104581772833905</v>
       </c>
       <c r="J3" s="18" t="n">
-        <v>10.33137473739778</v>
+        <v>4.177853497516715</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>9.22071009098655</v>
+        <v>5.673787343398651</v>
       </c>
       <c r="L3" s="18" t="n">
-        <v>-1.000198055032664</v>
+        <v>4.397434081668616</v>
       </c>
       <c r="M3" s="18" t="n">
-        <v>-0.9998054655761757</v>
+        <v>3.594106221688387</v>
       </c>
       <c r="N3" s="18" t="n">
-        <v>-1.000295305116627</v>
+        <v>2.919710360643801</v>
       </c>
       <c r="O3" s="18" t="n">
-        <v>-31.34916854857929</v>
+        <v>53.51980013655266</v>
       </c>
     </row>
     <row r="4" ht="15.5" customHeight="1">
@@ -6887,40 +6887,40 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>229647318.017368</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>290116737.3511548</v>
+        <v>6365388741.45123</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>287218123.3790964</v>
+        <v>0</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>284344626.7566781</v>
+        <v>0</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>281503733.8905646</v>
+        <v>0</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>278687458.5388331</v>
+        <v>0</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>307479736.5889629</v>
+        <v>0</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>335831571.1215243</v>
+        <v>0</v>
       </c>
       <c r="L6" s="18" t="n">
-        <v>332472559.0280945</v>
+        <v>0</v>
       </c>
       <c r="M6" s="18" t="n">
-        <v>329148452.4442264</v>
+        <v>0</v>
       </c>
       <c r="N6" s="18" t="n">
-        <v>325855971.3821337</v>
+        <v>0</v>
       </c>
       <c r="O6" s="18" t="n">
-        <v>223702286.7583565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="15.5" customHeight="1">
@@ -6943,37 +6943,37 @@
         <v>0</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>26.33142849472054</v>
+        <v>-44.18299334965431</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>-0.9991198710296967</v>
+        <v>-100</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>-1.00045797549676</v>
+        <v>0</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>-0.9991020046756782</v>
+        <v>0</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>-1.000439785578922</v>
+        <v>0</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>10.33138634981585</v>
+        <v>0</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>9.220716411131203</v>
+        <v>0</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>-1.000207360556449</v>
+        <v>0</v>
       </c>
       <c r="M7" s="18" t="n">
-        <v>-0.9998138172922499</v>
+        <v>0</v>
       </c>
       <c r="N7" s="18" t="n">
-        <v>-1.000302762368488</v>
+        <v>0</v>
       </c>
       <c r="O7" s="18" t="n">
-        <v>-31.34933639254406</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="15.5" customHeight="1">
@@ -6993,40 +6993,40 @@
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>-99.99759381163925</v>
+        <v>-99.9999515445256</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-99.99986239282356</v>
+        <v>-99.99999372823891</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>-99.99984772432572</v>
+        <v>-0</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>-99.99983436886946</v>
+        <v>-0</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>-99.99982224992057</v>
+        <v>-0</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>-99.99981128859895</v>
+        <v>-0</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>-99.99982181361614</v>
+        <v>-0</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>-99.99982760018665</v>
+        <v>-0</v>
       </c>
       <c r="L8" s="18" t="n">
-        <v>-99.99981820066508</v>
+        <v>-0</v>
       </c>
       <c r="M8" s="18" t="n">
-        <v>-99.99980976462014</v>
+        <v>-0</v>
       </c>
       <c r="N8" s="18" t="n">
-        <v>-99.99980223203437</v>
+        <v>-0</v>
       </c>
       <c r="O8" s="18" t="n">
-        <v>-99.99955774317783</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9" ht="15.5" customHeight="1">
@@ -7311,40 +7311,40 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>4.932087774678509e-05</v>
+        <v>9.932167274948448e-07</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>4.809728391458859e-05</v>
+        <v>2.192143477463922e-06</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>5.865387652452504e-05</v>
+        <v>38.5182182287005</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>6.924971465962382e-05</v>
+        <v>41.80960090796708</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>7.988548263427168e-05</v>
+        <v>44.94258618116812</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>9.056517867330019e-05</v>
+        <v>47.99136574330096</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>9.113881779102203e-05</v>
+        <v>51.14802591273679</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>8.984230432265483e-05</v>
+        <v>52.11276193786524</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>9.561755138978217e-05</v>
+        <v>52.59510516129183</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>0.0001014267618249157</v>
+        <v>53.3164555915256</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>0.0001072773460099995</v>
+        <v>54.24404587734858</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>0.0001616379411983629</v>
+        <v>36.54843364571459</v>
       </c>
     </row>
     <row r="15" ht="15.5" customHeight="1">
@@ -7470,40 +7470,40 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>8.02062786918142e-05</v>
+        <v>1.615182480243184e-06</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>6.880358821881136e-05</v>
+        <v>3.13588055009137e-06</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>7.613783713497571e-05</v>
+        <v>50</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>8.281556527178888e-05</v>
+        <v>50</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>0.0001777500794285518</v>
+        <v>100</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>0.0001887114010418469</v>
+        <v>100</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>0.000178186383862621</v>
+        <v>100</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>0.0001723998133696599</v>
+        <v>100</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>0.0001817993349315582</v>
+        <v>100</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>0.000190235379864668</v>
+        <v>100</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>0.000197767965635463</v>
+        <v>100</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>0.000294837881453807</v>
+        <v>66.66666666666667</v>
       </c>
     </row>
     <row r="18" ht="15.5" customHeight="1">
@@ -7629,40 +7629,40 @@
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>4.543164406614517e-05</v>
+        <v>9.148959001855677e-07</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>4.112780542018968e-05</v>
+        <v>1.874493589999329e-06</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>4.772323893183307e-05</v>
+        <v>31.34002798584245</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>5.431779947608646e-05</v>
+        <v>32.79443864074536</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>6.091205002580824e-05</v>
+        <v>34.26836726128855</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>6.750918966529457e-05</v>
+        <v>35.77377375854699</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>6.649206805170556e-05</v>
+        <v>37.31602079257074</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>6.364191157374496e-05</v>
+        <v>36.91530189611278</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>6.551807000953175e-05</v>
+        <v>36.03867419767914</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>6.738891718668771e-05</v>
+        <v>35.42396647491528</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>6.926119933611916e-05</v>
+        <v>35.02144501187077</v>
       </c>
       <c r="O20" s="18" t="n">
-        <v>0.0001025778450808341</v>
+        <v>23.194180380313</v>
       </c>
     </row>
     <row r="21" ht="15.5" customHeight="1">
@@ -7841,40 +7841,40 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>-229653408.7224307</v>
+        <v>-11404037090.29971</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>-290117475.4640662</v>
+        <v>-6365389479.564141</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>-287218938.3632964</v>
+        <v>-814.9842</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>-284345511.2008781</v>
+        <v>-884.4442000000001</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>-281504931.1272646</v>
+        <v>-1197.2367</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>-278688724.8066331</v>
+        <v>-1266.2678</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>-307481064.2093629</v>
+        <v>-1327.6204</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>-335832971.7482243</v>
+        <v>-1400.6267</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>-332474015.9477945</v>
+        <v>-1456.9197</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>-329149957.8781264</v>
+        <v>-1505.4339</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>-325857518.176334</v>
+        <v>-1546.7942002345</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>-223704214.6005065</v>
+        <v>-1927.84215</v>
       </c>
     </row>
     <row r="25" ht="15.5" customHeight="1">
@@ -7894,40 +7894,40 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>-459300726.7397987</v>
+        <v>-22808068089.89436</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>-580234212.8152211</v>
+        <v>-12730778221.01537</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>-574437061.7423928</v>
+        <v>-814.9842</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>-568690137.9575562</v>
+        <v>-884.4442000000001</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>-563008665.0178292</v>
+        <v>-1197.2367</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>-557376183.3454663</v>
+        <v>-1266.2678</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>-614960800.7983258</v>
+        <v>-1327.6204</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>-671664542.8697486</v>
+        <v>-1400.6267</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>-664946574.975889</v>
+        <v>-1456.9197</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>-658298410.3223529</v>
+        <v>-1505.4339</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>-651713489.5584676</v>
+        <v>-1546.7942002345</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>-447406501.3588631</v>
+        <v>-1927.84215</v>
       </c>
     </row>
     <row r="26" ht="15.5" customHeight="1">
@@ -7947,40 +7947,40 @@
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>-100.0002459473408</v>
+        <v>-100.0000049528521</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>-100.0001168117524</v>
+        <v>-100.0000053239622</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>-100.0001314748598</v>
+        <v>-186.3400279858424</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>-100.0001454149213</v>
+        <v>-187.7944386407454</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>-100.0002475496334</v>
+        <v>-239.2683672612885</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>-100.0002656561607</v>
+        <v>-240.773773758547</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>-100.0002535877711</v>
+        <v>-242.3160207925708</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>-100.0002446617156</v>
+        <v>-241.9153018961127</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>-100.0002564073717</v>
+        <v>-241.0386741976791</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>-100.000267136066</v>
+        <v>-240.4239664749153</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>-100.0002769175633</v>
+        <v>-240.0214450118708</v>
       </c>
       <c r="O26" s="18" t="n">
-        <v>-100.0004195285676</v>
+        <v>-194.8608470469796</v>
       </c>
     </row>
     <row r="27" ht="15.5" customHeight="1">
@@ -8000,40 +8000,40 @@
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>-199.99783975898</v>
+        <v>-199.9999564973777</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>-199.9999792045761</v>
+        <v>-199.9999990522011</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>-199.9999791991855</v>
+        <v>-186.3400279858424</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>-199.9999797837908</v>
+        <v>-187.7944386407454</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>-200.000069799554</v>
+        <v>-239.2683672612885</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>-200.0000769447597</v>
+        <v>-240.773773758547</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>-200.0000754013873</v>
+        <v>-242.3160207925708</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>-200.0000722619022</v>
+        <v>-241.9153018961127</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>-200.0000746080368</v>
+        <v>-241.0386741976791</v>
       </c>
       <c r="M27" s="18" t="n">
-        <v>-200.0000769006862</v>
+        <v>-240.4239664749153</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>-200.0000791495976</v>
+        <v>-240.0214450118708</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>-199.9999772717455</v>
+        <v>-194.8608470469796</v>
       </c>
     </row>
     <row r="28" ht="15.5" customHeight="1">
@@ -8106,40 +8106,40 @@
         </is>
       </c>
       <c r="D29" s="19" t="n">
-        <v>3.889233680639917e-06</v>
+        <v>7.832082730927681e-08</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>6.9694784943989e-06</v>
+        <v>3.176498874645925e-07</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>1.093063759269196e-05</v>
+        <v>7.178190242858054</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>1.493191518353735e-05</v>
+        <v>9.01516226722171</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>1.897343260846343e-05</v>
+        <v>10.67421891987956</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>2.30559890080056e-05</v>
+        <v>12.21759198475397</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>2.464674973931648e-05</v>
+        <v>13.83200512016606</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>2.620039274890987e-05</v>
+        <v>15.19746004175246</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>3.009948138025043e-05</v>
+        <v>16.55643096361269</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>3.403784463822802e-05</v>
+        <v>17.89248911661032</v>
       </c>
       <c r="N29" s="19" t="n">
-        <v>3.801614667388036e-05</v>
+        <v>19.22260086547781</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>5.906009611752884e-05</v>
+        <v>13.35425326540159</v>
       </c>
     </row>
     <row r="30" ht="15.5" customHeight="1">
@@ -8159,40 +8159,40 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>-229653417.6541664</v>
+        <v>-11404037099.23145</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>-290117495.6837177</v>
+        <v>-6365389499.783792</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-287218969.7581164</v>
+        <v>-846.3790199737737</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>-284345553.6590469</v>
+        <v>-926.9023688201981</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>-281504984.5382808</v>
+        <v>-1250.647716178158</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>-278688789.0609042</v>
+        <v>-1330.522071062539</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>-307481139.9932591</v>
+        <v>-1403.404296212776</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>-335833059.7375666</v>
+        <v>-1488.616042302136</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>-332474116.0204924</v>
+        <v>-1556.992397930603</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>-329150069.9133784</v>
+        <v>-1617.469152002785</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>-325857642.054463</v>
+        <v>-1670.672329251985</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>-223704346.7198764</v>
+        <v>-2059.961519883522</v>
       </c>
     </row>
     <row r="31" ht="15.5" customHeight="1">
@@ -8212,40 +8212,40 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>-100.0002498365745</v>
+        <v>-100.0000050311729</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>-100.000123781231</v>
+        <v>-100.0000056416121</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>-100.0001424054974</v>
+        <v>-193.5182182287005</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>-100.0001603468365</v>
+        <v>-196.8096009079671</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>-100.000266523066</v>
+        <v>-249.9425861811681</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>-100.0002887121498</v>
+        <v>-252.991365743301</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>-100.0002782345208</v>
+        <v>-256.1480259127368</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>-100.0002708621084</v>
+        <v>-257.1127619378652</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>-100.0002865068531</v>
+        <v>-257.5951051612918</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>-100.0003011739107</v>
+        <v>-258.3164555915256</v>
       </c>
       <c r="N31" s="19" t="n">
-        <v>-100.0003149337099</v>
+        <v>-259.2440458773486</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>-100.0004785886638</v>
+        <v>-208.2151003123813</v>
       </c>
     </row>
     <row r="32" ht="15.5" customHeight="1">
@@ -8318,40 +8318,40 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>-229653417.6541664</v>
+        <v>-11404037099.23145</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>-290117495.6837177</v>
+        <v>-6365389499.783792</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>-287218969.7581164</v>
+        <v>-846.3790199737737</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>-284345553.6590469</v>
+        <v>-926.9023688201981</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>-281504984.5382808</v>
+        <v>-1250.647716178158</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>-278688789.0609042</v>
+        <v>-1330.522071062539</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>-307481139.9932591</v>
+        <v>-1403.404296212776</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>-335833059.7375666</v>
+        <v>-1488.616042302136</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>-332474116.0204924</v>
+        <v>-1556.992397930603</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>-329150069.9133784</v>
+        <v>-1617.469152002785</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>-325857642.054463</v>
+        <v>-1670.672329251985</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>-223704346.7198764</v>
+        <v>-2059.961519883522</v>
       </c>
     </row>
     <row r="34" ht="15.5" customHeight="1">
@@ -8371,40 +8371,40 @@
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>-459300735.6715345</v>
+        <v>-22808068098.8261</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>-580234233.0348725</v>
+        <v>-12730778241.23502</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-574437093.1372128</v>
+        <v>-846.3790199737737</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>-568690180.415725</v>
+        <v>-926.9023688201981</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>-563008718.4288454</v>
+        <v>-1250.647716178158</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>-557376247.5997374</v>
+        <v>-1330.522071062539</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>-614960876.582222</v>
+        <v>-1403.404296212776</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>-671664630.859091</v>
+        <v>-1488.616042302136</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>-664946675.0485868</v>
+        <v>-1556.992397930603</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>-658298522.3576049</v>
+        <v>-1617.469152002785</v>
       </c>
       <c r="N34" s="19" t="n">
-        <v>-651713613.4365966</v>
+        <v>-1670.672329251985</v>
       </c>
       <c r="O34" s="19" t="n">
-        <v>-447406633.478233</v>
+        <v>-2059.961519883522</v>
       </c>
     </row>
     <row r="35" ht="15.5" customHeight="1">
@@ -8530,40 +8530,40 @@
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>-459300735.6715345</v>
+        <v>-22808068098.8261</v>
       </c>
       <c r="E37" s="19" t="n">
-        <v>-618513263.9445796</v>
+        <v>-19742826250.21725</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>-625982481.1198653</v>
+        <v>-4373214239.247481</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>-620856750.7252771</v>
+        <v>-3114215154.647815</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>-614746986.2063509</v>
+        <v>-2452968500.227537</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>-608624830.7316256</v>
+        <v>-2058703204.852578</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>-665703878.0007443</v>
+        <v>-1798005452.936255</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>-727158594.0642114</v>
+        <v>-1709221542.357202</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>-725562400.559692</v>
+        <v>-1691868235.648214</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>-718781305.1302665</v>
+        <v>-1614502332.227269</v>
       </c>
       <c r="N37" s="19" t="n">
-        <v>-711631365.9192364</v>
+        <v>-1506232534.199242</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>-506731148.2315705</v>
+        <v>-1414916209.063952</v>
       </c>
     </row>
     <row r="38" ht="15.5" customHeight="1">
@@ -8583,40 +8583,40 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>-229653417.6541664</v>
+        <v>-11404037099.23145</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>-290117495.6837177</v>
+        <v>-6365389499.783792</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-287218969.7581164</v>
+        <v>-846.3790199737737</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>-284345553.6590469</v>
+        <v>-926.9023688201981</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>-281504984.5382808</v>
+        <v>-1250.647716178158</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>-278688789.0609042</v>
+        <v>-1330.522071062539</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>-307481139.9932591</v>
+        <v>-1403.404296212776</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>-335833059.7375666</v>
+        <v>-1488.616042302136</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>-332474116.0204924</v>
+        <v>-1556.992397930603</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>-329150069.9133784</v>
+        <v>-1617.469152002785</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>-325857642.054463</v>
+        <v>-1670.672329251985</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>-223704346.7198764</v>
+        <v>-2059.961519883522</v>
       </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
@@ -8636,40 +8636,40 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>-100.0002498365745</v>
+        <v>-100.0000050311729</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>-100.000123781231</v>
+        <v>-100.0000056416121</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>-100.0001424054974</v>
+        <v>-193.5182182287005</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>-100.0001603468365</v>
+        <v>-196.8096009079671</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>-100.000266523066</v>
+        <v>-249.9425861811681</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>-100.0002887121498</v>
+        <v>-252.991365743301</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>-100.0002782345208</v>
+        <v>-256.1480259127368</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>-100.0002708621084</v>
+        <v>-257.1127619378652</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>-100.0002865068531</v>
+        <v>-257.5951051612918</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>-100.0003011739107</v>
+        <v>-258.3164555915256</v>
       </c>
       <c r="N39" s="19" t="n">
-        <v>-100.0003149337099</v>
+        <v>-259.2440458773486</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>-100.0004785886638</v>
+        <v>-208.2151003123813</v>
       </c>
     </row>
     <row r="40" ht="15.5" customHeight="1">
@@ -8848,40 +8848,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>-50266242.13656235</v>
+        <v>-6842424539.638599</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>-175394796.3231033</v>
+        <v>1131245869.382056</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>-180025398.6897788</v>
+        <v>16909891877.35421</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>-174664855.479233</v>
+        <v>18202975389.95265</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>-168537268.9977562</v>
+        <v>18867060667.60071</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>-162397257.7515707</v>
+        <v>19261560803.45984</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>-219476557.0195454</v>
+        <v>19522276385.4367</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>-280931357.834957</v>
+        <v>19611078101.06219</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>-279335315.3825813</v>
+        <v>19628431146.757</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>-272554376.7594017</v>
+        <v>19705796997.67352</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>-265404610.1645752</v>
+        <v>19814066676.98817</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>-60504197.75087576</v>
+        <v>19905383028.76796</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -8901,40 +8901,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>-50266702.88239282</v>
+        <v>-6842425000.38443</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>-175394835.7352284</v>
+        <v>1131245829.96993</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>-180025441.3453405</v>
+        <v>16909891834.69865</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>-174664900.8487673</v>
+        <v>18202975344.58311</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>-168537337.1575918</v>
+        <v>18867060599.44088</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>-162397328.7399543</v>
+        <v>19261560732.47146</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>-219476630.2792167</v>
+        <v>19522276312.17703</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>-280931435.4419159</v>
+        <v>19611078023.45523</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>-279335396.8377594</v>
+        <v>19628431065.30182</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>-272554461.4585249</v>
+        <v>19705796912.97439</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>-265404697.5498739</v>
+        <v>19814066589.60287</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>-60504314.41676617</v>
+        <v>19905382912.10207</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -9060,40 +9060,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>-50265954.27354674</v>
+        <v>-6842424251.775584</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>-175394153.73469</v>
+        <v>1131246511.970469</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>-180024416.2972869</v>
+        <v>16909892859.7467</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>-174663548.0597003</v>
+        <v>18202976697.37218</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>-168535651.1755821</v>
+        <v>18867062285.42289</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>-162395344.0097468</v>
+        <v>19261562717.20166</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>-219474321.6767374</v>
+        <v>19522278620.77951</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>-280928776.4548782</v>
+        <v>19611080682.44227</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>-279332404.3897534</v>
+        <v>19628434057.74983</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>-272551152.4124333</v>
+        <v>19705800222.02048</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>-265401088.5615252</v>
+        <v>19814070198.59122</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>-60500519.15576524</v>
+        <v>19905386707.36307</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -9113,40 +9113,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>-112786465.1456</v>
+        <v>-6842424699.393587</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>-402903960.8293177</v>
+        <v>-13207814199.17738</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>-479612078.2065203</v>
+        <v>-5309805000.634465</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>-480473693.8846037</v>
+        <v>2375000501.137561</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>-475070723.0177279</v>
+        <v>3004499256.240862</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>-469200270.6047463</v>
+        <v>3335121878.252787</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>-494932209.060774</v>
+        <v>3532253787.797006</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>-551824354.1417892</v>
+        <v>3662601876.841274</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>-579190196.3677251</v>
+        <v>3706993019.446423</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>-575068307.161132</v>
+        <v>3715668833.827964</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>-568385566.2933545</v>
+        <v>3754354239.997428</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>-462657548.2934567</v>
+        <v>3808488439.229504</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -9166,40 +9166,40 @@
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
     </row>
     <row r="50" ht="15.5" customHeight="1">
@@ -9219,40 +9219,40 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>-229653417.6541664</v>
+        <v>-11404037099.23145</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>-290117495.6837177</v>
+        <v>-6365389499.783792</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>-287218969.7581164</v>
+        <v>-846.3790199737737</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>-284345553.6590469</v>
+        <v>-926.9023688201981</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>-281504984.5382808</v>
+        <v>-1250.647716178158</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>-278688789.0609042</v>
+        <v>-1330.522071062539</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>-307481139.9932591</v>
+        <v>-1403.404296212776</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>-335833059.7375666</v>
+        <v>-1488.616042302136</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>-332474116.0204924</v>
+        <v>-1556.992397930603</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>-329150069.9133784</v>
+        <v>-1617.469152002785</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>-325857642.054463</v>
+        <v>-1670.672329251985</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>-223704346.7198764</v>
+        <v>-2059.961519883522</v>
       </c>
     </row>
     <row r="51" ht="15.5" customHeight="1">
@@ -9275,37 +9275,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>-229653417.6541664</v>
+        <v>-11404037099.23145</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>-309260060.9569704</v>
+        <v>-9871416554.093306</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>-312995092.7341233</v>
+        <v>-2186610971.797931</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>-310432690.9880135</v>
+        <v>-1557111892.949282</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>-307378434.0524086</v>
+        <v>-1226489191.063002</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>-304318021.5760814</v>
+        <v>-1029357208.636558</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>-332858246.9127889</v>
+        <v>-899009034.3805442</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>-363583032.8557992</v>
+        <v>-854617823.3990391</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>-362785189.75632</v>
+        <v>-845941948.5407437</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>-359394876.747458</v>
+        <v>-807256489.168103</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>-355820154.0821467</v>
+        <v>-753121900.6468358</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -9325,40 +9325,40 @@
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>273030915.6349618</v>
+        <v>7898010044.921936</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>290744366.4194118</v>
+        <v>12723448686.81781</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>292462021.0070488</v>
+        <v>13645116073.84025</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>292844589.3197446</v>
+        <v>14000086276.52888</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>293103021.481392</v>
+        <v>14199247412.03898</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>293369442.114091</v>
+        <v>14329764943.29478</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>290991661.8628128</v>
+        <v>14374170607.4073</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>288431145.85156</v>
+        <v>14382861003.77298</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>288497972.5274707</v>
+        <v>14421541763.1579</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>288780832.9558733</v>
+        <v>14475677118.34179</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>289077661.8328309</v>
+        <v>14521335887.70069</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>297613757.0963305</v>
+        <v>14649273739.20915</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -9378,40 +9378,40 @@
         </is>
       </c>
       <c r="D53" s="18" t="n">
-        <v>273030915.6349618</v>
+        <v>7898010044.921936</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>290744366.4194118</v>
+        <v>12723448686.81781</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>292462021.0070488</v>
+        <v>13645116073.84025</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>292844589.3197446</v>
+        <v>14000086276.52888</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>293103021.481392</v>
+        <v>14199247412.03898</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>293369442.114091</v>
+        <v>14329764943.29478</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>290991661.8628128</v>
+        <v>14374170607.4073</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>288431145.85156</v>
+        <v>14382861003.77298</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>288497972.5274707</v>
+        <v>14421541763.1579</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>288780832.9558733</v>
+        <v>14475677118.34179</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>289077661.8328309</v>
+        <v>14521335887.70069</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>297613757.0963305</v>
+        <v>14649273739.20915</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -9643,40 +9643,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>160244443.9254492</v>
+        <v>1055585338.964436</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>-112159601.0092639</v>
+        <v>-484365518.9589237</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>-187150063.9073071</v>
+        <v>8335311066.497948</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>-187629111.2250235</v>
+        <v>16375086771.00628</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>-181967728.5695413</v>
+        <v>17203746641.24663</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>-175830856.2530663</v>
+        <v>17664886793.78515</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>-203940575.4257421</v>
+        <v>17906424366.97653</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>-263393238.310284</v>
+        <v>18045462850.5942</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>-290692255.6159257</v>
+        <v>18128534750.82865</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>-286287507.4393408</v>
+        <v>18191345918.93568</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>-279307938.878151</v>
+        <v>18275690093.28049</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>-165043826.5471535</v>
+        <v>18457762143.08863</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -9696,40 +9696,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>-210510398.1989959</v>
+        <v>-7898009590.740021</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>-63234552.72542617</v>
+        <v>1615612030.929392</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>7125647.610020161</v>
+        <v>8574581793.248755</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>12965563.16532323</v>
+        <v>1827889926.365898</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>13432077.39395919</v>
+        <v>1663315644.176254</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>13435512.24331951</v>
+        <v>1596675923.416512</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>-15533746.25099534</v>
+        <v>1615854253.802979</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>-17535538.14459416</v>
+        <v>1565617831.848072</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>11359851.22617227</v>
+        <v>1499899306.921181</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>13736355.02690756</v>
+        <v>1514454303.084808</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>13906850.31662583</v>
+        <v>1538380105.310726</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>104543307.3913883</v>
+        <v>1447624564.274445</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -9802,40 +9802,40 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>-459300726.7397987</v>
+        <v>-22808068089.89436</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>-580234212.8152211</v>
+        <v>-12730778221.01537</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>-574437061.7423928</v>
+        <v>-814.9842</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>-568690137.9575562</v>
+        <v>-884.4442000000001</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>-563008665.0178292</v>
+        <v>-1197.2367</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>-557376183.3454663</v>
+        <v>-1266.2678</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>-614960800.7983258</v>
+        <v>-1327.6204</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>-671664542.8697486</v>
+        <v>-1400.6267</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>-664946574.975889</v>
+        <v>-1456.9197</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>-658298410.3223529</v>
+        <v>-1505.4339</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>-651713489.5584676</v>
+        <v>-1546.7942002345</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>-447406501.3588631</v>
+        <v>-1927.84215</v>
       </c>
     </row>
     <row r="62" ht="15.5" customHeight="1">
@@ -9961,40 +9961,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>-459300739.867624</v>
+        <v>-22808068103.02219</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>-580234212.8861117</v>
+        <v>-12730778221.08626</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>-574437061.9593481</v>
+        <v>-815.2011553019889</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>-568690137.8622137</v>
+        <v>-884.3488575342467</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>-563008705.7639114</v>
+        <v>-1237.982782191781</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>-557376184.8038772</v>
+        <v>-1267.726210958904</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>-614960801.7290655</v>
+        <v>-1328.551139726027</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>-671664546.4542966</v>
+        <v>-1404.211247945206</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>-664946578.4871218</v>
+        <v>-1460.430932876712</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>-658298413.2391748</v>
+        <v>-1508.350721917808</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>-651713491.925558</v>
+        <v>-1549.161290606911</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>-447406503.2236632</v>
+        <v>-1929.706950038548</v>
       </c>
     </row>
     <row r="65" ht="15.5" customHeight="1">
@@ -10120,40 +10120,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>-459301036.6623754</v>
+        <v>-22808068399.81694</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>-580234587.8311608</v>
+        <v>-12730778596.03131</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>-574437433.1582466</v>
+        <v>-1186.400053912951</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>-568690505.3474233</v>
+        <v>-1251.8340671591</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>-563009069.5775689</v>
+        <v>-1601.796439720385</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>-557376544.9777982</v>
+        <v>-1627.900131912223</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-614961199.1139458</v>
+        <v>-1725.936019984313</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>-671664980.4809097</v>
+        <v>-1838.237861072821</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>-664947008.1725688</v>
+        <v>-1890.116379873052</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>-658298838.6285673</v>
+        <v>-1933.740114444184</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>-651713913.0597687</v>
+        <v>-1970.295501289023</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>-447406792.3350934</v>
+        <v>-2218.81838034984</v>
       </c>
     </row>
     <row r="68" ht="15.5" customHeight="1">
@@ -10332,40 +10332,40 @@
         </is>
       </c>
       <c r="D71" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="E71" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="F71" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="G71" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="I71" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="J71" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="K71" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="L71" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="M71" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="N71" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="O71" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
     </row>
     <row r="72" ht="15.5" customHeight="1">
@@ -10438,40 +10438,40 @@
         </is>
       </c>
       <c r="D73" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="E73" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="F73" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="G73" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="I73" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="J73" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="K73" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="N73" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="O73" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
     </row>
     <row r="74" ht="15.5" customHeight="1">
@@ -10491,40 +10491,40 @@
         </is>
       </c>
       <c r="D74" s="18" t="n">
-        <v>409034333.7799826</v>
+        <v>15965643399.43251</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>409034333.7799826</v>
+        <v>15965643399.43251</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>409034333.7799826</v>
+        <v>15965643399.43251</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>409034333.7799826</v>
+        <v>15965643399.43251</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>409034333.7799826</v>
+        <v>15965643399.43251</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>409034333.7799826</v>
+        <v>15965643399.43251</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>409034333.7799826</v>
+        <v>15965643399.43251</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>409034333.7799826</v>
+        <v>15965643399.43251</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>409034333.7799826</v>
+        <v>15965643399.43251</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>409034333.7799826</v>
+        <v>15965643399.43251</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>409034333.7799826</v>
+        <v>15965643399.43251</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>409034333.7799826</v>
+        <v>15965643399.43251</v>
       </c>
     </row>
     <row r="75" ht="15.5" customHeight="1">
@@ -10544,40 +10544,40 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>-50266702.88239282</v>
+        <v>-6842425000.38443</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-171200254.0511782</v>
+        <v>3234864803.401199</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>-165403099.3782641</v>
+        <v>15965642213.03246</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>-159656171.5674407</v>
+        <v>15965642147.59844</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>-153974735.7975863</v>
+        <v>15965641797.63607</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>-148342211.1978157</v>
+        <v>15965641771.53238</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>-205926865.3339633</v>
+        <v>15965641673.49649</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>-262630646.7009271</v>
+        <v>15965641561.19465</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>-255912674.3925862</v>
+        <v>15965641509.31613</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>-249264504.8485848</v>
+        <v>15965641465.6924</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>-242679579.2797861</v>
+        <v>15965641429.13701</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>-38372458.55511087</v>
+        <v>15965641180.61413</v>
       </c>
     </row>
     <row r="76" ht="15.5" customHeight="1">
@@ -10600,37 +10600,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>-50266702.88239282</v>
+        <v>-6842425000.38443</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>-175394835.7352284</v>
+        <v>1131245829.96993</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>-180025441.3453405</v>
+        <v>16909891834.69865</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>-174664900.8487673</v>
+        <v>18202975344.58311</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>-168537337.1575918</v>
+        <v>18867060599.44088</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>-162397328.7399543</v>
+        <v>19261560732.47146</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>-219476630.2792167</v>
+        <v>19522276312.17703</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>-280931435.4419159</v>
+        <v>19611078023.45523</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>-279335396.8377594</v>
+        <v>19628431065.30182</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>-272554461.4585249</v>
+        <v>19705796912.97439</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>-265404697.5498739</v>
+        <v>19814066589.60287</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -10650,40 +10650,40 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>-50266702.88239282</v>
+        <v>-6842425000.38443</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-171200254.0511782</v>
+        <v>3234864803.401199</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>-165403099.3782641</v>
+        <v>15965642213.03246</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>-159656171.5674407</v>
+        <v>15965642147.59844</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>-153974735.7975863</v>
+        <v>15965641797.63607</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>-148342211.1978157</v>
+        <v>15965641771.53238</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>-205926865.3339633</v>
+        <v>15965641673.49649</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>-262630646.7009271</v>
+        <v>15965641561.19465</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>-255912674.3925862</v>
+        <v>15965641509.31613</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>-249264504.8485848</v>
+        <v>15965641465.6924</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>-242679579.2797861</v>
+        <v>15965641429.13701</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>-38372458.55511087</v>
+        <v>15965641180.61413</v>
       </c>
     </row>
     <row r="78" ht="15.5" customHeight="1">
@@ -10703,40 +10703,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>-50266702.88239282</v>
+        <v>-6842425000.38443</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>-175394835.7352284</v>
+        <v>1131245829.96993</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>-180025441.3453405</v>
+        <v>16909891834.69865</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>-174664900.8487673</v>
+        <v>18202975344.58311</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>-168537337.1575918</v>
+        <v>18867060599.44088</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>-162397328.7399543</v>
+        <v>19261560732.47146</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>-219476630.2792167</v>
+        <v>19522276312.17703</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>-280931435.4419159</v>
+        <v>19611078023.45523</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>-279335396.8377594</v>
+        <v>19628431065.30182</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>-272554461.4585249</v>
+        <v>19705796912.97439</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>-265404697.5498739</v>
+        <v>19814066589.60287</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>-60504314.41676617</v>
+        <v>19905382912.10207</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -10862,40 +10862,40 @@
         </is>
       </c>
       <c r="D81" s="18" t="n">
-        <v>0.0001292362621478237</v>
+        <v>2.602541220436699e-06</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>0.0001292391940478971</v>
+        <v>5.890371206155771e-06</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>0.0001292391750904226</v>
+        <v>84.87184555906802</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>0.0001292391578299148</v>
+        <v>78.02830144657609</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>0.0001292391421674614</v>
+        <v>72.70834566316478</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>0.0001292391280011182</v>
+        <v>68.48506623744441</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>0.0001292391416035843</v>
+        <v>72.5303128117947</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>0.0001292391490821116</v>
+        <v>74.96478479648752</v>
       </c>
       <c r="L81" s="18" t="n">
-        <v>0.000129239136934229</v>
+        <v>71.0888942376404</v>
       </c>
       <c r="M81" s="18" t="n">
-        <v>0.0001292391260315375</v>
+        <v>67.93643018637086</v>
       </c>
       <c r="N81" s="18" t="n">
-        <v>0.000129239116296471</v>
+        <v>65.34886268420833</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>0.0001292388003206084</v>
+        <v>29.22256793764059</v>
       </c>
     </row>
     <row r="82" ht="15.5" customHeight="1">
@@ -11684,37 +11684,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>-112786465.1456</v>
+        <v>-6842424699.393587</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>-182654608.3865474</v>
+        <v>-3907395772.386359</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>-185578511.1390696</v>
+        <v>3894276762.417581</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>-182948927.9547646</v>
+        <v>4533514341.328087</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>-179889485.2131674</v>
+        <v>4864948172.238997</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>-176823886.9308479</v>
+        <v>5062147336.103637</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>-205364092.7642468</v>
+        <v>5192500696.165643</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>-236088878.7072571</v>
+        <v>5236897092.95314</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>-235291035.6077779</v>
+        <v>5245572987.314744</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>-231900722.5989158</v>
+        <v>5284258446.687385</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>-228325920.3749734</v>
+        <v>5338393035.208652</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -11734,40 +11734,40 @@
         </is>
       </c>
       <c r="D97" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="E97" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="F97" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="G97" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="H97" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="I97" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="J97" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="K97" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="N97" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
       <c r="O97" s="19" t="n">
-        <v>116866952.5085665</v>
+        <v>4561612399.83786</v>
       </c>
     </row>
     <row r="98" ht="15.5" customHeight="1">
@@ -11787,40 +11787,40 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>-229653417.6541664</v>
+        <v>-11404037099.23145</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>-290117495.6837177</v>
+        <v>-6365389499.783792</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>-287218969.7581164</v>
+        <v>-846.3790199737737</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>-284345553.6590469</v>
+        <v>-926.9023688201981</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>-281504984.5382808</v>
+        <v>-1250.647716178158</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>-278688789.0609042</v>
+        <v>-1330.522071062539</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>-307481139.9932591</v>
+        <v>-1403.404296212776</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>-335833059.7375666</v>
+        <v>-1488.616042302136</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>-332474116.0204924</v>
+        <v>-1556.992397930603</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>-329150069.9133784</v>
+        <v>-1617.469152002785</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>-325857642.054463</v>
+        <v>-1670.672329251985</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>-223704346.7198764</v>
+        <v>-2059.961519883522</v>
       </c>
     </row>
     <row r="99" ht="15.5" customHeight="1">
@@ -11893,40 +11893,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>-112786465.1456</v>
+        <v>-6842424699.393587</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>-182654608.3865474</v>
+        <v>-3907395772.386359</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>-185578511.1390696</v>
+        <v>3894276762.417581</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>-182948927.9547646</v>
+        <v>4533514341.328087</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>-179889485.2131674</v>
+        <v>4864948172.238997</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>-176823886.9308479</v>
+        <v>5062147336.103637</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>-205364092.7642468</v>
+        <v>5192500696.165643</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>-236088878.7072571</v>
+        <v>5236897092.95314</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>-235291035.6077779</v>
+        <v>5245572987.314744</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>-231900722.5989158</v>
+        <v>5284258446.687385</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>-228325920.3749734</v>
+        <v>5338393035.208652</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>-125847943.4647366</v>
+        <v>5384050741.824263</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -11999,40 +11999,40 @@
         </is>
       </c>
       <c r="D102" s="18" t="n">
-        <v>-77375801.61306392</v>
+        <v>-3842396453.100017</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>-77375801.61306392</v>
+        <v>-1697685769.340534</v>
       </c>
       <c r="F102" s="18" t="n">
-        <v>-77375801.6130639</v>
+        <v>-0</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>-77375801.61306393</v>
+        <v>-0</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>-77375801.61306393</v>
+        <v>-0</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>-77375801.61306392</v>
+        <v>-0</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>-77375801.61306393</v>
+        <v>-0</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>-77375801.61306393</v>
+        <v>-0</v>
       </c>
       <c r="L102" s="18" t="n">
-        <v>-77375801.61306392</v>
+        <v>-0</v>
       </c>
       <c r="M102" s="18" t="n">
-        <v>-77375801.61306392</v>
+        <v>-0</v>
       </c>
       <c r="N102" s="18" t="n">
-        <v>-77375801.6130639</v>
+        <v>-0</v>
       </c>
       <c r="O102" s="18" t="n">
-        <v>-77375801.61306393</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="103" ht="15.5" customHeight="1">
@@ -12055,37 +12055,37 @@
         <v>0</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>273030915.6349618</v>
+        <v>7898010044.921936</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>290744366.4194118</v>
+        <v>12723448686.81781</v>
       </c>
       <c r="G103" s="18" t="n">
-        <v>292462021.0070488</v>
+        <v>13645116073.84025</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>292844589.3197446</v>
+        <v>14000086276.52888</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>293103021.481392</v>
+        <v>14199247412.03898</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>293369442.114091</v>
+        <v>14329764943.29478</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>290991661.8628128</v>
+        <v>14374170607.4073</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>288431145.85156</v>
+        <v>14382861003.77298</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>288497972.5274707</v>
+        <v>14421541763.1579</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>288780832.9558733</v>
+        <v>14475677118.34179</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>289077661.8328309</v>
+        <v>14521335887.70069</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -12105,40 +12105,40 @@
         </is>
       </c>
       <c r="D104" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="E104" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="F104" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="G104" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="H104" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="I104" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="J104" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="K104" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="L104" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="M104" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="N104" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
       <c r="O104" s="19" t="n">
-        <v>292167381.2714161</v>
+        <v>11404030999.59465</v>
       </c>
     </row>
     <row r="105" ht="15.5" customHeight="1">
@@ -12158,40 +12158,40 @@
         </is>
       </c>
       <c r="D105" s="18" t="n">
-        <v>-229647318.017368</v>
+        <v>-11404030999.59465</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>-290116737.3511548</v>
+        <v>-6365388741.45123</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>-287218123.3790964</v>
+        <v>-0</v>
       </c>
       <c r="G105" s="18" t="n">
-        <v>-284344626.7566781</v>
+        <v>-0</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>-281503733.8905646</v>
+        <v>-0</v>
       </c>
       <c r="I105" s="18" t="n">
-        <v>-278687458.5388331</v>
+        <v>-0</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>-307479736.5889629</v>
+        <v>-0</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>-335831571.1215243</v>
+        <v>-0</v>
       </c>
       <c r="L105" s="18" t="n">
-        <v>-332472559.0280945</v>
+        <v>-0</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>-329148452.4442264</v>
+        <v>-0</v>
       </c>
       <c r="N105" s="18" t="n">
-        <v>-325855971.3821337</v>
+        <v>-0</v>
       </c>
       <c r="O105" s="18" t="n">
-        <v>-223702286.7583565</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="106" ht="15.5" customHeight="1">
@@ -12211,37 +12211,37 @@
         </is>
       </c>
       <c r="D106" s="18" t="n">
-        <v>6.550107140012762</v>
+        <v>100</v>
       </c>
       <c r="E106" s="18" t="n">
-        <v>8.274843917912808</v>
+        <v>55.81700665034569</v>
       </c>
       <c r="F106" s="18" t="n">
-        <v>8.192168308032249</v>
+        <v>35.59163150601903</v>
       </c>
       <c r="G106" s="18" t="n">
-        <v>8.110209106828421</v>
+        <v>26.05494754848285</v>
       </c>
       <c r="H106" s="18" t="n">
-        <v>8.029179845058708</v>
+        <v>20.50535195805378</v>
       </c>
       <c r="I106" s="18" t="n">
-        <v>7.948852735433058</v>
+        <v>16.87462436906618</v>
       </c>
       <c r="J106" s="18" t="n">
-        <v>8.770079421908553</v>
+        <v>15.69576784956749</v>
       </c>
       <c r="K106" s="18" t="n">
-        <v>9.578743574433714</v>
+        <v>14.63427237466156</v>
       </c>
       <c r="L106" s="18" t="n">
-        <v>9.482936276153401</v>
+        <v>12.65452453327308</v>
       </c>
       <c r="M106" s="18" t="n">
-        <v>9.3881245689794</v>
+        <v>11.13323131251713</v>
       </c>
       <c r="N106" s="18" t="n">
-        <v>9.294214899581306</v>
+        <v>9.927652776462367</v>
       </c>
       <c r="O106" s="18" t="n">
         <v>6.380540205665611</v>
@@ -12264,40 +12264,40 @@
         </is>
       </c>
       <c r="D107" s="18" t="n">
-        <v>273030915.6349618</v>
+        <v>7898010044.921936</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>290744366.4194118</v>
+        <v>12723448686.81781</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>292462021.0070488</v>
+        <v>13645116073.84025</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>292844589.3197446</v>
+        <v>14000086276.52888</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>293103021.481392</v>
+        <v>14199247412.03898</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>293369442.114091</v>
+        <v>14329764943.29478</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>290991661.8628128</v>
+        <v>14374170607.4073</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>288431145.85156</v>
+        <v>14382861003.77298</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>288497972.5274707</v>
+        <v>14421541763.1579</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>288780832.9558733</v>
+        <v>14475677118.34179</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>289077661.8328309</v>
+        <v>14521335887.70069</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>297613757.0963305</v>
+        <v>14649273739.20915</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -14582,19 +14582,19 @@
         <v>-1171.51564613548</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>-1432.834014906238</v>
+        <v>-1507.977370884035</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>-1676.949118661038</v>
+        <v>-1842.520009836448</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>-1904.422665130769</v>
+        <v>-2118.975076444603</v>
       </c>
       <c r="N37" s="19" t="n">
-        <v>-2093.003080619859</v>
+        <v>-2377.69763856445</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>-2277.127090380663</v>
+        <v>-2618.396353926828</v>
       </c>
     </row>
     <row r="38" ht="15.5" customHeight="1">
@@ -14897,22 +14897,22 @@
         <v>7875.178448236859</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>7601.879222458402</v>
+        <v>9066.294850669048</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>7342.792241389992</v>
+        <v>10194.1889891508</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>7100.452640530194</v>
+        <v>9859.607525630629</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>6861.545439548302</v>
+        <v>9585.587748594122</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>6662.699673802575</v>
+        <v>9329.005825248072</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>6477.853758840154</v>
+        <v>9077.282077401229</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -14950,22 +14950,22 @@
         <v>7871.407442016904</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>7598.152244849609</v>
+        <v>9062.567873060256</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>7334.732680139832</v>
+        <v>10186.12942790064</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>7092.99128931924</v>
+        <v>9852.146174419675</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>6853.159398440248</v>
+        <v>9577.201707486069</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>6654.951582602245</v>
+        <v>9321.257734047742</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>6469.288906738766</v>
+        <v>9068.717225299841</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -15109,22 +15109,22 @@
         <v>7895.732376356505</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>7624.085388379882</v>
+        <v>9088.501016590528</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>7365.439508859761</v>
+        <v>10216.83625662057</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>7123.356582129665</v>
+        <v>9882.511467230101</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>6884.522433770483</v>
+        <v>9608.564742816303</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>6685.566896992949</v>
+        <v>9351.873048438445</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>6500.384124828158</v>
+        <v>9099.812443389232</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -15168,16 +15168,16 @@
         <v>-43.56174267338793</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>-300.6698729653133</v>
+        <v>-378.1043816258002</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>-563.9971115626749</v>
+        <v>-729.7028042117529</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>-800.9246027973618</v>
+        <v>-1001.418392868726</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>-1017.243533896909</v>
+        <v>-1277.970800358735</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -15327,16 +15327,16 @@
         <v>-1171.51564613548</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>-1430.542862223548</v>
+        <v>-1507.977370884035</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>-1676.81431718737</v>
+        <v>-1842.520009836448</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>-1916.190133690548</v>
+        <v>-2116.683923761912</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>-2116.835570628956</v>
+        <v>-2377.562837090783</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -15698,16 +15698,16 @@
         <v>-42.84722238875423</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>-299.5473228801035</v>
+        <v>-376.9818315405904</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>-563.2283116701815</v>
+        <v>-728.9340043192594</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>-799.7285578113909</v>
+        <v>-1000.222347882755</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>-1016.347918504324</v>
+        <v>-1277.075184966151</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -15745,22 +15745,22 @@
         <v>7327.910227625837</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>7328.495262483371</v>
+        <v>8792.910890694016</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>7408.286731248515</v>
+        <v>10259.68347900932</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>7422.903905009769</v>
+        <v>10259.49329877069</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>7447.750745440664</v>
+        <v>10337.49874713556</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>7485.29545480434</v>
+        <v>10352.0953963212</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>7516.732043332482</v>
+        <v>10376.88762835538</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -16649,19 +16649,19 @@
         <v>7871.407442016904</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>7598.152244849609</v>
+        <v>9062.567873060256</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>7334.732680139832</v>
+        <v>10186.12942790064</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>7092.99128931924</v>
+        <v>9852.146174419675</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>6853.159398440248</v>
+        <v>9577.201707486069</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>6654.951582602245</v>
+        <v>9321.257734047742</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -16752,22 +16752,22 @@
         <v>7871.407442016904</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>7598.152244849609</v>
+        <v>9062.567873060256</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>7334.732680139832</v>
+        <v>10186.12942790064</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>7092.99128931924</v>
+        <v>9852.146174419675</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>6853.159398440248</v>
+        <v>9577.201707486069</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>6654.951582602245</v>
+        <v>9321.257734047742</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>6469.288906738766</v>
+        <v>9068.717225299841</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -17733,19 +17733,19 @@
         <v>7887.839209431258</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>7614.978123128402</v>
+        <v>9079.393751339048</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>7382.294749726126</v>
+        <v>10207.34765480114</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>7125.839513266985</v>
+        <v>9872.805015848728</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>6896.031679428144</v>
+        <v>9624.984944609054</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>6717.323178653118</v>
+        <v>9353.922249784866</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -17942,22 +17942,22 @@
         <v>7887.839209431258</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>7614.978123128402</v>
+        <v>9079.393751339048</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>7382.294749726126</v>
+        <v>10207.34765480114</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>7125.839513266985</v>
+        <v>9872.805015848728</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>6896.031679428144</v>
+        <v>9624.984944609054</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>6717.323178653118</v>
+        <v>9353.922249784866</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>6563.639079885875</v>
+        <v>9110.889247053377</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -18242,37 +18242,37 @@
         </is>
       </c>
       <c r="D106" s="18" t="n">
-        <v>6.2421657353545</v>
+        <v>100</v>
       </c>
       <c r="E106" s="18" t="n">
-        <v>11.12661391787442</v>
+        <v>64.06099990914412</v>
       </c>
       <c r="F106" s="18" t="n">
-        <v>11.07764103683917</v>
+        <v>38.94212617303683</v>
       </c>
       <c r="G106" s="18" t="n">
-        <v>11.02915788461427</v>
+        <v>27.93919249023449</v>
       </c>
       <c r="H106" s="18" t="n">
-        <v>10.98115956391162</v>
+        <v>21.76351458500686</v>
       </c>
       <c r="I106" s="18" t="n">
-        <v>10.93364122641599</v>
+        <v>17.81002388241915</v>
       </c>
       <c r="J106" s="18" t="n">
-        <v>8.50464406700079</v>
+        <v>12.16773905981095</v>
       </c>
       <c r="K106" s="18" t="n">
-        <v>6.092324847828738</v>
+        <v>8.017551586867413</v>
       </c>
       <c r="L106" s="18" t="n">
-        <v>6.067647705184863</v>
+        <v>7.394610934223008</v>
       </c>
       <c r="M106" s="18" t="n">
-        <v>6.043217333967423</v>
+        <v>6.85963665583744</v>
       </c>
       <c r="N106" s="18" t="n">
-        <v>6.019031266462161</v>
+        <v>6.395248068484591</v>
       </c>
       <c r="O106" s="18" t="n">
         <v>5.882755414546067</v>
@@ -18737,40 +18737,40 @@
         </is>
       </c>
       <c r="D2" s="18" t="n">
-        <v>341438002.8327024</v>
+        <v>17322239727.41479</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>400524666.6287988</v>
+        <v>9350915474.2104</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>396523873.7286324</v>
+        <v>6033194253.202795</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>392556374.7394217</v>
+        <v>4441401530.805142</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>388635259.7584491</v>
+        <v>3506863396.081661</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>384746776.509854</v>
+        <v>2892126654.865548</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>391293573.6183391</v>
+        <v>2514391708.108677</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>397732813.4526422</v>
+        <v>2227167120.45852</v>
       </c>
       <c r="L2" s="18" t="n">
-        <v>393754290.6790842</v>
+        <v>1955925642.147624</v>
       </c>
       <c r="M2" s="18" t="n">
-        <v>389817833.2193102</v>
+        <v>1741677799.801931</v>
       </c>
       <c r="N2" s="18" t="n">
-        <v>385917936.0963264</v>
+        <v>1568159021.994978</v>
       </c>
       <c r="O2" s="18" t="n">
-        <v>277742561.6210265</v>
+        <v>1059559226.804739</v>
       </c>
     </row>
     <row r="3">
@@ -18793,37 +18793,37 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>17.30523940097193</v>
+        <v>-46.0178613080195</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>-0.9988880170205161</v>
+        <v>-35.48017549894232</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>-1.00057001660534</v>
+        <v>-26.38391299190524</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>-0.9988667190987344</v>
+        <v>-21.04151422116674</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>-1.000548239244137</v>
+        <v>-17.52953200010527</v>
       </c>
       <c r="J3" s="18" t="n">
-        <v>1.701585954240592</v>
+        <v>-13.06080237258596</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>1.645628824097112</v>
+        <v>-11.42322362597222</v>
       </c>
       <c r="L3" s="18" t="n">
-        <v>-1.000300362200757</v>
+        <v>-12.17876628203158</v>
       </c>
       <c r="M3" s="18" t="n">
-        <v>-0.999724333920271</v>
+        <v>-10.95378258400698</v>
       </c>
       <c r="N3" s="18" t="n">
-        <v>-1.000440921539314</v>
+        <v>-9.962736955519901</v>
       </c>
       <c r="O3" s="18" t="n">
-        <v>-28.03066775530717</v>
+        <v>-32.432922175406</v>
       </c>
     </row>
     <row r="4">
@@ -18949,40 +18949,40 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>341432569.8796971</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>400524291.4939544</v>
+        <v>9350915099.075556</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>396523478.1175651</v>
+        <v>6033193857.591728</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>392555961.4528939</v>
+        <v>4441401117.518615</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>388634831.3769153</v>
+        <v>3506862967.700128</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>384746335.4080915</v>
+        <v>2892126213.763785</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>391293121.9791849</v>
+        <v>2514391256.469523</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>397732351.4566109</v>
+        <v>2227166658.462489</v>
       </c>
       <c r="L6" s="18" t="n">
-        <v>393753819.8860762</v>
+        <v>1955925171.354616</v>
       </c>
       <c r="M6" s="18" t="n">
-        <v>389817355.5147429</v>
+        <v>1741677322.097364</v>
       </c>
       <c r="N6" s="18" t="n">
-        <v>385917453.2060013</v>
+        <v>1568158539.104653</v>
       </c>
       <c r="O6" s="18" t="n">
-        <v>277741831.8725704</v>
+        <v>1059558497.056283</v>
       </c>
     </row>
     <row r="7">
@@ -19005,37 +19005,37 @@
         <v>0</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>17.30699611788007</v>
+        <v>-46.01784654266452</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>-0.9988940649433009</v>
+        <v>-35.480177141292</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>-1.000575472480558</v>
+        <v>-26.38391501493224</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>-0.9988716160279631</v>
+        <v>-21.04151651901704</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>-1.000552615175287</v>
+        <v>-17.52953450415256</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>1.701585166275676</v>
+        <v>-13.06080472894304</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>1.645628076684802</v>
+        <v>-11.42322608973466</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>-1.000303735907859</v>
+        <v>-12.17876920333939</v>
       </c>
       <c r="M7" s="18" t="n">
-        <v>-0.9997272845434835</v>
+        <v>-10.95378557395784</v>
       </c>
       <c r="N7" s="18" t="n">
-        <v>-1.000443477841528</v>
+        <v>-9.96273998582906</v>
       </c>
       <c r="O7" s="18" t="n">
-        <v>-28.03076679605034</v>
+        <v>-32.43294790453761</v>
       </c>
     </row>
     <row r="8">
@@ -19055,40 +19055,40 @@
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>-99.99840880248823</v>
+        <v>-99.99996863596688</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-99.99990633914071</v>
+        <v>-99.99999598825544</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>-99.99990023020213</v>
+        <v>-99.99999344275933</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>-99.99989471919083</v>
+        <v>-99.9999906946822</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>-99.99988977285949</v>
+        <v>-99.99998778448187</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>-99.99988535270742</v>
+        <v>-99.99998474818653</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>-99.99988457792698</v>
+        <v>-99.9999820378363</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>-99.99988384261601</v>
+        <v>-99.99997925633748</v>
       </c>
       <c r="L8" s="18" t="n">
-        <v>-99.99988043482469</v>
+        <v>-99.99997592991278</v>
       </c>
       <c r="M8" s="18" t="n">
-        <v>-99.99987745440906</v>
+        <v>-99.99997257216189</v>
       </c>
       <c r="N8" s="18" t="n">
-        <v>-99.99987487227729</v>
+        <v>-99.99996920654613</v>
       </c>
       <c r="O8" s="18" t="n">
-        <v>-99.99973725724577</v>
+        <v>-99.99993112716706</v>
       </c>
     </row>
     <row r="9">
@@ -19373,40 +19373,40 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>3.222764012148544e-05</v>
+        <v>6.352377782692932e-07</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>3.232418123127826e-05</v>
+        <v>1.384530952869064e-06</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>3.823183683213804e-05</v>
+        <v>2.512737930225368e-06</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>4.416239399723883e-05</v>
+        <v>3.903324022187055e-06</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>5.011614356995771e-05</v>
+        <v>5.553937600239704e-06</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>5.609606643411961e-05</v>
+        <v>7.462598741690828e-06</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>6.040944034002736e-05</v>
+        <v>9.401011670020782e-06</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>6.327533602551403e-05</v>
+        <v>1.129986034205094e-05</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>6.697765073279261e-05</v>
+        <v>1.348350713715512e-05</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>7.069809663998497e-05</v>
+        <v>1.582346565367169e-05</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>7.444298299468611e-05</v>
+        <v>1.832013332271297e-05</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>0.0001068452427538067</v>
+        <v>2.800737388598234e-05</v>
       </c>
     </row>
     <row r="15">
@@ -19532,40 +19532,40 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>5.303991705879161e-05</v>
+        <v>1.045467770677755e-06</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>4.683042964434373e-05</v>
+        <v>2.005872288452915e-06</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>4.988489892830283e-05</v>
+        <v>3.278620335009301e-06</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>5.264040458189161e-05</v>
+        <v>4.652658906013786e-06</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>0.0001102271404954327</v>
+        <v>1.221551812560994e-05</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>0.0001146472925769747</v>
+        <v>1.525181346410424e-05</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>0.0001154220730155678</v>
+        <v>1.796216368318787e-05</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>0.0001161573839838666</v>
+        <v>2.074366252573392e-05</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>0.0001195651753239247</v>
+        <v>2.407008721860143e-05</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>0.0001225455909358651</v>
+        <v>2.742783810796202e-05</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>0.0001251277227197287</v>
+        <v>3.079345386732452e-05</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>0.0001751618361546774</v>
+        <v>4.591522195371158e-05</v>
       </c>
     </row>
     <row r="18">
@@ -19691,40 +19691,40 @@
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>2.996675876621635e-05</v>
+        <v>5.906736325968917e-07</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>2.812465518183992e-05</v>
+        <v>1.204654043962209e-06</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>3.171775415292017e-05</v>
+        <v>2.084608287891899e-06</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>3.53102940368382e-05</v>
+        <v>3.120924987741749e-06</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>3.890254227754549e-05</v>
+        <v>4.311231409866379e-06</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>4.249694923145588e-05</v>
+        <v>5.653474477266864e-06</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>4.486436664143553e-05</v>
+        <v>6.981862966950232e-06</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>4.590247690709712e-05</v>
+        <v>8.197373747573112e-06</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>4.734979974530174e-05</v>
+        <v>9.532155216307956e-06</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>4.879258211598033e-05</v>
+        <v>1.092062988905856e-05</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>5.023664856606389e-05</v>
+        <v>1.236304702462372e-05</v>
       </c>
       <c r="O20" s="18" t="n">
-        <v>7.108931752842216e-05</v>
+        <v>1.86346630322659e-05</v>
       </c>
     </row>
     <row r="21">
@@ -19903,40 +19903,40 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>-341438557.8966888</v>
+        <v>-17322240282.47878</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>-400524985.5991447</v>
+        <v>-9350915793.180746</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>-396524217.0831868</v>
+        <v>-6033194596.55735</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>-392556740.6598221</v>
+        <v>-4441401896.725543</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>-388635860.7480558</v>
+        <v>-3506863997.071268</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>-384747403.1723469</v>
+        <v>-2892127281.528041</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>-391294223.3908346</v>
+        <v>-2514392357.881173</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>-397733481.1176879</v>
+        <v>-2227167788.123566</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>-393754971.4536107</v>
+        <v>-1955926322.922151</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>-389818525.0112923</v>
+        <v>-1741678491.593913</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>-385918637.0034049</v>
+        <v>-1568159722.902057</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>-277743282.0527115</v>
+        <v>-1059559947.236424</v>
       </c>
     </row>
     <row r="25">
@@ -19956,40 +19956,40 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>-682871127.7763858</v>
+        <v>-34644474576.94057</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>-801049277.0930991</v>
+        <v>-18701830892.2563</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>-793047695.2007519</v>
+        <v>-12066388454.14908</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>-785112702.112716</v>
+        <v>-8882803014.244158</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>-777270692.1249712</v>
+        <v>-7013726964.771396</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>-769493738.5804384</v>
+        <v>-5784253495.291826</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>-782587345.3700194</v>
+        <v>-5028783614.350697</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>-795465832.5742989</v>
+        <v>-4454334446.586056</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>-787508791.3396869</v>
+        <v>-3911851494.276768</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>-779635880.5260352</v>
+        <v>-3483355813.691278</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>-771836090.2094063</v>
+        <v>-3136318262.00671</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>-555485113.925282</v>
+        <v>-2119118444.292707</v>
       </c>
     </row>
     <row r="26">
@@ -20009,40 +20009,40 @@
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>-100.0001625665514</v>
+        <v>-100.0000032043431</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>-100.0000796381278</v>
+        <v>-100.0000034111136</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>-100.000086591143</v>
+        <v>-100.0000056910907</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>-100.0000932147391</v>
+        <v>-100.0000082388498</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>-100.0001546410398</v>
+        <v>-100.0000171375254</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>-100.0001628766064</v>
+        <v>-100.0000216678786</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>-100.0001660575433</v>
+        <v>-100.0000258421349</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>-100.0001678677301</v>
+        <v>-100.0000299782194</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>-100.0001728932338</v>
+        <v>-100.0000348057468</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>-100.0001774654526</v>
+        <v>-100.0000397198599</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>-100.0001816207574</v>
+        <v>-100.0000446961736</v>
       </c>
       <c r="O26" s="18" t="n">
-        <v>-100.0002593882914</v>
+        <v>-100.0000679935266</v>
       </c>
     </row>
     <row r="27">
@@ -20062,40 +20062,40 @@
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>-199.9985713690396</v>
+        <v>-199.9999718403099</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>-199.9999859772685</v>
+        <v>-199.999999399369</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>-199.9999868213451</v>
+        <v>-199.99999913385</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>-199.9999879339299</v>
+        <v>-199.999998933532</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>-200.0000444138993</v>
+        <v>-200.0000049220073</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>-200.0000482293138</v>
+        <v>-200.0000064160652</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>-200.0000506354703</v>
+        <v>-200.0000078799712</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>-200.0000517103461</v>
+        <v>-200.0000092345569</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>-200.0000533280585</v>
+        <v>-200.0000107356596</v>
       </c>
       <c r="M27" s="18" t="n">
-        <v>-200.0000549198617</v>
+        <v>-200.0000122920218</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>-200.0000564930347</v>
+        <v>-200.0000139027197</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>-199.9999966455372</v>
+        <v>-199.9999991206937</v>
       </c>
     </row>
     <row r="28">
@@ -20168,40 +20168,40 @@
         </is>
       </c>
       <c r="D29" s="19" t="n">
-        <v>2.260881355269103e-06</v>
+        <v>4.456414567240165e-08</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>4.199526049438328e-06</v>
+        <v>1.798769089068548e-07</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>6.514082679217862e-06</v>
+        <v>4.281296423334693e-07</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>8.852099960400628e-06</v>
+        <v>7.823990344453063e-07</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>1.121360129241222e-05</v>
+        <v>1.242706190373326e-06</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>1.359911720266373e-05</v>
+        <v>1.809124264423964e-06</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>1.554507369859181e-05</v>
+        <v>2.419148703070546e-06</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>1.73728591184169e-05</v>
+        <v>3.102486594477828e-06</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>1.962785098749087e-05</v>
+        <v>3.95135192084716e-06</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>2.190551452400463e-05</v>
+        <v>4.902835764613129e-06</v>
       </c>
       <c r="N29" s="19" t="n">
-        <v>2.42063344286222e-05</v>
+        <v>5.957086298089252e-06</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>3.575592522538453e-05</v>
+        <v>9.372710853716439e-06</v>
       </c>
     </row>
     <row r="30">
@@ -20221,40 +20221,40 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>-341438565.6161969</v>
+        <v>-17322240290.19829</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>-400525002.4192824</v>
+        <v>-9350915810.000883</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-396524242.9130798</v>
+        <v>-6033194622.387243</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>-392556775.4093048</v>
+        <v>-4441401931.475026</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>-388635904.3280643</v>
+        <v>-3506864040.651277</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>-384747455.494512</v>
+        <v>-2892127333.850206</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>-391294284.2177089</v>
+        <v>-2514392418.708047</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>-397733550.2152493</v>
+        <v>-2227167857.221128</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>-393755048.7391161</v>
+        <v>-1955926400.207657</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>-389818610.4028944</v>
+        <v>-1741678576.985515</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>-385918730.4199911</v>
+        <v>-1568159816.318643</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>-277743381.3621342</v>
+        <v>-1059560046.545847</v>
       </c>
     </row>
     <row r="31">
@@ -20274,40 +20274,40 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>-100.0001648274328</v>
+        <v>-100.0000032489072</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>-100.0000838376538</v>
+        <v>-100.0000035909905</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>-100.0000931052257</v>
+        <v>-100.0000061192203</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>-100.000102066839</v>
+        <v>-100.0000090212488</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>-100.0001658546411</v>
+        <v>-100.0000183802316</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>-100.0001764757236</v>
+        <v>-100.0000234770029</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>-100.000181602617</v>
+        <v>-100.0000282612835</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>-100.0001852405892</v>
+        <v>-100.000033080706</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>-100.0001925210848</v>
+        <v>-100.0000387570987</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>-100.0001993709671</v>
+        <v>-100.0000446226957</v>
       </c>
       <c r="N31" s="19" t="n">
-        <v>-100.0002058270918</v>
+        <v>-100.0000506532599</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>-100.0002951442167</v>
+        <v>-100.0000773662375</v>
       </c>
     </row>
     <row r="32">
@@ -20380,40 +20380,40 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>-341438565.6161969</v>
+        <v>-17322240290.19829</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>-400525002.4192824</v>
+        <v>-9350915810.000883</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>-396524242.9130798</v>
+        <v>-6033194622.387243</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>-392556775.4093048</v>
+        <v>-4441401931.475026</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>-388635904.3280643</v>
+        <v>-3506864040.651277</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>-384747455.494512</v>
+        <v>-2892127333.850206</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>-391294284.2177089</v>
+        <v>-2514392418.708047</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>-397733550.2152493</v>
+        <v>-2227167857.221128</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>-393755048.7391161</v>
+        <v>-1955926400.207657</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>-389818610.4028944</v>
+        <v>-1741678576.985515</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>-385918730.4199911</v>
+        <v>-1568159816.318643</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>-277743381.3621342</v>
+        <v>-1059560046.545847</v>
       </c>
     </row>
     <row r="34">
@@ -20433,40 +20433,40 @@
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>-682871135.495894</v>
+        <v>-34644474584.66008</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>-801049293.9132369</v>
+        <v>-18701830909.07644</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-793047721.0306449</v>
+        <v>-12066388479.97897</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>-785112736.8621987</v>
+        <v>-8882803048.993641</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>-777270735.7049797</v>
+        <v>-7013727008.351404</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>-769493790.9026035</v>
+        <v>-5784253547.613991</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>-782587406.1968938</v>
+        <v>-5028783675.17757</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>-795465901.6718602</v>
+        <v>-4454334515.683617</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>-787508868.6251923</v>
+        <v>-3911851571.562273</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>-779635965.9176373</v>
+        <v>-3483355899.08288</v>
       </c>
       <c r="N34" s="19" t="n">
-        <v>-771836183.6259925</v>
+        <v>-3136318355.423296</v>
       </c>
       <c r="O34" s="19" t="n">
-        <v>-555485213.2347046</v>
+        <v>-2119118543.60213</v>
       </c>
     </row>
     <row r="35">
@@ -20592,40 +20592,40 @@
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>-682871135.495894</v>
+        <v>-34644474584.66008</v>
       </c>
       <c r="E37" s="19" t="n">
-        <v>-852785924.6054109</v>
+        <v>-28691341393.67142</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>-857655496.5264665</v>
+        <v>-18141809969.20319</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>-850088299.8335174</v>
+        <v>-13214853215.49895</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>-841671970.4218833</v>
+        <v>-10432680876.99387</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>-833277415.2088397</v>
+        <v>-8656704629.756916</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>-845737940.3717122</v>
+        <v>-7538307881.403408</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>-859555020.0431517</v>
+        <v>-6737629431.455149</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>-852645357.9556391</v>
+        <v>-6041968404.351931</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>-844249194.8345419</v>
+        <v>-5470868446.628437</v>
       </c>
       <c r="N37" s="19" t="n">
-        <v>-835813519.2415581</v>
+        <v>-4993367352.59445</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>-618824062.8142952</v>
+        <v>-3867705402.016022</v>
       </c>
     </row>
     <row r="38">
@@ -20645,40 +20645,40 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>-341438565.6161969</v>
+        <v>-17322240290.19829</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>-400525002.4192824</v>
+        <v>-9350915810.000883</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-396524242.9130798</v>
+        <v>-6033194622.387243</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>-392556775.4093048</v>
+        <v>-4441401931.475026</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>-388635904.3280643</v>
+        <v>-3506864040.651277</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>-384747455.494512</v>
+        <v>-2892127333.850206</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>-391294284.2177089</v>
+        <v>-2514392418.708047</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>-397733550.2152493</v>
+        <v>-2227167857.221128</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>-393755048.7391161</v>
+        <v>-1955926400.207657</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>-389818610.4028944</v>
+        <v>-1741678576.985515</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>-385918730.4199911</v>
+        <v>-1568159816.318643</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>-277743381.3621342</v>
+        <v>-1059560046.545847</v>
       </c>
     </row>
     <row r="39">
@@ -20698,40 +20698,40 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>-100.0001648274328</v>
+        <v>-100.0000032489072</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>-100.0000838376538</v>
+        <v>-100.0000035909905</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>-100.0000931052257</v>
+        <v>-100.0000061192203</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>-100.000102066839</v>
+        <v>-100.0000090212488</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>-100.0001658546411</v>
+        <v>-100.0000183802316</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>-100.0001764757236</v>
+        <v>-100.0000234770029</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>-100.000181602617</v>
+        <v>-100.0000282612835</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>-100.0001852405892</v>
+        <v>-100.000033080706</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>-100.0001925210848</v>
+        <v>-100.0000387570987</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>-100.0001993709671</v>
+        <v>-100.0000446226957</v>
       </c>
       <c r="N39" s="19" t="n">
-        <v>-100.0002058270918</v>
+        <v>-100.0000506532599</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>-100.0002951442167</v>
+        <v>-100.0000773662375</v>
       </c>
     </row>
     <row r="40">
@@ -20910,40 +20910,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>-132486287.3294363</v>
+        <v>-9448497235.6576</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>-260707233.7314882</v>
+        <v>3769729432.082538</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>-262419663.5706231</v>
+        <v>14869645243.63602</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>-254614792.5984507</v>
+        <v>19838296281.08943</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>-246181967.581073</v>
+        <v>22623625767.43283</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>-237770888.160159</v>
+        <v>24399839711.57009</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>-250231641.0170678</v>
+        <v>25518252987.73656</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>-264048690.2289988</v>
+        <v>26318947968.558</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>-257139083.69375</v>
+        <v>27014608781.92084</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>-248743023.9939961</v>
+        <v>27585708792.0268</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>-240307431.7102009</v>
+        <v>28063209852.46104</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>-23317799.14978604</v>
+        <v>29188871817.00977</v>
       </c>
     </row>
     <row r="44">
@@ -20963,40 +20963,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>-132486740.348631</v>
+        <v>-9448497688.676796</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>-260707270.7223993</v>
+        <v>3769729395.091627</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>-262419702.007456</v>
+        <v>14869645205.19918</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>-254614832.1587506</v>
+        <v>19838296241.52913</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>-246182025.5734624</v>
+        <v>22623625709.44044</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>-237770947.2312178</v>
+        <v>24399839652.49903</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>-250231700.8302397</v>
+        <v>25518252927.92339</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>-264048751.1678632</v>
+        <v>26318947907.61914</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>-257139145.7603923</v>
+        <v>27014608719.8542</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>-248743086.8877178</v>
+        <v>27585708729.13308</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>-240307495.154728</v>
+        <v>28063209789.01651</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>-23317882.88694784</v>
+        <v>29188871733.27261</v>
       </c>
     </row>
     <row r="45">
@@ -21122,40 +21122,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>-132486040.6821593</v>
+        <v>-9448496989.010323</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>-260706705.5143142</v>
+        <v>3769729960.299712</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>-262418865.7739077</v>
+        <v>14869646041.43273</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>-254613737.097578</v>
+        <v>19838297336.5903</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>-246180666.1278051</v>
+        <v>22623627068.88609</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>-237769352.3935766</v>
+        <v>24399841247.33667</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>-250229874.5645334</v>
+        <v>25518254754.18909</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>-264046696.5639825</v>
+        <v>26318949962.22302</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>-257136873.9681962</v>
+        <v>27014610991.6464</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>-248740609.2466618</v>
+        <v>27585711206.77414</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>-240304822.8714922</v>
+        <v>28063212461.29974</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>-23315082.70322528</v>
+        <v>29188874533.45633</v>
       </c>
     </row>
     <row r="48">
@@ -21175,40 +21175,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>-169443361.0084581</v>
+        <v>-9448497429.079298</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>-569968363.4277406</v>
+        <v>-18799413239.08018</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>-650925353.9389603</v>
+        <v>-12505125811.43487</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>-649393054.7934705</v>
+        <v>-5638567790.686301</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>-641688992.343961</v>
+        <v>-2240551929.988637</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>-633592915.2801661</v>
+        <v>-234729590.4105988</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>-635943026.4400514</v>
+        <v>1030992888.306826</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>-648613136.1382902</v>
+        <v>1877415242.851239</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>-651540512.9598424</v>
+        <v>2548995325.45952</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>-644149374.7812946</v>
+        <v>3111073047.80675</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>-636051560.8472726</v>
+        <v>3570144420.808647</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>-523658493.496337</v>
+        <v>4317494582.216532</v>
       </c>
     </row>
     <row r="49">
@@ -21228,40 +21228,40 @@
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
     </row>
     <row r="50">
@@ -21281,40 +21281,40 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>-341438565.6161969</v>
+        <v>-17322240290.19829</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>-400525002.4192824</v>
+        <v>-9350915810.000883</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>-396524242.9130798</v>
+        <v>-6033194622.387243</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>-392556775.4093048</v>
+        <v>-4441401931.475026</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>-388635904.3280643</v>
+        <v>-3506864040.651277</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>-384747455.494512</v>
+        <v>-2892127333.850206</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>-391294284.2177089</v>
+        <v>-2514392418.708047</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>-397733550.2152493</v>
+        <v>-2227167857.221128</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>-393755048.7391161</v>
+        <v>-1955926400.207657</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>-389818610.4028944</v>
+        <v>-1741678576.985515</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>-385918730.4199911</v>
+        <v>-1568159816.318643</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>-277743381.3621342</v>
+        <v>-1059560046.545847</v>
       </c>
     </row>
     <row r="51">
@@ -21337,37 +21337,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>-341438565.6161969</v>
+        <v>-17322240290.19829</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>-426396315.6336194</v>
+        <v>-14345674050.16662</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>-428831483.9919045</v>
+        <v>-9070908720.330269</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>-425048292.6236354</v>
+        <v>-6607430750.456354</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>-420840664.3933929</v>
+        <v>-5216345117.679386</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>-416643946.8300813</v>
+        <v>-4328357554.10412</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>-422874790.5307796</v>
+        <v>-3769159761.046627</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>-429780668.8284651</v>
+        <v>-3368821135.451817</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>-426325968.986139</v>
+        <v>-3020991236.326728</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>-422128035.0350204</v>
+        <v>-2735438623.991703</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>-417910316.7419416</v>
+        <v>-2496688232.356615</v>
       </c>
     </row>
     <row r="52">
@@ -21387,40 +21387,40 @@
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>352524132.6591883</v>
+        <v>12327482050.03255</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>374753911.7440073</v>
+        <v>19279279147.60983</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>376741119.6012489</v>
+        <v>20529354641.50407</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>377192267.7200502</v>
+        <v>21014568193.43768</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>377513130.1882982</v>
+        <v>21289990842.36025</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>377841756.0845569</v>
+        <v>21471618417.3754</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>377370048.6136078</v>
+        <v>21584745164.50915</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>376846607.0506854</v>
+        <v>21661346326.16674</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>377108469.2862191</v>
+        <v>21732646086.72334</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>377426636.4027589</v>
+        <v>21797878133.89196</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>377745981.5521668</v>
+        <v>21852109459.47982</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>385964854.7369099</v>
+        <v>22002979003.44093</v>
       </c>
     </row>
     <row r="53">
@@ -21440,40 +21440,40 @@
         </is>
       </c>
       <c r="D53" s="18" t="n">
-        <v>352524132.6591883</v>
+        <v>12327482050.03255</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>374753911.7440073</v>
+        <v>19279279147.60983</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>376741119.6012489</v>
+        <v>20529354641.50407</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>377192267.7200502</v>
+        <v>21014568193.43768</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>377513130.1882982</v>
+        <v>21289990842.36025</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>377841756.0845569</v>
+        <v>21471618417.3754</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>377370048.6136078</v>
+        <v>21584745164.50915</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>376846607.0506854</v>
+        <v>21661346326.16674</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>377108469.2862191</v>
+        <v>21732646086.72334</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>377426636.4027589</v>
+        <v>21797878133.89196</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>377745981.5521668</v>
+        <v>21852109459.47982</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>385964854.7369099</v>
+        <v>22002979003.44093</v>
       </c>
     </row>
     <row r="54">
@@ -21705,40 +21705,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>183080765.175618</v>
+        <v>2878984614.478139</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>-195214457.8416435</v>
+        <v>479865902.3717376</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>-274184240.2585662</v>
+        <v>8024228824.14834</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>-272200792.6649644</v>
+        <v>15376000397.15983</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>-264175884.9386111</v>
+        <v>19049438889.58867</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>-255751182.0117287</v>
+        <v>21236888804.14868</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>-258573000.5185891</v>
+        <v>22615738030.12383</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>-271766552.0541926</v>
+        <v>23538761546.0514</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>-274432067.0449499</v>
+        <v>24281641388.81153</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>-266722762.0088684</v>
+        <v>24908951158.06837</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>-258305603.0500171</v>
+        <v>25422253856.53356</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>-137693662.5172638</v>
+        <v>26320473561.89963</v>
       </c>
     </row>
     <row r="59">
@@ -21758,40 +21758,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>-315566805.8577773</v>
+        <v>-12327481603.48846</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>-65492247.67267072</v>
+        <v>3289864057.927975</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>11765374.48465848</v>
+        <v>6845417217.284391</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>17587055.56738645</v>
+        <v>4462296939.430471</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>17995218.81080601</v>
+        <v>3574188179.297424</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>17981829.61815208</v>
+        <v>3162952443.187992</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>8343125.954055697</v>
+        <v>2902516724.065262</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>7719855.490210146</v>
+        <v>2780188416.171623</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>17295193.07675368</v>
+        <v>2732969602.834862</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>17982152.76220652</v>
+        <v>2676760048.705761</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>18000780.17852488</v>
+        <v>2640958604.766182</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>114378579.8140385</v>
+        <v>2868400971.556698</v>
       </c>
     </row>
     <row r="60">
@@ -21864,40 +21864,40 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>-682871127.7763858</v>
+        <v>-34644474576.94057</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>-801049277.0930991</v>
+        <v>-18701830892.2563</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>-793047695.2007519</v>
+        <v>-12066388454.14908</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>-785112702.112716</v>
+        <v>-8882803014.244158</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>-777270692.1249712</v>
+        <v>-7013726964.771396</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>-769493738.5804384</v>
+        <v>-5784253495.291826</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>-782587345.3700194</v>
+        <v>-5028783614.350697</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>-795465832.5742989</v>
+        <v>-4454334446.586056</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>-787508791.3396869</v>
+        <v>-3911851494.276768</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>-779635880.5260352</v>
+        <v>-3483355813.691278</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>-771836090.2094063</v>
+        <v>-3136318262.00671</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>-555485113.925282</v>
+        <v>-2119118444.292707</v>
       </c>
     </row>
     <row r="62">
@@ -22023,40 +22023,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>-682871140.7266101</v>
+        <v>-34644474589.89079</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>-801049276.4586953</v>
+        <v>-18701830891.6219</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>-793047694.7266411</v>
+        <v>-12066388453.67497</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>-785112701.4540948</v>
+        <v>-8882803013.585537</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>-777270726.5077795</v>
+        <v>-7013726999.154204</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>-769493738.6467807</v>
+        <v>-5784253495.358169</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>-782587345.1220716</v>
+        <v>-5028783614.102749</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>-795465833.1231834</v>
+        <v>-4454334447.13494</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>-787508792.1491643</v>
+        <v>-3911851495.086245</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>-779635881.0440475</v>
+        <v>-3483355814.20929</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>-771836090.4585636</v>
+        <v>-3136318262.255867</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>-555485113.9311327</v>
+        <v>-2119118444.298558</v>
       </c>
     </row>
     <row r="65">
@@ -22182,40 +22182,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>-682871395.0933951</v>
+        <v>-34644474844.25758</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>-801049574.84873</v>
+        <v>-18701831190.01193</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>-793047990.1360755</v>
+        <v>-12066388749.0844</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>-785112993.9077348</v>
+        <v>-8882803306.039177</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>-777271016.0401831</v>
+        <v>-7013727288.686608</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>-769494025.2822603</v>
+        <v>-5784253781.993649</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-782587636.6348981</v>
+        <v>-5028783905.615575</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>-795466129.4332267</v>
+        <v>-4454334743.444983</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>-787509085.4952072</v>
+        <v>-3911851788.432288</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>-779636171.4574299</v>
+        <v>-3483356104.622672</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>-771836377.9665242</v>
+        <v>-3136318549.763828</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>-555485320.8484074</v>
+        <v>-2119118651.215833</v>
       </c>
     </row>
     <row r="68">
@@ -22394,40 +22394,40 @@
         </is>
       </c>
       <c r="D71" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="E71" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="F71" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="G71" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="I71" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="J71" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="K71" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="L71" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="M71" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="N71" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="O71" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
     </row>
     <row r="72">
@@ -22500,40 +22500,40 @@
         </is>
       </c>
       <c r="D73" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="E73" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="F73" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="G73" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="I73" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="J73" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="K73" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="N73" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="O73" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
     </row>
     <row r="74">
@@ -22553,40 +22553,40 @@
         </is>
       </c>
       <c r="D74" s="18" t="n">
-        <v>550384654.7447641</v>
+        <v>25195977155.58078</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>550384654.7447641</v>
+        <v>25195977155.58078</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>550384654.7447641</v>
+        <v>25195977155.58078</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>550384654.7447641</v>
+        <v>25195977155.58078</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>550384654.7447641</v>
+        <v>25195977155.58078</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>550384654.7447641</v>
+        <v>25195977155.58078</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>550384654.7447641</v>
+        <v>25195977155.58078</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>550384654.7447641</v>
+        <v>25195977155.58078</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>550384654.7447641</v>
+        <v>25195977155.58078</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>550384654.7447641</v>
+        <v>25195977155.58078</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>550384654.7447641</v>
+        <v>25195977155.58078</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>550384654.7447641</v>
+        <v>25195977155.58078</v>
       </c>
     </row>
     <row r="75">
@@ -22606,40 +22606,40 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>-132486740.348631</v>
+        <v>-9448497688.676796</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-250664920.1039659</v>
+        <v>6494145965.568848</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>-242663335.3913114</v>
+        <v>13129588406.49638</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>-234728339.1629707</v>
+        <v>16313173849.5416</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>-226886361.295419</v>
+        <v>18182249866.89417</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>-219109370.5374962</v>
+        <v>19411723373.58713</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>-232202981.890134</v>
+        <v>20167193249.96521</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>-245081474.6884626</v>
+        <v>20741642412.1358</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>-237124430.7504431</v>
+        <v>21284125367.14849</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>-229251516.7126658</v>
+        <v>21712621050.95811</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>-221451723.2217602</v>
+        <v>22059658605.81695</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>-5100666.103643298</v>
+        <v>23076858504.36495</v>
       </c>
     </row>
     <row r="76">
@@ -22662,37 +22662,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>-132486740.348631</v>
+        <v>-9448497688.676796</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>-260707270.7223993</v>
+        <v>3769729395.091627</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>-262419702.007456</v>
+        <v>14869645205.19918</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>-254614832.1587506</v>
+        <v>19838296241.52913</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>-246182025.5734624</v>
+        <v>22623625709.44044</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>-237770947.2312178</v>
+        <v>24399839652.49903</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>-250231700.8302397</v>
+        <v>25518252927.92339</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>-264048751.1678632</v>
+        <v>26318947907.61914</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>-257139145.7603923</v>
+        <v>27014608719.8542</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>-248743086.8877178</v>
+        <v>27585708729.13308</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>-240307495.154728</v>
+        <v>28063209789.01651</v>
       </c>
     </row>
     <row r="77">
@@ -22712,40 +22712,40 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>-132486740.348631</v>
+        <v>-9448497688.676796</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-250664920.1039659</v>
+        <v>6494145965.568848</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>-242663335.3913114</v>
+        <v>13129588406.49638</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>-234728339.1629707</v>
+        <v>16313173849.5416</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>-226886361.295419</v>
+        <v>18182249866.89417</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>-219109370.5374962</v>
+        <v>19411723373.58713</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>-232202981.890134</v>
+        <v>20167193249.96521</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>-245081474.6884626</v>
+        <v>20741642412.1358</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>-237124430.7504431</v>
+        <v>21284125367.14849</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>-229251516.7126658</v>
+        <v>21712621050.95811</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>-221451723.2217602</v>
+        <v>22059658605.81695</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>-5100666.103643298</v>
+        <v>23076858504.36495</v>
       </c>
     </row>
     <row r="78">
@@ -22765,40 +22765,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>-132486740.348631</v>
+        <v>-9448497688.676796</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>-260707270.7223993</v>
+        <v>3769729395.091627</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>-262419702.007456</v>
+        <v>14869645205.19918</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>-254614832.1587506</v>
+        <v>19838296241.52913</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>-246182025.5734624</v>
+        <v>22623625709.44044</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>-237770947.2312178</v>
+        <v>24399839652.49903</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>-250231700.8302397</v>
+        <v>25518252927.92339</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>-264048751.1678632</v>
+        <v>26318947907.61914</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>-257139145.7603923</v>
+        <v>27014608719.8542</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>-248743086.8877178</v>
+        <v>27585708729.13308</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>-240307495.154728</v>
+        <v>28063209789.01651</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>-23317882.88694784</v>
+        <v>29188871733.27261</v>
       </c>
     </row>
     <row r="79">
@@ -22924,40 +22924,40 @@
         </is>
       </c>
       <c r="D81" s="18" t="n">
-        <v>7.449867413537622e-05</v>
+        <v>1.468440508314301e-06</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>7.44997897980794e-05</v>
+        <v>3.191024831214291e-06</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>7.449978524692877e-05</v>
+        <v>4.896401839271334e-06</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>7.449978114123307e-05</v>
+        <v>6.584715162734038e-06</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>7.449977745622319e-05</v>
+        <v>8.256164296560967e-06</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>7.44997741632161e-05</v>
+        <v>9.910889591155212e-06</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>7.449977358600575e-05</v>
+        <v>1.159377138662015e-05</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>7.449977303820011e-05</v>
+        <v>1.330434706038867e-05</v>
       </c>
       <c r="L81" s="18" t="n">
-        <v>7.449977049940036e-05</v>
+        <v>1.499781160215083e-05</v>
       </c>
       <c r="M81" s="18" t="n">
-        <v>7.44997682789949e-05</v>
+        <v>1.667434599508655e-05</v>
       </c>
       <c r="N81" s="18" t="n">
-        <v>7.449976635531034e-05</v>
+        <v>1.833410749052973e-05</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>7.449966383230512e-05</v>
+        <v>1.952861807932038e-05</v>
       </c>
     </row>
     <row r="82">
@@ -23746,37 +23746,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>-169443361.0084581</v>
+        <v>-9448497429.079298</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>-241371567.3786175</v>
+        <v>-4201589259.76161</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>-242820045.1927059</v>
+        <v>1245171274.682483</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>-238962500.636533</v>
+        <v>3721678788.20366</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>-234749635.6847724</v>
+        <v>5113751111.524825</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>-230547681.3999428</v>
+        <v>6001813028.287994</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>-236778524.4750614</v>
+        <v>6561016058.067003</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>-243684402.772747</v>
+        <v>6961359920.383334</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>-240229696.1510769</v>
+        <v>7309189820.134003</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>-236031696.1930805</v>
+        <v>7594742432.469027</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>-231813924.9220206</v>
+        <v>7833492830.883459</v>
       </c>
     </row>
     <row r="97">
@@ -23796,40 +23796,40 @@
         </is>
       </c>
       <c r="D97" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="E97" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="F97" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="G97" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="H97" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="I97" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="J97" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="K97" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="N97" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
       <c r="O97" s="19" t="n">
-        <v>171995204.6077388</v>
+        <v>7873742861.118994</v>
       </c>
     </row>
     <row r="98">
@@ -23849,40 +23849,40 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>-341438565.6161969</v>
+        <v>-17322240290.19829</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>-400525002.4192824</v>
+        <v>-9350915810.000883</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>-396524242.9130798</v>
+        <v>-6033194622.387243</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>-392556775.4093048</v>
+        <v>-4441401931.475026</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>-388635904.3280643</v>
+        <v>-3506864040.651277</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>-384747455.494512</v>
+        <v>-2892127333.850206</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>-391294284.2177089</v>
+        <v>-2514392418.708047</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>-397733550.2152493</v>
+        <v>-2227167857.221128</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>-393755048.7391161</v>
+        <v>-1955926400.207657</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>-389818610.4028944</v>
+        <v>-1741678576.985515</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>-385918730.4199911</v>
+        <v>-1568159816.318643</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>-277743381.3621342</v>
+        <v>-1059560046.545847</v>
       </c>
     </row>
     <row r="99">
@@ -23955,40 +23955,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>-169443361.0084581</v>
+        <v>-9448497429.079298</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>-241371567.3786175</v>
+        <v>-4201589259.76161</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>-242820045.1927059</v>
+        <v>1245171274.682483</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>-238962500.636533</v>
+        <v>3721678788.20366</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>-234749635.6847724</v>
+        <v>5113751111.524825</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>-230547681.3999428</v>
+        <v>6001813028.287994</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>-236778524.4750614</v>
+        <v>6561016058.067003</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>-243684402.772747</v>
+        <v>6961359920.383334</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>-240229696.1510769</v>
+        <v>7309189820.134003</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>-236031696.1930805</v>
+        <v>7594742432.469027</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>-231813924.9220206</v>
+        <v>7833492830.883459</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>-123291647.4822437</v>
+        <v>8396323577.269415</v>
       </c>
     </row>
     <row r="101">
@@ -24061,40 +24061,40 @@
         </is>
       </c>
       <c r="D102" s="18" t="n">
-        <v>-134228440.9260423</v>
+        <v>-6809943478.797247</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>-134228440.9260423</v>
+        <v>-3133789339.715107</v>
       </c>
       <c r="F102" s="18" t="n">
-        <v>-134228440.9260423</v>
+        <v>-2042315903.092647</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>-134228440.9260423</v>
+        <v>-1518668434.750657</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>-134228440.9260423</v>
+        <v>-1211216058.601644</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>-134228440.9260423</v>
+        <v>-1008991007.602684</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>-134228440.9260423</v>
+        <v>-862531946.7075384</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>-134228440.9260423</v>
+        <v>-751633874.2700844</v>
       </c>
       <c r="L102" s="18" t="n">
-        <v>-134228440.9260423</v>
+        <v>-666763782.4945865</v>
       </c>
       <c r="M102" s="18" t="n">
-        <v>-134228440.9260423</v>
+        <v>-599723507.0066856</v>
       </c>
       <c r="N102" s="18" t="n">
-        <v>-134228440.9260423</v>
+        <v>-545431345.6938113</v>
       </c>
       <c r="O102" s="18" t="n">
-        <v>-134228440.9260423</v>
+        <v>-512068650.8435581</v>
       </c>
     </row>
     <row r="103">
@@ -24117,37 +24117,37 @@
         <v>0</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>352524132.6591883</v>
+        <v>12327482050.03255</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>374753911.7440073</v>
+        <v>19279279147.60983</v>
       </c>
       <c r="G103" s="18" t="n">
-        <v>376741119.6012489</v>
+        <v>20529354641.50407</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>377192267.7200502</v>
+        <v>21014568193.43768</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>377513130.1882982</v>
+        <v>21289990842.36025</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>377841756.0845569</v>
+        <v>21471618417.3754</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>377370048.6136078</v>
+        <v>21584745164.50915</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>376846607.0506854</v>
+        <v>21661346326.16674</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>377108469.2862191</v>
+        <v>21732646086.72334</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>377426636.4027589</v>
+        <v>21797878133.89196</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>377745981.5521668</v>
+        <v>21852109459.47982</v>
       </c>
     </row>
     <row r="104">
@@ -24167,40 +24167,40 @@
         </is>
       </c>
       <c r="D104" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="E104" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="F104" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="G104" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="H104" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="I104" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="J104" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="K104" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="L104" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="M104" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="N104" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
       <c r="O104" s="19" t="n">
-        <v>378389450.1370254</v>
+        <v>17322234294.46179</v>
       </c>
     </row>
     <row r="105">
@@ -24220,40 +24220,40 @@
         </is>
       </c>
       <c r="D105" s="18" t="n">
-        <v>-341432569.8796971</v>
+        <v>-17322234294.46179</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>-400524291.4939544</v>
+        <v>-9350915099.075556</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>-396523478.1175651</v>
+        <v>-6033193857.591728</v>
       </c>
       <c r="G105" s="18" t="n">
-        <v>-392555961.4528939</v>
+        <v>-4441401117.518615</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>-388634831.3769153</v>
+        <v>-3506862967.700128</v>
       </c>
       <c r="I105" s="18" t="n">
-        <v>-384746335.4080915</v>
+        <v>-2892126213.763785</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>-391293121.9791849</v>
+        <v>-2514391256.469523</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>-397732351.4566109</v>
+        <v>-2227166658.462489</v>
       </c>
       <c r="L105" s="18" t="n">
-        <v>-393753819.8860762</v>
+        <v>-1955925171.354616</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>-389817355.5147429</v>
+        <v>-1741677322.097364</v>
       </c>
       <c r="N105" s="18" t="n">
-        <v>-385917453.2060013</v>
+        <v>-1568158539.104653</v>
       </c>
       <c r="O105" s="18" t="n">
-        <v>-277741831.8725704</v>
+        <v>-1059558497.056283</v>
       </c>
     </row>
     <row r="106">
@@ -24273,37 +24273,37 @@
         </is>
       </c>
       <c r="D106" s="18" t="n">
-        <v>7.519425857760544</v>
+        <v>100</v>
       </c>
       <c r="E106" s="18" t="n">
-        <v>8.820812599050031</v>
+        <v>53.98215345733547</v>
       </c>
       <c r="F106" s="18" t="n">
-        <v>8.73270202551835</v>
+        <v>34.82918978598877</v>
       </c>
       <c r="G106" s="18" t="n">
-        <v>8.6453247509662</v>
+        <v>25.63988595246403</v>
       </c>
       <c r="H106" s="18" t="n">
-        <v>8.558969055915359</v>
+        <v>20.24486511431918</v>
       </c>
       <c r="I106" s="18" t="n">
-        <v>8.473332067194354</v>
+        <v>16.69603449878545</v>
       </c>
       <c r="J106" s="18" t="n">
-        <v>8.617513028739014</v>
+        <v>14.51539803542212</v>
       </c>
       <c r="K106" s="18" t="n">
-        <v>8.759325242651913</v>
+        <v>12.85727130001094</v>
       </c>
       <c r="L106" s="18" t="n">
-        <v>8.671705385009346</v>
+        <v>11.29141390253542</v>
       </c>
       <c r="M106" s="18" t="n">
-        <v>8.585011980240182</v>
+        <v>10.05457663538362</v>
       </c>
       <c r="N106" s="18" t="n">
-        <v>8.499123787811955</v>
+        <v>9.052865308524433</v>
       </c>
       <c r="O106" s="18" t="n">
         <v>6.116754219142746</v>
@@ -24326,40 +24326,40 @@
         </is>
       </c>
       <c r="D107" s="18" t="n">
-        <v>352524132.6591883</v>
+        <v>12327482050.03255</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>374753911.7440073</v>
+        <v>19279279147.60983</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>376741119.6012489</v>
+        <v>20529354641.50407</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>377192267.7200502</v>
+        <v>21014568193.43768</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>377513130.1882982</v>
+        <v>21289990842.36025</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>377841756.0845569</v>
+        <v>21471618417.3754</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>377370048.6136078</v>
+        <v>21584745164.50915</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>376846607.0506854</v>
+        <v>21661346326.16674</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>377108469.2862191</v>
+        <v>21732646086.72334</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>377426636.4027589</v>
+        <v>21797878133.89196</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>377745981.5521668</v>
+        <v>21852109459.47982</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>385964854.7369099</v>
+        <v>22002979003.44093</v>
       </c>
     </row>
     <row r="108">

--- a/backend/Rwanda/financial-statements-CleanStep.xlsx
+++ b/backend/Rwanda/financial-statements-CleanStep.xlsx
@@ -644,40 +644,40 @@
         </is>
       </c>
       <c r="D2" s="18" t="n">
-        <v>5.641200851700228</v>
+        <v>7.566198474185208</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>10.17871584032626</v>
+        <v>13.65209044755598</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>10.07692868192302</v>
+        <v>13.51556954308045</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>9.976159395103771</v>
+        <v>13.38041384764962</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>9.876397801152752</v>
+        <v>13.24660970917315</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>9.777633823141219</v>
+        <v>13.11414361208141</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>14.07669452410551</v>
+        <v>18.88021139998192</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>18.31072519586925</v>
+        <v>24.55905837787261</v>
       </c>
       <c r="L2" s="18" t="n">
-        <v>18.12761794391055</v>
+        <v>24.31346779409387</v>
       </c>
       <c r="M2" s="18" t="n">
-        <v>17.94634176447144</v>
+        <v>24.07033311615292</v>
       </c>
       <c r="N2" s="18" t="n">
-        <v>17.76687834682674</v>
+        <v>23.82962978499141</v>
       </c>
       <c r="O2" s="18" t="n">
-        <v>10.92849319237411</v>
+        <v>14.65772105816139</v>
       </c>
     </row>
     <row r="3" ht="15.5" customHeight="1">
@@ -703,16 +703,16 @@
         <v>80.43526738209385</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>-0.9999999999998233</v>
+        <v>-0.9999999999998122</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>-1.000000000000167</v>
+        <v>-1.000000000000179</v>
       </c>
       <c r="H3" s="18" t="n">
         <v>-0.9999999999998122</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>-1.000000000000056</v>
+        <v>-1.000000000000068</v>
       </c>
       <c r="J3" s="18" t="n">
         <v>43.96831358921918</v>
@@ -727,10 +727,10 @@
         <v>-1.000000000000023</v>
       </c>
       <c r="N3" s="18" t="n">
-        <v>-0.9999999999999232</v>
+        <v>-0.9999999999999343</v>
       </c>
       <c r="O3" s="18" t="n">
-        <v>-38.4895141451453</v>
+        <v>-38.48951414514529</v>
       </c>
     </row>
     <row r="4" ht="15.5" customHeight="1">
@@ -856,40 +856,40 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>5.641200851700228</v>
+        <v>7.566198474185208</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>10.17871584032626</v>
+        <v>13.65209044755598</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>10.07692868192302</v>
+        <v>13.51556954308045</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>9.976159395103771</v>
+        <v>13.38041384764962</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>9.876397801152752</v>
+        <v>13.24660970917315</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>9.777633823141219</v>
+        <v>13.11414361208141</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>14.07669452410551</v>
+        <v>18.88021139998192</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>18.31072519586925</v>
+        <v>24.55905837787261</v>
       </c>
       <c r="L6" s="18" t="n">
-        <v>18.12761794391055</v>
+        <v>24.31346779409387</v>
       </c>
       <c r="M6" s="18" t="n">
-        <v>17.94634176447144</v>
+        <v>24.07033311615292</v>
       </c>
       <c r="N6" s="18" t="n">
-        <v>17.76687834682674</v>
+        <v>23.82962978499141</v>
       </c>
       <c r="O6" s="18" t="n">
-        <v>10.92849319237411</v>
+        <v>14.65772105816139</v>
       </c>
     </row>
     <row r="7" ht="15.5" customHeight="1">
@@ -915,16 +915,16 @@
         <v>80.43526738209385</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>-0.9999999999998233</v>
+        <v>-0.9999999999998122</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>-1.000000000000167</v>
+        <v>-1.000000000000179</v>
       </c>
       <c r="H7" s="18" t="n">
         <v>-0.9999999999998122</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>-1.000000000000056</v>
+        <v>-1.000000000000068</v>
       </c>
       <c r="J7" s="18" t="n">
         <v>43.96831358921918</v>
@@ -939,10 +939,10 @@
         <v>-1.000000000000023</v>
       </c>
       <c r="N7" s="18" t="n">
-        <v>-0.9999999999999232</v>
+        <v>-0.9999999999999343</v>
       </c>
       <c r="O7" s="18" t="n">
-        <v>-38.4895141451453</v>
+        <v>-38.48951414514529</v>
       </c>
     </row>
     <row r="8" ht="15.5" customHeight="1">
@@ -1280,40 +1280,40 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>349.035557690684</v>
+        <v>260.2336816878687</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>486.3111395263507</v>
+        <v>362.5835118979995</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>777.1579506191596</v>
+        <v>579.4328694781595</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>1063.263849878372</v>
+        <v>792.747501401205</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>1344.510112052637</v>
+        <v>1002.438888579074</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>1620.772147156062</v>
+        <v>1208.414139299114</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>1346.453765359833</v>
+        <v>1003.88803622295</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>1222.417880023534</v>
+        <v>911.4094494679453</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>1405.408648661313</v>
+        <v>1047.843575986663</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>1584.597586120927</v>
+        <v>1181.443135932293</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>1759.889061985083</v>
+        <v>1312.136829246643</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>2996.170472142633</v>
+        <v>2233.882639605254</v>
       </c>
     </row>
     <row r="15" ht="15.5" customHeight="1">
@@ -1598,40 +1598,40 @@
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>-35.75763450367739</v>
+        <v>-26.66015158142582</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>-65.55473320547782</v>
+        <v>-48.87625113899046</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>-112.152550939361</v>
+        <v>-83.61861878697387</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>-158.7503686732449</v>
+        <v>-118.3609864349579</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>-205.3481864071275</v>
+        <v>-153.1033540829409</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>-251.9460041410113</v>
+        <v>-187.8457217309248</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>-205.2940513698419</v>
+        <v>-153.0629921205255</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>-170.1777882613999</v>
+        <v>-126.8810337656457</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>-173.1508903819558</v>
+        <v>-129.0977171201592</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>-176.1239925025116</v>
+        <v>-131.3144004746726</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>-179.0970946230672</v>
+        <v>-133.5310838291858</v>
       </c>
       <c r="O20" s="18" t="n">
-        <v>-293.0386458034463</v>
+        <v>-218.4835441374675</v>
       </c>
     </row>
     <row r="21" ht="15.5" customHeight="1">
@@ -1810,40 +1810,40 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>7.658360833869532</v>
+        <v>9.58335845635451</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>16.85134585319585</v>
+        <v>20.32472046042557</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>21.37846125503981</v>
+        <v>24.81710211619724</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>25.81334921426157</v>
+        <v>29.21760366680742</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>30.15740156817334</v>
+        <v>33.52761347619374</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>34.41199154008551</v>
+        <v>37.74850132902571</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>42.9753110115984</v>
+        <v>47.7788278874748</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>49.47151234882244</v>
+        <v>55.71984553082579</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>49.51574981883086</v>
+        <v>55.70159966901417</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>49.55415538820424</v>
+        <v>55.67814673988572</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>49.58684127120826</v>
+        <v>55.64959270937293</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>42.953201650029</v>
+        <v>46.68242951581628</v>
       </c>
     </row>
     <row r="25" ht="15.5" customHeight="1">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>2.017159982169304</v>
+        <v>2.017159982169303</v>
       </c>
       <c r="E25" s="18" t="n">
         <v>6.67263001286959</v>
@@ -1881,7 +1881,7 @@
         <v>24.63435771694429</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>28.89861648749289</v>
+        <v>28.89861648749288</v>
       </c>
       <c r="K25" s="18" t="n">
         <v>31.16078715295319</v>
@@ -1893,7 +1893,7 @@
         <v>31.6078136237328</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>31.81996292438152</v>
+        <v>31.81996292438151</v>
       </c>
       <c r="O25" s="18" t="n">
         <v>32.0247084576549</v>
@@ -1916,40 +1916,40 @@
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>135.7576345036774</v>
+        <v>126.6601515814258</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>165.5547332054778</v>
+        <v>148.8762511389905</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>212.152550939361</v>
+        <v>183.6186187869739</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>258.750368673245</v>
+        <v>218.3609864349579</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>305.3481864071275</v>
+        <v>253.1033540829409</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>351.9460041410112</v>
+        <v>287.8457217309248</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>305.2940513698419</v>
+        <v>253.0629921205255</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>270.1777882613999</v>
+        <v>226.8810337656457</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>273.1508903819558</v>
+        <v>229.0977171201592</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>276.1239925025116</v>
+        <v>231.3144004746726</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>279.0970946230672</v>
+        <v>233.5310838291858</v>
       </c>
       <c r="O26" s="18" t="n">
-        <v>393.0386458034463</v>
+        <v>318.4835441374674</v>
       </c>
     </row>
     <row r="27" ht="15.5" customHeight="1">
@@ -1969,40 +1969,40 @@
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>35.75763450367739</v>
+        <v>26.66015158142581</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>65.55473320547782</v>
+        <v>48.87625113899046</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>112.152550939361</v>
+        <v>83.61861878697387</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>158.7503686732449</v>
+        <v>118.3609864349579</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>205.3481864071275</v>
+        <v>153.1033540829409</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>251.9460041410112</v>
+        <v>187.8457217309248</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>205.2940513698419</v>
+        <v>153.0629921205255</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>170.1777882613999</v>
+        <v>126.8810337656457</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>173.1508903819558</v>
+        <v>129.0977171201592</v>
       </c>
       <c r="M27" s="18" t="n">
-        <v>176.1239925025116</v>
+        <v>131.3144004746726</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>179.0970946230672</v>
+        <v>133.5310838291858</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>293.0386458034463</v>
+        <v>218.4835441374675</v>
       </c>
     </row>
     <row r="28" ht="15.5" customHeight="1">
@@ -2075,40 +2075,40 @@
         </is>
       </c>
       <c r="D29" s="19" t="n">
-        <v>21.48882196227302</v>
+        <v>16.02162052306769</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>33.39825755878961</v>
+        <v>24.90104900482891</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>55.22443565802008</v>
+        <v>41.1741952754201</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>77.27108020269742</v>
+        <v>57.61171676086582</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>99.5404181266137</v>
+        <v>74.21527381687143</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>122.0346988578425</v>
+        <v>90.98654357041264</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>106.2537926807887</v>
+        <v>79.22062681970463</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>103.1733082726524</v>
+        <v>76.92388145595059</v>
       </c>
       <c r="L29" s="19" t="n">
-        <v>125.7042848639421</v>
+        <v>93.72251088261369</v>
       </c>
       <c r="M29" s="19" t="n">
-        <v>148.4628470773663</v>
+        <v>110.6908234347989</v>
       </c>
       <c r="N29" s="19" t="n">
-        <v>171.451293757592</v>
+        <v>127.8305330834702</v>
       </c>
       <c r="O29" s="19" t="n">
-        <v>300.2238886339342</v>
+        <v>223.8407123525646</v>
       </c>
     </row>
     <row r="30" ht="15.5" customHeight="1">
@@ -2128,40 +2128,40 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>6.446133226313441</v>
+        <v>8.371130848798419</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>13.45183212066637</v>
+        <v>16.92520672789609</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>15.81353425878666</v>
+        <v>19.25217511994409</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>18.104663086922</v>
+        <v>21.50891753946785</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>20.32639390105821</v>
+        <v>23.69660580907861</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>22.47988554859257</v>
+        <v>25.81639533753277</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>28.01828919564739</v>
+        <v>32.8218060715238</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>30.57973139553002</v>
+        <v>36.82806457753337</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>26.72855731957046</v>
+        <v>32.91440716975377</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>22.91050545843548</v>
+        <v>29.03449681011696</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>19.12529848523634</v>
+        <v>25.18804992340101</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>10.14325441878869</v>
+        <v>13.87248228457597</v>
       </c>
     </row>
     <row r="31" ht="15.5" customHeight="1">
@@ -2181,40 +2181,40 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>114.2688125414044</v>
+        <v>110.6385310583581</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>132.1564756466882</v>
+        <v>123.9752021341615</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>156.9281152813409</v>
+        <v>142.4444235115538</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>181.4792884705475</v>
+        <v>160.7492696740921</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>205.8077682805138</v>
+        <v>178.8880802660694</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>229.9113052831687</v>
+        <v>196.8591781605121</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>199.0402586890532</v>
+        <v>173.8423653008209</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>167.0044799887475</v>
+        <v>149.9571523096951</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>147.4466055180137</v>
+        <v>135.3752062375455</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>127.6611454251453</v>
+        <v>120.6235770398737</v>
       </c>
       <c r="N31" s="19" t="n">
-        <v>107.6458008654752</v>
+        <v>105.7005507457156</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>92.81475716951209</v>
+        <v>94.64283178490287</v>
       </c>
     </row>
     <row r="32" ht="15.5" customHeight="1">
@@ -2287,40 +2287,40 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>6.446133226313441</v>
+        <v>8.371130848798419</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>13.45183212066637</v>
+        <v>16.92520672789609</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>15.81353425878666</v>
+        <v>19.25217511994409</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>18.104663086922</v>
+        <v>21.50891753946785</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>20.32639390105821</v>
+        <v>23.69660580907861</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>22.47988554859257</v>
+        <v>25.81639533753277</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>28.01828919564739</v>
+        <v>32.8218060715238</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>30.57973139553002</v>
+        <v>36.82806457753337</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>26.72855731957046</v>
+        <v>32.91440716975377</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>22.91050545843548</v>
+        <v>29.03449681011696</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>19.12529848523634</v>
+        <v>25.18804992340101</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>10.14325441878869</v>
+        <v>13.87248228457597</v>
       </c>
     </row>
     <row r="34" ht="15.5" customHeight="1">
@@ -2340,28 +2340,28 @@
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>0.8049323746132124</v>
+        <v>0.8049323746132115</v>
       </c>
       <c r="E34" s="19" t="n">
         <v>3.273116280340108</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>5.736605576863639</v>
+        <v>5.73660557686364</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>8.128503691818231</v>
+        <v>8.12850369181823</v>
       </c>
       <c r="H34" s="19" t="n">
         <v>10.44999609990546</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>12.70225172545135</v>
+        <v>12.70225172545136</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>13.94159467154188</v>
+        <v>13.94159467154187</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>12.26900619966077</v>
+        <v>12.26900619966076</v>
       </c>
       <c r="L34" s="19" t="n">
         <v>8.600939375659905</v>
@@ -2370,10 +2370,10 @@
         <v>4.964163693964039</v>
       </c>
       <c r="N34" s="19" t="n">
-        <v>1.358420138409603</v>
+        <v>1.358420138409599</v>
       </c>
       <c r="O34" s="19" t="n">
-        <v>-0.7852387735854194</v>
+        <v>-0.7852387735854212</v>
       </c>
     </row>
     <row r="35" ht="15.5" customHeight="1">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>-0.2253810648916995</v>
+        <v>-0.2253810648916992</v>
       </c>
       <c r="E36" s="19" t="n">
         <v>-0.9164725584952303</v>
@@ -2455,19 +2455,19 @@
         <v>-1.606249561521819</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>-2.275981033709105</v>
+        <v>-2.275981033709104</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>-2.92599890797353</v>
+        <v>-2.925998907973529</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>-3.556630483126378</v>
+        <v>-3.55663048312638</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>-3.903646508031727</v>
+        <v>-3.903646508031725</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>-3.435321735905014</v>
+        <v>-3.435321735905013</v>
       </c>
       <c r="L36" s="19" t="n">
         <v>-2.408263025184774</v>
@@ -2476,7 +2476,7 @@
         <v>-1.389965834309931</v>
       </c>
       <c r="N36" s="19" t="n">
-        <v>-0.3803576387546888</v>
+        <v>-0.3803576387546878</v>
       </c>
       <c r="O36" s="19" t="n">
         <v>0</v>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>-0.7852387735854194</v>
+        <v>-0.7852387735854212</v>
       </c>
     </row>
     <row r="38" ht="15.5" customHeight="1">
@@ -2552,40 +2552,40 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>6.220752161421741</v>
+        <v>8.145749783906719</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>12.53535956217114</v>
+        <v>16.00873416940086</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>14.20728469726484</v>
+        <v>17.64592555842227</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>15.8286820532129</v>
+        <v>19.23293650575875</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>17.40039499308469</v>
+        <v>20.77060690110508</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>18.92325506546619</v>
+        <v>22.25976485440639</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>24.11464268761566</v>
+        <v>28.91815956349207</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>27.144409659625</v>
+        <v>33.39274284162835</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>24.32029429438568</v>
+        <v>30.506144144569</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>21.52053962412555</v>
+        <v>27.64453097580703</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>18.74494084648165</v>
+        <v>24.80769228464632</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>10.14325441878869</v>
+        <v>13.87248228457597</v>
       </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
@@ -2605,40 +2605,40 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>110.2735450298111</v>
+        <v>107.6597423620179</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>123.1526624656155</v>
+        <v>117.2621455365963</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>140.9882430025654</v>
+        <v>130.5599849283187</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>158.6650876987942</v>
+        <v>143.7394741653463</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>176.1815931619699</v>
+        <v>156.79941779157</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>193.5361398038815</v>
+        <v>169.7386082755687</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>171.3089862561183</v>
+        <v>153.166503016591</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>148.2432255918982</v>
+        <v>135.9691496629805</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>134.1615559729699</v>
+        <v>125.4701484910327</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>119.9160247061047</v>
+        <v>114.8489754687091</v>
       </c>
       <c r="N39" s="19" t="n">
-        <v>105.5049766231421</v>
+        <v>104.1043965369152</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>92.81475716951209</v>
+        <v>94.64283178490287</v>
       </c>
     </row>
     <row r="40" ht="15.5" customHeight="1">
@@ -2817,40 +2817,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>148.922428219931</v>
+        <v>214.4942041409722</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>267.4653394661041</v>
+        <v>398.6088913081865</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>390.7151100409467</v>
+        <v>587.4304378040704</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>518.5963650303744</v>
+        <v>780.8834687145394</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>651.0292805535145</v>
+        <v>978.8881601587207</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>787.9351660586706</v>
+        <v>1181.365821584918</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>944.1052300356724</v>
+        <v>1355.434436145405</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>-62504588519.96039</v>
+        <v>1500.553585379281</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>-125009177981.2272</v>
+        <v>1648.471549711873</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>-187513767439.8918</v>
+        <v>1798.991516858651</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>-250018356895.9846</v>
+        <v>1952.083620707639</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>-259248690699.5797</v>
+        <v>2157.1935306402</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -2870,40 +2870,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>148.7566342487938</v>
+        <v>214.328410169835</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>266.9169041225805</v>
+        <v>398.060455964663</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>389.7862169527453</v>
+        <v>586.501544715869</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>517.2946781959231</v>
+        <v>779.5817818800881</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>649.362348737047</v>
+        <v>977.2212283422532</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>785.9104243285108</v>
+        <v>1179.341079854758</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>941.7300012832758</v>
+        <v>1353.059207393008</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>-62504588522.52155</v>
+        <v>1497.992424791367</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>-125009177983.8071</v>
+        <v>1645.8917032564</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>-187513767442.4897</v>
+        <v>1796.393614369029</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>-250018356898.5999</v>
+        <v>1949.468281289197</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>-259248690702.2119</v>
+        <v>2154.561362821763</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -3029,40 +3029,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>190.1381668768381</v>
+        <v>255.7099427978793</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>381.8365787645505</v>
+        <v>512.9801306066329</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>575.3108865734682</v>
+        <v>772.0262143365919</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>770.5150250235812</v>
+        <v>1032.802128707746</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>967.3981867717508</v>
+        <v>1295.257066376957</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>1165.910407638637</v>
+        <v>1559.341063164885</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>1412.995503655721</v>
+        <v>1824.324709765453</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>-62504587932.24532</v>
+        <v>2088.268647852986</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>-125009177279.96</v>
+        <v>2349.738823795197</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>-187513766630.2922</v>
+        <v>2608.591151079998</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>-250018355983.2202</v>
+        <v>2864.847962110127</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>-259248689737.4312</v>
+        <v>3119.342080395842</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -3082,40 +3082,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>43.26137433877072</v>
+        <v>58.65648807822183</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>55.79673390094186</v>
+        <v>74.66522224762269</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>70.0040185982067</v>
+        <v>92.31114780604497</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>85.8327006514196</v>
+        <v>111.5440843118037</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>103.2330956445043</v>
+        <v>132.3146912129088</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>122.1563507099705</v>
+        <v>154.5744560673152</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>146.2709933975862</v>
+        <v>183.4926156308072</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>174.4827081285558</v>
+        <v>216.8853584724356</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>-1563061065.755302</v>
+        <v>247.3915026170046</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>-4383374817.854751</v>
+        <v>275.0360335928117</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>-7175485434.993605</v>
+        <v>299.843725877458</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>-9939674954.375303</v>
+        <v>313.716208162034</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -3135,40 +3135,40 @@
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
     </row>
     <row r="50" ht="15.5" customHeight="1">
@@ -3188,40 +3188,40 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>6.220752161421741</v>
+        <v>8.145749783906719</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>12.53535956217114</v>
+        <v>16.00873416940086</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>14.20728469726484</v>
+        <v>17.64592555842227</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>15.8286820532129</v>
+        <v>19.23293650575875</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>17.40039499308469</v>
+        <v>20.77060690110508</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>18.92325506546619</v>
+        <v>22.25976485440639</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>24.11464268761566</v>
+        <v>28.91815956349207</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>27.144409659625</v>
+        <v>33.39274284162835</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>24.32029429438568</v>
+        <v>30.506144144569</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>21.52053962412555</v>
+        <v>27.64453097580703</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>18.74494084648165</v>
+        <v>24.80769228464632</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>10.14325441878869</v>
+        <v>13.87248228457597</v>
       </c>
     </row>
     <row r="51" ht="15.5" customHeight="1">
@@ -3244,37 +3244,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>6.220752161421741</v>
+        <v>8.145749783906719</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>18.75611172359288</v>
+        <v>24.15448395330758</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>32.96339642085772</v>
+        <v>41.80040951172985</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>48.79207847407062</v>
+        <v>61.0333460174886</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>66.19247346715531</v>
+        <v>81.80395291859368</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>85.1157285326215</v>
+        <v>104.0637177730001</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>110.2976762915818</v>
+        <v>132.9818773364922</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>-1563061127.116218</v>
+        <v>166.3746201781206</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>-4383374876.415913</v>
+        <v>196.8807643226896</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>-7175485490.779168</v>
+        <v>224.5252952984966</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>-9939675001.559179</v>
+        <v>249.3329875831429</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -3294,40 +3294,40 @@
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>147.0425865092046</v>
+        <v>197.2192486907947</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>289.5476580297832</v>
+        <v>388.3526054082187</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>432.154516708765</v>
+        <v>579.6224830301181</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>574.8621446745661</v>
+        <v>771.0275163474485</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>717.6695342343182</v>
+        <v>962.5663538032552</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>859.5083827007372</v>
+        <v>1154.237657356154</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>1563062291.561279</v>
+        <v>1340.142893121152</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>-37922175429.41056</v>
+        <v>1520.369281908259</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>-77435616287.93544</v>
+        <v>1700.841261279145</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>-116976978252.6377</v>
+        <v>1881.556375327972</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>-157890383787.9721</v>
+        <v>2062.51219270796</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>-163688835192.558</v>
+        <v>2252.639918814778</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -3347,40 +3347,40 @@
         </is>
       </c>
       <c r="D53" s="18" t="n">
-        <v>147.0425865092046</v>
+        <v>197.2192486907947</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>289.5476580297832</v>
+        <v>388.3526054082187</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>432.154516708765</v>
+        <v>579.6224830301181</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>574.8621446745661</v>
+        <v>771.0275163474485</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>717.6695342343182</v>
+        <v>962.5663538032552</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>859.5083827007372</v>
+        <v>1154.237657356154</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>1563062291.561279</v>
+        <v>1340.142893121152</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>-37922175429.41056</v>
+        <v>1520.369281908259</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>-77435616287.93544</v>
+        <v>1700.841261279145</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>-116976978252.6377</v>
+        <v>1881.556375327972</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>-157890383787.9721</v>
+        <v>2062.51219270796</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>-163688835192.558</v>
+        <v>2252.639918814778</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -3612,40 +3612,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>190.1381668768381</v>
+        <v>255.7099427978794</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>344.7959565872015</v>
+        <v>462.4693923123178</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>501.2296422187703</v>
+        <v>671.0047377479617</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>659.3931584915345</v>
+        <v>881.2699138248008</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>819.235698062355</v>
+        <v>1093.214113199697</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>979.639991680548</v>
+        <v>1306.787371693309</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>1563062435.457044</v>
+        <v>1521.260279999563</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>-37922175257.48901</v>
+        <v>1734.693479792781</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>-78998677356.27058</v>
+        <v>1945.652917440676</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>-121360353073.0904</v>
+        <v>2153.994506431162</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>-165065869225.581</v>
+        <v>2359.740579166976</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>-173628510149.5655</v>
+        <v>2563.723959158375</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -3665,40 +3665,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>0</v>
+        <v>-2.842170943040401e-14</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>37.04062217734901</v>
+        <v>50.51073829431505</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>74.0812443546979</v>
+        <v>101.0214765886302</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>111.1218665320467</v>
+        <v>151.5322148829453</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>148.1624887093958</v>
+        <v>202.0429531772604</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>186.2704159580893</v>
+        <v>252.5536914715753</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>-1563061022.46154</v>
+        <v>303.0644297658898</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>-24582412674.75632</v>
+        <v>353.5751680602048</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>-46010499923.68939</v>
+        <v>404.0859063545208</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>-66153413557.20181</v>
+        <v>454.5966446488355</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>-84952486757.63922</v>
+        <v>505.1073829431512</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>-85620179587.86566</v>
+        <v>555.6181212374668</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>2.017159982169304</v>
+        <v>2.017159982169303</v>
       </c>
       <c r="E61" s="18" t="n">
         <v>6.67263001286959</v>
@@ -3789,7 +3789,7 @@
         <v>24.63435771694429</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>28.89861648749289</v>
+        <v>28.89861648749288</v>
       </c>
       <c r="K61" s="18" t="n">
         <v>31.16078715295319</v>
@@ -3801,7 +3801,7 @@
         <v>31.6078136237328</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>31.81996292438152</v>
+        <v>31.81996292438151</v>
       </c>
       <c r="O61" s="18" t="n">
         <v>32.0247084576549</v>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>-0.2253810648916995</v>
+        <v>-0.2253810648916992</v>
       </c>
       <c r="E62" s="18" t="n">
         <v>-0.9164725584952303</v>
@@ -3833,19 +3833,19 @@
         <v>-1.606249561521819</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>-2.275981033709105</v>
+        <v>-2.275981033709104</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>-2.92599890797353</v>
+        <v>-2.925998907973529</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>-3.556630483126378</v>
+        <v>-3.55663048312638</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>-3.903646508031727</v>
+        <v>-3.903646508031725</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>-3.435321735905014</v>
+        <v>-3.435321735905013</v>
       </c>
       <c r="L62" s="18" t="n">
         <v>-2.408263025184774</v>
@@ -3854,7 +3854,7 @@
         <v>-1.389965834309931</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>-0.3803576387546888</v>
+        <v>-0.3803576387546878</v>
       </c>
       <c r="O62" s="18" t="n">
         <v>0</v>
@@ -3930,13 +3930,13 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>1.460190975003198</v>
+        <v>1.460190975003197</v>
       </c>
       <c r="E64" s="18" t="n">
         <v>4.99087470960171</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>8.934367522239265</v>
+        <v>8.934367522239267</v>
       </c>
       <c r="G64" s="18" t="n">
         <v>12.8156212929488</v>
@@ -3945,13 +3945,13 @@
         <v>16.62451489501482</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>20.36210740643319</v>
+        <v>20.3621074064332</v>
       </c>
       <c r="J64" s="18" t="n">
         <v>24.29399593498742</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>27.35360174601361</v>
+        <v>27.3536017460136</v>
       </c>
       <c r="L64" s="18" t="n">
         <v>28.94249711461765</v>
@@ -4301,40 +4301,40 @@
         </is>
       </c>
       <c r="D71" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="E71" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="F71" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="G71" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="I71" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="J71" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="K71" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="L71" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="M71" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="N71" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="O71" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
     </row>
     <row r="72" ht="15.5" customHeight="1">
@@ -4407,40 +4407,40 @@
         </is>
       </c>
       <c r="D73" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="E73" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="F73" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="G73" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="I73" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="J73" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="K73" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="L73" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="M73" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="N73" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="O73" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
     </row>
     <row r="74" ht="15.5" customHeight="1">
@@ -4460,40 +4460,40 @@
         </is>
       </c>
       <c r="D74" s="18" t="n">
-        <v>189.7244095382538</v>
+        <v>255.296185459295</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>189.7244095382538</v>
+        <v>255.296185459295</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>189.7244095382538</v>
+        <v>255.296185459295</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>189.7244095382538</v>
+        <v>255.296185459295</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>189.7244095382538</v>
+        <v>255.296185459295</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>189.7244095382538</v>
+        <v>255.296185459295</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>189.7244095382538</v>
+        <v>255.296185459295</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>189.7244095382538</v>
+        <v>255.296185459295</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>189.7244095382538</v>
+        <v>255.296185459295</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>189.7244095382538</v>
+        <v>255.296185459295</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>189.7244095382538</v>
+        <v>255.296185459295</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>189.7244095382538</v>
+        <v>255.296185459295</v>
       </c>
     </row>
     <row r="75" ht="15.5" customHeight="1">
@@ -4513,40 +4513,40 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>148.7566342487938</v>
+        <v>214.328410169835</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>118.1602698737867</v>
+        <v>183.732045794828</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>122.8693128301648</v>
+        <v>188.4410887512061</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>127.5084612431778</v>
+        <v>193.080237164219</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>132.0676705411239</v>
+        <v>197.6394464621652</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>136.5480755914638</v>
+        <v>202.119851512505</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>108.1463516172088</v>
+        <v>173.71812753825</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>79.36144147731802</v>
+        <v>144.9332173983592</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>82.32750254399153</v>
+        <v>147.8992784650328</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>84.93013519158764</v>
+        <v>150.5019111126289</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>87.50289099912655</v>
+        <v>153.0746669201678</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>139.5213056115246</v>
+        <v>205.0930815325658</v>
       </c>
     </row>
     <row r="76" ht="15.5" customHeight="1">
@@ -4569,37 +4569,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>148.7566342487938</v>
+        <v>214.328410169835</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>266.9169041225805</v>
+        <v>398.060455964663</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>389.7862169527453</v>
+        <v>586.501544715869</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>517.2946781959231</v>
+        <v>779.5817818800881</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>649.362348737047</v>
+        <v>977.2212283422532</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>785.9104243285108</v>
+        <v>1179.341079854758</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>941.7300012832758</v>
+        <v>1353.059207393008</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>-62504588522.52155</v>
+        <v>1497.992424791367</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>-125009177983.8071</v>
+        <v>1645.8917032564</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>-187513767442.4897</v>
+        <v>1796.393614369029</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>-250018356898.5999</v>
+        <v>1949.468281289197</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -4619,40 +4619,40 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>148.7566342487938</v>
+        <v>214.328410169835</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>118.1602698737867</v>
+        <v>183.732045794828</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>122.8693128301648</v>
+        <v>188.4410887512061</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>127.5084612431778</v>
+        <v>193.080237164219</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>132.0676705411239</v>
+        <v>197.6394464621652</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>136.5480755914638</v>
+        <v>202.119851512505</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>108.1463516172088</v>
+        <v>173.71812753825</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>79.36144147731802</v>
+        <v>144.9332173983592</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>82.32750254399153</v>
+        <v>147.8992784650328</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>84.93013519158764</v>
+        <v>150.5019111126289</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>87.50289099912655</v>
+        <v>153.0746669201678</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>139.5213056115246</v>
+        <v>205.0930815325658</v>
       </c>
     </row>
     <row r="78" ht="15.5" customHeight="1">
@@ -4672,40 +4672,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>148.7566342487938</v>
+        <v>214.328410169835</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>266.9169041225805</v>
+        <v>398.060455964663</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>389.7862169527453</v>
+        <v>586.501544715869</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>517.2946781959231</v>
+        <v>779.5817818800881</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>649.362348737047</v>
+        <v>977.2212283422532</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>785.9104243285108</v>
+        <v>1179.341079854758</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>941.7300012832758</v>
+        <v>1353.059207393008</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>-62504588522.52155</v>
+        <v>1497.992424791367</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>-125009177983.8071</v>
+        <v>1645.8917032564</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>-187513767442.4897</v>
+        <v>1796.393614369029</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>-250018356898.5999</v>
+        <v>1949.468281289197</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>-259248690702.2119</v>
+        <v>2154.561362821763</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -4831,40 +4831,40 @@
         </is>
       </c>
       <c r="D81" s="18" t="n">
-        <v>752.108768679556</v>
+        <v>560.7567183073692</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>752.1087686795561</v>
+        <v>560.7567183073693</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>752.1087686795562</v>
+        <v>560.7567183073693</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>752.108768679556</v>
+        <v>560.7567183073692</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>752.1087686795562</v>
+        <v>560.7567183073693</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>752.1087686795561</v>
+        <v>560.7567183073693</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>752.108768679556</v>
+        <v>560.7567183073693</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>752.1087686795557</v>
+        <v>560.7567183073689</v>
       </c>
       <c r="L81" s="18" t="n">
-        <v>752.1087686795562</v>
+        <v>560.7567183073694</v>
       </c>
       <c r="M81" s="18" t="n">
-        <v>752.1087686795562</v>
+        <v>560.7567183073694</v>
       </c>
       <c r="N81" s="18" t="n">
-        <v>752.1087686795557</v>
+        <v>560.7567183073691</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>752.1087686795561</v>
+        <v>560.7567183073693</v>
       </c>
     </row>
     <row r="82" ht="15.5" customHeight="1">
@@ -5653,37 +5653,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>43.26137433877072</v>
+        <v>58.65648807822183</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>92.83735607829084</v>
+        <v>125.1759605419378</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>144.0852629529047</v>
+        <v>193.3326243946752</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>196.9545671834666</v>
+        <v>263.0762991947491</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>251.3955843539003</v>
+        <v>334.3576443901693</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>307.3594615967154</v>
+        <v>407.1281475388908</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>388.3677584732696</v>
+        <v>486.557045396698</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>-21762098726.65362</v>
+        <v>570.4605265326414</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>-44781450353.56084</v>
+        <v>651.4774089715255</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>-67772598845.53159</v>
+        <v>729.6326782416476</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>-90735826233.91908</v>
+        <v>804.951108820609</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -5703,40 +5703,40 @@
         </is>
       </c>
       <c r="D97" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="E97" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="F97" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="G97" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="H97" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="I97" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="J97" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="K97" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="L97" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="M97" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="N97" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
       <c r="O97" s="19" t="n">
-        <v>37.04062217734898</v>
+        <v>50.5107382943151</v>
       </c>
     </row>
     <row r="98" ht="15.5" customHeight="1">
@@ -5756,40 +5756,40 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>6.220752161421741</v>
+        <v>8.145749783906719</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>12.53535956217114</v>
+        <v>16.00873416940086</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>14.20728469726484</v>
+        <v>17.64592555842227</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>15.8286820532129</v>
+        <v>19.23293650575875</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>17.40039499308469</v>
+        <v>20.77060690110508</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>18.92325506546619</v>
+        <v>22.25976485440639</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>24.11464268761566</v>
+        <v>28.91815956349207</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>27.144409659625</v>
+        <v>33.39274284162835</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>24.32029429438568</v>
+        <v>30.506144144569</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>21.52053962412555</v>
+        <v>27.64453097580703</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>18.74494084648165</v>
+        <v>24.80769228464632</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>10.14325441878869</v>
+        <v>13.87248228457597</v>
       </c>
     </row>
     <row r="99" ht="15.5" customHeight="1">
@@ -5862,40 +5862,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>43.26137433877072</v>
+        <v>58.65648807822183</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>92.83735607829084</v>
+        <v>125.1759605419378</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>144.0852629529047</v>
+        <v>193.3326243946752</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>196.9545671834666</v>
+        <v>263.0762991947491</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>251.3955843539003</v>
+        <v>334.3576443901693</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>307.3594615967154</v>
+        <v>407.1281475388908</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>388.3677584732696</v>
+        <v>486.557045396698</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>-21762098726.65362</v>
+        <v>570.4605265326414</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>-44781450353.56084</v>
+        <v>651.4774089715255</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>-67772598845.53159</v>
+        <v>729.6326782416476</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>-90735826233.91908</v>
+        <v>804.951108820609</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>-95440102641.5406</v>
+        <v>869.3343293995</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -5968,40 +5968,40 @@
         </is>
       </c>
       <c r="D102" s="18" t="n">
-        <v>-13.29594922494596</v>
+        <v>-17.83304537159138</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>-13.29594922494596</v>
+        <v>-17.83304537159138</v>
       </c>
       <c r="F102" s="18" t="n">
-        <v>-13.29594922494596</v>
+        <v>-17.83304537159138</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>-13.29594922494596</v>
+        <v>-17.83304537159138</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>-13.29594922494596</v>
+        <v>-17.83304537159137</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>-13.29594922494596</v>
+        <v>-17.83304537159137</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>-13.29594922494596</v>
+        <v>-17.83304537159137</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>-13.29594922494596</v>
+        <v>-17.83304537159138</v>
       </c>
       <c r="L102" s="18" t="n">
-        <v>-13.29594922494595</v>
+        <v>-17.83304537159137</v>
       </c>
       <c r="M102" s="18" t="n">
-        <v>-13.29594922494595</v>
+        <v>-17.83304537159137</v>
       </c>
       <c r="N102" s="18" t="n">
-        <v>-13.29594922494596</v>
+        <v>-17.83304537159138</v>
       </c>
       <c r="O102" s="18" t="n">
-        <v>-13.29594922494596</v>
+        <v>-17.83304537159137</v>
       </c>
     </row>
     <row r="103" ht="15.5" customHeight="1">
@@ -6024,37 +6024,37 @@
         <v>0</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>147.0425865092046</v>
+        <v>197.2192486907947</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>289.5476580297832</v>
+        <v>388.3526054082187</v>
       </c>
       <c r="G103" s="18" t="n">
-        <v>432.154516708765</v>
+        <v>579.6224830301181</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>574.8621446745661</v>
+        <v>771.0275163474485</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>717.6695342343182</v>
+        <v>962.5663538032552</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>859.5083827007372</v>
+        <v>1154.237657356154</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>1563062291.561279</v>
+        <v>1340.142893121152</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>-37922175429.41056</v>
+        <v>1520.369281908259</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>-77435616287.93544</v>
+        <v>1700.841261279145</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>-116976978252.6377</v>
+        <v>1881.556375327972</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>-157890383787.9721</v>
+        <v>2062.51219270796</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -6074,40 +6074,40 @@
         </is>
       </c>
       <c r="D104" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="E104" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="F104" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="G104" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="H104" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="I104" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="J104" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="K104" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="L104" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="M104" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="N104" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
       <c r="O104" s="19" t="n">
-        <v>152.6837873609048</v>
+        <v>204.7854471649799</v>
       </c>
     </row>
     <row r="105" ht="15.5" customHeight="1">
@@ -6127,40 +6127,40 @@
         </is>
       </c>
       <c r="D105" s="18" t="n">
-        <v>-5.641200851700228</v>
+        <v>-7.566198474185208</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>-10.17871584032626</v>
+        <v>-13.65209044755598</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>-10.07692868192302</v>
+        <v>-13.51556954308045</v>
       </c>
       <c r="G105" s="18" t="n">
-        <v>-9.976159395103771</v>
+        <v>-13.38041384764962</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>-9.876397801152752</v>
+        <v>-13.24660970917315</v>
       </c>
       <c r="I105" s="18" t="n">
-        <v>-9.777633823141219</v>
+        <v>-13.11414361208141</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>-14.07669452410551</v>
+        <v>-18.88021139998192</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>-18.31072519586925</v>
+        <v>-24.55905837787261</v>
       </c>
       <c r="L105" s="18" t="n">
-        <v>-18.12761794391055</v>
+        <v>-24.31346779409387</v>
       </c>
       <c r="M105" s="18" t="n">
-        <v>-17.94634176447144</v>
+        <v>-24.07033311615292</v>
       </c>
       <c r="N105" s="18" t="n">
-        <v>-17.76687834682674</v>
+        <v>-23.82962978499141</v>
       </c>
       <c r="O105" s="18" t="n">
-        <v>-10.92849319237411</v>
+        <v>-14.65772105816139</v>
       </c>
     </row>
     <row r="106" ht="15.5" customHeight="1">
@@ -6233,40 +6233,40 @@
         </is>
       </c>
       <c r="D107" s="18" t="n">
-        <v>147.0425865092046</v>
+        <v>197.2192486907947</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>289.5476580297832</v>
+        <v>388.3526054082187</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>432.154516708765</v>
+        <v>579.6224830301181</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>574.8621446745661</v>
+        <v>771.0275163474485</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>717.6695342343182</v>
+        <v>962.5663538032552</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>859.5083827007372</v>
+        <v>1154.237657356154</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>1563062291.561279</v>
+        <v>1340.142893121152</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>-37922175429.41056</v>
+        <v>1520.369281908259</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>-77435616287.93544</v>
+        <v>1700.841261279145</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>-116976978252.6377</v>
+        <v>1881.556375327972</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>-157890383787.9721</v>
+        <v>2062.51219270796</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>-163688835192.558</v>
+        <v>2252.639918814778</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -6675,28 +6675,28 @@
         </is>
       </c>
       <c r="D2" s="18" t="n">
-        <v>2592.822120464618</v>
+        <v>354.4014304042142</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>5562.408786529471</v>
+        <v>418.0518325901635</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>8512.054378934978</v>
+        <v>469.4477587247691</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>400.3194</v>
+        <v>497.0304277487753</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>450.3366</v>
+        <v>546.0813859317948</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>499.6202</v>
+        <v>594.4071170007157</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>547.888</v>
+        <v>652.467719605139</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>607.9227</v>
+        <v>722.145418973485</v>
       </c>
       <c r="L2" s="18" t="n">
         <v>664.8774</v>
@@ -6731,28 +6731,28 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>114.5310602924323</v>
+        <v>17.95997327475585</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>53.0282060453501</v>
+        <v>12.29415161659908</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>-95.29702957501445</v>
+        <v>5.875556653829395</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>12.49432328285864</v>
+        <v>9.868803888966804</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>10.94372520465803</v>
+        <v>8.849547396028035</v>
       </c>
       <c r="J3" s="18" t="n">
-        <v>9.660898418438645</v>
+        <v>9.76781753512439</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>10.95747671056857</v>
+        <v>10.67910293102525</v>
       </c>
       <c r="L3" s="18" t="n">
-        <v>9.368740466509973</v>
+        <v>-7.930261339176026</v>
       </c>
       <c r="M3" s="18" t="n">
         <v>8.302929231765145</v>
@@ -6887,28 +6887,28 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>2316.528120464618</v>
+        <v>78.1074304042142</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>5243.031186529472</v>
+        <v>98.67423259016348</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>8140.294978934977</v>
+        <v>97.6883587247691</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0</v>
+        <v>96.71102774877525</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>0</v>
+        <v>95.74478593179478</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>0</v>
+        <v>94.78691700071575</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>0</v>
+        <v>104.579719605139</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>0</v>
+        <v>114.222718973485</v>
       </c>
       <c r="L6" s="18" t="n">
         <v>0</v>
@@ -6943,28 +6943,28 @@
         <v>0</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>126.3314284947206</v>
+        <v>26.33142849472057</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>55.2593278454881</v>
+        <v>-0.9991198710296967</v>
       </c>
       <c r="G7" s="18" t="n">
+        <v>-1.000457975496771</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>-0.9991020046756893</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>-1.00043978557891</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>10.33138634981585</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>9.22071641113118</v>
+      </c>
+      <c r="L7" s="18" t="n">
         <v>-100</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="18" t="n">
-        <v>0</v>
       </c>
       <c r="M7" s="18" t="n">
         <v>0</v>
@@ -6993,28 +6993,28 @@
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>-89.34388912300356</v>
+        <v>-22.03925371156894</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-94.25828607251162</v>
+        <v>-23.60334889068615</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>-95.63255374730683</v>
+        <v>-20.80920760813398</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>0</v>
+        <v>-19.45776804587464</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>0</v>
+        <v>-17.53306162751228</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>0</v>
+        <v>-15.94646401257702</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>0</v>
+        <v>-16.02833618626047</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>0</v>
+        <v>-15.8171354373265</v>
       </c>
       <c r="L8" s="18" t="n">
         <v>0</v>
@@ -7311,28 +7311,28 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>-6.144844246029611</v>
+        <v>-44.95604904794947</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>-4.35697228102834</v>
+        <v>-57.97190446098676</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>-3.825722959262599</v>
+        <v>-69.36823376565647</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>-101.4428214208459</v>
+        <v>-81.70431252958691</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>-107.4157783375887</v>
+        <v>-88.5825037239873</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>-111.8035185318645</v>
+        <v>-93.97481068438587</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>-116.426851015802</v>
+        <v>-97.76556392391262</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>-117.5708942789757</v>
+        <v>-98.97454669599414</v>
       </c>
       <c r="L14" s="18" t="n">
         <v>-117.865571967686</v>
@@ -7629,28 +7629,28 @@
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>4.023996162472419</v>
+        <v>29.43979726837795</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>2.145092459033007</v>
+        <v>28.54163099373543</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>1.610304562189018</v>
+        <v>29.19813705626024</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>38.58169251852395</v>
+        <v>31.07455628009699</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>38.07596362365395</v>
+        <v>31.40008145624954</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>37.65660395636525</v>
+        <v>31.65170715810481</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>37.31602079257074</v>
+        <v>31.33488352860265</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>35.15743037725027</v>
+        <v>29.59653199819682</v>
       </c>
       <c r="L20" s="18" t="n">
         <v>32.76243108879923</v>
@@ -7841,28 +7841,28 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>2474.672357837386</v>
+        <v>236.251667776982</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>5427.121095109038</v>
+        <v>282.7641411697304</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>8356.396408934977</v>
+        <v>313.7897887247692</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>225.85343</v>
+        <v>322.5644577487753</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>256.34977</v>
+        <v>352.0945559317947</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>286.49919</v>
+        <v>381.2861070007157</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>316.0436</v>
+        <v>420.623319605139</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>363.7965649999999</v>
+        <v>478.019283973485</v>
       </c>
       <c r="L24" s="18" t="n">
         <v>413.80353</v>
@@ -7894,19 +7894,19 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>158.1442373727677</v>
+        <v>158.1442373727678</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>184.0899085795663</v>
+        <v>184.0899085795669</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>216.1014300000006</v>
+        <v>216.1014300000001</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>225.85343</v>
+        <v>225.8534300000001</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>256.34977</v>
+        <v>256.3497699999999</v>
       </c>
       <c r="I25" s="18" t="n">
         <v>286.49919</v>
@@ -7915,7 +7915,7 @@
         <v>316.0436</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>363.7965649999999</v>
+        <v>363.796565</v>
       </c>
       <c r="L25" s="18" t="n">
         <v>413.80353</v>
@@ -7947,28 +7947,28 @@
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>95.44319829367777</v>
+        <v>66.6621654172005</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>97.56782184459256</v>
+        <v>67.63853645079887</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>98.17132312517633</v>
+        <v>66.84232332414646</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>56.41830748147605</v>
+        <v>64.89833212219675</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>56.92403637634605</v>
+        <v>64.47657162512606</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>57.34339604363474</v>
+        <v>64.14561604252404</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>57.68397920742926</v>
+        <v>64.46653328071038</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>59.84256962274973</v>
+        <v>66.19432477366949</v>
       </c>
       <c r="L26" s="18" t="n">
         <v>62.23756891120077</v>
@@ -8000,28 +8000,28 @@
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>6.099309170674202</v>
+        <v>44.62291170563156</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>3.309535772080943</v>
+        <v>44.03518756011272</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>2.538769377869495</v>
+        <v>46.03311571601248</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>56.41830748147605</v>
+        <v>45.4405640763221</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>56.92403637634605</v>
+        <v>46.94350999761377</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>57.34339604363474</v>
+        <v>48.19915202994702</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>57.68397920742926</v>
+        <v>48.43819709444991</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>59.84256962274973</v>
+        <v>50.37718933634301</v>
       </c>
       <c r="L27" s="18" t="n">
         <v>62.23756891120077</v>
@@ -8106,28 +8106,28 @@
         </is>
       </c>
       <c r="D29" s="19" t="n">
-        <v>0.3444793101272731</v>
+        <v>2.52023129342811</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>0.3635053125005482</v>
+        <v>4.836637437218035</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>0.3688277656151652</v>
+        <v>6.687606744370476</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>10.60607325555495</v>
+        <v>8.542368122713526</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>11.86024324431063</v>
+        <v>9.780779487112785</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>12.86062314184628</v>
+        <v>10.80980850073861</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>13.83200512016606</v>
+        <v>11.61496483820508</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>14.47377146833568</v>
+        <v>12.1844354322999</v>
       </c>
       <c r="L29" s="19" t="n">
         <v>15.05130087601154</v>
@@ -8159,28 +8159,28 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>2465.740622083982</v>
+        <v>227.3199320235781</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>5406.901443667006</v>
+        <v>262.5444897276985</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>8325.001588961204</v>
+        <v>282.3949687509955</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>183.395261179802</v>
+        <v>280.1062889285773</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>202.9387538218419</v>
+        <v>298.6835397536365</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>222.2449189374613</v>
+        <v>317.031835938177</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>240.2597037872246</v>
+        <v>344.8394233923635</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>275.8072226978641</v>
+        <v>390.0299416713491</v>
       </c>
       <c r="L30" s="19" t="n">
         <v>313.7308320693973</v>
@@ -8212,28 +8212,28 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>95.0987189835505</v>
+        <v>64.14193412377239</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>97.20431653209202</v>
+        <v>62.80189901358083</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>97.80249535956116</v>
+        <v>60.15471657977599</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>45.81223422592109</v>
+        <v>56.35596399948322</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>45.06379313203542</v>
+        <v>54.69579213801327</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>44.48277290178846</v>
+        <v>53.33580754178542</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>43.85197408726319</v>
+        <v>52.85156844250529</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>45.36879815441405</v>
+        <v>54.0098893413696</v>
       </c>
       <c r="L31" s="19" t="n">
         <v>47.18626803518923</v>
@@ -8318,28 +8318,28 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>2465.740622083982</v>
+        <v>227.3199320235781</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>5406.901443667006</v>
+        <v>262.5444897276985</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>8325.001588961204</v>
+        <v>282.3949687509955</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>183.395261179802</v>
+        <v>280.1062889285773</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>202.9387538218419</v>
+        <v>298.6835397536365</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>222.2449189374613</v>
+        <v>317.031835938177</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>240.2597037872246</v>
+        <v>344.8394233923635</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>275.8072226978641</v>
+        <v>390.0299416713491</v>
       </c>
       <c r="L33" s="19" t="n">
         <v>313.7308320693973</v>
@@ -8371,19 +8371,19 @@
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>149.212501619364</v>
+        <v>149.2125016193639</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>163.8702571375343</v>
+        <v>163.870257137535</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>184.7066100262273</v>
+        <v>184.7066100262264</v>
       </c>
       <c r="G34" s="19" t="n">
         <v>183.395261179802</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>202.9387538218419</v>
+        <v>202.9387538218417</v>
       </c>
       <c r="I34" s="19" t="n">
         <v>222.2449189374613</v>
@@ -8477,19 +8477,19 @@
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>-41.77950045342193</v>
+        <v>-41.7795004534219</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>-45.8836719985096</v>
+        <v>-45.8836719985098</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-51.71785080734364</v>
+        <v>-51.71785080734338</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>-51.35067313034455</v>
+        <v>-51.35067313034457</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>-56.82285107011572</v>
+        <v>-56.82285107011568</v>
       </c>
       <c r="I36" s="19" t="n">
         <v>-62.22857730248916</v>
@@ -8583,28 +8583,28 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>2423.96112163056</v>
+        <v>185.5404315701562</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>5361.017771668497</v>
+        <v>216.6608177291887</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>8273.283738153861</v>
+        <v>230.6771179436521</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>132.0445880494574</v>
+        <v>228.7556157982327</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>146.1159027517261</v>
+        <v>241.8606886835208</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>160.0163416349722</v>
+        <v>254.8032586356879</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>172.9869867268017</v>
+        <v>277.5667063319406</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>198.5812003424621</v>
+        <v>312.8039193159472</v>
       </c>
       <c r="L38" s="19" t="n">
         <v>225.886199089966</v>
@@ -8636,28 +8636,28 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>93.48736662259736</v>
+        <v>52.35318360835544</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>96.37942800340952</v>
+        <v>51.82630497917032</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>97.19491170812995</v>
+        <v>49.13797406771623</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>32.98480864266318</v>
+        <v>46.02446913247282</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>32.44593105506551</v>
+        <v>44.29022759507299</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>32.02759648928769</v>
+        <v>42.86679135360707</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>31.5734213428295</v>
+        <v>42.54106341075673</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>32.66553467117812</v>
+        <v>43.31591824823753</v>
       </c>
       <c r="L39" s="19" t="n">
         <v>33.97411298533626</v>
@@ -8848,40 +8848,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>943.5758334107995</v>
+        <v>943.5758334107996</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>1542.211229686728</v>
+        <v>1804.330947065474</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>2171.761815486074</v>
+        <v>2696.001250243566</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>2813.156803133768</v>
+        <v>3599.515955270006</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>3484.981521376297</v>
+        <v>4533.46039089128</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>4185.100606948038</v>
+        <v>5495.699193841769</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>4872.395924004825</v>
+        <v>6445.1142282773</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>5416.092325312885</v>
+        <v>7396.076523795097</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>24877210386.82224</v>
+        <v>8390.089435710555</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>49754415341.16072</v>
+        <v>9426.488326929337</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>74631620380.34578</v>
+        <v>10503.91472074392</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>99508825274.76175</v>
+        <v>11603.23802649004</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -8901,40 +8901,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>929.4422221198871</v>
+        <v>929.4422221198872</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>1525.768041584298</v>
+        <v>1787.887758963044</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>2152.472275760046</v>
+        <v>2676.711710517538</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>2792.948359298151</v>
+        <v>3579.30751143439</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>3462.060978910543</v>
+        <v>4510.539848425527</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>4159.499494619271</v>
+        <v>5470.098081513001</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>4844.168143182907</v>
+        <v>6416.886447455382</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>5383.692925312886</v>
+        <v>7363.677123795098</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>24877210350.07862</v>
+        <v>8353.345813792746</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>49754415300.20688</v>
+        <v>9385.534488573172</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>74631620335.33463</v>
+        <v>10458.90355911936</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>99508825223.14854</v>
+        <v>11551.62482649004</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -9063,37 +9063,37 @@
         <v>1231.438849026531</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>2184.799642962409</v>
+        <v>2446.919360341155</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>3154.154307398943</v>
+        <v>3678.393742156435</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>4120.576335851292</v>
+        <v>4906.93548798753</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>5102.803695444267</v>
+        <v>6151.282564959251</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>6098.842430906788</v>
+        <v>7409.441017800518</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>7107.738732009086</v>
+        <v>8680.457036281561</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>7997.472404142625</v>
+        <v>9977.456602624838</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>24877213297.81507</v>
+        <v>11301.08226360603</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>49754418565.50769</v>
+        <v>12650.8352953484</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>74631623901.94882</v>
+        <v>14025.51777082762</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>99508828953.35686</v>
+        <v>15281.8331370015</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -9113,40 +9113,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>2736.167198022183</v>
+        <v>497.7465079617789</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>8097.184969690679</v>
+        <v>714.4073256909676</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>15814.78473392759</v>
+        <v>945.0844436346197</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>14689.14184589459</v>
+        <v>1173.840059432852</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>12882.58062688381</v>
+        <v>1415.700748116373</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>11281.75282197111</v>
+        <v>1670.504006752061</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>15837.25527480561</v>
+        <v>1948.070713084002</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>12024.4757072718</v>
+        <v>2260.874632399949</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>14876.83729440885</v>
+        <v>2486.760831489916</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>17769441123.70641</v>
+        <v>2738.928132847911</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>27687806868.93195</v>
+        <v>2938.086417382266</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>34012238150.3058</v>
+        <v>3108.863491970128</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -9219,28 +9219,28 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>2423.96112163056</v>
+        <v>185.5404315701562</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>5361.017771668497</v>
+        <v>216.6608177291887</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>8273.283738153861</v>
+        <v>230.6771179436521</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>132.0445880494574</v>
+        <v>228.7556157982327</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>146.1159027517261</v>
+        <v>241.8606886835208</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>160.0163416349722</v>
+        <v>254.8032586356879</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>172.9869867268017</v>
+        <v>277.5667063319406</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>198.5812003424621</v>
+        <v>312.8039193159472</v>
       </c>
       <c r="L50" s="18" t="n">
         <v>225.886199089966</v>
@@ -9275,37 +9275,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>2423.96112163056</v>
+        <v>185.5404315701562</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>7229.294919382109</v>
+        <v>402.2012492993449</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>14244.89118145351</v>
+        <v>632.878367242997</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>12424.25864774046</v>
+        <v>861.6339830412297</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>10809.53040394452</v>
+        <v>1103.494671724751</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>15352.06221168718</v>
+        <v>1358.297930360439</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>11513.68843053771</v>
+        <v>1635.86463669238</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>14338.74501892726</v>
+        <v>1948.668556008327</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>17769440559.33303</v>
+        <v>2174.554755098293</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>27687806279.46016</v>
+        <v>2348.614626052073</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>34012237681.72867</v>
+        <v>2640.286363331365</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -9325,40 +9325,40 @@
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>-980.3289555686137</v>
+        <v>702.4077605748423</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>-4372.385844592817</v>
+        <v>1384.248718963735</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>-9966.716880342474</v>
+        <v>2067.075551218023</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>-7612.585912371995</v>
+        <v>2750.879714448304</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>-11401.81455705688</v>
+        <v>3435.650119495566</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>-6797.166967757807</v>
+        <v>4121.378393473906</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>-8830.355534382086</v>
+        <v>4797.313864847823</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>-17769434234.65431</v>
+        <v>5463.606336853395</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>-9918367540.137987</v>
+        <v>6322.228958236666</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>1526633541.154551</v>
+        <v>7088.338126875001</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>19296065495.46907</v>
+        <v>7966.541676578826</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>43430898813.28655</v>
+        <v>8731.818232389202</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -9378,40 +9378,40 @@
         </is>
       </c>
       <c r="D53" s="18" t="n">
-        <v>-980.3289555686137</v>
+        <v>702.4077605748423</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>-4372.385844592817</v>
+        <v>1384.248718963735</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>-9966.716880342474</v>
+        <v>2067.075551218023</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>-7612.585912371995</v>
+        <v>2750.879714448304</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>-11401.81455705688</v>
+        <v>3435.650119495566</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>-6797.166967757807</v>
+        <v>4121.378393473906</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>-8830.355534382086</v>
+        <v>4797.313864847823</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>-17769434234.65431</v>
+        <v>5463.606336853395</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>-9918367540.137987</v>
+        <v>6322.228958236666</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>1526633541.154551</v>
+        <v>7088.338126875001</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>19296065495.46907</v>
+        <v>7966.541676578826</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>43430898813.28655</v>
+        <v>8731.818232389202</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -9643,40 +9643,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>1764.413727053068</v>
+        <v>1208.72975313612</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>3734.606150694062</v>
+        <v>2108.463070250903</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>5859.333880982381</v>
+        <v>3023.426022249902</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>7089.25045407054</v>
+        <v>3937.414294429102</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>1494.859494484457</v>
+        <v>4865.444292269473</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>4500.04941585714</v>
+        <v>5807.345961869803</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>7023.703850012561</v>
+        <v>6762.188687520867</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>-17769422192.61175</v>
+        <v>7742.047818568413</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>-9918352645.396858</v>
+        <v>8826.89362534302</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>19296074683.09192</v>
+        <v>9845.497218627021</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>46983872382.95106</v>
+        <v>10923.17813781598</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>77443136982.4529</v>
+        <v>11859.54227230453</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -9696,40 +9696,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>-532.974878026537</v>
+        <v>22.70909589041071</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>-1549.806507731653</v>
+        <v>338.4562900902529</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>-2705.179573583438</v>
+        <v>654.9677199065327</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>-2968.674118219248</v>
+        <v>969.5211935584284</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>3607.94420095981</v>
+        <v>1285.838272689777</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>1598.793015049648</v>
+        <v>1602.095055930716</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>84.03488199652475</v>
+        <v>1918.268348760695</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>17769430190.08416</v>
+        <v>2235.408784056424</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>34795565943.21193</v>
+        <v>2474.188638263013</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>30458343882.41577</v>
+        <v>2805.338076721384</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>27647751518.99776</v>
+        <v>3102.339633011634</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>22065691970.90396</v>
+        <v>3422.29086469697</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -9802,19 +9802,19 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>158.1442373727677</v>
+        <v>158.1442373727678</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>184.0899085795663</v>
+        <v>184.0899085795669</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>216.1014300000006</v>
+        <v>216.1014300000001</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>225.85343</v>
+        <v>225.8534300000001</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>256.34977</v>
+        <v>256.3497699999999</v>
       </c>
       <c r="I61" s="18" t="n">
         <v>286.49919</v>
@@ -9823,7 +9823,7 @@
         <v>316.0436</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>363.7965649999999</v>
+        <v>363.796565</v>
       </c>
       <c r="L61" s="18" t="n">
         <v>413.80353</v>
@@ -9855,19 +9855,19 @@
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>-41.77950045342193</v>
+        <v>-41.7795004534219</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>-45.8836719985096</v>
+        <v>-45.8836719985098</v>
       </c>
       <c r="F62" s="18" t="n">
-        <v>-51.71785080734364</v>
+        <v>-51.71785080734338</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>-51.35067313034455</v>
+        <v>-51.35067313034457</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>-56.82285107011572</v>
+        <v>-56.82285107011568</v>
       </c>
       <c r="I62" s="18" t="n">
         <v>-62.22857730248916</v>
@@ -9961,19 +9961,19 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>133.5157061183429</v>
+        <v>133.515706118343</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>140.6693185744596</v>
+        <v>140.66931857446</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>167.3015827947776</v>
+        <v>167.3015827947773</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>177.3597431710253</v>
+        <v>177.3597431710254</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>202.3247271490624</v>
+        <v>202.3247271490623</v>
       </c>
       <c r="I64" s="18" t="n">
         <v>227.0108866701136</v>
@@ -9982,7 +9982,7 @@
         <v>251.4519788299881</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>288.0960220966528</v>
+        <v>288.0960220966529</v>
       </c>
       <c r="L64" s="18" t="n">
         <v>326.6328696233085</v>
@@ -10123,13 +10123,13 @@
         <v>-163.2790452507919</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>-234.2757305275226</v>
+        <v>-234.2757305275222</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>-203.8973158161847</v>
+        <v>-203.897315816185</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>-190.1254664538274</v>
+        <v>-190.1254664538273</v>
       </c>
       <c r="H67" s="18" t="n">
         <v>-161.4889303795418</v>
@@ -10544,19 +10544,19 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>929.4422221198871</v>
+        <v>929.4422221198872</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>858.4455368431564</v>
+        <v>858.4455368431568</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>888.8239515544943</v>
+        <v>888.823951554494</v>
       </c>
       <c r="G75" s="18" t="n">
         <v>902.5958009168517</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>931.2323369911372</v>
+        <v>931.2323369911371</v>
       </c>
       <c r="I75" s="18" t="n">
         <v>959.5582330874744</v>
@@ -10565,7 +10565,7 @@
         <v>946.7883659423813</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>946.7906763397161</v>
+        <v>946.7906763397162</v>
       </c>
       <c r="L75" s="18" t="n">
         <v>989.668689997648</v>
@@ -10600,37 +10600,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>929.4422221198871</v>
+        <v>929.4422221198872</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>1525.768041584298</v>
+        <v>1787.887758963044</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>2152.472275760046</v>
+        <v>2676.711710517538</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>2792.948359298151</v>
+        <v>3579.30751143439</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>3462.060978910543</v>
+        <v>4510.539848425527</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>4159.499494619271</v>
+        <v>5470.098081513001</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>4844.168143182907</v>
+        <v>6416.886447455382</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>5383.692925312886</v>
+        <v>7363.677123795098</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>24877210350.07862</v>
+        <v>8353.345813792746</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>49754415300.20688</v>
+        <v>9385.534488573172</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>74631620335.33463</v>
+        <v>10458.90355911936</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -10650,19 +10650,19 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>929.4422221198871</v>
+        <v>929.4422221198872</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>858.4455368431564</v>
+        <v>858.4455368431568</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>888.8239515544943</v>
+        <v>888.823951554494</v>
       </c>
       <c r="G77" s="18" t="n">
         <v>902.5958009168517</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>931.2323369911372</v>
+        <v>931.2323369911371</v>
       </c>
       <c r="I77" s="18" t="n">
         <v>959.5582330874744</v>
@@ -10671,7 +10671,7 @@
         <v>946.7883659423813</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>946.7906763397161</v>
+        <v>946.7906763397162</v>
       </c>
       <c r="L77" s="18" t="n">
         <v>989.668689997648</v>
@@ -10703,40 +10703,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>929.4422221198871</v>
+        <v>929.4422221198872</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>1525.768041584298</v>
+        <v>1787.887758963044</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>2152.472275760046</v>
+        <v>2676.711710517538</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>2792.948359298151</v>
+        <v>3579.30751143439</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>3462.060978910543</v>
+        <v>4510.539848425527</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>4159.499494619271</v>
+        <v>5470.098081513001</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>4844.168143182907</v>
+        <v>6416.886447455382</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>5383.692925312886</v>
+        <v>7363.677123795098</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>24877210350.07862</v>
+        <v>8353.345813792746</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>49754415300.20688</v>
+        <v>9385.534488573172</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>74631620335.33463</v>
+        <v>10458.90355911936</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>99508825223.14854</v>
+        <v>11551.62482649004</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -10862,28 +10862,28 @@
         </is>
       </c>
       <c r="D81" s="18" t="n">
-        <v>11.44678414406427</v>
+        <v>83.74535933182442</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>6.740695685832899</v>
+        <v>89.68865099308368</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>4.360861457012994</v>
+        <v>79.0713964892079</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>91.79800170185423</v>
+        <v>73.93615945995938</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>80.78705073684975</v>
+        <v>66.62260734410827</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>72.08954340783623</v>
+        <v>60.59381031147454</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>72.5303128117947</v>
+        <v>60.90491043737391</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>71.39503313951192</v>
+        <v>60.10238405231119</v>
       </c>
       <c r="L81" s="18" t="n">
         <v>64.62626748876401</v>
@@ -11684,37 +11684,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>2736.167198022183</v>
+        <v>497.7465079617789</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>7778.815724342855</v>
+        <v>1026.61340208259</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>15031.72671498338</v>
+        <v>1569.496596417865</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>13448.40890983945</v>
+        <v>2110.458288607721</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>12070.99539461263</v>
+        <v>2664.525053682864</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>16850.84193092441</v>
+        <v>3231.534388710174</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>13249.78287834408</v>
+        <v>3821.307171433737</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>16270.68385906532</v>
+        <v>4446.317167141307</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>24877215339.4565</v>
+        <v>4984.409442622896</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>41903353907.76831</v>
+        <v>5470.675389968297</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>55335558158.22143</v>
+        <v>6074.553203639211</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -11787,28 +11787,28 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>2423.96112163056</v>
+        <v>185.5404315701562</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>5361.017771668497</v>
+        <v>216.6608177291887</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>8273.283738153861</v>
+        <v>230.6771179436521</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>132.0445880494574</v>
+        <v>228.7556157982327</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>146.1159027517261</v>
+        <v>241.8606886835208</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>160.0163416349722</v>
+        <v>254.8032586356879</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>172.9869867268017</v>
+        <v>277.5667063319406</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>198.5812003424621</v>
+        <v>312.8039193159472</v>
       </c>
       <c r="L98" s="21" t="n">
         <v>225.886199089966</v>
@@ -11893,40 +11893,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>2736.167198022183</v>
+        <v>497.7465079617789</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>7778.815724342855</v>
+        <v>1026.61340208259</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>15031.72671498338</v>
+        <v>1569.496596417865</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>13448.40890983945</v>
+        <v>2110.458288607721</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>12070.99539461263</v>
+        <v>2664.525053682864</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>16850.84193092441</v>
+        <v>3231.534388710174</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>13249.78287834408</v>
+        <v>3821.307171433737</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>16270.68385906532</v>
+        <v>4446.317167141307</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>24877215339.4565</v>
+        <v>4984.409442622896</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>41903353907.76831</v>
+        <v>5470.675389968297</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>55335558158.22143</v>
+        <v>6074.553203639211</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>62443331587.62616</v>
+        <v>6784.976237226653</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -11999,28 +11999,28 @@
         </is>
       </c>
       <c r="D102" s="18" t="n">
-        <v>-780.5151909790563</v>
+        <v>-26.3169850692774</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>-1398.346557472054</v>
+        <v>-26.3169850692774</v>
       </c>
       <c r="F102" s="18" t="n">
-        <v>-2192.973904124234</v>
+        <v>-26.3169850692774</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>0</v>
+        <v>-26.3169850692774</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>0</v>
+        <v>-26.3169850692774</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>0</v>
+        <v>-26.3169850692774</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>0</v>
+        <v>-26.3169850692774</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>0</v>
+        <v>-26.3169850692774</v>
       </c>
       <c r="L102" s="18" t="n">
         <v>0</v>
@@ -12055,37 +12055,37 @@
         <v>0</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>-980.3289555686137</v>
+        <v>702.4077605748423</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>-4372.385844592817</v>
+        <v>1384.248718963735</v>
       </c>
       <c r="G103" s="18" t="n">
-        <v>-9966.716880342474</v>
+        <v>2067.075551218023</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>-7612.585912371995</v>
+        <v>2750.879714448304</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>-11401.81455705688</v>
+        <v>3435.650119495566</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>-6797.166967757807</v>
+        <v>4121.378393473906</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>-8830.355534382086</v>
+        <v>4797.313864847823</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>-17769434234.65431</v>
+        <v>5463.606336853395</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>-9918367540.137987</v>
+        <v>6322.228958236666</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>1526633541.154551</v>
+        <v>7088.338126875001</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>19296065495.46907</v>
+        <v>7966.541676578826</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -12158,28 +12158,28 @@
         </is>
       </c>
       <c r="D105" s="18" t="n">
-        <v>-2316.528120464618</v>
+        <v>-78.1074304042142</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>-5243.031186529472</v>
+        <v>-98.67423259016348</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>-8140.294978934977</v>
+        <v>-97.6883587247691</v>
       </c>
       <c r="G105" s="18" t="n">
-        <v>0</v>
+        <v>-96.71102774877525</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>0</v>
+        <v>-95.74478593179478</v>
       </c>
       <c r="I105" s="18" t="n">
-        <v>0</v>
+        <v>-94.78691700071575</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>0</v>
+        <v>-104.579719605139</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>0</v>
+        <v>-114.222718973485</v>
       </c>
       <c r="L105" s="18" t="n">
         <v>0</v>
@@ -12211,40 +12211,40 @@
         </is>
       </c>
       <c r="D106" s="18" t="n">
-        <v>296.7947513691348</v>
+        <v>10.00716338476877</v>
       </c>
       <c r="E106" s="18" t="n">
-        <v>671.739800471117</v>
+        <v>12.64219245577902</v>
       </c>
       <c r="F106" s="18" t="n">
-        <v>1042.938699082079</v>
+        <v>12.51588179881951</v>
       </c>
       <c r="G106" s="18" t="n">
-        <v>1113.629157337797</v>
+        <v>12.39066566115948</v>
       </c>
       <c r="H106" s="18" t="n">
-        <v>1102.497765764419</v>
+        <v>12.26687027214617</v>
       </c>
       <c r="I106" s="18" t="n">
-        <v>1091.472788106775</v>
+        <v>12.14414762149827</v>
       </c>
       <c r="J106" s="18" t="n">
-        <v>1121.372458740208</v>
+        <v>13.39880643116723</v>
       </c>
       <c r="K106" s="18" t="n">
-        <v>1191.58541433922</v>
+        <v>14.63427237466156</v>
       </c>
       <c r="L106" s="18" t="n">
-        <v>1261.096940382241</v>
+        <v>0</v>
       </c>
       <c r="M106" s="18" t="n">
-        <v>1289.101452650331</v>
+        <v>0</v>
       </c>
       <c r="N106" s="18" t="n">
-        <v>1276.209050204828</v>
+        <v>0</v>
       </c>
       <c r="O106" s="18" t="n">
-        <v>1135.63503351978</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" ht="15.5" customHeight="1">
@@ -12264,40 +12264,40 @@
         </is>
       </c>
       <c r="D107" s="18" t="n">
-        <v>-980.3289555686137</v>
+        <v>702.4077605748423</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>-4372.385844592817</v>
+        <v>1384.248718963735</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>-9966.716880342474</v>
+        <v>2067.075551218023</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>-7612.585912371995</v>
+        <v>2750.879714448304</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>-11401.81455705688</v>
+        <v>3435.650119495566</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>-6797.166967757807</v>
+        <v>4121.378393473906</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>-8830.355534382086</v>
+        <v>4797.313864847823</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>-17769434234.65431</v>
+        <v>5463.606336853395</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>-9918367540.137987</v>
+        <v>6322.228958236666</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>1526633541.154551</v>
+        <v>7088.338126875001</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>19296065495.46907</v>
+        <v>7966.541676578826</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>43430898813.28655</v>
+        <v>8731.818232389202</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -14903,16 +14903,16 @@
         <v>3998.2412586508</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>5336.950354881278</v>
+        <v>4450.873747371277</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>6672.679495074934</v>
+        <v>4900.52628005493</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>8005.911984479156</v>
+        <v>5347.682161949155</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>9336.261489147857</v>
+        <v>5791.955059107859</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -14956,16 +14956,16 @@
         <v>3990.181697400639</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>5329.489003670324</v>
+        <v>4443.412396160323</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>6664.293453966879</v>
+        <v>4892.140238946876</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>7998.163893278826</v>
+        <v>5339.934070748825</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>9327.696637046469</v>
+        <v>5783.390207006471</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -15115,16 +15115,16 @@
         <v>4020.888526120569</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>5359.854296480749</v>
+        <v>4473.777688970748</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>6695.656489297115</v>
+        <v>4923.503274277111</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>8028.77920766953</v>
+        <v>5370.549385139529</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>9358.79185513586</v>
+        <v>5814.485425095862</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -15751,16 +15751,16 @@
         <v>4057.147226439323</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>5521.37267441134</v>
+        <v>4635.296066901339</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>6986.359242326374</v>
+        <v>5214.20602730637</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>8450.564165722772</v>
+        <v>5792.334343192771</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>9915.496125241089</v>
+        <v>6371.18969520109</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -16655,13 +16655,13 @@
         <v>3990.181697400639</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>5329.489003670324</v>
+        <v>4443.412396160323</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>6664.293453966879</v>
+        <v>4892.140238946876</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>7998.163893278826</v>
+        <v>5339.934070748825</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -16758,16 +16758,16 @@
         <v>3990.181697400639</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>5329.489003670324</v>
+        <v>4443.412396160323</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>6664.293453966879</v>
+        <v>4892.140238946876</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>7998.163893278826</v>
+        <v>5339.934070748825</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>9327.696637046469</v>
+        <v>5783.390207006471</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -17739,13 +17739,13 @@
         <v>4011.39992430114</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>5350.147845099375</v>
+        <v>4464.071237589375</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>6685.732848404069</v>
+        <v>4913.57963338407</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>8018.639026497255</v>
+        <v>5360.409203967256</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -17948,16 +17948,16 @@
         <v>4011.39992430114</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>5350.147845099375</v>
+        <v>4464.071237589375</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>6685.732848404069</v>
+        <v>4913.57963338407</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>8018.639026497255</v>
+        <v>5360.409203967256</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>9348.435772249304</v>
+        <v>5804.129342209303</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -18242,40 +18242,40 @@
         </is>
       </c>
       <c r="D106" s="18" t="n">
-        <v>2.682342523664534</v>
+        <v>35.93900009085588</v>
       </c>
       <c r="E106" s="18" t="n">
-        <v>7.46359808810322</v>
+        <v>64.06099990914412</v>
       </c>
       <c r="F106" s="18" t="n">
-        <v>12.22380934726766</v>
+        <v>0</v>
       </c>
       <c r="G106" s="18" t="n">
-        <v>14.28084422054607</v>
+        <v>0</v>
       </c>
       <c r="H106" s="18" t="n">
-        <v>14.21834052945104</v>
+        <v>0</v>
       </c>
       <c r="I106" s="18" t="n">
-        <v>14.15646187526696</v>
+        <v>0</v>
       </c>
       <c r="J106" s="18" t="n">
-        <v>13.07164435332739</v>
+        <v>0</v>
       </c>
       <c r="K106" s="18" t="n">
-        <v>10.97084636011746</v>
+        <v>0</v>
       </c>
       <c r="L106" s="18" t="n">
-        <v>8.879863535366635</v>
+        <v>0</v>
       </c>
       <c r="M106" s="18" t="n">
-        <v>7.822155381687644</v>
+        <v>0</v>
       </c>
       <c r="N106" s="18" t="n">
-        <v>7.79066014456221</v>
+        <v>0</v>
       </c>
       <c r="O106" s="18" t="n">
-        <v>7.711209441952819</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" ht="15.5" customHeight="1">
@@ -18737,28 +18737,28 @@
         </is>
       </c>
       <c r="D2" s="18" t="n">
-        <v>1736.112890495718</v>
+        <v>335.19266781461</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>3482.493298279126</v>
+        <v>374.6506268127727</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>5219.414809680619</v>
+        <v>410.0675553337409</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>351.2935485872248</v>
+        <v>424.3532905700056</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>385.543380409862</v>
+        <v>457.8733493672335</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>419.0466744184446</v>
+        <v>490.6529439798577</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>451.639154246984</v>
+        <v>524.4638654693774</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>485.0958329196223</v>
+        <v>559.118968036656</v>
       </c>
       <c r="L2" s="18" t="n">
         <v>517.8723087955156</v>
@@ -18793,28 +18793,28 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>100.5914083896213</v>
+        <v>11.77172497698735</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>49.87580341532296</v>
+        <v>9.453321571157392</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>-93.26948400545461</v>
+        <v>3.483751652733891</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>9.749633023543304</v>
+        <v>7.89909246425371</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>8.689889571691278</v>
+        <v>7.159096430907042</v>
       </c>
       <c r="J3" s="18" t="n">
-        <v>7.777768401043028</v>
+        <v>6.89100552730153</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>7.407833966127342</v>
+        <v>6.607719778037224</v>
       </c>
       <c r="L3" s="18" t="n">
-        <v>6.756701181831049</v>
+        <v>-7.377081014793319</v>
       </c>
       <c r="M3" s="18" t="n">
         <v>6.080252420429089</v>
@@ -18949,28 +18949,28 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>1464.465240231228</v>
+        <v>63.54501755012017</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>3182.385422736978</v>
+        <v>74.54275127062567</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>4883.145402499216</v>
+        <v>73.79814815233796</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0</v>
+        <v>73.05974198278079</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>0</v>
+        <v>72.32996895737155</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>0</v>
+        <v>71.60626956141309</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>0</v>
+        <v>72.82471122239347</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>0</v>
+        <v>74.0231351170338</v>
       </c>
       <c r="L6" s="18" t="n">
         <v>0</v>
@@ -19005,28 +19005,28 @@
         <v>0</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>117.3069961178801</v>
+        <v>17.30699611788007</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>53.44292893032159</v>
+        <v>-0.9988940649432787</v>
       </c>
       <c r="G7" s="18" t="n">
+        <v>-1.000575472480569</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>-0.9988716160279409</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>-1.000552615175299</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>1.701585166275699</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>1.645628076684802</v>
+      </c>
+      <c r="L7" s="18" t="n">
         <v>-100</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="18" t="n">
-        <v>0</v>
       </c>
       <c r="M7" s="18" t="n">
         <v>0</v>
@@ -19055,28 +19055,28 @@
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>-84.35311138166105</v>
+        <v>-18.95775882104497</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-91.38238469287376</v>
+        <v>-19.89660391196344</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>-93.55733507599908</v>
+        <v>-17.99658304892617</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>0</v>
+        <v>-17.21672568737349</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>0</v>
+        <v>-15.79693796490433</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>0</v>
+        <v>-14.59407722709041</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>0</v>
+        <v>-13.88555361334909</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>0</v>
+        <v>-13.23924591164663</v>
       </c>
       <c r="L8" s="18" t="n">
         <v>0</v>
@@ -19373,28 +19373,28 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>-8.042972596447861</v>
+        <v>-41.65815587087948</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>-5.537767440633186</v>
+        <v>-51.47525886583125</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>-4.738729824487358</v>
+        <v>-60.3154195041713</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>-85.40504054435389</v>
+        <v>-70.70108899064238</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>-91.02565747929869</v>
+        <v>-76.64639083514759</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>-95.48334867347269</v>
+        <v>-81.54843502905408</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>-99.27229688111814</v>
+        <v>-85.48778887448741</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>-101.1978547010019</v>
+        <v>-87.80002185982542</v>
       </c>
       <c r="L14" s="18" t="n">
         <v>-102.1283492148867</v>
@@ -19691,28 +19691,28 @@
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>5.893505151951709</v>
+        <v>30.52510167127324</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>3.234641728190193</v>
+        <v>30.06699397939541</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>2.409627745884775</v>
+        <v>30.67018245921073</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>39.45782970916849</v>
+        <v>32.66448340594999</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>39.21452264911252</v>
+        <v>33.01982883299886</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>39.01847986503407</v>
+        <v>33.32409278069427</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>38.86983266656834</v>
+        <v>33.47254121223291</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>37.63570009419097</v>
+        <v>32.65301720815121</v>
       </c>
       <c r="L20" s="18" t="n">
         <v>36.00151329942941</v>
@@ -19903,28 +19903,28 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>1620.212605337431</v>
+        <v>219.2923826563226</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>3354.841723094455</v>
+        <v>246.9990516281018</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>5076.832871894666</v>
+        <v>267.4856175477875</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>195.1160609770213</v>
+        <v>268.1758029598021</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>215.0772151563895</v>
+        <v>287.407184113761</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>234.5886984144667</v>
+        <v>306.1949679758798</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>253.5058130221277</v>
+        <v>326.3305242445211</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>278.2718284265944</v>
+        <v>352.2949635436282</v>
       </c>
       <c r="L24" s="18" t="n">
         <v>305.5368252306601</v>
@@ -19956,10 +19956,10 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>155.7473651062023</v>
+        <v>155.7473651062024</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>172.4563003574763</v>
+        <v>172.4563003574761</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>193.6874693954496</v>
@@ -19974,7 +19974,7 @@
         <v>234.5886984144667</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>253.5058130221277</v>
+        <v>253.5058130221276</v>
       </c>
       <c r="K25" s="18" t="n">
         <v>278.2718284265944</v>
@@ -20009,28 +20009,28 @@
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>93.32415041713134</v>
+        <v>65.42278626977901</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>96.3344775064535</v>
+        <v>65.92783621620275</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>97.26823900791518</v>
+        <v>65.22964669323558</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>55.54217029083151</v>
+        <v>63.19635287841868</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>55.78547735088748</v>
+        <v>62.77001806524636</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>55.98152013496593</v>
+        <v>62.40561108066025</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>56.13016733343167</v>
+        <v>62.22173646843454</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>57.36429990580903</v>
+        <v>63.00894508743112</v>
       </c>
       <c r="L26" s="18" t="n">
         <v>58.99848670057059</v>
@@ -20062,28 +20062,28 @@
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>8.971039035470282</v>
+        <v>46.46502744873403</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>4.952092813579729</v>
+        <v>46.03123230423932</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>3.710903931916106</v>
+        <v>47.23306364430941</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>55.54217029083151</v>
+        <v>45.9796271910452</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>55.78547735088748</v>
+        <v>46.97308010034203</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>55.98152013496593</v>
+        <v>47.81153385356984</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>56.13016733343167</v>
+        <v>48.33618285508544</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>57.36429990580903</v>
+        <v>49.7696991757845</v>
       </c>
       <c r="L27" s="18" t="n">
         <v>58.99848670057059</v>
@@ -20168,28 +20168,28 @@
         </is>
       </c>
       <c r="D29" s="19" t="n">
-        <v>0.4446432134746481</v>
+        <v>2.303006266866584</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>0.4829912441702071</v>
+        <v>4.489552800857343</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>0.4948810148144004</v>
+        <v>6.298936026894013</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>9.891864747476378</v>
+        <v>8.188809528537369</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>11.3035291812595</v>
+        <v>9.517917688651076</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>12.48599935643416</v>
+        <v>10.66378296778215</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>13.46802504274475</v>
+        <v>11.59791520477515</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>14.24410532099799</v>
+        <v>12.35829318963713</v>
       </c>
       <c r="L29" s="19" t="n">
         <v>14.92366054695905</v>
@@ -20221,28 +20221,28 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>1612.493097191583</v>
+        <v>211.5728745104749</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>3338.021585384952</v>
+        <v>230.1789139185994</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>5051.002978917146</v>
+        <v>241.655724570267</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>160.3665782841628</v>
+        <v>233.4263202669436</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>171.4972066453465</v>
+        <v>243.827175602718</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>182.2665333434209</v>
+        <v>253.8728029048341</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>192.6789386253032</v>
+        <v>265.5036498476967</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>209.1742670777509</v>
+        <v>283.1974021947847</v>
       </c>
       <c r="L30" s="19" t="n">
         <v>228.2513197993178</v>
@@ -20274,28 +20274,28 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>92.87950720365669</v>
+        <v>63.11978000291242</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>95.85148626228329</v>
+        <v>61.43828341534541</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>96.77335799310079</v>
+        <v>58.93071066634157</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>45.65030554335512</v>
+        <v>55.00754334988132</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>44.48194816962799</v>
+        <v>53.25210037659528</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>43.49552077853176</v>
+        <v>51.74182811287811</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>42.66214229068691</v>
+        <v>50.62382126365939</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>43.12019458481103</v>
+        <v>50.650651897794</v>
       </c>
       <c r="L31" s="19" t="n">
         <v>44.07482615361154</v>
@@ -20380,28 +20380,28 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>1612.493097191583</v>
+        <v>211.5728745104749</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>3338.021585384952</v>
+        <v>230.1789139185994</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>5051.002978917146</v>
+        <v>241.655724570267</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>160.3665782841628</v>
+        <v>233.4263202669436</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>171.4972066453465</v>
+        <v>243.827175602718</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>182.2665333434209</v>
+        <v>253.8728029048341</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>192.6789386253032</v>
+        <v>265.5036498476967</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>209.1742670777509</v>
+        <v>283.1974021947847</v>
       </c>
       <c r="L33" s="19" t="n">
         <v>228.2513197993178</v>
@@ -20433,13 +20433,13 @@
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>148.0278569603545</v>
+        <v>148.0278569603547</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>155.6361626479738</v>
+        <v>155.6361626479737</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>167.8575764179295</v>
+        <v>167.857576417929</v>
       </c>
       <c r="G34" s="19" t="n">
         <v>160.3665782841628</v>
@@ -20448,7 +20448,7 @@
         <v>171.4972066453465</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>182.2665333434209</v>
+        <v>182.266533343421</v>
       </c>
       <c r="J34" s="19" t="n">
         <v>192.6789386253032</v>
@@ -20539,22 +20539,22 @@
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>-41.44779994889925</v>
+        <v>-41.44779994889931</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>-43.57812554143268</v>
+        <v>-43.57812554143263</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-47.00012139702027</v>
+        <v>-47.00012139702012</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>-44.90264191956558</v>
+        <v>-44.9026419195656</v>
       </c>
       <c r="H36" s="19" t="n">
         <v>-48.01921786069701</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>-51.03462933615786</v>
+        <v>-51.03462933615788</v>
       </c>
       <c r="J36" s="19" t="n">
         <v>-53.9501028150849</v>
@@ -20645,28 +20645,28 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>1571.045297242684</v>
+        <v>170.1250745615756</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>3294.44345984352</v>
+        <v>186.6007883771667</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>5004.002857520126</v>
+        <v>194.6556031732468</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>115.4639363645972</v>
+        <v>188.5236783473781</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>123.4779887846495</v>
+        <v>195.807957742021</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>131.2319040072631</v>
+        <v>202.8381735686762</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>138.7288358102183</v>
+        <v>211.5535470326118</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>150.6054722959807</v>
+        <v>224.6286074130145</v>
       </c>
       <c r="L38" s="19" t="n">
         <v>164.3409502555088</v>
@@ -20698,28 +20698,28 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>90.49211637349791</v>
+        <v>50.75441407198954</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>94.60013782284862</v>
+        <v>49.80661315439846</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>95.87287157631231</v>
+        <v>47.46915493346525</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>32.86821999121569</v>
+        <v>44.42611440437913</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>32.02700268213215</v>
+        <v>42.76465490132181</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>31.31677496054287</v>
+        <v>41.34045786485756</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>30.71674244929457</v>
+        <v>40.33710632157251</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>31.04654010106394</v>
+        <v>40.17545822167273</v>
       </c>
       <c r="L39" s="19" t="n">
         <v>31.73387483060031</v>
@@ -20910,40 +20910,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>728.0947567237048</v>
+        <v>728.0947567237049</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>1202.648133487993</v>
+        <v>1399.196074945698</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>1698.853912298529</v>
+        <v>2091.949795213938</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>2199.781392114736</v>
+        <v>2789.42521648785</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>2722.032840025575</v>
+        <v>3508.224605856394</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>3263.594592428043</v>
+        <v>4246.334299716566</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>3816.18351156799</v>
+        <v>4995.471160314218</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>4190.960912068281</v>
+        <v>5759.615904440761</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>87381798563.88548</v>
+        <v>6548.333656506655</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>174763592900.5616</v>
+        <v>7360.968960392492</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>262145387300.3685</v>
+        <v>8196.587383104083</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>349527181544.1685</v>
+        <v>9038.073332223403</v>
       </c>
     </row>
     <row r="44">
@@ -20963,40 +20963,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>714.1772432207382</v>
+        <v>714.1772432207383</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>1187.240323011178</v>
+        <v>1383.788264468883</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>1681.552465195417</v>
+        <v>2074.648348110827</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>2182.300783478595</v>
+        <v>2771.944607851709</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>2702.770835846653</v>
+        <v>3488.962601677472</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>3242.591219923764</v>
+        <v>4225.330927212288</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>3793.49136602817</v>
+        <v>4972.779014774398</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>4166.09571041848</v>
+        <v>5734.750702790961</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>87381798536.64462</v>
+        <v>6521.092798369359</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>174763592871.0418</v>
+        <v>7331.449119350613</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>262145387268.6756</v>
+        <v>8164.894548635995</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>349527181508.4148</v>
+        <v>9002.319630547379</v>
       </c>
     </row>
     <row r="45">
@@ -21122,40 +21122,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>974.7420336825286</v>
+        <v>974.7420336825287</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>1730.865307465228</v>
+        <v>1927.413248922933</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>2496.650627678877</v>
+        <v>2889.746510594287</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>3255.282264839054</v>
+        <v>3844.926089212167</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>4023.486107875309</v>
+        <v>4809.677873706129</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>4799.361174806826</v>
+        <v>5782.10088209535</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>5582.636045952201</v>
+        <v>6761.923694698429</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>6184.625928424315</v>
+        <v>7753.280920796797</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>87381800773.61104</v>
+        <v>8758.059210318806</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>174763595315.309</v>
+        <v>9775.716294590213</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>262145389909.2072</v>
+        <v>10805.42609178529</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>349527184260.615</v>
+        <v>11754.51989297923</v>
       </c>
     </row>
     <row r="48">
@@ -21175,40 +21175,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>1832.740635339991</v>
+        <v>431.8204126588831</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>5127.184095183511</v>
+        <v>618.4212010360498</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>9787.469485289315</v>
+        <v>922.1943080642168</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>9156.0113180834</v>
+        <v>1238.720452422614</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>8133.390154321482</v>
+        <v>1561.252267139688</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>7143.874285511839</v>
+        <v>1691.030698725584</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>9872.745663334987</v>
+        <v>2028.769907927984</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>7575.211531714775</v>
+        <v>2181.792245779586</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>9310.51679685722</v>
+        <v>2469.841199647154</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>60074989300.74668</v>
+        <v>2767.719251095017</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>92504759334.71292</v>
+        <v>2982.442168446919</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>113428389493.9023</v>
+        <v>3088.050784484931</v>
       </c>
     </row>
     <row r="49">
@@ -21281,28 +21281,28 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>1571.045297242684</v>
+        <v>170.1250745615756</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>3294.44345984352</v>
+        <v>186.6007883771667</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>5004.002857520126</v>
+        <v>194.6556031732468</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>115.4639363645972</v>
+        <v>188.5236783473781</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>123.4779887846495</v>
+        <v>195.807957742021</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>131.2319040072631</v>
+        <v>202.8381735686762</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>138.7288358102183</v>
+        <v>211.5535470326118</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>150.6054722959807</v>
+        <v>224.6286074130145</v>
       </c>
       <c r="L50" s="18" t="n">
         <v>164.3409502555088</v>
@@ -21337,37 +21337,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>1571.045297242684</v>
+        <v>170.1250745615756</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>4521.771289671882</v>
+        <v>465.8433667936624</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>8778.852043621495</v>
+        <v>788.5014359779282</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>7748.216827439525</v>
+        <v>1103.74897130036</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>6750.947043407268</v>
+        <v>1226.4971870596</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>9472.321489427461</v>
+        <v>1555.521022798065</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>7162.910721321487</v>
+        <v>1695.468300269264</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>8884.480508504404</v>
+        <v>2043.804911294337</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>60074988861.71646</v>
+        <v>2328.689028049315</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>92504758883.50916</v>
+        <v>2531.238404536048</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>113428389125.1864</v>
+        <v>2719.334945693648</v>
       </c>
     </row>
     <row r="52">
@@ -21387,40 +21387,40 @@
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>-545.0180290028316</v>
+        <v>403.0672224090362</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>-2539.878314107392</v>
+        <v>776.2517489414683</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>-5836.321529998138</v>
+        <v>1151.459487628153</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>-4274.970723119325</v>
+        <v>1727.18923144223</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>-6424.510231070351</v>
+        <v>2104.403344129146</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>-3535.767593092253</v>
+        <v>2680.133087943223</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>-4666.128873917286</v>
+        <v>3059.330116922845</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>-60074984071.88712</v>
+        <v>3440.49355912042</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>-32429770280.67094</v>
+        <v>3991.008811396158</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>6721583342.981387</v>
+        <v>4568.150439866198</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>66796566944.56824</v>
+        <v>5145.280800422396</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>169624299882.3739</v>
+        <v>5722.395457827415</v>
       </c>
     </row>
     <row r="53">
@@ -21440,40 +21440,40 @@
         </is>
       </c>
       <c r="D53" s="18" t="n">
-        <v>-545.0180290028316</v>
+        <v>403.0672224090362</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>-2539.878314107392</v>
+        <v>776.2517489414683</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>-5836.321529998138</v>
+        <v>1151.459487628153</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>-4274.970723119325</v>
+        <v>1727.18923144223</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>-6424.510231070351</v>
+        <v>2104.403344129146</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>-3535.767593092253</v>
+        <v>2680.133087943223</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>-4666.128873917286</v>
+        <v>3059.330116922845</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>-60074984071.88712</v>
+        <v>3440.49355912042</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>-32429770280.67094</v>
+        <v>3991.008811396158</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>6721583342.981387</v>
+        <v>4568.150439866198</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>66796566944.56824</v>
+        <v>5145.280800422396</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>169624299882.3739</v>
+        <v>5722.395457827415</v>
       </c>
     </row>
     <row r="54">
@@ -21705,40 +21705,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>1296.132296965521</v>
+        <v>843.2973256962806</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>2596.564371328795</v>
+        <v>1403.931540230195</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>3961.485089600237</v>
+        <v>2083.990930001429</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>4892.433428677568</v>
+        <v>2977.302517578337</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>1721.306416092199</v>
+        <v>3678.082104109901</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>3621.545512333261</v>
+        <v>4384.602606582482</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>5221.045670254345</v>
+        <v>5102.528905687474</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>-60074976481.6699</v>
+        <v>5637.291493627161</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>-32429760954.83015</v>
+        <v>6476.174000204278</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>66796572659.36112</v>
+        <v>7351.502747375703</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>159301326295.2159</v>
+        <v>8143.657673305763</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>283052689392.5046</v>
+        <v>8826.674622439114</v>
       </c>
     </row>
     <row r="59">
@@ -21758,40 +21758,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>-321.3902632829924</v>
+        <v>131.4447079862481</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>-865.6990638635677</v>
+        <v>523.481708692738</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>-1464.83446192136</v>
+        <v>805.7555805928578</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>-1637.151163838515</v>
+        <v>867.6235716338301</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>2302.179691783111</v>
+        <v>1131.595769596228</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>1177.815662473565</v>
+        <v>1397.498275512869</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>361.590375697856</v>
+        <v>1659.394789010955</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>60074982666.29583</v>
+        <v>2115.989427169636</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>119811561728.4412</v>
+        <v>2281.885210114528</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>107967022655.9479</v>
+        <v>2424.21354721451</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>102844063613.9913</v>
+        <v>2661.768418479527</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>66474494868.11041</v>
+        <v>2927.845270540112</v>
       </c>
     </row>
     <row r="60">
@@ -21864,10 +21864,10 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>155.7473651062023</v>
+        <v>155.7473651062024</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>172.4563003574763</v>
+        <v>172.4563003574761</v>
       </c>
       <c r="F61" s="18" t="n">
         <v>193.6874693954496</v>
@@ -21882,7 +21882,7 @@
         <v>234.5886984144667</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>253.5058130221277</v>
+        <v>253.5058130221276</v>
       </c>
       <c r="K61" s="18" t="n">
         <v>278.2718284265944</v>
@@ -21917,22 +21917,22 @@
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>-41.44779994889925</v>
+        <v>-41.44779994889931</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>-43.57812554143268</v>
+        <v>-43.57812554143263</v>
       </c>
       <c r="F62" s="18" t="n">
-        <v>-47.00012139702027</v>
+        <v>-47.00012139702012</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>-44.90264191956558</v>
+        <v>-44.9026419195656</v>
       </c>
       <c r="H62" s="18" t="n">
         <v>-48.01921786069701</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>-51.03462933615786</v>
+        <v>-51.03462933615788</v>
       </c>
       <c r="J62" s="18" t="n">
         <v>-53.9501028150849</v>
@@ -22023,13 +22023,13 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>131.1189464140257</v>
+        <v>131.1189464140258</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>130.5759740646738</v>
+        <v>130.5759740646737</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>148.8444361111942</v>
+        <v>148.8444361111943</v>
       </c>
       <c r="G64" s="18" t="n">
         <v>152.3248178663257</v>
@@ -22041,7 +22041,7 @@
         <v>185.5787232235269</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>201.53583205298</v>
+        <v>201.5358320529799</v>
       </c>
       <c r="K64" s="18" t="n">
         <v>220.8566494258443</v>
@@ -22185,10 +22185,10 @@
         <v>-123.2478386906458</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>-167.8140606632396</v>
+        <v>-167.8140606632397</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>-146.5649982694399</v>
+        <v>-146.5649982694397</v>
       </c>
       <c r="G67" s="18" t="n">
         <v>-140.1288221705022</v>
@@ -22200,7 +22200,7 @@
         <v>-101.0567563765681</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-89.97699434927341</v>
+        <v>-89.97699434927347</v>
       </c>
       <c r="K67" s="18" t="n">
         <v>-75.45339389482191</v>
@@ -22606,13 +22606,13 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>714.1772432207382</v>
+        <v>714.1772432207383</v>
       </c>
       <c r="E75" s="18" t="n">
         <v>669.6110212481444</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>690.8600836419441</v>
+        <v>690.8600836419444</v>
       </c>
       <c r="G75" s="18" t="n">
         <v>697.2962597408819</v>
@@ -22621,10 +22621,10 @@
         <v>717.0179938257629</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>736.3683255348159</v>
+        <v>736.368325534816</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>747.4480875621107</v>
+        <v>747.4480875621106</v>
       </c>
       <c r="K75" s="18" t="n">
         <v>761.9716880165621</v>
@@ -22662,37 +22662,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>714.1772432207382</v>
+        <v>714.1772432207383</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>1187.240323011178</v>
+        <v>1383.788264468883</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>1681.552465195417</v>
+        <v>2074.648348110827</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>2182.300783478595</v>
+        <v>2771.944607851709</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>2702.770835846653</v>
+        <v>3488.962601677472</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>3242.591219923764</v>
+        <v>4225.330927212288</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>3793.49136602817</v>
+        <v>4972.779014774398</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>4166.09571041848</v>
+        <v>5734.750702790961</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>87381798536.64462</v>
+        <v>6521.092798369359</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>174763592871.0418</v>
+        <v>7331.449119350613</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>262145387268.6756</v>
+        <v>8164.894548635995</v>
       </c>
     </row>
     <row r="77">
@@ -22712,13 +22712,13 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>714.1772432207382</v>
+        <v>714.1772432207383</v>
       </c>
       <c r="E77" s="18" t="n">
         <v>669.6110212481444</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>690.8600836419441</v>
+        <v>690.8600836419444</v>
       </c>
       <c r="G77" s="18" t="n">
         <v>697.2962597408819</v>
@@ -22727,10 +22727,10 @@
         <v>717.0179938257629</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>736.3683255348159</v>
+        <v>736.368325534816</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>747.4480875621107</v>
+        <v>747.4480875621106</v>
       </c>
       <c r="K77" s="18" t="n">
         <v>761.9716880165621</v>
@@ -22765,40 +22765,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>714.1772432207382</v>
+        <v>714.1772432207383</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>1187.240323011178</v>
+        <v>1383.788264468883</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>1681.552465195417</v>
+        <v>2074.648348110827</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>2182.300783478595</v>
+        <v>2771.944607851709</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>2702.770835846653</v>
+        <v>3488.962601677472</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>3242.591219923764</v>
+        <v>4225.330927212288</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>3793.49136602817</v>
+        <v>4972.779014774398</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>4166.09571041848</v>
+        <v>5734.750702790961</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>87381798536.64462</v>
+        <v>6521.092798369359</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>174763592871.0418</v>
+        <v>7331.449119350613</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>262145387268.6756</v>
+        <v>8164.894548635995</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>349527181508.4148</v>
+        <v>9002.319630547379</v>
       </c>
     </row>
     <row r="79">
@@ -22924,28 +22924,28 @@
         </is>
       </c>
       <c r="D81" s="18" t="n">
-        <v>14.65151180532053</v>
+        <v>75.88673903969702</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>8.568287407052955</v>
+        <v>79.64487802045781</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>5.659819063101261</v>
+        <v>72.03921171969085</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>83.2505012440366</v>
+        <v>68.91749081148737</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>75.09723116725918</v>
+        <v>63.23416814640645</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>68.40180273423941</v>
+        <v>58.41919081848247</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>64.54551684924029</v>
+        <v>55.58301450212576</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>61.08278472261443</v>
+        <v>52.99588464350579</v>
       </c>
       <c r="L81" s="18" t="n">
         <v>56.64447353242991</v>
@@ -23746,37 +23746,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>1832.740635339991</v>
+        <v>431.8204126588831</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>4983.740734160965</v>
+        <v>989.2340429882775</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>9441.095594502352</v>
+        <v>1573.58745026985</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>8610.734484712159</v>
+        <v>2150.530323689589</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>7813.738807071674</v>
+        <v>2534.973877546137</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>10735.38735948364</v>
+        <v>3125.693051381911</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>8626.250697769443</v>
+        <v>3527.335666950416</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>10487.83852816647</v>
+        <v>4137.367616072798</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>87381801190.86662</v>
+        <v>4683.94707092508</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>147118381938.4514</v>
+        <v>5148.191785509123</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>195348822905.9209</v>
+        <v>5597.98366476403</v>
       </c>
     </row>
     <row r="97">
@@ -23849,28 +23849,28 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>1571.045297242684</v>
+        <v>170.1250745615756</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>3294.44345984352</v>
+        <v>186.6007883771667</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>5004.002857520126</v>
+        <v>194.6556031732468</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>115.4639363645972</v>
+        <v>188.5236783473781</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>123.4779887846495</v>
+        <v>195.807957742021</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>131.2319040072631</v>
+        <v>202.8381735686762</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>138.7288358102183</v>
+        <v>211.5535470326118</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>150.6054722959807</v>
+        <v>224.6286074130145</v>
       </c>
       <c r="L98" s="21" t="n">
         <v>164.3409502555088</v>
@@ -23955,40 +23955,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>1832.740635339991</v>
+        <v>431.8204126588831</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>4983.740734160965</v>
+        <v>989.2340429882775</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>9441.095594502352</v>
+        <v>1573.58745026985</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>8610.734484712159</v>
+        <v>2150.530323689589</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>7813.738807071674</v>
+        <v>2534.973877546137</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>10735.38735948364</v>
+        <v>3125.693051381911</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>8626.250697769443</v>
+        <v>3527.335666950416</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>10487.83852816647</v>
+        <v>4137.367616072798</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>87381801190.86662</v>
+        <v>4683.94707092508</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>147118381938.4514</v>
+        <v>5148.191785509123</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>195348822905.9209</v>
+        <v>5597.98366476403</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>222655633874.9157</v>
+        <v>6189.120866510628</v>
       </c>
     </row>
     <row r="101">
@@ -24061,28 +24061,28 @@
         </is>
       </c>
       <c r="D102" s="18" t="n">
-        <v>-575.7297438140765</v>
+        <v>-24.98164904823225</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>-1066.51866763541</v>
+        <v>-24.98164904823225</v>
       </c>
       <c r="F102" s="18" t="n">
-        <v>-1653.009292928438</v>
+        <v>-24.98164904823225</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>0</v>
+        <v>-24.98164904823225</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>0</v>
+        <v>-24.98164904823225</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>0</v>
+        <v>-24.98164904823225</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>0</v>
+        <v>-24.98164904823225</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>0</v>
+        <v>-24.98164904823226</v>
       </c>
       <c r="L102" s="18" t="n">
         <v>0</v>
@@ -24117,37 +24117,37 @@
         <v>0</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>-545.0180290028316</v>
+        <v>403.0672224090362</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>-2539.878314107392</v>
+        <v>776.2517489414683</v>
       </c>
       <c r="G103" s="18" t="n">
-        <v>-5836.321529998138</v>
+        <v>1151.459487628153</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>-4274.970723119325</v>
+        <v>1727.18923144223</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>-6424.510231070351</v>
+        <v>2104.403344129146</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>-3535.767593092253</v>
+        <v>2680.133087943223</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>-4666.128873917286</v>
+        <v>3059.330116922845</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>-60074984071.88712</v>
+        <v>3440.49355912042</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>-32429770280.67094</v>
+        <v>3991.008811396158</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>6721583342.981387</v>
+        <v>4568.150439866198</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>66796566944.56824</v>
+        <v>5145.280800422396</v>
       </c>
     </row>
     <row r="104">
@@ -24220,28 +24220,28 @@
         </is>
       </c>
       <c r="D105" s="18" t="n">
-        <v>-1464.465240231228</v>
+        <v>-63.54501755012017</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>-3182.385422736978</v>
+        <v>-74.54275127062567</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>-4883.145402499216</v>
+        <v>-73.79814815233796</v>
       </c>
       <c r="G105" s="18" t="n">
-        <v>0</v>
+        <v>-73.05974198278079</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>0</v>
+        <v>-72.32996895737155</v>
       </c>
       <c r="I105" s="18" t="n">
-        <v>0</v>
+        <v>-71.60626956141309</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>0</v>
+        <v>-72.82471122239347</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>0</v>
+        <v>-74.0231351170338</v>
       </c>
       <c r="L105" s="18" t="n">
         <v>0</v>
@@ -24273,40 +24273,40 @@
         </is>
       </c>
       <c r="D106" s="18" t="n">
-        <v>254.3667851046716</v>
+        <v>11.03729974573645</v>
       </c>
       <c r="E106" s="18" t="n">
-        <v>552.7568198325851</v>
+        <v>12.94752478424984</v>
       </c>
       <c r="F106" s="18" t="n">
-        <v>848.1662542132192</v>
+        <v>12.81819272762291</v>
       </c>
       <c r="G106" s="18" t="n">
-        <v>886.2531091453754</v>
+        <v>12.68993703517502</v>
       </c>
       <c r="H106" s="18" t="n">
-        <v>877.3954780539216</v>
+        <v>12.56318085603884</v>
       </c>
       <c r="I106" s="18" t="n">
-        <v>868.6215232733824</v>
+        <v>12.43747962143455</v>
       </c>
       <c r="J106" s="18" t="n">
-        <v>867.6807096388078</v>
+        <v>12.64911392973144</v>
       </c>
       <c r="K106" s="18" t="n">
-        <v>874.4583493230145</v>
+        <v>12.85727130001094</v>
       </c>
       <c r="L106" s="18" t="n">
-        <v>881.1689126103792</v>
+        <v>0</v>
       </c>
       <c r="M106" s="18" t="n">
-        <v>880.0694686667107</v>
+        <v>0</v>
       </c>
       <c r="N106" s="18" t="n">
-        <v>871.2673860610435</v>
+        <v>0</v>
       </c>
       <c r="O106" s="18" t="n">
-        <v>784.8386179004815</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -24326,40 +24326,40 @@
         </is>
       </c>
       <c r="D107" s="18" t="n">
-        <v>-545.0180290028316</v>
+        <v>403.0672224090362</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>-2539.878314107392</v>
+        <v>776.2517489414683</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>-5836.321529998138</v>
+        <v>1151.459487628153</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>-4274.970723119325</v>
+        <v>1727.18923144223</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>-6424.510231070351</v>
+        <v>2104.403344129146</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>-3535.767593092253</v>
+        <v>2680.133087943223</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>-4666.128873917286</v>
+        <v>3059.330116922845</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>-60074984071.88712</v>
+        <v>3440.49355912042</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>-32429770280.67094</v>
+        <v>3991.008811396158</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>6721583342.981387</v>
+        <v>4568.150439866198</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>66796566944.56824</v>
+        <v>5145.280800422396</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>169624299882.3739</v>
+        <v>5722.395457827415</v>
       </c>
     </row>
     <row r="108">

--- a/backend/Rwanda/financial-statements-CleanStep.xlsx
+++ b/backend/Rwanda/financial-statements-CleanStep.xlsx
@@ -2820,37 +2820,37 @@
         <v>214.4942041409722</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>398.6088913081865</v>
+        <v>143.1469118777542</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>587.4304378040704</v>
+        <v>76.28963154195679</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>780.8834687145394</v>
+        <v>14.06601924845287</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>978.8881601587207</v>
+        <v>-43.59826851291083</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>1181.365821584918</v>
+        <v>-96.78203752802462</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>1355.434436145405</v>
+        <v>-178.3674183405251</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>1500.553585379281</v>
+        <v>-288.8949415881805</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>1648.471549711873</v>
+        <v>-396.4590945504012</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>1798.991516858651</v>
+        <v>-296.4685515654974</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>1952.083620707639</v>
+        <v>-193.9052420449733</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>2157.1935306402</v>
+        <v>-39.32350733554805</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -2870,40 +2870,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>214.328410169835</v>
+        <v>214.4942041409722</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>398.060455964663</v>
+        <v>143.1469118777542</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>586.501544715869</v>
+        <v>76.28963154195679</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>779.5817818800881</v>
+        <v>14.06601924845287</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>977.2212283422532</v>
+        <v>-43.59826851291083</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>1179.341079854758</v>
+        <v>-96.78203752802462</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>1353.059207393008</v>
+        <v>-178.3674183405251</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>1497.992424791367</v>
+        <v>-288.8949415881805</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>1645.8917032564</v>
+        <v>-396.4590945504012</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>1796.393614369029</v>
+        <v>-296.4685515654974</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>1949.468281289197</v>
+        <v>-193.9052420449733</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>2154.561362821763</v>
+        <v>-39.32350733554805</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -2976,40 +2976,40 @@
         </is>
       </c>
       <c r="D46" s="18" t="n">
-        <v>0.165793971137203</v>
+        <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>0.548435343523528</v>
+        <v>0</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>0.9288930882013798</v>
+        <v>0</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>1.301686834451326</v>
+        <v>0</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>1.666931816467446</v>
+        <v>0</v>
       </c>
       <c r="I46" s="18" t="n">
-        <v>2.024741730159805</v>
+        <v>0</v>
       </c>
       <c r="J46" s="18" t="n">
-        <v>2.375228752396676</v>
+        <v>0</v>
       </c>
       <c r="K46" s="18" t="n">
-        <v>2.561160587913961</v>
+        <v>0</v>
       </c>
       <c r="L46" s="18" t="n">
-        <v>2.579846455472902</v>
+        <v>0</v>
       </c>
       <c r="M46" s="18" t="n">
-        <v>2.597902489621874</v>
+        <v>0</v>
       </c>
       <c r="N46" s="18" t="n">
-        <v>2.615339418442316</v>
+        <v>0</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>2.632167818437388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" ht="15.5" customHeight="1">
@@ -3032,37 +3032,37 @@
         <v>255.7099427978793</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>512.9801306066329</v>
+        <v>257.5181511762007</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>772.0262143365919</v>
+        <v>260.8854080744783</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>1032.802128707746</v>
+        <v>265.9846792416596</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>1295.257066376957</v>
+        <v>272.7706377053256</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>1559.341063164885</v>
+        <v>281.1932040519421</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>1824.324709765453</v>
+        <v>290.522855279523</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>2088.268647852986</v>
+        <v>298.8201208855246</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>2349.738823795197</v>
+        <v>304.8081795329235</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>2608.591151079998</v>
+        <v>513.1310826558495</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>2864.847962110127</v>
+        <v>718.859099357515</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>3119.342080395842</v>
+        <v>922.825042420094</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -3668,37 +3668,37 @@
         <v>-2.842170943040401e-14</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>50.51073829431505</v>
+        <v>-204.9512411361172</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>101.0214765886302</v>
+        <v>-410.1193296734834</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>151.5322148829453</v>
+        <v>-615.2852345831411</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>202.0429531772604</v>
+        <v>-820.4434754943711</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>252.5536914715753</v>
+        <v>-1025.594167641367</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>303.0644297658898</v>
+        <v>-1230.73742472004</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>353.5751680602048</v>
+        <v>-1435.873358907256</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>404.0859063545208</v>
+        <v>-1640.844737907753</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>454.5966446488355</v>
+        <v>-1640.863423775313</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>505.1073829431512</v>
+        <v>-1640.881479809461</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>555.6181212374668</v>
+        <v>-1640.898916738281</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -3877,40 +3877,40 @@
         </is>
       </c>
       <c r="D63" s="18" t="n">
-        <v>-0.3315879422744061</v>
+        <v>-0.165793971137203</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>-0.7652827447726498</v>
+        <v>-0.3826413723863249</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>-0.7609154893557037</v>
+        <v>-0.3804577446778519</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>-0.7455874924998922</v>
+        <v>-0.3727937462499461</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>-0.7304899640322402</v>
+        <v>-0.3652449820161201</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>-0.7156198273847183</v>
+        <v>-0.3578099136923591</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>-0.7009740444737416</v>
+        <v>-0.3504870222368708</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>-0.3718636710345704</v>
+        <v>-0.1859318355172852</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>-0.0373717351178815</v>
+        <v>-0.01868586755894075</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>-0.03611206829794344</v>
+        <v>-0.01805603414897172</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>-0.03487385764088469</v>
+        <v>-0.01743692882044234</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>-0.03365679999014493</v>
+        <v>-0.01682839999507246</v>
       </c>
     </row>
     <row r="64" ht="15.5" customHeight="1">
@@ -3930,40 +3930,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>1.460190975003197</v>
+        <v>1.625984946140401</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>4.99087470960171</v>
+        <v>5.373516081988035</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>8.934367522239267</v>
+        <v>9.314825266917119</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>12.8156212929488</v>
+        <v>13.18841503919875</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>16.62451489501482</v>
+        <v>16.98975987703095</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>20.3621074064332</v>
+        <v>20.71991732012555</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>24.29399593498742</v>
+        <v>24.64448295722429</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>27.3536017460136</v>
+        <v>27.53953358153089</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>28.94249711461765</v>
+        <v>28.96118298217659</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>30.18173572112492</v>
+        <v>30.19979175527389</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>31.40473142798594</v>
+        <v>31.42216835680638</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>31.99105165766475</v>
+        <v>32.00788005765983</v>
       </c>
     </row>
     <row r="65" ht="15.5" customHeight="1">
@@ -4089,40 +4089,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>-40.96777528946001</v>
+        <v>-40.80198131832281</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>-71.56413966446706</v>
+        <v>-71.18149829208075</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>-66.85509670808896</v>
+        <v>-66.47463896341111</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>-62.215948295076</v>
+        <v>-61.84315454882606</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>-57.65673899712989</v>
+        <v>-57.29149401511377</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>-53.17633394679002</v>
+        <v>-52.81852403309767</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-81.57805792104502</v>
+        <v>-81.22757089880815</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>-110.3629680609358</v>
+        <v>-110.1770362254185</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>-107.3969069942623</v>
+        <v>-107.3782211267033</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>-104.7942743466662</v>
+        <v>-104.7762183125172</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>-102.2215185391273</v>
+        <v>-102.2040816103068</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>-50.20310392672924</v>
+        <v>-50.18627552673417</v>
       </c>
     </row>
     <row r="68" ht="15.5" customHeight="1">
@@ -4463,37 +4463,37 @@
         <v>255.296185459295</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>255.296185459295</v>
+        <v>0</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>255.296185459295</v>
+        <v>0</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>255.296185459295</v>
+        <v>0</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>255.296185459295</v>
+        <v>0</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>255.296185459295</v>
+        <v>0</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>255.296185459295</v>
+        <v>0</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>255.296185459295</v>
+        <v>0</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>255.296185459295</v>
+        <v>0</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>255.296185459295</v>
+        <v>0</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>255.296185459295</v>
+        <v>0</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>255.296185459295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" ht="15.5" customHeight="1">
@@ -4513,40 +4513,40 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>214.328410169835</v>
+        <v>214.4942041409722</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>183.732045794828</v>
+        <v>-71.18149829208075</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>188.4410887512061</v>
+        <v>-66.47463896341111</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>193.080237164219</v>
+        <v>-61.84315454882606</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>197.6394464621652</v>
+        <v>-57.29149401511377</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>202.119851512505</v>
+        <v>-52.81852403309767</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>173.71812753825</v>
+        <v>-81.22757089880815</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>144.9332173983592</v>
+        <v>-110.1770362254185</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>147.8992784650328</v>
+        <v>-107.3782211267033</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>150.5019111126289</v>
+        <v>-104.7762183125172</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>153.0746669201678</v>
+        <v>-102.2040816103068</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>205.0930815325658</v>
+        <v>-50.18627552673417</v>
       </c>
     </row>
     <row r="76" ht="15.5" customHeight="1">
@@ -4569,37 +4569,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>214.328410169835</v>
+        <v>214.4942041409722</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>398.060455964663</v>
+        <v>143.1469118777542</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>586.501544715869</v>
+        <v>76.28963154195679</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>779.5817818800881</v>
+        <v>14.06601924845287</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>977.2212283422532</v>
+        <v>-43.59826851291083</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>1179.341079854758</v>
+        <v>-96.78203752802462</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>1353.059207393008</v>
+        <v>-178.3674183405251</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>1497.992424791367</v>
+        <v>-288.8949415881805</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>1645.8917032564</v>
+        <v>-396.4590945504012</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>1796.393614369029</v>
+        <v>-296.4685515654974</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>1949.468281289197</v>
+        <v>-193.9052420449733</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -4619,40 +4619,40 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>214.328410169835</v>
+        <v>214.4942041409722</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>183.732045794828</v>
+        <v>-71.18149829208075</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>188.4410887512061</v>
+        <v>-66.47463896341111</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>193.080237164219</v>
+        <v>-61.84315454882606</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>197.6394464621652</v>
+        <v>-57.29149401511377</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>202.119851512505</v>
+        <v>-52.81852403309767</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>173.71812753825</v>
+        <v>-81.22757089880815</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>144.9332173983592</v>
+        <v>-110.1770362254185</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>147.8992784650328</v>
+        <v>-107.3782211267033</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>150.5019111126289</v>
+        <v>-104.7762183125172</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>153.0746669201678</v>
+        <v>-102.2040816103068</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>205.0930815325658</v>
+        <v>-50.18627552673417</v>
       </c>
     </row>
     <row r="78" ht="15.5" customHeight="1">
@@ -4672,40 +4672,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>214.328410169835</v>
+        <v>214.4942041409722</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>398.060455964663</v>
+        <v>143.1469118777542</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>586.501544715869</v>
+        <v>76.28963154195679</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>779.5817818800881</v>
+        <v>14.06601924845287</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>977.2212283422532</v>
+        <v>-43.59826851291083</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>1179.341079854758</v>
+        <v>-96.78203752802462</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>1353.059207393008</v>
+        <v>-178.3674183405251</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>1497.992424791367</v>
+        <v>-288.8949415881805</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>1645.8917032564</v>
+        <v>-396.4590945504012</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>1796.393614369029</v>
+        <v>-296.4685515654974</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>1949.468281289197</v>
+        <v>-193.9052420449733</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>2154.561362821763</v>
+        <v>-39.32350733554805</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -5202,40 +5202,40 @@
         </is>
       </c>
       <c r="D88" s="18" t="n">
-        <v>0.165793971137203</v>
+        <v>0</v>
       </c>
       <c r="E88" s="18" t="n">
-        <v>0.548435343523528</v>
+        <v>0</v>
       </c>
       <c r="F88" s="18" t="n">
-        <v>0.9288930882013798</v>
+        <v>0</v>
       </c>
       <c r="G88" s="18" t="n">
-        <v>1.301686834451326</v>
+        <v>0</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>1.666931816467446</v>
+        <v>0</v>
       </c>
       <c r="I88" s="18" t="n">
-        <v>2.024741730159805</v>
+        <v>0</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>2.375228752396676</v>
+        <v>0</v>
       </c>
       <c r="K88" s="18" t="n">
-        <v>2.561160587913961</v>
+        <v>0</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>2.579846455472902</v>
+        <v>0</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>2.597902489621874</v>
+        <v>0</v>
       </c>
       <c r="N88" s="18" t="n">
-        <v>2.615339418442316</v>
+        <v>0</v>
       </c>
       <c r="O88" s="18" t="n">
-        <v>2.632167818437388</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" ht="15.5" customHeight="1">
@@ -5308,40 +5308,40 @@
         </is>
       </c>
       <c r="D90" s="18" t="n">
-        <v>0.3315879422744061</v>
+        <v>0.165793971137203</v>
       </c>
       <c r="E90" s="18" t="n">
-        <v>1.096870687047056</v>
+        <v>0.548435343523528</v>
       </c>
       <c r="F90" s="18" t="n">
-        <v>1.85778617640276</v>
+        <v>0.9288930882013798</v>
       </c>
       <c r="G90" s="18" t="n">
-        <v>2.603373668902652</v>
+        <v>1.301686834451326</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>3.333863632934892</v>
+        <v>1.666931816467446</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>4.04948346031961</v>
+        <v>2.024741730159805</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>4.750457504793352</v>
+        <v>2.375228752396676</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>5.122321175827922</v>
+        <v>2.561160587913961</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>5.159692910945804</v>
+        <v>2.579846455472902</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>5.195804979243747</v>
+        <v>2.597902489621874</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>5.230678836884632</v>
+        <v>2.615339418442316</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>5.264335636874777</v>
+        <v>2.632167818437388</v>
       </c>
     </row>
     <row r="91" ht="15.5" customHeight="1">
@@ -5361,40 +5361,40 @@
         </is>
       </c>
       <c r="D91" s="18" t="n">
-        <v>0.3315879422744061</v>
+        <v>0.165793971137203</v>
       </c>
       <c r="E91" s="18" t="n">
-        <v>0.7652827447726498</v>
+        <v>0.3826413723863249</v>
       </c>
       <c r="F91" s="18" t="n">
-        <v>0.7609154893557037</v>
+        <v>0.3804577446778519</v>
       </c>
       <c r="G91" s="18" t="n">
-        <v>0.7455874924998922</v>
+        <v>0.3727937462499461</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>0.7304899640322402</v>
+        <v>0.3652449820161201</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>0.7156198273847183</v>
+        <v>0.3578099136923591</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>0.7009740444737416</v>
+        <v>0.3504870222368708</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>0.3718636710345704</v>
+        <v>0.1859318355172852</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>0.0373717351178815</v>
+        <v>0.01868586755894075</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>0.03611206829794344</v>
+        <v>0.01805603414897172</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>0.03487385764088469</v>
+        <v>0.01743692882044234</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>0.03365679999014493</v>
+        <v>0.01682839999507246</v>
       </c>
     </row>
     <row r="92" ht="15.5" customHeight="1">
@@ -5656,34 +5656,34 @@
         <v>58.65648807822183</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>125.1759605419378</v>
+        <v>74.66522224762269</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>193.3326243946752</v>
+        <v>92.31114780604497</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>263.0762991947491</v>
+        <v>111.5440843118037</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>334.3576443901693</v>
+        <v>132.3146912129088</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>407.1281475388908</v>
+        <v>154.5744560673152</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>486.557045396698</v>
+        <v>183.4926156308073</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>570.4605265326414</v>
+        <v>216.8853584724357</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>651.4774089715255</v>
+        <v>247.3915026170047</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>729.6326782416476</v>
+        <v>275.0360335928117</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>804.951108820609</v>
+        <v>299.843725877458</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -5865,37 +5865,37 @@
         <v>58.65648807822183</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>125.1759605419378</v>
+        <v>74.66522224762269</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>193.3326243946752</v>
+        <v>92.31114780604497</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>263.0762991947491</v>
+        <v>111.5440843118037</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>334.3576443901693</v>
+        <v>132.3146912129088</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>407.1281475388908</v>
+        <v>154.5744560673152</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>486.557045396698</v>
+        <v>183.4926156308073</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>570.4605265326414</v>
+        <v>216.8853584724357</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>651.4774089715255</v>
+        <v>247.3915026170047</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>729.6326782416476</v>
+        <v>275.0360335928117</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>804.951108820609</v>
+        <v>299.843725877458</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>869.3343293995</v>
+        <v>313.7162081620339</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -8848,40 +8848,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>943.5758334107996</v>
+        <v>920.8667375203886</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>1804.330947065474</v>
+        <v>693.9349505956635</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>2696.001250243566</v>
+        <v>489.8101739751198</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>3599.515955270006</v>
+        <v>299.7152161716678</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>4533.46039089128</v>
+        <v>138.2558748332219</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>5495.699193841769</v>
+        <v>5.121607673304986</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>6445.1142282773</v>
+        <v>-140.7817047138968</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>7396.076523795097</v>
+        <v>-286.1344875256816</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>8390.089435710555</v>
+        <v>-388.761311474055</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>9426.488326929337</v>
+        <v>331.2311499284457</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>10503.91472074392</v>
+        <v>1092.402182419898</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>11603.23802649004</v>
+        <v>1902.858096705899</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -8901,40 +8901,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>929.4422221198872</v>
+        <v>898.1576416299777</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>1787.887758963044</v>
+        <v>667.6847368970334</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>2676.711710517538</v>
+        <v>459.2546068518321</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>3579.30751143439</v>
+        <v>266.8122517881062</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>4510.539848425527</v>
+        <v>101.2419077099342</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>5470.098081513001</v>
+        <v>-35.94306629929775</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>6416.886447455382</v>
+        <v>-185.8135951248557</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>7363.677123795098</v>
+        <v>-336.1007368407501</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>8353.345813792746</v>
+        <v>-443.4087690083016</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>9385.534488573172</v>
+        <v>272.0463526681717</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>10458.90355911936</v>
+        <v>1028.840976940446</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>11551.62482649004</v>
+        <v>1832.384348760694</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -9007,40 +9007,40 @@
         </is>
       </c>
       <c r="D46" s="18" t="n">
-        <v>-8.575484599498539</v>
+        <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>-9.807025596199978</v>
+        <v>0</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>-11.26602739726027</v>
+        <v>0</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>-12.69452054794521</v>
+        <v>0</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>-14.09342465753425</v>
+        <v>0</v>
       </c>
       <c r="I46" s="18" t="n">
-        <v>-15.46356164383562</v>
+        <v>0</v>
       </c>
       <c r="J46" s="18" t="n">
-        <v>-16.8041095890411</v>
+        <v>0</v>
       </c>
       <c r="K46" s="18" t="n">
-        <v>-17.5668493150685</v>
+        <v>0</v>
       </c>
       <c r="L46" s="18" t="n">
-        <v>-17.90383561643835</v>
+        <v>0</v>
       </c>
       <c r="M46" s="18" t="n">
-        <v>-18.23095890410959</v>
+        <v>0</v>
       </c>
       <c r="N46" s="18" t="n">
-        <v>-18.55004385489041</v>
+        <v>0</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>-18.86054794520548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" ht="15.5" customHeight="1">
@@ -9060,40 +9060,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>1231.438849026531</v>
+        <v>1208.72975313612</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>2446.919360341155</v>
+        <v>1336.523363871345</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>3678.393742156435</v>
+        <v>1472.202665887989</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>4906.93548798753</v>
+        <v>1607.134748889192</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>6151.282564959251</v>
+        <v>1756.078048901192</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>7409.441017800518</v>
+        <v>1918.863431632054</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>8680.457036281561</v>
+        <v>2094.561103290363</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>9977.456602624838</v>
+        <v>2295.245591304059</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>11301.08226360603</v>
+        <v>2522.231516421421</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>12650.8352953484</v>
+        <v>3555.578118347514</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>14025.51777082762</v>
+        <v>4614.005232503593</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>15281.8331370015</v>
+        <v>5581.453207217364</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -9143,10 +9143,10 @@
         <v>2738.928132847911</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>2938.086417382266</v>
+        <v>3016.193847786481</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>3108.863491970128</v>
+        <v>3179.787946589689</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -9252,7 +9252,7 @@
         <v>277.2657149385706</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>156.3710522471393</v>
+        <v>163.5940988032079</v>
       </c>
     </row>
     <row r="51" ht="15.5" customHeight="1">
@@ -9302,10 +9302,10 @@
         <v>2174.554755098293</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>2348.614626052073</v>
+        <v>2426.722056456288</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>2640.286363331365</v>
+        <v>2703.987771394859</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -9349,16 +9349,16 @@
         <v>5463.606336853395</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>6322.228958236666</v>
+        <v>6244.121527832452</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>7088.338126875001</v>
+        <v>7024.636718811508</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>7966.541676578826</v>
+        <v>7805.151909790565</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>8731.818232389202</v>
+        <v>8585.66710076962</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -9402,16 +9402,16 @@
         <v>5463.606336853395</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>6322.228958236666</v>
+        <v>6244.121527832452</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>7088.338126875001</v>
+        <v>7024.636718811508</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>7966.541676578826</v>
+        <v>7805.151909790565</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>8731.818232389202</v>
+        <v>8585.66710076962</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -9667,16 +9667,16 @@
         <v>7742.047818568413</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>8826.89362534302</v>
+        <v>8748.786194938806</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>9845.497218627021</v>
+        <v>9781.795810563528</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>10923.17813781598</v>
+        <v>10839.89580143194</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>11859.54227230453</v>
+        <v>11784.31559530452</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -9696,40 +9696,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>22.70909589041071</v>
+        <v>-2.273736754432321e-13</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>338.4562900902529</v>
+        <v>-771.9397063795579</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>654.9677199065327</v>
+        <v>-1551.223356361913</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>969.5211935584284</v>
+        <v>-2330.27954553991</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>1285.838272689777</v>
+        <v>-3109.366243368282</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>1602.095055930716</v>
+        <v>-3888.482530237748</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>1918.268348760695</v>
+        <v>-4667.627584230503</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>2235.408784056424</v>
+        <v>-5446.802227264355</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>2474.188638263013</v>
+        <v>-6226.554678517385</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>2805.338076721384</v>
+        <v>-6226.217692216014</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>3102.339633011634</v>
+        <v>-6225.890568928343</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>3422.29086469697</v>
+        <v>-6202.862388087151</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -9908,40 +9908,40 @@
         </is>
       </c>
       <c r="D63" s="18" t="n">
-        <v>17.15096919899708</v>
+        <v>-14.13361129091242</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>2.463081993402877</v>
+        <v>-2.309576811517742</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>2.918003602120589</v>
+        <v>-2.84635162359724</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>2.856986301369869</v>
+        <v>-0.9189041095890396</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>2.797808219178084</v>
+        <v>-2.712098630136989</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>2.740273972602736</v>
+        <v>-2.680569863013694</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>2.681095890410962</v>
+        <v>-2.626668493150682</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>1.525479452054796</v>
+        <v>-4.171619178082196</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>0.6739726027397168</v>
+        <v>-4.344221917808227</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>0.6542465753424693</v>
+        <v>-4.210216438356156</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>0.6381699015616462</v>
+        <v>-4.057323268397262</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>0.6210081806301346</v>
+        <v>-6.602038375438362</v>
       </c>
     </row>
     <row r="64" ht="15.5" customHeight="1">
@@ -9961,40 +9961,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>133.515706118343</v>
+        <v>102.2311256284335</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>140.66931857446</v>
+        <v>135.8966597695394</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>167.3015827947773</v>
+        <v>161.5372275690594</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>177.3597431710254</v>
+        <v>173.5838527600665</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>202.3247271490623</v>
+        <v>196.8148202997473</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>227.0108866701136</v>
+        <v>221.5900428344972</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>251.4519788299881</v>
+        <v>246.1442144464265</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>288.0960220966529</v>
+        <v>282.3989234665158</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>326.6328696233085</v>
+        <v>321.6146751027605</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>364.8567999361223</v>
+        <v>359.9923369224236</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>401.7820138576175</v>
+        <v>397.0865206876585</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>458.8785621480164</v>
+        <v>451.6555155919479</v>
       </c>
     </row>
     <row r="65" ht="15.5" customHeight="1">
@@ -10120,40 +10120,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>-163.2790452507919</v>
+        <v>-194.5636257407014</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>-234.2757305275222</v>
+        <v>-239.0483893324428</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>-203.897315816185</v>
+        <v>-209.6616710419028</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>-190.1254664538273</v>
+        <v>-193.9013568647862</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>-161.4889303795418</v>
+        <v>-166.9988372288569</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>-133.1630342832046</v>
+        <v>-138.583878118821</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-145.9329014282977</v>
+        <v>-151.2406658118593</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>-145.9305910309628</v>
+        <v>-151.6276896610998</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>-103.0525773730309</v>
+        <v>-108.0707718935789</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>-60.53259259025373</v>
+        <v>-65.39705560395237</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>-19.35219682449474</v>
+        <v>-24.04768999445366</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>169.7671318367248</v>
+        <v>162.5440852806563</v>
       </c>
     </row>
     <row r="68" ht="15.5" customHeight="1">
@@ -10418,7 +10418,7 @@
         <v>0</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>-169.7671318367248</v>
+        <v>-162.5440852806563</v>
       </c>
     </row>
     <row r="73" ht="15.5" customHeight="1">
@@ -10494,37 +10494,37 @@
         <v>1092.721267370679</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>1092.721267370679</v>
+        <v>0</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>1092.721267370679</v>
+        <v>0</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>1092.721267370679</v>
+        <v>0</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>1092.721267370679</v>
+        <v>0</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>1092.721267370679</v>
+        <v>0</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>1092.721267370679</v>
+        <v>0</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>1092.721267370679</v>
+        <v>0</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>1092.721267370679</v>
+        <v>0</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>1092.721267370679</v>
+        <v>0</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>1092.721267370679</v>
+        <v>0</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>922.9541355339543</v>
+        <v>-162.5440852806563</v>
       </c>
     </row>
     <row r="75" ht="15.5" customHeight="1">
@@ -10544,40 +10544,40 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>929.4422221198872</v>
+        <v>898.1576416299777</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>858.4455368431568</v>
+        <v>-239.0483893324428</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>888.823951554494</v>
+        <v>-209.6616710419028</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>902.5958009168517</v>
+        <v>-193.9013568647862</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>931.2323369911371</v>
+        <v>-166.9988372288569</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>959.5582330874744</v>
+        <v>-138.583878118821</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>946.7883659423813</v>
+        <v>-151.2406658118593</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>946.7906763397162</v>
+        <v>-151.6276896610998</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>989.668689997648</v>
+        <v>-108.0707718935789</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>1032.188674780425</v>
+        <v>-65.39705560395237</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>1073.369070546184</v>
+        <v>-24.04768999445366</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>1092.721267370679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" ht="15.5" customHeight="1">
@@ -10600,37 +10600,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>929.4422221198872</v>
+        <v>898.1576416299777</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>1787.887758963044</v>
+        <v>667.6847368970334</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>2676.711710517538</v>
+        <v>459.2546068518321</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>3579.30751143439</v>
+        <v>266.8122517881062</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>4510.539848425527</v>
+        <v>101.2419077099342</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>5470.098081513001</v>
+        <v>-35.94306629929775</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>6416.886447455382</v>
+        <v>-185.8135951248557</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>7363.677123795098</v>
+        <v>-336.1007368407501</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>8353.345813792746</v>
+        <v>-443.4087690083016</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>9385.534488573172</v>
+        <v>272.0463526681717</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>10458.90355911936</v>
+        <v>1028.840976940446</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -10650,40 +10650,40 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>929.4422221198872</v>
+        <v>898.1576416299777</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>858.4455368431568</v>
+        <v>-239.0483893324428</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>888.823951554494</v>
+        <v>-209.6616710419028</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>902.5958009168517</v>
+        <v>-193.9013568647862</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>931.2323369911371</v>
+        <v>-166.9988372288569</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>959.5582330874744</v>
+        <v>-138.583878118821</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>946.7883659423813</v>
+        <v>-151.2406658118593</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>946.7906763397162</v>
+        <v>-151.6276896610998</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>989.668689997648</v>
+        <v>-108.0707718935789</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>1032.188674780425</v>
+        <v>-65.39705560395237</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>1073.369070546184</v>
+        <v>-24.04768999445366</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>1092.721267370679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" ht="15.5" customHeight="1">
@@ -10703,40 +10703,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>929.4422221198872</v>
+        <v>898.1576416299777</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>1787.887758963044</v>
+        <v>667.6847368970334</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>2676.711710517538</v>
+        <v>459.2546068518321</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>3579.30751143439</v>
+        <v>266.8122517881062</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>4510.539848425527</v>
+        <v>101.2419077099342</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>5470.098081513001</v>
+        <v>-35.94306629929775</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>6416.886447455382</v>
+        <v>-185.8135951248557</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>7363.677123795098</v>
+        <v>-336.1007368407501</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>8353.345813792746</v>
+        <v>-443.4087690083016</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>9385.534488573172</v>
+        <v>272.0463526681717</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>10458.90355911936</v>
+        <v>1028.840976940446</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>11551.62482649004</v>
+        <v>1832.384348760694</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -11233,40 +11233,40 @@
         </is>
       </c>
       <c r="D88" s="18" t="n">
-        <v>-8.575484599498539</v>
+        <v>0</v>
       </c>
       <c r="E88" s="18" t="n">
-        <v>-9.807025596199978</v>
+        <v>0</v>
       </c>
       <c r="F88" s="18" t="n">
-        <v>-11.26602739726027</v>
+        <v>0</v>
       </c>
       <c r="G88" s="18" t="n">
-        <v>-12.69452054794521</v>
+        <v>0</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>-14.09342465753425</v>
+        <v>0</v>
       </c>
       <c r="I88" s="18" t="n">
-        <v>-15.46356164383562</v>
+        <v>0</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>-16.8041095890411</v>
+        <v>0</v>
       </c>
       <c r="K88" s="18" t="n">
-        <v>-17.5668493150685</v>
+        <v>0</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>-17.90383561643835</v>
+        <v>0</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>-18.23095890410959</v>
+        <v>0</v>
       </c>
       <c r="N88" s="18" t="n">
-        <v>-18.55004385489041</v>
+        <v>0</v>
       </c>
       <c r="O88" s="18" t="n">
-        <v>-18.86054794520548</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" ht="15.5" customHeight="1">
@@ -11339,40 +11339,40 @@
         </is>
       </c>
       <c r="D90" s="18" t="n">
-        <v>-17.15096919899708</v>
+        <v>14.13361129091242</v>
       </c>
       <c r="E90" s="18" t="n">
-        <v>-19.61405119239996</v>
+        <v>16.44318810243016</v>
       </c>
       <c r="F90" s="18" t="n">
-        <v>-22.53205479452054</v>
+        <v>19.2895397260274</v>
       </c>
       <c r="G90" s="18" t="n">
-        <v>-25.38904109589041</v>
+        <v>20.20844383561644</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>-28.1868493150685</v>
+        <v>22.92054246575343</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>-30.92712328767123</v>
+        <v>25.60111232876712</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>-33.60821917808219</v>
+        <v>28.2277808219178</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>-35.13369863013699</v>
+        <v>32.3994</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>-35.80767123287671</v>
+        <v>36.74362191780823</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>-36.46191780821918</v>
+        <v>40.95383835616438</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>-37.10008770978082</v>
+        <v>45.01116162456164</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>-37.72109589041096</v>
+        <v>51.61320000000001</v>
       </c>
     </row>
     <row r="91" ht="15.5" customHeight="1">
@@ -11392,40 +11392,40 @@
         </is>
       </c>
       <c r="D91" s="18" t="n">
-        <v>-17.15096919899708</v>
+        <v>14.13361129091242</v>
       </c>
       <c r="E91" s="18" t="n">
-        <v>-2.463081993402877</v>
+        <v>2.309576811517742</v>
       </c>
       <c r="F91" s="18" t="n">
-        <v>-2.918003602120589</v>
+        <v>2.84635162359724</v>
       </c>
       <c r="G91" s="18" t="n">
-        <v>-2.856986301369869</v>
+        <v>0.9189041095890396</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>-2.797808219178084</v>
+        <v>2.712098630136989</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>-2.740273972602736</v>
+        <v>2.680569863013694</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>-2.681095890410962</v>
+        <v>2.626668493150682</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>-1.525479452054796</v>
+        <v>4.171619178082196</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>-0.6739726027397168</v>
+        <v>4.344221917808227</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>-0.6542465753424693</v>
+        <v>4.210216438356156</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>-0.6381699015616462</v>
+        <v>4.057323268397262</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>-0.6210081806301346</v>
+        <v>6.602038375438362</v>
       </c>
     </row>
     <row r="92" ht="15.5" customHeight="1">
@@ -11687,34 +11687,34 @@
         <v>497.7465079617789</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>1026.61340208259</v>
+        <v>714.4073256909676</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>1569.496596417865</v>
+        <v>945.0844436346197</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>2110.458288607721</v>
+        <v>1173.840059432852</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>2664.525053682864</v>
+        <v>1415.700748116373</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>3231.534388710174</v>
+        <v>1670.504006752061</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>3821.307171433737</v>
+        <v>1948.070713084002</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>4446.317167141307</v>
+        <v>2260.874632399949</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>4984.409442622896</v>
+        <v>2486.760831489915</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>5470.675389968297</v>
+        <v>2738.92813284791</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>6074.553203639211</v>
+        <v>3016.193847786481</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -11873,7 +11873,7 @@
         <v>0</v>
       </c>
       <c r="O99" s="20" t="n">
-        <v>169.7671318367248</v>
+        <v>162.5440852806563</v>
       </c>
     </row>
     <row r="100" ht="15.5" customHeight="1">
@@ -11896,37 +11896,37 @@
         <v>497.7465079617789</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>1026.61340208259</v>
+        <v>714.4073256909676</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>1569.496596417865</v>
+        <v>945.0844436346197</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>2110.458288607721</v>
+        <v>1173.840059432852</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>2664.525053682864</v>
+        <v>1415.700748116373</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>3231.534388710174</v>
+        <v>1670.504006752061</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>3821.307171433737</v>
+        <v>1948.070713084002</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>4446.317167141307</v>
+        <v>2260.874632399949</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>4984.409442622896</v>
+        <v>2486.760831489915</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>5470.675389968297</v>
+        <v>2738.92813284791</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>6074.553203639211</v>
+        <v>3016.193847786481</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>6784.976237226653</v>
+        <v>3504.876117151001</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -12079,13 +12079,13 @@
         <v>5463.606336853395</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>6322.228958236666</v>
+        <v>6244.121527832452</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>7088.338126875001</v>
+        <v>7024.636718811508</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>7966.541676578826</v>
+        <v>7805.151909790565</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -12288,16 +12288,16 @@
         <v>5463.606336853395</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>6322.228958236666</v>
+        <v>6244.121527832452</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>7088.338126875001</v>
+        <v>7024.636718811508</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>7966.541676578826</v>
+        <v>7805.151909790565</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>8731.818232389202</v>
+        <v>8585.66710076962</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -14879,40 +14879,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>551.0935917130184</v>
+        <v>549.108252377128</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>1087.876586707202</v>
+        <v>507.4961708575325</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>1609.562433646628</v>
+        <v>450.8415224890389</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>2115.646030219804</v>
+        <v>377.9778969038145</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>2606.453216564675</v>
+        <v>289.9035059336485</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>3081.73132727686</v>
+        <v>186.2232430411611</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>3542.921076999049</v>
+        <v>68.53091171767765</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>3998.2412586508</v>
+        <v>-56.21582396717889</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>4450.873747371277</v>
+        <v>-183.7077992454284</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>4900.52628005493</v>
+        <v>-312.5571971662302</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>5347.682161949155</v>
+        <v>-443.8833813511223</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>5791.955059107859</v>
+        <v>-576.0532517713705</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -14932,40 +14932,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>549.2144358801597</v>
+        <v>547.1229130412376</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>1086.570396891729</v>
+        <v>505.3485922054778</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>1608.016251180524</v>
+        <v>447.9572638961622</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>2113.118509930268</v>
+        <v>373.9887495629926</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>2603.817067525088</v>
+        <v>285.2482510539224</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>3077.960321056903</v>
+        <v>180.3911564685583</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>3539.194099390256</v>
+        <v>62.11379028754067</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>3990.181697400639</v>
+        <v>-64.98990550197341</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>4443.412396160323</v>
+        <v>-192.2917005415928</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>4892.140238946876</v>
+        <v>-321.7120381667781</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>5339.934070748825</v>
+        <v>-452.8275175374237</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>5783.390207006471</v>
+        <v>-585.5137192653431</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -15038,40 +15038,40 @@
         </is>
       </c>
       <c r="D46" s="18" t="n">
-        <v>-0.1061835030317407</v>
+        <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>-0.8413888365812087</v>
+        <v>0</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>-1.338076126772904</v>
+        <v>0</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>-1.461627051286592</v>
+        <v>0</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>-2.019105840138757</v>
+        <v>0</v>
       </c>
       <c r="I46" s="18" t="n">
-        <v>-2.06108035264661</v>
+        <v>0</v>
       </c>
       <c r="J46" s="18" t="n">
-        <v>-2.690143821343988</v>
+        <v>0</v>
       </c>
       <c r="K46" s="18" t="n">
-        <v>-0.7145202846336909</v>
+        <v>0</v>
       </c>
       <c r="L46" s="18" t="n">
-        <v>-1.122550085209791</v>
+        <v>0</v>
       </c>
       <c r="M46" s="18" t="n">
-        <v>-0.768799892493468</v>
+        <v>0</v>
       </c>
       <c r="N46" s="18" t="n">
-        <v>-1.196044985970805</v>
+        <v>0</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>-0.8956153925843086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" ht="15.5" customHeight="1">
@@ -15091,40 +15091,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>553.5971114017721</v>
+        <v>551.6117720658816</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>1094.663788754521</v>
+        <v>514.2833729048513</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>1620.29492632996</v>
+        <v>461.5740151723709</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>2129.987021183798</v>
+        <v>392.3188878678087</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>2624.067496827509</v>
+        <v>307.5177861964827</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>3102.285255396505</v>
+        <v>206.7771711608067</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>3565.127242920529</v>
+        <v>90.73707763915748</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>4020.888526120569</v>
+        <v>-33.56855649741013</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>4473.777688970748</v>
+        <v>-160.8038576459569</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>4923.503274277111</v>
+        <v>-289.5802029440493</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>5370.549385139529</v>
+        <v>-421.0161581607487</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>5814.485425095862</v>
+        <v>-553.522885783367</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -15727,40 +15727,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>1.985339335890444</v>
+        <v>0</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>580.4865993527017</v>
+        <v>0.1061835030317297</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>1159.562299994171</v>
+        <v>0.8413888365813023</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>1739.006209442762</v>
+        <v>1.338076126772933</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>2318.011337682313</v>
+        <v>1.461627051286712</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>2897.527190075838</v>
+        <v>2.019105840138906</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>3476.451245634018</v>
+        <v>2.061080352646712</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>4057.147226439323</v>
+        <v>2.690143821344094</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>4635.296066901339</v>
+        <v>0.7145202846337213</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>5214.20602730637</v>
+        <v>1.122550085209923</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>5792.334343192771</v>
+        <v>0.7687998924935755</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>6371.18969520109</v>
+        <v>3.181384321861174</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -15939,40 +15939,40 @@
         </is>
       </c>
       <c r="D63" s="18" t="n">
-        <v>0.2123670060634813</v>
+        <v>-1.87915583285867</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>1.470410667098936</v>
+        <v>0.5729660173850841</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>0.9933745803833898</v>
+        <v>-0.2399926506302228</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>0.2471018490273762</v>
+        <v>-0.9813378234315173</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>1.114957577704331</v>
+        <v>-0.1086287500519441</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>0.08394902501570645</v>
+        <v>-1.134857180368858</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>1.258126937394756</v>
+        <v>0.04402861116313073</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>-3.951247073420595</v>
+        <v>-4.332583641367831</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>0.8160596011522001</v>
+        <v>0.5982100392062355</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>-0.7075003854326458</v>
+        <v>-0.924689897099884</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>0.8544901869546733</v>
+        <v>0.637949907723911</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>-0.6008591867729922</v>
+        <v>-0.8167609010577284</v>
       </c>
     </row>
     <row r="64" ht="15.5" customHeight="1">
@@ -15992,40 +15992,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>-26.4422422968227</v>
+        <v>-28.53376513574485</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>-36.2018041246391</v>
+        <v>-37.09924877435296</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>-52.13295515268695</v>
+        <v>-53.36632238370056</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>-68.49738455395949</v>
+        <v>-69.72582422641838</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>-82.92171123248389</v>
+        <v>-84.14529756024017</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>-99.49743456385137</v>
+        <v>-100.7162407692359</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>-113.4506824922904</v>
+        <v>-114.6647808185221</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>-124.7334688101305</v>
+        <v>-125.1148053780777</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>-122.5009721607336</v>
+        <v>-122.7188217226796</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>-127.0143261927698</v>
+        <v>-127.2315157044371</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>-127.9587302556901</v>
+        <v>-128.1752705349209</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>-132.3549853653821</v>
+        <v>-132.5708870796668</v>
       </c>
     </row>
     <row r="65" ht="15.5" customHeight="1">
@@ -16151,40 +16151,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>-29.12458482048723</v>
+        <v>-31.21610765940938</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>-40.98305968907779</v>
+        <v>-41.88050433879165</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>-56.89316641185139</v>
+        <v>-58.126533642865</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>-73.23676195090243</v>
+        <v>-74.46520162336132</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>-87.64046310582754</v>
+        <v>-88.86404943358382</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>-104.1957671688317</v>
+        <v>-105.4145733742163</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-117.1052423672938</v>
+        <v>-118.3193406935254</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>-127.3514226902642</v>
+        <v>-127.7327592582115</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>-125.1083219409631</v>
+        <v>-125.3261715029091</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>-129.6111779140942</v>
+        <v>-129.8283674257615</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>-130.5451888986984</v>
+        <v>-130.7617291779292</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>-134.8828844430022</v>
+        <v>-135.098786157287</v>
       </c>
     </row>
     <row r="68" ht="15.5" customHeight="1">
@@ -16525,37 +16525,37 @@
         <v>578.339020700647</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>578.339020700647</v>
+        <v>0</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>578.339020700647</v>
+        <v>0</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>578.339020700647</v>
+        <v>0</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>578.339020700647</v>
+        <v>0</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>578.339020700647</v>
+        <v>0</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>578.339020700647</v>
+        <v>0</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>578.339020700647</v>
+        <v>0</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>578.339020700647</v>
+        <v>0</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>578.339020700647</v>
+        <v>0</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>578.339020700647</v>
+        <v>0</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>578.339020700647</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" ht="15.5" customHeight="1">
@@ -16575,40 +16575,40 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>549.2144358801597</v>
+        <v>547.1229130412376</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>537.3559610115692</v>
+        <v>-41.88050433879165</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>521.4458542887955</v>
+        <v>-58.126533642865</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>505.1022587497446</v>
+        <v>-74.46520162336132</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>490.6985575948195</v>
+        <v>-88.86404943358382</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>474.1432535318153</v>
+        <v>-105.4145733742163</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>461.2337783333531</v>
+        <v>-118.3193406935254</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>450.9875980103828</v>
+        <v>-127.7327592582115</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>453.2306987596838</v>
+        <v>-125.3261715029091</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>448.7278427865527</v>
+        <v>-129.8283674257615</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>447.7938318019486</v>
+        <v>-130.7617291779292</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>443.4561362576447</v>
+        <v>-135.098786157287</v>
       </c>
     </row>
     <row r="76" ht="15.5" customHeight="1">
@@ -16631,37 +16631,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>549.2144358801597</v>
+        <v>547.1229130412376</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>1086.570396891729</v>
+        <v>505.3485922054778</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>1608.016251180524</v>
+        <v>447.9572638961622</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>2113.118509930268</v>
+        <v>373.9887495629926</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>2603.817067525088</v>
+        <v>285.2482510539224</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>3077.960321056903</v>
+        <v>180.3911564685583</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>3539.194099390256</v>
+        <v>62.11379028754067</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>3990.181697400639</v>
+        <v>-64.98990550197341</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>4443.412396160323</v>
+        <v>-192.2917005415928</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>4892.140238946876</v>
+        <v>-321.7120381667781</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>5339.934070748825</v>
+        <v>-452.8275175374237</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -16681,40 +16681,40 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>549.2144358801597</v>
+        <v>547.1229130412376</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>537.3559610115692</v>
+        <v>-41.88050433879165</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>521.4458542887955</v>
+        <v>-58.126533642865</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>505.1022587497446</v>
+        <v>-74.46520162336132</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>490.6985575948195</v>
+        <v>-88.86404943358382</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>474.1432535318153</v>
+        <v>-105.4145733742163</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>461.2337783333531</v>
+        <v>-118.3193406935254</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>450.9875980103828</v>
+        <v>-127.7327592582115</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>453.2306987596838</v>
+        <v>-125.3261715029091</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>448.7278427865527</v>
+        <v>-129.8283674257615</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>447.7938318019486</v>
+        <v>-130.7617291779292</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>443.4561362576447</v>
+        <v>-135.098786157287</v>
       </c>
     </row>
     <row r="78" ht="15.5" customHeight="1">
@@ -16734,40 +16734,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>549.2144358801597</v>
+        <v>547.1229130412376</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>1086.570396891729</v>
+        <v>505.3485922054778</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>1608.016251180524</v>
+        <v>447.9572638961622</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>2113.118509930268</v>
+        <v>373.9887495629926</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>2603.817067525088</v>
+        <v>285.2482510539224</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>3077.960321056903</v>
+        <v>180.3911564685583</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>3539.194099390256</v>
+        <v>62.11379028754067</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>3990.181697400639</v>
+        <v>-64.98990550197341</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>4443.412396160323</v>
+        <v>-192.2917005415928</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>4892.140238946876</v>
+        <v>-321.7120381667781</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>5339.934070748825</v>
+        <v>-452.8275175374237</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>5783.390207006471</v>
+        <v>-585.5137192653431</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -17264,40 +17264,40 @@
         </is>
       </c>
       <c r="D88" s="18" t="n">
-        <v>-0.1061835030317407</v>
+        <v>0</v>
       </c>
       <c r="E88" s="18" t="n">
-        <v>-0.8413888365812087</v>
+        <v>0</v>
       </c>
       <c r="F88" s="18" t="n">
-        <v>-1.338076126772904</v>
+        <v>0</v>
       </c>
       <c r="G88" s="18" t="n">
-        <v>-1.461627051286592</v>
+        <v>0</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>-2.019105840138757</v>
+        <v>0</v>
       </c>
       <c r="I88" s="18" t="n">
-        <v>-2.06108035264661</v>
+        <v>0</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>-2.690143821343988</v>
+        <v>0</v>
       </c>
       <c r="K88" s="18" t="n">
-        <v>-0.7145202846336909</v>
+        <v>0</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>-1.122550085209791</v>
+        <v>0</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>-0.768799892493468</v>
+        <v>0</v>
       </c>
       <c r="N88" s="18" t="n">
-        <v>-1.196044985970805</v>
+        <v>0</v>
       </c>
       <c r="O88" s="18" t="n">
-        <v>-0.8956153925843086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" ht="15.5" customHeight="1">
@@ -17370,40 +17370,40 @@
         </is>
       </c>
       <c r="D90" s="18" t="n">
-        <v>-0.2123670060634813</v>
+        <v>1.87915583285867</v>
       </c>
       <c r="E90" s="18" t="n">
-        <v>-1.682777673162417</v>
+        <v>1.306189815473586</v>
       </c>
       <c r="F90" s="18" t="n">
-        <v>-2.676152253545807</v>
+        <v>1.546182466103809</v>
       </c>
       <c r="G90" s="18" t="n">
-        <v>-2.923254102573183</v>
+        <v>2.527520289535326</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>-4.038211680277514</v>
+        <v>2.63614903958727</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>-4.12216070529322</v>
+        <v>3.771006219956129</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>-5.380287642687977</v>
+        <v>3.726977608792998</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>-1.429040569267382</v>
+        <v>8.059561250160829</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>-2.245100170419582</v>
+        <v>7.461351210954594</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>-1.537599784986936</v>
+        <v>8.386041108054478</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>-2.392089971941609</v>
+        <v>7.748091200330567</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>-1.791230785168617</v>
+        <v>8.564852101388295</v>
       </c>
     </row>
     <row r="91" ht="15.5" customHeight="1">
@@ -17423,40 +17423,40 @@
         </is>
       </c>
       <c r="D91" s="18" t="n">
-        <v>-0.2123670060634813</v>
+        <v>1.87915583285867</v>
       </c>
       <c r="E91" s="18" t="n">
-        <v>-1.470410667098936</v>
+        <v>-0.5729660173850841</v>
       </c>
       <c r="F91" s="18" t="n">
-        <v>-0.9933745803833898</v>
+        <v>0.2399926506302228</v>
       </c>
       <c r="G91" s="18" t="n">
-        <v>-0.2471018490273762</v>
+        <v>0.9813378234315173</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>-1.114957577704331</v>
+        <v>0.1086287500519441</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>-0.08394902501570645</v>
+        <v>1.134857180368858</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>-1.258126937394756</v>
+        <v>-0.04402861116313073</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>3.951247073420595</v>
+        <v>4.332583641367831</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>-0.8160596011522001</v>
+        <v>-0.5982100392062355</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>0.7075003854326458</v>
+        <v>0.924689897099884</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>-0.8544901869546733</v>
+        <v>-0.637949907723911</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>0.6008591867729922</v>
+        <v>0.8167609010577284</v>
       </c>
     </row>
     <row r="92" ht="15.5" customHeight="1">
@@ -17718,34 +17718,34 @@
         <v>551.5055885628499</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>1091.674821265885</v>
+        <v>513.3358005652383</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>1616.07259161031</v>
+        <v>459.3945502090168</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>2124.536246791689</v>
+        <v>389.5191846897492</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>2617.393136107644</v>
+        <v>304.0370533050573</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>3094.392088471255</v>
+        <v>202.6969849680213</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>3556.019977669048</v>
+        <v>85.9858534651669</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>4011.39992430114</v>
+        <v>-36.97322060338779</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>4464.071237589375</v>
+        <v>-162.6409280158003</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>4913.57963338407</v>
+        <v>-291.4715529217525</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>5360.409203967256</v>
+        <v>-422.9810030392129</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -17927,37 +17927,37 @@
         <v>551.5055885628499</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>1091.674821265885</v>
+        <v>513.3358005652383</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>1616.07259161031</v>
+        <v>459.3945502090168</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>2124.536246791689</v>
+        <v>389.5191846897492</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>2617.393136107644</v>
+        <v>304.0370533050573</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>3094.392088471255</v>
+        <v>202.6969849680213</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>3556.019977669048</v>
+        <v>85.9858534651669</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>4011.39992430114</v>
+        <v>-36.97322060338779</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>4464.071237589375</v>
+        <v>-162.6409280158003</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>4913.57963338407</v>
+        <v>-291.4715529217525</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>5360.409203967256</v>
+        <v>-422.9810030392129</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>5804.129342209303</v>
+        <v>-557.5998854978122</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -20910,40 +20910,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>728.0947567237049</v>
+        <v>705.7675525923769</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>1399.196074945698</v>
+        <v>545.5142829331834</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>2091.949795213938</v>
+        <v>398.7196402316764</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>2789.42521648785</v>
+        <v>258.6136627131216</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>3508.224605856394</v>
+        <v>138.2286149043626</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>4246.334299716566</v>
+        <v>37.19319058275833</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>4995.471160314218</v>
+        <v>-52.76153761687472</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>5759.615904440761</v>
+        <v>-127.8016784792381</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>6548.333656506655</v>
+        <v>-178.6261573555255</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>7360.968960392492</v>
+        <v>370.0440587087102</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>8196.587383104083</v>
+        <v>941.801569128346</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>9038.073332223403</v>
+        <v>1544.514707993967</v>
       </c>
     </row>
     <row r="44">
@@ -20963,40 +20963,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>714.1772432207383</v>
+        <v>683.440348461049</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>1383.788264468883</v>
+        <v>520.8478822036918</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>2074.648348110827</v>
+        <v>371.0810588195063</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>2771.944607851709</v>
+        <v>229.7402203634867</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>3488.962601677472</v>
+        <v>106.5401178843739</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>4225.330927212288</v>
+        <v>2.750998164803988</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>4972.779014774398</v>
+        <v>-89.88256399333916</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>5734.750702790961</v>
+        <v>-167.6725688561934</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>6521.092798369359</v>
+        <v>-221.191004653787</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>7331.449119350613</v>
+        <v>324.8911612523441</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>8164.894548635995</v>
+        <v>894.1740302238113</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>9002.319630547379</v>
+        <v>1492.532626191176</v>
       </c>
     </row>
     <row r="45">
@@ -21069,40 +21069,40 @@
         </is>
       </c>
       <c r="D46" s="18" t="n">
-        <v>-8.409690628361332</v>
+        <v>0</v>
       </c>
       <c r="E46" s="18" t="n">
-        <v>-9.258590252676456</v>
+        <v>0</v>
       </c>
       <c r="F46" s="18" t="n">
-        <v>-10.3371343090589</v>
+        <v>0</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>-11.39283371349388</v>
+        <v>0</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>-12.4264928410668</v>
+        <v>0</v>
       </c>
       <c r="I46" s="18" t="n">
-        <v>-13.43881991367581</v>
+        <v>0</v>
       </c>
       <c r="J46" s="18" t="n">
-        <v>-14.42888083664442</v>
+        <v>0</v>
       </c>
       <c r="K46" s="18" t="n">
-        <v>-15.00568872715453</v>
+        <v>0</v>
       </c>
       <c r="L46" s="18" t="n">
-        <v>-15.32398916096545</v>
+        <v>0</v>
       </c>
       <c r="M46" s="18" t="n">
-        <v>-15.63305641448772</v>
+        <v>0</v>
       </c>
       <c r="N46" s="18" t="n">
-        <v>-15.9347044364481</v>
+        <v>0</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>-16.22838012676809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -21122,40 +21122,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>974.7420336825287</v>
+        <v>952.4148295512007</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>1927.413248922933</v>
+        <v>1073.731456910418</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>2889.746510594287</v>
+        <v>1196.516355612025</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>3844.926089212167</v>
+        <v>1314.114535437439</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>4809.677873706129</v>
+        <v>1439.681882754097</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>5782.10088209535</v>
+        <v>1572.959772961542</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>6761.923694698429</v>
+        <v>1713.690996767337</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>7753.280920796797</v>
+        <v>1865.863337876797</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>8758.059210318806</v>
+        <v>2031.099396456627</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>9775.716294590213</v>
+        <v>2784.791392906431</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>10805.42609178529</v>
+        <v>3550.640277809553</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>11754.51989297923</v>
+        <v>4260.96126874979</v>
       </c>
     </row>
     <row r="48">
@@ -21181,34 +21181,34 @@
         <v>618.4212010360498</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>922.1943080642168</v>
+        <v>813.0768042092967</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>1238.720452422614</v>
+        <v>1001.600482556675</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>1561.252267139688</v>
+        <v>1197.408440298696</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>1691.030698725584</v>
+        <v>1400.246613867372</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>2028.769907927984</v>
+        <v>1611.800160899984</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>2181.792245779586</v>
+        <v>1836.428768312999</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>2469.841199647154</v>
+        <v>2000.769718568508</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>2767.719251095017</v>
+        <v>2178.104603516902</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>2982.442168446919</v>
+        <v>2367.613029330465</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>3088.050784484931</v>
+        <v>2479.281748613017</v>
       </c>
     </row>
     <row r="49">
@@ -21314,7 +21314,7 @@
         <v>189.5084258135635</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>107.0205006939758</v>
+        <v>111.6687192825518</v>
       </c>
     </row>
     <row r="51">
@@ -21340,34 +21340,34 @@
         <v>170.1250745615756</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>465.8433667936624</v>
+        <v>356.7258629387424</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>788.5014359779282</v>
+        <v>551.3814661119893</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>1103.74897130036</v>
+        <v>739.9051444593674</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>1226.4971870596</v>
+        <v>935.7131022013884</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>1555.521022798065</v>
+        <v>1138.551275770065</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>1695.468300269264</v>
+        <v>1350.104822802677</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>2043.804911294337</v>
+        <v>1574.733430215691</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>2328.689028049315</v>
+        <v>1739.0743804712</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>2531.238404536048</v>
+        <v>1916.409265419594</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>2719.334945693648</v>
+        <v>2105.917691233158</v>
       </c>
     </row>
     <row r="52">
@@ -21387,40 +21387,40 @@
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>403.0672224090362</v>
+        <v>512.1847262639563</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>776.2517489414683</v>
+        <v>1013.371718807407</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>1151.459487628153</v>
+        <v>1515.303314469146</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>1727.18923144223</v>
+        <v>2017.973316300442</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>2104.403344129146</v>
+        <v>2521.373091157147</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>2680.133087943223</v>
+        <v>3025.49656540981</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>3059.330116922845</v>
+        <v>3528.401598001493</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>3440.49355912042</v>
+        <v>4030.108206698536</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>3991.008811396158</v>
+        <v>4605.837950512612</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>4568.150439866198</v>
+        <v>5181.567694326689</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>5145.280800422396</v>
+        <v>5757.297438140766</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>5722.395457827415</v>
+        <v>6333.027181954842</v>
       </c>
     </row>
     <row r="53">
@@ -21440,40 +21440,40 @@
         </is>
       </c>
       <c r="D53" s="18" t="n">
-        <v>403.0672224090362</v>
+        <v>512.1847262639563</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>776.2517489414683</v>
+        <v>1013.371718807407</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>1151.459487628153</v>
+        <v>1515.303314469146</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>1727.18923144223</v>
+        <v>2017.973316300442</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>2104.403344129146</v>
+        <v>2521.373091157147</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>2680.133087943223</v>
+        <v>3025.49656540981</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>3059.330116922845</v>
+        <v>3528.401598001493</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>3440.49355912042</v>
+        <v>4030.108206698536</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>3991.008811396158</v>
+        <v>4605.837950512612</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>4568.150439866198</v>
+        <v>5181.567694326689</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>5145.280800422396</v>
+        <v>5757.297438140766</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>5722.395457827415</v>
+        <v>6333.027181954842</v>
       </c>
     </row>
     <row r="54">
@@ -21705,40 +21705,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>843.2973256962806</v>
+        <v>952.4148295512008</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>1403.931540230195</v>
+        <v>1641.051510096134</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>2083.990930001429</v>
+        <v>2338.717252987501</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>2977.302517578337</v>
+        <v>3030.96663257061</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>3678.082104109901</v>
+        <v>3731.20802429691</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>4384.602606582482</v>
+        <v>4439.181999190858</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>5102.528905687474</v>
+        <v>5154.630639738121</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>5637.291493627161</v>
+        <v>5881.54266373869</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>6476.174000204278</v>
+        <v>6621.931658242086</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>7351.502747375703</v>
+        <v>7375.305354258077</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>8143.657673305763</v>
+        <v>8140.845171907678</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>8826.674622439114</v>
+        <v>8828.537310694626</v>
       </c>
     </row>
     <row r="59">
@@ -21758,40 +21758,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>131.4447079862481</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>523.481708692738</v>
+        <v>-567.3200531857153</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>805.7555805928578</v>
+        <v>-1142.200897375476</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>867.6235716338301</v>
+        <v>-1716.852097133171</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>1131.595769596228</v>
+        <v>-2291.526141542813</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>1397.498275512869</v>
+        <v>-2866.222226229316</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>1659.394789010955</v>
+        <v>-3440.939642970784</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>2115.989427169636</v>
+        <v>-4015.679325861893</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>2281.885210114528</v>
+        <v>-4590.832261785459</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>2424.21354721451</v>
+        <v>-4590.513961351647</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>2661.768418479527</v>
+        <v>-4590.204894098125</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>2927.845270540112</v>
+        <v>-4567.576041944836</v>
       </c>
     </row>
     <row r="60">
@@ -21970,40 +21970,40 @@
         </is>
       </c>
       <c r="D63" s="18" t="n">
-        <v>16.81938125672266</v>
+        <v>-13.9175135029666</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>1.697799248630247</v>
+        <v>-1.490296973848487</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>2.157088112764882</v>
+        <v>-1.893636626296129</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>2.111398808869975</v>
+        <v>-0.1791615330298164</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>2.067318255145832</v>
+        <v>-1.781395542780828</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>2.024654145218015</v>
+        <v>-1.741368325356682</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>1.98012184593723</v>
+        <v>-1.68877303554148</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>1.153615781020211</v>
+        <v>-2.173056109980713</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>0.6366008676218513</v>
+        <v>-2.375656487495363</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>0.6181345070445268</v>
+        <v>-2.278982904582236</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>0.6032960439207606</v>
+        <v>-2.172993426208347</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>0.587351380639987</v>
+        <v>-4.060867207935981</v>
       </c>
     </row>
     <row r="64">
@@ -22023,40 +22023,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>131.1189464140258</v>
+        <v>100.3820516543365</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>130.5759740646737</v>
+        <v>127.387877842195</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>148.8444361111943</v>
+        <v>144.7937113721333</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>152.3248178663257</v>
+        <v>150.0342575244259</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>169.1253155508383</v>
+        <v>165.2766017529117</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>185.5787232235269</v>
+        <v>181.8127007529522</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>201.5358320529799</v>
+        <v>197.8669371715012</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>220.8566494258443</v>
+        <v>217.5299775348434</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>242.2630565544729</v>
+        <v>239.2507991993558</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>263.3446215284549</v>
+        <v>260.4475041168282</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>283.5283080889975</v>
+        <v>280.7520186188684</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>318.828264575615</v>
+        <v>314.1800459870391</v>
       </c>
     </row>
     <row r="65">
@@ -22182,40 +22182,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>-123.2478386906458</v>
+        <v>-153.9847334503351</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>-167.8140606632397</v>
+        <v>-171.0021568857184</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>-146.5649982694397</v>
+        <v>-150.6157230085008</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>-140.1288221705022</v>
+        <v>-142.419382512402</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>-120.4070880856212</v>
+        <v>-124.2558018835478</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>-101.0567563765681</v>
+        <v>-104.8227788471428</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-89.97699434927347</v>
+        <v>-93.64588923075218</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>-75.45339389482191</v>
+        <v>-78.78006578582284</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>-51.08298633298654</v>
+        <v>-54.09524368810372</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>-27.06876093013</v>
+        <v>-29.96587834175676</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>-3.979652626001496</v>
+        <v>-6.755942096130582</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>111.9109898487174</v>
+        <v>107.2627712601415</v>
       </c>
     </row>
     <row r="68">
@@ -22480,7 +22480,7 @@
         <v>0</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>-111.9109898487174</v>
+        <v>-107.2627712601415</v>
       </c>
     </row>
     <row r="73">
@@ -22556,37 +22556,37 @@
         <v>837.425081911384</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>837.425081911384</v>
+        <v>0</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>837.425081911384</v>
+        <v>0</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>837.425081911384</v>
+        <v>0</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>837.425081911384</v>
+        <v>0</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>837.425081911384</v>
+        <v>0</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>837.425081911384</v>
+        <v>0</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>837.425081911384</v>
+        <v>0</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>837.425081911384</v>
+        <v>0</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>837.425081911384</v>
+        <v>0</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>837.425081911384</v>
+        <v>0</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>725.5140920626666</v>
+        <v>-107.2627712601415</v>
       </c>
     </row>
     <row r="75">
@@ -22606,40 +22606,40 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>714.1772432207383</v>
+        <v>683.440348461049</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>669.6110212481444</v>
+        <v>-171.0021568857184</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>690.8600836419444</v>
+        <v>-150.6157230085008</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>697.2962597408819</v>
+        <v>-142.419382512402</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>717.0179938257629</v>
+        <v>-124.2558018835478</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>736.368325534816</v>
+        <v>-104.8227788471428</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>747.4480875621106</v>
+        <v>-93.64588923075218</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>761.9716880165621</v>
+        <v>-78.78006578582284</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>786.3420955783974</v>
+        <v>-54.09524368810372</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>810.356320981254</v>
+        <v>-29.96587834175676</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>833.4454292853825</v>
+        <v>-6.755942096130582</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>837.425081911384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -22662,37 +22662,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>714.1772432207383</v>
+        <v>683.440348461049</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>1383.788264468883</v>
+        <v>520.8478822036918</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>2074.648348110827</v>
+        <v>371.0810588195063</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>2771.944607851709</v>
+        <v>229.7402203634867</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>3488.962601677472</v>
+        <v>106.5401178843739</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>4225.330927212288</v>
+        <v>2.750998164803988</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>4972.779014774398</v>
+        <v>-89.88256399333916</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>5734.750702790961</v>
+        <v>-167.6725688561934</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>6521.092798369359</v>
+        <v>-221.191004653787</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>7331.449119350613</v>
+        <v>324.8911612523441</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>8164.894548635995</v>
+        <v>894.1740302238113</v>
       </c>
     </row>
     <row r="77">
@@ -22712,40 +22712,40 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>714.1772432207383</v>
+        <v>683.440348461049</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>669.6110212481444</v>
+        <v>-171.0021568857184</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>690.8600836419444</v>
+        <v>-150.6157230085008</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>697.2962597408819</v>
+        <v>-142.419382512402</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>717.0179938257629</v>
+        <v>-124.2558018835478</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>736.368325534816</v>
+        <v>-104.8227788471428</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>747.4480875621106</v>
+        <v>-93.64588923075218</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>761.9716880165621</v>
+        <v>-78.78006578582284</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>786.3420955783974</v>
+        <v>-54.09524368810372</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>810.356320981254</v>
+        <v>-29.96587834175676</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>833.4454292853825</v>
+        <v>-6.755942096130582</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>837.425081911384</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -22765,40 +22765,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>714.1772432207383</v>
+        <v>683.440348461049</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>1383.788264468883</v>
+        <v>520.8478822036918</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>2074.648348110827</v>
+        <v>371.0810588195063</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>2771.944607851709</v>
+        <v>229.7402203634867</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>3488.962601677472</v>
+        <v>106.5401178843739</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>4225.330927212288</v>
+        <v>2.750998164803988</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>4972.779014774398</v>
+        <v>-89.88256399333916</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>5734.750702790961</v>
+        <v>-167.6725688561934</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>6521.092798369359</v>
+        <v>-221.191004653787</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>7331.449119350613</v>
+        <v>324.8911612523441</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>8164.894548635995</v>
+        <v>894.1740302238113</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>9002.319630547379</v>
+        <v>1492.532626191176</v>
       </c>
     </row>
     <row r="79">
@@ -23295,40 +23295,40 @@
         </is>
       </c>
       <c r="D88" s="18" t="n">
-        <v>-8.409690628361332</v>
+        <v>0</v>
       </c>
       <c r="E88" s="18" t="n">
-        <v>-9.258590252676456</v>
+        <v>0</v>
       </c>
       <c r="F88" s="18" t="n">
-        <v>-10.3371343090589</v>
+        <v>0</v>
       </c>
       <c r="G88" s="18" t="n">
-        <v>-11.39283371349388</v>
+        <v>0</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>-12.4264928410668</v>
+        <v>0</v>
       </c>
       <c r="I88" s="18" t="n">
-        <v>-13.43881991367581</v>
+        <v>0</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>-14.42888083664442</v>
+        <v>0</v>
       </c>
       <c r="K88" s="18" t="n">
-        <v>-15.00568872715453</v>
+        <v>0</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>-15.32398916096545</v>
+        <v>0</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>-15.63305641448772</v>
+        <v>0</v>
       </c>
       <c r="N88" s="18" t="n">
-        <v>-15.9347044364481</v>
+        <v>0</v>
       </c>
       <c r="O88" s="18" t="n">
-        <v>-16.22838012676809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -23401,40 +23401,40 @@
         </is>
       </c>
       <c r="D90" s="18" t="n">
-        <v>-16.81938125672266</v>
+        <v>13.9175135029666</v>
       </c>
       <c r="E90" s="18" t="n">
-        <v>-18.51718050535291</v>
+        <v>15.40781047681508</v>
       </c>
       <c r="F90" s="18" t="n">
-        <v>-20.67426861811779</v>
+        <v>17.30144710311121</v>
       </c>
       <c r="G90" s="18" t="n">
-        <v>-22.78566742698777</v>
+        <v>17.48060863614103</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>-24.8529856821336</v>
+        <v>19.26200417892186</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>-26.87763982735162</v>
+        <v>21.00337250427854</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>-28.85776167328885</v>
+        <v>22.69214553982002</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>-30.01137745430906</v>
+        <v>24.86520164980073</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>-30.64797832193091</v>
+        <v>27.24085813729609</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>-31.26611282897543</v>
+        <v>29.51984104187833</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>-31.86940887289619</v>
+        <v>31.69283446808668</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>-32.45676025353618</v>
+        <v>35.75370167602266</v>
       </c>
     </row>
     <row r="91">
@@ -23454,40 +23454,40 @@
         </is>
       </c>
       <c r="D91" s="18" t="n">
-        <v>-16.81938125672266</v>
+        <v>13.9175135029666</v>
       </c>
       <c r="E91" s="18" t="n">
-        <v>-1.697799248630247</v>
+        <v>1.490296973848487</v>
       </c>
       <c r="F91" s="18" t="n">
-        <v>-2.157088112764882</v>
+        <v>1.893636626296129</v>
       </c>
       <c r="G91" s="18" t="n">
-        <v>-2.111398808869975</v>
+        <v>0.1791615330298164</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>-2.067318255145832</v>
+        <v>1.781395542780828</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>-2.024654145218015</v>
+        <v>1.741368325356682</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>-1.98012184593723</v>
+        <v>1.68877303554148</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>-1.153615781020211</v>
+        <v>2.173056109980713</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>-0.6366008676218513</v>
+        <v>2.375656487495363</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>-0.6181345070445268</v>
+        <v>2.278982904582236</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>-0.6032960439207606</v>
+        <v>2.172993426208347</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>-0.587351380639987</v>
+        <v>4.060867207935981</v>
       </c>
     </row>
     <row r="92">
@@ -23749,34 +23749,34 @@
         <v>431.8204126588831</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>989.2340429882775</v>
+        <v>618.4212010360498</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>1573.58745026985</v>
+        <v>813.0768042092966</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>2150.530323689589</v>
+        <v>1001.600482556675</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>2534.973877546137</v>
+        <v>1197.408440298696</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>3125.693051381911</v>
+        <v>1400.246613867372</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>3527.335666950416</v>
+        <v>1611.800160899984</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>4137.367616072798</v>
+        <v>1836.428768312998</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>4683.94707092508</v>
+        <v>2000.769718568507</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>5148.191785509123</v>
+        <v>2178.104603516901</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>5597.98366476403</v>
+        <v>2367.613029330465</v>
       </c>
     </row>
     <row r="97">
@@ -23935,7 +23935,7 @@
         <v>0</v>
       </c>
       <c r="O99" s="20" t="n">
-        <v>111.9109898487174</v>
+        <v>107.2627712601415</v>
       </c>
     </row>
     <row r="100">
@@ -23958,37 +23958,37 @@
         <v>431.8204126588831</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>989.2340429882775</v>
+        <v>618.4212010360498</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>1573.58745026985</v>
+        <v>813.0768042092966</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>2150.530323689589</v>
+        <v>1001.600482556675</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>2534.973877546137</v>
+        <v>1197.408440298696</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>3125.693051381911</v>
+        <v>1400.246613867372</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>3527.335666950416</v>
+        <v>1611.800160899984</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>4137.367616072798</v>
+        <v>1836.428768312998</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>4683.94707092508</v>
+        <v>2000.769718568507</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>5148.191785509123</v>
+        <v>2178.104603516901</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>5597.98366476403</v>
+        <v>2367.613029330465</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>6189.120866510628</v>
+        <v>2693.8072911333</v>
       </c>
     </row>
     <row r="101">
@@ -24117,37 +24117,37 @@
         <v>0</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>403.0672224090362</v>
+        <v>512.1847262639563</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>776.2517489414683</v>
+        <v>1013.371718807407</v>
       </c>
       <c r="G103" s="18" t="n">
-        <v>1151.459487628153</v>
+        <v>1515.303314469146</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>1727.18923144223</v>
+        <v>2017.973316300442</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>2104.403344129146</v>
+        <v>2521.373091157147</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>2680.133087943223</v>
+        <v>3025.49656540981</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>3059.330116922845</v>
+        <v>3528.401598001493</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>3440.49355912042</v>
+        <v>4030.108206698536</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>3991.008811396158</v>
+        <v>4605.837950512612</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>4568.150439866198</v>
+        <v>5181.567694326689</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>5145.280800422396</v>
+        <v>5757.297438140766</v>
       </c>
     </row>
     <row r="104">
@@ -24326,40 +24326,40 @@
         </is>
       </c>
       <c r="D107" s="18" t="n">
-        <v>403.0672224090362</v>
+        <v>512.1847262639563</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>776.2517489414683</v>
+        <v>1013.371718807407</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>1151.459487628153</v>
+        <v>1515.303314469146</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>1727.18923144223</v>
+        <v>2017.973316300442</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>2104.403344129146</v>
+        <v>2521.373091157147</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>2680.133087943223</v>
+        <v>3025.49656540981</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>3059.330116922845</v>
+        <v>3528.401598001493</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>3440.49355912042</v>
+        <v>4030.108206698536</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>3991.008811396158</v>
+        <v>4605.837950512612</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>4568.150439866198</v>
+        <v>5181.567694326689</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>5145.280800422396</v>
+        <v>5757.297438140766</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>5722.395457827415</v>
+        <v>6333.027181954842</v>
       </c>
     </row>
     <row r="108">

--- a/backend/Rwanda/financial-statements-CleanStep.xlsx
+++ b/backend/Rwanda/financial-statements-CleanStep.xlsx
@@ -654,28 +654,28 @@
         </is>
       </c>
       <c r="D2" s="18" t="n">
-        <v>0</v>
+        <v>13.53164037743546</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>0</v>
+        <v>24.41585149620903</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>0</v>
+        <v>24.17169298124697</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>0</v>
+        <v>23.92997605143447</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>0</v>
+        <v>23.69067629092016</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>0</v>
+        <v>23.45376952801096</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>0</v>
+        <v>33.76599646257955</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>0</v>
+        <v>43.92223480677366</v>
       </c>
       <c r="L2" s="18" t="n">
         <v>0</v>
@@ -710,28 +710,28 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>0</v>
+        <v>80.43526738209378</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>0</v>
+        <v>-0.9999999999998677</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>0</v>
+        <v>-1.000000000000134</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>0</v>
+        <v>-0.9999999999998677</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>0</v>
+        <v>-0.9999999999999787</v>
       </c>
       <c r="J3" s="18" t="n">
-        <v>0</v>
+        <v>43.96831358921918</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>0</v>
+        <v>30.07830186634517</v>
       </c>
       <c r="L3" s="18" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M3" s="18" t="n">
         <v>0</v>
@@ -866,28 +866,28 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>0</v>
+        <v>13.53164037743546</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>0</v>
+        <v>24.41585149620903</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>0</v>
+        <v>24.17169298124697</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0</v>
+        <v>23.92997605143447</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>0</v>
+        <v>23.69067629092016</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>0</v>
+        <v>23.45376952801096</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>0</v>
+        <v>33.76599646257955</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>0</v>
+        <v>43.92223480677366</v>
       </c>
       <c r="L6" s="18" t="n">
         <v>0</v>
@@ -922,28 +922,28 @@
         <v>0</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>0</v>
+        <v>80.43526738209378</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>0</v>
+        <v>-0.9999999999998677</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>0</v>
+        <v>-1.000000000000134</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>0</v>
+        <v>-0.9999999999998677</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>0</v>
+        <v>-0.9999999999999787</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>0</v>
+        <v>43.96831358921918</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>0</v>
+        <v>30.07830186634517</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M7" s="18" t="n">
         <v>0</v>
@@ -972,28 +972,28 @@
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L8" s="18" t="n">
         <v>0</v>
@@ -1184,40 +1184,40 @@
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>0</v>
+        <v>15.9727170647754</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>0</v>
+        <v>33.84357787023427</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>0</v>
+        <v>51.17424615674241</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0</v>
+        <v>65.69866587915647</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>0</v>
+        <v>78.79481748459472</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>0</v>
+        <v>94.8624875656817</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>0</v>
+        <v>112.5371068556073</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>0</v>
+        <v>124.4023054054982</v>
       </c>
       <c r="L12" s="18" t="n">
-        <v>0</v>
+        <v>134.4902175763298</v>
       </c>
       <c r="M12" s="18" t="n">
-        <v>0</v>
+        <v>143.3465373242153</v>
       </c>
       <c r="N12" s="18" t="n">
-        <v>0</v>
+        <v>151.1276736863108</v>
       </c>
       <c r="O12" s="18" t="n">
-        <v>0</v>
+        <v>145.7201053343782</v>
       </c>
     </row>
     <row r="13" ht="15.5" customHeight="1">
@@ -1240,37 +1240,37 @@
         <v>0</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>0</v>
+        <v>111.8836622034046</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>0</v>
+        <v>51.20814457903584</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0</v>
+        <v>28.38228369388574</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>0</v>
+        <v>19.93366445146208</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>0</v>
+        <v>20.39178539150548</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>0</v>
+        <v>18.63183197434908</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>0</v>
+        <v>10.5433655452994</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>0</v>
+        <v>8.109103877094071</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>0</v>
+        <v>6.5851032941181</v>
       </c>
       <c r="N13" s="18" t="n">
-        <v>0</v>
+        <v>5.428199737044515</v>
       </c>
       <c r="O13" s="18" t="n">
-        <v>0</v>
+        <v>-3.578145696304991</v>
       </c>
     </row>
     <row r="14" ht="15.5" customHeight="1">
@@ -1290,28 +1290,28 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>0</v>
+        <v>118.0397691577034</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>0</v>
+        <v>138.6131377621176</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>0</v>
+        <v>211.7114684372531</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>0</v>
+        <v>274.545472749097</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>0</v>
+        <v>332.5984303571533</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>0</v>
+        <v>404.4658469607068</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>0</v>
+        <v>333.2853125786593</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>0</v>
+        <v>283.2330958403622</v>
       </c>
       <c r="L14" s="18" t="n">
         <v>0</v>
@@ -1343,40 +1343,40 @@
         </is>
       </c>
       <c r="D15" s="18" t="n">
-        <v>0</v>
+        <v>3.717079788408142</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0</v>
+        <v>15.65665112200551</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>0</v>
+        <v>27.13940627304481</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0</v>
+        <v>40.3742305752267</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>0</v>
+        <v>53.99434965844836</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>0</v>
+        <v>63.61067809070158</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>0</v>
+        <v>76.9990766024128</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>0</v>
+        <v>99.43127335078191</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>0</v>
+        <v>120.2768928036691</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>0</v>
+        <v>141.0307610726109</v>
       </c>
       <c r="N15" s="18" t="n">
-        <v>0</v>
+        <v>161.5496749956891</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>0</v>
+        <v>181.7161807456525</v>
       </c>
     </row>
     <row r="16" ht="15.5" customHeight="1">
@@ -1399,37 +1399,37 @@
         <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>0</v>
+        <v>321.2083682150538</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>0</v>
+        <v>73.3410680327431</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>0</v>
+        <v>48.76607899608651</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>0</v>
+        <v>33.73468395352863</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>0</v>
+        <v>17.80987916899297</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>0</v>
+        <v>21.04740731205677</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>0</v>
+        <v>29.13307241877519</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>0</v>
+        <v>20.9648521540565</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>0</v>
+        <v>17.2550751729335</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>0</v>
+        <v>14.54924710539844</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>0</v>
+        <v>12.48316082994385</v>
       </c>
     </row>
     <row r="17" ht="15.5" customHeight="1">
@@ -1449,28 +1449,28 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>0</v>
+        <v>-27.46954312062947</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>0</v>
+        <v>-64.12494409394843</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>0</v>
+        <v>-112.2776393614641</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0</v>
+        <v>-168.7182239064819</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>0</v>
+        <v>-227.9139227407475</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>0</v>
+        <v>-271.2172898890773</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>0</v>
+        <v>-228.037329470627</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>0</v>
+        <v>-226.3802691010788</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>0</v>
@@ -1502,40 +1502,40 @@
         </is>
       </c>
       <c r="D18" s="18" t="n">
-        <v>0</v>
+        <v>2.017159982169346</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>0</v>
+        <v>6.672630012869519</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>0</v>
+        <v>11.30153257311675</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0</v>
+        <v>15.83718981915774</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>0</v>
+        <v>20.28100376702062</v>
       </c>
       <c r="I18" s="18" t="n">
-        <v>0</v>
+        <v>24.63435771694432</v>
       </c>
       <c r="J18" s="18" t="n">
-        <v>0</v>
+        <v>28.89861648749286</v>
       </c>
       <c r="K18" s="18" t="n">
-        <v>0</v>
+        <v>31.16078715295325</v>
       </c>
       <c r="L18" s="18" t="n">
-        <v>0</v>
+        <v>31.3881318749203</v>
       </c>
       <c r="M18" s="18" t="n">
-        <v>0</v>
+        <v>31.6078136237328</v>
       </c>
       <c r="N18" s="18" t="n">
-        <v>0</v>
+        <v>31.81996292438149</v>
       </c>
       <c r="O18" s="18" t="n">
-        <v>0</v>
+        <v>32.02470845765492</v>
       </c>
     </row>
     <row r="19" ht="15.5" customHeight="1">
@@ -1558,37 +1558,37 @@
         <v>0</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>0</v>
+        <v>230.7932971034586</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>0</v>
+        <v>69.37148547603344</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>0</v>
+        <v>40.13311660783145</v>
       </c>
       <c r="H19" s="18" t="n">
-        <v>0</v>
+        <v>28.0593590062761</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>0</v>
+        <v>21.46517992863244</v>
       </c>
       <c r="J19" s="18" t="n">
-        <v>0</v>
+        <v>17.31020885361034</v>
       </c>
       <c r="K19" s="18" t="n">
-        <v>0</v>
+        <v>7.827954900330414</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>0</v>
+        <v>0.7295859403394722</v>
       </c>
       <c r="M19" s="18" t="n">
-        <v>0</v>
+        <v>0.699887937542476</v>
       </c>
       <c r="N19" s="18" t="n">
-        <v>0</v>
+        <v>0.6711925828662757</v>
       </c>
       <c r="O19" s="18" t="n">
-        <v>0</v>
+        <v>0.6434499429179175</v>
       </c>
     </row>
     <row r="20" ht="15.5" customHeight="1">
@@ -1608,28 +1608,28 @@
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>0</v>
+        <v>-14.90698781452276</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>0</v>
+        <v>-27.32908993120947</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>0</v>
+        <v>-46.75523796320253</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>0</v>
+        <v>-66.18138599519571</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>0</v>
+        <v>-85.60753402718879</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>0</v>
+        <v>-105.0336820591819</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>0</v>
+        <v>-85.58496569031847</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>0</v>
+        <v>-70.94535897373704</v>
       </c>
       <c r="L20" s="18" t="n">
         <v>0</v>
@@ -1820,40 +1820,40 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>0</v>
+        <v>19.26588014801295</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>0</v>
+        <v>46.74513263108406</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>0</v>
+        <v>62.61263182740853</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>0</v>
+        <v>80.14139644581891</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>0</v>
+        <v>97.96602971638913</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>0</v>
+        <v>111.6988053356569</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>0</v>
+        <v>139.6636895524852</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>0</v>
+        <v>174.5142953105088</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>0</v>
+        <v>151.6650246785894</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>0</v>
+        <v>172.6385746963437</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>0</v>
+        <v>193.3696379200706</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>0</v>
+        <v>213.7408892033075</v>
       </c>
     </row>
     <row r="25" ht="15.5" customHeight="1">
@@ -1873,40 +1873,40 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>0</v>
+        <v>5.734239770577489</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>0</v>
+        <v>22.32928113487503</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>0</v>
+        <v>38.44093884616156</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>0</v>
+        <v>56.21142039438444</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>0</v>
+        <v>74.27535342546898</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>0</v>
+        <v>88.24503580764591</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>0</v>
+        <v>105.8976930899057</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>0</v>
+        <v>130.5920605037351</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>0</v>
+        <v>151.6650246785894</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>0</v>
+        <v>172.6385746963437</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>0</v>
+        <v>193.3696379200706</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>0</v>
+        <v>213.7408892033075</v>
       </c>
     </row>
     <row r="26" ht="15.5" customHeight="1">
@@ -1926,28 +1926,28 @@
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>0</v>
+        <v>142.3765309351522</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>0</v>
+        <v>191.4540340251579</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>0</v>
+        <v>259.0328773246667</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>0</v>
+        <v>334.8996099016776</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>0</v>
+        <v>413.5214567679362</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>0</v>
+        <v>476.2509719482593</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>0</v>
+        <v>413.6222951609456</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>0</v>
+        <v>397.3256280748158</v>
       </c>
       <c r="L26" s="18" t="n">
         <v>0</v>
@@ -1979,28 +1979,28 @@
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>0</v>
+        <v>42.37653093515224</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>0</v>
+        <v>91.45403402515788</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>0</v>
+        <v>159.0328773246667</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>0</v>
+        <v>234.8996099016776</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>0</v>
+        <v>313.5214567679363</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>0</v>
+        <v>376.2509719482593</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>0</v>
+        <v>313.6222951609455</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>0</v>
+        <v>297.3256280748158</v>
       </c>
       <c r="L27" s="18" t="n">
         <v>0</v>
@@ -2032,40 +2032,40 @@
         </is>
       </c>
       <c r="D28" s="18" t="n">
-        <v>0</v>
+        <v>-1.212227607556091</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>0</v>
+        <v>-3.399513732529481</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>0</v>
+        <v>-5.564926996253149</v>
       </c>
       <c r="G28" s="18" t="n">
-        <v>0</v>
+        <v>-7.708686127339575</v>
       </c>
       <c r="H28" s="18" t="n">
-        <v>0</v>
+        <v>-9.831007667115124</v>
       </c>
       <c r="I28" s="18" t="n">
-        <v>0</v>
+        <v>-11.93210599149295</v>
       </c>
       <c r="J28" s="18" t="n">
-        <v>0</v>
+        <v>-14.95702181595101</v>
       </c>
       <c r="K28" s="18" t="n">
-        <v>0</v>
+        <v>-18.89178095329243</v>
       </c>
       <c r="L28" s="18" t="n">
-        <v>0</v>
+        <v>-22.78719249926041</v>
       </c>
       <c r="M28" s="18" t="n">
-        <v>0</v>
+        <v>-26.64364992976874</v>
       </c>
       <c r="N28" s="18" t="n">
-        <v>0</v>
+        <v>-30.46154278597193</v>
       </c>
       <c r="O28" s="18" t="n">
-        <v>0</v>
+        <v>-32.80994723124032</v>
       </c>
     </row>
     <row r="29" ht="15.5" customHeight="1">
@@ -2085,28 +2085,28 @@
         </is>
       </c>
       <c r="D29" s="19" t="n">
-        <v>0</v>
+        <v>8.95846751571619</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>0</v>
+        <v>13.92338798037542</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>0</v>
+        <v>23.02249577872168</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>0</v>
+        <v>32.21351375684925</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>0</v>
+        <v>41.49737030041231</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>0</v>
+        <v>50.8750031726984</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>0</v>
+        <v>44.29610668391442</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>0</v>
+        <v>43.01188461015865</v>
       </c>
       <c r="L29" s="19" t="n">
         <v>0</v>
@@ -2138,40 +2138,40 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>0</v>
+        <v>18.05365254045686</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>0</v>
+        <v>43.34561889855458</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>0</v>
+        <v>57.04770483115539</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>0</v>
+        <v>72.43271031847934</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>0</v>
+        <v>88.135022049274</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>0</v>
+        <v>99.76669934416392</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>0</v>
+        <v>124.7066677365342</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>0</v>
+        <v>155.6225143572164</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>0</v>
+        <v>128.877832179329</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>0</v>
+        <v>145.9949247665749</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>0</v>
+        <v>162.9080951340986</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>0</v>
+        <v>180.9309419720672</v>
       </c>
     </row>
     <row r="31" ht="15.5" customHeight="1">
@@ -2191,28 +2191,28 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>0</v>
+        <v>133.418063419436</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>0</v>
+        <v>177.5306460447824</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>0</v>
+        <v>236.010381545945</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>0</v>
+        <v>302.6860961448284</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>0</v>
+        <v>372.0240864675239</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>0</v>
+        <v>425.3759687755609</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>0</v>
+        <v>369.3261884770311</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>0</v>
+        <v>354.3137434646571</v>
       </c>
       <c r="L31" s="19" t="n">
         <v>0</v>
@@ -2297,40 +2297,40 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>0</v>
+        <v>18.05365254045686</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>0</v>
+        <v>43.34561889855458</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>0</v>
+        <v>57.04770483115539</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>0</v>
+        <v>72.43271031847934</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>0</v>
+        <v>88.135022049274</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>0</v>
+        <v>99.76669934416392</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>0</v>
+        <v>124.7066677365342</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>0</v>
+        <v>155.6225143572164</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>0</v>
+        <v>128.877832179329</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>0</v>
+        <v>145.9949247665749</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>0</v>
+        <v>162.9080951340986</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>0</v>
+        <v>180.9309419720672</v>
       </c>
     </row>
     <row r="34" ht="15.5" customHeight="1">
@@ -2350,40 +2350,40 @@
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>0</v>
+        <v>4.522012163021397</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>0</v>
+        <v>18.92976740234554</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>0</v>
+        <v>32.87601184990841</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>0</v>
+        <v>48.50273426704486</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>0</v>
+        <v>64.44434575835385</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>0</v>
+        <v>76.31292981615296</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>0</v>
+        <v>90.94067127395465</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>0</v>
+        <v>111.7002795504427</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>0</v>
+        <v>128.877832179329</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>0</v>
+        <v>145.9949247665749</v>
       </c>
       <c r="N34" s="19" t="n">
-        <v>0</v>
+        <v>162.9080951340986</v>
       </c>
       <c r="O34" s="19" t="n">
-        <v>0</v>
+        <v>180.9309419720672</v>
       </c>
     </row>
     <row r="35" ht="15.5" customHeight="1">
@@ -2456,40 +2456,40 @@
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>0</v>
+        <v>-1.266163405645991</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>0</v>
+        <v>-5.300334872656753</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>0</v>
+        <v>-9.205283317974354</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>0</v>
+        <v>-13.58076559477256</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>0</v>
+        <v>-18.04441681233908</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>0</v>
+        <v>-21.36762034852283</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>0</v>
+        <v>-25.4633879567073</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>0</v>
+        <v>-31.27607827412396</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>0</v>
+        <v>-36.08579301021212</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>0</v>
+        <v>-40.87857893464097</v>
       </c>
       <c r="N36" s="19" t="n">
-        <v>0</v>
+        <v>-45.61426663754762</v>
       </c>
       <c r="O36" s="19" t="n">
-        <v>0</v>
+        <v>-50.66066375217881</v>
       </c>
     </row>
     <row r="37" ht="15.5" customHeight="1">
@@ -2562,40 +2562,40 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>0</v>
+        <v>16.78748913481087</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>0</v>
+        <v>38.04528402589782</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>0</v>
+        <v>47.84242151318103</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>0</v>
+        <v>58.85194472370677</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>0</v>
+        <v>70.09060523693492</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>0</v>
+        <v>78.3990789956411</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>0</v>
+        <v>99.24327977982691</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>0</v>
+        <v>124.3464360830924</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>0</v>
+        <v>92.79203916911689</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>0</v>
+        <v>105.1163458319339</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>0</v>
+        <v>117.293828496551</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>0</v>
+        <v>130.2702782198884</v>
       </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
@@ -2615,28 +2615,28 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>0</v>
+        <v>124.061005661994</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>0</v>
+        <v>155.8220651522433</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>0</v>
+        <v>197.9274747130804</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>0</v>
+        <v>245.9339892242764</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>0</v>
+        <v>295.8573422566172</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>0</v>
+        <v>334.2706975184038</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>0</v>
+        <v>293.9148557034624</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>0</v>
+        <v>283.1058952945531</v>
       </c>
       <c r="L39" s="19" t="n">
         <v>0</v>
@@ -2721,40 +2721,40 @@
         </is>
       </c>
       <c r="D41" s="18" t="n">
-        <v>0</v>
+        <v>41.21573865690715</v>
       </c>
       <c r="E41" s="18" t="n">
-        <v>0</v>
+        <v>114.3712392984464</v>
       </c>
       <c r="F41" s="18" t="n">
-        <v>0</v>
+        <v>184.5957765325215</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>0</v>
+        <v>251.9186599932067</v>
       </c>
       <c r="H41" s="18" t="n">
-        <v>0</v>
+        <v>316.3689062182362</v>
       </c>
       <c r="I41" s="18" t="n">
-        <v>0</v>
+        <v>377.9752415799665</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>0</v>
+        <v>468.8902736200479</v>
       </c>
       <c r="K41" s="18" t="n">
-        <v>0</v>
+        <v>587.7150624737048</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>0</v>
+        <v>701.2672740833244</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>0</v>
+        <v>809.5996342213468</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>0</v>
+        <v>912.7643414024881</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>0</v>
+        <v>962.1485497556417</v>
       </c>
     </row>
     <row r="42" ht="15.5" customHeight="1">
@@ -2774,40 +2774,40 @@
         </is>
       </c>
       <c r="D42" s="18" t="n">
-        <v>0</v>
+        <v>41.21573865690715</v>
       </c>
       <c r="E42" s="18" t="n">
-        <v>0</v>
+        <v>114.3712392984464</v>
       </c>
       <c r="F42" s="18" t="n">
-        <v>0</v>
+        <v>184.5957765325215</v>
       </c>
       <c r="G42" s="18" t="n">
-        <v>0</v>
+        <v>251.9186599932067</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>0</v>
+        <v>316.3689062182362</v>
       </c>
       <c r="I42" s="18" t="n">
-        <v>0</v>
+        <v>377.9752415799665</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>0</v>
+        <v>468.8902736200479</v>
       </c>
       <c r="K42" s="18" t="n">
-        <v>0</v>
+        <v>587.7150624737048</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>0</v>
+        <v>701.2672740833244</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>0</v>
+        <v>809.5996342213468</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>0</v>
+        <v>912.7643414024881</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>0</v>
+        <v>962.1485497556417</v>
       </c>
     </row>
     <row r="43" ht="15.5" customHeight="1">
@@ -2827,40 +2827,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>0</v>
+        <v>223.9643754210162</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>0</v>
+        <v>164.4383073091657</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>0</v>
+        <v>117.8844986070247</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>0</v>
+        <v>85.48358381861181</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>0</v>
+        <v>67.43326653959704</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>0</v>
+        <v>60.77224064549691</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>0</v>
+        <v>35.33449192266283</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>0</v>
+        <v>-3.066095654675394</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>0</v>
+        <v>-23.82626809517802</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>0</v>
+        <v>-27.04228240126645</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>0</v>
+        <v>-27.04228240126645</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>0</v>
+        <v>-27.04228240126645</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -2880,40 +2880,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>0</v>
+        <v>223.9643754210162</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>0</v>
+        <v>164.4383073091657</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>0</v>
+        <v>117.8844986070247</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>0</v>
+        <v>85.48358381861181</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>0</v>
+        <v>67.43326653959704</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>0</v>
+        <v>60.77224064549691</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>0</v>
+        <v>35.33449192266283</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>0</v>
+        <v>-3.066095654675394</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>0</v>
+        <v>-23.82626809517802</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>0</v>
+        <v>-27.04228240126645</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>0</v>
+        <v>-27.04228240126645</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>0</v>
+        <v>-27.04228240126645</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -3039,40 +3039,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>0</v>
+        <v>265.1801140779233</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>0</v>
+        <v>278.8095466076122</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>0</v>
+        <v>302.4802751395462</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>0</v>
+        <v>337.4022438118185</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>0</v>
+        <v>383.8021727578332</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>0</v>
+        <v>438.7474822254634</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>0</v>
+        <v>504.2247655427107</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>0</v>
+        <v>584.6489668190295</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>0</v>
+        <v>677.4410059881463</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>0</v>
+        <v>782.5573518200804</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>0</v>
+        <v>885.7220590012216</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>0</v>
+        <v>935.1062673543753</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -3092,40 +3092,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>0</v>
+        <v>67.82991646074856</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>0</v>
+        <v>105.8752004866464</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>0</v>
+        <v>153.7176219998274</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>0</v>
+        <v>212.5695667235342</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>0</v>
+        <v>282.6601719604691</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>0</v>
+        <v>361.0592509561102</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>0</v>
+        <v>460.3025307359371</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>0</v>
+        <v>584.6489668190295</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>0</v>
+        <v>677.4410059881463</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>0</v>
+        <v>782.5573518200802</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>0</v>
+        <v>885.7220590012215</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>0</v>
+        <v>935.1062673543752</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -3145,40 +3145,40 @@
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>0</v>
+        <v>51.04242732593769</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>0</v>
+        <v>51.04242732593769</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>0</v>
+        <v>51.04242732593769</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>0</v>
+        <v>51.04242732593769</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>0</v>
+        <v>51.04242732593769</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>0</v>
+        <v>51.04242732593769</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>0</v>
+        <v>51.04242732593769</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>0</v>
+        <v>51.04242732593769</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>0</v>
+        <v>51.04242732593769</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>0</v>
+        <v>51.04242732593769</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>0</v>
+        <v>51.04242732593769</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>0</v>
+        <v>51.04242732593769</v>
       </c>
     </row>
     <row r="50" ht="15.5" customHeight="1">
@@ -3198,40 +3198,40 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>0</v>
+        <v>16.78748913481087</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>0</v>
+        <v>38.04528402589782</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>0</v>
+        <v>47.84242151318103</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>0</v>
+        <v>58.85194472370677</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>0</v>
+        <v>70.09060523693492</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>0</v>
+        <v>78.3990789956411</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>0</v>
+        <v>99.24327977982691</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>0</v>
+        <v>124.3464360830924</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>0</v>
+        <v>92.79203916911689</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>0</v>
+        <v>105.1163458319339</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>0</v>
+        <v>103.1647071811413</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>0</v>
+        <v>49.3842083531537</v>
       </c>
     </row>
     <row r="51" ht="15.5" customHeight="1">
@@ -3254,37 +3254,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>0</v>
+        <v>16.78748913481087</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>0</v>
+        <v>54.83277316070868</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>0</v>
+        <v>102.6751946738897</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>0</v>
+        <v>161.5271393975965</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>0</v>
+        <v>231.6177446345314</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>0</v>
+        <v>310.0168236301725</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>0</v>
+        <v>409.2601034099994</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>0</v>
+        <v>533.6065394930918</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>0</v>
+        <v>626.3985786622086</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>0</v>
+        <v>731.5149244941425</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>0</v>
+        <v>834.6796316752838</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -3304,25 +3304,25 @@
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>0</v>
+        <v>197.3501976171748</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>0</v>
+        <v>172.9343461209658</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>0</v>
+        <v>148.7626531397188</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>0</v>
+        <v>124.8326770882843</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>0</v>
+        <v>101.1420007973642</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>0</v>
+        <v>77.68823126935321</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>0</v>
+        <v>43.92223480677366</v>
       </c>
       <c r="K52" s="18" t="n">
         <v>0</v>
@@ -3357,25 +3357,25 @@
         </is>
       </c>
       <c r="D53" s="18" t="n">
-        <v>0</v>
+        <v>197.3501976171748</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>0</v>
+        <v>172.9343461209658</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>0</v>
+        <v>148.7626531397188</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>0</v>
+        <v>124.8326770882843</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>0</v>
+        <v>101.1420007973642</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>0</v>
+        <v>77.68823126935321</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>0</v>
+        <v>43.92223480677366</v>
       </c>
       <c r="K53" s="18" t="n">
         <v>0</v>
@@ -3622,40 +3622,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>0</v>
+        <v>265.1801140779233</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>0</v>
+        <v>278.8095466076121</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>0</v>
+        <v>302.4802751395462</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>0</v>
+        <v>337.4022438118185</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>0</v>
+        <v>383.8021727578333</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>0</v>
+        <v>438.7474822254634</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>0</v>
+        <v>504.2247655427108</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>0</v>
+        <v>584.6489668190295</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>0</v>
+        <v>677.4410059881463</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>0</v>
+        <v>782.5573518200802</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>0</v>
+        <v>885.7220590012215</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>0</v>
+        <v>935.1062673543752</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -3678,7 +3678,7 @@
         <v>0</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>0</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="F59" s="18" t="n">
         <v>0</v>
@@ -3687,13 +3687,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>0</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="I59" s="18" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>0</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="K59" s="18" t="n">
         <v>0</v>
@@ -3702,13 +3702,13 @@
         <v>0</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>0</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>0</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>0</v>
+        <v>1.13686837721616e-13</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -3781,40 +3781,40 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>0</v>
+        <v>5.734239770577489</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>0</v>
+        <v>22.32928113487503</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>0</v>
+        <v>38.44093884616156</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>0</v>
+        <v>56.21142039438444</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>0</v>
+        <v>74.27535342546898</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>0</v>
+        <v>88.24503580764591</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>0</v>
+        <v>105.8976930899057</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>0</v>
+        <v>130.5920605037351</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>0</v>
+        <v>151.6650246785894</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>0</v>
+        <v>172.6385746963437</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>0</v>
+        <v>193.3696379200706</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>0</v>
+        <v>213.7408892033075</v>
       </c>
     </row>
     <row r="62" ht="15.5" customHeight="1">
@@ -3834,40 +3834,40 @@
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>0</v>
+        <v>-1.266163405645991</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>0</v>
+        <v>-5.300334872656753</v>
       </c>
       <c r="F62" s="18" t="n">
-        <v>0</v>
+        <v>-9.205283317974354</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>0</v>
+        <v>-13.58076559477256</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>0</v>
+        <v>-18.04441681233908</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>0</v>
+        <v>-21.36762034852283</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>0</v>
+        <v>-25.4633879567073</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>0</v>
+        <v>-31.27607827412396</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>0</v>
+        <v>-36.08579301021212</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>0</v>
+        <v>-40.87857893464097</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>0</v>
+        <v>-45.61426663754762</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>0</v>
+        <v>-50.66066375217881</v>
       </c>
     </row>
     <row r="63" ht="15.5" customHeight="1">
@@ -3940,40 +3940,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>0</v>
+        <v>4.468076364931497</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>0</v>
+        <v>17.02894626221828</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>0</v>
+        <v>29.2356555281872</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>0</v>
+        <v>42.63065479961188</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>0</v>
+        <v>56.2309366131299</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>0</v>
+        <v>66.87741545912309</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>0</v>
+        <v>80.43430513319836</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>0</v>
+        <v>99.31598222961117</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>0</v>
+        <v>115.5792316683773</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>0</v>
+        <v>131.7599957617027</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>0</v>
+        <v>147.755371282523</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>0</v>
+        <v>163.0802254511287</v>
       </c>
     </row>
     <row r="65" ht="15.5" customHeight="1">
@@ -3993,40 +3993,40 @@
         </is>
       </c>
       <c r="D65" s="18" t="n">
-        <v>0</v>
+        <v>-42.42796626446324</v>
       </c>
       <c r="E65" s="18" t="n">
-        <v>0</v>
+        <v>-76.55501437406878</v>
       </c>
       <c r="F65" s="18" t="n">
-        <v>0</v>
+        <v>-75.78946423032818</v>
       </c>
       <c r="G65" s="18" t="n">
-        <v>0</v>
+        <v>-75.03156958802481</v>
       </c>
       <c r="H65" s="18" t="n">
-        <v>0</v>
+        <v>-74.28125389214466</v>
       </c>
       <c r="I65" s="18" t="n">
-        <v>0</v>
+        <v>-73.53844135322322</v>
       </c>
       <c r="J65" s="18" t="n">
-        <v>0</v>
+        <v>-105.8720538560324</v>
       </c>
       <c r="K65" s="18" t="n">
-        <v>0</v>
+        <v>-137.7165698069494</v>
       </c>
       <c r="L65" s="18" t="n">
-        <v>0</v>
+        <v>-136.3394041088799</v>
       </c>
       <c r="M65" s="18" t="n">
-        <v>0</v>
+        <v>-134.9760100677911</v>
       </c>
       <c r="N65" s="18" t="n">
-        <v>0</v>
+        <v>-133.6262499671132</v>
       </c>
       <c r="O65" s="18" t="n">
-        <v>0</v>
+        <v>-82.194155584394</v>
       </c>
     </row>
     <row r="66" ht="15.5" customHeight="1">
@@ -4046,40 +4046,40 @@
         </is>
       </c>
       <c r="D66" s="18" t="n">
-        <v>0</v>
+        <v>-42.42796626446324</v>
       </c>
       <c r="E66" s="18" t="n">
-        <v>0</v>
+        <v>-76.55501437406878</v>
       </c>
       <c r="F66" s="18" t="n">
-        <v>0</v>
+        <v>-75.78946423032818</v>
       </c>
       <c r="G66" s="18" t="n">
-        <v>0</v>
+        <v>-75.03156958802481</v>
       </c>
       <c r="H66" s="18" t="n">
-        <v>0</v>
+        <v>-74.28125389214466</v>
       </c>
       <c r="I66" s="18" t="n">
-        <v>0</v>
+        <v>-73.53844135322322</v>
       </c>
       <c r="J66" s="18" t="n">
-        <v>0</v>
+        <v>-105.8720538560324</v>
       </c>
       <c r="K66" s="18" t="n">
-        <v>0</v>
+        <v>-137.7165698069494</v>
       </c>
       <c r="L66" s="18" t="n">
-        <v>0</v>
+        <v>-136.3394041088799</v>
       </c>
       <c r="M66" s="18" t="n">
-        <v>0</v>
+        <v>-134.9760100677911</v>
       </c>
       <c r="N66" s="18" t="n">
-        <v>0</v>
+        <v>-133.6262499671132</v>
       </c>
       <c r="O66" s="18" t="n">
-        <v>0</v>
+        <v>-82.194155584394</v>
       </c>
     </row>
     <row r="67" ht="15.5" customHeight="1">
@@ -4099,40 +4099,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>0</v>
+        <v>-37.95988989953174</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>0</v>
+        <v>-59.5260681118505</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>0</v>
+        <v>-46.55380870214098</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>0</v>
+        <v>-32.40091478841293</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>0</v>
+        <v>-18.05031727901476</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>0</v>
+        <v>-6.661025894100135</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>0</v>
+        <v>-25.43774872283407</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>0</v>
+        <v>-38.40058757733823</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>0</v>
+        <v>-20.76017244050263</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>0</v>
+        <v>-3.216014306088425</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>0</v>
+        <v>14.12912131540975</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>0</v>
+        <v>80.88606986673466</v>
       </c>
     </row>
     <row r="68" ht="15.5" customHeight="1">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="D71" s="19" t="n">
-        <v>0</v>
+        <v>210.8818379946102</v>
       </c>
       <c r="E71" s="19" t="n">
         <v>0</v>
@@ -4394,10 +4394,10 @@
         <v>0</v>
       </c>
       <c r="N72" s="18" t="n">
-        <v>0</v>
+        <v>-14.12912131540975</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>0</v>
+        <v>-80.88606986673466</v>
       </c>
     </row>
     <row r="73" ht="15.5" customHeight="1">
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="D73" s="19" t="n">
-        <v>0</v>
+        <v>51.04242732593769</v>
       </c>
       <c r="E73" s="19" t="n">
         <v>0</v>
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="D74" s="18" t="n">
-        <v>0</v>
+        <v>261.9242653205479</v>
       </c>
       <c r="E74" s="18" t="n">
         <v>0</v>
@@ -4500,10 +4500,10 @@
         <v>0</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>0</v>
+        <v>-14.12912131540975</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>0</v>
+        <v>-80.88606986673466</v>
       </c>
     </row>
     <row r="75" ht="15.5" customHeight="1">
@@ -4523,34 +4523,34 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>0</v>
+        <v>223.9643754210162</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>0</v>
+        <v>-59.5260681118505</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>0</v>
+        <v>-46.55380870214098</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>0</v>
+        <v>-32.40091478841293</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>0</v>
+        <v>-18.05031727901476</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>0</v>
+        <v>-6.661025894100135</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>0</v>
+        <v>-25.43774872283407</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>0</v>
+        <v>-38.40058757733823</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>0</v>
+        <v>-20.76017244050263</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>0</v>
+        <v>-3.216014306088425</v>
       </c>
       <c r="N75" s="18" t="n">
         <v>0</v>
@@ -4579,37 +4579,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>0</v>
+        <v>223.9643754210162</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>0</v>
+        <v>164.4383073091657</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>0</v>
+        <v>117.8844986070247</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>0</v>
+        <v>85.48358381861181</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>0</v>
+        <v>67.43326653959704</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>0</v>
+        <v>60.77224064549691</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>0</v>
+        <v>35.33449192266283</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>0</v>
+        <v>-3.066095654675394</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>0</v>
+        <v>-23.82626809517802</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>0</v>
+        <v>-27.04228240126645</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>0</v>
+        <v>-27.04228240126645</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -4629,34 +4629,34 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>0</v>
+        <v>223.9643754210162</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>0</v>
+        <v>-59.5260681118505</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>0</v>
+        <v>-46.55380870214098</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>0</v>
+        <v>-32.40091478841293</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>0</v>
+        <v>-18.05031727901476</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>0</v>
+        <v>-6.661025894100135</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>0</v>
+        <v>-25.43774872283407</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>0</v>
+        <v>-38.40058757733823</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>0</v>
+        <v>-20.76017244050263</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>0</v>
+        <v>-3.216014306088425</v>
       </c>
       <c r="N77" s="18" t="n">
         <v>0</v>
@@ -4682,40 +4682,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>0</v>
+        <v>223.9643754210162</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>0</v>
+        <v>164.4383073091657</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>0</v>
+        <v>117.8844986070247</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>0</v>
+        <v>85.48358381861181</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>0</v>
+        <v>67.43326653959704</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>0</v>
+        <v>60.77224064549691</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>0</v>
+        <v>35.33449192266283</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>0</v>
+        <v>-3.066095654675394</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>0</v>
+        <v>-23.82626809517802</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>0</v>
+        <v>-27.04228240126645</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>0</v>
+        <v>-27.04228240126645</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>0</v>
+        <v>-27.04228240126645</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -4788,40 +4788,40 @@
         </is>
       </c>
       <c r="D80" s="18" t="n">
-        <v>0</v>
+        <v>42.42796626446324</v>
       </c>
       <c r="E80" s="18" t="n">
-        <v>0</v>
+        <v>76.55501437406878</v>
       </c>
       <c r="F80" s="18" t="n">
-        <v>0</v>
+        <v>75.78946423032818</v>
       </c>
       <c r="G80" s="18" t="n">
-        <v>0</v>
+        <v>75.03156958802481</v>
       </c>
       <c r="H80" s="18" t="n">
-        <v>0</v>
+        <v>74.28125389214466</v>
       </c>
       <c r="I80" s="18" t="n">
-        <v>0</v>
+        <v>73.53844135322322</v>
       </c>
       <c r="J80" s="18" t="n">
-        <v>0</v>
+        <v>105.8720538560324</v>
       </c>
       <c r="K80" s="18" t="n">
-        <v>0</v>
+        <v>137.7165698069494</v>
       </c>
       <c r="L80" s="18" t="n">
-        <v>0</v>
+        <v>136.3394041088799</v>
       </c>
       <c r="M80" s="18" t="n">
-        <v>0</v>
+        <v>134.9760100677911</v>
       </c>
       <c r="N80" s="18" t="n">
-        <v>0</v>
+        <v>133.6262499671132</v>
       </c>
       <c r="O80" s="18" t="n">
-        <v>0</v>
+        <v>82.194155584394</v>
       </c>
     </row>
     <row r="81" ht="15.5" customHeight="1">
@@ -4841,28 +4841,28 @@
         </is>
       </c>
       <c r="D81" s="18" t="n">
-        <v>0</v>
+        <v>313.546363050067</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>0</v>
+        <v>313.5463630500669</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>0</v>
+        <v>313.5463630500669</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>0</v>
+        <v>313.5463630500669</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>0</v>
+        <v>313.5463630500669</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>0</v>
+        <v>313.5463630500669</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>0</v>
+        <v>313.5463630500669</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>0</v>
+        <v>313.5463630500669</v>
       </c>
       <c r="L81" s="18" t="n">
         <v>0</v>
@@ -4897,37 +4897,37 @@
         <v>0</v>
       </c>
       <c r="E82" s="18" t="n">
-        <v>0</v>
+        <v>41.21573865690715</v>
       </c>
       <c r="F82" s="18" t="n">
-        <v>0</v>
+        <v>114.3712392984464</v>
       </c>
       <c r="G82" s="18" t="n">
-        <v>0</v>
+        <v>184.5957765325215</v>
       </c>
       <c r="H82" s="18" t="n">
-        <v>0</v>
+        <v>251.9186599932067</v>
       </c>
       <c r="I82" s="18" t="n">
-        <v>0</v>
+        <v>316.3689062182362</v>
       </c>
       <c r="J82" s="18" t="n">
-        <v>0</v>
+        <v>377.9752415799665</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>0</v>
+        <v>468.8902736200479</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>0</v>
+        <v>587.7150624737048</v>
       </c>
       <c r="M82" s="18" t="n">
-        <v>0</v>
+        <v>701.2672740833244</v>
       </c>
       <c r="N82" s="18" t="n">
-        <v>0</v>
+        <v>809.5996342213468</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>0</v>
+        <v>912.7643414024881</v>
       </c>
     </row>
     <row r="83" ht="15.5" customHeight="1">
@@ -4947,40 +4947,40 @@
         </is>
       </c>
       <c r="D83" s="18" t="n">
-        <v>0</v>
+        <v>42.42796626446324</v>
       </c>
       <c r="E83" s="18" t="n">
-        <v>0</v>
+        <v>76.55501437406878</v>
       </c>
       <c r="F83" s="18" t="n">
-        <v>0</v>
+        <v>75.78946423032818</v>
       </c>
       <c r="G83" s="18" t="n">
-        <v>0</v>
+        <v>75.03156958802481</v>
       </c>
       <c r="H83" s="18" t="n">
-        <v>0</v>
+        <v>74.28125389214466</v>
       </c>
       <c r="I83" s="18" t="n">
-        <v>0</v>
+        <v>73.53844135322322</v>
       </c>
       <c r="J83" s="18" t="n">
-        <v>0</v>
+        <v>105.8720538560324</v>
       </c>
       <c r="K83" s="18" t="n">
-        <v>0</v>
+        <v>137.7165698069494</v>
       </c>
       <c r="L83" s="18" t="n">
-        <v>0</v>
+        <v>136.3394041088799</v>
       </c>
       <c r="M83" s="18" t="n">
-        <v>0</v>
+        <v>134.9760100677911</v>
       </c>
       <c r="N83" s="18" t="n">
-        <v>0</v>
+        <v>133.6262499671132</v>
       </c>
       <c r="O83" s="18" t="n">
-        <v>0</v>
+        <v>82.194155584394</v>
       </c>
     </row>
     <row r="84" ht="15.5" customHeight="1">
@@ -5000,40 +5000,40 @@
         </is>
       </c>
       <c r="D84" s="18" t="n">
-        <v>0</v>
+        <v>1.212227607556091</v>
       </c>
       <c r="E84" s="18" t="n">
-        <v>0</v>
+        <v>3.399513732529481</v>
       </c>
       <c r="F84" s="18" t="n">
-        <v>0</v>
+        <v>5.564926996253149</v>
       </c>
       <c r="G84" s="18" t="n">
-        <v>0</v>
+        <v>7.708686127339575</v>
       </c>
       <c r="H84" s="18" t="n">
-        <v>0</v>
+        <v>9.831007667115124</v>
       </c>
       <c r="I84" s="18" t="n">
-        <v>0</v>
+        <v>11.93210599149295</v>
       </c>
       <c r="J84" s="18" t="n">
-        <v>0</v>
+        <v>14.95702181595101</v>
       </c>
       <c r="K84" s="18" t="n">
-        <v>0</v>
+        <v>18.89178095329243</v>
       </c>
       <c r="L84" s="18" t="n">
-        <v>0</v>
+        <v>22.78719249926041</v>
       </c>
       <c r="M84" s="18" t="n">
-        <v>0</v>
+        <v>26.64364992976874</v>
       </c>
       <c r="N84" s="18" t="n">
-        <v>0</v>
+        <v>30.46154278597193</v>
       </c>
       <c r="O84" s="18" t="n">
-        <v>0</v>
+        <v>32.80994723124032</v>
       </c>
     </row>
     <row r="85" ht="15.5" customHeight="1">
@@ -5053,40 +5053,40 @@
         </is>
       </c>
       <c r="D85" s="18" t="n">
-        <v>0</v>
+        <v>41.21573865690715</v>
       </c>
       <c r="E85" s="18" t="n">
-        <v>0</v>
+        <v>114.3712392984464</v>
       </c>
       <c r="F85" s="18" t="n">
-        <v>0</v>
+        <v>184.5957765325215</v>
       </c>
       <c r="G85" s="18" t="n">
-        <v>0</v>
+        <v>251.9186599932067</v>
       </c>
       <c r="H85" s="18" t="n">
-        <v>0</v>
+        <v>316.3689062182362</v>
       </c>
       <c r="I85" s="18" t="n">
-        <v>0</v>
+        <v>377.9752415799665</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>0</v>
+        <v>468.8902736200479</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>0</v>
+        <v>587.7150624737048</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>0</v>
+        <v>701.2672740833244</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>0</v>
+        <v>809.5996342213468</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>0</v>
+        <v>912.7643414024881</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>0</v>
+        <v>962.1485497556417</v>
       </c>
     </row>
     <row r="86" ht="15.5" customHeight="1">
@@ -5663,37 +5663,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>0</v>
+        <v>67.82991646074856</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>0</v>
+        <v>105.8752004866464</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>0</v>
+        <v>153.7176219998274</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>0</v>
+        <v>212.5695667235342</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>0</v>
+        <v>282.6601719604691</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>0</v>
+        <v>361.0592509561102</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>0</v>
+        <v>460.3025307359371</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>0</v>
+        <v>584.6489668190295</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>0</v>
+        <v>677.4410059881463</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>0</v>
+        <v>782.5573518200803</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>0</v>
+        <v>913.980301632041</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -5713,7 +5713,7 @@
         </is>
       </c>
       <c r="D97" s="19" t="n">
-        <v>0</v>
+        <v>51.04242732593769</v>
       </c>
       <c r="E97" s="19" t="n">
         <v>0</v>
@@ -5766,40 +5766,40 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>0</v>
+        <v>16.78748913481087</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>0</v>
+        <v>38.04528402589782</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>0</v>
+        <v>47.84242151318103</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>0</v>
+        <v>58.85194472370677</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>0</v>
+        <v>70.09060523693492</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>0</v>
+        <v>78.3990789956411</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>0</v>
+        <v>99.24327977982691</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>0</v>
+        <v>124.3464360830924</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>0</v>
+        <v>92.79203916911689</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>0</v>
+        <v>105.1163458319339</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>0</v>
+        <v>117.293828496551</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>0</v>
+        <v>130.2702782198884</v>
       </c>
     </row>
     <row r="99" ht="15.5" customHeight="1">
@@ -5849,10 +5849,10 @@
         <v>0</v>
       </c>
       <c r="N99" s="20" t="n">
-        <v>0</v>
+        <v>14.12912131540975</v>
       </c>
       <c r="O99" s="20" t="n">
-        <v>0</v>
+        <v>80.88606986673466</v>
       </c>
     </row>
     <row r="100" ht="15.5" customHeight="1">
@@ -5872,40 +5872,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>0</v>
+        <v>67.82991646074856</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>0</v>
+        <v>105.8752004866464</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>0</v>
+        <v>153.7176219998274</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>0</v>
+        <v>212.5695667235342</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>0</v>
+        <v>282.6601719604691</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>0</v>
+        <v>361.0592509561102</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>0</v>
+        <v>460.3025307359371</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>0</v>
+        <v>584.6489668190295</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>0</v>
+        <v>677.4410059881463</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>0</v>
+        <v>782.5573518200803</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>0</v>
+        <v>913.980301632041</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>0</v>
+        <v>1125.136649718664</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -5978,28 +5978,28 @@
         </is>
       </c>
       <c r="D102" s="18" t="n">
-        <v>0</v>
+        <v>-31.89320999524145</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>0</v>
+        <v>-31.89320999524145</v>
       </c>
       <c r="F102" s="18" t="n">
-        <v>0</v>
+        <v>-31.89320999524146</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>0</v>
+        <v>-31.89320999524145</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>0</v>
+        <v>-31.89320999524145</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>0</v>
+        <v>-31.89320999524146</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>0</v>
+        <v>-31.89320999524145</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>0</v>
+        <v>-31.89320999524146</v>
       </c>
       <c r="L102" s="18" t="n">
         <v>0</v>
@@ -6034,25 +6034,25 @@
         <v>0</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>0</v>
+        <v>197.3501976171748</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>0</v>
+        <v>172.9343461209658</v>
       </c>
       <c r="G103" s="18" t="n">
-        <v>0</v>
+        <v>148.7626531397188</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>0</v>
+        <v>124.8326770882843</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>0</v>
+        <v>101.1420007973642</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>0</v>
+        <v>77.68823126935321</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>0</v>
+        <v>43.92223480677366</v>
       </c>
       <c r="L103" s="18" t="n">
         <v>0</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="D104" s="19" t="n">
-        <v>0</v>
+        <v>210.8818379946102</v>
       </c>
       <c r="E104" s="19" t="n">
         <v>0</v>
@@ -6137,28 +6137,28 @@
         </is>
       </c>
       <c r="D105" s="18" t="n">
-        <v>0</v>
+        <v>-13.53164037743546</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>0</v>
+        <v>-24.41585149620903</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>0</v>
+        <v>-24.17169298124697</v>
       </c>
       <c r="G105" s="18" t="n">
-        <v>0</v>
+        <v>-23.92997605143447</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>0</v>
+        <v>-23.69067629092016</v>
       </c>
       <c r="I105" s="18" t="n">
-        <v>0</v>
+        <v>-23.45376952801096</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>0</v>
+        <v>-33.76599646257955</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>0</v>
+        <v>-43.92223480677366</v>
       </c>
       <c r="L105" s="18" t="n">
         <v>0</v>
@@ -6190,28 +6190,28 @@
         </is>
       </c>
       <c r="D106" s="18" t="n">
-        <v>0</v>
+        <v>6.41669311407524</v>
       </c>
       <c r="E106" s="18" t="n">
-        <v>0</v>
+        <v>11.57797737747006</v>
       </c>
       <c r="F106" s="18" t="n">
-        <v>0</v>
+        <v>11.46219760369537</v>
       </c>
       <c r="G106" s="18" t="n">
-        <v>0</v>
+        <v>11.34757562765841</v>
       </c>
       <c r="H106" s="18" t="n">
-        <v>0</v>
+        <v>11.23409987138184</v>
       </c>
       <c r="I106" s="18" t="n">
-        <v>0</v>
+        <v>11.12175887266802</v>
       </c>
       <c r="J106" s="18" t="n">
-        <v>0</v>
+        <v>16.0118086904395</v>
       </c>
       <c r="K106" s="18" t="n">
-        <v>0</v>
+        <v>20.82788884261158</v>
       </c>
       <c r="L106" s="18" t="n">
         <v>0</v>
@@ -6243,25 +6243,25 @@
         </is>
       </c>
       <c r="D107" s="18" t="n">
-        <v>0</v>
+        <v>197.3501976171748</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>0</v>
+        <v>172.9343461209658</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>0</v>
+        <v>148.7626531397188</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>0</v>
+        <v>124.8326770882843</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>0</v>
+        <v>101.1420007973642</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>0</v>
+        <v>77.68823126935321</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>0</v>
+        <v>43.92223480677366</v>
       </c>
       <c r="K107" s="18" t="n">
         <v>0</v>
@@ -6688,25 +6688,25 @@
         <v>358.5099338432954</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>319.3776</v>
+        <v>423.2421636745095</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>371.7594</v>
+        <v>474.5862321798792</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>400.3194</v>
+        <v>502.117492936385</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>450.3366</v>
+        <v>551.117626149136</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>499.6202</v>
+        <v>599.3929726672253</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>547.888</v>
+        <v>657.9686832833999</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>607.9227</v>
+        <v>728.1536109123975</v>
       </c>
       <c r="L2" s="18" t="n">
         <v>664.8774</v>
@@ -6741,28 +6741,28 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>-10.91527183746048</v>
+        <v>18.055909675158</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>16.40121285901079</v>
+        <v>12.1311326970853</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>7.682388125222928</v>
+        <v>5.801108184291093</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>12.49432328285864</v>
+        <v>9.758698691455269</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>10.94372520465803</v>
+        <v>8.759535937075213</v>
       </c>
       <c r="J3" s="18" t="n">
-        <v>9.660898418438645</v>
+        <v>9.772505399174069</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>10.95747671056857</v>
+        <v>10.66691005394973</v>
       </c>
       <c r="L3" s="18" t="n">
-        <v>9.368740466509973</v>
+        <v>-8.68995359826763</v>
       </c>
       <c r="M3" s="18" t="n">
         <v>8.302929231765145</v>
@@ -6900,25 +6900,25 @@
         <v>82.21593384329545</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>0</v>
+        <v>103.8645636745095</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>0</v>
+        <v>102.8268321798792</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0</v>
+        <v>101.7980929363849</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>0</v>
+        <v>100.7810261491359</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>0</v>
+        <v>99.77277266722525</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>0</v>
+        <v>110.0806832833998</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>0</v>
+        <v>120.2309109123976</v>
       </c>
       <c r="L6" s="18" t="n">
         <v>0</v>
@@ -6953,28 +6953,28 @@
         <v>0</v>
       </c>
       <c r="E7" s="18" t="n">
+        <v>26.33142849472054</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>-0.9991198710296967</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>-1.000457975496771</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>-0.9991020046757004</v>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>-1.000439785578899</v>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>10.33138634981587</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>9.22071641113118</v>
+      </c>
+      <c r="L7" s="18" t="n">
         <v>-100</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="18" t="n">
-        <v>0</v>
       </c>
       <c r="M7" s="18" t="n">
         <v>0</v>
@@ -7006,25 +7006,25 @@
         <v>-22.93267942729643</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>0</v>
+        <v>-24.54022131745495</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>0</v>
+        <v>-21.66662772907948</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>0</v>
+        <v>-20.27375950219725</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>0</v>
+        <v>-18.28666356642055</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>0</v>
+        <v>-16.6456360379483</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>0</v>
+        <v>-16.730383387561</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>0</v>
+        <v>-16.51175096992855</v>
       </c>
       <c r="L8" s="18" t="n">
         <v>0</v>
@@ -7215,40 +7215,40 @@
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>-159.324880879153</v>
+        <v>61.71031912084698</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>-242.3526089865739</v>
+        <v>17.14169101342608</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>-325.6476186798328</v>
+        <v>-41.3610186798328</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>-406.0952940550021</v>
+        <v>-76.420494055002</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>-483.7325640290336</v>
+        <v>-108.4520640290336</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>-558.5929628959386</v>
+        <v>-164.1559628959387</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>-637.8887454934571</v>
+        <v>-199.5783454934571</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>-714.7401549148944</v>
+        <v>-222.6122549148944</v>
       </c>
       <c r="L12" s="18" t="n">
-        <v>-783.6615503938792</v>
+        <v>-239.6709503938793</v>
       </c>
       <c r="M12" s="18" t="n">
-        <v>-849.740766949836</v>
+        <v>-254.890666949836</v>
       </c>
       <c r="N12" s="18" t="n">
-        <v>-913.0268172653765</v>
+        <v>-268.5868172653765</v>
       </c>
       <c r="O12" s="18" t="n">
-        <v>-950.1645875653564</v>
+        <v>-257.6244875653564</v>
       </c>
     </row>
     <row r="13" ht="15.5" customHeight="1">
@@ -7271,37 +7271,37 @@
         <v>0</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>52.1122172816165</v>
+        <v>-72.22232641536401</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>34.36934722574962</v>
+        <v>-341.2890224624696</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>24.70390408543508</v>
+        <v>84.76453553177072</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>19.11799302050425</v>
+        <v>41.91489517324705</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>15.47557564522613</v>
+        <v>51.36269131032183</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>14.1956286356387</v>
+        <v>21.57849277761132</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>12.04777635040208</v>
+        <v>11.54128688885863</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>9.642860416481192</v>
+        <v>7.662963337533424</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>8.432111607714376</v>
+        <v>6.350255018784901</v>
       </c>
       <c r="N13" s="18" t="n">
-        <v>7.447689080836639</v>
+        <v>5.373343198256797</v>
       </c>
       <c r="O13" s="18" t="n">
-        <v>4.06754430403391</v>
+        <v>-4.081484643078648</v>
       </c>
     </row>
     <row r="14" ht="15.5" customHeight="1">
@@ -7321,40 +7321,40 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>-44.44085528430403</v>
+        <v>17.21300117385884</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>-75.8827823199166</v>
+        <v>4.050090582801373</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>-87.59633749135402</v>
+        <v>-8.715174582678582</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>-101.4428214208459</v>
+        <v>-15.21964383437324</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>-107.4157783375887</v>
+        <v>-19.67856930775895</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>-111.8035185318645</v>
+        <v>-27.38703494728421</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>-116.426851015802</v>
+        <v>-30.33249918484264</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>-117.5708942789757</v>
+        <v>-30.5721555972173</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>-117.865571967686</v>
+        <v>-36.04739014950415</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>-118.0061605439822</v>
+        <v>-35.39746489180825</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>-118.064626816225</v>
+        <v>-34.73129348289167</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>-110.8153345081638</v>
+        <v>-30.04610373893308</v>
       </c>
     </row>
     <row r="15" ht="15.5" customHeight="1">
@@ -7374,40 +7374,40 @@
         </is>
       </c>
       <c r="D15" s="18" t="n">
-        <v>0</v>
+        <v>-221.0352</v>
       </c>
       <c r="E15" s="18" t="n">
-        <v>0</v>
+        <v>-259.4943</v>
       </c>
       <c r="F15" s="18" t="n">
-        <v>0</v>
+        <v>-284.2866</v>
       </c>
       <c r="G15" s="18" t="n">
-        <v>0</v>
+        <v>-329.6748000000001</v>
       </c>
       <c r="H15" s="18" t="n">
-        <v>0</v>
+        <v>-375.2805</v>
       </c>
       <c r="I15" s="18" t="n">
-        <v>0</v>
+        <v>-394.437</v>
       </c>
       <c r="J15" s="18" t="n">
-        <v>0</v>
+        <v>-438.3104</v>
       </c>
       <c r="K15" s="18" t="n">
-        <v>0</v>
+        <v>-492.1279</v>
       </c>
       <c r="L15" s="18" t="n">
-        <v>0</v>
+        <v>-543.9906</v>
       </c>
       <c r="M15" s="18" t="n">
-        <v>0</v>
+        <v>-594.8501</v>
       </c>
       <c r="N15" s="18" t="n">
-        <v>0</v>
+        <v>-644.4400000000001</v>
       </c>
       <c r="O15" s="18" t="n">
-        <v>0</v>
+        <v>-692.5401000000001</v>
       </c>
     </row>
     <row r="16" ht="15.5" customHeight="1">
@@ -7430,37 +7430,37 @@
         <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>0</v>
+        <v>17.39953636343894</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>0</v>
+        <v>9.554082690833665</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>0</v>
+        <v>15.96564875024009</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>0</v>
+        <v>13.83354141717836</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>0</v>
+        <v>5.104581772833905</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>0</v>
+        <v>11.12304373068451</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>0</v>
+        <v>12.27839905236106</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>0</v>
+        <v>10.5384596158844</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>0</v>
+        <v>9.349334345115533</v>
       </c>
       <c r="N16" s="18" t="n">
-        <v>0</v>
+        <v>8.336537221730334</v>
       </c>
       <c r="O16" s="18" t="n">
-        <v>0</v>
+        <v>7.463860095586861</v>
       </c>
     </row>
     <row r="17" ht="15.5" customHeight="1">
@@ -7480,40 +7480,40 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>0</v>
+        <v>61.65385645816287</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>0</v>
+        <v>61.31107017956786</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>0</v>
+        <v>59.90199056011569</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0</v>
+        <v>65.65690393936698</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>0</v>
+        <v>68.09444702798287</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>0</v>
+        <v>65.80607681214606</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>0</v>
+        <v>66.6156932899512</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>0</v>
+        <v>67.58572540529593</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>0</v>
+        <v>81.81818181818183</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>0</v>
+        <v>82.60869565217391</v>
       </c>
       <c r="N17" s="18" t="n">
-        <v>0</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="O17" s="18" t="n">
-        <v>0</v>
+        <v>80.76923076923076</v>
       </c>
     </row>
     <row r="18" ht="15.5" customHeight="1">
@@ -7642,25 +7642,25 @@
         <v>29.10241886709813</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>37.35979336698412</v>
+        <v>28.19161739098237</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>36.87062115981465</v>
+        <v>28.88200093171841</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>38.58169251852395</v>
+        <v>30.75973296544118</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>38.07596362365395</v>
+        <v>31.11314025612368</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>37.65660395636525</v>
+        <v>31.38842271753705</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>37.31602079257074</v>
+        <v>31.07290744899167</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>35.15743037725027</v>
+        <v>29.35232302593269</v>
       </c>
       <c r="L20" s="18" t="n">
         <v>32.76243108879923</v>
@@ -7851,40 +7851,40 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>240.3601712160632</v>
+        <v>19.32497121606318</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>184.0899085795669</v>
+        <v>28.46017225407645</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>216.1014300000001</v>
+        <v>34.64166217987922</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>225.85343</v>
+        <v>-2.02327706361509</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>256.34977</v>
+        <v>-18.14970385086406</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>286.49919</v>
+        <v>-8.165037332774634</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>316.0436</v>
+        <v>-12.18611671660015</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>363.7965649999999</v>
+        <v>-8.100424087602491</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>413.80353</v>
+        <v>-130.18707</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>462.2676150000001</v>
+        <v>-132.5824849999999</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>508.9693997655</v>
+        <v>-135.4706002345001</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>585.0890700000001</v>
+        <v>-107.4510299999999</v>
       </c>
     </row>
     <row r="25" ht="15.5" customHeight="1">
@@ -7904,40 +7904,40 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>158.1442373727677</v>
+        <v>-62.89096262723227</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>184.0899085795669</v>
+        <v>-75.40439142043309</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>216.1014300000001</v>
+        <v>-68.18517</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>225.85343</v>
+        <v>-103.82137</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>256.34977</v>
+        <v>-118.9307299999999</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>286.49919</v>
+        <v>-107.9378099999999</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>316.0436</v>
+        <v>-122.2667999999999</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>363.7965649999999</v>
+        <v>-128.3313350000001</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>413.80353</v>
+        <v>-130.18707</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>462.2676150000001</v>
+        <v>-132.5824849999999</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>508.9693997655</v>
+        <v>-135.4706002345001</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>585.0890700000001</v>
+        <v>-107.4510299999999</v>
       </c>
     </row>
     <row r="26" ht="15.5" customHeight="1">
@@ -7957,40 +7957,40 @@
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>67.0442151042667</v>
+        <v>5.390358646103826</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>57.64020663301588</v>
+        <v>6.724323495322523</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>58.12937884018535</v>
+        <v>7.299339894619871</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>56.41830748147605</v>
+        <v>-0.402948929698298</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>56.92403637634605</v>
+        <v>-3.29325410578551</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>57.34339604363474</v>
+        <v>-1.362217727785699</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>57.68397920742926</v>
+        <v>-1.852081569564817</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>59.84256962274973</v>
+        <v>-1.112460882732206</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>62.23756891120077</v>
+        <v>-19.58061290698104</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>64.19655089137802</v>
+        <v>-18.41214476079588</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>65.81546249010769</v>
+        <v>-17.51787084322565</v>
       </c>
       <c r="O26" s="18" t="n">
-        <v>68.23748417656192</v>
+        <v>-12.53174659266883</v>
       </c>
     </row>
     <row r="27" ht="15.5" customHeight="1">
@@ -8010,40 +8010,40 @@
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>44.11153567697026</v>
+        <v>-17.5423207811926</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>57.64020663301588</v>
+        <v>-17.81589782213242</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>58.12937884018535</v>
+        <v>-14.3672878344596</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>56.41830748147605</v>
+        <v>-20.67670843189554</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>56.92403637634605</v>
+        <v>-21.57991767220607</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>57.34339604363474</v>
+        <v>-18.007853765734</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>57.68397920742926</v>
+        <v>-18.58246495712581</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>59.84256962274973</v>
+        <v>-17.62421185266076</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>62.23756891120077</v>
+        <v>-19.58061290698104</v>
       </c>
       <c r="M27" s="18" t="n">
-        <v>64.19655089137802</v>
+        <v>-18.41214476079588</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>65.81546249010769</v>
+        <v>-17.51787084322565</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>68.23748417656192</v>
+        <v>-12.53174659266883</v>
       </c>
     </row>
     <row r="28" ht="15.5" customHeight="1">
@@ -8119,25 +8119,25 @@
         <v>2.491349586231524</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>6.330954782687299</v>
+        <v>4.777324467507837</v>
       </c>
       <c r="F29" s="19" t="n">
-        <v>8.444929697480063</v>
+        <v>6.61519821794458</v>
       </c>
       <c r="G29" s="19" t="n">
-        <v>10.60607325555495</v>
+        <v>8.455823471096881</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>11.86024324431063</v>
+        <v>9.69140046406442</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>12.86062314184628</v>
+        <v>10.7198906214424</v>
       </c>
       <c r="J29" s="19" t="n">
-        <v>13.83200512016606</v>
+        <v>11.51785763337521</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>14.47377146833568</v>
+        <v>12.08389836752752</v>
       </c>
       <c r="L29" s="19" t="n">
         <v>15.05130087601154</v>
@@ -8169,40 +8169,40 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>231.4284354626594</v>
+        <v>10.39323546265933</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>163.870257137535</v>
+        <v>8.240520812044544</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>184.7066100262263</v>
+        <v>3.246842206105519</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>183.395261179802</v>
+        <v>-44.48144588381315</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>202.9387538218419</v>
+        <v>-71.56072002902224</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>222.2449189374613</v>
+        <v>-72.41930839531332</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>240.2597037872246</v>
+        <v>-87.97001292937559</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>275.8072226978641</v>
+        <v>-96.08976638973836</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>313.7308320693973</v>
+        <v>-230.2597679306027</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>350.2323629972152</v>
+        <v>-244.6177370027848</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>385.0912707480148</v>
+        <v>-259.3487292519853</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>452.969700116478</v>
+        <v>-239.570399883522</v>
       </c>
     </row>
     <row r="31" ht="15.5" customHeight="1">
@@ -8222,40 +8222,40 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>64.55286551803518</v>
+        <v>2.899009059872302</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>51.30925185032857</v>
+        <v>1.946999027814686</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>49.68444914270529</v>
+        <v>0.6841416766752918</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>45.81223422592109</v>
+        <v>-8.858772400795178</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>45.06379313203542</v>
+        <v>-12.98465456984993</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>44.48277290178846</v>
+        <v>-12.0821083492281</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>43.85197408726319</v>
+        <v>-13.36993920294003</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>45.36879815441405</v>
+        <v>-13.19635925025972</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>47.18626803518923</v>
+        <v>-34.63191378299258</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>48.63786470302122</v>
+        <v>-33.97083094915268</v>
       </c>
       <c r="N31" s="19" t="n">
-        <v>49.79662843554285</v>
+        <v>-33.5367048977905</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>52.82873040879086</v>
+        <v>-27.9405003604399</v>
       </c>
     </row>
     <row r="32" ht="15.5" customHeight="1">
@@ -8328,40 +8328,40 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>231.4284354626594</v>
+        <v>10.39323546265933</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>163.870257137535</v>
+        <v>8.240520812044544</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>184.7066100262263</v>
+        <v>3.246842206105519</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>183.395261179802</v>
+        <v>-44.48144588381315</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>202.9387538218419</v>
+        <v>-71.56072002902224</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>222.2449189374613</v>
+        <v>-72.41930839531332</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>240.2597037872246</v>
+        <v>-87.97001292937559</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>275.8072226978641</v>
+        <v>-96.08976638973836</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>313.7308320693973</v>
+        <v>-230.2597679306027</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>350.2323629972152</v>
+        <v>-244.6177370027848</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>385.0912707480148</v>
+        <v>-259.3487292519853</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>452.969700116478</v>
+        <v>-239.570399883522</v>
       </c>
     </row>
     <row r="34" ht="15.5" customHeight="1">
@@ -8381,40 +8381,40 @@
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>149.2125016193639</v>
+        <v>-71.82269838063611</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>163.870257137535</v>
+        <v>-95.62404286246499</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>184.7066100262263</v>
+        <v>-99.57998997377371</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>183.395261179802</v>
+        <v>-146.2795388201981</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>202.9387538218419</v>
+        <v>-172.3417461781581</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>222.2449189374613</v>
+        <v>-172.1920810625386</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>240.2597037872246</v>
+        <v>-198.0506962127754</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>275.8072226978641</v>
+        <v>-216.3206773021359</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>313.7308320693973</v>
+        <v>-230.2597679306027</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>350.2323629972152</v>
+        <v>-244.6177370027848</v>
       </c>
       <c r="N34" s="19" t="n">
-        <v>385.0912707480148</v>
+        <v>-259.3487292519853</v>
       </c>
       <c r="O34" s="19" t="n">
-        <v>452.969700116478</v>
+        <v>-239.570399883522</v>
       </c>
     </row>
     <row r="35" ht="15.5" customHeight="1">
@@ -8487,40 +8487,40 @@
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>-41.7795004534219</v>
+        <v>0</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>-45.8836719985098</v>
+        <v>0</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>-51.71785080734337</v>
+        <v>0</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>-51.35067313034455</v>
+        <v>0</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>-56.82285107011572</v>
+        <v>0</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>-62.22857730248916</v>
+        <v>0</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>-67.27271706042288</v>
+        <v>0</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>-77.22602235540194</v>
+        <v>0</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>-87.84463297943122</v>
+        <v>0</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>-98.06506163922026</v>
+        <v>0</v>
       </c>
       <c r="N36" s="19" t="n">
-        <v>-107.8255558094441</v>
+        <v>0</v>
       </c>
       <c r="O36" s="19" t="n">
-        <v>-126.8315160326138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" ht="15.5" customHeight="1">
@@ -8540,40 +8540,40 @@
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>0</v>
+        <v>-71.82269838063611</v>
       </c>
       <c r="E37" s="19" t="n">
-        <v>0</v>
+        <v>-167.4467412431011</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>0</v>
+        <v>-267.0267312168748</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>0</v>
+        <v>-413.3062700370729</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>0</v>
+        <v>-585.648016215231</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>0</v>
+        <v>-757.8400972777696</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>0</v>
+        <v>-955.890793490545</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>0</v>
+        <v>-1172.211470792681</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>0</v>
+        <v>-1402.471238723284</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>0</v>
+        <v>-1647.088975726069</v>
       </c>
       <c r="N37" s="19" t="n">
-        <v>0</v>
+        <v>-1906.437704978054</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>0</v>
+        <v>-2146.008104861576</v>
       </c>
     </row>
     <row r="38" ht="15.5" customHeight="1">
@@ -8593,40 +8593,40 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>189.6489350092375</v>
+        <v>10.39323546265933</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>117.9865851390252</v>
+        <v>8.240520812044544</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>132.988759218883</v>
+        <v>3.246842206105519</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>132.0445880494574</v>
+        <v>-44.48144588381315</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>146.1159027517261</v>
+        <v>-71.56072002902224</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>160.0163416349722</v>
+        <v>-72.41930839531332</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>172.9869867268017</v>
+        <v>-87.97001292937559</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>198.5812003424621</v>
+        <v>-96.08976638973836</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>225.886199089966</v>
+        <v>-230.2597679306027</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>252.1673013579949</v>
+        <v>-244.6177370027848</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>277.2657149385706</v>
+        <v>-259.3487292519853</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>326.1381840838642</v>
+        <v>-239.570399883522</v>
       </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
@@ -8646,40 +8646,40 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>52.89921341262833</v>
+        <v>2.899009059872302</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>36.94266133223658</v>
+        <v>1.946999027814686</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>35.77280338274781</v>
+        <v>0.6841416766752918</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>32.98480864266318</v>
+        <v>-8.858772400795178</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>32.44593105506551</v>
+        <v>-12.98465456984993</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>32.02759648928769</v>
+        <v>-12.0821083492281</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>31.5734213428295</v>
+        <v>-13.36993920294003</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>32.66553467117812</v>
+        <v>-13.19635925025972</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>33.97411298533626</v>
+        <v>-34.63191378299258</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>35.01926258617528</v>
+        <v>-33.97083094915268</v>
       </c>
       <c r="N39" s="19" t="n">
-        <v>35.85357247359085</v>
+        <v>-33.5367048977905</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>38.03668589432942</v>
+        <v>-27.9405003604399</v>
       </c>
     </row>
     <row r="40" ht="15.5" customHeight="1">
@@ -8858,40 +8858,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>969.7691274549296</v>
+        <v>790.5134279083514</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>733.0303149340045</v>
+        <v>340.1639873859361</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>526.214995515699</v>
+        <v>-99.22008122502609</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>333.2325427605018</v>
+        <v>-570.5266608498788</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>168.945804161782</v>
+        <v>-1053.271048378483</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>33.04249590597462</v>
+        <v>-1521.382779331801</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>-115.5715014127341</v>
+        <v>-2041.034459590087</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>-263.0275718957517</v>
+        <v>-2603.392407717703</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>-366.7541218715223</v>
+        <v>-3163.264924714042</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>-427.9409610371185</v>
+        <v>-3721.236802240418</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>-447.9313277631749</v>
+        <v>-4277.84161315703</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>-447.9313277631749</v>
+        <v>-4674.404073468322</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -8911,40 +8911,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>969.7691274549296</v>
+        <v>790.5134279083514</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>733.0303149340045</v>
+        <v>340.1639873859361</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>526.214995515699</v>
+        <v>-99.22008122502609</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>333.2325427605018</v>
+        <v>-570.5266608498788</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>168.945804161782</v>
+        <v>-1053.271048378483</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>33.04249590597462</v>
+        <v>-1521.382779331801</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>-115.5715014127341</v>
+        <v>-2041.034459590087</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>-263.0275718957517</v>
+        <v>-2603.392407717703</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>-366.7541218715223</v>
+        <v>-3163.264924714042</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>-427.9409610371185</v>
+        <v>-3721.236802240418</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>-447.9313277631749</v>
+        <v>-4277.84161315703</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>-447.9313277631749</v>
+        <v>-4674.404073468322</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -9070,40 +9070,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>1257.632143070661</v>
+        <v>1078.376443524082</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>1375.618728209686</v>
+        <v>982.7524006616173</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>1508.607487428569</v>
+        <v>883.1724106878437</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>1640.652075478026</v>
+        <v>736.8928718676456</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>1786.767978229752</v>
+        <v>564.5511256894874</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>1946.784319864724</v>
+        <v>392.3590446269488</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>2119.771306591526</v>
+        <v>194.3083484141737</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>2318.352506933988</v>
+        <v>-22.01232888796221</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>2544.238706023955</v>
+        <v>-252.2720968185649</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>2796.40600738195</v>
+        <v>-496.8898338213498</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>3073.67172232052</v>
+        <v>-756.2385630733352</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>3230.66378274829</v>
+        <v>-995.8089629568576</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -9123,40 +9123,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>518.2772612677285</v>
+        <v>339.0215617211503</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>636.2638464067536</v>
+        <v>347.2620825331949</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>769.2526056256366</v>
+        <v>350.5089247393004</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>901.297193675094</v>
+        <v>306.0274788554872</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>1047.41309642682</v>
+        <v>234.466758826465</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>1207.429438061792</v>
+        <v>162.0474504311517</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>1380.416424788594</v>
+        <v>74.07743750177607</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>1578.997625131056</v>
+        <v>-22.01232888796233</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>1804.883824221022</v>
+        <v>-252.272096818565</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>2057.051125579017</v>
+        <v>-496.8898338213498</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>2334.316840517588</v>
+        <v>-756.2385630733351</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>2491.308900945357</v>
+        <v>-995.8089629568572</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -9229,40 +9229,40 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>189.6489350092375</v>
+        <v>10.39323546265933</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>117.9865851390252</v>
+        <v>8.240520812044544</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>132.988759218883</v>
+        <v>3.246842206105519</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>132.0445880494574</v>
+        <v>-44.48144588381315</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>146.1159027517261</v>
+        <v>-71.56072002902224</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>160.0163416349722</v>
+        <v>-72.41930839531332</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>172.9869867268017</v>
+        <v>-87.97001292937559</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>198.5812003424621</v>
+        <v>-96.08976638973836</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>225.886199089966</v>
+        <v>-230.2597679306027</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>252.1673013579949</v>
+        <v>-244.6177370027848</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>277.2657149385706</v>
+        <v>-259.3487292519853</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>156.9920604277695</v>
+        <v>-239.570399883522</v>
       </c>
     </row>
     <row r="51" ht="15.5" customHeight="1">
@@ -9285,37 +9285,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>189.6489350092375</v>
+        <v>10.39323546265933</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>307.6355201482627</v>
+        <v>18.63375627470387</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>440.6242793671456</v>
+        <v>21.88059848080939</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>572.668867416603</v>
+        <v>-22.60084740300376</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>718.7847701683291</v>
+        <v>-94.161567432026</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>878.8011118033013</v>
+        <v>-166.5808758273393</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>1051.788098530103</v>
+        <v>-254.5508887567149</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>1250.369298872565</v>
+        <v>-350.6406551464533</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>1476.255497962531</v>
+        <v>-580.900423077056</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>1728.422799320526</v>
+        <v>-825.5181600798408</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>2005.688514259097</v>
+        <v>-1084.866889331826</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -9338,37 +9338,37 @@
         <v>739.354881802932</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>635.4903181284225</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>532.6634859485432</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>430.8653930121583</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>330.0843668630224</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>230.3115941957972</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>120.2309109123974</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -9391,37 +9391,37 @@
         <v>739.354881802932</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>635.4903181284225</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>532.6634859485432</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>430.8653930121583</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>330.0843668630224</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>230.3115941957972</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>120.2309109123974</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -9653,40 +9653,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>1257.632143070661</v>
+        <v>1078.376443524082</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>1375.618728209686</v>
+        <v>982.7524006616173</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>1508.607487428569</v>
+        <v>883.1724106878436</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>1640.652075478026</v>
+        <v>736.8928718676455</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>1786.767978229752</v>
+        <v>564.5511256894874</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>1946.784319864724</v>
+        <v>392.3590446269488</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>2119.771306591526</v>
+        <v>194.3083484141735</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>2318.352506933988</v>
+        <v>-22.0123288879625</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>2544.238706023954</v>
+        <v>-252.2720968185652</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>2796.406007381949</v>
+        <v>-496.88983382135</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>3073.67172232052</v>
+        <v>-756.2385630733352</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>3230.66378274829</v>
+        <v>-995.8089629568574</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -9712,34 +9712,34 @@
         <v>0</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>0</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="G59" s="18" t="n">
+        <v>1.13686837721616e-13</v>
+      </c>
+      <c r="H59" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="18" t="n">
         <v>2.273736754432321e-13</v>
       </c>
-      <c r="H59" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="18" t="n">
-        <v>2.273736754432321e-13</v>
-      </c>
-      <c r="J59" s="18" t="n">
-        <v>4.547473508864641e-13</v>
-      </c>
       <c r="K59" s="18" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>2.842170943040401e-13</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>2.557953848736361e-13</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>1.70530256582424e-13</v>
       </c>
       <c r="N59" s="18" t="n">
         <v>0</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>0</v>
+        <v>-2.273736754432321e-13</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -9812,40 +9812,40 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>158.1442373727677</v>
+        <v>-62.89096262723227</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>184.0899085795669</v>
+        <v>-75.40439142043309</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>216.1014300000001</v>
+        <v>-68.18517</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>225.85343</v>
+        <v>-103.82137</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>256.34977</v>
+        <v>-118.9307299999999</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>286.49919</v>
+        <v>-107.9378099999999</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>316.0436</v>
+        <v>-122.2667999999999</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>363.7965649999999</v>
+        <v>-128.3313350000001</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>413.80353</v>
+        <v>-130.18707</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>462.2676150000001</v>
+        <v>-132.5824849999999</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>508.9693997655</v>
+        <v>-135.4706002345001</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>585.0890700000001</v>
+        <v>-107.4510299999999</v>
       </c>
     </row>
     <row r="62" ht="15.5" customHeight="1">
@@ -9865,40 +9865,40 @@
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>-41.7795004534219</v>
+        <v>0</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>-45.8836719985098</v>
+        <v>0</v>
       </c>
       <c r="F62" s="18" t="n">
-        <v>-51.71785080734337</v>
+        <v>0</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>-51.35067313034455</v>
+        <v>0</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>-56.82285107011572</v>
+        <v>0</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>-62.22857730248916</v>
+        <v>0</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>-67.27271706042288</v>
+        <v>0</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>-77.22602235540194</v>
+        <v>0</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>-87.84463297943122</v>
+        <v>0</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>-98.06506163922026</v>
+        <v>0</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>-107.8255558094441</v>
+        <v>0</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>-126.8315160326138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" ht="15.5" customHeight="1">
@@ -9971,40 +9971,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>116.3647369193459</v>
+        <v>-62.89096262723227</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>138.2062365810571</v>
+        <v>-75.40439142043309</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>164.3835791926567</v>
+        <v>-68.18517</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>174.5027568696555</v>
+        <v>-103.82137</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>199.5269189298843</v>
+        <v>-118.9307299999999</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>224.2706126975108</v>
+        <v>-107.9378099999999</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>248.7708829395771</v>
+        <v>-122.2667999999999</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>286.570542644598</v>
+        <v>-128.3313350000001</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>325.9588970205688</v>
+        <v>-130.18707</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>364.2025533607798</v>
+        <v>-132.5824849999999</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>401.1438439560558</v>
+        <v>-135.4706002345001</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>458.2575539673863</v>
+        <v>-107.4510299999999</v>
       </c>
     </row>
     <row r="65" ht="15.5" customHeight="1">
@@ -10130,40 +10130,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>-180.430014449789</v>
+        <v>-359.6857139963671</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>-236.7388125209251</v>
+        <v>-450.3494405224153</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>-206.8153194183056</v>
+        <v>-439.3840686109622</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>-192.9824527551972</v>
+        <v>-471.3065796248527</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>-164.2867385987198</v>
+        <v>-482.7443875286041</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>-135.9033082558074</v>
+        <v>-468.1117309533181</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-148.6139973187087</v>
+        <v>-519.6516802582858</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>-147.4560704830176</v>
+        <v>-562.3579481276157</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>-103.7265499757706</v>
+        <v>-559.8725169963394</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>-61.18683916559621</v>
+        <v>-557.9718775263759</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>-19.99036672605638</v>
+        <v>-556.6048109166122</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>169.1461236560947</v>
+        <v>-396.5624603112915</v>
       </c>
     </row>
     <row r="68" ht="15.5" customHeight="1">
@@ -10428,7 +10428,7 @@
         <v>0</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>-169.1461236560947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" ht="15.5" customHeight="1">
@@ -10534,7 +10534,7 @@
         <v>0</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>-169.1461236560947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" ht="15.5" customHeight="1">
@@ -10554,40 +10554,40 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>969.7691274549296</v>
+        <v>790.5134279083514</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-236.7388125209251</v>
+        <v>-450.3494405224153</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>-206.8153194183056</v>
+        <v>-439.3840686109622</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>-192.9824527551972</v>
+        <v>-471.3065796248527</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>-164.2867385987198</v>
+        <v>-482.7443875286041</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>-135.9033082558074</v>
+        <v>-468.1117309533181</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>-148.6139973187087</v>
+        <v>-519.6516802582858</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>-147.4560704830176</v>
+        <v>-562.3579481276157</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>-103.7265499757706</v>
+        <v>-559.8725169963394</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>-61.18683916559621</v>
+        <v>-557.9718775263759</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>-19.99036672605638</v>
+        <v>-556.6048109166122</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>0</v>
+        <v>-396.5624603112915</v>
       </c>
     </row>
     <row r="76" ht="15.5" customHeight="1">
@@ -10610,37 +10610,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>969.7691274549296</v>
+        <v>790.5134279083514</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>733.0303149340045</v>
+        <v>340.1639873859361</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>526.214995515699</v>
+        <v>-99.22008122502609</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>333.2325427605018</v>
+        <v>-570.5266608498788</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>168.945804161782</v>
+        <v>-1053.271048378483</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>33.04249590597462</v>
+        <v>-1521.382779331801</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>-115.5715014127341</v>
+        <v>-2041.034459590087</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>-263.0275718957517</v>
+        <v>-2603.392407717703</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>-366.7541218715223</v>
+        <v>-3163.264924714042</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>-427.9409610371185</v>
+        <v>-3721.236802240418</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>-447.9313277631749</v>
+        <v>-4277.84161315703</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -10660,40 +10660,40 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>969.7691274549296</v>
+        <v>790.5134279083514</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-236.7388125209251</v>
+        <v>-450.3494405224153</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>-206.8153194183056</v>
+        <v>-439.3840686109622</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>-192.9824527551972</v>
+        <v>-471.3065796248527</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>-164.2867385987198</v>
+        <v>-482.7443875286041</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>-135.9033082558074</v>
+        <v>-468.1117309533181</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>-148.6139973187087</v>
+        <v>-519.6516802582858</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>-147.4560704830176</v>
+        <v>-562.3579481276157</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>-103.7265499757706</v>
+        <v>-559.8725169963394</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>-61.18683916559621</v>
+        <v>-557.9718775263759</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>-19.99036672605638</v>
+        <v>-556.6048109166122</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>0</v>
+        <v>-396.5624603112915</v>
       </c>
     </row>
     <row r="78" ht="15.5" customHeight="1">
@@ -10713,40 +10713,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>969.7691274549296</v>
+        <v>790.5134279083514</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>733.0303149340045</v>
+        <v>340.1639873859361</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>526.214995515699</v>
+        <v>-99.22008122502609</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>333.2325427605018</v>
+        <v>-570.5266608498788</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>168.945804161782</v>
+        <v>-1053.271048378483</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>33.04249590597462</v>
+        <v>-1521.382779331801</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>-115.5715014127341</v>
+        <v>-2041.034459590087</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>-263.0275718957517</v>
+        <v>-2603.392407717703</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>-366.7541218715223</v>
+        <v>-3163.264924714042</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>-427.9409610371185</v>
+        <v>-3721.236802240418</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>-447.9313277631749</v>
+        <v>-4277.84161315703</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>-447.9313277631749</v>
+        <v>-4674.404073468322</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -10875,25 +10875,25 @@
         <v>82.78564227982137</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>117.3986682541237</v>
+        <v>88.58877524081703</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>99.84923006949178</v>
+        <v>78.21526909998292</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>91.79800170185423</v>
+        <v>73.18709560899738</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>80.78705073684975</v>
+        <v>66.01379456336855</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>72.08954340783623</v>
+        <v>60.08978039074906</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>72.5303128117947</v>
+        <v>60.39571340618417</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>71.39503313951192</v>
+        <v>59.60646306261776</v>
       </c>
       <c r="L81" s="18" t="n">
         <v>64.62626748876401</v>
@@ -11694,37 +11694,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>518.2772612677285</v>
+        <v>339.0215617211503</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>636.2638464067537</v>
+        <v>347.2620825331949</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>769.2526056256366</v>
+        <v>350.5089247393004</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>901.297193675094</v>
+        <v>306.0274788554872</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>1047.41309642682</v>
+        <v>234.466758826465</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>1207.429438061792</v>
+        <v>162.0474504311517</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>1380.416424788594</v>
+        <v>74.07743750177609</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>1578.997625131056</v>
+        <v>-22.01232888796227</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>1804.883824221022</v>
+        <v>-252.272096818565</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>2057.051125579017</v>
+        <v>-496.8898338213498</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>2334.316840517587</v>
+        <v>-756.2385630733351</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -11797,40 +11797,40 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>189.6489350092375</v>
+        <v>10.39323546265933</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>117.9865851390252</v>
+        <v>8.240520812044544</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>132.988759218883</v>
+        <v>3.246842206105519</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>132.0445880494574</v>
+        <v>-44.48144588381315</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>146.1159027517261</v>
+        <v>-71.56072002902224</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>160.0163416349722</v>
+        <v>-72.41930839531332</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>172.9869867268017</v>
+        <v>-87.97001292937559</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>198.5812003424621</v>
+        <v>-96.08976638973836</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>225.886199089966</v>
+        <v>-230.2597679306027</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>252.1673013579949</v>
+        <v>-244.6177370027848</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>277.2657149385706</v>
+        <v>-259.3487292519853</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>326.1381840838642</v>
+        <v>-239.570399883522</v>
       </c>
     </row>
     <row r="99" ht="15.5" customHeight="1">
@@ -11883,7 +11883,7 @@
         <v>0</v>
       </c>
       <c r="O99" s="20" t="n">
-        <v>169.1461236560947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" ht="15.5" customHeight="1">
@@ -11903,40 +11903,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>518.2772612677285</v>
+        <v>339.0215617211503</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>636.2638464067537</v>
+        <v>347.2620825331949</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>769.2526056256366</v>
+        <v>350.5089247393004</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>901.297193675094</v>
+        <v>306.0274788554872</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>1047.41309642682</v>
+        <v>234.466758826465</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>1207.429438061792</v>
+        <v>162.0474504311517</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>1380.416424788594</v>
+        <v>74.07743750177609</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>1578.997625131056</v>
+        <v>-22.01232888796227</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>1804.883824221022</v>
+        <v>-252.272096818565</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>2057.051125579017</v>
+        <v>-496.8898338213498</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>2334.316840517587</v>
+        <v>-756.2385630733351</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>2829.601148257546</v>
+        <v>-995.8089629568572</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -12012,25 +12012,25 @@
         <v>-27.70127620654598</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>0</v>
+        <v>-27.70127620654598</v>
       </c>
       <c r="F102" s="18" t="n">
-        <v>0</v>
+        <v>-27.70127620654598</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>0</v>
+        <v>-27.70127620654598</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>0</v>
+        <v>-27.70127620654598</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>0</v>
+        <v>-27.70127620654598</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>0</v>
+        <v>-27.70127620654598</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>0</v>
+        <v>-27.70127620654598</v>
       </c>
       <c r="L102" s="18" t="n">
         <v>0</v>
@@ -12068,34 +12068,34 @@
         <v>739.354881802932</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>635.4903181284225</v>
       </c>
       <c r="G103" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>532.6634859485432</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>430.8653930121583</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>330.0843668630224</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>230.3115941957972</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>120.2309109123974</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -12171,25 +12171,25 @@
         <v>-82.21593384329545</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>0</v>
+        <v>-103.8645636745095</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>0</v>
+        <v>-102.8268321798792</v>
       </c>
       <c r="G105" s="18" t="n">
-        <v>0</v>
+        <v>-101.7980929363849</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>0</v>
+        <v>-100.7810261491359</v>
       </c>
       <c r="I105" s="18" t="n">
-        <v>0</v>
+        <v>-99.77277266722525</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>0</v>
+        <v>-110.0806832833998</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>0</v>
+        <v>-120.2309109123976</v>
       </c>
       <c r="L105" s="18" t="n">
         <v>0</v>
@@ -12277,37 +12277,37 @@
         <v>739.354881802932</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>635.4903181284225</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>532.6634859485432</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>430.8653930121583</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>330.0843668630224</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>230.3115941957972</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>120.2309109123974</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>739.354881802932</v>
+        <v>-1.70530256582424e-13</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -12719,7 +12719,7 @@
         <v>108.039040917626</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>26.1288736</v>
+        <v>175.6516194599442</v>
       </c>
       <c r="F2" s="18" t="n">
         <v>35.09181288000001</v>
@@ -12772,10 +12772,10 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>-75.81534103035783</v>
+        <v>62.58161676376708</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>34.30281541107079</v>
+        <v>-80.0219246552393</v>
       </c>
       <c r="G3" s="18" t="n">
         <v>38.30754810522059</v>
@@ -12931,7 +12931,7 @@
         <v>83.88407899762598</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>0</v>
+        <v>149.5227458599442</v>
       </c>
       <c r="F6" s="18" t="n">
         <v>0</v>
@@ -12984,10 +12984,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="18" t="n">
+        <v>78.24925497981074</v>
+      </c>
+      <c r="F7" s="18" t="n">
         <v>-100</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>0</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>0</v>
@@ -13037,7 +13037,7 @@
         <v>-77.64237657531883</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>0</v>
+        <v>-85.12460421353619</v>
       </c>
       <c r="F8" s="18" t="n">
         <v>0</v>
@@ -13246,40 +13246,40 @@
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>-50.08106832444757</v>
+        <v>-24.6342071175614</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>-63.80668216328984</v>
+        <v>-27.44091105155179</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>-88.56637171422135</v>
+        <v>-37.19463262515102</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>-117.7041791159469</v>
+        <v>-51.38642401196002</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>-141.402832667732</v>
+        <v>-60.19811057604373</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>-171.2157403463935</v>
+        <v>-75.18220942252646</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>-193.547099943432</v>
+        <v>-82.74203938374679</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>-227.0905052379269</v>
+        <v>-111.645849768217</v>
       </c>
       <c r="L12" s="18" t="n">
-        <v>-227.6317728858491</v>
+        <v>-109.5366144124633</v>
       </c>
       <c r="M12" s="18" t="n">
-        <v>-237.4025681106139</v>
+        <v>-116.6649372452767</v>
       </c>
       <c r="N12" s="18" t="n">
-        <v>-237.6328243203052</v>
+        <v>-114.2606200576604</v>
       </c>
       <c r="O12" s="18" t="n">
-        <v>-246.6697631616598</v>
+        <v>-120.6707547085507</v>
       </c>
     </row>
     <row r="13" ht="15.5" customHeight="1">
@@ -13302,37 +13302,37 @@
         <v>0</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>27.4067912248229</v>
+        <v>11.39352251361698</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>38.80422662875365</v>
+        <v>35.54445242461311</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>32.89940282949042</v>
+        <v>38.15548208214457</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>20.13407997046581</v>
+        <v>17.1478882477458</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>21.08367075553281</v>
+        <v>24.89131087852738</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>13.04281928277094</v>
+        <v>10.05534423540793</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>17.33087465753746</v>
+        <v>34.93243652167932</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>0.2383488677146994</v>
+        <v>-1.889219671069353</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>4.292368811652936</v>
+        <v>6.507707829978671</v>
       </c>
       <c r="N13" s="18" t="n">
-        <v>0.09698977206684667</v>
+        <v>-2.060873853265333</v>
       </c>
       <c r="O13" s="18" t="n">
-        <v>3.802900069551685</v>
+        <v>5.610099654330125</v>
       </c>
     </row>
     <row r="14" ht="15.5" customHeight="1">
@@ -13352,40 +13352,40 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>-46.35460283531369</v>
+        <v>-22.80120862637393</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>-244.1998960234161</v>
+        <v>-15.62235015875242</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>-252.3847143978654</v>
+        <v>-105.992337165201</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>-242.5158878621009</v>
+        <v>-105.8758009861561</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>-249.6565908955888</v>
+        <v>-106.283974523237</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>-241.2948852632153</v>
+        <v>-105.9545259083165</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>-247.899015009426</v>
+        <v>-105.9776667751514</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>-212.7285113460185</v>
+        <v>-104.5849776690155</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>-217.9598779112056</v>
+        <v>-104.8824898276382</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>-213.1390358777407</v>
+        <v>-104.7412942627038</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>-218.3717309955741</v>
+        <v>-104.9993386140422</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>-214.3047066341543</v>
+        <v>-104.8377813140798</v>
       </c>
     </row>
     <row r="15" ht="15.5" customHeight="1">
@@ -13514,7 +13514,7 @@
         <v>22.35762342468115</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>100</v>
+        <v>14.87539578646382</v>
       </c>
       <c r="F17" s="18" t="n">
         <v>100</v>
@@ -13885,7 +13885,7 @@
         <v>82.67633090162597</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>-1.30644368</v>
+        <v>148.2163021799442</v>
       </c>
       <c r="F24" s="18" t="n">
         <v>-1.754590644000001</v>
@@ -13938,7 +13938,7 @@
         <v>-1.207748096000003</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>-1.30644368</v>
+        <v>-1.306443680000001</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>-1.754590644000001</v>
@@ -13991,7 +13991,7 @@
         <v>76.52449540408477</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>-5</v>
+        <v>84.38083442421299</v>
       </c>
       <c r="F26" s="18" t="n">
         <v>-5.000000000000001</v>
@@ -14044,7 +14044,7 @@
         <v>-1.11788117123406</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>-5</v>
+        <v>-0.7437697893231916</v>
       </c>
       <c r="F27" s="18" t="n">
         <v>-5.000000000000001</v>
@@ -14150,7 +14150,7 @@
         <v>0.1655168663032763</v>
       </c>
       <c r="E29" s="19" t="n">
-        <v>1.904304079428621</v>
+        <v>0.2832727687927837</v>
       </c>
       <c r="F29" s="19" t="n">
         <v>2.322252845522347</v>
@@ -14203,7 +14203,7 @@
         <v>82.497508066715</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>-1.804016885873548</v>
+        <v>147.7187289740706</v>
       </c>
       <c r="F30" s="19" t="n">
         <v>-2.569511267151178</v>
@@ -14256,7 +14256,7 @@
         <v>76.35897853778151</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>-6.904304079428621</v>
+        <v>84.09756165542021</v>
       </c>
       <c r="F31" s="19" t="n">
         <v>-7.322252845522346</v>
@@ -14362,7 +14362,7 @@
         <v>82.497508066715</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>-1.804016885873548</v>
+        <v>147.7187289740706</v>
       </c>
       <c r="F33" s="19" t="n">
         <v>-2.569511267151178</v>
@@ -14415,7 +14415,7 @@
         <v>-1.386570930910977</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>-1.804016885873548</v>
+        <v>-1.804016885873551</v>
       </c>
       <c r="F34" s="19" t="n">
         <v>-2.569511267151178</v>
@@ -14574,25 +14574,25 @@
         <v>-1.386570930910977</v>
       </c>
       <c r="E37" s="19" t="n">
-        <v>-3.190587816784526</v>
+        <v>-3.190587816784529</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>-5.760099083935703</v>
+        <v>-5.760099083935707</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>-9.317709499216409</v>
+        <v>-9.317709499216413</v>
       </c>
       <c r="H37" s="19" t="n">
         <v>-13.59511879222003</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>-18.901656205389</v>
+        <v>-18.90165620538901</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>-24.8077271485582</v>
+        <v>-24.80772714855821</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>-32.32214574740298</v>
+        <v>-32.32214574740299</v>
       </c>
       <c r="L37" s="19" t="n">
         <v>-39.89469468642974</v>
@@ -14627,7 +14627,7 @@
         <v>82.497508066715</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>-1.804016885873548</v>
+        <v>147.7187289740706</v>
       </c>
       <c r="F38" s="19" t="n">
         <v>-2.569511267151178</v>
@@ -14680,7 +14680,7 @@
         <v>76.35897853778151</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>-6.904304079428621</v>
+        <v>84.09756165542021</v>
       </c>
       <c r="F39" s="19" t="n">
         <v>-7.322252845522346</v>
@@ -15157,37 +15157,37 @@
         <v>666.0145702106405</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>664.2105533247669</v>
+        <v>813.7332991847111</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>661.6410420576158</v>
+        <v>811.1637879175601</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>658.0834316423351</v>
+        <v>807.6061775022793</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>653.8060223493314</v>
+        <v>803.3287682092756</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>648.4994849361625</v>
+        <v>798.0222307961067</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>642.5934139929933</v>
+        <v>792.1161598529375</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>635.0789953941485</v>
+        <v>784.6017412540926</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>627.5064464551217</v>
+        <v>777.029192315066</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>619.4134524145067</v>
+        <v>768.9361982744509</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>611.2762065596911</v>
+        <v>760.7989524196354</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>602.6563325542008</v>
+        <v>752.179078414145</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -15263,7 +15263,7 @@
         <v>82.497508066715</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>-1.804016885873548</v>
+        <v>147.7187289740706</v>
       </c>
       <c r="F50" s="18" t="n">
         <v>-2.569511267151178</v>
@@ -15319,34 +15319,34 @@
         <v>82.497508066715</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>80.69349118084145</v>
+        <v>230.2162370407856</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>78.12397991369028</v>
+        <v>227.6467257736345</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>74.56636949840957</v>
+        <v>224.0891153583538</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>70.28896020540596</v>
+        <v>219.8117060653501</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>64.98242279223697</v>
+        <v>214.5051686521812</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>59.07635184906778</v>
+        <v>208.599097709012</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>51.56193325022299</v>
+        <v>201.0846791101672</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>43.98938431119624</v>
+        <v>193.5121301711405</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>35.89639027058119</v>
+        <v>185.4191361305254</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>27.7591444157656</v>
+        <v>177.2818902757098</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -15369,37 +15369,37 @@
         <v>149.5227458599442</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -15422,37 +15422,37 @@
         <v>149.5227458599442</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -15696,7 +15696,7 @@
         <v>807.6061775022793</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>803.3287682092757</v>
+        <v>803.3287682092756</v>
       </c>
       <c r="I58" s="18" t="n">
         <v>798.0222307961067</v>
@@ -15705,19 +15705,19 @@
         <v>792.1161598529375</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>784.6017412540928</v>
+        <v>784.6017412540926</v>
       </c>
       <c r="L58" s="18" t="n">
         <v>777.029192315066</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>768.9361982744508</v>
+        <v>768.9361982744509</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>760.7989524196353</v>
+        <v>760.7989524196354</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>752.1790784141451</v>
+        <v>752.179078414145</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -15749,7 +15749,7 @@
         <v>0</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>0</v>
       </c>
       <c r="I59" s="18" t="n">
         <v>0</v>
@@ -15758,19 +15758,19 @@
         <v>0</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>0</v>
       </c>
       <c r="L59" s="18" t="n">
         <v>-1.13686837721616e-13</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>0</v>
+        <v>-1.13686837721616e-13</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>-2.273736754432321e-13</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>-3.410605131648481e-13</v>
+        <v>-2.273736754432321e-13</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -15846,7 +15846,7 @@
         <v>-1.207748096000003</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>-1.30644368</v>
+        <v>-1.306443680000001</v>
       </c>
       <c r="F61" s="18" t="n">
         <v>-1.754590644000001</v>
@@ -16005,7 +16005,7 @@
         <v>-1.207748096000003</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>-1.30644368</v>
+        <v>-1.306443680000001</v>
       </c>
       <c r="F64" s="18" t="n">
         <v>-1.754590644000001</v>
@@ -16164,7 +16164,7 @@
         <v>-3.890090619664537</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>-6.087699244438686</v>
+        <v>-6.087699244438687</v>
       </c>
       <c r="F67" s="18" t="n">
         <v>-6.514801903164442</v>
@@ -16588,7 +16588,7 @@
         <v>813.0337963818312</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-6.087699244438686</v>
+        <v>-6.087699244438687</v>
       </c>
       <c r="F75" s="18" t="n">
         <v>-6.514801903164442</v>
@@ -16694,7 +16694,7 @@
         <v>813.0337963818312</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-6.087699244438686</v>
+        <v>-6.087699244438687</v>
       </c>
       <c r="F77" s="18" t="n">
         <v>-6.514801903164442</v>
@@ -16906,7 +16906,7 @@
         <v>2.482752994549144</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>18.29874351888895</v>
+        <v>2.722010522384628</v>
       </c>
       <c r="F81" s="18" t="n">
         <v>13.56501949740375</v>
@@ -17728,34 +17728,34 @@
         <v>666.0145702106405</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>664.2105533247669</v>
+        <v>813.7332991847111</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>661.6410420576158</v>
+        <v>811.1637879175599</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>658.0834316423351</v>
+        <v>807.6061775022793</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>653.8060223493314</v>
+        <v>803.3287682092756</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>648.4994849361625</v>
+        <v>798.0222307961067</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>642.5934139929933</v>
+        <v>792.1161598529375</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>635.0789953941485</v>
+        <v>784.6017412540926</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>627.5064464551217</v>
+        <v>777.0291923150659</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>619.4134524145067</v>
+        <v>768.9361982744508</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>611.2762065596911</v>
+        <v>760.7989524196353</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -17831,7 +17831,7 @@
         <v>82.497508066715</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>-1.804016885873548</v>
+        <v>147.7187289740706</v>
       </c>
       <c r="F98" s="21" t="n">
         <v>-2.569511267151178</v>
@@ -17937,37 +17937,37 @@
         <v>666.0145702106405</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>664.2105533247669</v>
+        <v>813.7332991847111</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>661.6410420576158</v>
+        <v>811.1637879175599</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>658.0834316423351</v>
+        <v>807.6061775022793</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>653.8060223493314</v>
+        <v>803.3287682092756</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>648.4994849361625</v>
+        <v>798.0222307961067</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>642.5934139929933</v>
+        <v>792.1161598529375</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>635.0789953941485</v>
+        <v>784.6017412540926</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>627.5064464551217</v>
+        <v>777.0291923150659</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>619.4134524145067</v>
+        <v>768.9361982744508</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>611.2762065596911</v>
+        <v>760.7989524196353</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>602.6563325542008</v>
+        <v>752.179078414145</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -18043,7 +18043,7 @@
         <v>-3127.26947649572</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>0</v>
+        <v>-3127.26947649572</v>
       </c>
       <c r="F102" s="18" t="n">
         <v>0</v>
@@ -18099,34 +18099,34 @@
         <v>149.5227458599442</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="G103" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -18202,7 +18202,7 @@
         <v>-83.88407899762598</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>0</v>
+        <v>-149.5227458599442</v>
       </c>
       <c r="F105" s="18" t="n">
         <v>0</v>
@@ -18308,37 +18308,37 @@
         <v>149.5227458599442</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>149.5227458599442</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -18750,25 +18750,25 @@
         <v>339.0512232420723</v>
       </c>
       <c r="E2" s="27" t="n">
-        <v>300.107875542147</v>
+        <v>379.1769822782721</v>
       </c>
       <c r="F2" s="27" t="n">
-        <v>336.269407181403</v>
+        <v>414.5486973031373</v>
       </c>
       <c r="G2" s="27" t="n">
-        <v>351.2935485872248</v>
+        <v>428.7895953319691</v>
       </c>
       <c r="H2" s="27" t="n">
-        <v>385.543380409862</v>
+        <v>462.2653411401293</v>
       </c>
       <c r="I2" s="27" t="n">
-        <v>419.0466744184446</v>
+        <v>495.0009915642115</v>
       </c>
       <c r="J2" s="27" t="n">
-        <v>451.639154246984</v>
+        <v>528.8858987864492</v>
       </c>
       <c r="K2" s="27" t="n">
-        <v>485.0958329196223</v>
+        <v>563.613771575554</v>
       </c>
       <c r="L2" s="27" t="n">
         <v>517.8723087955156</v>
@@ -18803,28 +18803,28 @@
         <v>0</v>
       </c>
       <c r="E3" s="27" t="n">
-        <v>-11.48597764300673</v>
+        <v>11.83471885236387</v>
       </c>
       <c r="F3" s="27" t="n">
-        <v>12.04951105462657</v>
+        <v>9.328550169985373</v>
       </c>
       <c r="G3" s="27" t="n">
-        <v>4.4678882720119</v>
+        <v>3.435277476802256</v>
       </c>
       <c r="H3" s="27" t="n">
-        <v>9.749633023543304</v>
+        <v>7.807033139935049</v>
       </c>
       <c r="I3" s="27" t="n">
-        <v>8.689889571691278</v>
+        <v>7.081571450574931</v>
       </c>
       <c r="J3" s="27" t="n">
-        <v>7.777768401043028</v>
+        <v>6.845422089996389</v>
       </c>
       <c r="K3" s="27" t="n">
-        <v>7.407833966127342</v>
+        <v>6.566231557466251</v>
       </c>
       <c r="L3" s="27" t="n">
-        <v>6.756701181831049</v>
+        <v>-8.115746116737077</v>
       </c>
       <c r="M3" s="27" t="n">
         <v>6.080252420429089</v>
@@ -18962,25 +18962,25 @@
         <v>67.40357297758246</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>0</v>
+        <v>79.06910673612512</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>0</v>
+        <v>78.27929012173431</v>
       </c>
       <c r="G6" s="27" t="n">
-        <v>0</v>
+        <v>77.49604674474431</v>
       </c>
       <c r="H6" s="27" t="n">
-        <v>0</v>
+        <v>76.72196073026731</v>
       </c>
       <c r="I6" s="27" t="n">
-        <v>0</v>
+        <v>75.95431714576688</v>
       </c>
       <c r="J6" s="27" t="n">
-        <v>0</v>
+        <v>77.24674453946521</v>
       </c>
       <c r="K6" s="27" t="n">
-        <v>0</v>
+        <v>78.51793865593164</v>
       </c>
       <c r="L6" s="27" t="n">
         <v>0</v>
@@ -19015,28 +19015,28 @@
         <v>0</v>
       </c>
       <c r="E7" s="27" t="n">
+        <v>17.30699611788009</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>-0.9988940649432676</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>-1.000575472480603</v>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>-0.9988716160279409</v>
+      </c>
+      <c r="I7" s="27" t="n">
+        <v>-1.000552615175265</v>
+      </c>
+      <c r="J7" s="27" t="n">
+        <v>1.701585166275654</v>
+      </c>
+      <c r="K7" s="27" t="n">
+        <v>1.645628076684824</v>
+      </c>
+      <c r="L7" s="27" t="n">
         <v>-100</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="27" t="n">
-        <v>0</v>
       </c>
       <c r="M7" s="27" t="n">
         <v>0</v>
@@ -19068,25 +19068,25 @@
         <v>-19.88005597887442</v>
       </c>
       <c r="E8" s="27" t="n">
-        <v>0</v>
+        <v>-20.85282346545432</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>0</v>
+        <v>-18.88301437948866</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>0</v>
+        <v>-18.07321063486786</v>
       </c>
       <c r="H8" s="27" t="n">
-        <v>0</v>
+        <v>-16.59695285418556</v>
       </c>
       <c r="I8" s="27" t="n">
-        <v>0</v>
+        <v>-15.34427575705454</v>
       </c>
       <c r="J8" s="27" t="n">
-        <v>0</v>
+        <v>-14.60555948205674</v>
       </c>
       <c r="K8" s="27" t="n">
-        <v>0</v>
+        <v>-13.93116041796472</v>
       </c>
       <c r="L8" s="27" t="n">
         <v>0</v>
@@ -19277,40 +19277,40 @@
         </is>
       </c>
       <c r="D12" s="27" t="n">
-        <v>-139.6350840259695</v>
+        <v>77.68303618562237</v>
       </c>
       <c r="E12" s="27" t="n">
-        <v>-192.8523799943341</v>
+        <v>50.98526888366035</v>
       </c>
       <c r="F12" s="27" t="n">
-        <v>-247.3339662500456</v>
+        <v>9.813227476909617</v>
       </c>
       <c r="G12" s="27" t="n">
-        <v>-300.0223976006189</v>
+        <v>-10.72182817584553</v>
       </c>
       <c r="H12" s="27" t="n">
-        <v>-350.9433968859905</v>
+        <v>-29.65724654443886</v>
       </c>
       <c r="I12" s="27" t="n">
-        <v>-400.1197972395553</v>
+        <v>-69.29347533025697</v>
       </c>
       <c r="J12" s="27" t="n">
-        <v>-448.352562035437</v>
+        <v>-87.0412386378498</v>
       </c>
       <c r="K12" s="27" t="n">
-        <v>-490.9065761586144</v>
+        <v>-98.20994950939627</v>
       </c>
       <c r="L12" s="27" t="n">
-        <v>-528.8944400138803</v>
+        <v>-105.1807328175494</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>-565.3634685530099</v>
+        <v>-111.5441296256207</v>
       </c>
       <c r="N12" s="27" t="n">
-        <v>-600.3494685833766</v>
+        <v>-117.4591435790657</v>
       </c>
       <c r="O12" s="27" t="n">
-        <v>-622.7283014853257</v>
+        <v>-111.9043822309782</v>
       </c>
     </row>
     <row r="13">
@@ -19333,37 +19333,37 @@
         <v>0</v>
       </c>
       <c r="E13" s="27" t="n">
-        <v>38.11169401986913</v>
+        <v>-34.36756415926913</v>
       </c>
       <c r="F13" s="27" t="n">
-        <v>28.2504090731533</v>
+        <v>-80.75281803592776</v>
       </c>
       <c r="G13" s="27" t="n">
-        <v>21.30254576409745</v>
+        <v>-209.2589385202151</v>
       </c>
       <c r="H13" s="27" t="n">
-        <v>16.97239929172094</v>
+        <v>176.606247162696</v>
       </c>
       <c r="I13" s="27" t="n">
-        <v>14.01263018193801</v>
+        <v>133.6477030206651</v>
       </c>
       <c r="J13" s="27" t="n">
-        <v>12.05458093517036</v>
+        <v>25.61245950359092</v>
       </c>
       <c r="K13" s="27" t="n">
-        <v>9.491194592485442</v>
+        <v>12.83151647004455</v>
       </c>
       <c r="L13" s="27" t="n">
-        <v>7.738308203675781</v>
+        <v>7.097838195595685</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>6.895332183520875</v>
+        <v>6.049964321041079</v>
       </c>
       <c r="N13" s="27" t="n">
-        <v>6.188231461065197</v>
+        <v>5.302846481744661</v>
       </c>
       <c r="O13" s="27" t="n">
-        <v>3.727634331842689</v>
+        <v>-4.729100842071432</v>
       </c>
     </row>
     <row r="14">
@@ -19383,40 +19383,40 @@
         </is>
       </c>
       <c r="D14" s="27" t="n">
-        <v>-41.18406731901813</v>
+        <v>22.91188789788233</v>
       </c>
       <c r="E14" s="27" t="n">
-        <v>-64.26101935710449</v>
+        <v>13.44629850085232</v>
       </c>
       <c r="F14" s="27" t="n">
-        <v>-73.55232470392987</v>
+        <v>2.36720740910536</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>-85.40504054435389</v>
+        <v>-2.500487020340287</v>
       </c>
       <c r="H14" s="27" t="n">
-        <v>-91.02565747929869</v>
+        <v>-6.41563273406835</v>
       </c>
       <c r="I14" s="27" t="n">
-        <v>-95.48334867347269</v>
+        <v>-13.99865384335664</v>
       </c>
       <c r="J14" s="27" t="n">
-        <v>-99.27229688111814</v>
+        <v>-16.45747009658786</v>
       </c>
       <c r="K14" s="27" t="n">
-        <v>-101.1978547010019</v>
+        <v>-17.42504432332363</v>
       </c>
       <c r="L14" s="27" t="n">
-        <v>-102.1283492148867</v>
+        <v>-20.31016739670484</v>
       </c>
       <c r="M14" s="27" t="n">
-        <v>-102.9130640773015</v>
+        <v>-20.30436842512755</v>
       </c>
       <c r="N14" s="27" t="n">
-        <v>-103.6034888077358</v>
+        <v>-20.2701554744025</v>
       </c>
       <c r="O14" s="27" t="n">
-        <v>-98.46305937008314</v>
+        <v>-17.69382860085238</v>
       </c>
     </row>
     <row r="15">
@@ -19436,40 +19436,40 @@
         </is>
       </c>
       <c r="D15" s="27" t="n">
-        <v>0</v>
+        <v>-217.3181202115919</v>
       </c>
       <c r="E15" s="27" t="n">
-        <v>0</v>
+        <v>-243.8376488779945</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>0</v>
+        <v>-257.1471937269552</v>
       </c>
       <c r="G15" s="27" t="n">
-        <v>0</v>
+        <v>-289.3005694247734</v>
       </c>
       <c r="H15" s="27" t="n">
-        <v>0</v>
+        <v>-321.2861503415517</v>
       </c>
       <c r="I15" s="27" t="n">
-        <v>0</v>
+        <v>-330.8263219092984</v>
       </c>
       <c r="J15" s="27" t="n">
-        <v>0</v>
+        <v>-361.3113233975872</v>
       </c>
       <c r="K15" s="27" t="n">
-        <v>0</v>
+        <v>-392.6966266492181</v>
       </c>
       <c r="L15" s="27" t="n">
-        <v>0</v>
+        <v>-423.7137071963309</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>0</v>
+        <v>-453.8193389273891</v>
       </c>
       <c r="N15" s="27" t="n">
-        <v>0</v>
+        <v>-482.890325004311</v>
       </c>
       <c r="O15" s="27" t="n">
-        <v>0</v>
+        <v>-510.8239192543475</v>
       </c>
     </row>
     <row r="16">
@@ -19492,37 +19492,37 @@
         <v>0</v>
       </c>
       <c r="E16" s="27" t="n">
-        <v>0</v>
+        <v>12.20309132095469</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>0</v>
+        <v>5.45836334553087</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>0</v>
+        <v>12.50387967755127</v>
       </c>
       <c r="H16" s="27" t="n">
-        <v>0</v>
+        <v>11.05617627382358</v>
       </c>
       <c r="I16" s="27" t="n">
-        <v>0</v>
+        <v>2.969369067918048</v>
       </c>
       <c r="J16" s="27" t="n">
-        <v>0</v>
+        <v>9.214805313056939</v>
       </c>
       <c r="K16" s="27" t="n">
-        <v>0</v>
+        <v>8.686498656200282</v>
       </c>
       <c r="L16" s="27" t="n">
-        <v>0</v>
+        <v>7.898484082171464</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>0</v>
+        <v>7.105182395505705</v>
       </c>
       <c r="N16" s="27" t="n">
-        <v>0</v>
+        <v>6.405849989917067</v>
       </c>
       <c r="O16" s="27" t="n">
-        <v>0</v>
+        <v>5.78466637321573</v>
       </c>
     </row>
     <row r="17">
@@ -19542,40 +19542,40 @@
         </is>
       </c>
       <c r="D17" s="27" t="n">
-        <v>0</v>
+        <v>64.09595521690046</v>
       </c>
       <c r="E17" s="27" t="n">
-        <v>0</v>
+        <v>64.30708093431838</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>0</v>
+        <v>62.03063606274397</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>0</v>
+        <v>67.46912065363823</v>
       </c>
       <c r="H17" s="27" t="n">
-        <v>0</v>
+        <v>69.5025392881787</v>
       </c>
       <c r="I17" s="27" t="n">
-        <v>0</v>
+        <v>66.83346650758853</v>
       </c>
       <c r="J17" s="27" t="n">
-        <v>0</v>
+        <v>68.31555241435461</v>
       </c>
       <c r="K17" s="27" t="n">
-        <v>0</v>
+        <v>69.67477489974286</v>
       </c>
       <c r="L17" s="27" t="n">
-        <v>0</v>
+        <v>81.81818181818181</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>0</v>
+        <v>82.60869565217391</v>
       </c>
       <c r="N17" s="27" t="n">
-        <v>0</v>
+        <v>83.33333333333334</v>
       </c>
       <c r="O17" s="27" t="n">
-        <v>0</v>
+        <v>80.76923076923076</v>
       </c>
     </row>
     <row r="18">
@@ -19704,25 +19704,25 @@
         <v>30.17771228390791</v>
       </c>
       <c r="E20" s="27" t="n">
-        <v>37.53523002489268</v>
+        <v>29.70807477044961</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>37.40110302660882</v>
+        <v>30.33864736400692</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>39.45782970916849</v>
+        <v>32.326533033883</v>
       </c>
       <c r="H20" s="27" t="n">
-        <v>39.21452264911252</v>
+        <v>32.7061068130454</v>
       </c>
       <c r="I20" s="27" t="n">
-        <v>39.01847986503407</v>
+        <v>33.03137671833244</v>
       </c>
       <c r="J20" s="27" t="n">
-        <v>38.86983266656834</v>
+        <v>33.19267613587678</v>
       </c>
       <c r="K20" s="27" t="n">
-        <v>37.63570009419097</v>
+        <v>32.39261033964513</v>
       </c>
       <c r="L20" s="27" t="n">
         <v>36.00151329942941</v>
@@ -19913,40 +19913,40 @@
         </is>
       </c>
       <c r="D24" s="27" t="n">
-        <v>223.1509380837849</v>
+        <v>5.832817872193058</v>
       </c>
       <c r="E24" s="27" t="n">
-        <v>172.4563003574762</v>
+        <v>7.687758215606742</v>
       </c>
       <c r="F24" s="27" t="n">
-        <v>193.6874693954496</v>
+        <v>14.81956579022865</v>
       </c>
       <c r="G24" s="27" t="n">
-        <v>195.1160609770213</v>
+        <v>-16.68846170300773</v>
       </c>
       <c r="H24" s="27" t="n">
-        <v>215.0772151563895</v>
+        <v>-29.48697445489485</v>
       </c>
       <c r="I24" s="27" t="n">
-        <v>234.5886984144667</v>
+        <v>-20.28330634906481</v>
       </c>
       <c r="J24" s="27" t="n">
-        <v>253.5058130221277</v>
+        <v>-30.55876583599438</v>
       </c>
       <c r="K24" s="27" t="n">
-        <v>278.2718284265944</v>
+        <v>-35.90685956669201</v>
       </c>
       <c r="L24" s="27" t="n">
-        <v>305.5368252306601</v>
+        <v>-118.1768819656708</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>331.6900533902303</v>
+        <v>-122.1292855371588</v>
       </c>
       <c r="N24" s="27" t="n">
-        <v>356.6227331947959</v>
+        <v>-126.2675918095151</v>
       </c>
       <c r="O24" s="27" t="n">
-        <v>403.3809372949113</v>
+        <v>-107.4429819594362</v>
       </c>
     </row>
     <row r="25">
@@ -19966,40 +19966,40 @@
         </is>
       </c>
       <c r="D25" s="27" t="n">
-        <v>155.7473651062025</v>
+        <v>-61.5707551053894</v>
       </c>
       <c r="E25" s="27" t="n">
-        <v>172.4563003574762</v>
+        <v>-71.38134852051837</v>
       </c>
       <c r="F25" s="27" t="n">
-        <v>193.6874693954496</v>
+        <v>-63.45972433150565</v>
       </c>
       <c r="G25" s="27" t="n">
-        <v>195.1160609770213</v>
+        <v>-94.18450844775204</v>
       </c>
       <c r="H25" s="27" t="n">
-        <v>215.0772151563895</v>
+        <v>-106.2089351851622</v>
       </c>
       <c r="I25" s="27" t="n">
-        <v>234.5886984144667</v>
+        <v>-96.23762349483168</v>
       </c>
       <c r="J25" s="27" t="n">
-        <v>253.5058130221277</v>
+        <v>-107.8055103754596</v>
       </c>
       <c r="K25" s="27" t="n">
-        <v>278.2718284265944</v>
+        <v>-114.4247982226237</v>
       </c>
       <c r="L25" s="27" t="n">
-        <v>305.5368252306601</v>
+        <v>-118.1768819656708</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>331.6900533902303</v>
+        <v>-122.1292855371588</v>
       </c>
       <c r="N25" s="27" t="n">
-        <v>356.6227331947959</v>
+        <v>-126.2675918095151</v>
       </c>
       <c r="O25" s="27" t="n">
-        <v>403.3809372949113</v>
+        <v>-107.4429819594362</v>
       </c>
     </row>
     <row r="26">
@@ -20019,40 +20019,40 @@
         </is>
       </c>
       <c r="D26" s="27" t="n">
-        <v>65.81629051503582</v>
+        <v>1.720335298135351</v>
       </c>
       <c r="E26" s="27" t="n">
-        <v>57.46476997510732</v>
+        <v>2.027485468504735</v>
       </c>
       <c r="F26" s="27" t="n">
-        <v>57.59889697339118</v>
+        <v>3.574867292223548</v>
       </c>
       <c r="G26" s="27" t="n">
-        <v>55.54217029083151</v>
+        <v>-3.89199315577784</v>
       </c>
       <c r="H26" s="27" t="n">
-        <v>55.78547735088748</v>
+        <v>-6.378798458514821</v>
       </c>
       <c r="I26" s="27" t="n">
-        <v>55.98152013496593</v>
+        <v>-4.097629438068238</v>
       </c>
       <c r="J26" s="27" t="n">
-        <v>56.13016733343167</v>
+        <v>-5.777950576128566</v>
       </c>
       <c r="K26" s="27" t="n">
-        <v>57.36429990580903</v>
+        <v>-6.370827218489744</v>
       </c>
       <c r="L26" s="27" t="n">
-        <v>58.99848670057059</v>
+        <v>-22.81969511761122</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>60.37751219709682</v>
+        <v>-22.23118345507709</v>
       </c>
       <c r="N26" s="27" t="n">
-        <v>61.54308661972264</v>
+        <v>-21.7902467136107</v>
       </c>
       <c r="O26" s="27" t="n">
-        <v>63.78081915161612</v>
+        <v>-16.98841161761464</v>
       </c>
     </row>
     <row r="27">
@@ -20072,40 +20072,40 @@
         </is>
       </c>
       <c r="D27" s="27" t="n">
-        <v>45.93623453616139</v>
+        <v>-18.15972068073907</v>
       </c>
       <c r="E27" s="27" t="n">
-        <v>57.46476997510732</v>
+        <v>-18.82533799694959</v>
       </c>
       <c r="F27" s="27" t="n">
-        <v>57.59889697339118</v>
+        <v>-15.30814708726511</v>
       </c>
       <c r="G27" s="27" t="n">
-        <v>55.54217029083151</v>
+        <v>-21.9652037906457</v>
       </c>
       <c r="H27" s="27" t="n">
-        <v>55.78547735088748</v>
+        <v>-22.97575131270038</v>
       </c>
       <c r="I27" s="27" t="n">
-        <v>55.98152013496593</v>
+        <v>-19.44190519512278</v>
       </c>
       <c r="J27" s="27" t="n">
-        <v>56.13016733343167</v>
+        <v>-20.3835100581853</v>
       </c>
       <c r="K27" s="27" t="n">
-        <v>57.36429990580903</v>
+        <v>-20.30198763645446</v>
       </c>
       <c r="L27" s="27" t="n">
-        <v>58.99848670057059</v>
+        <v>-22.81969511761122</v>
       </c>
       <c r="M27" s="27" t="n">
-        <v>60.37751219709682</v>
+        <v>-22.23118345507709</v>
       </c>
       <c r="N27" s="27" t="n">
-        <v>61.54308661972264</v>
+        <v>-21.7902467136107</v>
       </c>
       <c r="O27" s="27" t="n">
-        <v>63.78081915161612</v>
+        <v>-16.98841161761464</v>
       </c>
     </row>
     <row r="28">
@@ -20181,25 +20181,25 @@
         <v>2.276797019645691</v>
       </c>
       <c r="E29" s="27" t="n">
-        <v>5.604697204002637</v>
+        <v>4.435959590278713</v>
       </c>
       <c r="F29" s="27" t="n">
-        <v>7.681309219897731</v>
+        <v>6.230846495371456</v>
       </c>
       <c r="G29" s="27" t="n">
-        <v>9.891864747476378</v>
+        <v>8.104087195948731</v>
       </c>
       <c r="H29" s="27" t="n">
-        <v>11.3035291812595</v>
+        <v>9.427487772186751</v>
       </c>
       <c r="I29" s="27" t="n">
-        <v>12.48599935643416</v>
+        <v>10.57011318415885</v>
       </c>
       <c r="J29" s="27" t="n">
-        <v>13.46802504274475</v>
+        <v>11.50094463406838</v>
       </c>
       <c r="K29" s="27" t="n">
-        <v>14.24410532099799</v>
+        <v>12.25973615862591</v>
       </c>
       <c r="L29" s="27" t="n">
         <v>14.92366054695905</v>
@@ -20231,40 +20231,40 @@
         </is>
       </c>
       <c r="D30" s="27" t="n">
-        <v>215.4314299379372</v>
+        <v>-1.886690273654702</v>
       </c>
       <c r="E30" s="27" t="n">
-        <v>155.6361626479737</v>
+        <v>-9.132379493895687</v>
       </c>
       <c r="F30" s="27" t="n">
-        <v>167.857576417929</v>
+        <v>-11.0103271872919</v>
       </c>
       <c r="G30" s="27" t="n">
-        <v>160.3665782841628</v>
+        <v>-51.43794439586622</v>
       </c>
       <c r="H30" s="27" t="n">
-        <v>171.4972066453465</v>
+        <v>-73.0669829659379</v>
       </c>
       <c r="I30" s="27" t="n">
-        <v>182.2665333434209</v>
+        <v>-72.60547142011055</v>
       </c>
       <c r="J30" s="27" t="n">
-        <v>192.6789386253032</v>
+        <v>-91.3856402328188</v>
       </c>
       <c r="K30" s="27" t="n">
-        <v>209.1742670777509</v>
+        <v>-105.0044209155354</v>
       </c>
       <c r="L30" s="27" t="n">
-        <v>228.2513197993178</v>
+        <v>-195.4623873970131</v>
       </c>
       <c r="M30" s="27" t="n">
-        <v>246.2984513172142</v>
+        <v>-207.5208876101749</v>
       </c>
       <c r="N30" s="27" t="n">
-        <v>263.2061469632826</v>
+        <v>-219.6841780410283</v>
       </c>
       <c r="O30" s="27" t="n">
-        <v>304.0715146426295</v>
+        <v>-206.752404611718</v>
       </c>
     </row>
     <row r="31">
@@ -20284,40 +20284,40 @@
         </is>
       </c>
       <c r="D31" s="27" t="n">
-        <v>63.53949349539012</v>
+        <v>-0.5564617215103402</v>
       </c>
       <c r="E31" s="27" t="n">
-        <v>51.86007277110468</v>
+        <v>-2.408474121773978</v>
       </c>
       <c r="F31" s="27" t="n">
-        <v>49.91758775349344</v>
+        <v>-2.655979203147908</v>
       </c>
       <c r="G31" s="27" t="n">
-        <v>45.65030554335512</v>
+        <v>-11.99608035172657</v>
       </c>
       <c r="H31" s="27" t="n">
-        <v>44.48194816962799</v>
+        <v>-15.80628623070157</v>
       </c>
       <c r="I31" s="27" t="n">
-        <v>43.49552077853176</v>
+        <v>-14.66774262222709</v>
       </c>
       <c r="J31" s="27" t="n">
-        <v>42.66214229068691</v>
+        <v>-17.27889521019694</v>
       </c>
       <c r="K31" s="27" t="n">
-        <v>43.12019458481103</v>
+        <v>-18.63056337711566</v>
       </c>
       <c r="L31" s="27" t="n">
-        <v>44.07482615361154</v>
+        <v>-37.74335566457027</v>
       </c>
       <c r="M31" s="27" t="n">
-        <v>44.83368613720742</v>
+        <v>-37.77500951496649</v>
       </c>
       <c r="N31" s="27" t="n">
-        <v>45.4220025635795</v>
+        <v>-37.91133076975383</v>
       </c>
       <c r="O31" s="27" t="n">
-        <v>48.07845014847756</v>
+        <v>-32.69078062075321</v>
       </c>
     </row>
     <row r="32">
@@ -20390,40 +20390,40 @@
         </is>
       </c>
       <c r="D33" s="27" t="n">
-        <v>215.4314299379372</v>
+        <v>-1.886690273654702</v>
       </c>
       <c r="E33" s="27" t="n">
-        <v>155.6361626479737</v>
+        <v>-9.132379493895687</v>
       </c>
       <c r="F33" s="27" t="n">
-        <v>167.857576417929</v>
+        <v>-11.0103271872919</v>
       </c>
       <c r="G33" s="27" t="n">
-        <v>160.3665782841628</v>
+        <v>-51.43794439586622</v>
       </c>
       <c r="H33" s="27" t="n">
-        <v>171.4972066453465</v>
+        <v>-73.0669829659379</v>
       </c>
       <c r="I33" s="27" t="n">
-        <v>182.2665333434209</v>
+        <v>-72.60547142011055</v>
       </c>
       <c r="J33" s="27" t="n">
-        <v>192.6789386253032</v>
+        <v>-91.3856402328188</v>
       </c>
       <c r="K33" s="27" t="n">
-        <v>209.1742670777509</v>
+        <v>-105.0044209155354</v>
       </c>
       <c r="L33" s="27" t="n">
-        <v>228.2513197993178</v>
+        <v>-195.4623873970131</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>246.2984513172142</v>
+        <v>-207.5208876101749</v>
       </c>
       <c r="N33" s="27" t="n">
-        <v>263.2061469632826</v>
+        <v>-219.6841780410283</v>
       </c>
       <c r="O33" s="27" t="n">
-        <v>304.0715146426295</v>
+        <v>-206.752404611718</v>
       </c>
     </row>
     <row r="34">
@@ -20443,40 +20443,40 @@
         </is>
       </c>
       <c r="D34" s="27" t="n">
-        <v>148.0278569603547</v>
+        <v>-69.29026325123716</v>
       </c>
       <c r="E34" s="27" t="n">
-        <v>155.6361626479737</v>
+        <v>-88.20148623002081</v>
       </c>
       <c r="F34" s="27" t="n">
-        <v>167.857576417929</v>
+        <v>-89.2896173090262</v>
       </c>
       <c r="G34" s="27" t="n">
-        <v>160.3665782841628</v>
+        <v>-128.9339911406105</v>
       </c>
       <c r="H34" s="27" t="n">
-        <v>171.4972066453465</v>
+        <v>-149.7889436962052</v>
       </c>
       <c r="I34" s="27" t="n">
-        <v>182.2665333434209</v>
+        <v>-148.5597885658774</v>
       </c>
       <c r="J34" s="27" t="n">
-        <v>192.6789386253032</v>
+        <v>-168.632384772284</v>
       </c>
       <c r="K34" s="27" t="n">
-        <v>209.1742670777509</v>
+        <v>-183.5223595714671</v>
       </c>
       <c r="L34" s="27" t="n">
-        <v>228.2513197993178</v>
+        <v>-195.4623873970131</v>
       </c>
       <c r="M34" s="27" t="n">
-        <v>246.2984513172142</v>
+        <v>-207.5208876101749</v>
       </c>
       <c r="N34" s="27" t="n">
-        <v>263.2061469632826</v>
+        <v>-219.6841780410283</v>
       </c>
       <c r="O34" s="27" t="n">
-        <v>304.0715146426295</v>
+        <v>-206.752404611718</v>
       </c>
     </row>
     <row r="35">
@@ -20549,40 +20549,40 @@
         </is>
       </c>
       <c r="D36" s="27" t="n">
-        <v>-41.44779994889932</v>
+        <v>0</v>
       </c>
       <c r="E36" s="27" t="n">
-        <v>-43.57812554143263</v>
+        <v>0</v>
       </c>
       <c r="F36" s="27" t="n">
-        <v>-47.00012139702012</v>
+        <v>0</v>
       </c>
       <c r="G36" s="27" t="n">
-        <v>-44.90264191956558</v>
+        <v>0</v>
       </c>
       <c r="H36" s="27" t="n">
-        <v>-48.01921786069701</v>
+        <v>0</v>
       </c>
       <c r="I36" s="27" t="n">
-        <v>-51.03462933615786</v>
+        <v>0</v>
       </c>
       <c r="J36" s="27" t="n">
-        <v>-53.9501028150849</v>
+        <v>0</v>
       </c>
       <c r="K36" s="27" t="n">
-        <v>-58.56879478177026</v>
+        <v>0</v>
       </c>
       <c r="L36" s="27" t="n">
-        <v>-63.91036954380898</v>
+        <v>0</v>
       </c>
       <c r="M36" s="27" t="n">
-        <v>-68.96356636881997</v>
+        <v>0</v>
       </c>
       <c r="N36" s="27" t="n">
-        <v>-73.69772114971913</v>
+        <v>0</v>
       </c>
       <c r="O36" s="27" t="n">
-        <v>-85.14002409993626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -20602,40 +20602,40 @@
         </is>
       </c>
       <c r="D37" s="27" t="n">
-        <v>0</v>
+        <v>-69.29026325123716</v>
       </c>
       <c r="E37" s="27" t="n">
-        <v>0</v>
+        <v>-157.491749481258</v>
       </c>
       <c r="F37" s="27" t="n">
-        <v>0</v>
+        <v>-246.7813667902842</v>
       </c>
       <c r="G37" s="27" t="n">
-        <v>0</v>
+        <v>-375.7153579308947</v>
       </c>
       <c r="H37" s="27" t="n">
-        <v>0</v>
+        <v>-525.5043016270999</v>
       </c>
       <c r="I37" s="27" t="n">
-        <v>0</v>
+        <v>-674.0640901929773</v>
       </c>
       <c r="J37" s="27" t="n">
-        <v>0</v>
+        <v>-842.6964749652614</v>
       </c>
       <c r="K37" s="27" t="n">
-        <v>0</v>
+        <v>-1026.218834536729</v>
       </c>
       <c r="L37" s="27" t="n">
-        <v>0</v>
+        <v>-1221.681221933742</v>
       </c>
       <c r="M37" s="27" t="n">
-        <v>0</v>
+        <v>-1429.202109543917</v>
       </c>
       <c r="N37" s="27" t="n">
-        <v>0</v>
+        <v>-1648.886287584945</v>
       </c>
       <c r="O37" s="27" t="n">
-        <v>0</v>
+        <v>-1855.638692196663</v>
       </c>
     </row>
     <row r="38">
@@ -20655,40 +20655,40 @@
         </is>
       </c>
       <c r="D38" s="27" t="n">
-        <v>173.9836299890379</v>
+        <v>-1.886690273654702</v>
       </c>
       <c r="E38" s="27" t="n">
-        <v>112.0580371065411</v>
+        <v>-9.132379493895687</v>
       </c>
       <c r="F38" s="27" t="n">
-        <v>120.8574550209089</v>
+        <v>-11.0103271872919</v>
       </c>
       <c r="G38" s="27" t="n">
-        <v>115.4639363645972</v>
+        <v>-51.43794439586622</v>
       </c>
       <c r="H38" s="27" t="n">
-        <v>123.4779887846495</v>
+        <v>-73.0669829659379</v>
       </c>
       <c r="I38" s="27" t="n">
-        <v>131.2319040072631</v>
+        <v>-72.60547142011055</v>
       </c>
       <c r="J38" s="27" t="n">
-        <v>138.7288358102183</v>
+        <v>-91.3856402328188</v>
       </c>
       <c r="K38" s="27" t="n">
-        <v>150.6054722959807</v>
+        <v>-105.0044209155354</v>
       </c>
       <c r="L38" s="27" t="n">
-        <v>164.3409502555088</v>
+        <v>-195.4623873970131</v>
       </c>
       <c r="M38" s="27" t="n">
-        <v>177.3348849483942</v>
+        <v>-207.5208876101749</v>
       </c>
       <c r="N38" s="27" t="n">
-        <v>189.5084258135635</v>
+        <v>-219.6841780410283</v>
       </c>
       <c r="O38" s="27" t="n">
-        <v>218.9314905426932</v>
+        <v>-206.752404611718</v>
       </c>
     </row>
     <row r="39">
@@ -20708,40 +20708,40 @@
         </is>
       </c>
       <c r="D39" s="27" t="n">
-        <v>51.31485099076573</v>
+        <v>-0.5564617215103402</v>
       </c>
       <c r="E39" s="27" t="n">
-        <v>37.33925239519537</v>
+        <v>-2.408474121773978</v>
       </c>
       <c r="F39" s="27" t="n">
-        <v>35.94066318251527</v>
+        <v>-2.655979203147908</v>
       </c>
       <c r="G39" s="27" t="n">
-        <v>32.86821999121569</v>
+        <v>-11.99608035172657</v>
       </c>
       <c r="H39" s="27" t="n">
-        <v>32.02700268213215</v>
+        <v>-15.80628623070157</v>
       </c>
       <c r="I39" s="27" t="n">
-        <v>31.31677496054287</v>
+        <v>-14.66774262222709</v>
       </c>
       <c r="J39" s="27" t="n">
-        <v>30.71674244929457</v>
+        <v>-17.27889521019694</v>
       </c>
       <c r="K39" s="27" t="n">
-        <v>31.04654010106394</v>
+        <v>-18.63056337711566</v>
       </c>
       <c r="L39" s="27" t="n">
-        <v>31.73387483060031</v>
+        <v>-37.74335566457027</v>
       </c>
       <c r="M39" s="27" t="n">
-        <v>32.28025401878934</v>
+        <v>-37.77500951496649</v>
       </c>
       <c r="N39" s="27" t="n">
-        <v>32.70384184577724</v>
+        <v>-37.91133076975383</v>
       </c>
       <c r="O39" s="27" t="n">
-        <v>34.61648410690385</v>
+        <v>-32.69078062075321</v>
       </c>
     </row>
     <row r="40">
@@ -20920,40 +20920,40 @@
         </is>
       </c>
       <c r="D43" s="27" t="n">
-        <v>748.2076566368021</v>
+        <v>572.3373363741096</v>
       </c>
       <c r="E43" s="27" t="n">
-        <v>578.6957967249322</v>
+        <v>202.5659531256778</v>
       </c>
       <c r="F43" s="27" t="n">
-        <v>429.9737103427275</v>
+        <v>-156.303205586462</v>
       </c>
       <c r="G43" s="27" t="n">
-        <v>287.7334893633554</v>
+        <v>-542.9413540710418</v>
       </c>
       <c r="H43" s="27" t="n">
-        <v>165.2590830225884</v>
+        <v>-938.6826928926635</v>
       </c>
       <c r="I43" s="27" t="n">
-        <v>62.17767250080223</v>
+        <v>-1321.55579598759</v>
       </c>
       <c r="J43" s="27" t="n">
-        <v>-29.7794436944084</v>
+        <v>-1720.874132765303</v>
       </c>
       <c r="K43" s="27" t="n">
-        <v>-106.3864533702505</v>
+        <v>-2131.608974308593</v>
       </c>
       <c r="L43" s="27" t="n">
-        <v>-158.1060405708589</v>
+        <v>-2543.131899161723</v>
       </c>
       <c r="M43" s="27" t="n">
-        <v>-185.7929360080335</v>
+        <v>-2955.674567157466</v>
       </c>
       <c r="N43" s="27" t="n">
-        <v>-190.3758846779557</v>
+        <v>-3369.45011968198</v>
       </c>
       <c r="O43" s="27" t="n">
-        <v>-190.3758846779557</v>
+        <v>-3683.810376368314</v>
       </c>
     </row>
     <row r="44">
@@ -20973,40 +20973,40 @@
         </is>
       </c>
       <c r="D44" s="27" t="n">
-        <v>748.2076566368021</v>
+        <v>572.3373363741096</v>
       </c>
       <c r="E44" s="27" t="n">
-        <v>578.6957967249322</v>
+        <v>202.5659531256778</v>
       </c>
       <c r="F44" s="27" t="n">
-        <v>429.9737103427275</v>
+        <v>-156.303205586462</v>
       </c>
       <c r="G44" s="27" t="n">
-        <v>287.7334893633554</v>
+        <v>-542.9413540710418</v>
       </c>
       <c r="H44" s="27" t="n">
-        <v>165.2590830225884</v>
+        <v>-938.6826928926635</v>
       </c>
       <c r="I44" s="27" t="n">
-        <v>62.17767250080223</v>
+        <v>-1321.55579598759</v>
       </c>
       <c r="J44" s="27" t="n">
-        <v>-29.7794436944084</v>
+        <v>-1720.874132765303</v>
       </c>
       <c r="K44" s="27" t="n">
-        <v>-106.3864533702505</v>
+        <v>-2131.608974308593</v>
       </c>
       <c r="L44" s="27" t="n">
-        <v>-158.1060405708589</v>
+        <v>-2543.131899161723</v>
       </c>
       <c r="M44" s="27" t="n">
-        <v>-185.7929360080335</v>
+        <v>-2955.674567157466</v>
       </c>
       <c r="N44" s="27" t="n">
-        <v>-190.3758846779557</v>
+        <v>-3369.45011968198</v>
       </c>
       <c r="O44" s="27" t="n">
-        <v>-190.3758846779557</v>
+        <v>-3683.810376368314</v>
       </c>
     </row>
     <row r="45">
@@ -21132,40 +21132,40 @@
         </is>
       </c>
       <c r="D47" s="27" t="n">
-        <v>994.8549335956259</v>
+        <v>818.9846133329333</v>
       </c>
       <c r="E47" s="27" t="n">
-        <v>1106.912970702167</v>
+        <v>730.7831271029125</v>
       </c>
       <c r="F47" s="27" t="n">
-        <v>1227.770425723076</v>
+        <v>641.4935097938865</v>
       </c>
       <c r="G47" s="27" t="n">
-        <v>1343.234362087673</v>
+        <v>512.559518653276</v>
       </c>
       <c r="H47" s="27" t="n">
-        <v>1466.712350872323</v>
+        <v>362.7705749570707</v>
       </c>
       <c r="I47" s="27" t="n">
-        <v>1597.944254879586</v>
+        <v>214.2107863911933</v>
       </c>
       <c r="J47" s="27" t="n">
-        <v>1736.673090689804</v>
+        <v>45.57840161890931</v>
       </c>
       <c r="K47" s="27" t="n">
-        <v>1887.278562985784</v>
+        <v>-137.9439579525579</v>
       </c>
       <c r="L47" s="27" t="n">
-        <v>2051.619513241293</v>
+        <v>-333.4063453495705</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>2228.954398189687</v>
+        <v>-540.9272329597457</v>
       </c>
       <c r="N47" s="27" t="n">
-        <v>2418.462824003251</v>
+        <v>-760.6114110007734</v>
       </c>
       <c r="O47" s="27" t="n">
-        <v>2526.070676077867</v>
+        <v>-967.3638156124912</v>
       </c>
     </row>
     <row r="48">
@@ -21185,40 +21185,40 @@
         </is>
       </c>
       <c r="D48" s="27" t="n">
-        <v>451.5695289215911</v>
+        <v>275.6992086588986</v>
       </c>
       <c r="E48" s="27" t="n">
-        <v>563.6275660281322</v>
+        <v>266.5668291650028</v>
       </c>
       <c r="F48" s="27" t="n">
-        <v>684.4850210490412</v>
+        <v>255.556501977711</v>
       </c>
       <c r="G48" s="27" t="n">
-        <v>799.9489574136384</v>
+        <v>204.1185575818448</v>
       </c>
       <c r="H48" s="27" t="n">
-        <v>923.4269461982879</v>
+        <v>131.0515746159069</v>
       </c>
       <c r="I48" s="27" t="n">
-        <v>1054.658850205551</v>
+        <v>58.44610319579633</v>
       </c>
       <c r="J48" s="27" t="n">
-        <v>1193.387686015769</v>
+        <v>-32.93953703702246</v>
       </c>
       <c r="K48" s="27" t="n">
-        <v>1343.99315831175</v>
+        <v>-137.9439579525579</v>
       </c>
       <c r="L48" s="27" t="n">
-        <v>1508.334108567259</v>
+        <v>-333.406345349571</v>
       </c>
       <c r="M48" s="27" t="n">
-        <v>1685.668993515653</v>
+        <v>-540.9272329597459</v>
       </c>
       <c r="N48" s="27" t="n">
-        <v>1875.177419329216</v>
+        <v>-760.6114110007742</v>
       </c>
       <c r="O48" s="27" t="n">
-        <v>1982.785271403832</v>
+        <v>-967.3638156124922</v>
       </c>
     </row>
     <row r="49">
@@ -21291,40 +21291,40 @@
         </is>
       </c>
       <c r="D50" s="27" t="n">
-        <v>173.9836299890379</v>
+        <v>-1.886690273654702</v>
       </c>
       <c r="E50" s="27" t="n">
-        <v>112.0580371065411</v>
+        <v>-9.132379493895687</v>
       </c>
       <c r="F50" s="27" t="n">
-        <v>120.8574550209089</v>
+        <v>-11.0103271872919</v>
       </c>
       <c r="G50" s="27" t="n">
-        <v>115.4639363645972</v>
+        <v>-51.43794439586622</v>
       </c>
       <c r="H50" s="27" t="n">
-        <v>123.4779887846495</v>
+        <v>-73.0669829659379</v>
       </c>
       <c r="I50" s="27" t="n">
-        <v>131.2319040072631</v>
+        <v>-72.60547142011055</v>
       </c>
       <c r="J50" s="27" t="n">
-        <v>138.7288358102183</v>
+        <v>-91.3856402328188</v>
       </c>
       <c r="K50" s="27" t="n">
-        <v>150.6054722959807</v>
+        <v>-105.0044209155354</v>
       </c>
       <c r="L50" s="27" t="n">
-        <v>164.3409502555088</v>
+        <v>-195.4623873970131</v>
       </c>
       <c r="M50" s="27" t="n">
-        <v>177.3348849483942</v>
+        <v>-207.5208876101749</v>
       </c>
       <c r="N50" s="27" t="n">
-        <v>189.5084258135635</v>
+        <v>-219.6841780410283</v>
       </c>
       <c r="O50" s="27" t="n">
-        <v>107.6078520746158</v>
+        <v>-206.752404611718</v>
       </c>
     </row>
     <row r="51">
@@ -21347,37 +21347,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="27" t="n">
-        <v>173.9836299890379</v>
+        <v>-1.886690273654702</v>
       </c>
       <c r="F51" s="27" t="n">
-        <v>286.041667095579</v>
+        <v>-11.01906976755039</v>
       </c>
       <c r="G51" s="27" t="n">
-        <v>406.8991221164879</v>
+        <v>-22.02939695484228</v>
       </c>
       <c r="H51" s="27" t="n">
-        <v>522.3630584810851</v>
+        <v>-73.46734135070849</v>
       </c>
       <c r="I51" s="27" t="n">
-        <v>645.8410472657346</v>
+        <v>-146.5343243166464</v>
       </c>
       <c r="J51" s="27" t="n">
-        <v>777.0729512729977</v>
+        <v>-219.139795736757</v>
       </c>
       <c r="K51" s="27" t="n">
-        <v>915.801787083216</v>
+        <v>-310.5254359695758</v>
       </c>
       <c r="L51" s="27" t="n">
-        <v>1066.407259379197</v>
+        <v>-415.5298568851112</v>
       </c>
       <c r="M51" s="27" t="n">
-        <v>1230.748209634705</v>
+        <v>-610.9922442821243</v>
       </c>
       <c r="N51" s="27" t="n">
-        <v>1408.083094583099</v>
+        <v>-818.5131318922992</v>
       </c>
       <c r="O51" s="27" t="n">
-        <v>1597.591520396663</v>
+        <v>-1038.197309933327</v>
       </c>
     </row>
     <row r="52">
@@ -21400,37 +21400,37 @@
         <v>543.2854046740348</v>
       </c>
       <c r="E52" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>464.2162979379096</v>
       </c>
       <c r="F52" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>385.9370078161753</v>
       </c>
       <c r="G52" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>308.440961071431</v>
       </c>
       <c r="H52" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>231.7190003411637</v>
       </c>
       <c r="I52" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>155.7646831953968</v>
       </c>
       <c r="J52" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>78.51793865593159</v>
       </c>
       <c r="K52" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="L52" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="M52" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="N52" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="O52" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
     </row>
     <row r="53">
@@ -21453,37 +21453,37 @@
         <v>543.2854046740348</v>
       </c>
       <c r="E53" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>464.2162979379096</v>
       </c>
       <c r="F53" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>385.9370078161753</v>
       </c>
       <c r="G53" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>308.440961071431</v>
       </c>
       <c r="H53" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>231.7190003411637</v>
       </c>
       <c r="I53" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>155.7646831953968</v>
       </c>
       <c r="J53" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>78.51793865593159</v>
       </c>
       <c r="K53" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="L53" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="M53" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="N53" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="O53" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
     </row>
     <row r="54">
@@ -21715,40 +21715,40 @@
         </is>
       </c>
       <c r="D58" s="27" t="n">
-        <v>994.8549335956259</v>
+        <v>818.9846133329333</v>
       </c>
       <c r="E58" s="27" t="n">
-        <v>1106.912970702167</v>
+        <v>730.7831271029124</v>
       </c>
       <c r="F58" s="27" t="n">
-        <v>1227.770425723076</v>
+        <v>641.4935097938862</v>
       </c>
       <c r="G58" s="27" t="n">
-        <v>1343.234362087673</v>
+        <v>512.5595186532757</v>
       </c>
       <c r="H58" s="27" t="n">
-        <v>1466.712350872323</v>
+        <v>362.7705749570706</v>
       </c>
       <c r="I58" s="27" t="n">
-        <v>1597.944254879586</v>
+        <v>214.2107863911931</v>
       </c>
       <c r="J58" s="27" t="n">
-        <v>1736.673090689804</v>
+        <v>45.57840161890913</v>
       </c>
       <c r="K58" s="27" t="n">
-        <v>1887.278562985785</v>
+        <v>-137.943957952558</v>
       </c>
       <c r="L58" s="27" t="n">
-        <v>2051.619513241294</v>
+        <v>-333.406345349571</v>
       </c>
       <c r="M58" s="27" t="n">
-        <v>2228.954398189688</v>
+        <v>-540.9272329597459</v>
       </c>
       <c r="N58" s="27" t="n">
-        <v>2418.462824003251</v>
+        <v>-760.6114110007743</v>
       </c>
       <c r="O58" s="27" t="n">
-        <v>2526.070676077867</v>
+        <v>-967.3638156124923</v>
       </c>
     </row>
     <row r="59">
@@ -21771,37 +21771,37 @@
         <v>0</v>
       </c>
       <c r="E59" s="27" t="n">
-        <v>0</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="F59" s="27" t="n">
-        <v>0</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="G59" s="27" t="n">
-        <v>0</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="H59" s="27" t="n">
-        <v>0</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="I59" s="27" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>1.989519660128281e-13</v>
       </c>
       <c r="J59" s="27" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>1.84741111297626e-13</v>
       </c>
       <c r="K59" s="27" t="n">
-        <v>-6.821210263296962e-13</v>
+        <v>1.13686837721616e-13</v>
       </c>
       <c r="L59" s="27" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>5.115907697472721e-13</v>
       </c>
       <c r="M59" s="27" t="n">
-        <v>-4.547473508864641e-13</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="N59" s="27" t="n">
-        <v>0</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="O59" s="27" t="n">
-        <v>4.547473508864641e-13</v>
+        <v>1.13686837721616e-12</v>
       </c>
     </row>
     <row r="60">
@@ -21874,40 +21874,40 @@
         </is>
       </c>
       <c r="D61" s="27" t="n">
-        <v>155.7473651062025</v>
+        <v>-61.5707551053894</v>
       </c>
       <c r="E61" s="27" t="n">
-        <v>172.4563003574762</v>
+        <v>-71.38134852051837</v>
       </c>
       <c r="F61" s="27" t="n">
-        <v>193.6874693954496</v>
+        <v>-63.45972433150565</v>
       </c>
       <c r="G61" s="27" t="n">
-        <v>195.1160609770213</v>
+        <v>-94.18450844775204</v>
       </c>
       <c r="H61" s="27" t="n">
-        <v>215.0772151563895</v>
+        <v>-106.2089351851622</v>
       </c>
       <c r="I61" s="27" t="n">
-        <v>234.5886984144667</v>
+        <v>-96.23762349483168</v>
       </c>
       <c r="J61" s="27" t="n">
-        <v>253.5058130221277</v>
+        <v>-107.8055103754596</v>
       </c>
       <c r="K61" s="27" t="n">
-        <v>278.2718284265944</v>
+        <v>-114.4247982226237</v>
       </c>
       <c r="L61" s="27" t="n">
-        <v>305.5368252306601</v>
+        <v>-118.1768819656708</v>
       </c>
       <c r="M61" s="27" t="n">
-        <v>331.6900533902303</v>
+        <v>-122.1292855371588</v>
       </c>
       <c r="N61" s="27" t="n">
-        <v>356.6227331947959</v>
+        <v>-126.2675918095151</v>
       </c>
       <c r="O61" s="27" t="n">
-        <v>403.3809372949113</v>
+        <v>-107.4429819594362</v>
       </c>
     </row>
     <row r="62">
@@ -21927,40 +21927,40 @@
         </is>
       </c>
       <c r="D62" s="27" t="n">
-        <v>-41.44779994889932</v>
+        <v>0</v>
       </c>
       <c r="E62" s="27" t="n">
-        <v>-43.57812554143263</v>
+        <v>0</v>
       </c>
       <c r="F62" s="27" t="n">
-        <v>-47.00012139702012</v>
+        <v>0</v>
       </c>
       <c r="G62" s="27" t="n">
-        <v>-44.90264191956558</v>
+        <v>0</v>
       </c>
       <c r="H62" s="27" t="n">
-        <v>-48.01921786069701</v>
+        <v>0</v>
       </c>
       <c r="I62" s="27" t="n">
-        <v>-51.03462933615786</v>
+        <v>0</v>
       </c>
       <c r="J62" s="27" t="n">
-        <v>-53.9501028150849</v>
+        <v>0</v>
       </c>
       <c r="K62" s="27" t="n">
-        <v>-58.56879478177026</v>
+        <v>0</v>
       </c>
       <c r="L62" s="27" t="n">
-        <v>-63.91036954380898</v>
+        <v>0</v>
       </c>
       <c r="M62" s="27" t="n">
-        <v>-68.96356636881997</v>
+        <v>0</v>
       </c>
       <c r="N62" s="27" t="n">
-        <v>-73.69772114971913</v>
+        <v>0</v>
       </c>
       <c r="O62" s="27" t="n">
-        <v>-85.14002409993626</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -22033,40 +22033,40 @@
         </is>
       </c>
       <c r="D64" s="27" t="n">
-        <v>114.2995651573031</v>
+        <v>-61.5707551053894</v>
       </c>
       <c r="E64" s="27" t="n">
-        <v>128.8781748160435</v>
+        <v>-71.38134852051837</v>
       </c>
       <c r="F64" s="27" t="n">
-        <v>146.6873479984295</v>
+        <v>-63.45972433150565</v>
       </c>
       <c r="G64" s="27" t="n">
-        <v>150.2134190574557</v>
+        <v>-94.18450844775204</v>
       </c>
       <c r="H64" s="27" t="n">
-        <v>167.0579972956925</v>
+        <v>-106.2089351851622</v>
       </c>
       <c r="I64" s="27" t="n">
-        <v>183.5540690783088</v>
+        <v>-96.23762349483168</v>
       </c>
       <c r="J64" s="27" t="n">
-        <v>199.5557102070428</v>
+        <v>-107.8055103754596</v>
       </c>
       <c r="K64" s="27" t="n">
-        <v>219.7030336448241</v>
+        <v>-114.4247982226237</v>
       </c>
       <c r="L64" s="27" t="n">
-        <v>241.6264556868511</v>
+        <v>-118.1768819656708</v>
       </c>
       <c r="M64" s="27" t="n">
-        <v>262.7264870214104</v>
+        <v>-122.1292855371588</v>
       </c>
       <c r="N64" s="27" t="n">
-        <v>282.9250120450768</v>
+        <v>-126.2675918095151</v>
       </c>
       <c r="O64" s="27" t="n">
-        <v>318.2409131949751</v>
+        <v>-107.4429819594362</v>
       </c>
     </row>
     <row r="65">
@@ -22192,40 +22192,40 @@
         </is>
       </c>
       <c r="D67" s="27" t="n">
-        <v>-140.0672199473684</v>
+        <v>-315.937540210061</v>
       </c>
       <c r="E67" s="27" t="n">
-        <v>-169.5118599118699</v>
+        <v>-369.7713832484318</v>
       </c>
       <c r="F67" s="27" t="n">
-        <v>-148.7220863822046</v>
+        <v>-358.8691587121397</v>
       </c>
       <c r="G67" s="27" t="n">
-        <v>-142.2402209793722</v>
+        <v>-386.6381484845799</v>
       </c>
       <c r="H67" s="27" t="n">
-        <v>-122.474406340767</v>
+        <v>-395.7413388216216</v>
       </c>
       <c r="I67" s="27" t="n">
-        <v>-103.0814105217862</v>
+        <v>-382.8731030949266</v>
       </c>
       <c r="J67" s="27" t="n">
-        <v>-91.95711619521063</v>
+        <v>-399.3183367777129</v>
       </c>
       <c r="K67" s="27" t="n">
-        <v>-76.60700967584214</v>
+        <v>-410.7348415432899</v>
       </c>
       <c r="L67" s="27" t="n">
-        <v>-51.71958720060837</v>
+        <v>-411.5229248531302</v>
       </c>
       <c r="M67" s="27" t="n">
-        <v>-27.68689543717454</v>
+        <v>-412.5426679957437</v>
       </c>
       <c r="N67" s="27" t="n">
-        <v>-4.582948669922246</v>
+        <v>-413.7755525245141</v>
       </c>
       <c r="O67" s="27" t="n">
-        <v>111.3236384680775</v>
+        <v>-314.3602566863339</v>
       </c>
     </row>
     <row r="68">
@@ -22490,7 +22490,7 @@
         <v>0</v>
       </c>
       <c r="O72" s="27" t="n">
-        <v>-111.3236384680775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -22596,7 +22596,7 @@
         <v>0</v>
       </c>
       <c r="O74" s="27" t="n">
-        <v>-111.3236384680775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -22616,40 +22616,40 @@
         </is>
       </c>
       <c r="D75" s="27" t="n">
-        <v>748.2076566368021</v>
+        <v>572.3373363741096</v>
       </c>
       <c r="E75" s="27" t="n">
-        <v>-169.5118599118699</v>
+        <v>-369.7713832484318</v>
       </c>
       <c r="F75" s="27" t="n">
-        <v>-148.7220863822046</v>
+        <v>-358.8691587121397</v>
       </c>
       <c r="G75" s="27" t="n">
-        <v>-142.2402209793722</v>
+        <v>-386.6381484845799</v>
       </c>
       <c r="H75" s="27" t="n">
-        <v>-122.474406340767</v>
+        <v>-395.7413388216216</v>
       </c>
       <c r="I75" s="27" t="n">
-        <v>-103.0814105217862</v>
+        <v>-382.8731030949266</v>
       </c>
       <c r="J75" s="27" t="n">
-        <v>-91.95711619521063</v>
+        <v>-399.3183367777129</v>
       </c>
       <c r="K75" s="27" t="n">
-        <v>-76.60700967584214</v>
+        <v>-410.7348415432899</v>
       </c>
       <c r="L75" s="27" t="n">
-        <v>-51.71958720060837</v>
+        <v>-411.5229248531302</v>
       </c>
       <c r="M75" s="27" t="n">
-        <v>-27.68689543717454</v>
+        <v>-412.5426679957437</v>
       </c>
       <c r="N75" s="27" t="n">
-        <v>-4.582948669922246</v>
+        <v>-413.7755525245141</v>
       </c>
       <c r="O75" s="27" t="n">
-        <v>0</v>
+        <v>-314.3602566863339</v>
       </c>
     </row>
     <row r="76">
@@ -22672,37 +22672,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="27" t="n">
-        <v>748.2076566368021</v>
+        <v>572.3373363741096</v>
       </c>
       <c r="F76" s="27" t="n">
-        <v>578.6957967249322</v>
+        <v>202.5659531256778</v>
       </c>
       <c r="G76" s="27" t="n">
-        <v>429.9737103427275</v>
+        <v>-156.303205586462</v>
       </c>
       <c r="H76" s="27" t="n">
-        <v>287.7334893633554</v>
+        <v>-542.9413540710418</v>
       </c>
       <c r="I76" s="27" t="n">
-        <v>165.2590830225884</v>
+        <v>-938.6826928926635</v>
       </c>
       <c r="J76" s="27" t="n">
-        <v>62.17767250080223</v>
+        <v>-1321.55579598759</v>
       </c>
       <c r="K76" s="27" t="n">
-        <v>-29.7794436944084</v>
+        <v>-1720.874132765303</v>
       </c>
       <c r="L76" s="27" t="n">
-        <v>-106.3864533702505</v>
+        <v>-2131.608974308593</v>
       </c>
       <c r="M76" s="27" t="n">
-        <v>-158.1060405708589</v>
+        <v>-2543.131899161723</v>
       </c>
       <c r="N76" s="27" t="n">
-        <v>-185.7929360080335</v>
+        <v>-2955.674567157466</v>
       </c>
       <c r="O76" s="27" t="n">
-        <v>-190.3758846779557</v>
+        <v>-3369.45011968198</v>
       </c>
     </row>
     <row r="77">
@@ -22722,40 +22722,40 @@
         </is>
       </c>
       <c r="D77" s="27" t="n">
-        <v>748.2076566368021</v>
+        <v>572.3373363741096</v>
       </c>
       <c r="E77" s="27" t="n">
-        <v>-169.5118599118699</v>
+        <v>-369.7713832484318</v>
       </c>
       <c r="F77" s="27" t="n">
-        <v>-148.7220863822046</v>
+        <v>-358.8691587121397</v>
       </c>
       <c r="G77" s="27" t="n">
-        <v>-142.2402209793722</v>
+        <v>-386.6381484845799</v>
       </c>
       <c r="H77" s="27" t="n">
-        <v>-122.474406340767</v>
+        <v>-395.7413388216216</v>
       </c>
       <c r="I77" s="27" t="n">
-        <v>-103.0814105217862</v>
+        <v>-382.8731030949266</v>
       </c>
       <c r="J77" s="27" t="n">
-        <v>-91.95711619521063</v>
+        <v>-399.3183367777129</v>
       </c>
       <c r="K77" s="27" t="n">
-        <v>-76.60700967584214</v>
+        <v>-410.7348415432899</v>
       </c>
       <c r="L77" s="27" t="n">
-        <v>-51.71958720060837</v>
+        <v>-411.5229248531302</v>
       </c>
       <c r="M77" s="27" t="n">
-        <v>-27.68689543717454</v>
+        <v>-412.5426679957437</v>
       </c>
       <c r="N77" s="27" t="n">
-        <v>-4.582948669922246</v>
+        <v>-413.7755525245141</v>
       </c>
       <c r="O77" s="27" t="n">
-        <v>0</v>
+        <v>-314.3602566863339</v>
       </c>
     </row>
     <row r="78">
@@ -22775,40 +22775,40 @@
         </is>
       </c>
       <c r="D78" s="27" t="n">
-        <v>748.2076566368021</v>
+        <v>572.3373363741096</v>
       </c>
       <c r="E78" s="27" t="n">
-        <v>578.6957967249322</v>
+        <v>202.5659531256778</v>
       </c>
       <c r="F78" s="27" t="n">
-        <v>429.9737103427275</v>
+        <v>-156.303205586462</v>
       </c>
       <c r="G78" s="27" t="n">
-        <v>287.7334893633554</v>
+        <v>-542.9413540710418</v>
       </c>
       <c r="H78" s="27" t="n">
-        <v>165.2590830225884</v>
+        <v>-938.6826928926635</v>
       </c>
       <c r="I78" s="27" t="n">
-        <v>62.17767250080223</v>
+        <v>-1321.55579598759</v>
       </c>
       <c r="J78" s="27" t="n">
-        <v>-29.7794436944084</v>
+        <v>-1720.874132765303</v>
       </c>
       <c r="K78" s="27" t="n">
-        <v>-106.3864533702505</v>
+        <v>-2131.608974308593</v>
       </c>
       <c r="L78" s="27" t="n">
-        <v>-158.1060405708589</v>
+        <v>-2543.131899161723</v>
       </c>
       <c r="M78" s="27" t="n">
-        <v>-185.7929360080335</v>
+        <v>-2955.674567157466</v>
       </c>
       <c r="N78" s="27" t="n">
-        <v>-190.3758846779557</v>
+        <v>-3369.45011968198</v>
       </c>
       <c r="O78" s="27" t="n">
-        <v>-190.3758846779557</v>
+        <v>-3683.810376368314</v>
       </c>
     </row>
     <row r="79">
@@ -22937,25 +22937,25 @@
         <v>75.02311381518344</v>
       </c>
       <c r="E81" s="27" t="n">
-        <v>99.42759222458581</v>
+        <v>78.69413194204114</v>
       </c>
       <c r="F81" s="27" t="n">
-        <v>87.84903653791892</v>
+        <v>71.26049033622147</v>
       </c>
       <c r="G81" s="27" t="n">
-        <v>83.2505012440366</v>
+        <v>68.20446279961857</v>
       </c>
       <c r="H81" s="27" t="n">
-        <v>75.09723116725918</v>
+        <v>62.63337911563043</v>
       </c>
       <c r="I81" s="27" t="n">
-        <v>68.40180273423941</v>
+        <v>57.90604149990125</v>
       </c>
       <c r="J81" s="27" t="n">
-        <v>64.54551684924029</v>
+        <v>55.11828299282355</v>
       </c>
       <c r="K81" s="27" t="n">
-        <v>61.08278472261443</v>
+        <v>52.57324399514695</v>
       </c>
       <c r="L81" s="27" t="n">
         <v>56.64447353242991</v>
@@ -23756,37 +23756,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="29" t="n">
-        <v>451.5695289215911</v>
+        <v>275.6992086588986</v>
       </c>
       <c r="F96" s="29" t="n">
-        <v>563.6275660281323</v>
+        <v>266.5668291650028</v>
       </c>
       <c r="G96" s="29" t="n">
-        <v>684.4850210490412</v>
+        <v>255.556501977711</v>
       </c>
       <c r="H96" s="29" t="n">
-        <v>799.9489574136384</v>
+        <v>204.1185575818447</v>
       </c>
       <c r="I96" s="29" t="n">
-        <v>923.4269461982879</v>
+        <v>131.0515746159068</v>
       </c>
       <c r="J96" s="29" t="n">
-        <v>1054.658850205551</v>
+        <v>58.44610319579627</v>
       </c>
       <c r="K96" s="29" t="n">
-        <v>1193.387686015769</v>
+        <v>-32.93953703702253</v>
       </c>
       <c r="L96" s="29" t="n">
-        <v>1343.99315831175</v>
+        <v>-137.943957952558</v>
       </c>
       <c r="M96" s="29" t="n">
-        <v>1508.334108567259</v>
+        <v>-333.406345349571</v>
       </c>
       <c r="N96" s="29" t="n">
-        <v>1685.668993515653</v>
+        <v>-540.927232959746</v>
       </c>
       <c r="O96" s="29" t="n">
-        <v>1875.177419329216</v>
+        <v>-760.6114110007743</v>
       </c>
     </row>
     <row r="97">
@@ -23859,40 +23859,40 @@
         </is>
       </c>
       <c r="D98" s="29" t="n">
-        <v>173.9836299890379</v>
+        <v>-1.886690273654702</v>
       </c>
       <c r="E98" s="29" t="n">
-        <v>112.0580371065411</v>
+        <v>-9.132379493895687</v>
       </c>
       <c r="F98" s="29" t="n">
-        <v>120.8574550209089</v>
+        <v>-11.0103271872919</v>
       </c>
       <c r="G98" s="29" t="n">
-        <v>115.4639363645972</v>
+        <v>-51.43794439586622</v>
       </c>
       <c r="H98" s="29" t="n">
-        <v>123.4779887846495</v>
+        <v>-73.0669829659379</v>
       </c>
       <c r="I98" s="29" t="n">
-        <v>131.2319040072631</v>
+        <v>-72.60547142011055</v>
       </c>
       <c r="J98" s="29" t="n">
-        <v>138.7288358102183</v>
+        <v>-91.3856402328188</v>
       </c>
       <c r="K98" s="29" t="n">
-        <v>150.6054722959807</v>
+        <v>-105.0044209155354</v>
       </c>
       <c r="L98" s="29" t="n">
-        <v>164.3409502555088</v>
+        <v>-195.4623873970131</v>
       </c>
       <c r="M98" s="29" t="n">
-        <v>177.3348849483942</v>
+        <v>-207.5208876101749</v>
       </c>
       <c r="N98" s="29" t="n">
-        <v>189.5084258135635</v>
+        <v>-219.6841780410283</v>
       </c>
       <c r="O98" s="29" t="n">
-        <v>218.9314905426932</v>
+        <v>-206.752404611718</v>
       </c>
     </row>
     <row r="99">
@@ -23945,7 +23945,7 @@
         <v>0</v>
       </c>
       <c r="O99" s="29" t="n">
-        <v>111.3236384680775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -23965,40 +23965,40 @@
         </is>
       </c>
       <c r="D100" s="29" t="n">
-        <v>451.5695289215911</v>
+        <v>275.6992086588986</v>
       </c>
       <c r="E100" s="29" t="n">
-        <v>563.6275660281323</v>
+        <v>266.5668291650028</v>
       </c>
       <c r="F100" s="29" t="n">
-        <v>684.4850210490412</v>
+        <v>255.556501977711</v>
       </c>
       <c r="G100" s="29" t="n">
-        <v>799.9489574136384</v>
+        <v>204.1185575818447</v>
       </c>
       <c r="H100" s="29" t="n">
-        <v>923.4269461982879</v>
+        <v>131.0515746159068</v>
       </c>
       <c r="I100" s="29" t="n">
-        <v>1054.658850205551</v>
+        <v>58.44610319579627</v>
       </c>
       <c r="J100" s="29" t="n">
-        <v>1193.387686015769</v>
+        <v>-32.93953703702253</v>
       </c>
       <c r="K100" s="29" t="n">
-        <v>1343.99315831175</v>
+        <v>-137.943957952558</v>
       </c>
       <c r="L100" s="29" t="n">
-        <v>1508.334108567259</v>
+        <v>-333.406345349571</v>
       </c>
       <c r="M100" s="29" t="n">
-        <v>1685.668993515653</v>
+        <v>-540.927232959746</v>
       </c>
       <c r="N100" s="29" t="n">
-        <v>1875.177419329216</v>
+        <v>-760.6114110007743</v>
       </c>
       <c r="O100" s="29" t="n">
-        <v>2205.432548339987</v>
+        <v>-967.3638156124923</v>
       </c>
     </row>
     <row r="101">
@@ -24074,25 +24074,25 @@
         <v>-26.49857486300579</v>
       </c>
       <c r="E102" s="27" t="n">
-        <v>0</v>
+        <v>-26.49857486300579</v>
       </c>
       <c r="F102" s="27" t="n">
-        <v>0</v>
+        <v>-26.4985748630058</v>
       </c>
       <c r="G102" s="27" t="n">
-        <v>0</v>
+        <v>-26.49857486300579</v>
       </c>
       <c r="H102" s="27" t="n">
-        <v>0</v>
+        <v>-26.49857486300579</v>
       </c>
       <c r="I102" s="27" t="n">
-        <v>0</v>
+        <v>-26.4985748630058</v>
       </c>
       <c r="J102" s="27" t="n">
-        <v>0</v>
+        <v>-26.49857486300579</v>
       </c>
       <c r="K102" s="27" t="n">
-        <v>0</v>
+        <v>-26.4985748630058</v>
       </c>
       <c r="L102" s="27" t="n">
         <v>0</v>
@@ -24130,34 +24130,34 @@
         <v>543.2854046740348</v>
       </c>
       <c r="F103" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>464.2162979379096</v>
       </c>
       <c r="G103" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>385.9370078161753</v>
       </c>
       <c r="H103" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>308.440961071431</v>
       </c>
       <c r="I103" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>231.7190003411637</v>
       </c>
       <c r="J103" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>155.7646831953968</v>
       </c>
       <c r="K103" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>78.51793865593159</v>
       </c>
       <c r="L103" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="M103" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="N103" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="O103" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
     </row>
     <row r="104">
@@ -24233,25 +24233,25 @@
         <v>-67.40357297758246</v>
       </c>
       <c r="E105" s="27" t="n">
-        <v>0</v>
+        <v>-79.06910673612512</v>
       </c>
       <c r="F105" s="27" t="n">
-        <v>0</v>
+        <v>-78.27929012173431</v>
       </c>
       <c r="G105" s="27" t="n">
-        <v>0</v>
+        <v>-77.49604674474431</v>
       </c>
       <c r="H105" s="27" t="n">
-        <v>0</v>
+        <v>-76.72196073026731</v>
       </c>
       <c r="I105" s="27" t="n">
-        <v>0</v>
+        <v>-75.95431714576688</v>
       </c>
       <c r="J105" s="27" t="n">
-        <v>0</v>
+        <v>-77.24674453946521</v>
       </c>
       <c r="K105" s="27" t="n">
-        <v>0</v>
+        <v>-78.51793865593164</v>
       </c>
       <c r="L105" s="27" t="n">
         <v>0</v>
@@ -24339,37 +24339,37 @@
         <v>543.2854046740348</v>
       </c>
       <c r="E107" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>464.2162979379096</v>
       </c>
       <c r="F107" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>385.9370078161753</v>
       </c>
       <c r="G107" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>308.440961071431</v>
       </c>
       <c r="H107" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>231.7190003411637</v>
       </c>
       <c r="I107" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>155.7646831953968</v>
       </c>
       <c r="J107" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>78.51793865593159</v>
       </c>
       <c r="K107" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="L107" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="M107" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="N107" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
       <c r="O107" s="27" t="n">
-        <v>543.2854046740348</v>
+        <v>-5.684341886080801e-14</v>
       </c>
     </row>
     <row r="108">

--- a/backend/Rwanda/financial-statements-CleanStep.xlsx
+++ b/backend/Rwanda/financial-statements-CleanStep.xlsx
@@ -8552,7 +8552,7 @@
         <v>-413.3062700370729</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>-585.648016215231</v>
+        <v>-585.6480162152311</v>
       </c>
       <c r="I37" s="19" t="n">
         <v>-757.8400972777696</v>
@@ -8858,40 +8858,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>790.5134279083514</v>
+        <v>780.9216357955212</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>340.1639873859361</v>
+        <v>360.9436023552403</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>-99.22008122502609</v>
+        <v>-73.54858901300697</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>-570.5266608498788</v>
+        <v>-542.2731375622076</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>-1053.271048378483</v>
+        <v>-1022.717593583962</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>-1521.382779331801</v>
+        <v>-1484.573182071527</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>-2041.034459590087</v>
+        <v>-2002.235270548991</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>-2603.392407717703</v>
+        <v>-2562.0211337451</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>-3163.264924714042</v>
+        <v>-3117.224376768836</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>-3721.236802240418</v>
+        <v>-3670.442454295212</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>-4277.84161315703</v>
+        <v>-4222.413613137756</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>-4674.404073468322</v>
+        <v>-4614.485796775267</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -8911,40 +8911,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>790.5134279083514</v>
+        <v>758.2125399051102</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>340.1639873859361</v>
+        <v>334.6933886566102</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>-99.22008122502609</v>
+        <v>-104.1041561362946</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>-570.5266608498788</v>
+        <v>-575.1761019457692</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>-1053.271048378483</v>
+        <v>-1059.73156070725</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>-1521.382779331801</v>
+        <v>-1525.63785604413</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>-2041.034459590087</v>
+        <v>-2047.26716095995</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>-2603.392407717703</v>
+        <v>-2611.987383060168</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>-3163.264924714042</v>
+        <v>-3171.871834303083</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>-3721.236802240418</v>
+        <v>-3729.627251555487</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>-4277.84161315703</v>
+        <v>-4285.974818617208</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>-4674.404073468322</v>
+        <v>-4684.959544720472</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -8964,40 +8964,40 @@
         </is>
       </c>
       <c r="D45" s="18" t="n">
-        <v>0</v>
+        <v>22.70909589041096</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>0</v>
+        <v>26.25021369863014</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>0</v>
+        <v>30.55556712328767</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>0</v>
+        <v>32.90296438356165</v>
       </c>
       <c r="H45" s="18" t="n">
-        <v>0</v>
+        <v>37.01396712328768</v>
       </c>
       <c r="I45" s="18" t="n">
-        <v>0</v>
+        <v>41.06467397260274</v>
       </c>
       <c r="J45" s="18" t="n">
-        <v>0</v>
+        <v>45.0318904109589</v>
       </c>
       <c r="K45" s="18" t="n">
-        <v>0</v>
+        <v>49.9662493150685</v>
       </c>
       <c r="L45" s="18" t="n">
-        <v>0</v>
+        <v>54.64745753424658</v>
       </c>
       <c r="M45" s="18" t="n">
-        <v>0</v>
+        <v>59.18479726027397</v>
       </c>
       <c r="N45" s="18" t="n">
-        <v>0</v>
+        <v>63.56120547945206</v>
       </c>
       <c r="O45" s="18" t="n">
-        <v>0</v>
+        <v>70.47374794520549</v>
       </c>
     </row>
     <row r="46" ht="15.5" customHeight="1">
@@ -9070,40 +9070,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>1078.376443524082</v>
+        <v>1068.784651411252</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>982.7524006616173</v>
+        <v>1003.532015630921</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>883.1724106878437</v>
+        <v>908.8439028998628</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>736.8928718676456</v>
+        <v>765.1463951553168</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>564.5511256894874</v>
+        <v>595.1045804840079</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>392.3590446269488</v>
+        <v>429.1686418872227</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>194.3083484141737</v>
+        <v>233.1075374552695</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>-22.01232888796221</v>
+        <v>19.35894508464071</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>-252.2720968185649</v>
+        <v>-206.2315488733593</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>-496.8898338213498</v>
+        <v>-446.0954858761443</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>-756.2385630733352</v>
+        <v>-700.8105630540613</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>-995.8089629568576</v>
+        <v>-935.8906862638023</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -9144,7 +9144,7 @@
         <v>74.07743750177607</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>-22.01232888796233</v>
+        <v>-22.01232888796227</v>
       </c>
       <c r="L48" s="18" t="n">
         <v>-252.272096818565</v>
@@ -9297,7 +9297,7 @@
         <v>-22.60084740300376</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>-94.161567432026</v>
+        <v>-94.16156743202599</v>
       </c>
       <c r="J51" s="18" t="n">
         <v>-166.5808758273393</v>
@@ -9306,7 +9306,7 @@
         <v>-254.5508887567149</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>-350.6406551464533</v>
+        <v>-350.6406551464532</v>
       </c>
       <c r="M51" s="18" t="n">
         <v>-580.900423077056</v>
@@ -9356,7 +9356,7 @@
         <v>120.2309109123974</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>-1.70530256582424e-13</v>
+        <v>-1.56319401867222e-13</v>
       </c>
       <c r="L52" s="18" t="n">
         <v>-1.70530256582424e-13</v>
@@ -9409,7 +9409,7 @@
         <v>120.2309109123974</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>-1.70530256582424e-13</v>
+        <v>-1.56319401867222e-13</v>
       </c>
       <c r="L53" s="18" t="n">
         <v>-1.70530256582424e-13</v>
@@ -9494,40 +9494,40 @@
         </is>
       </c>
       <c r="D55" s="18" t="n">
-        <v>0</v>
+        <v>-9.591792112830227</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>0</v>
+        <v>-11.52127303393701</v>
       </c>
       <c r="F55" s="18" t="n">
-        <v>0</v>
+        <v>-12.09999452054795</v>
       </c>
       <c r="G55" s="18" t="n">
-        <v>0</v>
+        <v>-14.40203835616439</v>
       </c>
       <c r="H55" s="18" t="n">
-        <v>0</v>
+        <v>-16.75154794520548</v>
       </c>
       <c r="I55" s="18" t="n">
-        <v>0</v>
+        <v>-16.95591780821918</v>
       </c>
       <c r="J55" s="18" t="n">
-        <v>0</v>
+        <v>-19.22140273972603</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>0</v>
+        <v>-22.88201917808219</v>
       </c>
       <c r="L55" s="18" t="n">
-        <v>0</v>
+        <v>-26.8077205479452</v>
       </c>
       <c r="M55" s="18" t="n">
-        <v>0</v>
+        <v>-30.6608301369863</v>
       </c>
       <c r="N55" s="18" t="n">
-        <v>0</v>
+        <v>-34.41762737798631</v>
       </c>
       <c r="O55" s="18" t="n">
-        <v>0</v>
+        <v>-38.06055616438356</v>
       </c>
     </row>
     <row r="56" ht="15.5" customHeight="1">
@@ -9547,40 +9547,40 @@
         </is>
       </c>
       <c r="D56" s="18" t="n">
-        <v>0</v>
+        <v>-9.591792112830227</v>
       </c>
       <c r="E56" s="18" t="n">
-        <v>0</v>
+        <v>-11.52127303393701</v>
       </c>
       <c r="F56" s="18" t="n">
-        <v>0</v>
+        <v>-12.09999452054795</v>
       </c>
       <c r="G56" s="18" t="n">
-        <v>0</v>
+        <v>-14.40203835616439</v>
       </c>
       <c r="H56" s="18" t="n">
-        <v>0</v>
+        <v>-16.75154794520548</v>
       </c>
       <c r="I56" s="18" t="n">
-        <v>0</v>
+        <v>-16.95591780821918</v>
       </c>
       <c r="J56" s="18" t="n">
-        <v>0</v>
+        <v>-19.22140273972603</v>
       </c>
       <c r="K56" s="18" t="n">
-        <v>0</v>
+        <v>-22.88201917808219</v>
       </c>
       <c r="L56" s="18" t="n">
-        <v>0</v>
+        <v>-26.8077205479452</v>
       </c>
       <c r="M56" s="18" t="n">
-        <v>0</v>
+        <v>-30.6608301369863</v>
       </c>
       <c r="N56" s="18" t="n">
-        <v>0</v>
+        <v>-34.41762737798631</v>
       </c>
       <c r="O56" s="18" t="n">
-        <v>0</v>
+        <v>-38.06055616438356</v>
       </c>
     </row>
     <row r="57" ht="15.5" customHeight="1">
@@ -9653,40 +9653,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>1078.376443524082</v>
+        <v>1068.784651411252</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>982.7524006616173</v>
+        <v>971.2311276276803</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>883.1724106878436</v>
+        <v>871.0724161672956</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>736.8928718676455</v>
+        <v>722.490833511481</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>564.5511256894874</v>
+        <v>547.7995777442819</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>392.3590446269488</v>
+        <v>375.4031268187297</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>194.3083484141735</v>
+        <v>175.0869456744475</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>-22.0123288879625</v>
+        <v>-44.89434806604461</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>-252.2720968185652</v>
+        <v>-279.0798173665103</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>-496.88983382135</v>
+        <v>-527.5506639583363</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>-756.2385630733352</v>
+        <v>-790.6561904513214</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>-995.8089629568574</v>
+        <v>-1033.869519121241</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -9709,37 +9709,37 @@
         <v>0</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>0</v>
+        <v>32.3008880032412</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>37.77148673256715</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>42.65556164383577</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>0</v>
+        <v>47.30500273972598</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>0</v>
+        <v>53.76551506849307</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>58.02059178082203</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>2.842170943040401e-13</v>
+        <v>64.25329315068532</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>2.557953848736361e-13</v>
+        <v>72.84826849315101</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>1.70530256582424e-13</v>
+        <v>81.45517808219199</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>0</v>
+        <v>89.84562739726016</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>97.97883285743842</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -9918,40 +9918,40 @@
         </is>
       </c>
       <c r="D63" s="18" t="n">
-        <v>0</v>
+        <v>-32.30088800324118</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>0</v>
+        <v>-5.470598729325964</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>0</v>
+        <v>-4.88407491126847</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>0</v>
+        <v>-4.649441095890417</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>0</v>
+        <v>-6.460512328767123</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>0</v>
+        <v>-4.255076712328759</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>0</v>
+        <v>-6.232701369863008</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>0</v>
+        <v>-8.594975342465759</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>0</v>
+        <v>-8.606909589041095</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>0</v>
+        <v>-8.390449315068494</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>0</v>
+        <v>-8.13320546017809</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>0</v>
+        <v>-10.55547125215068</v>
       </c>
     </row>
     <row r="64" ht="15.5" customHeight="1">
@@ -9971,40 +9971,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>-62.89096262723227</v>
+        <v>-95.19185063047345</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>-75.40439142043309</v>
+        <v>-80.87499014975904</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>-68.18517</v>
+        <v>-73.06924491126847</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>-103.82137</v>
+        <v>-108.4708110958904</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>-118.9307299999999</v>
+        <v>-125.3912423287671</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>-107.9378099999999</v>
+        <v>-112.1928867123286</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>-122.2667999999999</v>
+        <v>-128.4995013698629</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>-128.3313350000001</v>
+        <v>-136.9263103424658</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>-130.18707</v>
+        <v>-138.7939795890411</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>-132.5824849999999</v>
+        <v>-140.9729343150684</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>-135.4706002345001</v>
+        <v>-143.6038056946782</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>-107.4510299999999</v>
+        <v>-118.0065012521506</v>
       </c>
     </row>
     <row r="65" ht="15.5" customHeight="1">
@@ -10130,40 +10130,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>-359.6857139963671</v>
+        <v>-391.9866019996083</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>-450.3494405224153</v>
+        <v>-455.8200392517413</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>-439.3840686109622</v>
+        <v>-444.2681435222307</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>-471.3065796248527</v>
+        <v>-475.9560207207431</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>-482.7443875286041</v>
+        <v>-489.2048998573712</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>-468.1117309533181</v>
+        <v>-472.3668076656468</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-519.6516802582858</v>
+        <v>-525.8843816281487</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>-562.3579481276157</v>
+        <v>-570.9529234700815</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>-559.8725169963394</v>
+        <v>-568.4794265853805</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>-557.9718775263759</v>
+        <v>-566.3623268414444</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>-556.6048109166122</v>
+        <v>-564.7380163767904</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>-396.5624603112915</v>
+        <v>-407.1179315634422</v>
       </c>
     </row>
     <row r="68" ht="15.5" customHeight="1">
@@ -10554,40 +10554,40 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>790.5134279083514</v>
+        <v>758.2125399051102</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-450.3494405224153</v>
+        <v>-455.8200392517413</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>-439.3840686109622</v>
+        <v>-444.2681435222307</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>-471.3065796248527</v>
+        <v>-475.9560207207431</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>-482.7443875286041</v>
+        <v>-489.2048998573712</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>-468.1117309533181</v>
+        <v>-472.3668076656468</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>-519.6516802582858</v>
+        <v>-525.8843816281487</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>-562.3579481276157</v>
+        <v>-570.9529234700815</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>-559.8725169963394</v>
+        <v>-568.4794265853805</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>-557.9718775263759</v>
+        <v>-566.3623268414444</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>-556.6048109166122</v>
+        <v>-564.7380163767904</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>-396.5624603112915</v>
+        <v>-407.1179315634422</v>
       </c>
     </row>
     <row r="76" ht="15.5" customHeight="1">
@@ -10610,37 +10610,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>790.5134279083514</v>
+        <v>758.2125399051102</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>340.1639873859361</v>
+        <v>334.6933886566102</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>-99.22008122502609</v>
+        <v>-104.1041561362946</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>-570.5266608498788</v>
+        <v>-575.1761019457692</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>-1053.271048378483</v>
+        <v>-1059.73156070725</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>-1521.382779331801</v>
+        <v>-1525.63785604413</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>-2041.034459590087</v>
+        <v>-2047.26716095995</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>-2603.392407717703</v>
+        <v>-2611.987383060168</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>-3163.264924714042</v>
+        <v>-3171.871834303083</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>-3721.236802240418</v>
+        <v>-3729.627251555487</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>-4277.84161315703</v>
+        <v>-4285.974818617208</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -10660,40 +10660,40 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>790.5134279083514</v>
+        <v>758.2125399051102</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-450.3494405224153</v>
+        <v>-455.8200392517413</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>-439.3840686109622</v>
+        <v>-444.2681435222307</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>-471.3065796248527</v>
+        <v>-475.9560207207431</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>-482.7443875286041</v>
+        <v>-489.2048998573712</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>-468.1117309533181</v>
+        <v>-472.3668076656468</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>-519.6516802582858</v>
+        <v>-525.8843816281487</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>-562.3579481276157</v>
+        <v>-570.9529234700815</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>-559.8725169963394</v>
+        <v>-568.4794265853805</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>-557.9718775263759</v>
+        <v>-566.3623268414444</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>-556.6048109166122</v>
+        <v>-564.7380163767904</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>-396.5624603112915</v>
+        <v>-407.1179315634422</v>
       </c>
     </row>
     <row r="78" ht="15.5" customHeight="1">
@@ -10713,40 +10713,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>790.5134279083514</v>
+        <v>758.2125399051102</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>340.1639873859361</v>
+        <v>334.6933886566102</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>-99.22008122502609</v>
+        <v>-104.1041561362946</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>-570.5266608498788</v>
+        <v>-575.1761019457692</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>-1053.271048378483</v>
+        <v>-1059.73156070725</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>-1521.382779331801</v>
+        <v>-1525.63785604413</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>-2041.034459590087</v>
+        <v>-2047.26716095995</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>-2603.392407717703</v>
+        <v>-2611.987383060168</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>-3163.264924714042</v>
+        <v>-3171.871834303083</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>-3721.236802240418</v>
+        <v>-3729.627251555487</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>-4277.84161315703</v>
+        <v>-4285.974818617208</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>-4674.404073468322</v>
+        <v>-4684.959544720472</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -11190,40 +11190,40 @@
         </is>
       </c>
       <c r="D87" s="18" t="n">
-        <v>0</v>
+        <v>22.70909589041096</v>
       </c>
       <c r="E87" s="18" t="n">
-        <v>0</v>
+        <v>26.25021369863014</v>
       </c>
       <c r="F87" s="18" t="n">
-        <v>0</v>
+        <v>30.55556712328767</v>
       </c>
       <c r="G87" s="18" t="n">
-        <v>0</v>
+        <v>32.90296438356165</v>
       </c>
       <c r="H87" s="18" t="n">
-        <v>0</v>
+        <v>37.01396712328768</v>
       </c>
       <c r="I87" s="18" t="n">
-        <v>0</v>
+        <v>41.06467397260274</v>
       </c>
       <c r="J87" s="18" t="n">
-        <v>0</v>
+        <v>45.0318904109589</v>
       </c>
       <c r="K87" s="18" t="n">
-        <v>0</v>
+        <v>49.9662493150685</v>
       </c>
       <c r="L87" s="18" t="n">
-        <v>0</v>
+        <v>54.64745753424658</v>
       </c>
       <c r="M87" s="18" t="n">
-        <v>0</v>
+        <v>59.18479726027397</v>
       </c>
       <c r="N87" s="18" t="n">
-        <v>0</v>
+        <v>63.56120547945206</v>
       </c>
       <c r="O87" s="18" t="n">
-        <v>0</v>
+        <v>70.47374794520549</v>
       </c>
     </row>
     <row r="88" ht="15.5" customHeight="1">
@@ -11296,40 +11296,40 @@
         </is>
       </c>
       <c r="D89" s="18" t="n">
-        <v>0</v>
+        <v>9.591792112830227</v>
       </c>
       <c r="E89" s="18" t="n">
-        <v>0</v>
+        <v>11.52127303393701</v>
       </c>
       <c r="F89" s="18" t="n">
-        <v>0</v>
+        <v>12.09999452054795</v>
       </c>
       <c r="G89" s="18" t="n">
-        <v>0</v>
+        <v>14.40203835616439</v>
       </c>
       <c r="H89" s="18" t="n">
-        <v>0</v>
+        <v>16.75154794520548</v>
       </c>
       <c r="I89" s="18" t="n">
-        <v>0</v>
+        <v>16.95591780821918</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>0</v>
+        <v>19.22140273972603</v>
       </c>
       <c r="K89" s="18" t="n">
-        <v>0</v>
+        <v>22.88201917808219</v>
       </c>
       <c r="L89" s="18" t="n">
-        <v>0</v>
+        <v>26.8077205479452</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>0</v>
+        <v>30.6608301369863</v>
       </c>
       <c r="N89" s="18" t="n">
-        <v>0</v>
+        <v>34.41762737798631</v>
       </c>
       <c r="O89" s="18" t="n">
-        <v>0</v>
+        <v>38.06055616438356</v>
       </c>
     </row>
     <row r="90" ht="15.5" customHeight="1">
@@ -11349,40 +11349,40 @@
         </is>
       </c>
       <c r="D90" s="18" t="n">
-        <v>0</v>
+        <v>32.30088800324118</v>
       </c>
       <c r="E90" s="18" t="n">
-        <v>0</v>
+        <v>37.77148673256715</v>
       </c>
       <c r="F90" s="18" t="n">
-        <v>0</v>
+        <v>42.65556164383562</v>
       </c>
       <c r="G90" s="18" t="n">
-        <v>0</v>
+        <v>47.30500273972604</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>0</v>
+        <v>53.76551506849316</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>0</v>
+        <v>58.02059178082192</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>0</v>
+        <v>64.25329315068493</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>0</v>
+        <v>72.84826849315068</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>0</v>
+        <v>81.45517808219178</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>0</v>
+        <v>89.84562739726027</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>0</v>
+        <v>97.97883285743836</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>0</v>
+        <v>108.534304109589</v>
       </c>
     </row>
     <row r="91" ht="15.5" customHeight="1">
@@ -11402,40 +11402,40 @@
         </is>
       </c>
       <c r="D91" s="18" t="n">
-        <v>0</v>
+        <v>32.30088800324118</v>
       </c>
       <c r="E91" s="18" t="n">
-        <v>0</v>
+        <v>5.470598729325964</v>
       </c>
       <c r="F91" s="18" t="n">
-        <v>0</v>
+        <v>4.88407491126847</v>
       </c>
       <c r="G91" s="18" t="n">
-        <v>0</v>
+        <v>4.649441095890417</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>0</v>
+        <v>6.460512328767123</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>0</v>
+        <v>4.255076712328759</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>0</v>
+        <v>6.232701369863008</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>0</v>
+        <v>8.594975342465759</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>0</v>
+        <v>8.606909589041095</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>0</v>
+        <v>8.390449315068494</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>0</v>
+        <v>8.13320546017809</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>0</v>
+        <v>10.55547125215068</v>
       </c>
     </row>
     <row r="92" ht="15.5" customHeight="1">
@@ -11532,40 +11532,40 @@
         </is>
       </c>
       <c r="D93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94" ht="15.5" customHeight="1">
@@ -11585,40 +11585,40 @@
         </is>
       </c>
       <c r="D94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95" ht="15.5" customHeight="1">
@@ -11703,16 +11703,16 @@
         <v>350.5089247393004</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>306.0274788554872</v>
+        <v>306.0274788554873</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>234.466758826465</v>
+        <v>234.4667588264649</v>
       </c>
       <c r="J96" s="20" t="n">
         <v>162.0474504311517</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>74.07743750177609</v>
+        <v>74.07743750177612</v>
       </c>
       <c r="L96" s="20" t="n">
         <v>-22.01232888796227</v>
@@ -11912,16 +11912,16 @@
         <v>350.5089247393004</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>306.0274788554872</v>
+        <v>306.0274788554873</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>234.466758826465</v>
+        <v>234.4667588264649</v>
       </c>
       <c r="I100" s="20" t="n">
         <v>162.0474504311517</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>74.07743750177609</v>
+        <v>74.07743750177612</v>
       </c>
       <c r="K100" s="20" t="n">
         <v>-22.01232888796227</v>
@@ -12086,7 +12086,7 @@
         <v>120.2309109123974</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>-1.70530256582424e-13</v>
+        <v>-1.56319401867222e-13</v>
       </c>
       <c r="M103" s="18" t="n">
         <v>-1.70530256582424e-13</v>
@@ -12295,7 +12295,7 @@
         <v>120.2309109123974</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>-1.70530256582424e-13</v>
+        <v>-1.56319401867222e-13</v>
       </c>
       <c r="L107" s="18" t="n">
         <v>-1.70530256582424e-13</v>
@@ -13246,40 +13246,40 @@
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>-24.6342071175614</v>
+        <v>0.8126540893247842</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>-27.44091105155179</v>
+        <v>8.924860060186244</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>-37.19463262515102</v>
+        <v>14.17710646391932</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>-51.38642401196002</v>
+        <v>14.93133109202685</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>-60.19811057604373</v>
+        <v>21.00661151564448</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>-75.18220942252646</v>
+        <v>20.85132150134064</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>-82.74203938374679</v>
+        <v>28.06302117593842</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>-111.645849768217</v>
+        <v>3.798805701492867</v>
       </c>
       <c r="L12" s="18" t="n">
-        <v>-109.5366144124633</v>
+        <v>8.558544060922458</v>
       </c>
       <c r="M12" s="18" t="n">
-        <v>-116.6649372452767</v>
+        <v>4.072693620060448</v>
       </c>
       <c r="N12" s="18" t="n">
-        <v>-114.2606200576604</v>
+        <v>9.111584204984368</v>
       </c>
       <c r="O12" s="18" t="n">
-        <v>-120.6707547085507</v>
+        <v>5.328253744558396</v>
       </c>
     </row>
     <row r="13" ht="15.5" customHeight="1">
@@ -13302,37 +13302,37 @@
         <v>0</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>11.39352251361698</v>
+        <v>998.2360363930129</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>35.54445242461311</v>
+        <v>58.8496219359597</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>38.15548208214457</v>
+        <v>5.320018087097211</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>17.1478882477458</v>
+        <v>40.68813681897223</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>24.89131087852738</v>
+        <v>-0.7392435195376135</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>10.05534423540793</v>
+        <v>34.58629552152897</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>34.93243652167932</v>
+        <v>-86.46330458265125</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>-1.889219671069353</v>
+        <v>125.2956516717634</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>6.507707829978671</v>
+        <v>-52.41370972598014</v>
       </c>
       <c r="N13" s="18" t="n">
-        <v>-2.060873853265333</v>
+        <v>123.7237822188336</v>
       </c>
       <c r="O13" s="18" t="n">
-        <v>5.610099654330125</v>
+        <v>-41.5222026742216</v>
       </c>
     </row>
     <row r="14" ht="15.5" customHeight="1">
@@ -13352,40 +13352,40 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>-22.80120862637393</v>
+        <v>0.7521855825658336</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>-15.62235015875242</v>
+        <v>5.081000726111427</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>-105.992337165201</v>
+        <v>40.40004006746349</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>-105.8758009861561</v>
+        <v>30.76428588978868</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>-106.283974523237</v>
+        <v>37.08864184911479</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>-105.9545259083165</v>
+        <v>29.38583344658231</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>-105.9776667751514</v>
+        <v>35.94368145912318</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>-104.5849776690155</v>
+        <v>3.558556007987514</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>-104.8824898276382</v>
+        <v>8.194898255929269</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>-104.7412942627038</v>
+        <v>3.656447352333001</v>
       </c>
       <c r="N14" s="18" t="n">
-        <v>-104.9993386140422</v>
+        <v>8.373053767489777</v>
       </c>
       <c r="O14" s="18" t="n">
-        <v>-104.8377813140798</v>
+        <v>4.629144005994664</v>
       </c>
     </row>
     <row r="15" ht="15.5" customHeight="1">
@@ -13564,40 +13564,40 @@
         </is>
       </c>
       <c r="D18" s="18" t="n">
-        <v>0</v>
+        <v>25.44686120688618</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>0</v>
+        <v>36.36577111173804</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>0</v>
+        <v>51.37173908907033</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>0</v>
+        <v>66.31775510398687</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>0</v>
+        <v>81.20472209168821</v>
       </c>
       <c r="I18" s="18" t="n">
-        <v>0</v>
+        <v>96.03353092386709</v>
       </c>
       <c r="J18" s="18" t="n">
-        <v>0</v>
+        <v>110.8050605596852</v>
       </c>
       <c r="K18" s="18" t="n">
-        <v>0</v>
+        <v>115.4446554697099</v>
       </c>
       <c r="L18" s="18" t="n">
-        <v>0</v>
+        <v>118.0951584733858</v>
       </c>
       <c r="M18" s="18" t="n">
-        <v>0</v>
+        <v>120.7376308653372</v>
       </c>
       <c r="N18" s="18" t="n">
-        <v>0</v>
+        <v>123.3722042626448</v>
       </c>
       <c r="O18" s="18" t="n">
-        <v>0</v>
+        <v>125.9990084531091</v>
       </c>
     </row>
     <row r="19" ht="15.5" customHeight="1">
@@ -13620,37 +13620,37 @@
         <v>0</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>0</v>
+        <v>42.90867080257856</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>0</v>
+        <v>41.26398951152368</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>0</v>
+        <v>29.09384864118101</v>
       </c>
       <c r="H19" s="18" t="n">
-        <v>0</v>
+        <v>22.44793564613041</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>0</v>
+        <v>18.2610178942989</v>
       </c>
       <c r="J19" s="18" t="n">
-        <v>0</v>
+        <v>15.38163753192476</v>
       </c>
       <c r="K19" s="18" t="n">
-        <v>0</v>
+        <v>4.187168786867446</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>0</v>
+        <v>2.295907933452423</v>
       </c>
       <c r="M19" s="18" t="n">
-        <v>0</v>
+        <v>2.237578937282958</v>
       </c>
       <c r="N19" s="18" t="n">
-        <v>0</v>
+        <v>2.182064844593512</v>
       </c>
       <c r="O19" s="18" t="n">
-        <v>0</v>
+        <v>2.129170185589091</v>
       </c>
     </row>
     <row r="20" ht="15.5" customHeight="1">
@@ -13670,40 +13670,40 @@
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>0</v>
+        <v>-23.55339420893976</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>0</v>
+        <v>-20.70335088486385</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>0</v>
+        <v>-146.3923772326644</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>0</v>
+        <v>-136.6400868759448</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>0</v>
+        <v>-143.3726163723518</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>0</v>
+        <v>-135.3403593548988</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>0</v>
+        <v>-141.9213482342746</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>0</v>
+        <v>-108.143533677003</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>0</v>
+        <v>-113.0773880835674</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>0</v>
+        <v>-108.3977416150368</v>
       </c>
       <c r="N20" s="18" t="n">
-        <v>0</v>
+        <v>-113.3723923815319</v>
       </c>
       <c r="O20" s="18" t="n">
-        <v>0</v>
+        <v>-109.4669253200745</v>
       </c>
     </row>
     <row r="21" ht="15.5" customHeight="1">
@@ -13882,40 +13882,40 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>82.67633090162597</v>
+        <v>108.1231921085122</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>148.2163021799442</v>
+        <v>184.5820732916822</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>-1.754590644000001</v>
+        <v>49.61714844507033</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>-2.426731299</v>
+        <v>63.89102380498687</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>-2.8319467185</v>
+        <v>78.3727753731882</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>-3.547852665</v>
+        <v>92.4856782588671</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>-3.903748870000001</v>
+        <v>106.9013116896852</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>-5.337566267</v>
+        <v>110.1070892027099</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>-5.221873288499999</v>
+        <v>112.8732851848858</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>-5.569194942</v>
+        <v>115.1684359233372</v>
       </c>
       <c r="N24" s="18" t="n">
-        <v>-5.44101618</v>
+        <v>117.9311880826448</v>
       </c>
       <c r="O24" s="18" t="n">
-        <v>-5.755117725500001</v>
+        <v>120.2438907276091</v>
       </c>
     </row>
     <row r="25" ht="15.5" customHeight="1">
@@ -13935,40 +13935,40 @@
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>-1.207748096000003</v>
+        <v>24.23911311088618</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>-1.306443680000001</v>
+        <v>35.05932743173804</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>-1.754590644000001</v>
+        <v>49.61714844507033</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>-2.426731299</v>
+        <v>63.89102380498687</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>-2.8319467185</v>
+        <v>78.3727753731882</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>-3.547852665</v>
+        <v>92.4856782588671</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>-3.903748870000001</v>
+        <v>106.9013116896852</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>-5.337566267</v>
+        <v>110.1070892027099</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>-5.221873288499999</v>
+        <v>112.8732851848858</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>-5.569194942</v>
+        <v>115.1684359233372</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>-5.44101618</v>
+        <v>117.9311880826448</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>-5.755117725500001</v>
+        <v>120.2438907276091</v>
       </c>
     </row>
     <row r="26" ht="15.5" customHeight="1">
@@ -13988,40 +13988,40 @@
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>76.52449540408477</v>
+        <v>100.0778896130246</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>84.38083442421299</v>
+        <v>105.0841853090768</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>-5.000000000000001</v>
+        <v>141.3923772326644</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>-5</v>
+        <v>131.6400868759448</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>-5</v>
+        <v>138.3726163723518</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>-5</v>
+        <v>130.3403593548988</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>-5</v>
+        <v>136.9213482342746</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>-5</v>
+        <v>103.143533677003</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>-5</v>
+        <v>108.0773880835674</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>-5</v>
+        <v>103.3977416150368</v>
       </c>
       <c r="N26" s="18" t="n">
-        <v>-5</v>
+        <v>108.3723923815319</v>
       </c>
       <c r="O26" s="18" t="n">
-        <v>-5</v>
+        <v>104.4669253200745</v>
       </c>
     </row>
     <row r="27" ht="15.5" customHeight="1">
@@ -14041,40 +14041,40 @@
         </is>
       </c>
       <c r="D27" s="18" t="n">
-        <v>-1.11788117123406</v>
+        <v>22.43551303770571</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>-0.7437697893231916</v>
+        <v>19.95958109554066</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>-5.000000000000001</v>
+        <v>141.3923772326644</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>-5</v>
+        <v>131.6400868759448</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>-5</v>
+        <v>138.3726163723518</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>-5</v>
+        <v>130.3403593548988</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>-5</v>
+        <v>136.9213482342746</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>-5</v>
+        <v>103.143533677003</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>-5</v>
+        <v>108.0773880835674</v>
       </c>
       <c r="M27" s="18" t="n">
-        <v>-5</v>
+        <v>103.3977416150368</v>
       </c>
       <c r="N27" s="18" t="n">
-        <v>-5</v>
+        <v>108.3723923815319</v>
       </c>
       <c r="O27" s="18" t="n">
-        <v>-5</v>
+        <v>104.4669253200745</v>
       </c>
     </row>
     <row r="28" ht="15.5" customHeight="1">
@@ -14200,40 +14200,40 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>82.497508066715</v>
+        <v>107.9443692736012</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>147.7187289740706</v>
+        <v>184.0845000858087</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-2.569511267151178</v>
+        <v>48.80222782191915</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>-3.557610415280707</v>
+        <v>62.76014468870616</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>-4.277409293003617</v>
+        <v>76.92731279868458</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>-5.306537413168975</v>
+        <v>90.72699351069812</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>-5.906070943169201</v>
+        <v>104.898989616516</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>-7.514418598844782</v>
+        <v>107.9302368708651</v>
       </c>
       <c r="L30" s="19" t="n">
-        <v>-7.572548939026751</v>
+        <v>110.522609534359</v>
       </c>
       <c r="M30" s="19" t="n">
-        <v>-8.092994040615043</v>
+        <v>112.6446368247222</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>-8.137245854815596</v>
+        <v>115.2349584078292</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>-8.619874005490272</v>
+        <v>117.3791344476188</v>
       </c>
     </row>
     <row r="31" ht="15.5" customHeight="1">
@@ -14253,40 +14253,40 @@
         </is>
       </c>
       <c r="D31" s="19" t="n">
-        <v>76.35897853778151</v>
+        <v>99.91237274672127</v>
       </c>
       <c r="E31" s="19" t="n">
-        <v>84.09756165542021</v>
+        <v>104.8009125402841</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>-7.322252845522346</v>
+        <v>139.0701243871421</v>
       </c>
       <c r="G31" s="19" t="n">
-        <v>-7.330046010340569</v>
+        <v>129.3100408656042</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>-7.552065272028205</v>
+        <v>135.8205511003236</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>-7.478519986918587</v>
+        <v>127.8618393679802</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>-7.564614348731403</v>
+        <v>134.3567338855432</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>-7.039180614302977</v>
+        <v>101.1043530627</v>
       </c>
       <c r="L31" s="19" t="n">
-        <v>-7.250797291178612</v>
+        <v>105.8265907923888</v>
       </c>
       <c r="M31" s="19" t="n">
-        <v>-7.265856308585869</v>
+        <v>101.131885306451</v>
       </c>
       <c r="N31" s="19" t="n">
-        <v>-7.477689447723344</v>
+        <v>105.8947029338086</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>-7.488877219050619</v>
+        <v>101.9780481010239</v>
       </c>
     </row>
     <row r="32" ht="15.5" customHeight="1">
@@ -14359,40 +14359,40 @@
         </is>
       </c>
       <c r="D33" s="19" t="n">
-        <v>82.497508066715</v>
+        <v>107.9443692736012</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>147.7187289740706</v>
+        <v>184.0845000858087</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>-2.569511267151178</v>
+        <v>48.80222782191915</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>-3.557610415280707</v>
+        <v>62.76014468870616</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>-4.277409293003617</v>
+        <v>76.92731279868458</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>-5.306537413168975</v>
+        <v>90.72699351069812</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>-5.906070943169201</v>
+        <v>104.898989616516</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>-7.514418598844782</v>
+        <v>107.9302368708651</v>
       </c>
       <c r="L33" s="19" t="n">
-        <v>-7.572548939026751</v>
+        <v>110.522609534359</v>
       </c>
       <c r="M33" s="19" t="n">
-        <v>-8.092994040615043</v>
+        <v>112.6446368247222</v>
       </c>
       <c r="N33" s="19" t="n">
-        <v>-8.137245854815596</v>
+        <v>115.2349584078292</v>
       </c>
       <c r="O33" s="19" t="n">
-        <v>-8.619874005490272</v>
+        <v>117.3791344476188</v>
       </c>
     </row>
     <row r="34" ht="15.5" customHeight="1">
@@ -14412,40 +14412,40 @@
         </is>
       </c>
       <c r="D34" s="19" t="n">
-        <v>-1.386570930910977</v>
+        <v>24.06029027597521</v>
       </c>
       <c r="E34" s="19" t="n">
-        <v>-1.804016885873551</v>
+        <v>34.56175422586449</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-2.569511267151178</v>
+        <v>48.80222782191915</v>
       </c>
       <c r="G34" s="19" t="n">
-        <v>-3.557610415280707</v>
+        <v>62.76014468870616</v>
       </c>
       <c r="H34" s="19" t="n">
-        <v>-4.277409293003617</v>
+        <v>76.92731279868458</v>
       </c>
       <c r="I34" s="19" t="n">
-        <v>-5.306537413168975</v>
+        <v>90.72699351069812</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>-5.906070943169201</v>
+        <v>104.898989616516</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>-7.514418598844782</v>
+        <v>107.9302368708651</v>
       </c>
       <c r="L34" s="19" t="n">
-        <v>-7.572548939026751</v>
+        <v>110.522609534359</v>
       </c>
       <c r="M34" s="19" t="n">
-        <v>-8.092994040615043</v>
+        <v>112.6446368247222</v>
       </c>
       <c r="N34" s="19" t="n">
-        <v>-8.137245854815596</v>
+        <v>115.2349584078292</v>
       </c>
       <c r="O34" s="19" t="n">
-        <v>-8.619874005490272</v>
+        <v>117.3791344476188</v>
       </c>
     </row>
     <row r="35" ht="15.5" customHeight="1">
@@ -14518,40 +14518,40 @@
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>0</v>
+        <v>-6.736881277273057</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>0</v>
+        <v>-9.289051322586984</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>0</v>
+        <v>-12.77125920143769</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>0</v>
+        <v>-15.96001276933573</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>0</v>
+        <v>-18.93068892385109</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>0</v>
+        <v>-21.59692492117386</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>0</v>
+        <v>-24.07925335511556</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>0</v>
+        <v>-23.27430272224593</v>
       </c>
       <c r="L36" s="19" t="n">
-        <v>0</v>
+        <v>-21.89612986034769</v>
       </c>
       <c r="M36" s="19" t="n">
-        <v>0</v>
+        <v>-20.36998379872188</v>
       </c>
       <c r="N36" s="19" t="n">
-        <v>0</v>
+        <v>-18.82923551061964</v>
       </c>
       <c r="O36" s="19" t="n">
-        <v>0</v>
+        <v>-17.15117596241236</v>
       </c>
     </row>
     <row r="37" ht="15.5" customHeight="1">
@@ -14571,40 +14571,40 @@
         </is>
       </c>
       <c r="D37" s="19" t="n">
-        <v>-1.386570930910977</v>
+        <v>0</v>
       </c>
       <c r="E37" s="19" t="n">
-        <v>-3.190587816784529</v>
+        <v>0</v>
       </c>
       <c r="F37" s="19" t="n">
-        <v>-5.760099083935707</v>
+        <v>0</v>
       </c>
       <c r="G37" s="19" t="n">
-        <v>-9.317709499216413</v>
+        <v>0</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>-13.59511879222003</v>
+        <v>0</v>
       </c>
       <c r="I37" s="19" t="n">
-        <v>-18.90165620538901</v>
+        <v>0</v>
       </c>
       <c r="J37" s="19" t="n">
-        <v>-24.80772714855821</v>
+        <v>0</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>-32.32214574740299</v>
+        <v>0</v>
       </c>
       <c r="L37" s="19" t="n">
-        <v>-39.89469468642974</v>
+        <v>0</v>
       </c>
       <c r="M37" s="19" t="n">
-        <v>-47.98768872704478</v>
+        <v>0</v>
       </c>
       <c r="N37" s="19" t="n">
-        <v>-56.12493458186038</v>
+        <v>0</v>
       </c>
       <c r="O37" s="19" t="n">
-        <v>-64.74480858735065</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" ht="15.5" customHeight="1">
@@ -14624,40 +14624,40 @@
         </is>
       </c>
       <c r="D38" s="19" t="n">
-        <v>82.497508066715</v>
+        <v>101.2074879963281</v>
       </c>
       <c r="E38" s="19" t="n">
-        <v>147.7187289740706</v>
+        <v>174.7954487632217</v>
       </c>
       <c r="F38" s="19" t="n">
-        <v>-2.569511267151178</v>
+        <v>36.03096862048146</v>
       </c>
       <c r="G38" s="19" t="n">
-        <v>-3.557610415280707</v>
+        <v>46.80013191937044</v>
       </c>
       <c r="H38" s="19" t="n">
-        <v>-4.277409293003617</v>
+        <v>57.99662387483349</v>
       </c>
       <c r="I38" s="19" t="n">
-        <v>-5.306537413168975</v>
+        <v>69.13006858952426</v>
       </c>
       <c r="J38" s="19" t="n">
-        <v>-5.906070943169201</v>
+        <v>80.81973626140045</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>-7.514418598844782</v>
+        <v>84.65593414861918</v>
       </c>
       <c r="L38" s="19" t="n">
-        <v>-7.572548939026751</v>
+        <v>88.62647967401134</v>
       </c>
       <c r="M38" s="19" t="n">
-        <v>-8.092994040615043</v>
+        <v>92.27465302600028</v>
       </c>
       <c r="N38" s="19" t="n">
-        <v>-8.137245854815596</v>
+        <v>96.40572289720956</v>
       </c>
       <c r="O38" s="19" t="n">
-        <v>-8.619874005490272</v>
+        <v>100.2279584852065</v>
       </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
@@ -14677,40 +14677,40 @@
         </is>
       </c>
       <c r="D39" s="19" t="n">
-        <v>76.35897853778151</v>
+        <v>93.67677381872859</v>
       </c>
       <c r="E39" s="19" t="n">
-        <v>84.09756165542021</v>
+        <v>99.51257454992169</v>
       </c>
       <c r="F39" s="19" t="n">
-        <v>-7.322252845522346</v>
+        <v>102.6762816264095</v>
       </c>
       <c r="G39" s="19" t="n">
-        <v>-7.330046010340569</v>
+        <v>96.42627500344948</v>
       </c>
       <c r="H39" s="19" t="n">
-        <v>-7.552065272028205</v>
+        <v>102.3970957786109</v>
       </c>
       <c r="I39" s="19" t="n">
-        <v>-7.478519986918587</v>
+        <v>97.42522465983555</v>
       </c>
       <c r="J39" s="19" t="n">
-        <v>-7.564614348731403</v>
+        <v>103.5155423066449</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>-7.039180614302977</v>
+        <v>79.30199824591628</v>
       </c>
       <c r="L39" s="19" t="n">
-        <v>-7.250797291178612</v>
+        <v>84.86081026629964</v>
       </c>
       <c r="M39" s="19" t="n">
-        <v>-7.265856308585869</v>
+        <v>82.84379877790985</v>
       </c>
       <c r="N39" s="19" t="n">
-        <v>-7.477689447723344</v>
+        <v>88.59165246703012</v>
       </c>
       <c r="O39" s="19" t="n">
-        <v>-7.488877219050619</v>
+        <v>87.07724434646445</v>
       </c>
     </row>
     <row r="40" ht="15.5" customHeight="1">
@@ -14889,40 +14889,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>813.0337963818312</v>
+        <v>818.909226337386</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>806.9460971373925</v>
+        <v>815.181375033886</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>800.4312952342281</v>
+        <v>809.8303557302692</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>793.2651865382851</v>
+        <v>804.4204425750499</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>785.7144879464414</v>
+        <v>797.9204414180111</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>777.468302676461</v>
+        <v>791.5465745190442</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>769.9099939314576</v>
+        <v>783.885424106598</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>761.9544737843239</v>
+        <v>778.6840754662521</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>754.1252507155943</v>
+        <v>770.5383750804883</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>745.9592040522699</v>
+        <v>763.2800917161422</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>737.9317292292616</v>
+        <v>754.9033402385713</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>729.6487124261414</v>
+        <v>747.3921967232342</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -14942,40 +14942,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
+        <v>816.9238870014956</v>
+      </c>
+      <c r="E44" s="18" t="n">
         <v>813.0337963818312</v>
       </c>
-      <c r="E44" s="18" t="n">
+      <c r="F44" s="18" t="n">
         <v>806.9460971373925</v>
       </c>
-      <c r="F44" s="18" t="n">
+      <c r="G44" s="18" t="n">
         <v>800.4312952342281</v>
       </c>
-      <c r="G44" s="18" t="n">
+      <c r="H44" s="18" t="n">
         <v>793.2651865382851</v>
       </c>
-      <c r="H44" s="18" t="n">
+      <c r="I44" s="18" t="n">
         <v>785.7144879464414</v>
       </c>
-      <c r="I44" s="18" t="n">
+      <c r="J44" s="18" t="n">
         <v>777.468302676461</v>
       </c>
-      <c r="J44" s="18" t="n">
+      <c r="K44" s="18" t="n">
         <v>769.9099939314576</v>
       </c>
-      <c r="K44" s="18" t="n">
+      <c r="L44" s="18" t="n">
         <v>761.9544737843239</v>
       </c>
-      <c r="L44" s="18" t="n">
+      <c r="M44" s="18" t="n">
         <v>754.1252507155943</v>
       </c>
-      <c r="M44" s="18" t="n">
+      <c r="N44" s="18" t="n">
         <v>745.9592040522699</v>
       </c>
-      <c r="N44" s="18" t="n">
+      <c r="O44" s="18" t="n">
         <v>737.9317292292616</v>
-      </c>
-      <c r="O44" s="18" t="n">
-        <v>729.6487124261414</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -14995,40 +14995,40 @@
         </is>
       </c>
       <c r="D45" s="18" t="n">
-        <v>0</v>
+        <v>1.985339335890411</v>
       </c>
       <c r="E45" s="18" t="n">
-        <v>0</v>
+        <v>2.147578652054795</v>
       </c>
       <c r="F45" s="18" t="n">
-        <v>0</v>
+        <v>2.884258592876713</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>0</v>
+        <v>3.989147340821918</v>
       </c>
       <c r="H45" s="18" t="n">
-        <v>0</v>
+        <v>4.655254879726027</v>
       </c>
       <c r="I45" s="18" t="n">
-        <v>0</v>
+        <v>5.832086572602739</v>
       </c>
       <c r="J45" s="18" t="n">
-        <v>0</v>
+        <v>6.417121430136986</v>
       </c>
       <c r="K45" s="18" t="n">
-        <v>0</v>
+        <v>8.77408153479452</v>
       </c>
       <c r="L45" s="18" t="n">
-        <v>0</v>
+        <v>8.583901296164385</v>
       </c>
       <c r="M45" s="18" t="n">
-        <v>0</v>
+        <v>9.154841000547945</v>
       </c>
       <c r="N45" s="18" t="n">
-        <v>0</v>
+        <v>8.944136186301371</v>
       </c>
       <c r="O45" s="18" t="n">
-        <v>0</v>
+        <v>9.460467493972605</v>
       </c>
     </row>
     <row r="46" ht="15.5" customHeight="1">
@@ -15101,40 +15101,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>815.5373160705848</v>
+        <v>821.4127460261396</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>813.7332991847112</v>
+        <v>821.9685770812047</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>811.1637879175601</v>
+        <v>820.5628484136012</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>807.6061775022793</v>
+        <v>818.7614335390441</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>803.3287682092756</v>
+        <v>815.5347216808453</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>798.0222307961067</v>
+        <v>812.1005026386898</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>792.1161598529375</v>
+        <v>806.0915900280778</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>784.6017412540926</v>
+        <v>801.3313429360209</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>777.0291923150659</v>
+        <v>793.4423166799598</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>768.9361982744508</v>
+        <v>786.2570859383231</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>760.7989524196352</v>
+        <v>777.7705634289449</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>752.1790784141448</v>
+        <v>769.9225627112376</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -15154,40 +15154,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>666.0145702106405</v>
+        <v>675.966862341008</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>813.7332991847111</v>
+        <v>830.9952138415599</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>811.1637879175601</v>
+        <v>827.6949394598631</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>807.6061775022793</v>
+        <v>827.4320323823933</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>803.3287682092756</v>
+        <v>824.039594070976</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>798.0222307961067</v>
+        <v>819.9473856546333</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>792.1161598529375</v>
+        <v>813.8772915003592</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>784.6017412540926</v>
+        <v>807.5949949647922</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>777.029192315066</v>
+        <v>797.7466813928772</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>768.9361982744509</v>
+        <v>786.1280260116248</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>760.7989524196354</v>
+        <v>778.14667347714</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>752.179078414145</v>
+        <v>769.5332650206383</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -15260,40 +15260,40 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>82.497508066715</v>
+        <v>92.44980019708251</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>147.7187289740706</v>
+        <v>155.028351500552</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>-2.569511267151178</v>
+        <v>6.652017748670715</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>-3.557610415280707</v>
+        <v>7.046715449011536</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>-4.277409293003617</v>
+        <v>5.829090704404528</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>-5.306537413168975</v>
+        <v>6.512117447949379</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>-5.906070943169201</v>
+        <v>4.03640584313429</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>-7.514418598844782</v>
+        <v>5.536358325551248</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>-7.572548939026751</v>
+        <v>0.09416321438845898</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>-8.092994040615043</v>
+        <v>1.432121543143708</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>-8.137245854815596</v>
+        <v>-0.3146403810696938</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>-8.619874005490272</v>
+        <v>0.911707127257074</v>
       </c>
     </row>
     <row r="51" ht="15.5" customHeight="1">
@@ -15316,37 +15316,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>82.497508066715</v>
+        <v>92.44980019708251</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>230.2162370407856</v>
+        <v>237.525859567267</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>227.6467257736345</v>
+        <v>236.8682547894563</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>224.0891153583538</v>
+        <v>234.693441222646</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>219.8117060653501</v>
+        <v>229.9182060627583</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>214.5051686521812</v>
+        <v>226.3238235132995</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>208.599097709012</v>
+        <v>218.5415744953155</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>201.0846791101672</v>
+        <v>214.1354560345632</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>193.5121301711405</v>
+        <v>201.1788423245557</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>185.4191361305254</v>
+        <v>194.9442517142842</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>177.2818902757098</v>
+        <v>185.1044957494557</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -15369,7 +15369,7 @@
         <v>149.5227458599442</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="F52" s="18" t="n">
         <v>2.842170943040401e-14</v>
@@ -15422,7 +15422,7 @@
         <v>149.5227458599442</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="F53" s="18" t="n">
         <v>2.842170943040401e-14</v>
@@ -15525,40 +15525,40 @@
         </is>
       </c>
       <c r="D55" s="18" t="n">
-        <v>0</v>
+        <v>-4.076862174812563</v>
       </c>
       <c r="E55" s="18" t="n">
-        <v>0</v>
+        <v>-5.136546140690799</v>
       </c>
       <c r="F55" s="18" t="n">
-        <v>0</v>
+        <v>-7.106593312526329</v>
       </c>
       <c r="G55" s="18" t="n">
-        <v>0</v>
+        <v>-9.439921732930427</v>
       </c>
       <c r="H55" s="18" t="n">
-        <v>0</v>
+        <v>-11.32961559959081</v>
       </c>
       <c r="I55" s="18" t="n">
-        <v>0</v>
+        <v>-13.72525349785209</v>
       </c>
       <c r="J55" s="18" t="n">
-        <v>0</v>
+        <v>-15.52438668161796</v>
       </c>
       <c r="K55" s="18" t="n">
-        <v>0</v>
+        <v>-18.26268335422273</v>
       </c>
       <c r="L55" s="18" t="n">
-        <v>0</v>
+        <v>-18.29035267753856</v>
       </c>
       <c r="M55" s="18" t="n">
-        <v>0</v>
+        <v>-19.07848189358936</v>
       </c>
       <c r="N55" s="18" t="n">
-        <v>0</v>
+        <v>-19.08431735857354</v>
       </c>
       <c r="O55" s="18" t="n">
-        <v>0</v>
+        <v>-19.81655038052952</v>
       </c>
     </row>
     <row r="56" ht="15.5" customHeight="1">
@@ -15578,40 +15578,40 @@
         </is>
       </c>
       <c r="D56" s="18" t="n">
-        <v>0</v>
+        <v>-4.076862174812563</v>
       </c>
       <c r="E56" s="18" t="n">
-        <v>0</v>
+        <v>-5.136546140690799</v>
       </c>
       <c r="F56" s="18" t="n">
-        <v>0</v>
+        <v>-7.106593312526329</v>
       </c>
       <c r="G56" s="18" t="n">
-        <v>0</v>
+        <v>-9.439921732930427</v>
       </c>
       <c r="H56" s="18" t="n">
-        <v>0</v>
+        <v>-11.32961559959081</v>
       </c>
       <c r="I56" s="18" t="n">
-        <v>0</v>
+        <v>-13.72525349785209</v>
       </c>
       <c r="J56" s="18" t="n">
-        <v>0</v>
+        <v>-15.52438668161796</v>
       </c>
       <c r="K56" s="18" t="n">
-        <v>0</v>
+        <v>-18.26268335422273</v>
       </c>
       <c r="L56" s="18" t="n">
-        <v>0</v>
+        <v>-18.29035267753856</v>
       </c>
       <c r="M56" s="18" t="n">
-        <v>0</v>
+        <v>-19.07848189358936</v>
       </c>
       <c r="N56" s="18" t="n">
-        <v>0</v>
+        <v>-19.08431735857354</v>
       </c>
       <c r="O56" s="18" t="n">
-        <v>0</v>
+        <v>-19.81655038052952</v>
       </c>
     </row>
     <row r="57" ht="15.5" customHeight="1">
@@ -15684,40 +15684,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>815.5373160705847</v>
+        <v>821.4127460261396</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>813.7332991847111</v>
+        <v>825.8586677008691</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>811.1637879175601</v>
+        <v>820.5883461473368</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>807.6061775022793</v>
+        <v>817.9921106494629</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>803.3287682092756</v>
+        <v>812.7099784713852</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>798.0222307961067</v>
+        <v>806.2221321567812</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>792.1161598529375</v>
+        <v>798.3529048187412</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>784.6017412540926</v>
+        <v>789.3323116105695</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>777.029192315066</v>
+        <v>779.4563287153387</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>768.9361982744509</v>
+        <v>767.0495441180354</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>760.7989524196354</v>
+        <v>759.0623561185664</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>752.179078414145</v>
+        <v>749.7167146401088</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -15737,40 +15737,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>0</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>-3.89009061966442</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>0</v>
+        <v>-0.02549773373561948</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>0</v>
+        <v>0.7693228895811899</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>0</v>
+        <v>2.824743209460166</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>0</v>
+        <v>5.878370481908632</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>0</v>
+        <v>7.738685209336609</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>0</v>
+        <v>11.99903132545137</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>13.98598796462113</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>19.2075418202877</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>18.7082073103785</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>20.2058480711288</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -15843,40 +15843,40 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>-1.207748096000003</v>
+        <v>24.23911311088618</v>
       </c>
       <c r="E61" s="18" t="n">
-        <v>-1.306443680000001</v>
+        <v>35.05932743173804</v>
       </c>
       <c r="F61" s="18" t="n">
-        <v>-1.754590644000001</v>
+        <v>49.61714844507033</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>-2.426731299</v>
+        <v>63.89102380498687</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>-2.8319467185</v>
+        <v>78.3727753731882</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>-3.547852665</v>
+        <v>92.4856782588671</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>-3.903748870000001</v>
+        <v>106.9013116896852</v>
       </c>
       <c r="K61" s="18" t="n">
-        <v>-5.337566267</v>
+        <v>110.1070892027099</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>-5.221873288499999</v>
+        <v>112.8732851848858</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>-5.569194942</v>
+        <v>115.1684359233372</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>-5.44101618</v>
+        <v>117.9311880826448</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>-5.755117725500001</v>
+        <v>120.2438907276091</v>
       </c>
     </row>
     <row r="62" ht="15.5" customHeight="1">
@@ -15896,40 +15896,40 @@
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>0</v>
+        <v>-6.736881277273057</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>0</v>
+        <v>-9.289051322586984</v>
       </c>
       <c r="F62" s="18" t="n">
-        <v>0</v>
+        <v>-12.77125920143769</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>0</v>
+        <v>-15.96001276933573</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>0</v>
+        <v>-18.93068892385109</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>0</v>
+        <v>-21.59692492117386</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>0</v>
+        <v>-24.07925335511556</v>
       </c>
       <c r="K62" s="18" t="n">
-        <v>0</v>
+        <v>-23.27430272224593</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>0</v>
+        <v>-21.89612986034769</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>0</v>
+        <v>-20.36998379872188</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>0</v>
+        <v>-18.82923551061964</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>0</v>
+        <v>-17.15117596241236</v>
       </c>
     </row>
     <row r="63" ht="15.5" customHeight="1">
@@ -15949,40 +15949,40 @@
         </is>
       </c>
       <c r="D63" s="18" t="n">
-        <v>0</v>
+        <v>-6.062201510702974</v>
       </c>
       <c r="E63" s="18" t="n">
-        <v>0</v>
+        <v>-1.22192328204262</v>
       </c>
       <c r="F63" s="18" t="n">
-        <v>0</v>
+        <v>-2.706727112657449</v>
       </c>
       <c r="G63" s="18" t="n">
-        <v>0</v>
+        <v>-3.438217168349302</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>0</v>
+        <v>-2.555801405564495</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>0</v>
+        <v>-3.572469591137988</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>0</v>
+        <v>-2.384168041300121</v>
       </c>
       <c r="K63" s="18" t="n">
-        <v>0</v>
+        <v>-5.095256777262307</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>0</v>
+        <v>0.1625109153143143</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>0</v>
+        <v>-1.35906892043436</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>0</v>
+        <v>0.2048693492623883</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>0</v>
+        <v>-1.248564329627207</v>
       </c>
     </row>
     <row r="64" ht="15.5" customHeight="1">
@@ -16002,40 +16002,40 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>-1.207748096000003</v>
+        <v>11.44003032291015</v>
       </c>
       <c r="E64" s="18" t="n">
-        <v>-1.306443680000001</v>
+        <v>24.54835282710843</v>
       </c>
       <c r="F64" s="18" t="n">
-        <v>-1.754590644000001</v>
+        <v>34.13916213097519</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>-2.426731299</v>
+        <v>44.49279386730184</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>-2.8319467185</v>
+        <v>56.88628504377262</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>-3.547852665</v>
+        <v>67.31628374655524</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>-3.903748870000001</v>
+        <v>80.43789029326953</v>
       </c>
       <c r="K64" s="18" t="n">
-        <v>-5.337566267</v>
+        <v>81.73752970320166</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>-5.221873288499999</v>
+        <v>91.13966623985242</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>-5.569194942</v>
+        <v>93.43938320418096</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>-5.44101618</v>
+        <v>99.30682192128754</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>-5.755117725500001</v>
+        <v>101.8441504355695</v>
       </c>
     </row>
     <row r="65" ht="15.5" customHeight="1">
@@ -16161,40 +16161,40 @@
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>-3.890090619664537</v>
+        <v>8.757687799245616</v>
       </c>
       <c r="E67" s="18" t="n">
-        <v>-6.087699244438687</v>
+        <v>19.76709726266975</v>
       </c>
       <c r="F67" s="18" t="n">
-        <v>-6.514801903164442</v>
+        <v>29.37895087181074</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>-7.166108695942941</v>
+        <v>39.7534164703589</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>-7.550698591843656</v>
+        <v>52.16753317042896</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>-8.246185269980362</v>
+        <v>62.61795114157488</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-7.558308745003378</v>
+        <v>76.78333041826616</v>
       </c>
       <c r="K67" s="18" t="n">
-        <v>-7.955520147133723</v>
+        <v>79.11957582306793</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>-7.829223068729533</v>
+        <v>88.53231645962288</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>-8.166046663324387</v>
+        <v>90.84253148285657</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>-8.027474823008291</v>
+        <v>96.72036327827925</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>-8.283016803120145</v>
+        <v>99.31625135794938</v>
       </c>
     </row>
     <row r="68" ht="15.5" customHeight="1">
@@ -16426,40 +16426,40 @@
         </is>
       </c>
       <c r="D72" s="18" t="n">
-        <v>0</v>
+        <v>-8.757687799245616</v>
       </c>
       <c r="E72" s="18" t="n">
-        <v>0</v>
+        <v>-19.76709726266975</v>
       </c>
       <c r="F72" s="18" t="n">
-        <v>0</v>
+        <v>-29.37895087181074</v>
       </c>
       <c r="G72" s="18" t="n">
-        <v>0</v>
+        <v>-39.7534164703589</v>
       </c>
       <c r="H72" s="18" t="n">
-        <v>0</v>
+        <v>-52.16753317042896</v>
       </c>
       <c r="I72" s="18" t="n">
-        <v>0</v>
+        <v>-62.61795114157488</v>
       </c>
       <c r="J72" s="18" t="n">
-        <v>0</v>
+        <v>-76.78333041826616</v>
       </c>
       <c r="K72" s="18" t="n">
-        <v>0</v>
+        <v>-79.11957582306793</v>
       </c>
       <c r="L72" s="18" t="n">
-        <v>0</v>
+        <v>-88.53231645962288</v>
       </c>
       <c r="M72" s="18" t="n">
-        <v>0</v>
+        <v>-90.84253148285657</v>
       </c>
       <c r="N72" s="18" t="n">
-        <v>0</v>
+        <v>-96.72036327827925</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>0</v>
+        <v>-99.31625135794938</v>
       </c>
     </row>
     <row r="73" ht="15.5" customHeight="1">
@@ -16532,40 +16532,40 @@
         </is>
       </c>
       <c r="D74" s="18" t="n">
-        <v>816.9238870014957</v>
+        <v>808.16619920225</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>0</v>
+        <v>-19.76709726266975</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>0</v>
+        <v>-29.37895087181074</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>0</v>
+        <v>-39.7534164703589</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>0</v>
+        <v>-52.16753317042896</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>0</v>
+        <v>-62.61795114157488</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>0</v>
+        <v>-76.78333041826616</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>0</v>
+        <v>-79.11957582306793</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>0</v>
+        <v>-88.53231645962288</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>0</v>
+        <v>-90.84253148285657</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>0</v>
+        <v>-96.72036327827925</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>0</v>
+        <v>-99.31625135794938</v>
       </c>
     </row>
     <row r="75" ht="15.5" customHeight="1">
@@ -16585,40 +16585,40 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>813.0337963818312</v>
+        <v>816.9238870014956</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-6.087699244438687</v>
+        <v>0</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>-6.514801903164442</v>
+        <v>0</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>-7.166108695942941</v>
+        <v>0</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>-7.550698591843656</v>
+        <v>0</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>-8.246185269980362</v>
+        <v>0</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>-7.558308745003378</v>
+        <v>0</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>-7.955520147133723</v>
+        <v>0</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>-7.829223068729533</v>
+        <v>0</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>-8.166046663324387</v>
+        <v>0</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>-8.027474823008291</v>
+        <v>0</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>-8.283016803120145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" ht="15.5" customHeight="1">
@@ -16641,37 +16641,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
+        <v>816.9238870014956</v>
+      </c>
+      <c r="F76" s="18" t="n">
         <v>813.0337963818312</v>
       </c>
-      <c r="F76" s="18" t="n">
+      <c r="G76" s="18" t="n">
         <v>806.9460971373925</v>
       </c>
-      <c r="G76" s="18" t="n">
+      <c r="H76" s="18" t="n">
         <v>800.4312952342281</v>
       </c>
-      <c r="H76" s="18" t="n">
+      <c r="I76" s="18" t="n">
         <v>793.2651865382851</v>
       </c>
-      <c r="I76" s="18" t="n">
+      <c r="J76" s="18" t="n">
         <v>785.7144879464414</v>
       </c>
-      <c r="J76" s="18" t="n">
+      <c r="K76" s="18" t="n">
         <v>777.468302676461</v>
       </c>
-      <c r="K76" s="18" t="n">
+      <c r="L76" s="18" t="n">
         <v>769.9099939314576</v>
       </c>
-      <c r="L76" s="18" t="n">
+      <c r="M76" s="18" t="n">
         <v>761.9544737843239</v>
       </c>
-      <c r="M76" s="18" t="n">
+      <c r="N76" s="18" t="n">
         <v>754.1252507155943</v>
       </c>
-      <c r="N76" s="18" t="n">
+      <c r="O76" s="18" t="n">
         <v>745.9592040522699</v>
-      </c>
-      <c r="O76" s="18" t="n">
-        <v>737.9317292292616</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -16691,40 +16691,40 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>813.0337963818312</v>
+        <v>816.9238870014956</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-6.087699244438687</v>
+        <v>0</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>-6.514801903164442</v>
+        <v>0</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>-7.166108695942941</v>
+        <v>0</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>-7.550698591843656</v>
+        <v>0</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>-8.246185269980362</v>
+        <v>0</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>-7.558308745003378</v>
+        <v>0</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>-7.955520147133723</v>
+        <v>0</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>-7.829223068729533</v>
+        <v>0</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>-8.166046663324387</v>
+        <v>0</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>-8.027474823008291</v>
+        <v>0</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>-8.283016803120145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" ht="15.5" customHeight="1">
@@ -16744,40 +16744,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
+        <v>816.9238870014956</v>
+      </c>
+      <c r="E78" s="18" t="n">
         <v>813.0337963818312</v>
       </c>
-      <c r="E78" s="18" t="n">
+      <c r="F78" s="18" t="n">
         <v>806.9460971373925</v>
       </c>
-      <c r="F78" s="18" t="n">
+      <c r="G78" s="18" t="n">
         <v>800.4312952342281</v>
       </c>
-      <c r="G78" s="18" t="n">
+      <c r="H78" s="18" t="n">
         <v>793.2651865382851</v>
       </c>
-      <c r="H78" s="18" t="n">
+      <c r="I78" s="18" t="n">
         <v>785.7144879464414</v>
       </c>
-      <c r="I78" s="18" t="n">
+      <c r="J78" s="18" t="n">
         <v>777.468302676461</v>
       </c>
-      <c r="J78" s="18" t="n">
+      <c r="K78" s="18" t="n">
         <v>769.9099939314576</v>
       </c>
-      <c r="K78" s="18" t="n">
+      <c r="L78" s="18" t="n">
         <v>761.9544737843239</v>
       </c>
-      <c r="L78" s="18" t="n">
+      <c r="M78" s="18" t="n">
         <v>754.1252507155943</v>
       </c>
-      <c r="M78" s="18" t="n">
+      <c r="N78" s="18" t="n">
         <v>745.9592040522699</v>
       </c>
-      <c r="N78" s="18" t="n">
+      <c r="O78" s="18" t="n">
         <v>737.9317292292616</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>729.6487124261414</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -17221,40 +17221,40 @@
         </is>
       </c>
       <c r="D87" s="18" t="n">
-        <v>0</v>
+        <v>1.985339335890411</v>
       </c>
       <c r="E87" s="18" t="n">
-        <v>0</v>
+        <v>2.147578652054795</v>
       </c>
       <c r="F87" s="18" t="n">
-        <v>0</v>
+        <v>2.884258592876713</v>
       </c>
       <c r="G87" s="18" t="n">
-        <v>0</v>
+        <v>3.989147340821918</v>
       </c>
       <c r="H87" s="18" t="n">
-        <v>0</v>
+        <v>4.655254879726027</v>
       </c>
       <c r="I87" s="18" t="n">
-        <v>0</v>
+        <v>5.832086572602739</v>
       </c>
       <c r="J87" s="18" t="n">
-        <v>0</v>
+        <v>6.417121430136986</v>
       </c>
       <c r="K87" s="18" t="n">
-        <v>0</v>
+        <v>8.77408153479452</v>
       </c>
       <c r="L87" s="18" t="n">
-        <v>0</v>
+        <v>8.583901296164385</v>
       </c>
       <c r="M87" s="18" t="n">
-        <v>0</v>
+        <v>9.154841000547945</v>
       </c>
       <c r="N87" s="18" t="n">
-        <v>0</v>
+        <v>8.944136186301371</v>
       </c>
       <c r="O87" s="18" t="n">
-        <v>0</v>
+        <v>9.460467493972605</v>
       </c>
     </row>
     <row r="88" ht="15.5" customHeight="1">
@@ -17327,40 +17327,40 @@
         </is>
       </c>
       <c r="D89" s="18" t="n">
-        <v>0</v>
+        <v>4.076862174812563</v>
       </c>
       <c r="E89" s="18" t="n">
-        <v>0</v>
+        <v>5.136546140690799</v>
       </c>
       <c r="F89" s="18" t="n">
-        <v>0</v>
+        <v>7.106593312526329</v>
       </c>
       <c r="G89" s="18" t="n">
-        <v>0</v>
+        <v>9.439921732930427</v>
       </c>
       <c r="H89" s="18" t="n">
-        <v>0</v>
+        <v>11.32961559959081</v>
       </c>
       <c r="I89" s="18" t="n">
-        <v>0</v>
+        <v>13.72525349785209</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>0</v>
+        <v>15.52438668161796</v>
       </c>
       <c r="K89" s="18" t="n">
-        <v>0</v>
+        <v>18.26268335422273</v>
       </c>
       <c r="L89" s="18" t="n">
-        <v>0</v>
+        <v>18.29035267753856</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>0</v>
+        <v>19.07848189358936</v>
       </c>
       <c r="N89" s="18" t="n">
-        <v>0</v>
+        <v>19.08431735857354</v>
       </c>
       <c r="O89" s="18" t="n">
-        <v>0</v>
+        <v>19.81655038052952</v>
       </c>
     </row>
     <row r="90" ht="15.5" customHeight="1">
@@ -17380,40 +17380,40 @@
         </is>
       </c>
       <c r="D90" s="18" t="n">
-        <v>0</v>
+        <v>6.062201510702974</v>
       </c>
       <c r="E90" s="18" t="n">
-        <v>0</v>
+        <v>7.284124792745594</v>
       </c>
       <c r="F90" s="18" t="n">
-        <v>0</v>
+        <v>9.990851905403042</v>
       </c>
       <c r="G90" s="18" t="n">
-        <v>0</v>
+        <v>13.42906907375234</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>0</v>
+        <v>15.98487047931684</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>0</v>
+        <v>19.55734007045483</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>0</v>
+        <v>21.94150811175495</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>0</v>
+        <v>27.03676488901726</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>0</v>
+        <v>26.87425397370294</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>0</v>
+        <v>28.2333228941373</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>0</v>
+        <v>28.02845354487491</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>0</v>
+        <v>29.27701787450212</v>
       </c>
     </row>
     <row r="91" ht="15.5" customHeight="1">
@@ -17433,40 +17433,40 @@
         </is>
       </c>
       <c r="D91" s="18" t="n">
-        <v>0</v>
+        <v>6.062201510702974</v>
       </c>
       <c r="E91" s="18" t="n">
-        <v>0</v>
+        <v>1.22192328204262</v>
       </c>
       <c r="F91" s="18" t="n">
-        <v>0</v>
+        <v>2.706727112657449</v>
       </c>
       <c r="G91" s="18" t="n">
-        <v>0</v>
+        <v>3.438217168349302</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>0</v>
+        <v>2.555801405564495</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>0</v>
+        <v>3.572469591137988</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>0</v>
+        <v>2.384168041300121</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>0</v>
+        <v>5.095256777262307</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>0</v>
+        <v>-0.1625109153143143</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>0</v>
+        <v>1.35906892043436</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>0</v>
+        <v>-0.2048693492623883</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>0</v>
+        <v>1.248564329627207</v>
       </c>
     </row>
     <row r="92" ht="15.5" customHeight="1">
@@ -17563,40 +17563,40 @@
         </is>
       </c>
       <c r="D93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O93" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94" ht="15.5" customHeight="1">
@@ -17616,40 +17616,40 @@
         </is>
       </c>
       <c r="D94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O94" s="18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95" ht="15.5" customHeight="1">
@@ -17725,37 +17725,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>666.0145702106405</v>
+        <v>693.4822379394992</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>813.7332991847111</v>
+        <v>860.577116236532</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>811.1637879175599</v>
+        <v>879.1432186770032</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>807.6061775022793</v>
+        <v>897.7173363072893</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>803.3287682092756</v>
+        <v>917.7703345475417</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>798.0222307961067</v>
+        <v>935.0767879403747</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>792.1161598529375</v>
+        <v>955.6252974757733</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>784.6017412540926</v>
+        <v>955.8916698246246</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>777.0291923150659</v>
+        <v>961.7605373877268</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>768.9361982744508</v>
+        <v>960.1463768239228</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>760.7989524196353</v>
+        <v>962.0622844499396</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -17828,40 +17828,40 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>82.497508066715</v>
+        <v>101.2074879963281</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>147.7187289740706</v>
+        <v>174.7954487632217</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>-2.569511267151178</v>
+        <v>36.03096862048146</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>-3.557610415280707</v>
+        <v>46.80013191937044</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>-4.277409293003617</v>
+        <v>57.99662387483349</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>-5.306537413168975</v>
+        <v>69.13006858952426</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>-5.906070943169201</v>
+        <v>80.81973626140045</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>-7.514418598844782</v>
+        <v>84.65593414861918</v>
       </c>
       <c r="L98" s="21" t="n">
-        <v>-7.572548939026751</v>
+        <v>88.62647967401134</v>
       </c>
       <c r="M98" s="21" t="n">
-        <v>-8.092994040615043</v>
+        <v>92.27465302600028</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>-8.137245854815596</v>
+        <v>96.40572289720956</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>-8.619874005490272</v>
+        <v>100.2279584852065</v>
       </c>
     </row>
     <row r="99" ht="15.5" customHeight="1">
@@ -17881,40 +17881,40 @@
         </is>
       </c>
       <c r="D99" s="20" t="n">
-        <v>0</v>
+        <v>8.757687799245616</v>
       </c>
       <c r="E99" s="20" t="n">
-        <v>0</v>
+        <v>19.76709726266975</v>
       </c>
       <c r="F99" s="20" t="n">
-        <v>0</v>
+        <v>29.37895087181074</v>
       </c>
       <c r="G99" s="20" t="n">
-        <v>0</v>
+        <v>39.7534164703589</v>
       </c>
       <c r="H99" s="20" t="n">
-        <v>0</v>
+        <v>52.16753317042896</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>0</v>
+        <v>62.61795114157488</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>0</v>
+        <v>76.78333041826616</v>
       </c>
       <c r="K99" s="20" t="n">
-        <v>0</v>
+        <v>79.11957582306793</v>
       </c>
       <c r="L99" s="20" t="n">
-        <v>0</v>
+        <v>88.53231645962288</v>
       </c>
       <c r="M99" s="20" t="n">
-        <v>0</v>
+        <v>90.84253148285657</v>
       </c>
       <c r="N99" s="20" t="n">
-        <v>0</v>
+        <v>96.72036327827925</v>
       </c>
       <c r="O99" s="20" t="n">
-        <v>0</v>
+        <v>99.31625135794938</v>
       </c>
     </row>
     <row r="100" ht="15.5" customHeight="1">
@@ -17934,40 +17934,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>666.0145702106405</v>
+        <v>693.4822379394992</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>813.7332991847111</v>
+        <v>860.577116236532</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>811.1637879175599</v>
+        <v>879.1432186770032</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>807.6061775022793</v>
+        <v>897.7173363072893</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>803.3287682092756</v>
+        <v>917.7703345475417</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>798.0222307961067</v>
+        <v>935.0767879403747</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>792.1161598529375</v>
+        <v>955.6252974757733</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>784.6017412540926</v>
+        <v>955.8916698246246</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>777.0291923150659</v>
+        <v>961.7605373877268</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>768.9361982744508</v>
+        <v>960.1463768239228</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>760.7989524196353</v>
+        <v>962.0622844499396</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>752.179078414145</v>
+        <v>960.3431622627911</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -18099,7 +18099,7 @@
         <v>149.5227458599442</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="G103" s="18" t="n">
         <v>2.842170943040401e-14</v>
@@ -18308,7 +18308,7 @@
         <v>149.5227458599442</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>0</v>
       </c>
       <c r="F107" s="18" t="n">
         <v>2.842170943040401e-14</v>
@@ -20920,40 +20920,40 @@
         </is>
       </c>
       <c r="D43" s="27" t="n">
-        <v>572.3373363741096</v>
+        <v>562.8852636974085</v>
       </c>
       <c r="E43" s="27" t="n">
-        <v>202.5659531256778</v>
+        <v>223.5623695936713</v>
       </c>
       <c r="F43" s="27" t="n">
-        <v>-156.303205586462</v>
+        <v>-131.6521959936532</v>
       </c>
       <c r="G43" s="27" t="n">
-        <v>-542.9413540710418</v>
+        <v>-516.8898164624767</v>
       </c>
       <c r="H43" s="27" t="n">
-        <v>-938.6826928926635</v>
+        <v>-911.4045432716292</v>
       </c>
       <c r="I43" s="27" t="n">
-        <v>-1321.55579598759</v>
+        <v>-1289.639095585492</v>
       </c>
       <c r="J43" s="27" t="n">
-        <v>-1720.874132765303</v>
+        <v>-1687.947495985061</v>
       </c>
       <c r="K43" s="27" t="n">
-        <v>-2131.608974308593</v>
+        <v>-2096.490754007506</v>
       </c>
       <c r="L43" s="27" t="n">
-        <v>-2543.131899161723</v>
+        <v>-2505.492057437021</v>
       </c>
       <c r="M43" s="27" t="n">
-        <v>-2955.674567157466</v>
+        <v>-2915.275088090427</v>
       </c>
       <c r="N43" s="27" t="n">
-        <v>-3369.45011968198</v>
+        <v>-3326.384970319565</v>
       </c>
       <c r="O43" s="27" t="n">
-        <v>-3683.810376368314</v>
+        <v>-3638.185073629627</v>
       </c>
     </row>
     <row r="44">
@@ -20973,40 +20973,40 @@
         </is>
       </c>
       <c r="D44" s="27" t="n">
-        <v>572.3373363741096</v>
+        <v>540.5580595660806</v>
       </c>
       <c r="E44" s="27" t="n">
-        <v>202.5659531256778</v>
+        <v>198.8959688641797</v>
       </c>
       <c r="F44" s="27" t="n">
-        <v>-156.303205586462</v>
+        <v>-159.2907774058233</v>
       </c>
       <c r="G44" s="27" t="n">
-        <v>-542.9413540710418</v>
+        <v>-545.7632588121116</v>
       </c>
       <c r="H44" s="27" t="n">
-        <v>-938.6826928926635</v>
+        <v>-943.0930402916179</v>
       </c>
       <c r="I44" s="27" t="n">
-        <v>-1321.55579598759</v>
+        <v>-1324.081288003446</v>
       </c>
       <c r="J44" s="27" t="n">
-        <v>-1720.874132765303</v>
+        <v>-1725.068522361526</v>
       </c>
       <c r="K44" s="27" t="n">
-        <v>-2131.608974308593</v>
+        <v>-2136.361644384461</v>
       </c>
       <c r="L44" s="27" t="n">
-        <v>-2543.131899161723</v>
+        <v>-2548.056904735283</v>
       </c>
       <c r="M44" s="27" t="n">
-        <v>-2955.674567157466</v>
+        <v>-2960.427985546793</v>
       </c>
       <c r="N44" s="27" t="n">
-        <v>-3369.45011968198</v>
+        <v>-3374.0125092241</v>
       </c>
       <c r="O44" s="27" t="n">
-        <v>-3683.810376368314</v>
+        <v>-3690.167155432418</v>
       </c>
     </row>
     <row r="45">
@@ -21026,40 +21026,40 @@
         </is>
       </c>
       <c r="D45" s="27" t="n">
-        <v>0</v>
+        <v>22.32720413132793</v>
       </c>
       <c r="E45" s="27" t="n">
-        <v>0</v>
+        <v>24.66640072949154</v>
       </c>
       <c r="F45" s="27" t="n">
-        <v>0</v>
+        <v>27.63858141217011</v>
       </c>
       <c r="G45" s="27" t="n">
-        <v>0</v>
+        <v>28.87344234963491</v>
       </c>
       <c r="H45" s="27" t="n">
-        <v>0</v>
+        <v>31.68849701998866</v>
       </c>
       <c r="I45" s="27" t="n">
-        <v>0</v>
+        <v>34.44219241795435</v>
       </c>
       <c r="J45" s="27" t="n">
-        <v>0</v>
+        <v>37.12102637646444</v>
       </c>
       <c r="K45" s="27" t="n">
-        <v>0</v>
+        <v>39.87089037695526</v>
       </c>
       <c r="L45" s="27" t="n">
-        <v>0</v>
+        <v>42.56484729826155</v>
       </c>
       <c r="M45" s="27" t="n">
-        <v>0</v>
+        <v>45.15289745636605</v>
       </c>
       <c r="N45" s="27" t="n">
-        <v>0</v>
+        <v>47.62753890453477</v>
       </c>
       <c r="O45" s="27" t="n">
-        <v>0</v>
+        <v>51.98208180279074</v>
       </c>
     </row>
     <row r="46">
@@ -21132,40 +21132,40 @@
         </is>
       </c>
       <c r="D47" s="27" t="n">
-        <v>818.9846133329333</v>
+        <v>809.5325406562323</v>
       </c>
       <c r="E47" s="27" t="n">
-        <v>730.7831271029125</v>
+        <v>751.7795435709061</v>
       </c>
       <c r="F47" s="27" t="n">
-        <v>641.4935097938865</v>
+        <v>666.1445193866952</v>
       </c>
       <c r="G47" s="27" t="n">
-        <v>512.559518653276</v>
+        <v>538.6110562618411</v>
       </c>
       <c r="H47" s="27" t="n">
-        <v>362.7705749570707</v>
+        <v>390.048724578105</v>
       </c>
       <c r="I47" s="27" t="n">
-        <v>214.2107863911933</v>
+        <v>246.1274867932914</v>
       </c>
       <c r="J47" s="27" t="n">
-        <v>45.57840161890931</v>
+        <v>78.50503839915086</v>
       </c>
       <c r="K47" s="27" t="n">
-        <v>-137.9439579525579</v>
+        <v>-102.8257376514712</v>
       </c>
       <c r="L47" s="27" t="n">
-        <v>-333.4063453495705</v>
+        <v>-295.7665036248691</v>
       </c>
       <c r="M47" s="27" t="n">
-        <v>-540.9272329597457</v>
+        <v>-500.5277538927066</v>
       </c>
       <c r="N47" s="27" t="n">
-        <v>-760.6114110007734</v>
+        <v>-717.5462616383579</v>
       </c>
       <c r="O47" s="27" t="n">
-        <v>-967.3638156124912</v>
+        <v>-921.7385128738042</v>
       </c>
     </row>
     <row r="48">
@@ -21206,7 +21206,7 @@
         <v>-32.93953703702246</v>
       </c>
       <c r="K48" s="27" t="n">
-        <v>-137.9439579525579</v>
+        <v>-137.943957952558</v>
       </c>
       <c r="L48" s="27" t="n">
         <v>-333.406345349571</v>
@@ -21368,7 +21368,7 @@
         <v>-310.5254359695758</v>
       </c>
       <c r="L51" s="27" t="n">
-        <v>-415.5298568851112</v>
+        <v>-415.5298568851113</v>
       </c>
       <c r="M51" s="27" t="n">
         <v>-610.9922442821243</v>
@@ -21556,40 +21556,40 @@
         </is>
       </c>
       <c r="D55" s="27" t="n">
-        <v>0</v>
+        <v>-9.452072676701011</v>
       </c>
       <c r="E55" s="27" t="n">
-        <v>0</v>
+        <v>-10.78286034003542</v>
       </c>
       <c r="F55" s="27" t="n">
-        <v>0</v>
+        <v>-10.79825147671824</v>
       </c>
       <c r="G55" s="27" t="n">
-        <v>0</v>
+        <v>-12.38529528032311</v>
       </c>
       <c r="H55" s="27" t="n">
-        <v>0</v>
+        <v>-13.98058800892375</v>
       </c>
       <c r="I55" s="27" t="n">
-        <v>0</v>
+        <v>-13.75238462681447</v>
       </c>
       <c r="J55" s="27" t="n">
-        <v>0</v>
+        <v>-15.26794026452713</v>
       </c>
       <c r="K55" s="27" t="n">
-        <v>0</v>
+        <v>-17.27074633990449</v>
       </c>
       <c r="L55" s="27" t="n">
-        <v>0</v>
+        <v>-19.50179499215763</v>
       </c>
       <c r="M55" s="27" t="n">
-        <v>0</v>
+        <v>-21.66716322337989</v>
       </c>
       <c r="N55" s="27" t="n">
-        <v>0</v>
+        <v>-23.75491131733089</v>
       </c>
       <c r="O55" s="27" t="n">
-        <v>0</v>
+        <v>-25.75714748317828</v>
       </c>
     </row>
     <row r="56">
@@ -21609,40 +21609,40 @@
         </is>
       </c>
       <c r="D56" s="27" t="n">
-        <v>0</v>
+        <v>-9.452072676701011</v>
       </c>
       <c r="E56" s="27" t="n">
-        <v>0</v>
+        <v>-10.78286034003542</v>
       </c>
       <c r="F56" s="27" t="n">
-        <v>0</v>
+        <v>-10.79825147671824</v>
       </c>
       <c r="G56" s="27" t="n">
-        <v>0</v>
+        <v>-12.38529528032311</v>
       </c>
       <c r="H56" s="27" t="n">
-        <v>0</v>
+        <v>-13.98058800892375</v>
       </c>
       <c r="I56" s="27" t="n">
-        <v>0</v>
+        <v>-13.75238462681447</v>
       </c>
       <c r="J56" s="27" t="n">
-        <v>0</v>
+        <v>-15.26794026452713</v>
       </c>
       <c r="K56" s="27" t="n">
-        <v>0</v>
+        <v>-17.27074633990449</v>
       </c>
       <c r="L56" s="27" t="n">
-        <v>0</v>
+        <v>-19.50179499215763</v>
       </c>
       <c r="M56" s="27" t="n">
-        <v>0</v>
+        <v>-21.66716322337989</v>
       </c>
       <c r="N56" s="27" t="n">
-        <v>0</v>
+        <v>-23.75491131733089</v>
       </c>
       <c r="O56" s="27" t="n">
-        <v>0</v>
+        <v>-25.75714748317828</v>
       </c>
     </row>
     <row r="57">
@@ -21715,40 +21715,40 @@
         </is>
       </c>
       <c r="D58" s="27" t="n">
-        <v>818.9846133329333</v>
+        <v>809.5325406562323</v>
       </c>
       <c r="E58" s="27" t="n">
-        <v>730.7831271029124</v>
+        <v>720.000266762877</v>
       </c>
       <c r="F58" s="27" t="n">
-        <v>641.4935097938862</v>
+        <v>630.6952583171679</v>
       </c>
       <c r="G58" s="27" t="n">
-        <v>512.5595186532757</v>
+        <v>500.1742233729526</v>
       </c>
       <c r="H58" s="27" t="n">
-        <v>362.7705749570706</v>
+        <v>348.7899869481469</v>
       </c>
       <c r="I58" s="27" t="n">
-        <v>214.2107863911931</v>
+        <v>200.4584017643787</v>
       </c>
       <c r="J58" s="27" t="n">
-        <v>45.57840161890913</v>
+        <v>30.310461354382</v>
       </c>
       <c r="K58" s="27" t="n">
-        <v>-137.943957952558</v>
+        <v>-155.2147042924625</v>
       </c>
       <c r="L58" s="27" t="n">
-        <v>-333.406345349571</v>
+        <v>-352.9081403417287</v>
       </c>
       <c r="M58" s="27" t="n">
-        <v>-540.9272329597459</v>
+        <v>-562.5943961831258</v>
       </c>
       <c r="N58" s="27" t="n">
-        <v>-760.6114110007743</v>
+        <v>-784.3663223181051</v>
       </c>
       <c r="O58" s="27" t="n">
-        <v>-967.3638156124923</v>
+        <v>-993.1209630956705</v>
       </c>
     </row>
     <row r="59">
@@ -21771,37 +21771,37 @@
         <v>0</v>
       </c>
       <c r="E59" s="27" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>31.77927680802907</v>
       </c>
       <c r="F59" s="27" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>35.44926106952721</v>
       </c>
       <c r="G59" s="27" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>38.43683288888849</v>
       </c>
       <c r="H59" s="27" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>41.25873762995809</v>
       </c>
       <c r="I59" s="27" t="n">
-        <v>1.989519660128281e-13</v>
+        <v>45.66908502891269</v>
       </c>
       <c r="J59" s="27" t="n">
-        <v>1.84741111297626e-13</v>
+        <v>48.19457704476886</v>
       </c>
       <c r="K59" s="27" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>52.38896664099136</v>
       </c>
       <c r="L59" s="27" t="n">
-        <v>5.115907697472721e-13</v>
+        <v>57.14163671685964</v>
       </c>
       <c r="M59" s="27" t="n">
-        <v>2.273736754432321e-13</v>
+        <v>62.06664229041917</v>
       </c>
       <c r="N59" s="27" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>66.82006067974714</v>
       </c>
       <c r="O59" s="27" t="n">
-        <v>1.13686837721616e-12</v>
+        <v>71.38245022186629</v>
       </c>
     </row>
     <row r="60">
@@ -21980,40 +21980,40 @@
         </is>
       </c>
       <c r="D63" s="27" t="n">
-        <v>0</v>
+        <v>-31.77927680802894</v>
       </c>
       <c r="E63" s="27" t="n">
-        <v>0</v>
+        <v>-3.669984261498016</v>
       </c>
       <c r="F63" s="27" t="n">
-        <v>0</v>
+        <v>-2.987571819361392</v>
       </c>
       <c r="G63" s="27" t="n">
-        <v>0</v>
+        <v>-2.821904741069673</v>
       </c>
       <c r="H63" s="27" t="n">
-        <v>0</v>
+        <v>-4.410347398954386</v>
       </c>
       <c r="I63" s="27" t="n">
-        <v>0</v>
+        <v>-2.525492015856408</v>
       </c>
       <c r="J63" s="27" t="n">
-        <v>0</v>
+        <v>-4.194389596222756</v>
       </c>
       <c r="K63" s="27" t="n">
-        <v>0</v>
+        <v>-4.752670075868181</v>
       </c>
       <c r="L63" s="27" t="n">
-        <v>0</v>
+        <v>-4.925005573559432</v>
       </c>
       <c r="M63" s="27" t="n">
-        <v>0</v>
+        <v>-4.753418389326754</v>
       </c>
       <c r="N63" s="27" t="n">
-        <v>0</v>
+        <v>-4.562389542119732</v>
       </c>
       <c r="O63" s="27" t="n">
-        <v>0</v>
+        <v>-6.356779064103364</v>
       </c>
     </row>
     <row r="64">
@@ -22033,40 +22033,40 @@
         </is>
       </c>
       <c r="D64" s="27" t="n">
-        <v>-61.5707551053894</v>
+        <v>-93.35003191341833</v>
       </c>
       <c r="E64" s="27" t="n">
-        <v>-71.38134852051837</v>
+        <v>-75.05133278201639</v>
       </c>
       <c r="F64" s="27" t="n">
-        <v>-63.45972433150565</v>
+        <v>-66.44729615086705</v>
       </c>
       <c r="G64" s="27" t="n">
-        <v>-94.18450844775204</v>
+        <v>-97.00641318882171</v>
       </c>
       <c r="H64" s="27" t="n">
-        <v>-106.2089351851622</v>
+        <v>-110.6192825841165</v>
       </c>
       <c r="I64" s="27" t="n">
-        <v>-96.23762349483168</v>
+        <v>-98.7631155106881</v>
       </c>
       <c r="J64" s="27" t="n">
-        <v>-107.8055103754596</v>
+        <v>-111.9998999716823</v>
       </c>
       <c r="K64" s="27" t="n">
-        <v>-114.4247982226237</v>
+        <v>-119.1774682984918</v>
       </c>
       <c r="L64" s="27" t="n">
-        <v>-118.1768819656708</v>
+        <v>-123.1018875392302</v>
       </c>
       <c r="M64" s="27" t="n">
-        <v>-122.1292855371588</v>
+        <v>-126.8827039264855</v>
       </c>
       <c r="N64" s="27" t="n">
-        <v>-126.2675918095151</v>
+        <v>-130.8299813516348</v>
       </c>
       <c r="O64" s="27" t="n">
-        <v>-107.4429819594362</v>
+        <v>-113.7997610235396</v>
       </c>
     </row>
     <row r="65">
@@ -22192,40 +22192,40 @@
         </is>
       </c>
       <c r="D67" s="27" t="n">
-        <v>-315.937540210061</v>
+        <v>-347.7168170180899</v>
       </c>
       <c r="E67" s="27" t="n">
-        <v>-369.7713832484318</v>
+        <v>-373.4413675099298</v>
       </c>
       <c r="F67" s="27" t="n">
-        <v>-358.8691587121397</v>
+        <v>-361.8567305315011</v>
       </c>
       <c r="G67" s="27" t="n">
-        <v>-386.6381484845799</v>
+        <v>-389.4600532256496</v>
       </c>
       <c r="H67" s="27" t="n">
-        <v>-395.7413388216216</v>
+        <v>-400.151686220576</v>
       </c>
       <c r="I67" s="27" t="n">
-        <v>-382.8731030949266</v>
+        <v>-385.398595110783</v>
       </c>
       <c r="J67" s="27" t="n">
-        <v>-399.3183367777129</v>
+        <v>-403.5127263739357</v>
       </c>
       <c r="K67" s="27" t="n">
-        <v>-410.7348415432899</v>
+        <v>-415.4875116191581</v>
       </c>
       <c r="L67" s="27" t="n">
-        <v>-411.5229248531302</v>
+        <v>-416.4479304266897</v>
       </c>
       <c r="M67" s="27" t="n">
-        <v>-412.5426679957437</v>
+        <v>-417.2960863850705</v>
       </c>
       <c r="N67" s="27" t="n">
-        <v>-413.7755525245141</v>
+        <v>-418.3379420666338</v>
       </c>
       <c r="O67" s="27" t="n">
-        <v>-314.3602566863339</v>
+        <v>-320.7170357504372</v>
       </c>
     </row>
     <row r="68">
@@ -22616,40 +22616,40 @@
         </is>
       </c>
       <c r="D75" s="27" t="n">
-        <v>572.3373363741096</v>
+        <v>540.5580595660806</v>
       </c>
       <c r="E75" s="27" t="n">
-        <v>-369.7713832484318</v>
+        <v>-373.4413675099298</v>
       </c>
       <c r="F75" s="27" t="n">
-        <v>-358.8691587121397</v>
+        <v>-361.8567305315011</v>
       </c>
       <c r="G75" s="27" t="n">
-        <v>-386.6381484845799</v>
+        <v>-389.4600532256496</v>
       </c>
       <c r="H75" s="27" t="n">
-        <v>-395.7413388216216</v>
+        <v>-400.151686220576</v>
       </c>
       <c r="I75" s="27" t="n">
-        <v>-382.8731030949266</v>
+        <v>-385.398595110783</v>
       </c>
       <c r="J75" s="27" t="n">
-        <v>-399.3183367777129</v>
+        <v>-403.5127263739357</v>
       </c>
       <c r="K75" s="27" t="n">
-        <v>-410.7348415432899</v>
+        <v>-415.4875116191581</v>
       </c>
       <c r="L75" s="27" t="n">
-        <v>-411.5229248531302</v>
+        <v>-416.4479304266897</v>
       </c>
       <c r="M75" s="27" t="n">
-        <v>-412.5426679957437</v>
+        <v>-417.2960863850705</v>
       </c>
       <c r="N75" s="27" t="n">
-        <v>-413.7755525245141</v>
+        <v>-418.3379420666338</v>
       </c>
       <c r="O75" s="27" t="n">
-        <v>-314.3602566863339</v>
+        <v>-320.7170357504372</v>
       </c>
     </row>
     <row r="76">
@@ -22672,37 +22672,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="27" t="n">
-        <v>572.3373363741096</v>
+        <v>540.5580595660806</v>
       </c>
       <c r="F76" s="27" t="n">
-        <v>202.5659531256778</v>
+        <v>198.8959688641797</v>
       </c>
       <c r="G76" s="27" t="n">
-        <v>-156.303205586462</v>
+        <v>-159.2907774058233</v>
       </c>
       <c r="H76" s="27" t="n">
-        <v>-542.9413540710418</v>
+        <v>-545.7632588121116</v>
       </c>
       <c r="I76" s="27" t="n">
-        <v>-938.6826928926635</v>
+        <v>-943.0930402916179</v>
       </c>
       <c r="J76" s="27" t="n">
-        <v>-1321.55579598759</v>
+        <v>-1324.081288003446</v>
       </c>
       <c r="K76" s="27" t="n">
-        <v>-1720.874132765303</v>
+        <v>-1725.068522361526</v>
       </c>
       <c r="L76" s="27" t="n">
-        <v>-2131.608974308593</v>
+        <v>-2136.361644384461</v>
       </c>
       <c r="M76" s="27" t="n">
-        <v>-2543.131899161723</v>
+        <v>-2548.056904735283</v>
       </c>
       <c r="N76" s="27" t="n">
-        <v>-2955.674567157466</v>
+        <v>-2960.427985546793</v>
       </c>
       <c r="O76" s="27" t="n">
-        <v>-3369.45011968198</v>
+        <v>-3374.0125092241</v>
       </c>
     </row>
     <row r="77">
@@ -22722,40 +22722,40 @@
         </is>
       </c>
       <c r="D77" s="27" t="n">
-        <v>572.3373363741096</v>
+        <v>540.5580595660806</v>
       </c>
       <c r="E77" s="27" t="n">
-        <v>-369.7713832484318</v>
+        <v>-373.4413675099298</v>
       </c>
       <c r="F77" s="27" t="n">
-        <v>-358.8691587121397</v>
+        <v>-361.8567305315011</v>
       </c>
       <c r="G77" s="27" t="n">
-        <v>-386.6381484845799</v>
+        <v>-389.4600532256496</v>
       </c>
       <c r="H77" s="27" t="n">
-        <v>-395.7413388216216</v>
+        <v>-400.151686220576</v>
       </c>
       <c r="I77" s="27" t="n">
-        <v>-382.8731030949266</v>
+        <v>-385.398595110783</v>
       </c>
       <c r="J77" s="27" t="n">
-        <v>-399.3183367777129</v>
+        <v>-403.5127263739357</v>
       </c>
       <c r="K77" s="27" t="n">
-        <v>-410.7348415432899</v>
+        <v>-415.4875116191581</v>
       </c>
       <c r="L77" s="27" t="n">
-        <v>-411.5229248531302</v>
+        <v>-416.4479304266897</v>
       </c>
       <c r="M77" s="27" t="n">
-        <v>-412.5426679957437</v>
+        <v>-417.2960863850705</v>
       </c>
       <c r="N77" s="27" t="n">
-        <v>-413.7755525245141</v>
+        <v>-418.3379420666338</v>
       </c>
       <c r="O77" s="27" t="n">
-        <v>-314.3602566863339</v>
+        <v>-320.7170357504372</v>
       </c>
     </row>
     <row r="78">
@@ -22775,40 +22775,40 @@
         </is>
       </c>
       <c r="D78" s="27" t="n">
-        <v>572.3373363741096</v>
+        <v>540.5580595660806</v>
       </c>
       <c r="E78" s="27" t="n">
-        <v>202.5659531256778</v>
+        <v>198.8959688641797</v>
       </c>
       <c r="F78" s="27" t="n">
-        <v>-156.303205586462</v>
+        <v>-159.2907774058233</v>
       </c>
       <c r="G78" s="27" t="n">
-        <v>-542.9413540710418</v>
+        <v>-545.7632588121116</v>
       </c>
       <c r="H78" s="27" t="n">
-        <v>-938.6826928926635</v>
+        <v>-943.0930402916179</v>
       </c>
       <c r="I78" s="27" t="n">
-        <v>-1321.55579598759</v>
+        <v>-1324.081288003446</v>
       </c>
       <c r="J78" s="27" t="n">
-        <v>-1720.874132765303</v>
+        <v>-1725.068522361526</v>
       </c>
       <c r="K78" s="27" t="n">
-        <v>-2131.608974308593</v>
+        <v>-2136.361644384461</v>
       </c>
       <c r="L78" s="27" t="n">
-        <v>-2543.131899161723</v>
+        <v>-2548.056904735283</v>
       </c>
       <c r="M78" s="27" t="n">
-        <v>-2955.674567157466</v>
+        <v>-2960.427985546793</v>
       </c>
       <c r="N78" s="27" t="n">
-        <v>-3369.45011968198</v>
+        <v>-3374.0125092241</v>
       </c>
       <c r="O78" s="27" t="n">
-        <v>-3683.810376368314</v>
+        <v>-3690.167155432418</v>
       </c>
     </row>
     <row r="79">
@@ -23252,40 +23252,40 @@
         </is>
       </c>
       <c r="D87" s="27" t="n">
-        <v>0</v>
+        <v>22.32720413132793</v>
       </c>
       <c r="E87" s="27" t="n">
-        <v>0</v>
+        <v>24.66640072949154</v>
       </c>
       <c r="F87" s="27" t="n">
-        <v>0</v>
+        <v>27.63858141217011</v>
       </c>
       <c r="G87" s="27" t="n">
-        <v>0</v>
+        <v>28.87344234963491</v>
       </c>
       <c r="H87" s="27" t="n">
-        <v>0</v>
+        <v>31.68849701998866</v>
       </c>
       <c r="I87" s="27" t="n">
-        <v>0</v>
+        <v>34.44219241795435</v>
       </c>
       <c r="J87" s="27" t="n">
-        <v>0</v>
+        <v>37.12102637646444</v>
       </c>
       <c r="K87" s="27" t="n">
-        <v>0</v>
+        <v>39.87089037695526</v>
       </c>
       <c r="L87" s="27" t="n">
-        <v>0</v>
+        <v>42.56484729826155</v>
       </c>
       <c r="M87" s="27" t="n">
-        <v>0</v>
+        <v>45.15289745636605</v>
       </c>
       <c r="N87" s="27" t="n">
-        <v>0</v>
+        <v>47.62753890453477</v>
       </c>
       <c r="O87" s="27" t="n">
-        <v>0</v>
+        <v>51.98208180279074</v>
       </c>
     </row>
     <row r="88">
@@ -23358,40 +23358,40 @@
         </is>
       </c>
       <c r="D89" s="27" t="n">
-        <v>0</v>
+        <v>9.452072676701011</v>
       </c>
       <c r="E89" s="27" t="n">
-        <v>0</v>
+        <v>10.78286034003542</v>
       </c>
       <c r="F89" s="27" t="n">
-        <v>0</v>
+        <v>10.79825147671824</v>
       </c>
       <c r="G89" s="27" t="n">
-        <v>0</v>
+        <v>12.38529528032311</v>
       </c>
       <c r="H89" s="27" t="n">
-        <v>0</v>
+        <v>13.98058800892375</v>
       </c>
       <c r="I89" s="27" t="n">
-        <v>0</v>
+        <v>13.75238462681447</v>
       </c>
       <c r="J89" s="27" t="n">
-        <v>0</v>
+        <v>15.26794026452713</v>
       </c>
       <c r="K89" s="27" t="n">
-        <v>0</v>
+        <v>17.27074633990449</v>
       </c>
       <c r="L89" s="27" t="n">
-        <v>0</v>
+        <v>19.50179499215763</v>
       </c>
       <c r="M89" s="27" t="n">
-        <v>0</v>
+        <v>21.66716322337989</v>
       </c>
       <c r="N89" s="27" t="n">
-        <v>0</v>
+        <v>23.75491131733089</v>
       </c>
       <c r="O89" s="27" t="n">
-        <v>0</v>
+        <v>25.75714748317828</v>
       </c>
     </row>
     <row r="90">
@@ -23411,40 +23411,40 @@
         </is>
       </c>
       <c r="D90" s="27" t="n">
-        <v>0</v>
+        <v>31.77927680802894</v>
       </c>
       <c r="E90" s="27" t="n">
-        <v>0</v>
+        <v>35.44926106952695</v>
       </c>
       <c r="F90" s="27" t="n">
-        <v>0</v>
+        <v>38.43683288888835</v>
       </c>
       <c r="G90" s="27" t="n">
-        <v>0</v>
+        <v>41.25873762995802</v>
       </c>
       <c r="H90" s="27" t="n">
-        <v>0</v>
+        <v>45.66908502891241</v>
       </c>
       <c r="I90" s="27" t="n">
-        <v>0</v>
+        <v>48.19457704476881</v>
       </c>
       <c r="J90" s="27" t="n">
-        <v>0</v>
+        <v>52.38896664099157</v>
       </c>
       <c r="K90" s="27" t="n">
-        <v>0</v>
+        <v>57.14163671685975</v>
       </c>
       <c r="L90" s="27" t="n">
-        <v>0</v>
+        <v>62.06664229041918</v>
       </c>
       <c r="M90" s="27" t="n">
-        <v>0</v>
+        <v>66.82006067974594</v>
       </c>
       <c r="N90" s="27" t="n">
-        <v>0</v>
+        <v>71.38245022186567</v>
       </c>
       <c r="O90" s="27" t="n">
-        <v>0</v>
+        <v>77.73922928596903</v>
       </c>
     </row>
     <row r="91">
@@ -23464,40 +23464,40 @@
         </is>
       </c>
       <c r="D91" s="27" t="n">
-        <v>0</v>
+        <v>31.77927680802894</v>
       </c>
       <c r="E91" s="27" t="n">
-        <v>0</v>
+        <v>3.669984261498016</v>
       </c>
       <c r="F91" s="27" t="n">
-        <v>0</v>
+        <v>2.987571819361392</v>
       </c>
       <c r="G91" s="27" t="n">
-        <v>0</v>
+        <v>2.821904741069673</v>
       </c>
       <c r="H91" s="27" t="n">
-        <v>0</v>
+        <v>4.410347398954386</v>
       </c>
       <c r="I91" s="27" t="n">
-        <v>0</v>
+        <v>2.525492015856408</v>
       </c>
       <c r="J91" s="27" t="n">
-        <v>0</v>
+        <v>4.194389596222756</v>
       </c>
       <c r="K91" s="27" t="n">
-        <v>0</v>
+        <v>4.752670075868181</v>
       </c>
       <c r="L91" s="27" t="n">
-        <v>0</v>
+        <v>4.925005573559432</v>
       </c>
       <c r="M91" s="27" t="n">
-        <v>0</v>
+        <v>4.753418389326754</v>
       </c>
       <c r="N91" s="27" t="n">
-        <v>0</v>
+        <v>4.562389542119732</v>
       </c>
       <c r="O91" s="27" t="n">
-        <v>0</v>
+        <v>6.356779064103364</v>
       </c>
     </row>
     <row r="92">
@@ -23594,40 +23594,40 @@
         </is>
       </c>
       <c r="D93" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E93" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F93" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G93" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H93" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I93" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J93" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K93" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L93" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M93" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N93" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O93" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94">
@@ -23647,40 +23647,40 @@
         </is>
       </c>
       <c r="D94" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E94" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F94" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G94" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H94" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I94" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J94" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K94" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L94" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M94" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N94" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O94" s="27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95">
@@ -23759,19 +23759,19 @@
         <v>275.6992086588986</v>
       </c>
       <c r="F96" s="29" t="n">
-        <v>266.5668291650028</v>
+        <v>266.5668291650029</v>
       </c>
       <c r="G96" s="29" t="n">
-        <v>255.556501977711</v>
+        <v>255.5565019777109</v>
       </c>
       <c r="H96" s="29" t="n">
-        <v>204.1185575818447</v>
+        <v>204.1185575818448</v>
       </c>
       <c r="I96" s="29" t="n">
         <v>131.0515746159068</v>
       </c>
       <c r="J96" s="29" t="n">
-        <v>58.44610319579627</v>
+        <v>58.44610319579624</v>
       </c>
       <c r="K96" s="29" t="n">
         <v>-32.93953703702253</v>
@@ -23780,10 +23780,10 @@
         <v>-137.943957952558</v>
       </c>
       <c r="M96" s="29" t="n">
-        <v>-333.406345349571</v>
+        <v>-333.4063453495711</v>
       </c>
       <c r="N96" s="29" t="n">
-        <v>-540.927232959746</v>
+        <v>-540.9272329597459</v>
       </c>
       <c r="O96" s="29" t="n">
         <v>-760.6114110007743</v>
@@ -23968,19 +23968,19 @@
         <v>275.6992086588986</v>
       </c>
       <c r="E100" s="29" t="n">
-        <v>266.5668291650028</v>
+        <v>266.5668291650029</v>
       </c>
       <c r="F100" s="29" t="n">
-        <v>255.556501977711</v>
+        <v>255.5565019777109</v>
       </c>
       <c r="G100" s="29" t="n">
-        <v>204.1185575818447</v>
+        <v>204.1185575818448</v>
       </c>
       <c r="H100" s="29" t="n">
         <v>131.0515746159068</v>
       </c>
       <c r="I100" s="29" t="n">
-        <v>58.44610319579627</v>
+        <v>58.44610319579624</v>
       </c>
       <c r="J100" s="29" t="n">
         <v>-32.93953703702253</v>
@@ -23989,10 +23989,10 @@
         <v>-137.943957952558</v>
       </c>
       <c r="L100" s="29" t="n">
-        <v>-333.406345349571</v>
+        <v>-333.4063453495711</v>
       </c>
       <c r="M100" s="29" t="n">
-        <v>-540.927232959746</v>
+        <v>-540.9272329597459</v>
       </c>
       <c r="N100" s="29" t="n">
         <v>-760.6114110007743</v>

--- a/backend/Rwanda/financial-statements-CleanStep.xlsx
+++ b/backend/Rwanda/financial-statements-CleanStep.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="1" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity (Only E-Cooking)" sheetId="1" state="visible" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="Electricity (Low access)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1" iterate="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" iterate="1"/>
 </workbook>
 </file>
 
@@ -654,28 +654,28 @@
         </is>
       </c>
       <c r="D2" s="18" t="n">
-        <v>0</v>
+        <v>10.44257396619059</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>0</v>
+        <v>18.77752005002456</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>0</v>
+        <v>18.58974617641432</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>0</v>
+        <v>18.40384803110078</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>0</v>
+        <v>18.21981087767979</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>0</v>
+        <v>18.03761212556238</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>0</v>
+        <v>25.91973246371354</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>0</v>
+        <v>33.68262082722723</v>
       </c>
       <c r="L2" s="18" t="n">
         <v>0</v>
@@ -710,28 +710,28 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>0</v>
+        <v>79.81696955960882</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>0</v>
+        <v>-0.9999929336248825</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>0</v>
+        <v>-1.000003677023853</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>0</v>
+        <v>-0.9999927901490069</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>0</v>
+        <v>-1.000003530995031</v>
       </c>
       <c r="J3" s="18" t="n">
-        <v>0</v>
+        <v>43.69824721411355</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>0</v>
+        <v>29.94972411224297</v>
       </c>
       <c r="L3" s="18" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M3" s="18" t="n">
         <v>0</v>
@@ -866,28 +866,28 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>0</v>
+        <v>10.44257396619059</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>0</v>
+        <v>18.77752005002456</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>0</v>
+        <v>18.58974617641432</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0</v>
+        <v>18.40384803110078</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>0</v>
+        <v>18.21981087767979</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>0</v>
+        <v>18.03761212556238</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>0</v>
+        <v>25.91973246371354</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>0</v>
+        <v>33.68262082722723</v>
       </c>
       <c r="L6" s="18" t="n">
         <v>0</v>
@@ -922,28 +922,28 @@
         <v>0</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>0</v>
+        <v>79.81696955960882</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>0</v>
+        <v>-0.9999929336248825</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>0</v>
+        <v>-1.000003677023853</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>0</v>
+        <v>-0.9999927901490069</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>0</v>
+        <v>-1.000003530995031</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>0</v>
+        <v>43.69824721411355</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>0</v>
+        <v>29.94972411224297</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M7" s="18" t="n">
         <v>0</v>
@@ -972,28 +972,28 @@
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8" s="18" t="n">
         <v>0</v>
@@ -1449,28 +1449,28 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>0</v>
+        <v>19.31669326643227</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>0</v>
+        <v>35.53520377074922</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>0</v>
+        <v>60.7944426237273</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>0</v>
+        <v>86.05368720929654</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>0</v>
+        <v>111.3129214302981</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>0</v>
+        <v>136.5721667893791</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>0</v>
+        <v>111.4927267399446</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>0</v>
+        <v>92.51295293436471</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>0</v>
@@ -1661,28 +1661,28 @@
         </is>
       </c>
       <c r="D21" s="18" t="n">
-        <v>-2.017159982169346</v>
+        <v>8.42541398402124</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>-6.672630012869519</v>
+        <v>12.10489003715504</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>-11.30153257311675</v>
+        <v>7.288213603297578</v>
       </c>
       <c r="G21" s="18" t="n">
-        <v>-15.83718981915774</v>
+        <v>2.566658211943036</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>-20.28100376702062</v>
+        <v>-2.06119288934083</v>
       </c>
       <c r="I21" s="18" t="n">
-        <v>-24.63435771694432</v>
+        <v>-6.596745591381946</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>-28.89861648749286</v>
+        <v>-2.978884023779315</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>-31.16078715295325</v>
+        <v>2.521833674273978</v>
       </c>
       <c r="L21" s="18" t="n">
         <v>-31.3881318749203</v>
@@ -1767,28 +1767,28 @@
         </is>
       </c>
       <c r="D23" s="18" t="n">
-        <v>0</v>
+        <v>80.68330673356773</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>0</v>
+        <v>64.46479622925079</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>0</v>
+        <v>39.2055573762727</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>0</v>
+        <v>13.94631279070347</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>0</v>
+        <v>-11.31292143029815</v>
       </c>
       <c r="I23" s="18" t="n">
-        <v>0</v>
+        <v>-36.57216678937913</v>
       </c>
       <c r="J23" s="18" t="n">
-        <v>0</v>
+        <v>-11.49272673994463</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>0</v>
+        <v>7.487047065635292</v>
       </c>
       <c r="L23" s="18" t="n">
         <v>0</v>
@@ -1820,28 +1820,28 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>0</v>
+        <v>-19.31669326643227</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>0</v>
+        <v>-35.53520377074922</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>0</v>
+        <v>-60.7944426237273</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>0</v>
+        <v>-86.05368720929654</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>0</v>
+        <v>-111.3129214302981</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>0</v>
+        <v>-136.5721667893791</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>0</v>
+        <v>-111.4927267399446</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>0</v>
+        <v>-92.51295293436471</v>
       </c>
       <c r="L24" s="18" t="n">
         <v>0</v>
@@ -1876,7 +1876,7 @@
         <v>-1.212227607556091</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>-3.399513732529481</v>
+        <v>-3.399513732529485</v>
       </c>
       <c r="F25" s="18" t="n">
         <v>-5.564926996253149</v>
@@ -1885,16 +1885,16 @@
         <v>-7.708686127339575</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>-9.831007667115124</v>
+        <v>-9.831007667115131</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>-11.93210599149295</v>
+        <v>-11.93210599149294</v>
       </c>
       <c r="J25" s="18" t="n">
         <v>-14.95702181595101</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>-18.89178095329243</v>
+        <v>-18.89178095329241</v>
       </c>
       <c r="L25" s="18" t="n">
         <v>-22.78719249926041</v>
@@ -1903,10 +1903,10 @@
         <v>-26.64364992976874</v>
       </c>
       <c r="N25" s="18" t="n">
-        <v>-30.46154278597193</v>
+        <v>-30.46154278597196</v>
       </c>
       <c r="O25" s="18" t="n">
-        <v>-32.80994723124032</v>
+        <v>-32.80994723124034</v>
       </c>
     </row>
     <row r="26" ht="15.5" customHeight="1">
@@ -1926,28 +1926,28 @@
         </is>
       </c>
       <c r="D26" s="19" t="n">
-        <v>0</v>
+        <v>11.60851348988153</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>0</v>
+        <v>18.10416776801704</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>0</v>
+        <v>29.93546519378318</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>0</v>
+        <v>41.886273535364</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>0</v>
+        <v>53.95779206006262</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>0</v>
+        <v>66.15125055595972</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>0</v>
+        <v>57.70515508557106</v>
       </c>
       <c r="K26" s="19" t="n">
-        <v>0</v>
+        <v>56.0876217150576</v>
       </c>
       <c r="L26" s="19" t="n">
         <v>0</v>
@@ -1979,28 +1979,28 @@
         </is>
       </c>
       <c r="D27" s="19" t="n">
-        <v>-3.229387589725437</v>
+        <v>7.213186376465149</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>-10.072143745399</v>
+        <v>8.70537630462556</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>-16.86645956936989</v>
+        <v>1.723286607044429</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>-23.54587594649732</v>
+        <v>-5.14202791539654</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>-30.11201143413574</v>
+        <v>-11.89220055645596</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>-36.56646370843727</v>
+        <v>-18.52885158287489</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>-43.85563830344387</v>
+        <v>-17.93590583973032</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>-50.05256810624567</v>
+        <v>-16.36994727901843</v>
       </c>
       <c r="L27" s="19" t="n">
         <v>-54.17532437418072</v>
@@ -2009,10 +2009,10 @@
         <v>-58.25146355350154</v>
       </c>
       <c r="N27" s="19" t="n">
-        <v>-62.28150571035341</v>
+        <v>-62.28150571035344</v>
       </c>
       <c r="O27" s="19" t="n">
-        <v>-64.83465568889524</v>
+        <v>-64.83465568889527</v>
       </c>
     </row>
     <row r="28" ht="15.5" customHeight="1">
@@ -2032,28 +2032,28 @@
         </is>
       </c>
       <c r="D28" s="19" t="n">
-        <v>0</v>
+        <v>69.0747932436862</v>
       </c>
       <c r="E28" s="19" t="n">
-        <v>0</v>
+        <v>46.36062846123374</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>0</v>
+        <v>9.270092182489522</v>
       </c>
       <c r="G28" s="19" t="n">
-        <v>0</v>
+        <v>-27.93996074466054</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>0</v>
+        <v>-65.27071349036076</v>
       </c>
       <c r="I28" s="19" t="n">
-        <v>0</v>
+        <v>-102.7234173453388</v>
       </c>
       <c r="J28" s="19" t="n">
-        <v>0</v>
+        <v>-69.19788182551569</v>
       </c>
       <c r="K28" s="19" t="n">
-        <v>0</v>
+        <v>-48.60057464942231</v>
       </c>
       <c r="L28" s="19" t="n">
         <v>0</v>
@@ -2138,28 +2138,28 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>-3.229387589725437</v>
+        <v>7.213186376465149</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>-10.072143745399</v>
+        <v>8.70537630462556</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>-16.86645956936989</v>
+        <v>1.723286607044429</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>-23.54587594649732</v>
+        <v>-5.14202791539654</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>-30.11201143413574</v>
+        <v>-11.89220055645596</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>-36.56646370843727</v>
+        <v>-18.52885158287489</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>-43.85563830344387</v>
+        <v>-17.93590583973032</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>-50.05256810624567</v>
+        <v>-16.36994727901843</v>
       </c>
       <c r="L30" s="19" t="n">
         <v>-54.17532437418072</v>
@@ -2168,10 +2168,10 @@
         <v>-58.25146355350154</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>-62.28150571035341</v>
+        <v>-62.28150571035344</v>
       </c>
       <c r="O30" s="19" t="n">
-        <v>-64.83465568889524</v>
+        <v>-64.83465568889527</v>
       </c>
     </row>
     <row r="31" ht="15.5" customHeight="1">
@@ -2203,16 +2203,16 @@
         <v>-23.54587594649732</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>-30.11201143413574</v>
+        <v>-30.11201143413575</v>
       </c>
       <c r="I31" s="19" t="n">
-        <v>-36.56646370843727</v>
+        <v>-36.56646370843726</v>
       </c>
       <c r="J31" s="19" t="n">
         <v>-43.85563830344387</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>-50.05256810624567</v>
+        <v>-50.05256810624566</v>
       </c>
       <c r="L31" s="19" t="n">
         <v>-54.17532437418072</v>
@@ -2221,10 +2221,10 @@
         <v>-58.25146355350154</v>
       </c>
       <c r="N31" s="19" t="n">
-        <v>-62.28150571035341</v>
+        <v>-62.28150571035344</v>
       </c>
       <c r="O31" s="19" t="n">
-        <v>-64.83465568889524</v>
+        <v>-64.83465568889527</v>
       </c>
     </row>
     <row r="32" ht="15.5" customHeight="1">
@@ -2356,7 +2356,7 @@
         <v>-13.30153133512444</v>
       </c>
       <c r="F34" s="19" t="n">
-        <v>-30.16799090449433</v>
+        <v>-30.16799090449434</v>
       </c>
       <c r="G34" s="19" t="n">
         <v>-53.71386685099165</v>
@@ -2368,7 +2368,7 @@
         <v>-120.3923419935647</v>
       </c>
       <c r="J34" s="19" t="n">
-        <v>-164.2479802970086</v>
+        <v>-164.2479802970085</v>
       </c>
       <c r="K34" s="19" t="n">
         <v>-214.3005484032542</v>
@@ -2383,7 +2383,7 @@
         <v>-389.0088420412899</v>
       </c>
       <c r="O34" s="19" t="n">
-        <v>-453.8434977301851</v>
+        <v>-453.8434977301852</v>
       </c>
     </row>
     <row r="35" ht="15.5" customHeight="1">
@@ -2403,28 +2403,28 @@
         </is>
       </c>
       <c r="D35" s="19" t="n">
-        <v>-3.229387589725437</v>
+        <v>7.213186376465149</v>
       </c>
       <c r="E35" s="19" t="n">
-        <v>-10.072143745399</v>
+        <v>8.70537630462556</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>-16.86645956936989</v>
+        <v>1.723286607044429</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>-23.54587594649732</v>
+        <v>-5.14202791539654</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>-30.11201143413574</v>
+        <v>-11.89220055645596</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>-36.56646370843727</v>
+        <v>-18.52885158287489</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>-43.85563830344387</v>
+        <v>-17.93590583973032</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>-50.05256810624567</v>
+        <v>-16.36994727901843</v>
       </c>
       <c r="L35" s="19" t="n">
         <v>-54.17532437418072</v>
@@ -2433,10 +2433,10 @@
         <v>-58.25146355350154</v>
       </c>
       <c r="N35" s="19" t="n">
-        <v>-62.28150571035341</v>
+        <v>-62.28150571035344</v>
       </c>
       <c r="O35" s="19" t="n">
-        <v>-64.83465568889524</v>
+        <v>-64.83465568889527</v>
       </c>
     </row>
     <row r="36" ht="15.5" customHeight="1">
@@ -2456,28 +2456,28 @@
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>0</v>
+        <v>69.0747932436862</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>0</v>
+        <v>46.36062846123374</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>0</v>
+        <v>9.270092182489522</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>0</v>
+        <v>-27.93996074466054</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>0</v>
+        <v>-65.27071349036076</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>0</v>
+        <v>-102.7234173453388</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>0</v>
+        <v>-69.19788182551569</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>0</v>
+        <v>-48.60057464942231</v>
       </c>
       <c r="L36" s="19" t="n">
         <v>0</v>
@@ -2509,40 +2509,40 @@
         </is>
       </c>
       <c r="D37" s="18" t="n">
-        <v>-1646.281840729124</v>
+        <v>-20.23759514565197</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>-3942.812608284448</v>
+        <v>-52.6250552869862</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>-6143.963662567347</v>
+        <v>-83.98409683741158</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>-8251.931230698974</v>
+        <v>-113.2606702417213</v>
       </c>
       <c r="H37" s="18" t="n">
-        <v>-10266.12227280169</v>
+        <v>-142.5235034398179</v>
       </c>
       <c r="I37" s="18" t="n">
-        <v>-12188.14982227463</v>
+        <v>-170.6063151603716</v>
       </c>
       <c r="J37" s="18" t="n">
-        <v>-14563.86105359618</v>
+        <v>-203.7966931609673</v>
       </c>
       <c r="K37" s="18" t="n">
-        <v>-17365.57150027543</v>
+        <v>-244.4893693980132</v>
       </c>
       <c r="L37" s="18" t="n">
-        <v>-20036.49502196161</v>
+        <v>-280.6699392459341</v>
       </c>
       <c r="M37" s="18" t="n">
-        <v>-22579.91008037529</v>
+        <v>-315.4100272010004</v>
       </c>
       <c r="N37" s="18" t="n">
-        <v>-24997.12190214357</v>
+        <v>-348.6895131839137</v>
       </c>
       <c r="O37" s="18" t="n">
-        <v>-26206.43721150399</v>
+        <v>-371.6689491802108</v>
       </c>
     </row>
     <row r="38" ht="15.5" customHeight="1">
@@ -2565,37 +2565,37 @@
         <v>0</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>139.4980319128231</v>
+        <v>160.0361105568053</v>
       </c>
       <c r="F38" s="18" t="n">
-        <v>55.82692542014158</v>
+        <v>59.58956504541717</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>34.30957088783924</v>
+        <v>34.859663325293</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>24.40872307090352</v>
+        <v>25.83671201631048</v>
       </c>
       <c r="I38" s="18" t="n">
-        <v>18.72204030303657</v>
+        <v>19.70398639015494</v>
       </c>
       <c r="J38" s="18" t="n">
-        <v>19.4919759435495</v>
+        <v>19.45436660383668</v>
       </c>
       <c r="K38" s="18" t="n">
-        <v>19.23741538297252</v>
+        <v>19.96728975622048</v>
       </c>
       <c r="L38" s="18" t="n">
-        <v>15.38056793376377</v>
+        <v>14.79842249869818</v>
       </c>
       <c r="M38" s="18" t="n">
-        <v>12.69391206209411</v>
+        <v>12.3775592243335</v>
       </c>
       <c r="N38" s="18" t="n">
-        <v>10.70514370147619</v>
+        <v>10.55118198943796</v>
       </c>
       <c r="O38" s="18" t="n">
-        <v>4.837818186007725</v>
+        <v>6.590228592328429</v>
       </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
@@ -2615,28 +2615,28 @@
         </is>
       </c>
       <c r="D39" s="18" t="n">
-        <v>0</v>
+        <v>193.7989159681726</v>
       </c>
       <c r="E39" s="18" t="n">
-        <v>0</v>
+        <v>280.2556202671575</v>
       </c>
       <c r="F39" s="18" t="n">
-        <v>0</v>
+        <v>451.7764580560337</v>
       </c>
       <c r="G39" s="18" t="n">
-        <v>0</v>
+        <v>615.4184171175581</v>
       </c>
       <c r="H39" s="18" t="n">
-        <v>0</v>
+        <v>782.2446917625064</v>
       </c>
       <c r="I39" s="18" t="n">
-        <v>0</v>
+        <v>945.8364775379183</v>
       </c>
       <c r="J39" s="18" t="n">
-        <v>0</v>
+        <v>786.260789714066</v>
       </c>
       <c r="K39" s="18" t="n">
-        <v>0</v>
+        <v>725.8620718741134</v>
       </c>
       <c r="L39" s="18" t="n">
         <v>0</v>
@@ -2733,13 +2733,13 @@
         <v>251.9186599932067</v>
       </c>
       <c r="H41" s="18" t="n">
-        <v>316.3689062182362</v>
+        <v>316.3689062182361</v>
       </c>
       <c r="I41" s="18" t="n">
-        <v>377.9752415799665</v>
+        <v>377.9752415799664</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>468.8902736200479</v>
+        <v>468.8902736200478</v>
       </c>
       <c r="K41" s="18" t="n">
         <v>587.7150624737048</v>
@@ -2786,13 +2786,13 @@
         <v>251.9186599932067</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>316.3689062182362</v>
+        <v>316.3689062182361</v>
       </c>
       <c r="I42" s="18" t="n">
-        <v>377.9752415799665</v>
+        <v>377.9752415799664</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>468.8902736200479</v>
+        <v>468.8902736200478</v>
       </c>
       <c r="K42" s="18" t="n">
         <v>587.7150624737048</v>
@@ -2827,40 +2827,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>-48.41353452592415</v>
+        <v>0.2410375785965968</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>-131.6411789128624</v>
+        <v>-64.20908675831714</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>-218.7321757163074</v>
+        <v>-132.7103373853477</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>-309.6009351234899</v>
+        <v>-205.1752487614295</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>-404.1631927826552</v>
+        <v>-281.517695542915</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>-502.3359918528228</v>
+        <v>-361.6528824875202</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>-637.106662196348</v>
+        <v>-470.5038203673319</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>-805.9840191562506</v>
+        <v>-605.6985565000073</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>-973.7115551400509</v>
+        <v>-773.4260924838075</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>-1140.295378831575</v>
+        <v>-940.0099161753313</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>-1305.74159172307</v>
+        <v>-1105.456129066826</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>-1419.960455765118</v>
+        <v>-1219.674993108875</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -2880,40 +2880,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>-48.41353452592415</v>
+        <v>0.2410375785965968</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>-131.6411789128624</v>
+        <v>-64.20908675831714</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>-218.7321757163074</v>
+        <v>-132.7103373853477</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>-309.6009351234899</v>
+        <v>-205.1752487614295</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>-404.1631927826552</v>
+        <v>-281.517695542915</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>-502.3359918528228</v>
+        <v>-361.6528824875202</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>-637.106662196348</v>
+        <v>-470.5038203673319</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>-805.9840191562506</v>
+        <v>-605.6985565000073</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>-973.7115551400509</v>
+        <v>-773.4260924838075</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>-1140.295378831575</v>
+        <v>-940.0099161753313</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>-1305.74159172307</v>
+        <v>-1105.456129066826</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>-1419.960455765118</v>
+        <v>-1219.674993108875</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -3039,40 +3039,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>-7.197795869017</v>
+        <v>41.45677623550375</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>-17.269939614416</v>
+        <v>50.1621525401293</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>-34.13639918378593</v>
+        <v>51.88543914717371</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>-57.68227513028327</v>
+        <v>46.74341123177715</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>-87.794286564419</v>
+        <v>34.85121067532111</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>-124.3607502728563</v>
+        <v>16.32235909244622</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>-168.2163885763001</v>
+        <v>-1.61354674728409</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>-218.2689566825458</v>
+        <v>-17.98349402630242</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>-272.4442810567265</v>
+        <v>-72.15881840048303</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>-330.6957446102281</v>
+        <v>-130.4102819539845</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>-392.9772503205816</v>
+        <v>-192.6917876643379</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>-457.8119060094767</v>
+        <v>-257.526443353233</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -3092,40 +3092,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>-7.197795869017003</v>
+        <v>41.45677623550374</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>-17.269939614416</v>
+        <v>50.1621525401293</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>-34.1363991837859</v>
+        <v>51.88543914717373</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>-57.68227513028322</v>
+        <v>46.74341123177719</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>-87.79428656441897</v>
+        <v>34.85121067532123</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>-124.3607502728562</v>
+        <v>16.32235909244634</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>-168.2163885763001</v>
+        <v>-1.61354674728398</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>-218.2689566825458</v>
+        <v>-17.98349402630241</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>-272.4442810567265</v>
+        <v>-72.15881840048313</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>-330.695744610228</v>
+        <v>-130.4102819539847</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>-392.9772503205814</v>
+        <v>-192.6917876643381</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>-457.8119060094767</v>
+        <v>-257.5264433532334</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -3145,40 +3145,40 @@
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>-3.968408279291566</v>
+        <v>34.24358985903859</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>-3.968408279291566</v>
+        <v>34.24358985903859</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>-3.968408279291566</v>
+        <v>34.24358985903859</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>-3.968408279291566</v>
+        <v>34.24358985903859</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>-3.968408279291566</v>
+        <v>34.24358985903859</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>-3.968408279291566</v>
+        <v>34.24358985903859</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>-3.968408279291566</v>
+        <v>34.24358985903859</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>-3.968408279291566</v>
+        <v>34.24358985903859</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>-3.968408279291566</v>
+        <v>34.24358985903859</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>-3.968408279291566</v>
+        <v>34.24358985903859</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>-3.968408279291566</v>
+        <v>34.24358985903859</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>-3.968408279291566</v>
+        <v>34.24358985903859</v>
       </c>
     </row>
     <row r="50" ht="15.5" customHeight="1">
@@ -3198,28 +3198,28 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>-3.229387589725437</v>
+        <v>7.213186376465149</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>-10.072143745399</v>
+        <v>8.70537630462556</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>-16.86645956936989</v>
+        <v>1.723286607044429</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>-23.54587594649732</v>
+        <v>-5.14202791539654</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>-30.11201143413574</v>
+        <v>-11.89220055645596</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>-36.56646370843727</v>
+        <v>-18.52885158287489</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>-43.85563830344387</v>
+        <v>-17.93590583973032</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>-50.05256810624567</v>
+        <v>-16.36994727901843</v>
       </c>
       <c r="L50" s="18" t="n">
         <v>-54.17532437418072</v>
@@ -3228,10 +3228,10 @@
         <v>-58.25146355350154</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>-62.28150571035341</v>
+        <v>-62.28150571035344</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>-64.83465568889524</v>
+        <v>-64.83465568889527</v>
       </c>
     </row>
     <row r="51" ht="15.5" customHeight="1">
@@ -3254,37 +3254,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>-3.229387589725437</v>
+        <v>7.213186376465149</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>-13.30153133512444</v>
+        <v>15.91856268109071</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>-30.16799090449433</v>
+        <v>17.64184928813514</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>-53.71386685099165</v>
+        <v>12.4998213727386</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>-83.8258782851274</v>
+        <v>0.6076208162826369</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>-120.3923419935647</v>
+        <v>-17.92123076659225</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>-164.2479802970086</v>
+        <v>-35.85713660632257</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>-214.3005484032542</v>
+        <v>-52.227083885341</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>-268.4758727774349</v>
+        <v>-106.4024082595217</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>-326.7273363309365</v>
+        <v>-164.6538718130233</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>-389.0088420412899</v>
+        <v>-226.9353775233767</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -3304,40 +3304,40 @@
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-10.44257396619059</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-29.22009401621515</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-47.80984019262947</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-66.21368822373026</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-84.43349910141005</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-102.4711112269724</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-128.390843690686</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -3357,40 +3357,40 @@
         </is>
       </c>
       <c r="D53" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-10.44257396619059</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-29.22009401621515</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-47.80984019262947</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-66.21368822373026</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-84.43349910141005</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-102.4711112269724</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-128.390843690686</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -3622,40 +3622,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>213.6580950034761</v>
+        <v>31.01420226931315</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>203.5859512580771</v>
+        <v>20.94205852391415</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>186.7194916887072</v>
+        <v>4.075598954544255</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>163.1736157422099</v>
+        <v>-19.47027699195307</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>133.0616043080741</v>
+        <v>-49.58228842608882</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>96.49514059963685</v>
+        <v>-86.14875213452608</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>52.63950229619297</v>
+        <v>-130.00439043797</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>2.5869341899473</v>
+        <v>-180.0569585442156</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>-51.58839018423339</v>
+        <v>-234.2322829183963</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>-109.8398537377349</v>
+        <v>-292.4837464718979</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>-172.1213594480884</v>
+        <v>-354.7652521822513</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>-236.9560151369836</v>
+        <v>-419.5999078711466</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -3675,40 +3675,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>-220.8558908724931</v>
+        <v>10.44257396619059</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>-220.8558908724931</v>
+        <v>29.22009401621515</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>-220.8558908724931</v>
+        <v>47.80984019262946</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>-220.8558908724931</v>
+        <v>66.21368822373022</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>-220.8558908724931</v>
+        <v>84.43349910140994</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>-220.8558908724931</v>
+        <v>102.4711112269723</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>-220.8558908724931</v>
+        <v>128.3908436906859</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>-220.8558908724931</v>
+        <v>162.0734645179132</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>-220.8558908724931</v>
+        <v>162.0734645179133</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>-220.8558908724931</v>
+        <v>162.0734645179134</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>-220.8558908724932</v>
+        <v>162.0734645179134</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>-220.8558908724931</v>
+        <v>162.0734645179135</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -4311,28 +4311,28 @@
         </is>
       </c>
       <c r="D71" s="19" t="n">
-        <v>0</v>
+        <v>10.44257396619059</v>
       </c>
       <c r="E71" s="19" t="n">
-        <v>0</v>
+        <v>18.77752005002456</v>
       </c>
       <c r="F71" s="19" t="n">
-        <v>0</v>
+        <v>18.58974617641432</v>
       </c>
       <c r="G71" s="19" t="n">
-        <v>0</v>
+        <v>18.40384803110078</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>0</v>
+        <v>18.21981087767979</v>
       </c>
       <c r="I71" s="19" t="n">
-        <v>0</v>
+        <v>18.03761212556238</v>
       </c>
       <c r="J71" s="19" t="n">
-        <v>0</v>
+        <v>25.91973246371354</v>
       </c>
       <c r="K71" s="19" t="n">
-        <v>0</v>
+        <v>33.68262082722723</v>
       </c>
       <c r="L71" s="19" t="n">
         <v>0</v>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="D73" s="19" t="n">
-        <v>-3.968408279291566</v>
+        <v>34.24358985903859</v>
       </c>
       <c r="E73" s="19" t="n">
         <v>0</v>
@@ -4470,28 +4470,28 @@
         </is>
       </c>
       <c r="D74" s="18" t="n">
-        <v>-3.968408279291566</v>
+        <v>44.68616382522918</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>0</v>
+        <v>18.77752005002456</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>0</v>
+        <v>18.58974617641432</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>0</v>
+        <v>18.40384803110078</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>0</v>
+        <v>18.21981087767979</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>0</v>
+        <v>18.03761212556238</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>0</v>
+        <v>25.91973246371354</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>0</v>
+        <v>33.68262082722723</v>
       </c>
       <c r="L74" s="18" t="n">
         <v>0</v>
@@ -4523,28 +4523,28 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>-48.41353452592415</v>
+        <v>0.2410375785965968</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-83.22764438693829</v>
+        <v>-64.45012433691373</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>-87.09099680344492</v>
+        <v>-68.5012506270306</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>-90.86875940718255</v>
+        <v>-72.46491137608177</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>-94.56225765916528</v>
+        <v>-76.34244678148549</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>-98.17279907016754</v>
+        <v>-80.13518694460517</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>-134.7706703435253</v>
+        <v>-108.8509378798118</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>-168.8773569599026</v>
+        <v>-135.1947361326754</v>
       </c>
       <c r="L75" s="18" t="n">
         <v>-167.7275359838002</v>
@@ -4579,37 +4579,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>-48.41353452592415</v>
+        <v>0.2410375785965968</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>-131.6411789128624</v>
+        <v>-64.20908675831714</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>-218.7321757163074</v>
+        <v>-132.7103373853477</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>-309.6009351234899</v>
+        <v>-205.1752487614295</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>-404.1631927826552</v>
+        <v>-281.517695542915</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>-502.3359918528228</v>
+        <v>-361.6528824875202</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>-637.106662196348</v>
+        <v>-470.5038203673319</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>-805.9840191562506</v>
+        <v>-605.6985565000073</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>-973.7115551400509</v>
+        <v>-773.4260924838075</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>-1140.295378831575</v>
+        <v>-940.0099161753313</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>-1305.74159172307</v>
+        <v>-1105.456129066826</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -4629,28 +4629,28 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>-48.41353452592415</v>
+        <v>0.2410375785965968</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-83.22764438693829</v>
+        <v>-64.45012433691373</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>-87.09099680344492</v>
+        <v>-68.5012506270306</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>-90.86875940718255</v>
+        <v>-72.46491137608177</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>-94.56225765916528</v>
+        <v>-76.34244678148549</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>-98.17279907016754</v>
+        <v>-80.13518694460517</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>-134.7706703435253</v>
+        <v>-108.8509378798118</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>-168.8773569599026</v>
+        <v>-135.1947361326754</v>
       </c>
       <c r="L77" s="18" t="n">
         <v>-167.7275359838002</v>
@@ -4682,40 +4682,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>-48.41353452592415</v>
+        <v>0.2410375785965968</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>-131.6411789128624</v>
+        <v>-64.20908675831714</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>-218.7321757163074</v>
+        <v>-132.7103373853477</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>-309.6009351234899</v>
+        <v>-205.1752487614295</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>-404.1631927826552</v>
+        <v>-281.517695542915</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>-502.3359918528228</v>
+        <v>-361.6528824875202</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>-637.106662196348</v>
+        <v>-470.5038203673319</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>-805.9840191562506</v>
+        <v>-605.6985565000073</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>-973.7115551400509</v>
+        <v>-773.4260924838075</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>-1140.295378831575</v>
+        <v>-940.0099161753313</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>-1305.74159172307</v>
+        <v>-1105.456129066826</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>-1419.960455765118</v>
+        <v>-1219.674993108875</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -4841,28 +4841,28 @@
         </is>
       </c>
       <c r="D81" s="18" t="n">
-        <v>0</v>
+        <v>406.297972145854</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>0</v>
+        <v>407.6950213346657</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>0</v>
+        <v>407.6949922344061</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>0</v>
+        <v>407.695007376873</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>0</v>
+        <v>407.694977685762</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>0</v>
+        <v>407.694992226863</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>0</v>
+        <v>408.4612138811561</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>0</v>
+        <v>408.8653626846836</v>
       </c>
       <c r="L81" s="18" t="n">
         <v>0</v>
@@ -4909,13 +4909,13 @@
         <v>251.9186599932067</v>
       </c>
       <c r="I82" s="18" t="n">
-        <v>316.3689062182362</v>
+        <v>316.3689062182361</v>
       </c>
       <c r="J82" s="18" t="n">
-        <v>377.9752415799665</v>
+        <v>377.9752415799664</v>
       </c>
       <c r="K82" s="18" t="n">
-        <v>468.8902736200479</v>
+        <v>468.8902736200478</v>
       </c>
       <c r="L82" s="18" t="n">
         <v>587.7150624737048</v>
@@ -5003,7 +5003,7 @@
         <v>1.212227607556091</v>
       </c>
       <c r="E84" s="18" t="n">
-        <v>3.399513732529481</v>
+        <v>3.399513732529485</v>
       </c>
       <c r="F84" s="18" t="n">
         <v>5.564926996253149</v>
@@ -5012,16 +5012,16 @@
         <v>7.708686127339575</v>
       </c>
       <c r="H84" s="18" t="n">
-        <v>9.831007667115124</v>
+        <v>9.831007667115131</v>
       </c>
       <c r="I84" s="18" t="n">
-        <v>11.93210599149295</v>
+        <v>11.93210599149294</v>
       </c>
       <c r="J84" s="18" t="n">
         <v>14.95702181595101</v>
       </c>
       <c r="K84" s="18" t="n">
-        <v>18.89178095329243</v>
+        <v>18.89178095329241</v>
       </c>
       <c r="L84" s="18" t="n">
         <v>22.78719249926041</v>
@@ -5030,10 +5030,10 @@
         <v>26.64364992976874</v>
       </c>
       <c r="N84" s="18" t="n">
-        <v>30.46154278597193</v>
+        <v>30.46154278597196</v>
       </c>
       <c r="O84" s="18" t="n">
-        <v>32.80994723124032</v>
+        <v>32.80994723124034</v>
       </c>
     </row>
     <row r="85" ht="15.5" customHeight="1">
@@ -5065,13 +5065,13 @@
         <v>251.9186599932067</v>
       </c>
       <c r="H85" s="18" t="n">
-        <v>316.3689062182362</v>
+        <v>316.3689062182361</v>
       </c>
       <c r="I85" s="18" t="n">
-        <v>377.9752415799665</v>
+        <v>377.9752415799664</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>468.8902736200479</v>
+        <v>468.8902736200478</v>
       </c>
       <c r="K85" s="18" t="n">
         <v>587.7150624737048</v>
@@ -5663,37 +5663,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>-7.197795869017003</v>
+        <v>41.45677623550374</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>-17.269939614416</v>
+        <v>50.1621525401293</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>-34.1363991837859</v>
+        <v>51.88543914717373</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>-57.68227513028322</v>
+        <v>46.74341123177719</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>-87.79428656441897</v>
+        <v>34.85121067532123</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>-124.3607502728562</v>
+        <v>16.32235909244634</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>-168.2163885763001</v>
+        <v>-1.613546747283984</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>-218.2689566825458</v>
+        <v>-17.98349402630242</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>-272.4442810567265</v>
+        <v>-72.15881840048314</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>-330.695744610228</v>
+        <v>-130.4102819539847</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>-392.9772503205814</v>
+        <v>-192.6917876643381</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -5713,7 +5713,7 @@
         </is>
       </c>
       <c r="D97" s="19" t="n">
-        <v>-3.968408279291566</v>
+        <v>34.24358985903859</v>
       </c>
       <c r="E97" s="19" t="n">
         <v>0</v>
@@ -5766,28 +5766,28 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>-3.229387589725437</v>
+        <v>7.213186376465149</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>-10.072143745399</v>
+        <v>8.70537630462556</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>-16.86645956936989</v>
+        <v>1.723286607044429</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>-23.54587594649732</v>
+        <v>-5.14202791539654</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>-30.11201143413574</v>
+        <v>-11.89220055645596</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>-36.56646370843727</v>
+        <v>-18.52885158287489</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>-43.85563830344387</v>
+        <v>-17.93590583973032</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>-50.05256810624567</v>
+        <v>-16.36994727901843</v>
       </c>
       <c r="L98" s="21" t="n">
         <v>-54.17532437418072</v>
@@ -5796,10 +5796,10 @@
         <v>-58.25146355350154</v>
       </c>
       <c r="N98" s="21" t="n">
-        <v>-62.28150571035341</v>
+        <v>-62.28150571035344</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>-64.83465568889524</v>
+        <v>-64.83465568889527</v>
       </c>
     </row>
     <row r="99" ht="15.5" customHeight="1">
@@ -5872,40 +5872,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>-7.197795869017003</v>
+        <v>41.45677623550374</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>-17.269939614416</v>
+        <v>50.1621525401293</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>-34.1363991837859</v>
+        <v>51.88543914717373</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>-57.68227513028322</v>
+        <v>46.74341123177719</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>-87.79428656441897</v>
+        <v>34.85121067532123</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>-124.3607502728562</v>
+        <v>16.32235909244634</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>-168.2163885763001</v>
+        <v>-1.613546747283984</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>-218.2689566825458</v>
+        <v>-17.98349402630242</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>-272.4442810567265</v>
+        <v>-72.15881840048314</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>-330.695744610228</v>
+        <v>-130.4102819539847</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>-392.9772503205814</v>
+        <v>-192.6917876643381</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>-457.8119060094767</v>
+        <v>-257.5264433532334</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -5978,28 +5978,28 @@
         </is>
       </c>
       <c r="D102" s="18" t="n">
-        <v>0</v>
+        <v>-24.61247824394794</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>0</v>
+        <v>-24.52813862495336</v>
       </c>
       <c r="F102" s="18" t="n">
-        <v>0</v>
+        <v>-24.5281403757112</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>0</v>
+        <v>-24.5281394646955</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>0</v>
+        <v>-24.52814125100083</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>0</v>
+        <v>-24.52814037616502</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>0</v>
+        <v>-24.48212868238097</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>0</v>
+        <v>-24.45792897284866</v>
       </c>
       <c r="L102" s="18" t="n">
         <v>0</v>
@@ -6034,37 +6034,37 @@
         <v>0</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-10.44257396619059</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-29.22009401621515</v>
       </c>
       <c r="G103" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-47.80984019262947</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-66.21368822373026</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-84.43349910141005</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-102.4711112269724</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-128.390843690686</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="D104" s="19" t="n">
-        <v>220.8558908724931</v>
+        <v>0</v>
       </c>
       <c r="E104" s="19" t="n">
         <v>0</v>
@@ -6137,28 +6137,28 @@
         </is>
       </c>
       <c r="D105" s="18" t="n">
-        <v>0</v>
+        <v>-10.44257396619059</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>0</v>
+        <v>-18.77752005002456</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>0</v>
+        <v>-18.58974617641432</v>
       </c>
       <c r="G105" s="18" t="n">
-        <v>0</v>
+        <v>-18.40384803110078</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>0</v>
+        <v>-18.21981087767979</v>
       </c>
       <c r="I105" s="18" t="n">
-        <v>0</v>
+        <v>-18.03761212556238</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>0</v>
+        <v>-25.91973246371354</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>0</v>
+        <v>-33.68262082722723</v>
       </c>
       <c r="L105" s="18" t="n">
         <v>0</v>
@@ -6243,40 +6243,40 @@
         </is>
       </c>
       <c r="D107" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-10.44257396619059</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-29.22009401621515</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-47.80984019262947</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-66.21368822373026</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-84.43349910141005</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-102.4711112269724</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-128.390843690686</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>220.8558908724931</v>
+        <v>-162.0734645179132</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -6685,28 +6685,28 @@
         </is>
       </c>
       <c r="D2" s="18" t="n">
-        <v>276.294</v>
+        <v>348.6270835704482</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>319.3776</v>
+        <v>410.7570177488272</v>
       </c>
       <c r="F2" s="18" t="n">
-        <v>371.7594</v>
+        <v>462.2258278280675</v>
       </c>
       <c r="G2" s="18" t="n">
-        <v>400.3194</v>
+        <v>489.8807492357146</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>450.3366</v>
+        <v>539.003140000086</v>
       </c>
       <c r="I2" s="18" t="n">
-        <v>499.6202</v>
+        <v>587.3996846574288</v>
       </c>
       <c r="J2" s="18" t="n">
-        <v>547.888</v>
+        <v>644.7363223532651</v>
       </c>
       <c r="K2" s="18" t="n">
-        <v>607.9227</v>
+        <v>713.7011315063978</v>
       </c>
       <c r="L2" s="18" t="n">
         <v>664.8774</v>
@@ -6741,28 +6741,28 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>15.59338965015526</v>
+        <v>17.82131598672088</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>16.40121285901079</v>
+        <v>12.53023268143232</v>
       </c>
       <c r="G3" s="18" t="n">
-        <v>7.682388125222928</v>
+        <v>5.982989210618883</v>
       </c>
       <c r="H3" s="18" t="n">
-        <v>12.49432328285864</v>
+        <v>10.02741806878704</v>
       </c>
       <c r="I3" s="18" t="n">
-        <v>10.94372520465803</v>
+        <v>8.97889846380766</v>
       </c>
       <c r="J3" s="18" t="n">
-        <v>9.660898418438645</v>
+        <v>9.761094395083813</v>
       </c>
       <c r="K3" s="18" t="n">
-        <v>10.95747671056857</v>
+        <v>10.69659126717315</v>
       </c>
       <c r="L3" s="18" t="n">
-        <v>9.368740466509973</v>
+        <v>-6.840921129457422</v>
       </c>
       <c r="M3" s="18" t="n">
         <v>8.302929231765145</v>
@@ -6897,28 +6897,28 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>0</v>
+        <v>72.33308357044821</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>0</v>
+        <v>91.37941774882724</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>0</v>
+        <v>90.46642782806747</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0</v>
+        <v>89.56134923571453</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>0</v>
+        <v>88.66654000008592</v>
       </c>
       <c r="I6" s="18" t="n">
-        <v>0</v>
+        <v>87.77948465742882</v>
       </c>
       <c r="J6" s="18" t="n">
-        <v>0</v>
+        <v>96.84832235326512</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>0</v>
+        <v>105.7784315063979</v>
       </c>
       <c r="L6" s="18" t="n">
         <v>0</v>
@@ -6953,28 +6953,28 @@
         <v>0</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>0</v>
+        <v>26.33142849472054</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>0</v>
+        <v>-0.9991198710296967</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>0</v>
+        <v>-1.000457975496771</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>0</v>
+        <v>-0.9991020046756782</v>
       </c>
       <c r="I7" s="18" t="n">
-        <v>0</v>
+        <v>-1.000439785578899</v>
       </c>
       <c r="J7" s="18" t="n">
-        <v>0</v>
+        <v>10.33138634981585</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>0</v>
+        <v>9.22071641113118</v>
       </c>
       <c r="L7" s="18" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M7" s="18" t="n">
         <v>0</v>
@@ -7003,28 +7003,28 @@
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>0</v>
+        <v>20.74798172008103</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>0</v>
+        <v>22.24658710632294</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>0</v>
+        <v>19.57191104035795</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>0</v>
+        <v>18.28227571208775</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>0</v>
+        <v>16.45009711818595</v>
       </c>
       <c r="I8" s="18" t="n">
-        <v>0</v>
+        <v>14.94374051436915</v>
       </c>
       <c r="J8" s="18" t="n">
-        <v>0</v>
+        <v>15.02138455605729</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>0</v>
+        <v>14.82111024304151</v>
       </c>
       <c r="L8" s="18" t="n">
         <v>0</v>
@@ -7480,28 +7480,28 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>37.76233382818021</v>
+        <v>29.92741170843341</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>37.35979336698412</v>
+        <v>29.04851439285574</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>36.87062115981465</v>
+        <v>29.65433598638833</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>38.58169251852395</v>
+        <v>31.52808111789747</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>38.07596362365395</v>
+        <v>31.81243062887772</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>37.65660395636525</v>
+        <v>32.02929877460236</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>37.31602079257074</v>
+        <v>31.7106378083004</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>35.15743037725027</v>
+        <v>29.94670886241744</v>
       </c>
       <c r="L17" s="18" t="n">
         <v>32.76243108879923</v>
@@ -7692,28 +7692,28 @@
         </is>
       </c>
       <c r="D21" s="18" t="n">
-        <v>158.1442373727678</v>
+        <v>230.477320943216</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>184.0899085795669</v>
+        <v>275.4693263283941</v>
       </c>
       <c r="F21" s="18" t="n">
-        <v>216.1014300000001</v>
+        <v>306.5678578280675</v>
       </c>
       <c r="G21" s="18" t="n">
-        <v>225.85343</v>
+        <v>315.4147792357146</v>
       </c>
       <c r="H21" s="18" t="n">
-        <v>256.34977</v>
+        <v>345.0163100000859</v>
       </c>
       <c r="I21" s="18" t="n">
-        <v>286.49919</v>
+        <v>374.2786746574288</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>316.0436</v>
+        <v>412.8919223532651</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>363.7965649999999</v>
+        <v>469.5749965063978</v>
       </c>
       <c r="L21" s="18" t="n">
         <v>413.80353</v>
@@ -7745,7 +7745,7 @@
         </is>
       </c>
       <c r="D22" s="18" t="n">
-        <v>158.1442373727678</v>
+        <v>158.1442373727677</v>
       </c>
       <c r="E22" s="18" t="n">
         <v>184.0899085795669</v>
@@ -7754,13 +7754,13 @@
         <v>216.1014300000001</v>
       </c>
       <c r="G22" s="18" t="n">
-        <v>225.85343</v>
+        <v>225.8534300000001</v>
       </c>
       <c r="H22" s="18" t="n">
         <v>256.34977</v>
       </c>
       <c r="I22" s="18" t="n">
-        <v>286.49919</v>
+        <v>286.4991899999999</v>
       </c>
       <c r="J22" s="18" t="n">
         <v>316.0436</v>
@@ -7798,28 +7798,28 @@
         </is>
       </c>
       <c r="D23" s="18" t="n">
-        <v>57.2376661718198</v>
+        <v>66.10998737757065</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>57.64020663301588</v>
+        <v>67.06381496246041</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>58.12937884018535</v>
+        <v>66.32425956562957</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>56.41830748147605</v>
+        <v>64.38603266770691</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>56.92403637634605</v>
+        <v>64.01007422703157</v>
       </c>
       <c r="I23" s="18" t="n">
-        <v>57.34339604363474</v>
+        <v>63.71788825111609</v>
       </c>
       <c r="J23" s="18" t="n">
-        <v>57.68397920742926</v>
+        <v>64.04043141950247</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>59.84256962274973</v>
+        <v>65.79434664973462</v>
       </c>
       <c r="L23" s="18" t="n">
         <v>62.23756891120077</v>
@@ -7851,28 +7851,28 @@
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>57.2376661718198</v>
+        <v>45.36200565748961</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>57.64020663301588</v>
+        <v>44.81722785613746</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>58.12937884018535</v>
+        <v>46.75234852527162</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>56.41830748147605</v>
+        <v>46.10375695561917</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>56.92403637634605</v>
+        <v>47.55997710884562</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>57.34339604363474</v>
+        <v>48.77414773674694</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>57.68397920742926</v>
+        <v>49.01904686344518</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>59.84256962274973</v>
+        <v>50.97323640669313</v>
       </c>
       <c r="L24" s="18" t="n">
         <v>62.23756891120077</v>
@@ -7910,7 +7910,7 @@
         <v>-20.21965144203191</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>-31.3948199737737</v>
+        <v>-31.39481997377369</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>-42.45816882019806</v>
@@ -7957,28 +7957,28 @@
         </is>
       </c>
       <c r="D26" s="19" t="n">
-        <v>3.232692622135787</v>
+        <v>2.561974147828646</v>
       </c>
       <c r="E26" s="19" t="n">
-        <v>6.330954782687299</v>
+        <v>4.922533412294852</v>
       </c>
       <c r="F26" s="19" t="n">
-        <v>8.444929697480063</v>
+        <v>6.792095569668493</v>
       </c>
       <c r="G26" s="19" t="n">
-        <v>10.60607325555495</v>
+        <v>8.667041700748396</v>
       </c>
       <c r="H26" s="19" t="n">
-        <v>11.86024324431063</v>
+        <v>9.90922171216844</v>
       </c>
       <c r="I26" s="19" t="n">
-        <v>12.86062314184628</v>
+        <v>10.93876499099787</v>
       </c>
       <c r="J26" s="19" t="n">
-        <v>13.83200512016606</v>
+        <v>11.75424643925238</v>
       </c>
       <c r="K26" s="19" t="n">
-        <v>14.47377146833568</v>
+        <v>12.32859784268776</v>
       </c>
       <c r="L26" s="19" t="n">
         <v>15.05130087601154</v>
@@ -7987,7 +7987,7 @@
         <v>15.5586861883568</v>
       </c>
       <c r="N26" s="19" t="n">
-        <v>16.01883405456484</v>
+        <v>16.01883405456485</v>
       </c>
       <c r="O26" s="19" t="n">
         <v>15.40875376777107</v>
@@ -8010,28 +8010,28 @@
         </is>
       </c>
       <c r="D27" s="19" t="n">
-        <v>149.2125016193639</v>
+        <v>221.5455851898121</v>
       </c>
       <c r="E27" s="19" t="n">
-        <v>163.870257137535</v>
+        <v>255.2496748863622</v>
       </c>
       <c r="F27" s="19" t="n">
-        <v>184.7066100262263</v>
+        <v>275.1730378542939</v>
       </c>
       <c r="G27" s="19" t="n">
-        <v>183.395261179802</v>
+        <v>272.9566104155165</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>202.9387538218419</v>
+        <v>291.6052938219277</v>
       </c>
       <c r="I27" s="19" t="n">
-        <v>222.2449189374613</v>
+        <v>310.0244035948901</v>
       </c>
       <c r="J27" s="19" t="n">
-        <v>240.2597037872246</v>
+        <v>337.1080261404896</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>275.8072226978641</v>
+        <v>381.5856542042619</v>
       </c>
       <c r="L27" s="19" t="n">
         <v>313.7308320693973</v>
@@ -8040,7 +8040,7 @@
         <v>350.2323629972152</v>
       </c>
       <c r="N27" s="19" t="n">
-        <v>385.0912707480148</v>
+        <v>385.0912707480147</v>
       </c>
       <c r="O27" s="19" t="n">
         <v>452.969700116478</v>
@@ -8063,28 +8063,28 @@
         </is>
       </c>
       <c r="D28" s="19" t="n">
-        <v>54.00497354968401</v>
+        <v>63.548013229742</v>
       </c>
       <c r="E28" s="19" t="n">
-        <v>51.30925185032857</v>
+        <v>62.14128155016556</v>
       </c>
       <c r="F28" s="19" t="n">
-        <v>49.68444914270529</v>
+        <v>59.53216399596107</v>
       </c>
       <c r="G28" s="19" t="n">
-        <v>45.81223422592109</v>
+        <v>55.71899096695853</v>
       </c>
       <c r="H28" s="19" t="n">
-        <v>45.06379313203542</v>
+        <v>54.10085251486312</v>
       </c>
       <c r="I28" s="19" t="n">
-        <v>44.48277290178846</v>
+        <v>52.77912326011822</v>
       </c>
       <c r="J28" s="19" t="n">
-        <v>43.85197408726319</v>
+        <v>52.28618498025008</v>
       </c>
       <c r="K28" s="19" t="n">
-        <v>45.36879815441405</v>
+        <v>53.46574880704688</v>
       </c>
       <c r="L28" s="19" t="n">
         <v>47.18626803518923</v>
@@ -8093,7 +8093,7 @@
         <v>48.63786470302122</v>
       </c>
       <c r="N28" s="19" t="n">
-        <v>49.79662843554285</v>
+        <v>49.79662843554284</v>
       </c>
       <c r="O28" s="19" t="n">
         <v>52.82873040879086</v>
@@ -8169,28 +8169,28 @@
         </is>
       </c>
       <c r="D30" s="19" t="n">
-        <v>149.2125016193639</v>
+        <v>221.5455851898121</v>
       </c>
       <c r="E30" s="19" t="n">
-        <v>163.870257137535</v>
+        <v>255.2496748863622</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>184.7066100262263</v>
+        <v>275.1730378542939</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>183.395261179802</v>
+        <v>272.9566104155165</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>202.9387538218419</v>
+        <v>291.6052938219277</v>
       </c>
       <c r="I30" s="19" t="n">
-        <v>222.2449189374613</v>
+        <v>310.0244035948901</v>
       </c>
       <c r="J30" s="19" t="n">
-        <v>240.2597037872246</v>
+        <v>337.1080261404896</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>275.8072226978641</v>
+        <v>381.5856542042619</v>
       </c>
       <c r="L30" s="19" t="n">
         <v>313.7308320693973</v>
@@ -8199,7 +8199,7 @@
         <v>350.2323629972152</v>
       </c>
       <c r="N30" s="19" t="n">
-        <v>385.0912707480148</v>
+        <v>385.0912707480147</v>
       </c>
       <c r="O30" s="19" t="n">
         <v>452.969700116478</v>
@@ -8228,19 +8228,19 @@
         <v>163.870257137535</v>
       </c>
       <c r="F31" s="19" t="n">
-        <v>184.7066100262263</v>
+        <v>184.7066100262264</v>
       </c>
       <c r="G31" s="19" t="n">
         <v>183.395261179802</v>
       </c>
       <c r="H31" s="19" t="n">
-        <v>202.9387538218419</v>
+        <v>202.9387538218418</v>
       </c>
       <c r="I31" s="19" t="n">
         <v>222.2449189374613</v>
       </c>
       <c r="J31" s="19" t="n">
-        <v>240.2597037872246</v>
+        <v>240.2597037872245</v>
       </c>
       <c r="K31" s="19" t="n">
         <v>275.8072226978641</v>
@@ -8252,7 +8252,7 @@
         <v>350.2323629972152</v>
       </c>
       <c r="N31" s="19" t="n">
-        <v>385.0912707480148</v>
+        <v>385.0912707480147</v>
       </c>
       <c r="O31" s="19" t="n">
         <v>452.969700116478</v>
@@ -8331,22 +8331,22 @@
         <v>-41.7795004534219</v>
       </c>
       <c r="E33" s="19" t="n">
-        <v>-45.8836719985098</v>
+        <v>-45.88367199850979</v>
       </c>
       <c r="F33" s="19" t="n">
-        <v>-51.71785080734337</v>
+        <v>-51.71785080734338</v>
       </c>
       <c r="G33" s="19" t="n">
-        <v>-51.35067313034455</v>
+        <v>-51.35067313034456</v>
       </c>
       <c r="H33" s="19" t="n">
-        <v>-56.82285107011572</v>
+        <v>-56.8228510701157</v>
       </c>
       <c r="I33" s="19" t="n">
-        <v>-62.22857730248916</v>
+        <v>-62.22857730248915</v>
       </c>
       <c r="J33" s="19" t="n">
-        <v>-67.27271706042288</v>
+        <v>-67.27271706042286</v>
       </c>
       <c r="K33" s="19" t="n">
         <v>-77.22602235540194</v>
@@ -8434,28 +8434,28 @@
         </is>
       </c>
       <c r="D35" s="19" t="n">
-        <v>107.433001165942</v>
+        <v>179.7660847363902</v>
       </c>
       <c r="E35" s="19" t="n">
-        <v>117.9865851390252</v>
+        <v>209.3660028878524</v>
       </c>
       <c r="F35" s="19" t="n">
-        <v>132.988759218883</v>
+        <v>223.4551870469505</v>
       </c>
       <c r="G35" s="19" t="n">
-        <v>132.0445880494574</v>
+        <v>221.605937285172</v>
       </c>
       <c r="H35" s="19" t="n">
-        <v>146.1159027517261</v>
+        <v>234.782442751812</v>
       </c>
       <c r="I35" s="19" t="n">
-        <v>160.0163416349722</v>
+        <v>247.7958262924009</v>
       </c>
       <c r="J35" s="19" t="n">
-        <v>172.9869867268017</v>
+        <v>269.8353090800668</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>198.5812003424621</v>
+        <v>304.35963184886</v>
       </c>
       <c r="L35" s="19" t="n">
         <v>225.886199089966</v>
@@ -8467,7 +8467,7 @@
         <v>277.2657149385706</v>
       </c>
       <c r="O35" s="19" t="n">
-        <v>326.1381840838642</v>
+        <v>326.1381840838641</v>
       </c>
     </row>
     <row r="36" ht="15.5" customHeight="1">
@@ -8487,28 +8487,28 @@
         </is>
       </c>
       <c r="D36" s="19" t="n">
-        <v>38.88358095577249</v>
+        <v>51.56400440703693</v>
       </c>
       <c r="E36" s="19" t="n">
-        <v>36.94266133223658</v>
+        <v>50.97076710588963</v>
       </c>
       <c r="F36" s="19" t="n">
-        <v>35.77280338274781</v>
+        <v>48.3432931683922</v>
       </c>
       <c r="G36" s="19" t="n">
-        <v>32.98480864266318</v>
+        <v>45.23671069559471</v>
       </c>
       <c r="H36" s="19" t="n">
-        <v>32.44593105506551</v>
+        <v>43.55864100379352</v>
       </c>
       <c r="I36" s="19" t="n">
-        <v>32.02759648928769</v>
+        <v>42.18521609130848</v>
       </c>
       <c r="J36" s="19" t="n">
-        <v>31.5734213428295</v>
+        <v>41.85204086147611</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>32.66553467117812</v>
+        <v>42.64525000912537</v>
       </c>
       <c r="L36" s="19" t="n">
         <v>33.97411298533626</v>
@@ -8517,7 +8517,7 @@
         <v>35.01926258617528</v>
       </c>
       <c r="N36" s="19" t="n">
-        <v>35.85357247359085</v>
+        <v>35.85357247359084</v>
       </c>
       <c r="O36" s="19" t="n">
         <v>38.03668589432942</v>
@@ -8540,40 +8540,40 @@
         </is>
       </c>
       <c r="D37" s="18" t="n">
-        <v>-4645.617376272102</v>
+        <v>-215.2379926234873</v>
       </c>
       <c r="E37" s="18" t="n">
-        <v>-10318.66122039079</v>
+        <v>-290.5458577966015</v>
       </c>
       <c r="F37" s="18" t="n">
-        <v>-15753.6492298248</v>
+        <v>-380.2118211107734</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>-20959.33771152985</v>
+        <v>-458.3648712949356</v>
       </c>
       <c r="H37" s="18" t="n">
-        <v>-25923.87408783925</v>
+        <v>-543.2675137292863</v>
       </c>
       <c r="I37" s="18" t="n">
-        <v>-30656.54532497497</v>
+        <v>-623.5021100614416</v>
       </c>
       <c r="J37" s="18" t="n">
-        <v>-35799.48391479497</v>
+        <v>-707.7881310470307</v>
       </c>
       <c r="K37" s="18" t="n">
-        <v>-41320.1997616183</v>
+        <v>-796.1377964483786</v>
       </c>
       <c r="L37" s="18" t="n">
-        <v>-46572.55404541759</v>
+        <v>-875.8504052911187</v>
       </c>
       <c r="M37" s="18" t="n">
-        <v>-51565.25709606308</v>
+        <v>-952.0160450274125</v>
       </c>
       <c r="N37" s="18" t="n">
-        <v>-56300.97091674669</v>
+        <v>-1024.909696343218</v>
       </c>
       <c r="O37" s="18" t="n">
-        <v>-58785.1693522673</v>
+        <v>-1083.598141973409</v>
       </c>
     </row>
     <row r="38" ht="15.5" customHeight="1">
@@ -8596,37 +8596,37 @@
         <v>0</v>
       </c>
       <c r="E38" s="18" t="n">
-        <v>122.1160372159415</v>
+        <v>34.98818412827751</v>
       </c>
       <c r="F38" s="18" t="n">
-        <v>52.67144538764281</v>
+        <v>30.86120862096173</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>33.04433408260508</v>
+        <v>20.55513422908346</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>23.68651359426486</v>
+        <v>18.52293832956495</v>
       </c>
       <c r="I38" s="18" t="n">
-        <v>18.25603388251216</v>
+        <v>14.76889272862665</v>
       </c>
       <c r="J38" s="18" t="n">
-        <v>16.77598873357138</v>
+        <v>13.51816130618761</v>
       </c>
       <c r="K38" s="18" t="n">
-        <v>15.42121629452253</v>
+        <v>12.4825016874262</v>
       </c>
       <c r="L38" s="18" t="n">
-        <v>12.71134775267502</v>
+        <v>10.01241357945108</v>
       </c>
       <c r="M38" s="18" t="n">
-        <v>10.72026895019886</v>
+        <v>8.696192783170265</v>
       </c>
       <c r="N38" s="18" t="n">
-        <v>9.183923609381516</v>
+        <v>7.656767099309381</v>
       </c>
       <c r="O38" s="18" t="n">
-        <v>4.412354520837747</v>
+        <v>5.726206497956432</v>
       </c>
     </row>
     <row r="39" ht="15.5" customHeight="1">
@@ -8646,40 +8646,40 @@
         </is>
       </c>
       <c r="D39" s="18" t="n">
-        <v>1681.40364114751</v>
+        <v>61.73874686359344</v>
       </c>
       <c r="E39" s="18" t="n">
-        <v>3230.865665090723</v>
+        <v>70.73424074138805</v>
       </c>
       <c r="F39" s="18" t="n">
-        <v>4237.59270910831</v>
+        <v>82.25672349321844</v>
       </c>
       <c r="G39" s="18" t="n">
-        <v>5235.653758356413</v>
+        <v>93.56662249130052</v>
       </c>
       <c r="H39" s="18" t="n">
-        <v>5756.555005264783</v>
+        <v>100.7911593481996</v>
       </c>
       <c r="I39" s="18" t="n">
-        <v>6135.969947767318</v>
+        <v>106.1461431367754</v>
       </c>
       <c r="J39" s="18" t="n">
-        <v>6534.087973234487</v>
+        <v>109.7794720892455</v>
       </c>
       <c r="K39" s="18" t="n">
-        <v>6796.949638764649</v>
+        <v>111.5505862752358</v>
       </c>
       <c r="L39" s="18" t="n">
-        <v>7004.682975450452</v>
+        <v>131.7311139303455</v>
       </c>
       <c r="M39" s="18" t="n">
-        <v>7161.028685503751</v>
+        <v>132.2094485983205</v>
       </c>
       <c r="N39" s="18" t="n">
-        <v>7280.348172670159</v>
+        <v>132.5323402674179</v>
       </c>
       <c r="O39" s="18" t="n">
-        <v>6855.968209236677</v>
+        <v>126.3773583510325</v>
       </c>
     </row>
     <row r="40" ht="15.5" customHeight="1">
@@ -8858,40 +8858,40 @@
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>593.4334337728237</v>
+        <v>189.6037764802519</v>
       </c>
       <c r="E43" s="18" t="n">
-        <v>357.9261622486001</v>
+        <v>45.47592270485545</v>
       </c>
       <c r="F43" s="18" t="n">
-        <v>152.5698446313548</v>
+        <v>-69.41396708432237</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>-38.98411497315747</v>
+        <v>-171.4065774531201</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>-201.8719494622883</v>
+        <v>-245.6278719421649</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>-336.4051207317942</v>
+        <v>-292.3815585542421</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>-483.6785701052974</v>
+        <v>-342.8066855744802</v>
       </c>
       <c r="K43" s="18" t="n">
-        <v>-630.3719008622876</v>
+        <v>-383.7215848250727</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>-733.7614645366884</v>
+        <v>-487.1111484994735</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>-794.6211804146134</v>
+        <v>-547.9708643773985</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>-814.292462189889</v>
+        <v>-567.6421461526739</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>-807.3799197241356</v>
+        <v>-560.7296036869205</v>
       </c>
     </row>
     <row r="44" ht="15.5" customHeight="1">
@@ -8911,40 +8911,40 @@
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>570.7243378824128</v>
+        <v>166.8946805898409</v>
       </c>
       <c r="E44" s="18" t="n">
-        <v>331.67594854997</v>
+        <v>19.22570900622532</v>
       </c>
       <c r="F44" s="18" t="n">
-        <v>122.0142775080672</v>
+        <v>-99.96953420761004</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>-71.88707935671911</v>
+        <v>-204.3095418366817</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>-238.8859165855759</v>
+        <v>-282.6418390654526</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>-377.469794704397</v>
+        <v>-333.4462325268449</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>-528.7104605162563</v>
+        <v>-387.8385759854391</v>
       </c>
       <c r="K44" s="18" t="n">
-        <v>-680.3381501773561</v>
+        <v>-433.6878341401411</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>-788.408922070935</v>
+        <v>-541.7586060337201</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>-853.8059776748873</v>
+        <v>-607.1556616376724</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>-877.853667669341</v>
+        <v>-631.203351632126</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>-877.853667669341</v>
+        <v>-631.203351632126</v>
       </c>
     </row>
     <row r="45" ht="15.5" customHeight="1">
@@ -9070,40 +9070,40 @@
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>881.2964493885547</v>
+        <v>477.4667920959828</v>
       </c>
       <c r="E47" s="18" t="n">
-        <v>1000.514575524281</v>
+        <v>688.0643359805366</v>
       </c>
       <c r="F47" s="18" t="n">
-        <v>1134.962336544225</v>
+        <v>912.9785248285474</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>1268.435417744367</v>
+        <v>1136.012955264404</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>1415.950224605682</v>
+        <v>1372.194302125805</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>1577.336703226956</v>
+        <v>1621.360265404508</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>1751.664237898963</v>
+        <v>1892.53612242978</v>
       </c>
       <c r="K47" s="18" t="n">
-        <v>1951.008177967453</v>
+        <v>2197.658494004668</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>2177.231363358789</v>
+        <v>2423.881679396004</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>2429.725788004455</v>
+        <v>2676.37610404167</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>2707.310587893806</v>
+        <v>2953.960903931021</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>2871.215190787329</v>
+        <v>3117.865506824544</v>
       </c>
     </row>
     <row r="48" ht="15.5" customHeight="1">
@@ -9123,40 +9123,40 @@
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>872.7209647890562</v>
+        <v>468.8913074964843</v>
       </c>
       <c r="E48" s="18" t="n">
-        <v>990.7075499280814</v>
+        <v>678.2573103843367</v>
       </c>
       <c r="F48" s="18" t="n">
-        <v>1123.696309146964</v>
+        <v>901.7124974312873</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>1255.740897196422</v>
+        <v>1123.318434716459</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>1401.856799948148</v>
+        <v>1358.100877468271</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>1561.87314158312</v>
+        <v>1605.896703760672</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>1734.860128309922</v>
+        <v>1875.732012840739</v>
       </c>
       <c r="K48" s="18" t="n">
-        <v>1933.441328652384</v>
+        <v>2180.091644689599</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>2159.32752774235</v>
+        <v>2405.977843779565</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>2411.494829100345</v>
+        <v>2658.14514513756</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>2688.760544038916</v>
+        <v>2935.41086007613</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>2852.354642842124</v>
+        <v>3099.004958879338</v>
       </c>
     </row>
     <row r="49" ht="15.5" customHeight="1">
@@ -9176,40 +9176,40 @@
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>765.2879636231141</v>
+        <v>289.1252227600941</v>
       </c>
       <c r="E49" s="18" t="n">
-        <v>765.2879636231141</v>
+        <v>289.1252227600941</v>
       </c>
       <c r="F49" s="18" t="n">
-        <v>765.2879636231141</v>
+        <v>289.1252227600941</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>765.2879636231141</v>
+        <v>289.1252227600941</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>765.2879636231141</v>
+        <v>289.1252227600941</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>765.2879636231141</v>
+        <v>289.1252227600941</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>765.2879636231141</v>
+        <v>289.1252227600941</v>
       </c>
       <c r="K49" s="18" t="n">
-        <v>765.2879636231141</v>
+        <v>289.1252227600941</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>765.2879636231141</v>
+        <v>289.1252227600941</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>765.2879636231141</v>
+        <v>289.1252227600941</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>765.2879636231141</v>
+        <v>289.1252227600941</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>765.2879636231141</v>
+        <v>289.1252227600941</v>
       </c>
     </row>
     <row r="50" ht="15.5" customHeight="1">
@@ -9229,28 +9229,28 @@
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>107.433001165942</v>
+        <v>179.7660847363902</v>
       </c>
       <c r="E50" s="18" t="n">
-        <v>117.9865851390252</v>
+        <v>209.3660028878524</v>
       </c>
       <c r="F50" s="18" t="n">
-        <v>132.988759218883</v>
+        <v>223.4551870469505</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>132.0445880494574</v>
+        <v>221.605937285172</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>146.1159027517261</v>
+        <v>234.782442751812</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>160.0163416349722</v>
+        <v>247.7958262924009</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>172.9869867268017</v>
+        <v>269.8353090800668</v>
       </c>
       <c r="K50" s="18" t="n">
-        <v>198.5812003424621</v>
+        <v>304.35963184886</v>
       </c>
       <c r="L50" s="18" t="n">
         <v>225.886199089966</v>
@@ -9262,7 +9262,7 @@
         <v>277.2657149385706</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>163.5940988032079</v>
+        <v>163.5940988032078</v>
       </c>
     </row>
     <row r="51" ht="15.5" customHeight="1">
@@ -9285,37 +9285,37 @@
         <v>0</v>
       </c>
       <c r="E51" s="18" t="n">
-        <v>107.433001165942</v>
+        <v>179.7660847363902</v>
       </c>
       <c r="F51" s="18" t="n">
-        <v>225.4195863049673</v>
+        <v>389.1320876242427</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>358.4083455238502</v>
+        <v>612.5872746711932</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>490.4529335733076</v>
+        <v>834.1932119563652</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>636.5688363250338</v>
+        <v>1068.975654708177</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>796.5851779600059</v>
+        <v>1316.771481000578</v>
       </c>
       <c r="K51" s="18" t="n">
-        <v>969.5721646868076</v>
+        <v>1586.606790080645</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>1168.15336502927</v>
+        <v>1890.966421929505</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>1394.039564119236</v>
+        <v>2116.852621019471</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>1646.206865477231</v>
+        <v>2369.019922377466</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>1923.472580415802</v>
+        <v>2646.285637316036</v>
       </c>
     </row>
     <row r="52" ht="15.5" customHeight="1">
@@ -9335,40 +9335,40 @@
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-72.33308357044821</v>
       </c>
       <c r="E52" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-163.7125013192754</v>
       </c>
       <c r="F52" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-254.1789291473429</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-343.7402783830574</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-432.4068183831433</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-520.1863030405722</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-617.0346253938372</v>
       </c>
       <c r="K52" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
     </row>
     <row r="53" ht="15.5" customHeight="1">
@@ -9388,40 +9388,40 @@
         </is>
       </c>
       <c r="D53" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-72.33308357044821</v>
       </c>
       <c r="E53" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-163.7125013192754</v>
       </c>
       <c r="F53" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-254.1789291473429</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-343.7402783830574</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-432.4068183831433</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-520.1863030405722</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-617.0346253938372</v>
       </c>
       <c r="K53" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
     </row>
     <row r="54" ht="15.5" customHeight="1">
@@ -9653,40 +9653,40 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>2794.51635844634</v>
+        <v>405.1337085255346</v>
       </c>
       <c r="E58" s="18" t="n">
-        <v>2913.734484582067</v>
+        <v>524.3518346612613</v>
       </c>
       <c r="F58" s="18" t="n">
-        <v>3048.18224560201</v>
+        <v>658.7995956812046</v>
       </c>
       <c r="G58" s="18" t="n">
-        <v>3181.655326802153</v>
+        <v>792.272676881347</v>
       </c>
       <c r="H58" s="18" t="n">
-        <v>3329.170133663468</v>
+        <v>939.7874837426623</v>
       </c>
       <c r="I58" s="18" t="n">
-        <v>3490.556612284741</v>
+        <v>1101.173962363936</v>
       </c>
       <c r="J58" s="18" t="n">
-        <v>3664.884146956749</v>
+        <v>1275.501497035943</v>
       </c>
       <c r="K58" s="18" t="n">
-        <v>3864.228087025238</v>
+        <v>1474.845437104432</v>
       </c>
       <c r="L58" s="18" t="n">
-        <v>4090.451272416574</v>
+        <v>1701.068622495768</v>
       </c>
       <c r="M58" s="18" t="n">
-        <v>4342.94569706224</v>
+        <v>1953.563047141434</v>
       </c>
       <c r="N58" s="18" t="n">
-        <v>4620.530496951592</v>
+        <v>2231.147847030785</v>
       </c>
       <c r="O58" s="18" t="n">
-        <v>4784.435099845115</v>
+        <v>2395.052449924308</v>
       </c>
     </row>
     <row r="59" ht="15.5" customHeight="1">
@@ -9706,40 +9706,40 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>-1913.219909057786</v>
+        <v>72.33308357044814</v>
       </c>
       <c r="E59" s="18" t="n">
-        <v>-1913.219909057786</v>
+        <v>163.7125013192754</v>
       </c>
       <c r="F59" s="18" t="n">
-        <v>-1913.219909057786</v>
+        <v>254.1789291473428</v>
       </c>
       <c r="G59" s="18" t="n">
-        <v>-1913.219909057786</v>
+        <v>343.7402783830573</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>-1913.219909057786</v>
+        <v>432.406818383143</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>-1913.219909057786</v>
+        <v>520.1863030405718</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>-1913.219909057786</v>
+        <v>617.0346253938374</v>
       </c>
       <c r="K59" s="18" t="n">
-        <v>-1913.219909057785</v>
+        <v>722.8130569002353</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>-1913.219909057786</v>
+        <v>722.8130569002356</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>-1913.219909057786</v>
+        <v>722.8130569002356</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>-1913.219909057786</v>
+        <v>722.813056900236</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>-1913.219909057786</v>
+        <v>722.8130569002356</v>
       </c>
     </row>
     <row r="60" ht="15.5" customHeight="1">
@@ -9812,7 +9812,7 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>158.1442373727678</v>
+        <v>158.1442373727677</v>
       </c>
       <c r="E61" s="18" t="n">
         <v>184.0899085795669</v>
@@ -9821,13 +9821,13 @@
         <v>216.1014300000001</v>
       </c>
       <c r="G61" s="18" t="n">
-        <v>225.85343</v>
+        <v>225.8534300000001</v>
       </c>
       <c r="H61" s="18" t="n">
         <v>256.34977</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>286.49919</v>
+        <v>286.4991899999999</v>
       </c>
       <c r="J61" s="18" t="n">
         <v>316.0436</v>
@@ -9868,22 +9868,22 @@
         <v>-41.7795004534219</v>
       </c>
       <c r="E62" s="18" t="n">
-        <v>-45.8836719985098</v>
+        <v>-45.88367199850979</v>
       </c>
       <c r="F62" s="18" t="n">
-        <v>-51.71785080734337</v>
+        <v>-51.71785080734338</v>
       </c>
       <c r="G62" s="18" t="n">
-        <v>-51.35067313034455</v>
+        <v>-51.35067313034456</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>-56.82285107011572</v>
+        <v>-56.8228510701157</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>-62.22857730248916</v>
+        <v>-62.22857730248915</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>-67.27271706042288</v>
+        <v>-67.27271706042286</v>
       </c>
       <c r="K62" s="18" t="n">
         <v>-77.22602235540194</v>
@@ -9971,7 +9971,7 @@
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>102.2311256284335</v>
+        <v>102.2311256284334</v>
       </c>
       <c r="E64" s="18" t="n">
         <v>135.8966597695394</v>
@@ -9980,16 +9980,16 @@
         <v>161.5372275690594</v>
       </c>
       <c r="G64" s="18" t="n">
-        <v>173.5838527600664</v>
+        <v>173.5838527600665</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>196.8148202997473</v>
+        <v>196.8148202997474</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>221.5900428344972</v>
+        <v>221.5900428344971</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>246.1442144464265</v>
+        <v>246.1442144464264</v>
       </c>
       <c r="K64" s="18" t="n">
         <v>282.3989234665158</v>
@@ -10001,7 +10001,7 @@
         <v>359.9923369224236</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>397.0865206876585</v>
+        <v>397.0865206876586</v>
       </c>
       <c r="O64" s="18" t="n">
         <v>451.6555155919479</v>
@@ -10139,16 +10139,16 @@
         <v>-209.6616710419028</v>
       </c>
       <c r="G67" s="18" t="n">
-        <v>-193.9013568647863</v>
+        <v>-193.9013568647862</v>
       </c>
       <c r="H67" s="18" t="n">
         <v>-166.9988372288568</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>-138.583878118821</v>
+        <v>-138.5838781188211</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-151.2406658118593</v>
+        <v>-151.2406658118594</v>
       </c>
       <c r="K67" s="18" t="n">
         <v>-151.6276896610999</v>
@@ -10160,7 +10160,7 @@
         <v>-65.39705560395237</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>-24.04768999445366</v>
+        <v>-24.04768999445361</v>
       </c>
       <c r="O67" s="18" t="n">
         <v>162.5440852806563</v>
@@ -10342,28 +10342,28 @@
         </is>
       </c>
       <c r="D71" s="19" t="n">
-        <v>0</v>
+        <v>72.33308357044821</v>
       </c>
       <c r="E71" s="19" t="n">
-        <v>0</v>
+        <v>91.37941774882724</v>
       </c>
       <c r="F71" s="19" t="n">
-        <v>0</v>
+        <v>90.46642782806747</v>
       </c>
       <c r="G71" s="19" t="n">
-        <v>0</v>
+        <v>89.56134923571453</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>0</v>
+        <v>88.66654000008592</v>
       </c>
       <c r="I71" s="19" t="n">
-        <v>0</v>
+        <v>87.77948465742882</v>
       </c>
       <c r="J71" s="19" t="n">
-        <v>0</v>
+        <v>96.84832235326512</v>
       </c>
       <c r="K71" s="19" t="n">
-        <v>0</v>
+        <v>105.7784315063979</v>
       </c>
       <c r="L71" s="19" t="n">
         <v>0</v>
@@ -10448,7 +10448,7 @@
         </is>
       </c>
       <c r="D73" s="19" t="n">
-        <v>765.2879636231141</v>
+        <v>289.1252227600941</v>
       </c>
       <c r="E73" s="19" t="n">
         <v>0</v>
@@ -10501,28 +10501,28 @@
         </is>
       </c>
       <c r="D74" s="18" t="n">
-        <v>765.2879636231141</v>
+        <v>361.4583063305423</v>
       </c>
       <c r="E74" s="18" t="n">
-        <v>0</v>
+        <v>91.37941774882724</v>
       </c>
       <c r="F74" s="18" t="n">
-        <v>0</v>
+        <v>90.46642782806747</v>
       </c>
       <c r="G74" s="18" t="n">
-        <v>0</v>
+        <v>89.56134923571453</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>0</v>
+        <v>88.66654000008592</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>0</v>
+        <v>87.77948465742882</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>0</v>
+        <v>96.84832235326512</v>
       </c>
       <c r="K74" s="18" t="n">
-        <v>0</v>
+        <v>105.7784315063979</v>
       </c>
       <c r="L74" s="18" t="n">
         <v>0</v>
@@ -10554,28 +10554,28 @@
         </is>
       </c>
       <c r="D75" s="18" t="n">
-        <v>570.7243378824128</v>
+        <v>166.8946805898409</v>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-239.0483893324428</v>
+        <v>-147.6689715836156</v>
       </c>
       <c r="F75" s="18" t="n">
-        <v>-209.6616710419028</v>
+        <v>-119.1952432138354</v>
       </c>
       <c r="G75" s="18" t="n">
-        <v>-193.9013568647863</v>
+        <v>-104.3400076290717</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>-166.9988372288568</v>
+        <v>-78.33229722877087</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>-138.583878118821</v>
+        <v>-50.80439346139228</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>-151.2406658118593</v>
+        <v>-54.39234345859425</v>
       </c>
       <c r="K75" s="18" t="n">
-        <v>-151.6276896610999</v>
+        <v>-45.84925815470199</v>
       </c>
       <c r="L75" s="18" t="n">
         <v>-108.0707718935789</v>
@@ -10584,7 +10584,7 @@
         <v>-65.39705560395237</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>-24.04768999445366</v>
+        <v>-24.04768999445361</v>
       </c>
       <c r="O75" s="18" t="n">
         <v>0</v>
@@ -10610,37 +10610,37 @@
         <v>0</v>
       </c>
       <c r="E76" s="18" t="n">
-        <v>570.7243378824128</v>
+        <v>166.8946805898409</v>
       </c>
       <c r="F76" s="18" t="n">
-        <v>331.67594854997</v>
+        <v>19.22570900622532</v>
       </c>
       <c r="G76" s="18" t="n">
-        <v>122.0142775080672</v>
+        <v>-99.96953420761004</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>-71.88707935671911</v>
+        <v>-204.3095418366817</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>-238.8859165855759</v>
+        <v>-282.6418390654526</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>-377.469794704397</v>
+        <v>-333.4462325268449</v>
       </c>
       <c r="K76" s="18" t="n">
-        <v>-528.7104605162563</v>
+        <v>-387.8385759854391</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>-680.3381501773561</v>
+        <v>-433.6878341401411</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>-788.408922070935</v>
+        <v>-541.7586060337201</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>-853.8059776748873</v>
+        <v>-607.1556616376724</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>-877.853667669341</v>
+        <v>-631.203351632126</v>
       </c>
     </row>
     <row r="77" ht="15.5" customHeight="1">
@@ -10660,28 +10660,28 @@
         </is>
       </c>
       <c r="D77" s="18" t="n">
-        <v>570.7243378824128</v>
+        <v>166.8946805898409</v>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-239.0483893324428</v>
+        <v>-147.6689715836156</v>
       </c>
       <c r="F77" s="18" t="n">
-        <v>-209.6616710419028</v>
+        <v>-119.1952432138354</v>
       </c>
       <c r="G77" s="18" t="n">
-        <v>-193.9013568647863</v>
+        <v>-104.3400076290717</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>-166.9988372288568</v>
+        <v>-78.33229722877087</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>-138.583878118821</v>
+        <v>-50.80439346139228</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>-151.2406658118593</v>
+        <v>-54.39234345859425</v>
       </c>
       <c r="K77" s="18" t="n">
-        <v>-151.6276896610999</v>
+        <v>-45.84925815470199</v>
       </c>
       <c r="L77" s="18" t="n">
         <v>-108.0707718935789</v>
@@ -10690,7 +10690,7 @@
         <v>-65.39705560395237</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>-24.04768999445366</v>
+        <v>-24.04768999445361</v>
       </c>
       <c r="O77" s="18" t="n">
         <v>0</v>
@@ -10713,40 +10713,40 @@
         </is>
       </c>
       <c r="D78" s="18" t="n">
-        <v>570.7243378824128</v>
+        <v>166.8946805898409</v>
       </c>
       <c r="E78" s="18" t="n">
-        <v>331.67594854997</v>
+        <v>19.22570900622532</v>
       </c>
       <c r="F78" s="18" t="n">
-        <v>122.0142775080672</v>
+        <v>-99.96953420761004</v>
       </c>
       <c r="G78" s="18" t="n">
-        <v>-71.88707935671911</v>
+        <v>-204.3095418366817</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>-238.8859165855759</v>
+        <v>-282.6418390654526</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>-377.469794704397</v>
+        <v>-333.4462325268449</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>-528.7104605162563</v>
+        <v>-387.8385759854391</v>
       </c>
       <c r="K78" s="18" t="n">
-        <v>-680.3381501773561</v>
+        <v>-433.6878341401411</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>-788.408922070935</v>
+        <v>-541.7586060337201</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>-853.8059776748873</v>
+        <v>-607.1556616376724</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>-877.853667669341</v>
+        <v>-631.203351632126</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>-877.853667669341</v>
+        <v>-631.203351632126</v>
       </c>
     </row>
     <row r="79" ht="15.5" customHeight="1">
@@ -10872,28 +10872,28 @@
         </is>
       </c>
       <c r="D81" s="18" t="n">
-        <v>107.4199046555969</v>
+        <v>85.13244247392517</v>
       </c>
       <c r="E81" s="18" t="n">
-        <v>117.3986682541237</v>
+        <v>91.28147125930698</v>
       </c>
       <c r="F81" s="18" t="n">
-        <v>99.84923006949178</v>
+        <v>80.30682758580851</v>
       </c>
       <c r="G81" s="18" t="n">
-        <v>91.79800170185423</v>
+        <v>75.01523793253423</v>
       </c>
       <c r="H81" s="18" t="n">
-        <v>80.78705073684975</v>
+        <v>67.49750243171981</v>
       </c>
       <c r="I81" s="18" t="n">
-        <v>72.08954340783623</v>
+        <v>61.31666910297567</v>
       </c>
       <c r="J81" s="18" t="n">
-        <v>72.5303128117947</v>
+        <v>61.63525560462374</v>
       </c>
       <c r="K81" s="18" t="n">
-        <v>71.39503313951192</v>
+        <v>60.81349656984884</v>
       </c>
       <c r="L81" s="18" t="n">
         <v>64.62626748876401</v>
@@ -11037,7 +11037,7 @@
         <v>20.21965144203191</v>
       </c>
       <c r="F84" s="18" t="n">
-        <v>31.3948199737737</v>
+        <v>31.39481997377369</v>
       </c>
       <c r="G84" s="18" t="n">
         <v>42.45816882019806</v>
@@ -11694,37 +11694,37 @@
         <v>0</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>872.7209647890562</v>
+        <v>468.8913074964843</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>990.7075499280814</v>
+        <v>678.2573103843367</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>1123.696309146964</v>
+        <v>901.7124974312871</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>1255.740897196422</v>
+        <v>1123.318434716459</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>1401.856799948148</v>
+        <v>1358.100877468271</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>1561.87314158312</v>
+        <v>1605.896703760672</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>1734.860128309922</v>
+        <v>1875.732012840739</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>1933.441328652384</v>
+        <v>2180.091644689599</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>2159.32752774235</v>
+        <v>2405.977843779565</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>2411.494829100345</v>
+        <v>2658.14514513756</v>
       </c>
       <c r="O96" s="20" t="n">
-        <v>2688.760544038915</v>
+        <v>2935.41086007613</v>
       </c>
     </row>
     <row r="97" ht="15.5" customHeight="1">
@@ -11744,7 +11744,7 @@
         </is>
       </c>
       <c r="D97" s="19" t="n">
-        <v>765.2879636231141</v>
+        <v>289.1252227600941</v>
       </c>
       <c r="E97" s="19" t="n">
         <v>0</v>
@@ -11797,28 +11797,28 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>107.433001165942</v>
+        <v>179.7660847363902</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>117.9865851390252</v>
+        <v>209.3660028878524</v>
       </c>
       <c r="F98" s="21" t="n">
-        <v>132.988759218883</v>
+        <v>223.4551870469505</v>
       </c>
       <c r="G98" s="21" t="n">
-        <v>132.0445880494574</v>
+        <v>221.605937285172</v>
       </c>
       <c r="H98" s="21" t="n">
-        <v>146.1159027517261</v>
+        <v>234.782442751812</v>
       </c>
       <c r="I98" s="21" t="n">
-        <v>160.0163416349722</v>
+        <v>247.7958262924009</v>
       </c>
       <c r="J98" s="21" t="n">
-        <v>172.9869867268017</v>
+        <v>269.8353090800668</v>
       </c>
       <c r="K98" s="21" t="n">
-        <v>198.5812003424621</v>
+        <v>304.35963184886</v>
       </c>
       <c r="L98" s="21" t="n">
         <v>225.886199089966</v>
@@ -11830,7 +11830,7 @@
         <v>277.2657149385706</v>
       </c>
       <c r="O98" s="21" t="n">
-        <v>326.1381840838642</v>
+        <v>326.1381840838641</v>
       </c>
     </row>
     <row r="99" ht="15.5" customHeight="1">
@@ -11903,40 +11903,40 @@
         </is>
       </c>
       <c r="D100" s="20" t="n">
-        <v>872.7209647890562</v>
+        <v>468.8913074964843</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>990.7075499280814</v>
+        <v>678.2573103843367</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>1123.696309146964</v>
+        <v>901.7124974312871</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>1255.740897196422</v>
+        <v>1123.318434716459</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>1401.856799948148</v>
+        <v>1358.100877468271</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>1561.87314158312</v>
+        <v>1605.896703760672</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>1734.860128309922</v>
+        <v>1875.732012840739</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>1933.441328652384</v>
+        <v>2180.091644689599</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>2159.32752774235</v>
+        <v>2405.977843779565</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>2411.494829100345</v>
+        <v>2658.14514513756</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>2688.760544038915</v>
+        <v>2935.41086007613</v>
       </c>
       <c r="O100" s="20" t="n">
-        <v>2852.354642842123</v>
+        <v>3099.004958879338</v>
       </c>
     </row>
     <row r="101" ht="15.5" customHeight="1">
@@ -12009,28 +12009,28 @@
         </is>
       </c>
       <c r="D102" s="18" t="n">
-        <v>0</v>
+        <v>-24.37141601621008</v>
       </c>
       <c r="E102" s="18" t="n">
-        <v>0</v>
+        <v>-24.37141601621008</v>
       </c>
       <c r="F102" s="18" t="n">
-        <v>0</v>
+        <v>-24.37141601621008</v>
       </c>
       <c r="G102" s="18" t="n">
-        <v>0</v>
+        <v>-24.37141601621008</v>
       </c>
       <c r="H102" s="18" t="n">
-        <v>0</v>
+        <v>-24.37141601621008</v>
       </c>
       <c r="I102" s="18" t="n">
-        <v>0</v>
+        <v>-24.37141601621008</v>
       </c>
       <c r="J102" s="18" t="n">
-        <v>0</v>
+        <v>-24.37141601621008</v>
       </c>
       <c r="K102" s="18" t="n">
-        <v>0</v>
+        <v>-24.37141601621008</v>
       </c>
       <c r="L102" s="18" t="n">
         <v>0</v>
@@ -12065,37 +12065,37 @@
         <v>0</v>
       </c>
       <c r="E103" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-72.33308357044821</v>
       </c>
       <c r="F103" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-163.7125013192754</v>
       </c>
       <c r="G103" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-254.1789291473429</v>
       </c>
       <c r="H103" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-343.7402783830574</v>
       </c>
       <c r="I103" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-432.4068183831433</v>
       </c>
       <c r="J103" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-520.1863030405722</v>
       </c>
       <c r="K103" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-617.0346253938372</v>
       </c>
       <c r="L103" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
       <c r="M103" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
       <c r="N103" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
       <c r="O103" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
     </row>
     <row r="104" ht="15.5" customHeight="1">
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="D104" s="19" t="n">
-        <v>1913.219909057786</v>
+        <v>0</v>
       </c>
       <c r="E104" s="19" t="n">
         <v>0</v>
@@ -12168,28 +12168,28 @@
         </is>
       </c>
       <c r="D105" s="18" t="n">
-        <v>0</v>
+        <v>-72.33308357044821</v>
       </c>
       <c r="E105" s="18" t="n">
-        <v>0</v>
+        <v>-91.37941774882724</v>
       </c>
       <c r="F105" s="18" t="n">
-        <v>0</v>
+        <v>-90.46642782806747</v>
       </c>
       <c r="G105" s="18" t="n">
-        <v>0</v>
+        <v>-89.56134923571453</v>
       </c>
       <c r="H105" s="18" t="n">
-        <v>0</v>
+        <v>-88.66654000008592</v>
       </c>
       <c r="I105" s="18" t="n">
-        <v>0</v>
+        <v>-87.77948465742882</v>
       </c>
       <c r="J105" s="18" t="n">
-        <v>0</v>
+        <v>-96.84832235326512</v>
       </c>
       <c r="K105" s="18" t="n">
-        <v>0</v>
+        <v>-105.7784315063979</v>
       </c>
       <c r="L105" s="18" t="n">
         <v>0</v>
@@ -12274,40 +12274,40 @@
         </is>
       </c>
       <c r="D107" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-72.33308357044821</v>
       </c>
       <c r="E107" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-163.7125013192754</v>
       </c>
       <c r="F107" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-254.1789291473429</v>
       </c>
       <c r="G107" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-343.7402783830574</v>
       </c>
       <c r="H107" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-432.4068183831433</v>
       </c>
       <c r="I107" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-520.1863030405722</v>
       </c>
       <c r="J107" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-617.0346253938372</v>
       </c>
       <c r="K107" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
       <c r="L107" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
       <c r="M107" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
       <c r="N107" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
       <c r="O107" s="18" t="n">
-        <v>1913.219909057786</v>
+        <v>-722.8130569002351</v>
       </c>
     </row>
     <row r="108" ht="15.5" customHeight="1">
@@ -12716,10 +12716,10 @@
         </is>
       </c>
       <c r="D2" s="18" t="n">
-        <v>24.15496192</v>
+        <v>26.49959567197683</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>26.1288736</v>
+        <v>30.30816579490387</v>
       </c>
       <c r="F2" s="18" t="n">
         <v>35.09181288000001</v>
@@ -12772,10 +12772,10 @@
         <v>0</v>
       </c>
       <c r="E3" s="18" t="n">
-        <v>8.171868316487085</v>
+        <v>14.37218201391122</v>
       </c>
       <c r="F3" s="18" t="n">
-        <v>34.30281541107079</v>
+        <v>15.78336055526155</v>
       </c>
       <c r="G3" s="18" t="n">
         <v>38.30754810522059</v>
@@ -12928,10 +12928,10 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>0</v>
+        <v>2.344633751976825</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>0</v>
+        <v>4.179292194903873</v>
       </c>
       <c r="F6" s="18" t="n">
         <v>0</v>
@@ -12984,10 +12984,10 @@
         <v>0</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>0</v>
+        <v>78.2492549798107</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>0</v>
@@ -13034,10 +13034,10 @@
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>0</v>
+        <v>8.847809532642273</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>0</v>
+  